--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 22-Apr-2026 08:07 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 23-Apr-2026 03:12 PM</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>22-Apr-2026 08:07 PM</t>
+          <t>23-Apr-2026 03:12 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  22-Apr-2026 08:07 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  23-Apr-2026 03:12 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>451.2</v>
+        <v>470.4</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v/>
+        <v>468</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v/>
+        <v>480.2</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v/>
+        <v>463.6</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v/>
+        <v>465.9</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v/>
+        <v>-4.5</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v/>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7255</v>
+        <v>7587</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v/>
+        <v>7587</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v/>
+        <v>7650</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v/>
+        <v>7533.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v/>
+        <v>7575.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v/>
+        <v>-11.5</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v/>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25385</v>
+        <v>25420</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v/>
+        <v>25440</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v/>
+        <v>25675</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v/>
+        <v>25350</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v/>
+        <v>25410</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v/>
+        <v>-10</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v/>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>344.6</v>
+        <v>350.7</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v/>
+        <v>348.25</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v/>
+        <v>354.35</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v/>
+        <v>346.95</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v/>
+        <v>349.75</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v/>
+        <v>-0.95</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v/>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>64.45</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v/>
+        <v>64.25</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v/>
+        <v>65.27</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v/>
+        <v>63</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v/>
+        <v>63.2</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v/>
+        <v>-1.79</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v/>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1438</v>
+        <v>1446.4</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v/>
+        <v>1439</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v/>
+        <v>1439.7</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v/>
+        <v>1420</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v/>
+        <v>1423.1</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v/>
+        <v>-23.3</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v/>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2226</v>
+        <v>2260.8</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v/>
+        <v>2243.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v/>
+        <v>2333.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v/>
+        <v>2221.8</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v/>
+        <v>2300</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v/>
+        <v>39.2</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1594.1</v>
+        <v>1588.6</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v/>
+        <v>1575</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v/>
+        <v>1611</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v/>
+        <v>1566.2</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v/>
+        <v>1602.9</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v/>
+        <v>14.3</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5696.5</v>
+        <v>5627</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v/>
+        <v>5545.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v/>
+        <v>5579.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v/>
+        <v>5432.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v/>
+        <v>5520.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v/>
+        <v>-106.5</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v/>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>456.25</v>
+        <v>460.9</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v/>
+        <v>457.95</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v/>
+        <v>457.95</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v/>
+        <v>449</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v/>
+        <v>450.4</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v/>
+        <v>-10.5</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v/>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>324.05</v>
+        <v>328.59</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v/>
+        <v>328</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v/>
+        <v>328</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v/>
+        <v>320.31</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v/>
+        <v>321.21</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v/>
+        <v>-7.38</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v/>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2106.6</v>
+        <v>2121.9</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v/>
+        <v>2121.1</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v/>
+        <v>2121.1</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v/>
+        <v>2017</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v/>
+        <v>2022.9</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v/>
+        <v>-99</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v/>
+        <v>-4.67</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7744</v>
+        <v>7662</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v/>
+        <v>7685</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v/>
+        <v>7815</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v/>
+        <v>7601</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v/>
+        <v>7781</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v/>
+        <v>119</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>441.95</v>
+        <v>434</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v/>
+        <v>432</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v/>
+        <v>437.45</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v/>
+        <v>431.2</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v/>
+        <v>432.45</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v/>
+        <v>-1.55</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v/>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>176.61</v>
+        <v>178.97</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v/>
+        <v>177</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v/>
+        <v>177.79</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v/>
+        <v>169.25</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v/>
+        <v>170.63</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v/>
+        <v>-8.34</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v/>
+        <v>-4.66</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2543.6</v>
+        <v>2562.9</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v/>
+        <v>2530</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v/>
+        <v>2541.7</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v/>
+        <v>2510</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v/>
+        <v>2521.4</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v/>
+        <v>-41.5</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v/>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1582.5</v>
+        <v>1589.6</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v/>
+        <v>1585</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v/>
+        <v>1594.5</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v/>
+        <v>1562.8</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v/>
+        <v>1574.9</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v/>
+        <v>-14.7</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v/>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>614.65</v>
+        <v>629.1</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v/>
+        <v>629</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v/>
+        <v>638</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v/>
+        <v>620.1</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v/>
+        <v>621.7</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v/>
+        <v>-7.4</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v/>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6557</v>
+        <v>6666.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v/>
+        <v>6670</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v/>
+        <v>6889</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v/>
+        <v>6575</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v/>
+        <v>6727</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v/>
+        <v>60.5</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1037.9</v>
+        <v>1043.2</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v/>
+        <v>1039.05</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v/>
+        <v>1059.2</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v/>
+        <v>1035.3</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v/>
+        <v>1056.25</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v/>
+        <v>13.05</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1391.7</v>
+        <v>1421.2</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v/>
+        <v>1420</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v/>
+        <v>1459.5</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v/>
+        <v>1409.1</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v/>
+        <v>1435.4</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v/>
+        <v>14.2</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1377.7</v>
+        <v>1379.6</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v/>
+        <v>1369</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v/>
+        <v>1384.2</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v/>
+        <v>1365.4</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v/>
+        <v>1369.6</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v/>
+        <v>-10</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v/>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>9793</v>
+        <v>9602</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v/>
+        <v>9575</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v/>
+        <v>9591</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v/>
+        <v>9477</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v/>
+        <v>9550.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v/>
+        <v>-51.5</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v/>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1851.4</v>
+        <v>1842.9</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v/>
+        <v>1821.5</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v/>
+        <v>1830</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v/>
+        <v>1786</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v/>
+        <v>1792.6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v/>
+        <v>-50.3</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v/>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>938.85</v>
+        <v>934.75</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v/>
+        <v>926.1</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v/>
+        <v>929.85</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v/>
+        <v>909.35</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v/>
+        <v>918.35</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v/>
+        <v>-16.4</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v/>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2304.1</v>
+        <v>2309.7</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v/>
+        <v>2300</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v/>
+        <v>2311.1</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v/>
+        <v>2256.2</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v/>
+        <v>2265.4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v/>
+        <v>-44.3</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v/>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>508.85</v>
+        <v>541.55</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v/>
+        <v>543.7</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v/>
+        <v>552.7</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v/>
+        <v>530.55</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v/>
+        <v>540.3</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v/>
+        <v>-1.25</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v/>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>176.13</v>
+        <v>176.52</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v/>
+        <v>173.73</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v/>
+        <v>174.68</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v/>
+        <v>171.1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v/>
+        <v>173.9</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v/>
+        <v>-2.62</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v/>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>284.05</v>
+        <v>282.77</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v/>
+        <v>281</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v/>
+        <v>281.49</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v/>
+        <v>274.05</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v/>
+        <v>276.34</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v/>
+        <v>-6.43</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v/>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>451.5</v>
+        <v>448.7</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v/>
+        <v>451.7</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v/>
+        <v>455.7</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v/>
+        <v>444.5</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v/>
+        <v>449.95</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v/>
+        <v>1.25</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>480.6</v>
+        <v>478.25</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v/>
+        <v>470.5</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v/>
+        <v>476.4</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v/>
+        <v>467</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v/>
+        <v>468.65</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v/>
+        <v>-9.6</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v/>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1855</v>
+        <v>1829</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v/>
+        <v>1821.8</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v/>
+        <v>1846</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v/>
+        <v>1812.1</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v/>
+        <v>1841.2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v/>
+        <v>12.2</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>332.61</v>
+        <v>333.64</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v/>
+        <v>333</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v/>
+        <v>341.25</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v/>
+        <v>330.65</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v/>
+        <v>337.6</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v/>
+        <v>3.96</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>361.5</v>
+        <v>357.8</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v/>
+        <v>357.45</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v/>
+        <v>364.8</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v/>
+        <v>355.6</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v/>
+        <v>358</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v/>
+        <v>0.2</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>38100</v>
+        <v>37885</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v/>
+        <v>37885</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v/>
+        <v>37905</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v/>
+        <v>37210</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v/>
+        <v>37380</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v/>
+        <v>-505</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v/>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>318.05</v>
+        <v>314.4</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v/>
+        <v>312</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v/>
+        <v>313.75</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v/>
+        <v>308.4</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v/>
+        <v>309.8</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v/>
+        <v>-4.6</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v/>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5837.5</v>
+        <v>5729.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v/>
+        <v>5724</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v/>
+        <v>5728</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v/>
+        <v>5640.5</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v/>
+        <v>5671.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v/>
+        <v>-58</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v/>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>394.4</v>
+        <v>387.85</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v/>
+        <v>387.5</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v/>
+        <v>388</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v/>
+        <v>380.05</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v/>
+        <v>385</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v/>
+        <v>-2.85</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v/>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>144.26</v>
+        <v>145.23</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v/>
+        <v>144.5</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v/>
+        <v>144.58</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v/>
+        <v>140.21</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v/>
+        <v>140.87</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v/>
+        <v>-4.36</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v/>
+        <v>-3</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>886.1</v>
+        <v>912.3</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v/>
+        <v>903</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v/>
+        <v>914.4</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v/>
+        <v>888</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v/>
+        <v>899.8</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v/>
+        <v>-12.5</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v/>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>451.4</v>
+        <v>452.3</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v/>
+        <v>452.5</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v/>
+        <v>455.4</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v/>
+        <v>446</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v/>
+        <v>446.95</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v/>
+        <v>-5.35</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v/>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1589.2</v>
+        <v>1565.6</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v/>
+        <v>1558</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v/>
+        <v>1560.8</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v/>
+        <v>1532.5</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v/>
+        <v>1543.4</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v/>
+        <v>-22.2</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v/>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1232.5</v>
+        <v>1236.3</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v/>
+        <v>1234.1</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v/>
+        <v>1308.4</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v/>
+        <v>1227.6</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v/>
+        <v>1305.9</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v/>
+        <v>69.59999999999999</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>5.63</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>443.15</v>
+        <v>444.15</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v/>
+        <v>444.25</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v/>
+        <v>451.5</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v/>
+        <v>442.65</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v/>
+        <v>450.65</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v/>
+        <v>6.5</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1292.8</v>
+        <v>1235.8</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v/>
+        <v>1237.5</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v/>
+        <v>1243.1</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v/>
+        <v>1215.8</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v/>
+        <v>1220.6</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v/>
+        <v>-15.2</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v/>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2106.6</v>
+        <v>2118.3</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v/>
+        <v>2110.3</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v/>
+        <v>2155</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v/>
+        <v>2057.6</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v/>
+        <v>2150.2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v/>
+        <v>31.9</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>504.2</v>
+        <v>515.7</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v/>
+        <v>516</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v/>
+        <v>516.9</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v/>
+        <v>502.3</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v/>
+        <v>505.05</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v/>
+        <v>-10.65</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v/>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2055.6</v>
+        <v>2034.5</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v/>
+        <v>2034.5</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v/>
+        <v>2058</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v/>
+        <v>2023</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v/>
+        <v>2039.8</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v/>
+        <v>5.3</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>258.65</v>
+        <v>261.37</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v/>
+        <v>261.01</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v/>
+        <v>261.01</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v/>
+        <v>250.21</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v/>
+        <v>253.39</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v/>
+        <v>-7.98</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v/>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>264.93</v>
+        <v>270.15</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v/>
+        <v>270.15</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v/>
+        <v>271.39</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v/>
+        <v>263.5</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v/>
+        <v>265.52</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v/>
+        <v>-4.63</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v/>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5116.4</v>
+        <v>5211.8</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v/>
+        <v>5200</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v/>
+        <v>5269</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v/>
+        <v>5155.7</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v/>
+        <v>5176.9</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v/>
+        <v>-34.9</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v/>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v/>
+        <v>458.9</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v/>
+        <v>461.3</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v/>
+        <v>452.7</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v/>
+        <v>460</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1990</v>
+        <v>1992.8</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v/>
+        <v>2004.4</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v/>
+        <v>2004.4</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v/>
+        <v>1944.7</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v/>
+        <v>1958.8</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v/>
+        <v>-34</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v/>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1644.8</v>
+        <v>1745.5</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v/>
+        <v>1739.5</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v/>
+        <v>1780</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v/>
+        <v>1708</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v/>
+        <v>1731.9</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v/>
+        <v>-13.6</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v/>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>61.68</v>
+        <v>68</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v/>
+        <v>66.5</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v/>
+        <v>81.59999999999999</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v/>
+        <v>81.59999999999999</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J57" s="10" t="n">
-        <v/>
+        <v>13.6</v>
+      </c>
+      <c r="J57" s="13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6286</v>
+        <v>6285.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v/>
+        <v>6265</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v/>
+        <v>6469.5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v/>
+        <v>6250.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v/>
+        <v>6378.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v/>
+        <v>93</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11265</v>
+        <v>11267</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v/>
+        <v>11249</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v/>
+        <v>11249</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v/>
+        <v>10820</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v/>
+        <v>10866.5</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v/>
+        <v>-400.5</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v/>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>607.55</v>
+        <v>610.65</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v/>
+        <v>604</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v/>
+        <v>605.25</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v/>
+        <v>591</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v/>
+        <v>592.8</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v/>
+        <v>-17.85</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v/>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1220.6</v>
+        <v>1217</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v/>
+        <v>1230</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v/>
+        <v>1357</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v/>
+        <v>1217.5</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v/>
+        <v>1331</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v/>
+        <v>114</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7240.5</v>
+        <v>7230</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v/>
+        <v>7195.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v/>
+        <v>7195.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v/>
+        <v>7062</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v/>
+        <v>7092.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v/>
+        <v>-137.5</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v/>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3359.9</v>
+        <v>3338.6</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v/>
+        <v>3320</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v/>
+        <v>3373.8</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v/>
+        <v>3275.1</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v/>
+        <v>3309</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v/>
+        <v>-29.6</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v/>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>333.1</v>
+        <v>354.55</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v/>
+        <v>353.8</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v/>
+        <v>359.85</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v/>
+        <v>345.05</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v/>
+        <v>347.25</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v/>
+        <v>-7.3</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v/>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>295.75</v>
+        <v>296.45</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v/>
+        <v>294.95</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v/>
+        <v>296.65</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v/>
+        <v>293.55</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v/>
+        <v>295.4</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v/>
+        <v>-1.05</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v/>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>160.77</v>
+        <v>166.12</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v/>
+        <v>166</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v/>
+        <v>167.89</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v/>
+        <v>164.02</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v/>
+        <v>164.96</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v/>
+        <v>-1.16</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v/>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2233.1</v>
+        <v>2240</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v/>
+        <v>2247.9</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v/>
+        <v>2359.4</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v/>
+        <v>2212.1</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v/>
+        <v>2335</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J67" s="10" t="n">
-        <v/>
+        <v>95</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>4.24</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>483.3</v>
+        <v>488.5</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v/>
+        <v>487.1</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v/>
+        <v>491</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v/>
+        <v>481.5</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v/>
+        <v>481.95</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v/>
+        <v>-6.55</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v/>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1125.05</v>
+        <v>1139.55</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v/>
+        <v>1139</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v/>
+        <v>1145.75</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v/>
+        <v>1120.3</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v/>
+        <v>1142.95</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J70" s="10" t="n">
-        <v/>
+        <v>3.4</v>
+      </c>
+      <c r="J70" s="13" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1805</v>
+        <v>1832.2</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v/>
+        <v>1829.1</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v/>
+        <v>1833.1</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v/>
+        <v>1780.4</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v/>
+        <v>1791</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v/>
+        <v>-41.2</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v/>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>667.75</v>
+        <v>672.75</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v/>
+        <v>674</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v/>
+        <v>696.4</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v/>
+        <v>670.3</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v/>
+        <v>686.95</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v/>
+        <v>14.2</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>2.11</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2777.7</v>
+        <v>2776.6</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v/>
+        <v>2762.3</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v/>
+        <v>2768.4</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v/>
+        <v>2727</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v/>
+        <v>2735</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v/>
+        <v>-41.6</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v/>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>374.25</v>
+        <v>382.85</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v/>
+        <v>382.8</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v/>
+        <v>387.9</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v/>
+        <v>378.75</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v/>
+        <v>386</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J74" s="10" t="n">
-        <v/>
+        <v>3.15</v>
+      </c>
+      <c r="J74" s="13" t="n">
+        <v>0.82</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4358.4</v>
+        <v>4400.6</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v/>
+        <v>4400.6</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v/>
+        <v>4402.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v/>
+        <v>4335</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v/>
+        <v>4352.5</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v/>
+        <v>-48.1</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v/>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1328.8</v>
+        <v>1348.7</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v/>
+        <v>1294.6</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v/>
+        <v>1299.9</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v/>
+        <v>1255.2</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v/>
+        <v>1260.3</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v/>
+        <v>-88.40000000000001</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v/>
+        <v>-6.55</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1441.2</v>
+        <v>1285.3</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v/>
+        <v>1290</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v/>
+        <v>1294.3</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v/>
+        <v>1272</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v/>
+        <v>1277.6</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v/>
+        <v>-7.7</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v/>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2794</v>
+        <v>2766.4</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v/>
+        <v>2745</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v/>
+        <v>2762.9</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v/>
+        <v>2700</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v/>
+        <v>2708.2</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v/>
+        <v>-58.2</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v/>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>811.75</v>
+        <v>799.9</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v/>
+        <v>792</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v/>
+        <v>796.65</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v/>
+        <v>782.5</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v/>
+        <v>784.35</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v/>
+        <v>-15.55</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v/>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>614.2</v>
+        <v>604.05</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v/>
+        <v>604.2</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v/>
+        <v>607.75</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v/>
+        <v>595.5</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v/>
+        <v>598.65</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v/>
+        <v>-5.4</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v/>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5259</v>
+        <v>5189</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v/>
+        <v>5150</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v/>
+        <v>5160</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v/>
+        <v>4995</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v/>
+        <v>5032</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v/>
+        <v>-157</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v/>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1021.65</v>
+        <v>1039.9</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v/>
+        <v>1039.75</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v/>
+        <v>1049</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v/>
+        <v>1031.15</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v/>
+        <v>1041.35</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J82" s="10" t="n">
-        <v/>
+        <v>1.45</v>
+      </c>
+      <c r="J82" s="13" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>551.85</v>
+        <v>556.95</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v/>
+        <v>556.45</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v/>
+        <v>560.8</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v/>
+        <v>548</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v/>
+        <v>549.45</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v/>
+        <v>-7.5</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v/>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>384.4</v>
+        <v>382.55</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v/>
+        <v>377.35</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v/>
+        <v>378.9</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v/>
+        <v>371.1</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v/>
+        <v>376.9</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v/>
+        <v>-5.65</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v/>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2310.7</v>
+        <v>2368.8</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v/>
+        <v>2336</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v/>
+        <v>2400</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v/>
+        <v>2336</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v/>
+        <v>2366.4</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v/>
+        <v>-2.4</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v/>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>32620</v>
+        <v>32705</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v/>
+        <v>32700</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v/>
+        <v>32850</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v/>
+        <v>32400</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v/>
+        <v>32650</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v/>
+        <v>-55</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v/>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>67.94</v>
+        <v>68.38</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v/>
+        <v>67.5</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v/>
+        <v>68.45</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v/>
+        <v>67.45999999999999</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v/>
+        <v>67.83</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v/>
+        <v>-0.55</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v/>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>126.06</v>
+        <v>125.78</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v/>
+        <v>125.8</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v/>
+        <v>128.05</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v/>
+        <v>125.05</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v/>
+        <v>126.92</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v/>
+        <v>1.14</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>167.2</v>
+        <v>169.08</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v/>
+        <v>172</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v/>
+        <v>173.29</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v/>
+        <v>165</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v/>
+        <v>165.55</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v/>
+        <v>-3.53</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v/>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>666.15</v>
+        <v>659.7</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v/>
+        <v>657</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v/>
+        <v>657</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v/>
+        <v>636</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v/>
+        <v>639.45</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v/>
+        <v>-20.25</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v/>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2167</v>
+        <v>2168.4</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v/>
+        <v>2168.4</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v/>
+        <v>2190</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v/>
+        <v>2148.4</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v/>
+        <v>2159.4</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v/>
+        <v>-9</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v/>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4693.1</v>
+        <v>4640.9</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v/>
+        <v>4549.7</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v/>
+        <v>4589</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v/>
+        <v>4510</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v/>
+        <v>4556</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v/>
+        <v>-84.90000000000001</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v/>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>856.4</v>
+        <v>870.1</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v/>
+        <v>861.7</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v/>
+        <v>869.7</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v/>
+        <v>854.15</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v/>
+        <v>860.35</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v/>
+        <v>-9.75</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v/>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>414.75</v>
+        <v>408.15</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v/>
+        <v>405.15</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v/>
+        <v>408.3</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v/>
+        <v>400.95</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v/>
+        <v>404.7</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v/>
+        <v>-3.45</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v/>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1313.2</v>
+        <v>1268.6</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v/>
+        <v>1254</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v/>
+        <v>1265.7</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v/>
+        <v>1226</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v/>
+        <v>1240.6</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v/>
+        <v>-28</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v/>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>147.31</v>
+        <v>147.36</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v/>
+        <v>146.4</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v/>
+        <v>147.35</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v/>
+        <v>145.1</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v/>
+        <v>145.48</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v/>
+        <v>-1.88</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v/>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1476.5</v>
+        <v>1494.8</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v/>
+        <v>1494.6</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v/>
+        <v>1541.1</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v/>
+        <v>1486.3</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v/>
+        <v>1526.1</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J97" s="10" t="n">
-        <v/>
+        <v>31.3</v>
+      </c>
+      <c r="J97" s="13" t="n">
+        <v>2.09</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>561.2</v>
+        <v>558.55</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v/>
+        <v>557</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v/>
+        <v>558.1</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v/>
+        <v>550.2</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v/>
+        <v>551.35</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v/>
+        <v>-7.2</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v/>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>309.65</v>
+        <v>305.5</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v/>
+        <v>304</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v/>
+        <v>306.35</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v/>
+        <v>303.25</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v/>
+        <v>305.3</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v/>
+        <v>-0.2</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v/>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1288.8</v>
+        <v>1278.6</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v/>
+        <v>1278.6</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v/>
+        <v>1279.9</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v/>
+        <v>1251.7</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v/>
+        <v>1254.5</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v/>
+        <v>-24.1</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v/>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5920.5</v>
+        <v>5977</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v/>
+        <v>5889</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v/>
+        <v>5898</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v/>
+        <v>5780.5</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v/>
+        <v>5799</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v/>
+        <v>-178</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v/>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>789.4</v>
+        <v>784.5</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v/>
+        <v>789</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v/>
+        <v>789</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v/>
+        <v>770.5</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v/>
+        <v>775.8</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v/>
+        <v>-8.699999999999999</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v/>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>546.65</v>
+        <v>560.55</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v/>
+        <v>562.55</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v/>
+        <v>567.95</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v/>
+        <v>559.1</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v/>
+        <v>561.4</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v/>
+        <v>0.85</v>
+      </c>
+      <c r="J103" s="13" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1279.6</v>
+        <v>1263.4</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v/>
+        <v>1263.4</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v/>
+        <v>1269.9</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v/>
+        <v>1251</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v/>
+        <v>1257</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v/>
+        <v>-6.4</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v/>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>471.9</v>
+        <v>493.1</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v/>
+        <v>494.9</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v/>
+        <v>498.75</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v/>
+        <v>486</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v/>
+        <v>492.85</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v/>
+        <v>-0.25</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v/>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1194.1</v>
+        <v>1202.7</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v/>
+        <v>1210</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v/>
+        <v>1210</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v/>
+        <v>1178</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v/>
+        <v>1191.9</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v/>
+        <v>-10.8</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v/>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>382.15</v>
+        <v>376.85</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v/>
+        <v>370.05</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v/>
+        <v>375.95</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v/>
+        <v>367.65</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v/>
+        <v>370.4</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v/>
+        <v>-6.45</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v/>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>744.7</v>
+        <v>735.95</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v/>
+        <v>735</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v/>
+        <v>743.95</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v/>
+        <v>728</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v/>
+        <v>733.65</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v/>
+        <v>-2.3</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v/>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1437</v>
+        <v>1459.1</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v/>
+        <v>1450</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v/>
+        <v>1469</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v/>
+        <v>1423</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v/>
+        <v>1430.9</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v/>
+        <v>-28.2</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v/>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1114.35</v>
+        <v>1096.1</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v/>
+        <v>1096.5</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v/>
+        <v>1130</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v/>
+        <v>1091.1</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v/>
+        <v>1129</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v/>
+        <v>32.9</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>565.15</v>
+        <v>559.05</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v/>
+        <v>555</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v/>
+        <v>563.95</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v/>
+        <v>544.95</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v/>
+        <v>545.55</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v/>
+        <v>-13.5</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v/>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4075.4</v>
+        <v>4021.1</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v/>
+        <v>4009.9</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v/>
+        <v>4064</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v/>
+        <v>3978.5</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v/>
+        <v>4054.1</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J112" s="10" t="n">
-        <v/>
+        <v>33</v>
+      </c>
+      <c r="J112" s="13" t="n">
+        <v>0.82</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>291.9</v>
+        <v>294.04</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v/>
+        <v>291.99</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v/>
+        <v>295.19</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v/>
+        <v>287.14</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v/>
+        <v>292.12</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v/>
+        <v>-1.92</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v/>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="114">
@@ -4607,7 +4607,7 @@
         <v>150</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>4757.9</v>
+        <v>4604.3</v>
       </c>
       <c r="E114" s="12" t="n">
         <v/>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3642.4</v>
+        <v>3550.2</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v/>
+        <v>3498.6</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v/>
+        <v>3510</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v/>
+        <v>3424</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v/>
+        <v>3449.6</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v/>
+        <v>-100.6</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v/>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2311.5</v>
+        <v>2307.9</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v/>
+        <v>2307.9</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v/>
+        <v>2381</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v/>
+        <v>2293.9</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v/>
+        <v>2341.4</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v/>
+        <v>33.5</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3247.3</v>
+        <v>3149.7</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v/>
+        <v>3105</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v/>
+        <v>3114.7</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v/>
+        <v>3032.2</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v/>
+        <v>3047.7</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v/>
+        <v>-102</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v/>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>281.8</v>
+        <v>295.05</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v/>
+        <v>293.95</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v/>
+        <v>296.25</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v/>
+        <v>291.35</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v/>
+        <v>292.85</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v/>
+        <v>-2.2</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v/>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>762.5</v>
+        <v>772.5</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v/>
+        <v>774.95</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v/>
+        <v>780.1</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v/>
+        <v>765.65</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v/>
+        <v>778.9</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v/>
+        <v>6.4</v>
+      </c>
+      <c r="J119" s="13" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13461</v>
+        <v>13337</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v/>
+        <v>13250</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v/>
+        <v>13358</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v/>
+        <v>13125</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v/>
+        <v>13160</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v/>
+        <v>-177</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v/>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2825.6</v>
+        <v>2783.2</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v/>
+        <v>2771</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v/>
+        <v>2852</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v/>
+        <v>2765.5</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v/>
+        <v>2791.4</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J122" s="10" t="n">
-        <v/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J122" s="13" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>484.3</v>
+        <v>476.65</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v/>
+        <v>476</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v/>
+        <v>477.75</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v/>
+        <v>469.55</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v/>
+        <v>472.2</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v/>
+        <v>-4.45</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v/>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1648.8</v>
+        <v>1627.4</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v/>
+        <v>1620</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v/>
+        <v>1625.2</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v/>
+        <v>1588</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v/>
+        <v>1595.4</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v/>
+        <v>-32</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v/>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1136.95</v>
+        <v>1147.25</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v/>
+        <v>1146.45</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v/>
+        <v>1159.9</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v/>
+        <v>1130.25</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v/>
+        <v>1137.4</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v/>
+        <v>-9.85</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v/>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>124.7</v>
+        <v>131.76</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v/>
+        <v>131.76</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v/>
+        <v>131.76</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v/>
+        <v>126.11</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v/>
+        <v>127.22</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v/>
+        <v>-4.54</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v/>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2419</v>
+        <v>2331</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v/>
+        <v>2331</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v/>
+        <v>2360.2</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v/>
+        <v>2270.7</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v/>
+        <v>2277</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v/>
+        <v>-54</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v/>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>139665</v>
+        <v>137040</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v/>
+        <v>136880</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v/>
+        <v>136890</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v/>
+        <v>134205</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v/>
+        <v>134615</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v/>
+        <v>-2425</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v/>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3610.2</v>
+        <v>3586.9</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v/>
+        <v>3579</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v/>
+        <v>3609</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v/>
+        <v>3544</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v/>
+        <v>3561.4</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v/>
+        <v>-25.5</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v/>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>422.95</v>
+        <v>435.95</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v/>
+        <v>435</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v/>
+        <v>443.15</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v/>
+        <v>432.35</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v/>
+        <v>439.25</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v/>
+        <v>3.3</v>
+      </c>
+      <c r="J130" s="13" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1077.7</v>
+        <v>1052.7</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v/>
+        <v>1041.7</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v/>
+        <v>1044.95</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v/>
+        <v>1014.3</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v/>
+        <v>1018.05</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v/>
+        <v>-34.65</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v/>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6373.5</v>
+        <v>6267</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v/>
+        <v>6280</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v/>
+        <v>6389.5</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v/>
+        <v>6250.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v/>
+        <v>6280.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J132" s="10" t="n">
-        <v/>
+        <v>13.5</v>
+      </c>
+      <c r="J132" s="13" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1379.9</v>
+        <v>1395.8</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v/>
+        <v>1388.9</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v/>
+        <v>1415</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v/>
+        <v>1382.1</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v/>
+        <v>1410.5</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v/>
+        <v>14.7</v>
+      </c>
+      <c r="J133" s="13" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>88.47</v>
+        <v>88.59</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v/>
+        <v>88.41</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v/>
+        <v>88.54000000000001</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v/>
+        <v>86.63</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v/>
+        <v>87.31</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v/>
+        <v>-1.28</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v/>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>396.2</v>
+        <v>405.4</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v/>
+        <v>404</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v/>
+        <v>405.9</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v/>
+        <v>400.4</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v/>
+        <v>402.25</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v/>
+        <v>-3.15</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v/>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1723.9</v>
+        <v>1733.6</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v/>
+        <v>1736.9</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v/>
+        <v>1736.9</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v/>
+        <v>1701.4</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v/>
+        <v>1707.7</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v/>
+        <v>-25.9</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v/>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>7931</v>
+        <v>8126.5</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v/>
+        <v>8430</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v/>
+        <v>8900</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v/>
+        <v>8261</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v/>
+        <v>8791.5</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J137" s="10" t="n">
-        <v/>
+        <v>665</v>
+      </c>
+      <c r="J137" s="13" t="n">
+        <v>8.18</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>283.1</v>
+        <v>283.65</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v/>
+        <v>284.85</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v/>
+        <v>289.8</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v/>
+        <v>284.05</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v/>
+        <v>286.25</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J138" s="10" t="n">
-        <v/>
+        <v>2.6</v>
+      </c>
+      <c r="J138" s="13" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37960</v>
+        <v>37855</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v/>
+        <v>37830</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v/>
+        <v>38285</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v/>
+        <v>37270</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v/>
+        <v>37965</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v/>
+        <v>110</v>
+      </c>
+      <c r="J139" s="13" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5329.9</v>
+        <v>5073.3</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v/>
+        <v>5081</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v/>
+        <v>5119.4</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v/>
+        <v>5011</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v/>
+        <v>5065.2</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v/>
+        <v>-8.1</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v/>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>277.78</v>
+        <v>279.55</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v/>
+        <v>277.54</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v/>
+        <v>279.9</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v/>
+        <v>273.41</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v/>
+        <v>275.81</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v/>
+        <v>-3.74</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v/>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>471.1</v>
+        <v>470.3</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v/>
+        <v>467.5</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v/>
+        <v>472.3</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v/>
+        <v>466.1</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v/>
+        <v>469.8</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v/>
+        <v>-0.5</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v/>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1407.8</v>
+        <v>1419</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v/>
+        <v>1408</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v/>
+        <v>1412</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v/>
+        <v>1396.8</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v/>
+        <v>1402.1</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v/>
+        <v>-16.9</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v/>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3021.3</v>
+        <v>3057.3</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v/>
+        <v>3047.3</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v/>
+        <v>3089.9</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v/>
+        <v>3036.1</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v/>
+        <v>3069.6</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J145" s="10" t="n">
-        <v/>
+        <v>12.3</v>
+      </c>
+      <c r="J145" s="13" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>114.11</v>
+        <v>114.67</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v/>
+        <v>114.2</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v/>
+        <v>114.39</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v/>
+        <v>111.57</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v/>
+        <v>112.71</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v/>
+        <v>-1.96</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v/>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>7955.5</v>
+        <v>8038</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v/>
+        <v>8000</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v/>
+        <v>8125</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v/>
+        <v>7950</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v/>
+        <v>7963.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v/>
+        <v>-74.5</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v/>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>319.35</v>
+        <v>319.75</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v/>
+        <v>320</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v/>
+        <v>321.85</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v/>
+        <v>318.05</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v/>
+        <v>319.15</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v/>
+        <v>-0.6</v>
       </c>
       <c r="J148" s="10" t="n">
-        <v/>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>973</v>
+        <v>990.3</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>994.9</v>
+        <v>1010.25</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>969</v>
+        <v>989.65</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>990.3</v>
+        <v>1005</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>17.3</v>
+        <v>14.7</v>
       </c>
       <c r="J149" s="13" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>320.4</v>
+        <v>317.65</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v/>
+        <v>315.4</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v/>
+        <v>316.4</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v/>
+        <v>311.2</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v/>
+        <v>312.45</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v/>
+        <v>-5.2</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v/>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="151">
@@ -5868,22 +5868,22 @@
         <v>383.35</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v/>
+        <v>381.85</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v/>
+        <v>386.1</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v/>
+        <v>375.85</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v/>
+        <v>376.45</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v/>
+        <v>-6.9</v>
       </c>
       <c r="J151" s="10" t="n">
-        <v/>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1353.3</v>
+        <v>1362.1</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v/>
+        <v>1346</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v/>
+        <v>1355.5</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v/>
+        <v>1340.7</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v/>
+        <v>1343.4</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v/>
+        <v>-18.7</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v/>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>175.06</v>
+        <v>176.23</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v/>
+        <v>174.71</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v/>
+        <v>178.09</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v/>
+        <v>173.8</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v/>
+        <v>176.45</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J153" s="10" t="n">
-        <v/>
+        <v>0.22</v>
+      </c>
+      <c r="J153" s="13" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>679.75</v>
+        <v>686.2</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v/>
+        <v>686</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v/>
+        <v>689.7</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v/>
+        <v>678.95</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v/>
+        <v>680.55</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v/>
+        <v>-5.65</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v/>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1911.6</v>
+        <v>1884.8</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v/>
+        <v>1865</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v/>
+        <v>1886.7</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v/>
+        <v>1807.7</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v/>
+        <v>1828.1</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v/>
+        <v>-56.7</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v/>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1111.85</v>
+        <v>1103.3</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v/>
+        <v>1095</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v/>
+        <v>1101.9</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v/>
+        <v>1082.2</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v/>
+        <v>1094.25</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v/>
+        <v>-9.050000000000001</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v/>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>25540</v>
+        <v>25735</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v/>
+        <v>25605</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v/>
+        <v>25850</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v/>
+        <v>25125</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v/>
+        <v>25470</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v/>
+        <v>-265</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v/>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1045.3</v>
+        <v>1044.55</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v/>
+        <v>1044.9</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v/>
+        <v>1044.9</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v/>
+        <v>1006.35</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v/>
+        <v>1009.3</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v/>
+        <v>-35.25</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v/>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3721.7</v>
+        <v>3844.3</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v/>
+        <v>3849</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v/>
+        <v>3901</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v/>
+        <v>3811.5</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v/>
+        <v>3864.4</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v/>
+        <v>20.1</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2471</v>
+        <v>2492.8</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v/>
+        <v>2484.3</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v/>
+        <v>2549.9</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v/>
+        <v>2466</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v/>
+        <v>2542.4</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J160" s="10" t="n">
-        <v/>
+        <v>49.6</v>
+      </c>
+      <c r="J160" s="13" t="n">
+        <v>1.99</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1665.2</v>
+        <v>1669.8</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v/>
+        <v>1669</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v/>
+        <v>1713</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v/>
+        <v>1661.2</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v/>
+        <v>1680.1</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J161" s="10" t="n">
-        <v/>
+        <v>10.3</v>
+      </c>
+      <c r="J161" s="13" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>645.05</v>
+        <v>652.45</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v/>
+        <v>648.95</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v/>
+        <v>653.5</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v/>
+        <v>621</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v/>
+        <v>625.85</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v/>
+        <v>-26.6</v>
       </c>
       <c r="J162" s="10" t="n">
-        <v/>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>444.65</v>
+        <v>435.95</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v/>
+        <v>431</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v/>
+        <v>442.4</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v/>
+        <v>427</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v/>
+        <v>428.35</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v/>
+        <v>-7.6</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v/>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
+        <v>709.85</v>
+      </c>
+      <c r="E164" s="12" t="n">
+        <v>709.85</v>
+      </c>
+      <c r="F164" s="12" t="n">
+        <v>721.65</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>705</v>
+      </c>
+      <c r="H164" s="12" t="n">
         <v>707.7</v>
       </c>
-      <c r="E164" s="12" t="n">
-        <v/>
-      </c>
-      <c r="F164" s="12" t="n">
-        <v/>
-      </c>
-      <c r="G164" s="12" t="n">
-        <v/>
-      </c>
-      <c r="H164" s="12" t="n">
-        <v/>
-      </c>
       <c r="I164" s="12" t="n">
-        <v/>
+        <v>-2.15</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v/>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1513.4</v>
+        <v>1525</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v/>
+        <v>1535</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v/>
+        <v>1612</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v/>
+        <v>1511.8</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v/>
+        <v>1580.7</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J165" s="10" t="n">
-        <v/>
+        <v>55.7</v>
+      </c>
+      <c r="J165" s="13" t="n">
+        <v>3.65</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1142</v>
+        <v>1178.6</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v/>
+        <v>1178</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v/>
+        <v>1188.9</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v/>
+        <v>1160.1</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v/>
+        <v>1184.4</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J166" s="10" t="n">
-        <v/>
+        <v>5.8</v>
+      </c>
+      <c r="J166" s="13" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="167">
@@ -6446,22 +6446,22 @@
         <v>436.05</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v/>
+        <v>435.5</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v/>
+        <v>437.8</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v/>
+        <v>427.55</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v/>
+        <v>430.3</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v/>
+        <v>-5.75</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v/>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>212.01</v>
+        <v>213.03</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v/>
+        <v>213.04</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v/>
+        <v>213.1</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v/>
+        <v>210.16</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v/>
+        <v>210.91</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v/>
+        <v>-2.12</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v/>
+        <v>-1</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2610.5</v>
+        <v>2538.5</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v/>
+        <v>2529</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v/>
+        <v>2559.5</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v/>
+        <v>2516.3</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v/>
+        <v>2521.8</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v/>
+        <v>-16.7</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v/>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1500.8</v>
+        <v>1462.6</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v/>
+        <v>1470.2</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v/>
+        <v>1473.9</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v/>
+        <v>1413.9</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v/>
+        <v>1421.5</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v/>
+        <v>-41.1</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v/>
+        <v>-2.81</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2885.2</v>
+        <v>3024.4</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v/>
+        <v>3037.9</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v/>
+        <v>3153</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v/>
+        <v>3032</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v/>
+        <v>3086.8</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J172" s="10" t="n">
-        <v/>
+        <v>62.4</v>
+      </c>
+      <c r="J172" s="13" t="n">
+        <v>2.06</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4479.7</v>
+        <v>4454.6</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v/>
+        <v>4411</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v/>
+        <v>4474</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v/>
+        <v>4393.5</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v/>
+        <v>4456.5</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J173" s="10" t="n">
-        <v/>
+        <v>1.9</v>
+      </c>
+      <c r="J173" s="13" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4135.7</v>
+        <v>4084.6</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v/>
+        <v>4068.6</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v/>
+        <v>4174</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v/>
+        <v>4065.1</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v/>
+        <v>4147.2</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v/>
+        <v>62.6</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1621.5</v>
+        <v>1657.4</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v/>
+        <v>1648.1</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v/>
+        <v>1741</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v/>
+        <v>1645.1</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v/>
+        <v>1737</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v/>
-      </c>
-      <c r="J175" s="10" t="n">
-        <v/>
+        <v>79.59999999999999</v>
+      </c>
+      <c r="J175" s="13" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4390.5</v>
+        <v>4434.5</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v/>
+        <v>4440</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v/>
+        <v>4479.4</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v/>
+        <v>4225</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v/>
+        <v>4251.4</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v/>
+        <v>-183.1</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v/>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3752.7</v>
+        <v>3660.7</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v/>
+        <v>3636</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v/>
+        <v>3636</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v/>
+        <v>3482.2</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v/>
+        <v>3513</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v/>
+        <v>-147.7</v>
       </c>
       <c r="J177" s="10" t="n">
-        <v/>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1498.4</v>
+        <v>1500</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v/>
+        <v>1500</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v/>
+        <v>1506.3</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v/>
+        <v>1478.6</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v/>
+        <v>1483.2</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v/>
+        <v>-16.8</v>
       </c>
       <c r="J178" s="10" t="n">
-        <v/>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>12039</v>
+        <v>12193</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v/>
+        <v>12105</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v/>
+        <v>12213</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v/>
+        <v>11936</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v/>
+        <v>12167</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v/>
+        <v>-26</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v/>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>191.38</v>
+        <v>194.05</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v/>
+        <v>194.89</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v/>
+        <v>194.89</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v/>
+        <v>177.3</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v/>
+        <v>179.71</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v/>
+        <v>-14.34</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v/>
+        <v>-7.39</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>654.3</v>
+        <v>653.85</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v/>
+        <v>653.5</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v/>
+        <v>656.55</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v/>
+        <v>638.45</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v/>
+        <v>642.05</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v/>
+        <v>-11.8</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v/>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>766.8</v>
+        <v>757</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v/>
+        <v>758.8</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v/>
+        <v>758.8</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v/>
+        <v>733.05</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v/>
+        <v>735.6</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v/>
+        <v>-21.4</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v/>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1457.2</v>
+        <v>1481.6</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v/>
+        <v>1476</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v/>
+        <v>1476.5</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v/>
+        <v>1429.6</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v/>
+        <v>1445.5</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v/>
+        <v>-36.1</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v/>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>205.01</v>
+        <v>204</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v/>
+        <v>204</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v/>
+        <v>204.9</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v/>
+        <v>202.3</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v/>
+        <v>202.76</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v/>
+        <v>-1.24</v>
       </c>
       <c r="J184" s="10" t="n">
-        <v/>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>928.6</v>
+        <v>929.9</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v/>
+        <v>927</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v/>
+        <v>962.9</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v/>
+        <v>921.7</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v/>
+        <v>946.35</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v/>
-      </c>
-      <c r="J186" s="10" t="n">
-        <v/>
+        <v>16.45</v>
+      </c>
+      <c r="J186" s="13" t="n">
+        <v>1.77</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  22-Apr-2026 08:07 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  23-Apr-2026 03:12 PM</t>
         </is>
       </c>
     </row>
@@ -7256,14 +7256,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-Apr-2026 08:07 PM</t>
+          <t>23-Apr-2026 03:12 PM</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>184</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>178</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 23-Apr-2026 03:12 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 24-Apr-2026 02:45 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>23-Apr-2026 03:12 PM</t>
+          <t>24-Apr-2026 02:45 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  23-Apr-2026 03:12 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  24-Apr-2026 02:45 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>470.4</v>
+        <v>465.9</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>468</v>
+        <v>470.3</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>480.2</v>
+        <v>476.35</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>463.6</v>
+        <v>458.55</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>465.9</v>
+        <v>472.75</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-4.5</v>
+        <v>6.85</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-0.96</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7587</v>
+        <v>7575.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7587</v>
+        <v>7575.5</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7650</v>
+        <v>7594</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7533.5</v>
+        <v>7304</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7575.5</v>
+        <v>7328.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>-0.15</v>
+        <v>-247</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>-3.26</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25420</v>
+        <v>25410</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25440</v>
+        <v>25390</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25675</v>
+        <v>25510</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25350</v>
+        <v>25150</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25410</v>
+        <v>25180</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>-0.04</v>
+        <v>-230</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>350.7</v>
+        <v>349.75</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>348.25</v>
+        <v>349.95</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>354.35</v>
+        <v>351.55</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>346.95</v>
+        <v>338.65</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>349.75</v>
+        <v>340.6</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>-0.27</v>
+        <v>-9.15</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>64.98999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>64.25</v>
+        <v>63.45</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>65.27</v>
+        <v>63.79</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>63</v>
+        <v>61.41</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>63.2</v>
+        <v>61.79</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-1.79</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>-2.75</v>
+        <v>-1.41</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1446.4</v>
+        <v>1423.1</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1439</v>
+        <v>1423</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1439.7</v>
+        <v>1429</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1420</v>
+        <v>1398.8</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1423.1</v>
+        <v>1412.7</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-23.3</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>-1.61</v>
+        <v>-10.4</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2260.8</v>
+        <v>2300</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2243.5</v>
+        <v>2310.2</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2333.9</v>
+        <v>2321.4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2221.8</v>
+        <v>2227</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2300</v>
+        <v>2287.6</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>39.2</v>
+        <v>-12.4</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>1.73</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1588.6</v>
+        <v>1602.9</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1575</v>
+        <v>1612</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1611</v>
+        <v>1618.8</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1566.2</v>
+        <v>1556.5</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1602.9</v>
+        <v>1585.1</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>14.3</v>
+        <v>-17.8</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>0.9</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5627</v>
+        <v>5520.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5545.5</v>
+        <v>5572.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5579.5</v>
+        <v>5578.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5432.5</v>
+        <v>5193.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5520.5</v>
+        <v>5235</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-106.5</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>-1.89</v>
+        <v>-285.5</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>-5.17</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>460.9</v>
+        <v>450.4</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>457.95</v>
+        <v>451</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>457.95</v>
+        <v>457.7</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>449</v>
+        <v>440.4</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>450.4</v>
+        <v>451.2</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-10.5</v>
+        <v>0.8</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>-2.28</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>328.59</v>
+        <v>321.21</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>328</v>
+        <v>322.81</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>320.31</v>
+        <v>309.51</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>321.21</v>
+        <v>314.52</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-7.38</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-2.25</v>
+        <v>-6.69</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2121.9</v>
+        <v>2022.9</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2121.1</v>
+        <v>2028</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2121.1</v>
+        <v>2039.5</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2017</v>
+        <v>1979</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2022.9</v>
+        <v>2004.5</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-99</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>-4.67</v>
+        <v>-18.4</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7662</v>
+        <v>7781</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7685</v>
+        <v>7814</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7815</v>
+        <v>7845</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7601</v>
+        <v>7684.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7781</v>
+        <v>7732.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>119</v>
+        <v>-48.5</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>1.55</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>434</v>
+        <v>432.45</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>432</v>
+        <v>432.45</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>437.45</v>
+        <v>434.2</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>431.2</v>
+        <v>421.9</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>432.45</v>
+        <v>423.85</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>-0.36</v>
+        <v>-8.6</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>178.97</v>
+        <v>170.63</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>177</v>
+        <v>170.69</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>177.79</v>
+        <v>172.2</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>169.25</v>
+        <v>168.37</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>170.63</v>
+        <v>169.9</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-8.34</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>-4.66</v>
+        <v>-0.73</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2562.9</v>
+        <v>2521.4</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2530</v>
+        <v>2521.4</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2541.7</v>
+        <v>2538.9</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2510</v>
+        <v>2470.7</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2521.4</v>
+        <v>2485.1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-41.5</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>-1.62</v>
+        <v>-36.3</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1589.6</v>
+        <v>1574.9</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1585</v>
+        <v>1578.3</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1594.5</v>
+        <v>1591</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1562.8</v>
+        <v>1551.9</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1574.9</v>
+        <v>1563.2</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-14.7</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>-0.92</v>
+        <v>-11.7</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>629.1</v>
+        <v>621.7</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>638</v>
+        <v>629.7</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>620.1</v>
+        <v>604.4</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>621.7</v>
+        <v>626.85</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-7.4</v>
+        <v>5.15</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-1.18</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6666.5</v>
+        <v>6727</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6670</v>
+        <v>6798</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6889</v>
+        <v>6999</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6575</v>
+        <v>6605</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6727</v>
+        <v>6680.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>60.5</v>
+        <v>-46.5</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0.91</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1043.2</v>
+        <v>1056.25</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1039.05</v>
+        <v>1058.7</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1059.2</v>
+        <v>1079.55</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1035.3</v>
+        <v>1047.25</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1056.25</v>
+        <v>1065.65</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>13.05</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>1.25</v>
+        <v>9.4</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1421.2</v>
+        <v>1435.4</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1420</v>
+        <v>1436.9</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1459.5</v>
+        <v>1446</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1409.1</v>
+        <v>1411.7</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1435.4</v>
+        <v>1413.8</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>14.2</v>
+        <v>-21.6</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1379.6</v>
+        <v>1369.6</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>1369</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1384.2</v>
+        <v>1375</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1365.4</v>
+        <v>1350</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1369.6</v>
+        <v>1365.9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>-0.72</v>
+        <v>-3.7</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>9602</v>
+        <v>9550.5</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>9575</v>
+        <v>9600</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>9591</v>
+        <v>9663</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>9477</v>
+        <v>9528</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>9550.5</v>
+        <v>9576</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-51.5</v>
+        <v>25.5</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>-0.54</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1842.9</v>
+        <v>1792.6</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1821.5</v>
+        <v>1792.7</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1830</v>
+        <v>1799.9</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1786</v>
+        <v>1757.3</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1792.6</v>
+        <v>1770.7</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-50.3</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>-2.73</v>
+        <v>-21.9</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>934.75</v>
+        <v>918.35</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>926.1</v>
+        <v>920</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>929.85</v>
+        <v>924.7</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>909.35</v>
+        <v>909.8</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>918.35</v>
+        <v>921.55</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-16.4</v>
+        <v>3.2</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>-1.75</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2309.7</v>
+        <v>2265.4</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2300</v>
+        <v>2275</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2311.1</v>
+        <v>2284</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2256.2</v>
+        <v>2187</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2265.4</v>
+        <v>2225.4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-44.3</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>-1.92</v>
+        <v>-40</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>541.55</v>
+        <v>540.3</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>543.7</v>
+        <v>540.15</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>552.7</v>
+        <v>549</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>530.55</v>
+        <v>507</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>540.3</v>
+        <v>516.1</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>-0.23</v>
+        <v>-24.2</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>-4.48</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>176.52</v>
+        <v>173.9</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>173.73</v>
+        <v>173.81</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>174.68</v>
+        <v>175.08</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>171.1</v>
+        <v>168.8</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>173.9</v>
+        <v>174.67</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-2.62</v>
+        <v>0.77</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>-1.48</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>282.77</v>
+        <v>276.34</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>281</v>
+        <v>276.2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>281.49</v>
+        <v>276.8</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>274.05</v>
+        <v>269.55</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>276.34</v>
+        <v>274.13</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-6.43</v>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>-2.27</v>
+        <v>-2.21</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>448.7</v>
+        <v>449.95</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>451.7</v>
+        <v>450</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>455.7</v>
+        <v>451.2</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>444.5</v>
+        <v>438.75</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>449.95</v>
+        <v>444.45</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>1.25</v>
+        <v>-5.5</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>0.28</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>478.25</v>
+        <v>468.65</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>470.5</v>
+        <v>468.65</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>476.4</v>
+        <v>474.6</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>467</v>
+        <v>458.2</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>468.65</v>
+        <v>460.4</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-9.6</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>-2.01</v>
+        <v>-8.25</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1829</v>
+        <v>1841.2</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1821.8</v>
+        <v>1845</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1846</v>
+        <v>1850.7</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1812.1</v>
+        <v>1807.3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1841.2</v>
+        <v>1814.5</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>12.2</v>
+        <v>-26.7</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>0.67</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>333.64</v>
+        <v>337.6</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>341.25</v>
+        <v>340.49</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>330.65</v>
+        <v>333.02</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>337.6</v>
+        <v>337.39</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>3.96</v>
+        <v>-0.21</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>1.19</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>357.8</v>
+        <v>358</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>357.45</v>
+        <v>358.05</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>364.8</v>
+        <v>358.95</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>355.6</v>
+        <v>348.5</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>358</v>
+        <v>349.85</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.2</v>
+        <v>-8.15</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>0.06</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>37885</v>
+        <v>37380</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>37885</v>
+        <v>37495</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>37905</v>
+        <v>37690</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>37210</v>
+        <v>36295</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>37380</v>
+        <v>36690</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-505</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>-1.33</v>
+        <v>-690</v>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>314.4</v>
+        <v>309.8</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>313.75</v>
+        <v>310.75</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>308.4</v>
+        <v>300.15</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>309.8</v>
+        <v>308.1</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>-1.46</v>
+        <v>-1.7</v>
+      </c>
+      <c r="J38" s="13" t="n">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5729.5</v>
+        <v>5671.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5724</v>
+        <v>5707.5</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5728</v>
+        <v>5753.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5640.5</v>
+        <v>5665.5</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5671.5</v>
+        <v>5730.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-58</v>
+        <v>59</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>-1.01</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>387.85</v>
+        <v>385</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>387.5</v>
+        <v>385</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>388</v>
+        <v>385.95</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>380.05</v>
+        <v>366.2</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>385</v>
+        <v>368.65</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-2.85</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>-0.73</v>
+        <v>-16.35</v>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>145.23</v>
+        <v>140.87</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>144.5</v>
+        <v>141.33</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>144.58</v>
+        <v>141.86</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>140.21</v>
+        <v>138.15</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>140.87</v>
+        <v>140.85</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-4.36</v>
-      </c>
-      <c r="J41" s="10" t="n">
-        <v>-3</v>
+        <v>-0.02</v>
+      </c>
+      <c r="J41" s="13" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>912.3</v>
+        <v>899.8</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>903</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>914.4</v>
+        <v>913.5</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>888</v>
+        <v>876.3</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>899.8</v>
+        <v>909.6</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>-1.37</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>452.3</v>
+        <v>446.95</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>452.5</v>
+        <v>449.9</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>455.4</v>
+        <v>450.2</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>446.95</v>
+        <v>440.8</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-5.35</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>-1.18</v>
+        <v>-6.15</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1565.6</v>
+        <v>1543.4</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1558</v>
+        <v>1546.9</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1560.8</v>
+        <v>1575</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1532.5</v>
+        <v>1529.9</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1543.4</v>
+        <v>1568.2</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-22.2</v>
+        <v>24.8</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>-1.42</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1236.3</v>
+        <v>1305.9</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1234.1</v>
+        <v>1295</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1308.4</v>
+        <v>1303.9</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1227.6</v>
+        <v>1254.1</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1305.9</v>
+        <v>1295</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>69.59999999999999</v>
+        <v>-10.9</v>
       </c>
       <c r="J45" s="13" t="n">
-        <v>5.63</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>444.15</v>
+        <v>450.65</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>444.25</v>
+        <v>452.75</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>451.5</v>
+        <v>462</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>442.65</v>
+        <v>451.05</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>450.65</v>
+        <v>456</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>1.46</v>
+        <v>5.35</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1235.8</v>
+        <v>1220.6</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1237.5</v>
+        <v>1211</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1243.1</v>
+        <v>1214.5</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1215.8</v>
+        <v>1136.3</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1220.6</v>
+        <v>1150.9</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>-1.23</v>
+        <v>-69.7</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>-5.71</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2118.3</v>
+        <v>2150.2</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2110.3</v>
+        <v>2150.2</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2155</v>
+        <v>2177.8</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2057.6</v>
+        <v>2139</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2150.2</v>
+        <v>2171.3</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>1.51</v>
+        <v>21.1</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>515.7</v>
+        <v>505.05</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>516</v>
+        <v>505.05</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>516.9</v>
+        <v>506.9</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>502.3</v>
+        <v>499.05</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>505.05</v>
+        <v>502.8</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-10.65</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>-2.07</v>
+        <v>-2.25</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2034.5</v>
+        <v>2039.8</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>2034.5</v>
+        <v>2039.8</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2058</v>
+        <v>2054</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>2023</v>
+        <v>1983</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2039.8</v>
+        <v>1995.3</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>5.3</v>
+        <v>-44.5</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>0.26</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>261.37</v>
+        <v>253.39</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>261.01</v>
+        <v>254.63</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>261.01</v>
+        <v>257</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>250.21</v>
+        <v>248.31</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>253.39</v>
+        <v>250.23</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-7.98</v>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v>-3.05</v>
+        <v>-3.16</v>
+      </c>
+      <c r="J51" s="13" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>270.15</v>
+        <v>265.52</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>270.15</v>
+        <v>265.52</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>271.39</v>
+        <v>267.29</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>263.5</v>
+        <v>260</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>265.52</v>
+        <v>262.51</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>-1.71</v>
+        <v>-3.01</v>
+      </c>
+      <c r="J52" s="13" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5211.8</v>
+        <v>5176.9</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5200</v>
+        <v>5179</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5269</v>
+        <v>5250</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5155.7</v>
+        <v>5102.1</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5176.9</v>
+        <v>5232</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-34.9</v>
+        <v>55.1</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>-0.67</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="54">
@@ -2570,22 +2570,22 @@
         <v>460</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>458.9</v>
+        <v>460</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>461.3</v>
+        <v>462.5</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>452.7</v>
+        <v>448.1</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>460</v>
+        <v>451.1</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>0</v>
+        <v>-8.9</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>0</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1992.8</v>
+        <v>1958.8</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>2004.4</v>
+        <v>1971</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>2004.4</v>
+        <v>1975.2</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1944.7</v>
+        <v>1919.1</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1958.8</v>
+        <v>1962.5</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-34</v>
+        <v>3.7</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>-1.71</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1745.5</v>
+        <v>1731.9</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1739.5</v>
+        <v>1723.4</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1780</v>
+        <v>1738.9</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1708</v>
+        <v>1675.6</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1731.9</v>
+        <v>1690.3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-13.6</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>-0.78</v>
+        <v>-41.6</v>
+      </c>
+      <c r="J56" s="13" t="n">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>68</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>66.5</v>
+        <v>80.88</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>81.59999999999999</v>
+        <v>83.48</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>65</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>81.59999999999999</v>
+        <v>76.69</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>13.6</v>
+        <v>-4.91</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>20</v>
+        <v>-6.02</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6285.5</v>
+        <v>6378.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6265</v>
+        <v>6408.5</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6469.5</v>
+        <v>6442.5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6250.5</v>
+        <v>6320</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6378.5</v>
+        <v>6361.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>93</v>
+        <v>-17</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>1.48</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11267</v>
+        <v>10866.5</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>11249</v>
+        <v>10857</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11249</v>
+        <v>11086</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>10820</v>
+        <v>10765.5</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>10866.5</v>
+        <v>10815.5</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-400.5</v>
-      </c>
-      <c r="J59" s="10" t="n">
-        <v>-3.55</v>
+        <v>-51</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>610.65</v>
+        <v>592.8</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>604</v>
+        <v>591.1</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>605.25</v>
+        <v>595.5</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>591</v>
+        <v>583.05</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>592.8</v>
+        <v>587.05</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-17.85</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>-2.92</v>
+        <v>-5.75</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1217</v>
+        <v>1331</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1230</v>
+        <v>1293</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1357</v>
+        <v>1348.8</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1217.5</v>
+        <v>1293</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1331</v>
+        <v>1317.1</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>114</v>
+        <v>-13.9</v>
       </c>
       <c r="J61" s="13" t="n">
-        <v>9.369999999999999</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7230</v>
+        <v>7092.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7195.5</v>
+        <v>7054.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7195.5</v>
+        <v>7160</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7062</v>
+        <v>7049</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7092.5</v>
+        <v>7111.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-137.5</v>
+        <v>19</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>-1.9</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3338.6</v>
+        <v>3309</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3320</v>
+        <v>3309</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3373.8</v>
+        <v>3349</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3275.1</v>
+        <v>3214</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3309</v>
+        <v>3231.3</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-29.6</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>-0.89</v>
+        <v>-77.7</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>354.55</v>
+        <v>347.25</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>353.8</v>
+        <v>346.45</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>359.85</v>
+        <v>347.95</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>345.05</v>
+        <v>339.4</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>347.25</v>
+        <v>342.8</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="J64" s="10" t="n">
-        <v>-2.06</v>
+        <v>-4.45</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>296.45</v>
+        <v>295.4</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>294.95</v>
+        <v>296</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>296.65</v>
+        <v>298.3</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>293.55</v>
+        <v>291.25</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>295.4</v>
+        <v>293</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="J65" s="10" t="n">
-        <v>-0.35</v>
+        <v>-2.4</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>166.12</v>
+        <v>164.96</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>166</v>
+        <v>165.96</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>167.89</v>
+        <v>166.3</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>164.02</v>
+        <v>163.35</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>164.96</v>
+        <v>165.61</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-1.16</v>
+        <v>0.65</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>-0.7</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2240</v>
+        <v>2335</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2247.9</v>
+        <v>2351</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2359.4</v>
+        <v>2372.8</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2212.1</v>
+        <v>2283.2</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2335</v>
+        <v>2299.5</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>95</v>
+        <v>-35.5</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>4.24</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="10" t="n">
+      <c r="J68" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>488.5</v>
+        <v>481.95</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>487.1</v>
+        <v>486</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>481.5</v>
+        <v>465.9</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>481.95</v>
+        <v>468.45</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-6.55</v>
-      </c>
-      <c r="J69" s="10" t="n">
-        <v>-1.34</v>
+        <v>-13.5</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1139.55</v>
+        <v>1142.95</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1139</v>
+        <v>1143.2</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1145.75</v>
+        <v>1148</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1120.3</v>
+        <v>1083.95</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1142.95</v>
+        <v>1089.9</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>3.4</v>
+        <v>-53.05</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>0.3</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1832.2</v>
+        <v>1791</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1829.1</v>
+        <v>1795.6</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1833.1</v>
+        <v>1832</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1780.4</v>
+        <v>1759.8</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1791</v>
+        <v>1769.4</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-41.2</v>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>-2.25</v>
+        <v>-21.6</v>
+      </c>
+      <c r="J71" s="13" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>672.75</v>
+        <v>686.95</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>674</v>
+        <v>686.95</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>696.4</v>
+        <v>694.45</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>670.3</v>
+        <v>682</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>686.95</v>
+        <v>689.45</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J72" s="13" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2776.6</v>
+        <v>2735</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2762.3</v>
+        <v>2760.7</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2768.4</v>
+        <v>2768.9</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2727</v>
+        <v>2732.1</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2735</v>
+        <v>2739.3</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-41.6</v>
+        <v>4.3</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>-1.5</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>382.85</v>
+        <v>386</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>382.8</v>
+        <v>389</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>387.9</v>
+        <v>391.5</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>378.75</v>
+        <v>374.85</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>386</v>
+        <v>383.85</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>3.15</v>
+        <v>-2.15</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>0.82</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4400.6</v>
+        <v>4352.5</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4400.6</v>
+        <v>4352.5</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4402.5</v>
+        <v>4387.3</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4335</v>
+        <v>4236.1</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4352.5</v>
+        <v>4265.8</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-48.1</v>
-      </c>
-      <c r="J75" s="10" t="n">
-        <v>-1.09</v>
+        <v>-86.7</v>
+      </c>
+      <c r="J75" s="13" t="n">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1348.7</v>
+        <v>1260.3</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1294.6</v>
+        <v>1262</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1299.9</v>
+        <v>1267.4</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1255.2</v>
+        <v>1233</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1260.3</v>
+        <v>1238.6</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-88.40000000000001</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>-6.55</v>
+        <v>-21.7</v>
+      </c>
+      <c r="J76" s="13" t="n">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1285.3</v>
+        <v>1253.6</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1290</v>
+        <v>1264.4</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1294.3</v>
+        <v>1264.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1272</v>
+        <v>1198.1</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1277.6</v>
+        <v>1203.2</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>-0.6</v>
+        <v>-50.4</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>-4.02</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2766.4</v>
+        <v>2708.2</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2745</v>
+        <v>2700</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2762.9</v>
+        <v>2764</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2700</v>
+        <v>2692.9</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2708.2</v>
+        <v>2735</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-58.2</v>
+        <v>26.8</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>-2.1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>799.9</v>
+        <v>784.35</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>792</v>
+        <v>777.3</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>796.65</v>
+        <v>787.6</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>782.5</v>
+        <v>777</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>784.35</v>
+        <v>784.85</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-15.55</v>
+        <v>0.5</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>-1.94</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>604.05</v>
+        <v>598.65</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>604.2</v>
+        <v>598</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>607.75</v>
+        <v>603.15</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>595.5</v>
+        <v>585.6</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>598.65</v>
+        <v>588.2</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>-0.89</v>
+        <v>-10.45</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5189</v>
+        <v>5032</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5150</v>
+        <v>5035.5</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5160</v>
+        <v>5060.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>4995</v>
+        <v>4941.5</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5032</v>
+        <v>4961.5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-157</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>-3.03</v>
+        <v>-70.5</v>
+      </c>
+      <c r="J81" s="13" t="n">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1039.9</v>
+        <v>1041.35</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1039.75</v>
+        <v>1031</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1031.15</v>
+        <v>1027.55</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1041.35</v>
+        <v>1048.35</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J82" s="13" t="n">
-        <v>0.14</v>
+        <v>7</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>556.95</v>
+        <v>549.45</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>556.45</v>
+        <v>551.4</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>560.8</v>
+        <v>554.95</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>548</v>
+        <v>537.45</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>549.45</v>
+        <v>541.5</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="J83" s="10" t="n">
-        <v>-1.35</v>
+        <v>-7.95</v>
+      </c>
+      <c r="J83" s="13" t="n">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>382.55</v>
+        <v>376.9</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>377.35</v>
+        <v>375</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>378.9</v>
+        <v>376.4</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>371.1</v>
+        <v>368.7</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>376.9</v>
+        <v>373.5</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-5.65</v>
-      </c>
-      <c r="J84" s="10" t="n">
-        <v>-1.48</v>
+        <v>-3.4</v>
+      </c>
+      <c r="J84" s="13" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2368.8</v>
+        <v>2366.4</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2336</v>
+        <v>2388.6</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2400</v>
+        <v>2388.6</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2336</v>
+        <v>2299</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2366.4</v>
+        <v>2327.3</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>-0.1</v>
+        <v>-39.1</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>32705</v>
+        <v>32650</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>32700</v>
+        <v>32805</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>32850</v>
+        <v>32880</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>32400</v>
+        <v>31215</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>32650</v>
+        <v>31365</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-55</v>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v>-0.17</v>
+        <v>-1285</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>-3.94</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>68.38</v>
+        <v>67.83</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>67.5</v>
+        <v>67.83</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>68.45</v>
+        <v>68.64</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>67.45999999999999</v>
+        <v>66.69</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>67.83</v>
+        <v>67.23</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="J87" s="10" t="n">
-        <v>-0.8</v>
+        <v>-0.6</v>
+      </c>
+      <c r="J87" s="13" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>125.78</v>
+        <v>126.92</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>125.8</v>
+        <v>128.4</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>128.05</v>
+        <v>129.7</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>125.05</v>
+        <v>122.34</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>126.92</v>
+        <v>123.23</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>1.14</v>
+        <v>-3.69</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>0.91</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>169.08</v>
+        <v>165.55</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>172</v>
+        <v>165.55</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>173.29</v>
+        <v>167.05</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>165</v>
+        <v>162.6</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>165.55</v>
+        <v>164.61</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="J89" s="10" t="n">
-        <v>-2.09</v>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="J89" s="13" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>659.7</v>
+        <v>639.45</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>657</v>
+        <v>636.85</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>657</v>
+        <v>641.55</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>636</v>
+        <v>630.4</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>639.45</v>
+        <v>635.35</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-20.25</v>
-      </c>
-      <c r="J90" s="10" t="n">
-        <v>-3.07</v>
+        <v>-4.1</v>
+      </c>
+      <c r="J90" s="13" t="n">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2168.4</v>
+        <v>2159.4</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2168.4</v>
+        <v>2164.7</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2190</v>
+        <v>2170</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2148.4</v>
+        <v>2099.6</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2159.4</v>
+        <v>2107.1</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J91" s="10" t="n">
-        <v>-0.42</v>
+        <v>-52.3</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>-2.42</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4640.9</v>
+        <v>4556</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4549.7</v>
+        <v>4566.1</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4589</v>
+        <v>4598.8</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4510</v>
+        <v>4507</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4556</v>
+        <v>4523.1</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-84.90000000000001</v>
-      </c>
-      <c r="J92" s="10" t="n">
-        <v>-1.83</v>
+        <v>-32.9</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>870.1</v>
+        <v>860.35</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>861.7</v>
+        <v>868</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>869.7</v>
+        <v>868</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>854.15</v>
+        <v>839</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>860.35</v>
+        <v>847.95</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-9.75</v>
-      </c>
-      <c r="J93" s="10" t="n">
-        <v>-1.12</v>
+        <v>-12.4</v>
+      </c>
+      <c r="J93" s="13" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>408.15</v>
+        <v>404.7</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>405.15</v>
+        <v>405.9</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>408.3</v>
+        <v>406.6</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>400.95</v>
+        <v>395.65</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>404.7</v>
+        <v>402.2</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="J94" s="10" t="n">
-        <v>-0.85</v>
+        <v>-2.5</v>
+      </c>
+      <c r="J94" s="13" t="n">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1268.6</v>
+        <v>1240.6</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1254</v>
+        <v>1200</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1265.7</v>
+        <v>1223.9</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1226</v>
+        <v>1152.2</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1240.6</v>
+        <v>1154.6</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-28</v>
-      </c>
-      <c r="J95" s="10" t="n">
-        <v>-2.21</v>
+        <v>-86</v>
+      </c>
+      <c r="J95" s="13" t="n">
+        <v>-6.93</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>147.36</v>
+        <v>145.48</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>146.4</v>
+        <v>145</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>147.35</v>
+        <v>145.6</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>145.1</v>
+        <v>142.9</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>145.48</v>
+        <v>143.47</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-1.88</v>
-      </c>
-      <c r="J96" s="10" t="n">
-        <v>-1.28</v>
+        <v>-2.01</v>
+      </c>
+      <c r="J96" s="13" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1494.8</v>
+        <v>1526.1</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1494.6</v>
+        <v>1535</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1541.1</v>
+        <v>1573.2</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1486.3</v>
+        <v>1516</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1526.1</v>
+        <v>1555.9</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="J97" s="13" t="n">
-        <v>2.09</v>
+        <v>29.8</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>558.55</v>
+        <v>551.35</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>558.1</v>
+        <v>556</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>550.2</v>
+        <v>539.2</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>551.35</v>
+        <v>541.2</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>-1.29</v>
+        <v>-10.15</v>
+      </c>
+      <c r="J98" s="13" t="n">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>305.5</v>
+        <v>305.3</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>304</v>
+        <v>306.65</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>306.35</v>
+        <v>306.65</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>303.25</v>
+        <v>301.1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>305.3</v>
+        <v>301.6</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.7</v>
+      </c>
+      <c r="J99" s="13" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1278.6</v>
+        <v>1254.5</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1278.6</v>
+        <v>1252.2</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1279.9</v>
+        <v>1273.1</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1251.7</v>
+        <v>1237.3</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1254.5</v>
+        <v>1256</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-24.1</v>
+        <v>1.5</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>-1.88</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5977</v>
+        <v>5799</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5889</v>
+        <v>5820</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5898</v>
+        <v>5820</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5780.5</v>
+        <v>5567.5</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5799</v>
+        <v>5584.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-178</v>
-      </c>
-      <c r="J101" s="10" t="n">
-        <v>-2.98</v>
+        <v>-214.5</v>
+      </c>
+      <c r="J101" s="13" t="n">
+        <v>-3.7</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>784.5</v>
+        <v>775.8</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>789</v>
+        <v>777.3</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>789</v>
+        <v>784.75</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>770.5</v>
+        <v>763.55</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>775.8</v>
+        <v>766.3</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>-1.11</v>
+        <v>-9.5</v>
+      </c>
+      <c r="J102" s="13" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>560.55</v>
+        <v>561.4</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>562.55</v>
+        <v>561</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>567.95</v>
+        <v>563.6</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>559.1</v>
+        <v>538.35</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>561.4</v>
+        <v>544.95</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>0.85</v>
+        <v>-16.45</v>
       </c>
       <c r="J103" s="13" t="n">
-        <v>0.15</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1263.4</v>
+        <v>1257</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1263.4</v>
+        <v>1264</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1269.9</v>
+        <v>1268</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1251</v>
+        <v>1246.5</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1257</v>
+        <v>1255.7</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>-0.51</v>
+        <v>-1.3</v>
+      </c>
+      <c r="J104" s="13" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>493.1</v>
+        <v>492.85</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>494.9</v>
+        <v>493.2</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>498.75</v>
+        <v>496.4</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>486</v>
+        <v>483.6</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>492.85</v>
+        <v>491.95</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.9</v>
+      </c>
+      <c r="J105" s="13" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1202.7</v>
+        <v>1191.9</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1210</v>
+        <v>1191.9</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1210</v>
+        <v>1219.9</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1178</v>
+        <v>1189.85</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1191.9</v>
+        <v>1211.15</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-10.8</v>
+        <v>19.25</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>-0.9</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>376.85</v>
+        <v>370.4</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>370.05</v>
+        <v>370.6</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>375.95</v>
+        <v>372.8</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>367.65</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>370.4</v>
+        <v>370.85</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-6.45</v>
+        <v>0.45</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>-1.71</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>735.95</v>
+        <v>733.65</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>735</v>
+        <v>733.5</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>743.95</v>
+        <v>733.95</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>728</v>
+        <v>690.15</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>733.65</v>
+        <v>709.6</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>-0.31</v>
+        <v>-24.05</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1459.1</v>
+        <v>1430.9</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1450</v>
+        <v>1435.5</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1469</v>
+        <v>1435.5</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1423</v>
+        <v>1399.9</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1430.9</v>
+        <v>1408.9</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-28.2</v>
-      </c>
-      <c r="J109" s="10" t="n">
-        <v>-1.93</v>
+        <v>-22</v>
+      </c>
+      <c r="J109" s="13" t="n">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1096.1</v>
+        <v>1129</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1096.5</v>
+        <v>1129.2</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1130</v>
+        <v>1137.2</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1091.1</v>
+        <v>1110.2</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1129</v>
+        <v>1113.45</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>32.9</v>
+        <v>-15.55</v>
       </c>
       <c r="J110" s="13" t="n">
-        <v>3</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>559.05</v>
+        <v>545.55</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>555</v>
+        <v>545.55</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>563.95</v>
+        <v>549.9</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>544.95</v>
+        <v>533.3</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>545.55</v>
+        <v>540.75</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="J111" s="10" t="n">
-        <v>-2.41</v>
+        <v>-4.8</v>
+      </c>
+      <c r="J111" s="13" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4021.1</v>
+        <v>4054.1</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>4009.9</v>
+        <v>4072</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4064</v>
+        <v>4088.1</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3978.5</v>
+        <v>3983.2</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4054.1</v>
+        <v>4014.3</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>33</v>
+        <v>-39.8</v>
       </c>
       <c r="J112" s="13" t="n">
-        <v>0.82</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>294.04</v>
+        <v>292.12</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>291.99</v>
+        <v>293.9</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>295.19</v>
+        <v>295.01</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>287.14</v>
+        <v>287.22</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>292.12</v>
+        <v>290.05</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>-0.65</v>
+        <v>-2.07</v>
+      </c>
+      <c r="J113" s="13" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="114">
@@ -4607,7 +4607,7 @@
         <v>150</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>4604.3</v>
+        <v>4531.5</v>
       </c>
       <c r="E114" s="12" t="n">
         <v/>
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="10" t="n">
+      <c r="J114" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3550.2</v>
+        <v>3449.6</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3498.6</v>
+        <v>3450</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3510</v>
+        <v>3495</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3424</v>
+        <v>3362</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3449.6</v>
+        <v>3379.8</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-100.6</v>
-      </c>
-      <c r="J115" s="10" t="n">
-        <v>-2.83</v>
+        <v>-69.8</v>
+      </c>
+      <c r="J115" s="13" t="n">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2307.9</v>
+        <v>2341.4</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2307.9</v>
+        <v>2347.3</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2381</v>
+        <v>2351.5</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2293.9</v>
+        <v>2262</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2341.4</v>
+        <v>2296.1</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>33.5</v>
+        <v>-45.3</v>
       </c>
       <c r="J116" s="13" t="n">
-        <v>1.45</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3149.7</v>
+        <v>3047.7</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3105</v>
+        <v>3047.7</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3114.7</v>
+        <v>3089</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3032.2</v>
+        <v>3035</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3047.7</v>
+        <v>3038.4</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-102</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>-3.24</v>
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>295.05</v>
+        <v>292.85</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>293.95</v>
+        <v>292.85</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>296.25</v>
+        <v>294.2</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>291.35</v>
+        <v>285.15</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>292.85</v>
+        <v>289.4</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="J118" s="10" t="n">
-        <v>-0.75</v>
+        <v>-3.45</v>
+      </c>
+      <c r="J118" s="13" t="n">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>772.5</v>
+        <v>778.9</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>774.95</v>
+        <v>783.9</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>780.1</v>
+        <v>787.1</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>765.65</v>
+        <v>769.4</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>778.9</v>
+        <v>783.3</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J119" s="13" t="n">
-        <v>0.83</v>
+        <v>4.4</v>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13337</v>
+        <v>13160</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13250</v>
+        <v>13200</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13358</v>
+        <v>13253</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13125</v>
+        <v>12978</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13160</v>
+        <v>13048</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-177</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>-1.33</v>
+        <v>-112</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="10" t="n">
+      <c r="J121" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2783.2</v>
+        <v>2791.4</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>2771</v>
+        <v>2791.6</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>2852</v>
+        <v>2813.3</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2765.5</v>
+        <v>2756</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>2791.4</v>
+        <v>2760.9</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>8.199999999999999</v>
+        <v>-30.5</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>0.29</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>476.65</v>
+        <v>472.2</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>476</v>
+        <v>470.8</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>477.75</v>
+        <v>477.95</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>469.55</v>
+        <v>463.25</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>472.2</v>
+        <v>467.1</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-4.45</v>
-      </c>
-      <c r="J123" s="10" t="n">
-        <v>-0.93</v>
+        <v>-5.1</v>
+      </c>
+      <c r="J123" s="13" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1627.4</v>
+        <v>1595.4</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1620</v>
+        <v>1582.6</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1625.2</v>
+        <v>1605.5</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1588</v>
+        <v>1566.6</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1595.4</v>
+        <v>1587.3</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-32</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>-1.97</v>
+        <v>-8.1</v>
+      </c>
+      <c r="J124" s="13" t="n">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1147.25</v>
+        <v>1137.4</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1146.45</v>
+        <v>1148.05</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1159.9</v>
+        <v>1154.9</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1130.25</v>
+        <v>1123.55</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1137.4</v>
+        <v>1130.15</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-9.85</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>-0.86</v>
+        <v>-7.25</v>
+      </c>
+      <c r="J125" s="13" t="n">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>131.76</v>
+        <v>127.22</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>131.76</v>
+        <v>128.07</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>131.76</v>
+        <v>129.1</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>126.11</v>
+        <v>125.33</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>127.22</v>
+        <v>125.7</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-4.54</v>
-      </c>
-      <c r="J126" s="10" t="n">
-        <v>-3.45</v>
+        <v>-1.52</v>
+      </c>
+      <c r="J126" s="13" t="n">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2331</v>
+        <v>2277</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2331</v>
+        <v>2266</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2360.2</v>
+        <v>2284.2</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2270.7</v>
+        <v>2130</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2277</v>
+        <v>2175.8</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-54</v>
-      </c>
-      <c r="J127" s="10" t="n">
-        <v>-2.32</v>
+        <v>-101.2</v>
+      </c>
+      <c r="J127" s="13" t="n">
+        <v>-4.44</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>137040</v>
+        <v>134615</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>136880</v>
+        <v>134615</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>136890</v>
+        <v>135770</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>134205</v>
+        <v>131740</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>134615</v>
+        <v>132145</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-2425</v>
-      </c>
-      <c r="J128" s="10" t="n">
-        <v>-1.77</v>
+        <v>-2470</v>
+      </c>
+      <c r="J128" s="13" t="n">
+        <v>-1.83</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3586.9</v>
+        <v>3561.4</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3579</v>
+        <v>3589.5</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3609</v>
+        <v>3589.5</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3544</v>
+        <v>3443.3</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3561.4</v>
+        <v>3493.5</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-25.5</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>-0.71</v>
+        <v>-67.90000000000001</v>
+      </c>
+      <c r="J129" s="13" t="n">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>435.95</v>
+        <v>439.25</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>435</v>
+        <v>436.05</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>443.15</v>
+        <v>439.95</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>432.35</v>
+        <v>428.2</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>439.25</v>
+        <v>437.05</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>3.3</v>
+        <v>-2.2</v>
       </c>
       <c r="J130" s="13" t="n">
-        <v>0.76</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1052.7</v>
+        <v>1018.05</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1041.7</v>
+        <v>1015</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1044.95</v>
+        <v>1016.3</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>1014.3</v>
+        <v>979.35</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1018.05</v>
+        <v>984.95</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-34.65</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>-3.29</v>
+        <v>-33.1</v>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6267</v>
+        <v>6280.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>6280</v>
+        <v>6309</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>6389.5</v>
+        <v>6515</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6250.5</v>
+        <v>6262</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>6280.5</v>
+        <v>6452</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J132" s="13" t="n">
-        <v>0.22</v>
+        <v>171.5</v>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>2.73</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1395.8</v>
+        <v>1410.5</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1388.9</v>
+        <v>1420</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1415</v>
+        <v>1430.9</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1382.1</v>
+        <v>1409.1</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1410.5</v>
+        <v>1421.3</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="J133" s="13" t="n">
-        <v>1.05</v>
+        <v>10.8</v>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>88.59</v>
+        <v>87.31</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>88.41</v>
+        <v>87.5</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>88.54000000000001</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>86.63</v>
+        <v>86.7</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>87.31</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-1.28</v>
+        <v>1.98</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>-1.44</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>405.4</v>
+        <v>402.25</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>404</v>
+        <v>404.75</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>405.9</v>
+        <v>405.25</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>400.4</v>
+        <v>399.2</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>402.25</v>
+        <v>401.85</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-3.15</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>-0.78</v>
+        <v>-0.4</v>
+      </c>
+      <c r="J135" s="13" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1733.6</v>
+        <v>1707.7</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1736.9</v>
+        <v>1712.1</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1736.9</v>
+        <v>1735.5</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1701.4</v>
+        <v>1681.7</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1707.7</v>
+        <v>1687</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-25.9</v>
-      </c>
-      <c r="J136" s="10" t="n">
-        <v>-1.49</v>
+        <v>-20.7</v>
+      </c>
+      <c r="J136" s="13" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>8126.5</v>
+        <v>8791.5</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>8430</v>
+        <v>8820</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>8900</v>
+        <v>9013.5</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>8261</v>
+        <v>8752.5</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>8791.5</v>
+        <v>8949</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>665</v>
-      </c>
-      <c r="J137" s="13" t="n">
-        <v>8.18</v>
+        <v>157.5</v>
+      </c>
+      <c r="J137" s="10" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>283.65</v>
+        <v>286.25</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>284.85</v>
+        <v>288.8</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>289.8</v>
+        <v>288.8</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>284.05</v>
+        <v>283.9</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>286.25</v>
+        <v>284.8</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>2.6</v>
+        <v>-1.45</v>
       </c>
       <c r="J138" s="13" t="n">
-        <v>0.92</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37855</v>
+        <v>37965</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37830</v>
+        <v>37900</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>38285</v>
+        <v>38250</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>37270</v>
+        <v>37565</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37965</v>
+        <v>37665</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>110</v>
+        <v>-300</v>
       </c>
       <c r="J139" s="13" t="n">
-        <v>0.29</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="10" t="n">
+      <c r="J140" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5073.3</v>
+        <v>5065.2</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5081</v>
+        <v>5062.1</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5119.4</v>
+        <v>5090</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5011</v>
+        <v>4734</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5065.2</v>
+        <v>4747.3</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>-0.16</v>
+        <v>-317.9</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>-6.28</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>279.55</v>
+        <v>275.81</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>277.54</v>
+        <v>276</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>279.9</v>
+        <v>276.9</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>273.41</v>
+        <v>271.1</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>275.81</v>
+        <v>273.45</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-3.74</v>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v>-1.34</v>
+        <v>-2.36</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>470.3</v>
+        <v>469.8</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>467.5</v>
+        <v>469.55</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>472.3</v>
+        <v>471.15</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>466.1</v>
+        <v>462.3</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>469.8</v>
+        <v>469.35</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J143" s="10" t="n">
-        <v>-0.11</v>
+        <v>-0.45</v>
+      </c>
+      <c r="J143" s="13" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1419</v>
+        <v>1402.1</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1412</v>
+        <v>1408.9</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1396.8</v>
+        <v>1389.4</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1402.1</v>
+        <v>1394.3</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="J144" s="10" t="n">
-        <v>-1.19</v>
+        <v>-7.8</v>
+      </c>
+      <c r="J144" s="13" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3057.3</v>
+        <v>3069.6</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3047.3</v>
+        <v>3071.1</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3089.9</v>
+        <v>3134.8</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3036.1</v>
+        <v>3070</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3069.6</v>
+        <v>3081.2</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J145" s="13" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="J145" s="10" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>114.67</v>
+        <v>112.71</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>114.2</v>
+        <v>112.71</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>114.39</v>
+        <v>113.45</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>111.57</v>
+        <v>111.6</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>112.71</v>
+        <v>113.09</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-1.96</v>
+        <v>0.38</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>-1.71</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8038</v>
+        <v>7963.5</v>
       </c>
       <c r="E147" s="9" t="n">
         <v>8000</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8125</v>
+        <v>8088</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>7950</v>
+        <v>7901</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>7963.5</v>
+        <v>8033</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-74.5</v>
+        <v>69.5</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>-0.93</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>319.75</v>
+        <v>319.15</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>321.85</v>
+        <v>317.9</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>318.05</v>
+        <v>314.5</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>319.15</v>
+        <v>316.4</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v>-0.19</v>
+        <v>-2.75</v>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>990.3</v>
+        <v>1005</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>993</v>
+        <v>1010</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1010.25</v>
+        <v>1012.1</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>989.65</v>
+        <v>992.9</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1005</v>
+        <v>1004.15</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>14.7</v>
+        <v>-0.85</v>
       </c>
       <c r="J149" s="13" t="n">
-        <v>1.48</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>317.65</v>
+        <v>312.45</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>315.4</v>
+        <v>313.4</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>316.4</v>
+        <v>324.4</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>311.2</v>
+        <v>307.7</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>312.45</v>
+        <v>321.4</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-5.2</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>-1.64</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>383.35</v>
+        <v>376.45</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>381.85</v>
+        <v>377</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>386.1</v>
+        <v>378.75</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>375.85</v>
+        <v>369.05</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>376.45</v>
+        <v>374</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>-1.8</v>
+        <v>-2.45</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1362.1</v>
+        <v>1343.4</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1346</v>
+        <v>1340</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1355.5</v>
+        <v>1345.9</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1340.7</v>
+        <v>1325</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1343.4</v>
+        <v>1327.8</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-18.7</v>
-      </c>
-      <c r="J152" s="10" t="n">
-        <v>-1.37</v>
+        <v>-15.6</v>
+      </c>
+      <c r="J152" s="13" t="n">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>176.23</v>
+        <v>176.45</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>174.71</v>
+        <v>176.5</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>178.09</v>
+        <v>179.07</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>173.8</v>
+        <v>176</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>176.45</v>
+        <v>178.46</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="J153" s="13" t="n">
-        <v>0.12</v>
+        <v>2.01</v>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>686.2</v>
+        <v>680.55</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>686</v>
+        <v>681.25</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>689.7</v>
+        <v>687.9</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>678.95</v>
+        <v>666</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>680.55</v>
+        <v>670.3</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-5.65</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>-0.82</v>
+        <v>-10.25</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1884.8</v>
+        <v>1828.1</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1865</v>
+        <v>1817</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1886.7</v>
+        <v>1836.3</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1807.7</v>
+        <v>1762.1</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1828.1</v>
+        <v>1768.9</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-56.7</v>
-      </c>
-      <c r="J155" s="10" t="n">
-        <v>-3.01</v>
+        <v>-59.2</v>
+      </c>
+      <c r="J155" s="13" t="n">
+        <v>-3.24</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1103.3</v>
+        <v>1094.25</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1095</v>
+        <v>1091.35</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1101.9</v>
+        <v>1106</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1082.2</v>
+        <v>1090.05</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1094.25</v>
+        <v>1101.1</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-9.050000000000001</v>
+        <v>6.85</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>-0.82</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>25735</v>
+        <v>25470</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25605</v>
+        <v>25470</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25850</v>
+        <v>25550</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>25125</v>
+        <v>24815</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>25470</v>
+        <v>24950</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-265</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>-1.03</v>
+        <v>-520</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1044.55</v>
+        <v>1009.3</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1044.9</v>
+        <v>1006.95</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1044.9</v>
+        <v>1030.4</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1006.35</v>
+        <v>983.55</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1009.3</v>
+        <v>1011.3</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-35.25</v>
+        <v>2</v>
       </c>
       <c r="J158" s="10" t="n">
-        <v>-3.37</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3844.3</v>
+        <v>3864.4</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3849</v>
+        <v>3882</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3901</v>
+        <v>3893.6</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3811.5</v>
+        <v>3767.9</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3864.4</v>
+        <v>3808.9</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>20.1</v>
+        <v>-55.5</v>
       </c>
       <c r="J159" s="13" t="n">
-        <v>0.52</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2492.8</v>
+        <v>2542.4</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2484.3</v>
+        <v>2559</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2549.9</v>
+        <v>2563.7</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2466</v>
+        <v>2472.2</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2542.4</v>
+        <v>2493.6</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>49.6</v>
+        <v>-48.8</v>
       </c>
       <c r="J160" s="13" t="n">
-        <v>1.99</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1669.8</v>
+        <v>1680.1</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1669</v>
+        <v>1670.4</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1713</v>
+        <v>1673.3</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1661.2</v>
+        <v>1613.6</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1680.1</v>
+        <v>1620.4</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>10.3</v>
+        <v>-59.7</v>
       </c>
       <c r="J161" s="13" t="n">
-        <v>0.62</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>652.45</v>
+        <v>625.85</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>648.95</v>
+        <v>625.85</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>653.5</v>
+        <v>625.85</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>621</v>
+        <v>594.55</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>625.85</v>
+        <v>600.15</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-26.6</v>
-      </c>
-      <c r="J162" s="10" t="n">
-        <v>-4.08</v>
+        <v>-25.7</v>
+      </c>
+      <c r="J162" s="13" t="n">
+        <v>-4.11</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>435.95</v>
+        <v>428.35</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>442.4</v>
+        <v>432.55</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>427</v>
+        <v>417.45</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>428.35</v>
+        <v>421.2</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="J163" s="10" t="n">
-        <v>-1.74</v>
+        <v>-7.15</v>
+      </c>
+      <c r="J163" s="13" t="n">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>709.85</v>
+        <v>707.7</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>709.85</v>
+        <v>709</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>721.65</v>
+        <v>713.25</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>705</v>
+        <v>690.3</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>707.7</v>
+        <v>693.25</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J164" s="10" t="n">
-        <v>-0.3</v>
+        <v>-14.45</v>
+      </c>
+      <c r="J164" s="13" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1525</v>
+        <v>1580.7</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1535</v>
+        <v>1590</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1612</v>
+        <v>1595</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1511.8</v>
+        <v>1490.9</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1580.7</v>
+        <v>1520.6</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>55.7</v>
+        <v>-60.1</v>
       </c>
       <c r="J165" s="13" t="n">
-        <v>3.65</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1178.6</v>
+        <v>1184.4</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1178</v>
+        <v>1185</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1188.9</v>
+        <v>1197</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1160.1</v>
+        <v>1162</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1184.4</v>
+        <v>1174</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>5.8</v>
+        <v>-10.4</v>
       </c>
       <c r="J166" s="13" t="n">
-        <v>0.49</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="10" t="n">
+      <c r="J167" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>436.05</v>
+        <v>430.3</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>435.5</v>
+        <v>431</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>437.8</v>
+        <v>436.7</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>427.55</v>
+        <v>426</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>430.3</v>
+        <v>435</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-5.75</v>
+        <v>4.7</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>-1.32</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>213.03</v>
+        <v>210.91</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>213.04</v>
+        <v>211</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>213.1</v>
+        <v>212</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>210.16</v>
+        <v>208.6</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>210.91</v>
+        <v>210.07</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="J169" s="10" t="n">
-        <v>-1</v>
+        <v>-0.84</v>
+      </c>
+      <c r="J169" s="13" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2538.5</v>
+        <v>2521.8</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2529</v>
+        <v>2488</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2559.5</v>
+        <v>2505</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2516.3</v>
+        <v>2388.8</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2521.8</v>
+        <v>2396.9</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-16.7</v>
-      </c>
-      <c r="J170" s="10" t="n">
-        <v>-0.66</v>
+        <v>-124.9</v>
+      </c>
+      <c r="J170" s="13" t="n">
+        <v>-4.95</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1462.6</v>
+        <v>1421.5</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1470.2</v>
+        <v>1407.1</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1473.9</v>
+        <v>1426.7</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1413.9</v>
+        <v>1347.4</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1421.5</v>
+        <v>1358.5</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-41.1</v>
-      </c>
-      <c r="J171" s="10" t="n">
-        <v>-2.81</v>
+        <v>-63</v>
+      </c>
+      <c r="J171" s="13" t="n">
+        <v>-4.43</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>3024.4</v>
+        <v>3086.8</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>3037.9</v>
+        <v>3086.8</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3153</v>
+        <v>3129.8</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>3032</v>
+        <v>2897.1</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>3086.8</v>
+        <v>2968.7</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>62.4</v>
+        <v>-118.1</v>
       </c>
       <c r="J172" s="13" t="n">
-        <v>2.06</v>
+        <v>-3.83</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4454.6</v>
+        <v>4456.5</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4411</v>
+        <v>4475.5</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4474</v>
+        <v>4486.6</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4393.5</v>
+        <v>4361.4</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4456.5</v>
+        <v>4410</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>1.9</v>
+        <v>-46.5</v>
       </c>
       <c r="J173" s="13" t="n">
-        <v>0.04</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4084.6</v>
+        <v>4147.2</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4068.6</v>
+        <v>4151</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4174</v>
+        <v>4158</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4065.1</v>
+        <v>4097.4</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4147.2</v>
+        <v>4117.2</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>62.6</v>
+        <v>-30</v>
       </c>
       <c r="J174" s="13" t="n">
-        <v>1.53</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1657.4</v>
+        <v>1737</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1648.1</v>
+        <v>1737</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1741</v>
+        <v>1744.4</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1645.1</v>
+        <v>1675</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1737</v>
+        <v>1699.5</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>79.59999999999999</v>
+        <v>-37.5</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>4.8</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4434.5</v>
+        <v>4251.4</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4440</v>
+        <v>4260</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4479.4</v>
+        <v>4344</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4225</v>
+        <v>4200</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4251.4</v>
+        <v>4297.3</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-183.1</v>
+        <v>45.9</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-4.13</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3660.7</v>
+        <v>3513</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3636</v>
+        <v>3513</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3636</v>
+        <v>3543.3</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3482.2</v>
+        <v>3462.7</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3513</v>
+        <v>3488.2</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-147.7</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>-4.03</v>
+        <v>-24.8</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1500</v>
+        <v>1483.2</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1500</v>
+        <v>1497.9</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1506.3</v>
+        <v>1498.9</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1478.6</v>
+        <v>1465</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1483.2</v>
+        <v>1477.1</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-16.8</v>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v>-1.12</v>
+        <v>-6.1</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>12193</v>
+        <v>12167</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>12105</v>
+        <v>12203</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>12213</v>
+        <v>12246</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11936</v>
+        <v>11954</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>12167</v>
+        <v>11998</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-26</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>-0.21</v>
+        <v>-169</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>-1.39</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>194.05</v>
+        <v>179.71</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>194.89</v>
+        <v>179.3</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>194.89</v>
+        <v>180.75</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>177.3</v>
+        <v>174.4</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>179.71</v>
+        <v>177</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-14.34</v>
-      </c>
-      <c r="J180" s="10" t="n">
-        <v>-7.39</v>
+        <v>-2.71</v>
+      </c>
+      <c r="J180" s="13" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>653.85</v>
+        <v>642.05</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>653.5</v>
+        <v>643.6</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>656.55</v>
+        <v>645.15</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>638.45</v>
+        <v>629.95</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>642.05</v>
+        <v>631.4</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="J181" s="10" t="n">
-        <v>-1.8</v>
+        <v>-10.65</v>
+      </c>
+      <c r="J181" s="13" t="n">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>757</v>
+        <v>735.6</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>758.8</v>
+        <v>734.95</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>758.8</v>
+        <v>734.95</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>733.05</v>
+        <v>707.6</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>735.6</v>
+        <v>720.95</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-21.4</v>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>-2.83</v>
+        <v>-14.65</v>
+      </c>
+      <c r="J182" s="13" t="n">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1481.6</v>
+        <v>1445.5</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1476</v>
+        <v>1452.9</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1476.5</v>
+        <v>1470</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1429.6</v>
+        <v>1431.9</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1445.5</v>
+        <v>1464</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-36.1</v>
+        <v>18.5</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>-2.44</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>204</v>
+        <v>202.76</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>204</v>
+        <v>202.75</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>204.9</v>
+        <v>202.75</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>202.3</v>
+        <v>197.88</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>202.76</v>
+        <v>199.36</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="J184" s="10" t="n">
-        <v>-0.61</v>
+        <v>-3.4</v>
+      </c>
+      <c r="J184" s="13" t="n">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="10" t="n">
+      <c r="J185" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>929.9</v>
+        <v>946.35</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>927</v>
+        <v>948</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>962.9</v>
+        <v>951.75</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>921.7</v>
+        <v>922.55</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>946.35</v>
+        <v>927.4</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>16.45</v>
+        <v>-18.95</v>
       </c>
       <c r="J186" s="13" t="n">
-        <v>1.77</v>
+        <v>-2</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  23-Apr-2026 03:12 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  24-Apr-2026 02:45 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23-Apr-2026 03:12 PM</t>
+          <t>24-Apr-2026 02:45 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 24-Apr-2026 02:45 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 27-Apr-2026 03:07 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>24-Apr-2026 02:45 PM</t>
+          <t>27-Apr-2026 03:07 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  24-Apr-2026 02:45 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  27-Apr-2026 03:07 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>465.9</v>
+        <v>472.75</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>470.3</v>
+        <v>478</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>476.35</v>
+        <v>498.35</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>458.55</v>
+        <v>477.1</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>472.75</v>
+        <v>488.75</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>6.85</v>
+        <v>16</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>1.47</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7575.5</v>
+        <v>7328.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7575.5</v>
+        <v>7330.5</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7594</v>
+        <v>7475</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7304</v>
+        <v>7282.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7328.5</v>
+        <v>7430.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-247</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>-3.26</v>
+        <v>102</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>1.39</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25410</v>
+        <v>25180</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25390</v>
+        <v>25320</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25510</v>
+        <v>25560</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25150</v>
+        <v>25180</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25180</v>
+        <v>25425</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-230</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>-0.91</v>
+        <v>245</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>349.75</v>
+        <v>340.6</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>349.95</v>
+        <v>342</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>351.55</v>
+        <v>348.95</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>338.65</v>
+        <v>337.95</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>340.6</v>
+        <v>342.55</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-9.15</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>-2.62</v>
+        <v>1.95</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>63.2</v>
+        <v>61.79</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>63.45</v>
+        <v>62.54</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>63.79</v>
+        <v>64.66</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>61.41</v>
+        <v>62.33</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>61.79</v>
+        <v>63.92</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>-2.23</v>
+        <v>2.13</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>3.45</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1423.1</v>
+        <v>1412.7</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1429</v>
+        <v>1459.6</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1398.8</v>
+        <v>1416.4</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1412.7</v>
+        <v>1439.8</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>-0.73</v>
+        <v>27.1</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>1.92</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2300</v>
+        <v>2287.6</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2310.2</v>
+        <v>2300.2</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2321.4</v>
+        <v>2337</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2227</v>
+        <v>2286</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2287.6</v>
+        <v>2321.8</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>-0.54</v>
+        <v>34.2</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1602.9</v>
+        <v>1585.1</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1612</v>
+        <v>1600</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1618.8</v>
+        <v>1649.9</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1556.5</v>
+        <v>1593</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1585.1</v>
+        <v>1628.5</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-17.8</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>-1.11</v>
+        <v>43.4</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>2.74</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5520.5</v>
+        <v>5235</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5572.5</v>
+        <v>5280</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5578.5</v>
+        <v>5486</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5193.5</v>
+        <v>5248</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5235</v>
+        <v>5344</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-285.5</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>-5.17</v>
+        <v>109</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>450.4</v>
+        <v>451.2</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>451</v>
+        <v>453.5</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>457.7</v>
+        <v>468.8</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>440.4</v>
+        <v>453.45</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>451.2</v>
+        <v>460.5</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>0.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.18</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>321.21</v>
+        <v>314.52</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>322.81</v>
+        <v>316.85</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>323</v>
+        <v>322.98</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>309.51</v>
+        <v>316.52</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>314.52</v>
+        <v>318.64</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-6.69</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>-2.08</v>
+        <v>4.12</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>1.31</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2022.9</v>
+        <v>2004.5</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2028</v>
+        <v>2015</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2039.5</v>
+        <v>2050</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1979</v>
+        <v>1985</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>2004.5</v>
+        <v>1987.7</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-18.4</v>
+        <v>-16.8</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>-0.91</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7781</v>
+        <v>7732.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7814</v>
+        <v>7759</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7845</v>
+        <v>7850</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7684.5</v>
+        <v>7735</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7732.5</v>
+        <v>7825</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>-0.62</v>
+        <v>92.5</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>432.45</v>
+        <v>423.85</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>432.45</v>
+        <v>426.2</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>434.2</v>
+        <v>430.25</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>421.9</v>
+        <v>424.7</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>423.85</v>
+        <v>428.55</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>-1.99</v>
+        <v>4.7</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>170.63</v>
+        <v>169.9</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>170.69</v>
+        <v>170.68</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>172.2</v>
+        <v>171.49</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>168.37</v>
+        <v>167.75</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>169.9</v>
+        <v>169.3</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-0.73</v>
+        <v>-0.6</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>-0.43</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2521.4</v>
+        <v>2485.1</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2521.4</v>
+        <v>2503</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2538.9</v>
+        <v>2519.8</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2470.7</v>
+        <v>2475.5</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2485.1</v>
+        <v>2485.2</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-36.3</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>-1.44</v>
+        <v>0.1</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1574.9</v>
+        <v>1563.2</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1578.3</v>
+        <v>1565</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1591</v>
+        <v>1598</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1551.9</v>
+        <v>1530</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1563.2</v>
+        <v>1535</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-11.7</v>
+        <v>-28.2</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>-0.74</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>621.7</v>
+        <v>626.85</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>629.7</v>
+        <v>649</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>604.4</v>
+        <v>626</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>626.85</v>
+        <v>635.6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>5.15</v>
+        <v>8.75</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.83</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6727</v>
+        <v>6680.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6798</v>
+        <v>6750</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6999</v>
+        <v>6770</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6605</v>
+        <v>6554.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6680.5</v>
+        <v>6700</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-46.5</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>19.5</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1056.25</v>
+        <v>1065.65</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1058.7</v>
+        <v>1057</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1079.55</v>
+        <v>1059.9</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1047.25</v>
+        <v>1028</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1065.65</v>
+        <v>1043</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>0.89</v>
+        <v>-22.65</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1435.4</v>
+        <v>1413.8</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1436.9</v>
+        <v>1414.9</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1446</v>
+        <v>1433.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1411.7</v>
+        <v>1386.6</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1413.8</v>
+        <v>1416.7</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-21.6</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>-1.5</v>
+        <v>2.9</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1369.6</v>
+        <v>1365.9</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1369</v>
+        <v>1325</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1375</v>
+        <v>1327.3</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1350</v>
+        <v>1299.9</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1365.9</v>
+        <v>1324.2</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-3.7</v>
+        <v>-41.7</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>-0.27</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>9550.5</v>
+        <v>9576</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>9600</v>
+        <v>9642.5</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>9663</v>
+        <v>9715</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>9528</v>
+        <v>9617</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>9576</v>
+        <v>9662</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>25.5</v>
+        <v>86</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.27</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1792.6</v>
+        <v>1770.7</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1792.7</v>
+        <v>1781</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1799.9</v>
+        <v>1798</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1757.3</v>
+        <v>1765</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1770.7</v>
+        <v>1772.2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-21.9</v>
-      </c>
-      <c r="J26" s="13" t="n">
-        <v>-1.22</v>
+        <v>1.5</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>918.35</v>
+        <v>921.55</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>920</v>
+        <v>923.05</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>924.7</v>
+        <v>928.95</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>909.8</v>
+        <v>908.3</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>921.55</v>
+        <v>921.8</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>3.2</v>
+        <v>0.25</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.35</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2265.4</v>
+        <v>2225.4</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2275</v>
+        <v>2249.9</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2284</v>
+        <v>2255.9</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2187</v>
+        <v>2215.5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2225.4</v>
+        <v>2223.4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-40</v>
+        <v>-2</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>-1.77</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>540.3</v>
+        <v>516.1</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>540.15</v>
+        <v>516.1</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>507</v>
+        <v>516.1</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>516.1</v>
+        <v>520.5</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-24.2</v>
-      </c>
-      <c r="J29" s="13" t="n">
-        <v>-4.48</v>
+        <v>4.4</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>173.9</v>
+        <v>174.67</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>173.81</v>
+        <v>174.6</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>175.08</v>
+        <v>182.6</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>168.8</v>
+        <v>174.07</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>174.67</v>
+        <v>181.87</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0.77</v>
+        <v>7.2</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.44</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>276.34</v>
+        <v>274.13</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>276.2</v>
+        <v>275.19</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>276.8</v>
+        <v>277.2</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>269.55</v>
+        <v>272.7</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>274.13</v>
+        <v>273.99</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-2.21</v>
+        <v>-0.14</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>-0.8</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>449.95</v>
+        <v>444.45</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>451.2</v>
+        <v>448.3</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>438.75</v>
+        <v>432.95</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>444.45</v>
+        <v>435.6</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-5.5</v>
+        <v>-8.85</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>-1.22</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>468.65</v>
+        <v>460.4</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>468.65</v>
+        <v>460.4</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>474.6</v>
+        <v>466.75</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>458.2</v>
+        <v>459</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>460.4</v>
+        <v>463.6</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-8.25</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>-1.76</v>
+        <v>3.2</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1841.2</v>
+        <v>1814.5</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1845</v>
+        <v>1816.1</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1850.7</v>
+        <v>1828.4</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1807.3</v>
+        <v>1814</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1814.5</v>
+        <v>1820.1</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-26.7</v>
-      </c>
-      <c r="J34" s="13" t="n">
-        <v>-1.45</v>
+        <v>5.6</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>337.6</v>
+        <v>337.39</v>
       </c>
       <c r="E35" s="9" t="n">
+        <v>339.43</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>354</v>
+      </c>
+      <c r="G35" s="9" t="n">
         <v>339</v>
       </c>
-      <c r="F35" s="9" t="n">
-        <v>340.49</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>333.02</v>
-      </c>
       <c r="H35" s="9" t="n">
-        <v>337.39</v>
+        <v>348.58</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>-0.06</v>
+        <v>11.19</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>3.32</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>358</v>
+        <v>349.85</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>358.05</v>
+        <v>351.25</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>358.95</v>
+        <v>362.55</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>348.5</v>
+        <v>350.5</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>349.85</v>
+        <v>362</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-8.15</v>
-      </c>
-      <c r="J36" s="13" t="n">
-        <v>-2.28</v>
+        <v>12.15</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>3.47</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>37380</v>
+        <v>36690</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>37495</v>
+        <v>36800</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>37690</v>
+        <v>37460</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>36295</v>
+        <v>36730</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>36690</v>
+        <v>37225</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-690</v>
-      </c>
-      <c r="J37" s="13" t="n">
-        <v>-1.85</v>
+        <v>535</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>309.8</v>
+        <v>308.1</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>309</v>
+        <v>308.3</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>310.75</v>
+        <v>315.1</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>300.15</v>
+        <v>306.7</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>308.1</v>
+        <v>312.65</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J38" s="13" t="n">
-        <v>-0.55</v>
+        <v>4.55</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5671.5</v>
+        <v>5730.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5707.5</v>
+        <v>5750</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5753.5</v>
+        <v>5804</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5665.5</v>
+        <v>5689</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5730.5</v>
+        <v>5717.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>1.04</v>
+        <v>-13</v>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>385</v>
+        <v>368.65</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>385</v>
+        <v>368.95</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>385.95</v>
+        <v>378.4</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>366.2</v>
+        <v>368.95</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>368.65</v>
+        <v>371.85</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-16.35</v>
-      </c>
-      <c r="J40" s="13" t="n">
-        <v>-4.25</v>
+        <v>3.2</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>140.87</v>
+        <v>140.85</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>141.33</v>
+        <v>141.19</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>141.86</v>
+        <v>142.42</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>138.15</v>
+        <v>139.81</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>140.85</v>
+        <v>140.52</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.02</v>
+        <v>-0.33</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>-0.01</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>899.8</v>
+        <v>909.6</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>903</v>
+        <v>909.2</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>913.5</v>
+        <v>943.9</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>876.3</v>
+        <v>897.1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>909.6</v>
+        <v>915.45</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>9.800000000000001</v>
+        <v>5.85</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1.09</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>446.95</v>
+        <v>440.8</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>449.9</v>
+        <v>441.05</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>450.2</v>
+        <v>448</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>439</v>
+        <v>441.05</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>440.8</v>
+        <v>445.95</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-6.15</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>-1.38</v>
+        <v>5.15</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1543.4</v>
+        <v>1568.2</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1546.9</v>
+        <v>1570.5</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1575</v>
+        <v>1577.8</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1529.9</v>
+        <v>1534.8</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1568.2</v>
+        <v>1560.7</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>1.61</v>
+        <v>-7.5</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1305.9</v>
+        <v>1295</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1295</v>
+        <v>1303.2</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1303.9</v>
+        <v>1320.7</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1254.1</v>
+        <v>1299</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1295</v>
+        <v>1317.2</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>-0.83</v>
+        <v>22.2</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
+        <v>456</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>458.5</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>460.65</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>450.65</v>
       </c>
-      <c r="E46" s="12" t="n">
-        <v>452.75</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>462</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>451.05</v>
-      </c>
       <c r="H46" s="12" t="n">
-        <v>456</v>
+        <v>452.5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>1.19</v>
+        <v>-3.5</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1220.6</v>
+        <v>1150.9</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1211</v>
+        <v>1156</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1214.5</v>
+        <v>1205.9</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1136.3</v>
+        <v>1155.9</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1150.9</v>
+        <v>1202.4</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-69.7</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>-5.71</v>
+        <v>51.5</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>4.47</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2150.2</v>
+        <v>2171.3</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2150.2</v>
+        <v>2180</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2177.8</v>
+        <v>2190.1</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2139</v>
+        <v>2135.4</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2171.3</v>
+        <v>2141</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>0.98</v>
+        <v>-30.3</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>505.05</v>
+        <v>502.8</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>505.05</v>
+        <v>505.15</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>506.9</v>
+        <v>521.8</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>499.05</v>
+        <v>505.15</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>502.8</v>
+        <v>514.2</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>-0.45</v>
+        <v>11.4</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>2.27</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2039.8</v>
+        <v>1995.3</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>2039.8</v>
+        <v>1986</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2054</v>
+        <v>2043.9</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1983</v>
+        <v>1982.4</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1995.3</v>
+        <v>2031.1</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-44.5</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>-2.18</v>
+        <v>35.8</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>253.39</v>
+        <v>250.23</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>254.63</v>
+        <v>253</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>257</v>
+        <v>259.83</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>248.31</v>
+        <v>252.1</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>250.23</v>
+        <v>258.68</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-3.16</v>
-      </c>
-      <c r="J51" s="13" t="n">
-        <v>-1.25</v>
+        <v>8.449999999999999</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>3.38</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>265.52</v>
+        <v>262.51</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>265.52</v>
+        <v>264</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>267.29</v>
+        <v>274.5</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>260</v>
+        <v>263.83</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>262.51</v>
+        <v>271.21</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="J52" s="13" t="n">
-        <v>-1.13</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>3.31</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5176.9</v>
+        <v>5232</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5179</v>
+        <v>5264.5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5250</v>
+        <v>5308.7</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5102.1</v>
+        <v>5200</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5232</v>
+        <v>5233.2</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>55.1</v>
+        <v>1.2</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>1.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>460</v>
+        <v>451.1</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>460</v>
+        <v>452.45</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>462.5</v>
+        <v>457.4</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>448.1</v>
+        <v>451</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>451.1</v>
+        <v>452</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="J54" s="13" t="n">
-        <v>-1.93</v>
+        <v>0.9</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1958.8</v>
+        <v>1962.5</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1971</v>
+        <v>1964.7</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1975.2</v>
+        <v>1999.8</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1919.1</v>
+        <v>1960.2</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1962.5</v>
+        <v>1972.7</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>3.7</v>
+        <v>10.2</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1731.9</v>
+        <v>1690.3</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1723.4</v>
+        <v>1690.3</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1738.9</v>
+        <v>1717.1</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1675.6</v>
+        <v>1680.5</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1690.3</v>
+        <v>1684.9</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-41.6</v>
+        <v>-5.4</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>-2.4</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>81.59999999999999</v>
+        <v>76.69</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>80.88</v>
+        <v>77</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>83.48</v>
+        <v>78.34</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>74.59999999999999</v>
+        <v>75.05</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>76.69</v>
+        <v>75.44</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-4.91</v>
+        <v>-1.25</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>-6.02</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6378.5</v>
+        <v>6361.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6408.5</v>
+        <v>6351.5</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6442.5</v>
+        <v>6507.5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6320</v>
+        <v>6346.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6361.5</v>
+        <v>6477</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-17</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>-0.27</v>
+        <v>115.5</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>1.82</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>10866.5</v>
+        <v>10815.5</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>10857</v>
+        <v>10920</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11086</v>
+        <v>11350</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>10765.5</v>
+        <v>10855</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>10815.5</v>
+        <v>11252</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-51</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>-0.47</v>
+        <v>436.5</v>
+      </c>
+      <c r="J59" s="10" t="n">
+        <v>4.04</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>592.8</v>
+        <v>587.05</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>591.1</v>
+        <v>592.9</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>595.5</v>
+        <v>599.8</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>583.05</v>
+        <v>590.3</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>587.05</v>
+        <v>592.45</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="J60" s="13" t="n">
-        <v>-0.97</v>
+        <v>5.4</v>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1331</v>
+        <v>1317.1</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1293</v>
+        <v>1320.4</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1348.8</v>
+        <v>1350</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1293</v>
+        <v>1309</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1317.1</v>
+        <v>1334.5</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-13.9</v>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v>-1.04</v>
+        <v>17.4</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7092.5</v>
+        <v>7111.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7054.5</v>
+        <v>7150</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7160</v>
+        <v>7214</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7049</v>
+        <v>7102</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7111.5</v>
+        <v>7174</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>19</v>
+        <v>62.5</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>0.27</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3309</v>
+        <v>3231.3</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3309</v>
+        <v>3250</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3349</v>
+        <v>3302.7</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3214</v>
+        <v>3240.1</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3231.3</v>
+        <v>3262.5</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-77.7</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>-2.35</v>
+        <v>31.2</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>347.25</v>
+        <v>342.8</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>346.45</v>
+        <v>345</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>347.95</v>
+        <v>353.7</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>339.4</v>
+        <v>344.8</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>342.8</v>
+        <v>352.35</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-4.45</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>-1.28</v>
+        <v>9.550000000000001</v>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>2.79</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>295.4</v>
+        <v>293</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>296</v>
+        <v>294.7</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>298.3</v>
+        <v>297.65</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>291.25</v>
+        <v>292.8</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>293</v>
+        <v>294.05</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.05</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>164.96</v>
+        <v>165.61</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>165.96</v>
+        <v>166.8</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>166.3</v>
+        <v>167.78</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>163.35</v>
+        <v>164.9</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>165.61</v>
+        <v>165.74</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0.65</v>
+        <v>0.13</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2335</v>
+        <v>2299.5</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2351</v>
+        <v>2312</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2372.8</v>
+        <v>2339.9</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2283.2</v>
+        <v>2290.9</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2299.5</v>
+        <v>2325.1</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-35.5</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>-1.52</v>
+        <v>25.6</v>
+      </c>
+      <c r="J67" s="10" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>481.95</v>
+        <v>468.45</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>486</v>
+        <v>471.45</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>486</v>
+        <v>478.9</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>465.9</v>
+        <v>470.5</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>468.45</v>
+        <v>474.85</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="J69" s="13" t="n">
-        <v>-2.8</v>
+        <v>6.4</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1142.95</v>
+        <v>1089.9</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1143.2</v>
+        <v>1100</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1148</v>
+        <v>1104.55</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>1083.95</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1089.9</v>
+        <v>1089.25</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-53.05</v>
+        <v>-0.65</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>-4.64</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1791</v>
+        <v>1769.4</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1795.6</v>
+        <v>1784</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1832</v>
+        <v>1842.4</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1759.8</v>
+        <v>1778.1</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1769.4</v>
+        <v>1828.2</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-21.6</v>
-      </c>
-      <c r="J71" s="13" t="n">
-        <v>-1.21</v>
+        <v>58.8</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>3.32</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>686.95</v>
+        <v>689.45</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>686.95</v>
+        <v>690</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>694.45</v>
+        <v>710</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>682</v>
+        <v>686.15</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>689.45</v>
+        <v>694.9</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>2.5</v>
+        <v>5.45</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>0.36</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2735</v>
+        <v>2739.3</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2760.7</v>
+        <v>2766</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2768.9</v>
+        <v>2810.9</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2732.1</v>
+        <v>2752.2</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2739.3</v>
+        <v>2778.2</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>4.3</v>
+        <v>38.9</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.16</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>386</v>
+        <v>383.85</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>389</v>
+        <v>385.65</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>391.5</v>
+        <v>385.65</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>374.85</v>
+        <v>379</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>383.85</v>
+        <v>383</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>-2.15</v>
+        <v>-0.85</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4352.5</v>
+        <v>4265.8</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4352.5</v>
+        <v>4280</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4387.3</v>
+        <v>4340.2</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4236.1</v>
+        <v>4280</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4265.8</v>
+        <v>4310.3</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-86.7</v>
-      </c>
-      <c r="J75" s="13" t="n">
-        <v>-1.99</v>
+        <v>44.5</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>1.04</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1260.3</v>
+        <v>1238.6</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1262</v>
+        <v>1248</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1267.4</v>
+        <v>1281.5</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1233</v>
+        <v>1243.1</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1238.6</v>
+        <v>1274.1</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-21.7</v>
-      </c>
-      <c r="J76" s="13" t="n">
-        <v>-1.72</v>
+        <v>35.5</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>2.87</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1253.6</v>
+        <v>1203.2</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1264.4</v>
+        <v>1209</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1264.8</v>
+        <v>1232</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1198.1</v>
+        <v>1201</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1203.2</v>
+        <v>1228.2</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-50.4</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>-4.02</v>
+        <v>25</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2708.2</v>
+        <v>2735</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2700</v>
+        <v>2749.9</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2764</v>
+        <v>2776.5</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2692.9</v>
+        <v>2719.6</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2735</v>
+        <v>2756</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>26.8</v>
+        <v>21</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>784.35</v>
+        <v>784.85</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>777.3</v>
+        <v>787.5</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>787.6</v>
+        <v>793</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>784.85</v>
+        <v>789.8</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>0.5</v>
+        <v>4.95</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>0.06</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>598.65</v>
+        <v>588.2</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>603.15</v>
+        <v>603.45</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>585.6</v>
+        <v>590.1</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>588.2</v>
+        <v>597.3</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-10.45</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>-1.75</v>
+        <v>9.1</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5032</v>
+        <v>4961.5</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5035.5</v>
+        <v>5012.5</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5060.5</v>
+        <v>5098</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>4941.5</v>
+        <v>5005.5</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>4961.5</v>
+        <v>5043</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-70.5</v>
-      </c>
-      <c r="J81" s="13" t="n">
-        <v>-1.4</v>
+        <v>81.5</v>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1041.35</v>
+        <v>1048.35</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1031</v>
+        <v>1058.35</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1054</v>
+        <v>1066.5</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1027.55</v>
+        <v>1052</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1048.35</v>
+        <v>1061.8</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>7</v>
+        <v>13.45</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>0.67</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>549.45</v>
+        <v>541.5</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>551.4</v>
+        <v>546.8</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>554.95</v>
+        <v>562</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>537.45</v>
+        <v>546</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>541.5</v>
+        <v>559.35</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-7.95</v>
-      </c>
-      <c r="J83" s="13" t="n">
-        <v>-1.45</v>
+        <v>17.85</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>376.9</v>
+        <v>373.5</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>376.4</v>
+        <v>384.95</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>368.7</v>
+        <v>372.75</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>373.5</v>
+        <v>380.9</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="J84" s="13" t="n">
-        <v>-0.9</v>
+        <v>7.4</v>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>1.98</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2366.4</v>
+        <v>2327.3</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2388.6</v>
+        <v>2334.9</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2388.6</v>
+        <v>2362.8</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2299</v>
+        <v>2325</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2327.3</v>
+        <v>2328.3</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-39.1</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>-1.65</v>
+        <v>1</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>32650</v>
+        <v>31365</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>32805</v>
+        <v>31365</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>32880</v>
+        <v>31895</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>31215</v>
+        <v>31295</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>31365</v>
+        <v>31850</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-1285</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>-3.94</v>
+        <v>485</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>67.83</v>
+        <v>67.23</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>67.83</v>
+        <v>67.86</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>68.64</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>66.69</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>67.23</v>
+        <v>70.27</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="J87" s="13" t="n">
-        <v>-0.88</v>
+        <v>3.04</v>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>4.52</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>126.92</v>
+        <v>123.23</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>128.4</v>
+        <v>123.19</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>129.7</v>
+        <v>127.3</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>122.34</v>
+        <v>122.38</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>123.23</v>
+        <v>126.45</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-3.69</v>
-      </c>
-      <c r="J88" s="13" t="n">
-        <v>-2.91</v>
+        <v>3.22</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>2.61</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>165.55</v>
+        <v>164.61</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>165.55</v>
+        <v>165.43</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>167.05</v>
+        <v>166.12</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>162.6</v>
+        <v>163.6</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>164.61</v>
+        <v>164.88</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="J89" s="13" t="n">
-        <v>-0.57</v>
+        <v>0.27</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>639.45</v>
+        <v>635.35</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>636.85</v>
+        <v>635.55</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>641.55</v>
+        <v>652.5</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>630.4</v>
+        <v>635.35</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>635.35</v>
+        <v>647.85</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="J90" s="13" t="n">
-        <v>-0.64</v>
+        <v>12.5</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>1.97</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2159.4</v>
+        <v>2107.1</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2164.7</v>
+        <v>2125</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2170</v>
+        <v>2142.4</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2099.6</v>
+        <v>2101</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2107.1</v>
+        <v>2119.5</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-52.3</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>-2.42</v>
+        <v>12.4</v>
+      </c>
+      <c r="J91" s="10" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4556</v>
+        <v>4523.1</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4566.1</v>
+        <v>4522.2</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4598.8</v>
+        <v>4584.3</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>4507</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4523.1</v>
+        <v>4561.2</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-32.9</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>-0.72</v>
+        <v>38.1</v>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>860.35</v>
+        <v>847.95</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>868</v>
+        <v>865.2</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>868</v>
+        <v>903.5</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>839</v>
+        <v>865.2</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>847.95</v>
+        <v>900.15</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="J93" s="13" t="n">
-        <v>-1.44</v>
+        <v>52.2</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>6.16</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>404.7</v>
+        <v>402.2</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>405.9</v>
+        <v>403.45</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>406.6</v>
+        <v>407.5</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>395.65</v>
+        <v>399.5</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>402.2</v>
+        <v>402.3</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="J94" s="13" t="n">
-        <v>-0.62</v>
+        <v>0.1</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1240.6</v>
+        <v>1154.6</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1200</v>
+        <v>1154.6</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1223.9</v>
+        <v>1179.9</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1152.2</v>
+        <v>1154.5</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1154.6</v>
+        <v>1170.3</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-86</v>
-      </c>
-      <c r="J95" s="13" t="n">
-        <v>-6.93</v>
+        <v>15.7</v>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>1.36</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>145.48</v>
+        <v>143.47</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>145.6</v>
+        <v>146.6</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>142.9</v>
+        <v>143.69</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>143.47</v>
+        <v>146.26</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="J96" s="13" t="n">
-        <v>-1.38</v>
+        <v>2.79</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>1.94</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1526.1</v>
+        <v>1555.9</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1535</v>
+        <v>1557.1</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1573.2</v>
+        <v>1585.9</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1516</v>
+        <v>1528.5</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1555.9</v>
+        <v>1541.3</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="J97" s="10" t="n">
-        <v>1.95</v>
+        <v>-14.6</v>
+      </c>
+      <c r="J97" s="13" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>551.35</v>
+        <v>541.2</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>552</v>
+        <v>543.2</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>556</v>
+        <v>546.85</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>539.2</v>
+        <v>541</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>541.2</v>
+        <v>545.1</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-10.15</v>
-      </c>
-      <c r="J98" s="13" t="n">
-        <v>-1.84</v>
+        <v>3.9</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>305.3</v>
+        <v>301.6</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>306.65</v>
+        <v>303.65</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>306.65</v>
+        <v>305.65</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>301.1</v>
+        <v>302.85</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>301.6</v>
+        <v>303.85</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="J99" s="13" t="n">
-        <v>-1.21</v>
+        <v>2.25</v>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1254.5</v>
+        <v>1256</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1252.2</v>
+        <v>1257.9</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1273.1</v>
+        <v>1293.6</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1237.3</v>
+        <v>1257.6</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1256</v>
+        <v>1278.2</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>1.5</v>
+        <v>22.2</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>0.12</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5799</v>
+        <v>5584.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5820</v>
+        <v>5620.5</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5820</v>
+        <v>5645</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5567.5</v>
+        <v>5559</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5584.5</v>
+        <v>5606.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-214.5</v>
-      </c>
-      <c r="J101" s="13" t="n">
-        <v>-3.7</v>
+        <v>22</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>775.8</v>
+        <v>766.3</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>777.3</v>
+        <v>769.5</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>784.75</v>
+        <v>787.9</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>763.55</v>
+        <v>765.15</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>766.3</v>
+        <v>770.4</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="J102" s="13" t="n">
-        <v>-1.22</v>
+        <v>4.1</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>561.4</v>
+        <v>544.95</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>561</v>
+        <v>546.5</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>563.6</v>
+        <v>575.5</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>538.35</v>
+        <v>545</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>544.95</v>
+        <v>573.8</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-16.45</v>
-      </c>
-      <c r="J103" s="13" t="n">
-        <v>-2.93</v>
+        <v>28.85</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>5.29</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1257</v>
+        <v>1255.7</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1264</v>
+        <v>1273</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1268</v>
+        <v>1297</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1246.5</v>
+        <v>1268.1</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1255.7</v>
+        <v>1282.7</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J104" s="13" t="n">
-        <v>-0.1</v>
+        <v>27</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>492.85</v>
+        <v>491.95</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>493.2</v>
+        <v>496</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>496.4</v>
+        <v>498.05</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>483.6</v>
+        <v>483.5</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>491.95</v>
+        <v>485.1</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-0.9</v>
+        <v>-6.85</v>
       </c>
       <c r="J105" s="13" t="n">
-        <v>-0.18</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1191.9</v>
+        <v>1211.15</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1191.9</v>
+        <v>1213</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1219.9</v>
+        <v>1240</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1189.85</v>
+        <v>1213</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1211.15</v>
+        <v>1236.25</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>19.25</v>
+        <v>25.1</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>370.4</v>
+        <v>370.85</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>370.6</v>
+        <v>375</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>372.8</v>
+        <v>380.45</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>367.65</v>
+        <v>373.25</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>370.85</v>
+        <v>376.8</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>0.45</v>
+        <v>5.95</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>0.12</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>733.65</v>
+        <v>709.6</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>733.5</v>
+        <v>713.1</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>733.95</v>
+        <v>740</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>690.15</v>
+        <v>713.1</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>709.6</v>
+        <v>735.3</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-24.05</v>
-      </c>
-      <c r="J108" s="13" t="n">
-        <v>-3.28</v>
+        <v>25.7</v>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>3.62</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1430.9</v>
+        <v>1408.9</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1435.5</v>
+        <v>1405</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1435.5</v>
+        <v>1429</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1399.9</v>
+        <v>1394.1</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1408.9</v>
+        <v>1416</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-22</v>
-      </c>
-      <c r="J109" s="13" t="n">
-        <v>-1.54</v>
+        <v>7.1</v>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1129</v>
+        <v>1113.45</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1129.2</v>
+        <v>1118.8</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1137.2</v>
+        <v>1132.4</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1110.2</v>
+        <v>1106.3</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1113.45</v>
+        <v>1123.55</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-15.55</v>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v>-1.38</v>
+        <v>10.1</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>545.55</v>
+        <v>540.75</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>545.55</v>
+        <v>544</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>549.9</v>
+        <v>545.4</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>533.3</v>
+        <v>534.4</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>540.75</v>
+        <v>543.1</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="J111" s="13" t="n">
-        <v>-0.88</v>
+        <v>2.35</v>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4054.1</v>
+        <v>4014.3</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>4072</v>
+        <v>4058</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4088.1</v>
+        <v>4089.5</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3983.2</v>
+        <v>4030.2</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4014.3</v>
+        <v>4053.6</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-39.8</v>
-      </c>
-      <c r="J112" s="13" t="n">
-        <v>-0.98</v>
+        <v>39.3</v>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>292.12</v>
+        <v>290.05</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>293.9</v>
+        <v>291.7</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>295.01</v>
+        <v>300.83</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>287.22</v>
+        <v>286.81</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>290.05</v>
+        <v>287.79</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-2.07</v>
+        <v>-2.26</v>
       </c>
       <c r="J113" s="13" t="n">
-        <v>-0.71</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="114">
@@ -4607,7 +4607,7 @@
         <v>150</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>4531.5</v>
+        <v>4282.3</v>
       </c>
       <c r="E114" s="12" t="n">
         <v/>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3449.6</v>
+        <v>3379.8</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3450</v>
+        <v>3397.9</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3495</v>
+        <v>3608</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3362</v>
+        <v>3388</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3379.8</v>
+        <v>3589.8</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-69.8</v>
-      </c>
-      <c r="J115" s="13" t="n">
-        <v>-2.02</v>
+        <v>210</v>
+      </c>
+      <c r="J115" s="10" t="n">
+        <v>6.21</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2341.4</v>
+        <v>2296.1</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2347.3</v>
+        <v>2304.9</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2351.5</v>
+        <v>2341</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2262</v>
+        <v>2296.2</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2296.1</v>
+        <v>2324.5</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-45.3</v>
-      </c>
-      <c r="J116" s="13" t="n">
-        <v>-1.93</v>
+        <v>28.4</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3047.7</v>
+        <v>3038.4</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3047.7</v>
+        <v>3050</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3089</v>
+        <v>3114</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3035</v>
+        <v>3050</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3038.4</v>
+        <v>3102.4</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>-0.31</v>
+        <v>64</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>2.11</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>292.85</v>
+        <v>289.4</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>292.85</v>
+        <v>289.5</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>294.2</v>
+        <v>292.95</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>285.15</v>
+        <v>286.75</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>289.4</v>
+        <v>288.2</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-3.45</v>
+        <v>-1.2</v>
       </c>
       <c r="J118" s="13" t="n">
-        <v>-1.18</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>778.9</v>
+        <v>783.3</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>783.9</v>
+        <v>783.3</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>787.1</v>
+        <v>794</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>769.4</v>
+        <v>781.3</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>783.3</v>
+        <v>787</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13160</v>
+        <v>13048</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13200</v>
+        <v>13153</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13253</v>
+        <v>13270</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12978</v>
+        <v>13043</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13048</v>
+        <v>13222</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-112</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>-0.85</v>
+        <v>174</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2791.4</v>
+        <v>2760.9</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>2791.6</v>
+        <v>2786.5</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>2813.3</v>
+        <v>2834.5</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2756</v>
+        <v>2773.8</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>2760.9</v>
+        <v>2830</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>-30.5</v>
-      </c>
-      <c r="J122" s="13" t="n">
-        <v>-1.09</v>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="J122" s="10" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>472.2</v>
+        <v>467.1</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>470.8</v>
+        <v>467.1</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>477.95</v>
+        <v>480</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>463.25</v>
+        <v>463</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>467.1</v>
+        <v>476.5</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="J123" s="13" t="n">
-        <v>-1.08</v>
+        <v>9.4</v>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1595.4</v>
+        <v>1587.3</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1582.6</v>
+        <v>1580.1</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1605.5</v>
+        <v>1605.9</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1566.6</v>
+        <v>1579.5</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1587.3</v>
+        <v>1603</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="J124" s="13" t="n">
-        <v>-0.51</v>
+        <v>15.7</v>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1137.4</v>
+        <v>1130.15</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1148.05</v>
+        <v>1127</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1154.9</v>
+        <v>1150.5</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1123.55</v>
+        <v>1124.5</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1130.15</v>
+        <v>1141.8</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="J125" s="13" t="n">
-        <v>-0.64</v>
+        <v>11.65</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>127.22</v>
+        <v>125.7</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>128.07</v>
+        <v>126.13</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>129.1</v>
+        <v>128.54</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>125.33</v>
+        <v>125.44</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>125.7</v>
+        <v>127.93</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="J126" s="13" t="n">
-        <v>-1.19</v>
+        <v>2.23</v>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>1.77</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2277</v>
+        <v>2175.8</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2266</v>
+        <v>2187.9</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2284.2</v>
+        <v>2275</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2130</v>
+        <v>2185</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2175.8</v>
+        <v>2264.9</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-101.2</v>
-      </c>
-      <c r="J127" s="13" t="n">
-        <v>-4.44</v>
+        <v>89.09999999999999</v>
+      </c>
+      <c r="J127" s="10" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>134615</v>
+        <v>132145</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>134615</v>
+        <v>132550</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>135770</v>
+        <v>133545</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>131740</v>
+        <v>131800</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>132145</v>
+        <v>132205</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-2470</v>
-      </c>
-      <c r="J128" s="13" t="n">
-        <v>-1.83</v>
+        <v>60</v>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3561.4</v>
+        <v>3493.5</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3589.5</v>
+        <v>3501.4</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3589.5</v>
+        <v>3542</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3443.3</v>
+        <v>3480.7</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3493.5</v>
+        <v>3493.8</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-67.90000000000001</v>
-      </c>
-      <c r="J129" s="13" t="n">
-        <v>-1.91</v>
+        <v>0.3</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>439.25</v>
+        <v>437.05</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>436.05</v>
+        <v>442.95</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>439.95</v>
+        <v>445.15</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>428.2</v>
+        <v>439.4</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>437.05</v>
+        <v>441</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="J130" s="13" t="n">
-        <v>-0.5</v>
+        <v>3.95</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1018.05</v>
+        <v>984.95</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1015</v>
+        <v>991.2</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1016.3</v>
+        <v>1023.5</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>979.35</v>
+        <v>990.95</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>984.95</v>
+        <v>1000.9</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-33.1</v>
-      </c>
-      <c r="J131" s="13" t="n">
-        <v>-3.25</v>
+        <v>15.95</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6280.5</v>
+        <v>6452</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>6309</v>
+        <v>6520</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>6515</v>
+        <v>6620</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6262</v>
+        <v>6437.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>6452</v>
+        <v>6578.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>171.5</v>
+        <v>126.5</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>2.73</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1410.5</v>
+        <v>1421.3</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1430.9</v>
+        <v>1437.9</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1409.1</v>
+        <v>1410</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1421.3</v>
+        <v>1417.3</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v>0.77</v>
+        <v>-4</v>
+      </c>
+      <c r="J133" s="13" t="n">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>87.31</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>87.5</v>
+        <v>90.25</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>89.98999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>86.7</v>
+        <v>89.81</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>89.29000000000001</v>
+        <v>90.42</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>1.98</v>
+        <v>1.13</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>2.27</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>402.25</v>
+        <v>401.85</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>404.75</v>
+        <v>403.9</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>405.25</v>
+        <v>414.4</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>399.2</v>
+        <v>402.6</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>401.85</v>
+        <v>410.2</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J135" s="13" t="n">
-        <v>-0.1</v>
+        <v>8.35</v>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1707.7</v>
+        <v>1687</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1712.1</v>
+        <v>1697</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1735.5</v>
+        <v>1735</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1681.7</v>
+        <v>1690</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1687</v>
+        <v>1723.3</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-20.7</v>
-      </c>
-      <c r="J136" s="13" t="n">
-        <v>-1.21</v>
+        <v>36.3</v>
+      </c>
+      <c r="J136" s="10" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>8791.5</v>
+        <v>8949</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>8820</v>
+        <v>9050</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9013.5</v>
+        <v>9490</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>8752.5</v>
+        <v>9010</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>8949</v>
+        <v>9360</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>157.5</v>
+        <v>411</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>1.79</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>286.25</v>
+        <v>284.8</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>288.8</v>
+        <v>286</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>288.8</v>
+        <v>286.7</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>283.9</v>
+        <v>284.2</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>284.8</v>
+        <v>285.9</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="J138" s="13" t="n">
-        <v>-0.51</v>
+        <v>1.1</v>
+      </c>
+      <c r="J138" s="10" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37965</v>
+        <v>37665</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37900</v>
+        <v>37765</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>38250</v>
+        <v>38190</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>37565</v>
+        <v>37325</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37665</v>
+        <v>37705</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-300</v>
-      </c>
-      <c r="J139" s="13" t="n">
-        <v>-0.79</v>
+        <v>40</v>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5065.2</v>
+        <v>4747.3</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5062.1</v>
+        <v>4764.9</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5090</v>
+        <v>4846.6</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4734</v>
+        <v>4751.2</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4747.3</v>
+        <v>4817.5</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-317.9</v>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v>-6.28</v>
+        <v>70.2</v>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>275.81</v>
+        <v>273.45</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>276</v>
+        <v>273.45</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>276.9</v>
+        <v>281.2</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>271.1</v>
+        <v>272.9</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>273.45</v>
+        <v>279.9</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="J142" s="13" t="n">
-        <v>-0.86</v>
+        <v>6.45</v>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>469.8</v>
+        <v>469.35</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>469.55</v>
+        <v>471</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>471.15</v>
+        <v>478.35</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>462.3</v>
+        <v>470.95</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>469.35</v>
+        <v>474.9</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="J143" s="13" t="n">
-        <v>-0.1</v>
+        <v>5.55</v>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1402.1</v>
+        <v>1394.3</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1406</v>
+        <v>1394.3</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1408.9</v>
+        <v>1406.9</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1389.4</v>
+        <v>1390.3</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1394.3</v>
+        <v>1399.3</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="J144" s="13" t="n">
-        <v>-0.5600000000000001</v>
+        <v>5</v>
+      </c>
+      <c r="J144" s="10" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3069.6</v>
+        <v>3081.2</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3071.1</v>
+        <v>3083.3</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3134.8</v>
+        <v>3123.8</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3070</v>
+        <v>3075.1</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3081.2</v>
+        <v>3083.6</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>11.6</v>
+        <v>2.4</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>0.38</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>112.71</v>
+        <v>113.09</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>112.71</v>
+        <v>113.5</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>113.45</v>
+        <v>114.54</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>111.6</v>
+        <v>113.42</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>113.09</v>
+        <v>113.88</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>0.38</v>
+        <v>0.79</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>7963.5</v>
+        <v>8033</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8000</v>
+        <v>8087.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8088</v>
+        <v>8147</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>7901</v>
+        <v>8020</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8033</v>
+        <v>8065.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>69.5</v>
+        <v>32.5</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>0.87</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>319.15</v>
+        <v>316.4</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>317.9</v>
+        <v>324.95</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>314.5</v>
+        <v>316.95</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>316.4</v>
+        <v>320.9</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>-0.86</v>
+        <v>4.5</v>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
+        <v>1004.15</v>
+      </c>
+      <c r="E149" s="9" t="n">
         <v>1005</v>
       </c>
-      <c r="E149" s="9" t="n">
-        <v>1010</v>
-      </c>
       <c r="F149" s="9" t="n">
-        <v>1012.1</v>
+        <v>1029.5</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>992.9</v>
+        <v>1005</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1004.15</v>
+        <v>1018.9</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J149" s="13" t="n">
-        <v>-0.08</v>
+        <v>14.75</v>
+      </c>
+      <c r="J149" s="10" t="n">
+        <v>1.47</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>312.45</v>
+        <v>321.4</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>313.4</v>
+        <v>318</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>324.4</v>
+        <v>318</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>307.7</v>
+        <v>306.1</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>321.4</v>
+        <v>312.8</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="J150" s="10" t="n">
-        <v>2.86</v>
+        <v>-8.6</v>
+      </c>
+      <c r="J150" s="13" t="n">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>376.45</v>
+        <v>374</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>378.75</v>
+        <v>381.95</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>369.05</v>
+        <v>376</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>374</v>
+        <v>378.05</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-2.45</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>-0.65</v>
+        <v>4.05</v>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1343.4</v>
+        <v>1327.8</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1340</v>
+        <v>1313</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1345.9</v>
+        <v>1371.6</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1325</v>
+        <v>1311</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1327.8</v>
+        <v>1365.8</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-15.6</v>
-      </c>
-      <c r="J152" s="13" t="n">
-        <v>-1.16</v>
+        <v>38</v>
+      </c>
+      <c r="J152" s="10" t="n">
+        <v>2.86</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>176.45</v>
+        <v>178.46</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>176.5</v>
+        <v>179.96</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>179.07</v>
+        <v>185.32</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>176</v>
+        <v>179.5</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>178.46</v>
+        <v>184.2</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>2.01</v>
+        <v>5.74</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>1.14</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>680.55</v>
+        <v>670.3</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>681.25</v>
+        <v>672.5</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>687.9</v>
+        <v>681.3</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>670.3</v>
+        <v>670.7</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-10.25</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>-1.51</v>
+        <v>0.4</v>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1828.1</v>
+        <v>1768.9</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1817</v>
+        <v>1768.9</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1836.3</v>
+        <v>1818.5</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1762.1</v>
+        <v>1759</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1768.9</v>
+        <v>1815.4</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-59.2</v>
-      </c>
-      <c r="J155" s="13" t="n">
-        <v>-3.24</v>
+        <v>46.5</v>
+      </c>
+      <c r="J155" s="10" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1094.25</v>
+        <v>1101.1</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1091.35</v>
+        <v>1110.95</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1106</v>
+        <v>1114.8</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1090.05</v>
+        <v>1103.4</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1101.1</v>
+        <v>1111.85</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>6.85</v>
+        <v>10.75</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>0.63</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>25470</v>
+        <v>24950</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25470</v>
+        <v>25070</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25550</v>
+        <v>25465</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>24815</v>
+        <v>25020</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>24950</v>
+        <v>25125</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-520</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>-2.04</v>
+        <v>175</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1009.3</v>
+        <v>1011.3</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1006.95</v>
+        <v>1011.3</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1030.4</v>
+        <v>1012</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>983.55</v>
+        <v>963.75</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1011.3</v>
+        <v>974.65</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>0.2</v>
+        <v>-36.65</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>-3.62</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3864.4</v>
+        <v>3808.9</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3882</v>
+        <v>3830.5</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3893.6</v>
+        <v>3881</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3767.9</v>
+        <v>3797</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3808.9</v>
+        <v>3856</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-55.5</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>-1.44</v>
+        <v>47.1</v>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2542.4</v>
+        <v>2493.6</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2559</v>
+        <v>2516.8</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2563.7</v>
+        <v>2549</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2472.2</v>
+        <v>2496.7</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2493.6</v>
+        <v>2508.2</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-48.8</v>
-      </c>
-      <c r="J160" s="13" t="n">
-        <v>-1.92</v>
+        <v>14.6</v>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1680.1</v>
+        <v>1620.4</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1670.4</v>
+        <v>1625</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1673.3</v>
+        <v>1766.9</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1613.6</v>
+        <v>1621.9</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1620.4</v>
+        <v>1733.5</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-59.7</v>
-      </c>
-      <c r="J161" s="13" t="n">
-        <v>-3.55</v>
+        <v>113.1</v>
+      </c>
+      <c r="J161" s="10" t="n">
+        <v>6.98</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>625.85</v>
+        <v>600.15</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>625.85</v>
+        <v>603.15</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>625.85</v>
+        <v>612.7</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>594.55</v>
+        <v>593.5</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>600.15</v>
+        <v>611</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-25.7</v>
-      </c>
-      <c r="J162" s="13" t="n">
-        <v>-4.11</v>
+        <v>10.85</v>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>1.81</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>428.35</v>
+        <v>421.2</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>432.55</v>
+        <v>440.9</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>417.45</v>
+        <v>421.25</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>421.2</v>
+        <v>437.95</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-7.15</v>
-      </c>
-      <c r="J163" s="13" t="n">
-        <v>-1.67</v>
+        <v>16.75</v>
+      </c>
+      <c r="J163" s="10" t="n">
+        <v>3.98</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>707.7</v>
+        <v>693.25</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>709</v>
+        <v>698.85</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>713.25</v>
+        <v>724.75</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>690.3</v>
+        <v>695</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>693.25</v>
+        <v>722.3</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-14.45</v>
-      </c>
-      <c r="J164" s="13" t="n">
-        <v>-2.04</v>
+        <v>29.05</v>
+      </c>
+      <c r="J164" s="10" t="n">
+        <v>4.19</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1580.7</v>
+        <v>1520.6</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1590</v>
+        <v>1520.6</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1595</v>
+        <v>1579</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1490.9</v>
+        <v>1518.2</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1520.6</v>
+        <v>1574.7</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-60.1</v>
-      </c>
-      <c r="J165" s="13" t="n">
-        <v>-3.8</v>
+        <v>54.1</v>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>3.56</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1184.4</v>
+        <v>1174</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1185</v>
+        <v>1168</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1197</v>
+        <v>1183.9</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1162</v>
+        <v>1155</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1174</v>
+        <v>1160.5</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-10.4</v>
+        <v>-13.5</v>
       </c>
       <c r="J166" s="13" t="n">
-        <v>-0.88</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>430.3</v>
+        <v>435</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>431</v>
+        <v>436.6</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>436.7</v>
+        <v>455.95</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>426</v>
+        <v>435.2</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>435</v>
+        <v>453.2</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>4.7</v>
+        <v>18.2</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>1.09</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>210.91</v>
+        <v>210.07</v>
       </c>
       <c r="E169" s="9" t="n">
         <v>211</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>208.6</v>
+        <v>210.93</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>210.07</v>
+        <v>213.27</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="J169" s="13" t="n">
-        <v>-0.4</v>
+        <v>3.2</v>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2521.8</v>
+        <v>2396.9</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2488</v>
+        <v>2396.9</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2505</v>
+        <v>2459</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2388.8</v>
+        <v>2396.9</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2396.9</v>
+        <v>2447.6</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-124.9</v>
-      </c>
-      <c r="J170" s="13" t="n">
-        <v>-4.95</v>
+        <v>50.7</v>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>2.12</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1421.5</v>
+        <v>1358.5</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1407.1</v>
+        <v>1362.9</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1426.7</v>
+        <v>1400.5</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1347.4</v>
+        <v>1360.2</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1358.5</v>
+        <v>1396.1</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-63</v>
-      </c>
-      <c r="J171" s="13" t="n">
-        <v>-4.43</v>
+        <v>37.6</v>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v>2.77</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>3086.8</v>
+        <v>2968.7</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>3086.8</v>
+        <v>2970</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3129.8</v>
+        <v>3013.9</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2897.1</v>
+        <v>2950</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2968.7</v>
+        <v>2994.4</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-118.1</v>
-      </c>
-      <c r="J172" s="13" t="n">
-        <v>-3.83</v>
+        <v>25.7</v>
+      </c>
+      <c r="J172" s="10" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4456.5</v>
+        <v>4410</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4475.5</v>
+        <v>4438.8</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4486.6</v>
+        <v>4464</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4361.4</v>
+        <v>4388.4</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4410</v>
+        <v>4441.8</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-46.5</v>
-      </c>
-      <c r="J173" s="13" t="n">
-        <v>-1.04</v>
+        <v>31.8</v>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4147.2</v>
+        <v>4117.2</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4151</v>
+        <v>4125</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4158</v>
+        <v>4244</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4097.4</v>
+        <v>4118.6</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4117.2</v>
+        <v>4219.8</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-30</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>-0.72</v>
+        <v>102.6</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>2.49</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1737</v>
+        <v>1699.5</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1737</v>
+        <v>1710</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1744.4</v>
+        <v>1824.1</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1675</v>
+        <v>1704.1</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1699.5</v>
+        <v>1772.5</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-37.5</v>
-      </c>
-      <c r="J175" s="13" t="n">
-        <v>-2.16</v>
+        <v>73</v>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>4.3</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4251.4</v>
+        <v>4297.3</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4260</v>
+        <v>4336</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4344</v>
+        <v>4348.5</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4200</v>
+        <v>4246.4</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4297.3</v>
+        <v>4260.8</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="J176" s="10" t="n">
-        <v>1.08</v>
+        <v>-36.5</v>
+      </c>
+      <c r="J176" s="13" t="n">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3513</v>
+        <v>3488.2</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3513</v>
+        <v>3500.5</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3543.3</v>
+        <v>3564.1</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3462.7</v>
+        <v>3483.6</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3488.2</v>
+        <v>3552.6</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-24.8</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>-0.71</v>
+        <v>64.40000000000001</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1483.2</v>
+        <v>1477.1</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1497.9</v>
+        <v>1475</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1498.9</v>
+        <v>1500</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1465</v>
+        <v>1467.9</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1477.1</v>
+        <v>1479.2</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="J178" s="13" t="n">
-        <v>-0.41</v>
+        <v>2.1</v>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>12167</v>
+        <v>11998</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>12203</v>
+        <v>12148</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>12246</v>
+        <v>12240</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11954</v>
+        <v>11869</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11998</v>
+        <v>12010</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-169</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>-1.39</v>
+        <v>12</v>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>179.71</v>
+        <v>177</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>179.3</v>
+        <v>177.2</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>180.75</v>
+        <v>178.8</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>174.4</v>
+        <v>175.36</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>177</v>
+        <v>176.1</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-2.71</v>
+        <v>-0.9</v>
       </c>
       <c r="J180" s="13" t="n">
-        <v>-1.51</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>642.05</v>
+        <v>631.4</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>643.6</v>
+        <v>634.9</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>645.15</v>
+        <v>643.75</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>629.95</v>
+        <v>632.5</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>631.4</v>
+        <v>639.5</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-10.65</v>
-      </c>
-      <c r="J181" s="13" t="n">
-        <v>-1.66</v>
+        <v>8.1</v>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>1.28</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>735.6</v>
+        <v>720.95</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>734.95</v>
+        <v>724.25</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>734.95</v>
+        <v>746.6</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>707.6</v>
+        <v>720.55</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>720.95</v>
+        <v>742.5</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-14.65</v>
-      </c>
-      <c r="J182" s="13" t="n">
-        <v>-1.99</v>
+        <v>21.55</v>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>2.99</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1445.5</v>
+        <v>1464</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1452.9</v>
+        <v>1481.4</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1470</v>
+        <v>1529.9</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1431.9</v>
+        <v>1475</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1464</v>
+        <v>1515</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>18.5</v>
+        <v>51</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>1.28</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>202.76</v>
+        <v>199.36</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>202.75</v>
+        <v>199.36</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>202.75</v>
+        <v>205.25</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>197.88</v>
+        <v>199.36</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>199.36</v>
+        <v>205.05</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="J184" s="13" t="n">
-        <v>-1.68</v>
+        <v>5.69</v>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>946.35</v>
+        <v>927.4</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>948</v>
+        <v>929.6</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>951.75</v>
+        <v>953.9</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>922.55</v>
+        <v>922.3</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>927.4</v>
+        <v>939.65</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-18.95</v>
-      </c>
-      <c r="J186" s="13" t="n">
-        <v>-2</v>
+        <v>12.25</v>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  24-Apr-2026 02:45 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  27-Apr-2026 03:07 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-Apr-2026 02:45 PM</t>
+          <t>27-Apr-2026 03:07 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 27-Apr-2026 03:07 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 28-Apr-2026 03:26 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>27-Apr-2026 03:07 PM</t>
+          <t>28-Apr-2026 03:26 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  27-Apr-2026 03:07 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  28-Apr-2026 03:26 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>472.75</v>
+        <v>488.75</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>478</v>
+        <v>492.7</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>498.35</v>
+        <v>506.4</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>477.1</v>
+        <v>488.1</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>488.75</v>
+        <v>501.7</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>16</v>
+        <v>12.95</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>3.38</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7328.5</v>
+        <v>7430.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7330.5</v>
+        <v>7449</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7475</v>
+        <v>7490</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7282.5</v>
+        <v>7251.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7430.5</v>
+        <v>7288</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>102</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>1.39</v>
+        <v>-142.5</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25180</v>
+        <v>25425</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25320</v>
+        <v>25425</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25560</v>
+        <v>25600</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25180</v>
+        <v>25200</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25425</v>
+        <v>25345</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>245</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>0.97</v>
+        <v>-80</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>340.6</v>
+        <v>342.55</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>342</v>
+        <v>342.85</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>348.95</v>
+        <v>346.7</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>337.95</v>
+        <v>337.45</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>342.55</v>
+        <v>338.3</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>0.57</v>
+        <v>-4.25</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>61.79</v>
+        <v>63.92</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>62.54</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>64.66</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>62.33</v>
+        <v>63.14</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>63.92</v>
+        <v>63.58</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>3.45</v>
+        <v>-0.34</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1412.7</v>
+        <v>1439.8</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1418</v>
+        <v>1441.9</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1459.6</v>
+        <v>1443</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1416.4</v>
+        <v>1432</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1439.8</v>
+        <v>1439.3</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>1.92</v>
+        <v>-0.5</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2287.6</v>
+        <v>2321.8</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2300.2</v>
+        <v>2321.8</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2337</v>
+        <v>2420</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2286</v>
+        <v>2320.9</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2321.8</v>
+        <v>2412.4</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>34.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1585.1</v>
+        <v>1628.5</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1600</v>
+        <v>1628.4</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1649.9</v>
+        <v>1648</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1593</v>
+        <v>1624.5</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1628.5</v>
+        <v>1637.6</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>43.4</v>
+        <v>9.1</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>2.74</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5235</v>
+        <v>5344</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5280</v>
+        <v>5344</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5486</v>
+        <v>5454</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5248</v>
+        <v>5315</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5344</v>
+        <v>5418.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>109</v>
+        <v>74.5</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>2.08</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>451.2</v>
+        <v>460.5</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>453.5</v>
+        <v>462.85</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>468.8</v>
+        <v>465</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>453.45</v>
+        <v>456</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>460.5</v>
+        <v>458.8</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>2.06</v>
+        <v>-1.7</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>314.52</v>
+        <v>318.64</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>316.85</v>
+        <v>318.15</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>322.98</v>
+        <v>320.43</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>316.52</v>
+        <v>316</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>318.64</v>
+        <v>319.27</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>4.12</v>
+        <v>0.63</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>1.31</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2004.5</v>
+        <v>1987.7</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2015</v>
+        <v>2008.3</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2050</v>
+        <v>2014.8</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1985</v>
+        <v>1958</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1987.7</v>
+        <v>1976</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-16.8</v>
+        <v>-11.7</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>-0.84</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7732.5</v>
+        <v>7825</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7759</v>
+        <v>7840</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7850</v>
+        <v>7878.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7735</v>
+        <v>7711</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7825</v>
+        <v>7753</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>1.2</v>
+        <v>-72</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>423.85</v>
+        <v>428.55</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>426.2</v>
+        <v>429.6</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>430.25</v>
+        <v>432.45</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>424.7</v>
+        <v>422.25</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>428.55</v>
+        <v>423.65</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>1.11</v>
+        <v>-4.9</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>169.9</v>
+        <v>169.3</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>170.68</v>
+        <v>169.26</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>171.49</v>
+        <v>172.01</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>167.75</v>
+        <v>167.01</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>169.3</v>
+        <v>167.52</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-0.6</v>
+        <v>-1.78</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>-0.35</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2485.1</v>
+        <v>2485.2</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2503</v>
+        <v>2475</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2519.8</v>
+        <v>2499</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2475.5</v>
+        <v>2456.1</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2485.2</v>
+        <v>2462.6</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>0</v>
+        <v>-22.6</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1563.2</v>
+        <v>1535</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1565</v>
+        <v>1545.5</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1598</v>
+        <v>1558.9</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1535</v>
+        <v>1548.9</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-28.2</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>-1.8</v>
+        <v>13.9</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>0.91</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>626.85</v>
+        <v>635.6</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>649</v>
+        <v>684.9</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>626</v>
+        <v>636.85</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>635.6</v>
+        <v>653.85</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>8.75</v>
+        <v>18.25</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>1.4</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6680.5</v>
+        <v>6700</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6750</v>
+        <v>6700</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6770</v>
+        <v>7029.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6554.5</v>
+        <v>6680</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6700</v>
+        <v>6855</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>19.5</v>
+        <v>155</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.29</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1065.65</v>
+        <v>1043</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1057</v>
+        <v>1062.9</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1059.9</v>
+        <v>1062.9</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1028</v>
+        <v>1017.1</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1043</v>
+        <v>1022.8</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-22.65</v>
+        <v>-20.2</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>-2.13</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1413.8</v>
+        <v>1416.7</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1414.9</v>
+        <v>1415</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1433.4</v>
+        <v>1430</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1386.6</v>
+        <v>1410.3</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1416.7</v>
+        <v>1422.6</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>0.21</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1365.9</v>
+        <v>1324.2</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1325</v>
+        <v>1312</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1327.3</v>
+        <v>1321.4</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1299.9</v>
+        <v>1285.5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1324.2</v>
+        <v>1289</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-41.7</v>
+        <v>-35.2</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>-3.05</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>9576</v>
+        <v>9662</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>9642.5</v>
+        <v>9622</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>9715</v>
+        <v>9662.5</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>9617</v>
+        <v>9475</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>9662</v>
+        <v>9495.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>86</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>0.9</v>
+        <v>-166.5</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1770.7</v>
+        <v>1772.2</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1781</v>
+        <v>1772.1</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1798</v>
+        <v>1790.8</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1765</v>
+        <v>1757.7</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1772.2</v>
+        <v>1779</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>921.55</v>
+        <v>921.8</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>923.05</v>
+        <v>921.8</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>928.95</v>
+        <v>929.9</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>908.3</v>
+        <v>914.35</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>921.8</v>
+        <v>923.65</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>0.25</v>
+        <v>1.85</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2225.4</v>
+        <v>2223.4</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2249.9</v>
+        <v>2237</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2255.9</v>
+        <v>2247.6</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2215.5</v>
+        <v>2185</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2223.4</v>
+        <v>2189.3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-2</v>
+        <v>-34.1</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>-0.09</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>516.1</v>
+        <v>520.5</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>516.1</v>
+        <v>519.7</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>535</v>
+        <v>521.45</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>516.1</v>
+        <v>500</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>520.5</v>
+        <v>508.7</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>0.85</v>
+        <v>-11.8</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>174.67</v>
+        <v>181.87</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>174.6</v>
+        <v>179.66</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>182.6</v>
+        <v>183.09</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>174.07</v>
+        <v>177.7</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>181.87</v>
+        <v>178.65</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>4.12</v>
+        <v>-3.22</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>274.13</v>
+        <v>273.99</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>275.19</v>
+        <v>270</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>277.2</v>
+        <v>272.06</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>272.7</v>
+        <v>265.61</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>273.99</v>
+        <v>267.83</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-0.14</v>
+        <v>-6.16</v>
       </c>
       <c r="J31" s="13" t="n">
-        <v>-0.05</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>444.45</v>
+        <v>435.6</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>445</v>
+        <v>435.6</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>448.3</v>
+        <v>441</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>432.95</v>
+        <v>433.55</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>435.6</v>
+        <v>435.75</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-8.85</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>-1.99</v>
+        <v>0.15</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>460.4</v>
+        <v>463.6</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>460.4</v>
+        <v>463.6</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>466.75</v>
+        <v>469</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>459</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>463.6</v>
+        <v>459.85</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>0.7</v>
+        <v>-3.75</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1814.5</v>
+        <v>1820.1</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1816.1</v>
+        <v>1826</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1828.4</v>
+        <v>1852</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1814</v>
+        <v>1812.6</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1820.1</v>
+        <v>1843.8</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>5.6</v>
+        <v>23.7</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>0.31</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>337.39</v>
+        <v>348.58</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>339.43</v>
+        <v>349.69</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>339</v>
+        <v>347.28</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>348.58</v>
+        <v>354.71</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>11.19</v>
+        <v>6.13</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>3.32</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>349.85</v>
+        <v>362</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>351.25</v>
+        <v>361.95</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>362.55</v>
+        <v>364.7</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>350.5</v>
+        <v>359.15</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>362</v>
+        <v>362.8</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>12.15</v>
+        <v>0.8</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>3.47</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>36690</v>
+        <v>37225</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>36800</v>
+        <v>37180</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>37460</v>
+        <v>37565</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>36730</v>
+        <v>37000</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>37225</v>
+        <v>37320</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>535</v>
+        <v>95</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1.46</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>308.1</v>
+        <v>312.65</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>308.3</v>
+        <v>308.7</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>315.1</v>
+        <v>313.1</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>306.7</v>
+        <v>305.15</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>312.65</v>
+        <v>307.75</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>1.48</v>
+        <v>-4.9</v>
+      </c>
+      <c r="J38" s="13" t="n">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5730.5</v>
+        <v>5717.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5750</v>
+        <v>5723</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5804</v>
+        <v>5735</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5689</v>
+        <v>5641</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5717.5</v>
+        <v>5662</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-13</v>
+        <v>-55.5</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>-0.23</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>368.65</v>
+        <v>371.85</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>368.95</v>
+        <v>372.2</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>378.4</v>
+        <v>374.15</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>368.95</v>
+        <v>367.2</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>371.85</v>
+        <v>371</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>0.87</v>
+        <v>-0.85</v>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>140.85</v>
+        <v>140.52</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>141.19</v>
+        <v>136.27</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>142.42</v>
+        <v>138.36</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>139.81</v>
+        <v>136.21</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>140.52</v>
+        <v>137.1</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.33</v>
+        <v>-3.42</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>-0.23</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>909.6</v>
+        <v>915.45</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>909.2</v>
+        <v>916.95</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>943.9</v>
+        <v>919.15</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>897.1</v>
+        <v>877</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>915.45</v>
+        <v>883.3</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>0.64</v>
+        <v>-32.15</v>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v>-3.51</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>440.8</v>
+        <v>445.95</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>441.05</v>
+        <v>447.9</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>448</v>
+        <v>455.85</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>441.05</v>
+        <v>446.1</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>445.95</v>
+        <v>448.5</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>5.15</v>
+        <v>2.55</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1.17</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1568.2</v>
+        <v>1560.7</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1570.5</v>
+        <v>1560.1</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1577.8</v>
+        <v>1579.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1534.8</v>
+        <v>1530.8</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1560.7</v>
+        <v>1536.4</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-7.5</v>
+        <v>-24.3</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>-0.48</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1295</v>
+        <v>1317.2</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1303.2</v>
+        <v>1316</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1320.7</v>
+        <v>1326</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1299</v>
+        <v>1296.3</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1317.2</v>
+        <v>1306.5</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v>1.71</v>
+        <v>-10.7</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>456</v>
+        <v>452.5</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>458.5</v>
+        <v>456.2</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>460.65</v>
+        <v>473.9</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>450.65</v>
+        <v>456.2</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>452.5</v>
+        <v>467</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>-0.77</v>
+        <v>14.5</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1150.9</v>
+        <v>1202.4</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1156</v>
+        <v>1206</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1205.9</v>
+        <v>1213.8</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1155.9</v>
+        <v>1192</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1202.4</v>
+        <v>1200.9</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>4.47</v>
+        <v>-1.5</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2171.3</v>
+        <v>2141</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2180</v>
+        <v>2132.7</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2190.1</v>
+        <v>2136.4</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2135.4</v>
+        <v>2105</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2141</v>
+        <v>2125.2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-30.3</v>
+        <v>-15.8</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>-1.4</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>502.8</v>
+        <v>514.2</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>505.15</v>
+        <v>517</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>521.8</v>
+        <v>519.15</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>505.15</v>
+        <v>508.8</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>514.2</v>
+        <v>510.5</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>2.27</v>
+        <v>-3.7</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1995.3</v>
+        <v>2031.1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1986</v>
+        <v>2031.1</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2043.9</v>
+        <v>2038.3</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1982.4</v>
+        <v>1996.1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2031.1</v>
+        <v>2010.7</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>1.79</v>
+        <v>-20.4</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>250.23</v>
+        <v>258.68</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>253</v>
+        <v>258.67</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>259.83</v>
+        <v>272.5</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>252.1</v>
+        <v>256.5</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>258.68</v>
+        <v>269.63</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>8.449999999999999</v>
+        <v>10.95</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>3.38</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>262.51</v>
+        <v>271.21</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>264</v>
+        <v>281.52</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>274.5</v>
+        <v>293.51</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>263.83</v>
+        <v>273.21</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>271.21</v>
+        <v>275.65</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>8.699999999999999</v>
+        <v>4.44</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>3.31</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5232</v>
+        <v>5233.2</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5264.5</v>
+        <v>5260</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5308.7</v>
+        <v>5286.8</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5200</v>
+        <v>5195.1</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5233.2</v>
+        <v>5258</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>1.2</v>
+        <v>24.8</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.02</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>451.1</v>
+        <v>452</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>452.45</v>
+        <v>452.15</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>457.4</v>
+        <v>453.1</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>452</v>
+        <v>450.15</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>0.2</v>
+        <v>-1.85</v>
+      </c>
+      <c r="J54" s="13" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1962.5</v>
+        <v>1972.7</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1964.7</v>
+        <v>1982.5</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1999.8</v>
+        <v>1982.6</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1960.2</v>
+        <v>1884</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1972.7</v>
+        <v>1918.8</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J55" s="10" t="n">
-        <v>0.52</v>
+        <v>-53.9</v>
+      </c>
+      <c r="J55" s="13" t="n">
+        <v>-2.73</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1690.3</v>
+        <v>1684.9</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1690.3</v>
+        <v>1685</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1717.1</v>
+        <v>1694</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1680.5</v>
+        <v>1674.7</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1684.9</v>
+        <v>1682.6</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-5.4</v>
+        <v>-2.3</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>-0.32</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>76.69</v>
+        <v>75.44</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>77</v>
+        <v>75.12</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>78.34</v>
+        <v>76.8</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>75.05</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>75.44</v>
+        <v>73.34</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-1.25</v>
+        <v>-2.1</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>-1.63</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6361.5</v>
+        <v>6477</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6351.5</v>
+        <v>6505</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6507.5</v>
+        <v>6505</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6346.5</v>
+        <v>6416.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6477</v>
+        <v>6432.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>1.82</v>
+        <v>-44.5</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>10815.5</v>
+        <v>11252</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>10920</v>
+        <v>11284</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11350</v>
+        <v>11595</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>10855</v>
+        <v>11254.5</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>11252</v>
+        <v>11370</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>436.5</v>
+        <v>118</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>4.04</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>587.05</v>
+        <v>592.45</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>592.9</v>
+        <v>594</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>599.8</v>
+        <v>595.7</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>590.3</v>
+        <v>586.45</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>592.45</v>
+        <v>587.9</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>0.92</v>
+        <v>-4.55</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1317.1</v>
+        <v>1334.5</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1320.4</v>
+        <v>1342.4</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1350</v>
+        <v>1367.9</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1309</v>
+        <v>1327.4</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1334.5</v>
+        <v>1354.6</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7111.5</v>
+        <v>7174</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7150</v>
+        <v>7170</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7214</v>
+        <v>7254</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7102</v>
+        <v>7053</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7174</v>
+        <v>7071.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>0.88</v>
+        <v>-102.5</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3231.3</v>
+        <v>3262.5</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3250</v>
+        <v>3260.1</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3302.7</v>
+        <v>3314.9</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3240.1</v>
+        <v>3256.2</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3262.5</v>
+        <v>3308.6</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>31.2</v>
+        <v>46.1</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>0.97</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>342.8</v>
+        <v>352.35</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>345</v>
+        <v>352.7</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>353.7</v>
+        <v>358.5</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>344.8</v>
+        <v>351.25</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>352.35</v>
+        <v>356.25</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>9.550000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>2.79</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>293</v>
+        <v>294.05</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>294.7</v>
+        <v>292.85</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>297.65</v>
+        <v>295.85</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>292.8</v>
+        <v>290</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>294.05</v>
+        <v>290.6</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="J65" s="10" t="n">
-        <v>0.36</v>
+        <v>-3.45</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>165.61</v>
+        <v>165.74</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>166.8</v>
+        <v>165.89</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>167.78</v>
+        <v>167.22</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>164.9</v>
+        <v>165.06</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>165.74</v>
+        <v>165.68</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>0.08</v>
+        <v>-0.06</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2299.5</v>
+        <v>2325.1</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2312</v>
+        <v>2328.1</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2339.9</v>
+        <v>2427.4</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2290.9</v>
+        <v>2327.3</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2325.1</v>
+        <v>2403.7</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>25.6</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>1.11</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>468.45</v>
+        <v>474.85</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>471.45</v>
+        <v>474</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>478.9</v>
+        <v>477</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>470.5</v>
+        <v>471.85</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>474.85</v>
+        <v>475.25</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>1.37</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1089.9</v>
+        <v>1089.25</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1100</v>
+        <v>1088.2</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1104.55</v>
+        <v>1105.2</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1083.95</v>
+        <v>1081.5</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1089.25</v>
+        <v>1092</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="J70" s="13" t="n">
-        <v>-0.06</v>
+        <v>2.75</v>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1769.4</v>
+        <v>1828.2</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1784</v>
+        <v>1829.3</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1842.4</v>
+        <v>1845.2</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1778.1</v>
+        <v>1820</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1828.2</v>
+        <v>1824.6</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>3.32</v>
+        <v>-3.6</v>
+      </c>
+      <c r="J71" s="13" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>689.45</v>
+        <v>694.9</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>710</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>686.15</v>
+        <v>695</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>694.9</v>
+        <v>705.15</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>5.45</v>
+        <v>10.25</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>0.79</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2739.3</v>
+        <v>2778.2</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2766</v>
+        <v>2780</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2810.9</v>
+        <v>2848.2</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2752.2</v>
+        <v>2772</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2778.2</v>
+        <v>2783</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>38.9</v>
+        <v>4.8</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>1.42</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>383.85</v>
+        <v>383</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>385.65</v>
+        <v>384.3</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>385.65</v>
+        <v>393</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>379</v>
+        <v>383.55</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>383</v>
+        <v>389.45</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J74" s="13" t="n">
-        <v>-0.22</v>
+        <v>6.45</v>
+      </c>
+      <c r="J74" s="10" t="n">
+        <v>1.68</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4265.8</v>
+        <v>4310.3</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4280</v>
+        <v>4310.3</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4340.2</v>
+        <v>4360</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4280</v>
+        <v>4302.5</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4310.3</v>
+        <v>4341.4</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>44.5</v>
+        <v>31.1</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>1.04</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1238.6</v>
+        <v>1274.1</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1248</v>
+        <v>1273.1</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1281.5</v>
+        <v>1281.2</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1243.1</v>
+        <v>1263</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1274.1</v>
+        <v>1272.2</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>2.87</v>
+        <v>-1.9</v>
+      </c>
+      <c r="J76" s="13" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1203.2</v>
+        <v>1228.2</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1209</v>
+        <v>1227.9</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1232</v>
+        <v>1232.7</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1201</v>
+        <v>1192.3</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1228.2</v>
+        <v>1196</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>2.08</v>
+        <v>-32.2</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2735</v>
+        <v>2756</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2749.9</v>
+        <v>2756</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2776.5</v>
+        <v>2788.8</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2719.6</v>
+        <v>2738.1</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2756</v>
+        <v>2760.2</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>0.77</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>784.85</v>
+        <v>789.8</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>787.5</v>
+        <v>785</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>793</v>
+        <v>794.5</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>785</v>
+        <v>778.3</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>789.8</v>
+        <v>782.55</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="J79" s="10" t="n">
-        <v>0.63</v>
+        <v>-7.25</v>
+      </c>
+      <c r="J79" s="13" t="n">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>588.2</v>
+        <v>597.3</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>595</v>
+        <v>594.2</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>603.45</v>
+        <v>598.6</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>590.1</v>
+        <v>588.5</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>597.3</v>
+        <v>590.15</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>1.55</v>
+        <v>-7.15</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>4961.5</v>
+        <v>5043</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5012.5</v>
+        <v>5042.5</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5098</v>
+        <v>5105.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5005.5</v>
+        <v>5019</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5043</v>
+        <v>5068</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>81.5</v>
+        <v>25</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>1.64</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1048.35</v>
+        <v>1061.8</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1058.35</v>
+        <v>1060</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1066.5</v>
+        <v>1079.7</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1052</v>
+        <v>1055.15</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1061.8</v>
+        <v>1074.3</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>13.45</v>
+        <v>12.5</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>541.5</v>
+        <v>559.35</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>546.8</v>
+        <v>562</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>562</v>
+        <v>568.45</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>559.35</v>
+        <v>556.4</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>17.85</v>
-      </c>
-      <c r="J83" s="10" t="n">
-        <v>3.3</v>
+        <v>-2.95</v>
+      </c>
+      <c r="J83" s="13" t="n">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>373.5</v>
+        <v>380.9</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>376</v>
+        <v>379.5</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>384.95</v>
+        <v>382.2</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>372.75</v>
+        <v>375</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>380.9</v>
+        <v>380.05</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J84" s="10" t="n">
-        <v>1.98</v>
+        <v>-0.85</v>
+      </c>
+      <c r="J84" s="13" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2327.3</v>
+        <v>2328.3</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2334.9</v>
+        <v>2321</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2362.8</v>
+        <v>2334.4</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2325</v>
+        <v>2281.1</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2328.3</v>
+        <v>2289.5</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>0.04</v>
+        <v>-38.8</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>31365</v>
+        <v>31850</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>31365</v>
+        <v>31900</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>31895</v>
+        <v>32005</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>31295</v>
+        <v>31150</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>31850</v>
+        <v>31255</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>485</v>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v>1.55</v>
+        <v>-595</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>67.23</v>
+        <v>70.27</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>67.86</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>70.48999999999999</v>
+        <v>69.98</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>67.84999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>70.27</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="J87" s="10" t="n">
-        <v>4.52</v>
+        <v>-1.56</v>
+      </c>
+      <c r="J87" s="13" t="n">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>123.23</v>
+        <v>126.45</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>123.19</v>
+        <v>126.41</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>127.3</v>
+        <v>127.64</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>122.38</v>
+        <v>125</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>126.45</v>
+        <v>125.94</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v>2.61</v>
+        <v>-0.51</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>164.61</v>
+        <v>164.88</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>165.43</v>
+        <v>164.8</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>166.12</v>
+        <v>168.1</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>163.6</v>
+        <v>163.9</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>164.88</v>
+        <v>166.45</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0.27</v>
+        <v>1.57</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>0.16</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>635.35</v>
+        <v>647.85</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>635.55</v>
+        <v>645.1</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>652.5</v>
+        <v>655</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>635.35</v>
+        <v>643.25</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>647.85</v>
+        <v>652.45</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>12.5</v>
+        <v>4.6</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>1.97</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2107.1</v>
+        <v>2119.5</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2125</v>
+        <v>2105.1</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2142.4</v>
+        <v>2140.1</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2101</v>
+        <v>2101.8</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2119.5</v>
+        <v>2129.3</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>12.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>0.59</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4523.1</v>
+        <v>4561.2</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4522.2</v>
+        <v>4514.8</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4584.3</v>
+        <v>4547.9</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4507</v>
+        <v>4421</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4561.2</v>
+        <v>4442.4</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="J92" s="10" t="n">
-        <v>0.84</v>
+        <v>-118.8</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>847.95</v>
+        <v>900.15</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>865.2</v>
+        <v>890.15</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>903.5</v>
+        <v>895.7</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>865.2</v>
+        <v>882.45</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>900.15</v>
+        <v>885.55</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="J93" s="10" t="n">
-        <v>6.16</v>
+        <v>-14.6</v>
+      </c>
+      <c r="J93" s="13" t="n">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>402.2</v>
+        <v>402.3</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>403.45</v>
+        <v>411</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>407.5</v>
+        <v>419.05</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>399.5</v>
+        <v>409.6</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>402.3</v>
+        <v>413.95</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>0.1</v>
+        <v>11.65</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>0.02</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1154.6</v>
+        <v>1170.3</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1154.6</v>
+        <v>1162.7</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1179.9</v>
+        <v>1169.4</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1154.5</v>
+        <v>1149.8</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1170.3</v>
+        <v>1152.1</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="J95" s="10" t="n">
-        <v>1.36</v>
+        <v>-18.2</v>
+      </c>
+      <c r="J95" s="13" t="n">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>143.47</v>
+        <v>146.26</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>144</v>
+        <v>146.15</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>146.6</v>
+        <v>146.19</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>143.69</v>
+        <v>144.31</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>146.26</v>
+        <v>145.39</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="J96" s="10" t="n">
-        <v>1.94</v>
+        <v>-0.87</v>
+      </c>
+      <c r="J96" s="13" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1555.9</v>
+        <v>1541.3</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1557.1</v>
+        <v>1548</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1585.9</v>
+        <v>1573.9</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1528.5</v>
+        <v>1530.2</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1541.3</v>
+        <v>1537</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-14.6</v>
+        <v>-4.3</v>
       </c>
       <c r="J97" s="13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>541.2</v>
+        <v>545.1</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>543.2</v>
+        <v>545.1</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>546.85</v>
+        <v>554</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>541</v>
+        <v>541.8</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>545.1</v>
+        <v>543.85</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>0.72</v>
+        <v>-1.25</v>
+      </c>
+      <c r="J98" s="13" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>301.6</v>
+        <v>303.85</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>303.65</v>
+        <v>304.4</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>305.65</v>
+        <v>305.8</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>302.85</v>
+        <v>302.55</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>303.85</v>
+        <v>304.45</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>2.25</v>
+        <v>0.6</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>0.75</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1256</v>
+        <v>1278.2</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1257.9</v>
+        <v>1283.5</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1293.6</v>
+        <v>1290.5</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1257.6</v>
+        <v>1262.5</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1278.2</v>
+        <v>1265.5</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="J100" s="10" t="n">
-        <v>1.77</v>
+        <v>-12.7</v>
+      </c>
+      <c r="J100" s="13" t="n">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5584.5</v>
+        <v>5606.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5620.5</v>
+        <v>5606.5</v>
       </c>
       <c r="F101" s="9" t="n">
         <v>5645</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5559</v>
+        <v>5401</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5606.5</v>
+        <v>5472.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="J101" s="10" t="n">
-        <v>0.39</v>
+        <v>-134</v>
+      </c>
+      <c r="J101" s="13" t="n">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>766.3</v>
+        <v>770.4</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>769.5</v>
+        <v>776.65</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>787.9</v>
+        <v>788</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>765.15</v>
+        <v>770.65</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>770.4</v>
+        <v>773.85</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>544.95</v>
+        <v>573.8</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>546.5</v>
+        <v>578.9</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>575.5</v>
+        <v>585.65</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>573.8</v>
+        <v>580.9</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>28.85</v>
+        <v>7.1</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>5.29</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1255.7</v>
+        <v>1282.7</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1273</v>
+        <v>1284</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1297</v>
+        <v>1306.8</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1268.1</v>
+        <v>1275.6</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1282.7</v>
+        <v>1281.6</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>2.15</v>
+        <v>-1.1</v>
+      </c>
+      <c r="J104" s="13" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>491.95</v>
+        <v>485.1</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>496</v>
+        <v>482.75</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>498.05</v>
+        <v>490</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>483.5</v>
+        <v>475.5</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>485.1</v>
+        <v>482.4</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-6.85</v>
+        <v>-2.7</v>
       </c>
       <c r="J105" s="13" t="n">
-        <v>-1.39</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1211.15</v>
+        <v>1236.25</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1213</v>
+        <v>1240</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1240</v>
+        <v>1246.8</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1213</v>
+        <v>1206</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1236.25</v>
+        <v>1212</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="J106" s="10" t="n">
-        <v>2.07</v>
+        <v>-24.25</v>
+      </c>
+      <c r="J106" s="13" t="n">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>370.85</v>
+        <v>376.8</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>380.45</v>
+        <v>383.25</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>373.25</v>
+        <v>372</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>376.8</v>
+        <v>377.95</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>5.95</v>
+        <v>1.15</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>1.6</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>709.6</v>
+        <v>735.3</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>713.1</v>
+        <v>736</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>740</v>
+        <v>739.8</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>713.1</v>
+        <v>722.9</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>735.3</v>
+        <v>734.45</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>3.62</v>
+        <v>-0.85</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1408.9</v>
+        <v>1416</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1405</v>
+        <v>1416</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1429</v>
+        <v>1428.7</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1394.1</v>
+        <v>1403.4</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1416</v>
+        <v>1411.7</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J109" s="10" t="n">
-        <v>0.5</v>
+        <v>-4.3</v>
+      </c>
+      <c r="J109" s="13" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1113.45</v>
+        <v>1123.55</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1118.8</v>
+        <v>1132</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1132.4</v>
+        <v>1133</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1106.3</v>
+        <v>1085</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1123.55</v>
+        <v>1090.45</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>0.91</v>
+        <v>-33.1</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>-2.95</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>540.75</v>
+        <v>543.1</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>544</v>
+        <v>543.15</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>545.4</v>
+        <v>552.95</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>534.4</v>
+        <v>540.3</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>543.1</v>
+        <v>550</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>2.35</v>
+        <v>6.9</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>0.43</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4014.3</v>
+        <v>4053.6</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>4058</v>
+        <v>4060</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4089.5</v>
+        <v>4087.9</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>4030.2</v>
+        <v>4023.9</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4053.6</v>
+        <v>4037.7</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="J112" s="10" t="n">
-        <v>0.98</v>
+        <v>-15.9</v>
+      </c>
+      <c r="J112" s="13" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>290.05</v>
+        <v>287.79</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>291.7</v>
+        <v>288</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>300.83</v>
+        <v>292.58</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>286.81</v>
+        <v>284.71</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>287.79</v>
+        <v>285.78</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-2.26</v>
+        <v>-2.01</v>
       </c>
       <c r="J113" s="13" t="n">
-        <v>-0.78</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="114">
@@ -4607,7 +4607,7 @@
         <v>150</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>4282.3</v>
+        <v>4346</v>
       </c>
       <c r="E114" s="12" t="n">
         <v/>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3379.8</v>
+        <v>3589.8</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3397.9</v>
+        <v>3598.9</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3608</v>
+        <v>3605</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3388</v>
+        <v>3552</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3589.8</v>
+        <v>3566.4</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>210</v>
-      </c>
-      <c r="J115" s="10" t="n">
-        <v>6.21</v>
+        <v>-23.4</v>
+      </c>
+      <c r="J115" s="13" t="n">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2296.1</v>
+        <v>2324.5</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2304.9</v>
+        <v>2299.1</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2341</v>
+        <v>2319.4</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2296.2</v>
+        <v>2260.3</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2324.5</v>
+        <v>2302.7</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v>1.24</v>
+        <v>-21.8</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3038.4</v>
+        <v>3102.4</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3050</v>
+        <v>3115.9</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3114</v>
+        <v>3144</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3050</v>
+        <v>3075</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3102.4</v>
+        <v>3088.1</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>64</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>2.11</v>
+        <v>-14.3</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>289.4</v>
+        <v>288.2</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>289.5</v>
+        <v>290.4</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>292.95</v>
+        <v>299.75</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>286.75</v>
+        <v>289.25</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>288.2</v>
+        <v>292.75</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J118" s="13" t="n">
-        <v>-0.41</v>
+        <v>4.55</v>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v>1.58</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>783.3</v>
+        <v>787</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>783.3</v>
+        <v>785</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>781.3</v>
+        <v>775.75</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>787</v>
+        <v>780.85</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v>0.47</v>
+        <v>-6.15</v>
+      </c>
+      <c r="J119" s="13" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13048</v>
+        <v>13222</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13153</v>
+        <v>13222</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13270</v>
+        <v>13307</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13043</v>
+        <v>12828</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13222</v>
+        <v>12892</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>174</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>1.33</v>
+        <v>-330</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2760.9</v>
+        <v>2830</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>2786.5</v>
+        <v>2835</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>2834.5</v>
+        <v>2915</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2773.8</v>
+        <v>2833.1</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>2830</v>
+        <v>2898</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>69.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>467.1</v>
+        <v>476.5</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>467.1</v>
+        <v>478.85</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>480</v>
+        <v>485.9</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>463</v>
+        <v>474.5</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>476.5</v>
+        <v>480.85</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>9.4</v>
+        <v>4.35</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>2.01</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1587.3</v>
+        <v>1603</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1580.1</v>
+        <v>1601.8</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1605.9</v>
+        <v>1622.1</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1579.5</v>
+        <v>1592.9</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1603</v>
+        <v>1610.8</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>15.7</v>
+        <v>7.8</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>0.99</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1130.15</v>
+        <v>1141.8</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1127</v>
+        <v>1139.65</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1150.5</v>
+        <v>1177.6</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1124.5</v>
+        <v>1130</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1141.8</v>
+        <v>1133</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>1.03</v>
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="J125" s="13" t="n">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>125.7</v>
+        <v>127.93</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>126.13</v>
+        <v>128</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>128.54</v>
+        <v>128.8</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>125.44</v>
+        <v>124.82</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>127.93</v>
+        <v>125.22</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="J126" s="10" t="n">
-        <v>1.77</v>
+        <v>-2.71</v>
+      </c>
+      <c r="J126" s="13" t="n">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2175.8</v>
+        <v>2264.9</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2187.9</v>
+        <v>2270</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2275</v>
+        <v>2288</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2185</v>
+        <v>2250.7</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2264.9</v>
+        <v>2270.3</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>89.09999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>4.1</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>132145</v>
+        <v>132205</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>132550</v>
+        <v>132205</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>133545</v>
+        <v>132695</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>131800</v>
+        <v>130000</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>132205</v>
+        <v>130120</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="J128" s="10" t="n">
-        <v>0.05</v>
+        <v>-2085</v>
+      </c>
+      <c r="J128" s="13" t="n">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3493.5</v>
+        <v>3493.8</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3501.4</v>
+        <v>3500</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3542</v>
+        <v>3529</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3480.7</v>
+        <v>3475</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3493.8</v>
+        <v>3496</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>437.05</v>
+        <v>441</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>442.95</v>
+        <v>438</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>445.15</v>
+        <v>444.2</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>439.4</v>
+        <v>436.05</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>441</v>
+        <v>441.5</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>3.95</v>
+        <v>0.5</v>
       </c>
       <c r="J130" s="10" t="n">
-        <v>0.9</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>984.95</v>
+        <v>1000.9</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>991.2</v>
+        <v>1000.6</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1023.5</v>
+        <v>1014.75</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>990.95</v>
+        <v>991.45</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1000.9</v>
+        <v>1004.6</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>15.95</v>
+        <v>3.7</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>1.62</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6452</v>
+        <v>6578.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>6520</v>
+        <v>6590</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>6620</v>
+        <v>6675</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6437.5</v>
+        <v>6567.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>6578.5</v>
+        <v>6627</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>126.5</v>
+        <v>48.5</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>1.96</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1421.3</v>
+        <v>1417.3</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1429</v>
+        <v>1417.9</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1437.9</v>
+        <v>1445.1</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1410</v>
+        <v>1401</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1417.3</v>
+        <v>1440</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J133" s="13" t="n">
-        <v>-0.28</v>
+        <v>22.7</v>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>1.6</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>89.29000000000001</v>
+        <v>90.42</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>90.25</v>
+        <v>90.84</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>91.2</v>
+        <v>91.86</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>89.81</v>
+        <v>90.55</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>90.42</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>1.13</v>
+        <v>0.48</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>1.27</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>401.85</v>
+        <v>410.2</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>403.9</v>
+        <v>414</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>414.4</v>
+        <v>414.2</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>402.6</v>
+        <v>405.95</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>410.2</v>
+        <v>406.85</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>2.08</v>
+        <v>-3.35</v>
+      </c>
+      <c r="J135" s="13" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1687</v>
+        <v>1723.3</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1697</v>
+        <v>1725</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1735</v>
+        <v>1727.4</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1690</v>
+        <v>1700</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1723.3</v>
+        <v>1710.3</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="J136" s="10" t="n">
-        <v>2.15</v>
+        <v>-13</v>
+      </c>
+      <c r="J136" s="13" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>8949</v>
+        <v>9360</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9050</v>
+        <v>9400</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9490</v>
+        <v>9624.5</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9010</v>
+        <v>9380</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9360</v>
+        <v>9570</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>411</v>
+        <v>210</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>4.59</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>284.8</v>
+        <v>285.9</v>
       </c>
       <c r="E138" s="12" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>302.4</v>
+      </c>
+      <c r="G138" s="12" t="n">
         <v>286</v>
       </c>
-      <c r="F138" s="12" t="n">
-        <v>286.7</v>
-      </c>
-      <c r="G138" s="12" t="n">
-        <v>284.2</v>
-      </c>
       <c r="H138" s="12" t="n">
-        <v>285.9</v>
+        <v>301.3</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>1.1</v>
+        <v>15.4</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>0.39</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37665</v>
+        <v>37705</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37765</v>
+        <v>37800</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>38190</v>
+        <v>37800</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>37325</v>
+        <v>37205</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37705</v>
+        <v>37505</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v>0.11</v>
+        <v>-200</v>
+      </c>
+      <c r="J139" s="13" t="n">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4747.3</v>
+        <v>4817.5</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>4764.9</v>
+        <v>4827.6</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>4846.6</v>
+        <v>4852</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4751.2</v>
+        <v>4745.2</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4817.5</v>
+        <v>4803.5</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>1.48</v>
+        <v>-14</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>273.45</v>
+        <v>279.9</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>273.45</v>
+        <v>280</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>281.2</v>
+        <v>281.5</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>272.9</v>
+        <v>275.55</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>279.9</v>
+        <v>277.72</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v>2.36</v>
+        <v>-2.18</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>469.35</v>
+        <v>474.9</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>471</v>
+        <v>471.65</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>478.35</v>
+        <v>486.5</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>470.95</v>
+        <v>470.2</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>474.9</v>
+        <v>481.4</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>5.55</v>
+        <v>6.5</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1394.3</v>
+        <v>1399.3</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1394.3</v>
+        <v>1399.9</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1406.9</v>
+        <v>1405.3</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1390.3</v>
+        <v>1389</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1399.3</v>
+        <v>1392.6</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J144" s="10" t="n">
-        <v>0.36</v>
+        <v>-6.7</v>
+      </c>
+      <c r="J144" s="13" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3081.2</v>
+        <v>3083.6</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3083.3</v>
+        <v>3078.5</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3123.8</v>
+        <v>3152</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3075.1</v>
+        <v>3065</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3083.6</v>
+        <v>3097.6</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>0.08</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>113.09</v>
+        <v>113.88</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>113.5</v>
+        <v>112.5</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>114.54</v>
+        <v>113</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>113.42</v>
+        <v>111.21</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>113.88</v>
+        <v>111.39</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J146" s="10" t="n">
-        <v>0.7</v>
+        <v>-2.49</v>
+      </c>
+      <c r="J146" s="13" t="n">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8033</v>
+        <v>8065.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8087.5</v>
+        <v>8040</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8147</v>
+        <v>8290</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8020</v>
+        <v>8040</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8065.5</v>
+        <v>8254</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>32.5</v>
+        <v>188.5</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>0.4</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>316.4</v>
+        <v>320.9</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>318</v>
+        <v>322.8</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>324.95</v>
+        <v>322.8</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>316.95</v>
+        <v>317.65</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>320.9</v>
+        <v>319</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v>1.42</v>
+        <v>-1.9</v>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1004.15</v>
+        <v>1018.9</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1005</v>
+        <v>1025.2</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1029.5</v>
+        <v>1079.9</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1005</v>
+        <v>1025</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1018.9</v>
+        <v>1051.75</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>14.75</v>
+        <v>32.85</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>1.47</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>321.4</v>
+        <v>312.8</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>318</v>
+        <v>327.95</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>306.1</v>
+        <v>310</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>312.8</v>
+        <v>320.75</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="J150" s="13" t="n">
-        <v>-2.68</v>
+        <v>7.95</v>
+      </c>
+      <c r="J150" s="10" t="n">
+        <v>2.54</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>374</v>
+        <v>378.05</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>381.95</v>
+        <v>383.5</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>376</v>
+        <v>371.5</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>378.05</v>
+        <v>375.8</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>1.08</v>
+        <v>-2.25</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1327.8</v>
+        <v>1365.8</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1313</v>
+        <v>1358</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1371.6</v>
+        <v>1395.2</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1311</v>
+        <v>1357</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1365.8</v>
+        <v>1388.9</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>38</v>
+        <v>23.1</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>2.86</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>178.46</v>
+        <v>184.2</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>179.96</v>
+        <v>184.2</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>185.32</v>
+        <v>189.1</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>179.5</v>
+        <v>183.91</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>184.2</v>
+        <v>185.63</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>5.74</v>
+        <v>1.43</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>3.22</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>670.3</v>
+        <v>670.7</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>672.5</v>
+        <v>653.1</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>681.3</v>
+        <v>669.6</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>664</v>
+        <v>646.1</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>670.7</v>
+        <v>647.45</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>0.06</v>
+        <v>-23.25</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>-3.47</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1768.9</v>
+        <v>1815.4</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1768.9</v>
+        <v>1814.6</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1818.5</v>
+        <v>1824</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1759</v>
+        <v>1798.8</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1815.4</v>
+        <v>1808.3</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="J155" s="10" t="n">
-        <v>2.63</v>
+        <v>-7.1</v>
+      </c>
+      <c r="J155" s="13" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1101.1</v>
+        <v>1111.85</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1110.95</v>
+        <v>1102.3</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1114.8</v>
+        <v>1110.5</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1103.4</v>
+        <v>1089.15</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1111.85</v>
+        <v>1091.3</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="J156" s="10" t="n">
-        <v>0.98</v>
+        <v>-20.55</v>
+      </c>
+      <c r="J156" s="13" t="n">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>24950</v>
+        <v>25125</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25070</v>
+        <v>25200</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25465</v>
+        <v>25230</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>25020</v>
+        <v>24680</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>25125</v>
+        <v>24890</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>175</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>0.7</v>
+        <v>-235</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1011.3</v>
+        <v>974.65</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1011.3</v>
+        <v>974.5</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1012</v>
+        <v>979.75</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>963.75</v>
+        <v>949.3</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>974.65</v>
+        <v>953.25</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-36.65</v>
+        <v>-21.4</v>
       </c>
       <c r="J158" s="13" t="n">
-        <v>-3.62</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3808.9</v>
+        <v>3856</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3830.5</v>
+        <v>3856</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3881</v>
+        <v>3892</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3797</v>
+        <v>3805.5</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3856</v>
+        <v>3827.3</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>1.24</v>
+        <v>-28.7</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2493.6</v>
+        <v>2508.2</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2516.8</v>
+        <v>2508.2</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2549</v>
+        <v>2544.8</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2496.7</v>
+        <v>2484.4</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2508.2</v>
+        <v>2532.8</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>14.6</v>
+        <v>24.6</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>0.59</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1620.4</v>
+        <v>1733.5</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1625</v>
+        <v>1724</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1766.9</v>
+        <v>1763.9</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1621.9</v>
+        <v>1714.3</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1733.5</v>
+        <v>1747.3</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>113.1</v>
+        <v>13.8</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>6.98</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>600.15</v>
+        <v>611</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>603.15</v>
+        <v>609.75</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>612.7</v>
+        <v>612.55</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>593.5</v>
+        <v>591.05</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>611</v>
+        <v>595.05</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>10.85</v>
-      </c>
-      <c r="J162" s="10" t="n">
-        <v>1.81</v>
+        <v>-15.95</v>
+      </c>
+      <c r="J162" s="13" t="n">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>421.2</v>
+        <v>437.95</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>440.9</v>
+        <v>445.6</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>421.25</v>
+        <v>434.1</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>437.95</v>
+        <v>440.25</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>16.75</v>
+        <v>2.3</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>3.98</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>693.25</v>
+        <v>722.3</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>698.85</v>
+        <v>720</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>724.75</v>
+        <v>818</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>695</v>
+        <v>717.1</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>722.3</v>
+        <v>802.15</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>29.05</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>4.19</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1520.6</v>
+        <v>1574.7</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1520.6</v>
+        <v>1574.7</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1579</v>
+        <v>1623</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1518.2</v>
+        <v>1569.7</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1574.7</v>
+        <v>1598.6</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>54.1</v>
+        <v>23.9</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>3.56</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1174</v>
+        <v>1160.5</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1168</v>
+        <v>1150.2</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1183.9</v>
+        <v>1159.8</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1155</v>
+        <v>1144</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1160.5</v>
+        <v>1147.7</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-13.5</v>
+        <v>-12.8</v>
       </c>
       <c r="J166" s="13" t="n">
-        <v>-1.15</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>435</v>
+        <v>453.2</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>436.6</v>
+        <v>454</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>455.95</v>
+        <v>464.9</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>435.2</v>
+        <v>454</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>453.2</v>
+        <v>461.8</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>18.2</v>
+        <v>8.6</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>4.18</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>210.07</v>
+        <v>213.27</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>211</v>
+        <v>213.2</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>215</v>
+        <v>218.24</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>210.93</v>
+        <v>212.2</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>213.27</v>
+        <v>215.05</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>1.52</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2396.9</v>
+        <v>2447.6</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2396.9</v>
+        <v>2444</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2459</v>
+        <v>2487</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2396.9</v>
+        <v>2427.4</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2447.6</v>
+        <v>2444.7</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="J170" s="10" t="n">
-        <v>2.12</v>
+        <v>-2.9</v>
+      </c>
+      <c r="J170" s="13" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1358.5</v>
+        <v>1396.1</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1362.9</v>
+        <v>1392.5</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1400.5</v>
+        <v>1413</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1360.2</v>
+        <v>1383.6</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1396.1</v>
+        <v>1408.1</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>37.6</v>
+        <v>12</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>2.77</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2968.7</v>
+        <v>2994.4</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2970</v>
+        <v>2992.1</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3013.9</v>
+        <v>3034</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2950</v>
+        <v>2950.6</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2994.4</v>
+        <v>3001</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>25.7</v>
+        <v>6.6</v>
       </c>
       <c r="J172" s="10" t="n">
-        <v>0.87</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4410</v>
+        <v>4441.8</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4438.8</v>
+        <v>4412.3</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4464</v>
+        <v>4475</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4388.4</v>
+        <v>4395.4</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4441.8</v>
+        <v>4417</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="J173" s="10" t="n">
-        <v>0.72</v>
+        <v>-24.8</v>
+      </c>
+      <c r="J173" s="13" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4117.2</v>
+        <v>4219.8</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4125</v>
+        <v>4219.8</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4244</v>
+        <v>4250.4</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4118.6</v>
+        <v>4172.8</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4219.8</v>
+        <v>4182.9</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>102.6</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>2.49</v>
+        <v>-36.9</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1699.5</v>
+        <v>1772.5</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1710</v>
+        <v>1774</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1824.1</v>
+        <v>1816.6</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1704.1</v>
+        <v>1740.3</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1772.5</v>
+        <v>1754.9</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="J175" s="10" t="n">
-        <v>4.3</v>
+        <v>-17.6</v>
+      </c>
+      <c r="J175" s="13" t="n">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4297.3</v>
+        <v>4260.8</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4336</v>
+        <v>4260.8</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4348.5</v>
+        <v>4269.9</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4246.4</v>
+        <v>4202</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4260.8</v>
+        <v>4253.9</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-36.5</v>
+        <v>-6.9</v>
       </c>
       <c r="J176" s="13" t="n">
-        <v>-0.85</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3488.2</v>
+        <v>3552.6</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3500.5</v>
+        <v>3557.9</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3564.1</v>
+        <v>3565</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3483.6</v>
+        <v>3482.8</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3552.6</v>
+        <v>3495.9</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>1.85</v>
+        <v>-56.7</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1477.1</v>
+        <v>1479.2</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1475</v>
+        <v>1485</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1500</v>
+        <v>1498.7</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1467.9</v>
+        <v>1472</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1479.2</v>
+        <v>1477.2</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v>0.14</v>
+        <v>-2</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11998</v>
+        <v>12010</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>12148</v>
+        <v>12282</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>12240</v>
+        <v>12282</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11869</v>
+        <v>11790</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>12010</v>
+        <v>11817</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>0.1</v>
+        <v>-193</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>177</v>
+        <v>176.1</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>177.2</v>
+        <v>173.25</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>178.8</v>
+        <v>174.3</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>175.36</v>
+        <v>169.17</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>176.1</v>
+        <v>170.48</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-0.9</v>
+        <v>-5.62</v>
       </c>
       <c r="J180" s="13" t="n">
-        <v>-0.51</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>631.4</v>
+        <v>639.5</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>634.9</v>
+        <v>636.8</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>643.75</v>
+        <v>651.9</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>632.5</v>
+        <v>634.95</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>639.5</v>
+        <v>645.5</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>8.1</v>
+        <v>6</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>1.28</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>720.95</v>
+        <v>742.5</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>724.25</v>
+        <v>747</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>746.6</v>
+        <v>757.95</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>720.55</v>
+        <v>728.7</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>742.5</v>
+        <v>739.3</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>2.99</v>
+        <v>-3.2</v>
+      </c>
+      <c r="J182" s="13" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1464</v>
+        <v>1515</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1481.4</v>
+        <v>1522.4</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1529.9</v>
+        <v>1533.7</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1475</v>
+        <v>1499</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1515</v>
+        <v>1511.1</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>51</v>
-      </c>
-      <c r="J183" s="10" t="n">
-        <v>3.48</v>
+        <v>-3.9</v>
+      </c>
+      <c r="J183" s="13" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>199.36</v>
+        <v>205.05</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>199.36</v>
+        <v>204.56</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>205.25</v>
+        <v>205.68</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>199.36</v>
+        <v>201.02</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>205.05</v>
+        <v>201.58</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="J184" s="10" t="n">
-        <v>2.85</v>
+        <v>-3.47</v>
+      </c>
+      <c r="J184" s="13" t="n">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>927.4</v>
+        <v>939.65</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>929.6</v>
+        <v>925</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>953.9</v>
+        <v>925</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>922.3</v>
+        <v>905</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>939.65</v>
+        <v>911.3</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="J186" s="10" t="n">
-        <v>1.32</v>
+        <v>-28.35</v>
+      </c>
+      <c r="J186" s="13" t="n">
+        <v>-3.02</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  27-Apr-2026 03:07 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  28-Apr-2026 03:26 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27-Apr-2026 03:07 PM</t>
+          <t>28-Apr-2026 03:26 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 28-Apr-2026 03:26 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 29-Apr-2026 03:13 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>28-Apr-2026 03:26 PM</t>
+          <t>29-Apr-2026 03:13 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  28-Apr-2026 03:26 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  29-Apr-2026 03:13 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>488.75</v>
+        <v>501.7</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>492.7</v>
+        <v>505</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>506.4</v>
+        <v>512.4</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>488.1</v>
+        <v>499.55</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>501.7</v>
+        <v>502.35</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>12.95</v>
+        <v>0.65</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>2.65</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7430.5</v>
+        <v>7288</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7449</v>
+        <v>7340</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7490</v>
+        <v>7373</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7251.5</v>
+        <v>7212</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7288</v>
+        <v>7264.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-142.5</v>
+        <v>-23.5</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>-1.92</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25425</v>
+        <v>25345</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25425</v>
+        <v>25570</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25600</v>
+        <v>25770</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25200</v>
+        <v>25405</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25345</v>
+        <v>25475</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-80</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>-0.31</v>
+        <v>130</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>342.55</v>
+        <v>338.3</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>342.85</v>
+        <v>339.95</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>346.7</v>
+        <v>354.65</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>337.45</v>
+        <v>337.55</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>338.3</v>
+        <v>348.45</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>-1.24</v>
+        <v>10.15</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>63.92</v>
+        <v>63.58</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>64.34999999999999</v>
+        <v>63.95</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>64.40000000000001</v>
+        <v>66.41</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>63.14</v>
+        <v>63.3</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>63.58</v>
+        <v>65.05</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>-0.53</v>
+        <v>1.47</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>2.31</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1439.8</v>
+        <v>1439.3</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1441.9</v>
+        <v>1447.9</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1443</v>
+        <v>1457.5</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1432</v>
+        <v>1433.3</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1439.3</v>
+        <v>1436.6</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-0.5</v>
+        <v>-2.7</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>-0.03</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2321.8</v>
+        <v>2412.4</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2321.8</v>
+        <v>2427.6</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2420</v>
+        <v>2443.8</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2320.9</v>
+        <v>2388</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2412.4</v>
+        <v>2425.9</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>90.59999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>3.9</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1628.5</v>
+        <v>1637.6</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1628.4</v>
+        <v>1645</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1648</v>
+        <v>1672</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1624.5</v>
+        <v>1644.9</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1637.6</v>
+        <v>1661.1</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>9.1</v>
+        <v>23.5</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
+        <v>5418.5</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>5453.5</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>5305.5</v>
+      </c>
+      <c r="H11" s="9" t="n">
         <v>5344</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>5344</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>5454</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>5315</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>5418.5</v>
-      </c>
       <c r="I11" s="9" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>1.39</v>
+        <v>-74.5</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>460.5</v>
+        <v>458.8</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>462.85</v>
+        <v>463.7</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>465</v>
+        <v>465.5</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>458.8</v>
+        <v>454.6</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-1.7</v>
+        <v>-4.2</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>-0.37</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>318.64</v>
+        <v>319.27</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>318.15</v>
+        <v>319.27</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>320.43</v>
+        <v>323.4</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>316</v>
+        <v>311.79</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>319.27</v>
+        <v>313.1</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>0.2</v>
+        <v>-6.17</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1987.7</v>
+        <v>1976</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>2008.3</v>
+        <v>1989.4</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2014.8</v>
+        <v>1998.4</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1958</v>
+        <v>1959.5</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1976</v>
+        <v>1966.6</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-11.7</v>
+        <v>-9.4</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>-0.59</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7825</v>
+        <v>7753</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7840</v>
+        <v>7745</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7878.5</v>
+        <v>7799</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7711</v>
+        <v>7681</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7753</v>
+        <v>7709</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-72</v>
+        <v>-44</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>-0.92</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>428.55</v>
+        <v>423.65</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>429.6</v>
+        <v>428.25</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>432.45</v>
+        <v>439.45</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>422.25</v>
+        <v>422</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>423.65</v>
+        <v>424.15</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>-1.14</v>
+        <v>0.5</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>169.3</v>
+        <v>167.52</v>
       </c>
       <c r="E17" s="9" t="n">
+        <v>168.35</v>
+      </c>
+      <c r="F17" s="9" t="n">
         <v>169.26</v>
       </c>
-      <c r="F17" s="9" t="n">
-        <v>172.01</v>
-      </c>
       <c r="G17" s="9" t="n">
-        <v>167.01</v>
+        <v>165.11</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>167.52</v>
+        <v>165.73</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-1.78</v>
+        <v>-1.79</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>-1.05</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2485.2</v>
+        <v>2462.6</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2475</v>
+        <v>2469.9</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2499</v>
+        <v>2477.9</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2456.1</v>
+        <v>2438.6</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2462.6</v>
+        <v>2447.3</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-22.6</v>
+        <v>-15.3</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>-0.91</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1535</v>
+        <v>1548.9</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1545.5</v>
+        <v>1557</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1558.9</v>
+        <v>1601</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1532</v>
+        <v>1544.2</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1548.9</v>
+        <v>1552.8</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.91</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>635.6</v>
+        <v>653.85</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>639</v>
+        <v>658</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>684.9</v>
+        <v>679.95</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>636.85</v>
+        <v>650</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>653.85</v>
+        <v>656.95</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>18.25</v>
+        <v>3.1</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>2.87</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6700</v>
+        <v>6855</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6700</v>
+        <v>6867.5</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7029.5</v>
+        <v>6983.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6680</v>
+        <v>6769.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6855</v>
+        <v>6812</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>155</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>2.31</v>
+        <v>-43</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1043</v>
+        <v>1022.8</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1062.9</v>
+        <v>1030.5</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1062.9</v>
+        <v>1037.2</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1017.1</v>
+        <v>1013.5</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1022.8</v>
+        <v>1017.65</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-20.2</v>
+        <v>-5.15</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>-1.94</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1416.7</v>
+        <v>1422.6</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1415</v>
+        <v>1425.9</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1410.3</v>
+        <v>1389.3</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1422.6</v>
+        <v>1396.8</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>0.42</v>
+        <v>-25.8</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1324.2</v>
+        <v>1289</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1312</v>
+        <v>1295</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1321.4</v>
+        <v>1309.2</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1285.5</v>
+        <v>1279</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1289</v>
+        <v>1296.4</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-35.2</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>-2.66</v>
+        <v>7.4</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>9662</v>
+        <v>9495.5</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>9622</v>
+        <v>9510</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>9662.5</v>
+        <v>9709.5</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>9475</v>
+        <v>9496</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>9495.5</v>
+        <v>9543.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-166.5</v>
-      </c>
-      <c r="J25" s="13" t="n">
-        <v>-1.72</v>
+        <v>48</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1772.2</v>
+        <v>1779</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1772.1</v>
+        <v>1778</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1790.8</v>
+        <v>1793.9</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1757.7</v>
+        <v>1760.8</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1779</v>
+        <v>1764.2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>0.38</v>
+        <v>-14.8</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>921.8</v>
+        <v>923.65</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>921.8</v>
+        <v>925</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>929.9</v>
+        <v>937</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>914.35</v>
+        <v>916.6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>923.65</v>
+        <v>930</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>1.85</v>
+        <v>6.35</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.2</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2223.4</v>
+        <v>2189.3</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2237</v>
+        <v>2216</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2247.6</v>
+        <v>2247.9</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2185</v>
+        <v>2193.2</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2189.3</v>
+        <v>2199.9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-34.1</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>-1.53</v>
+        <v>10.6</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>520.5</v>
+        <v>508.7</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>519.7</v>
+        <v>513</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>521.45</v>
+        <v>518.45</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>500</v>
+        <v>500.25</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>508.7</v>
+        <v>510.2</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="J29" s="13" t="n">
-        <v>-2.27</v>
+        <v>1.5</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>181.87</v>
+        <v>178.65</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>179.66</v>
+        <v>186.01</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>183.09</v>
+        <v>204.44</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>177.7</v>
+        <v>186.01</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>178.65</v>
+        <v>198.3</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-3.22</v>
-      </c>
-      <c r="J30" s="13" t="n">
-        <v>-1.77</v>
+        <v>19.65</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>273.99</v>
+        <v>267.83</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>270</v>
+        <v>269.2</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>272.06</v>
+        <v>271.81</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>265.61</v>
+        <v>267.4</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>267.83</v>
+        <v>268.25</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-6.16</v>
-      </c>
-      <c r="J31" s="13" t="n">
-        <v>-2.25</v>
+        <v>0.42</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>435.6</v>
+        <v>435.75</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>435.6</v>
+        <v>437.05</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>441</v>
+        <v>442.8</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>433.55</v>
+        <v>435.25</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>435.75</v>
+        <v>437.55</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0.15</v>
+        <v>1.8</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.03</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>463.6</v>
+        <v>459.85</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>463.6</v>
+        <v>459.95</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>469</v>
+        <v>469.05</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>459</v>
+        <v>456.85</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>459.85</v>
+        <v>463.8</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>3.95</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1820.1</v>
+        <v>1843.8</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1826</v>
+        <v>1848</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1852</v>
+        <v>1900.4</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1812.6</v>
+        <v>1845.4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1843.8</v>
+        <v>1888.1</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>23.7</v>
+        <v>44.3</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>348.58</v>
+        <v>354.71</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>349.69</v>
+        <v>356.8</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>356</v>
+        <v>358.1</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>347.28</v>
+        <v>342.51</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>354.71</v>
+        <v>344.5</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v>1.76</v>
+        <v>-10.21</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>-2.88</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>362</v>
+        <v>362.8</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>361.95</v>
+        <v>364.7</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>364.7</v>
+        <v>368.2</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>359.15</v>
+        <v>361.25</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>362.8</v>
+        <v>362.25</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>0.22</v>
+        <v>-0.55</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>37225</v>
+        <v>37320</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>37180</v>
+        <v>37165</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>37565</v>
+        <v>37470</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>37000</v>
+        <v>36190</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>37320</v>
+        <v>36345</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>0.26</v>
+        <v>-975</v>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>312.65</v>
+        <v>307.75</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>308.7</v>
+        <v>308.4</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>313.1</v>
+        <v>310.9</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>305.15</v>
+        <v>303.15</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>307.75</v>
+        <v>303.9</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-4.9</v>
+        <v>-3.85</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>-1.57</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5717.5</v>
+        <v>5662</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5723</v>
+        <v>5674</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5735</v>
+        <v>5734.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5641</v>
+        <v>5665</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5662</v>
+        <v>5709</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-55.5</v>
-      </c>
-      <c r="J39" s="13" t="n">
-        <v>-0.97</v>
+        <v>47</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>371.85</v>
+        <v>371</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>372.2</v>
+        <v>372</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>374.15</v>
+        <v>376.9</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>367.2</v>
+        <v>367.7</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>371</v>
+        <v>369.4</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-0.85</v>
+        <v>-1.6</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>-0.23</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>140.52</v>
+        <v>137.1</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>136.27</v>
+        <v>137.36</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>138.36</v>
+        <v>139.5</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>136.21</v>
+        <v>136.22</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>137.1</v>
+        <v>137.06</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-3.42</v>
+        <v>-0.04</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>-2.43</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>915.45</v>
+        <v>883.3</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>916.95</v>
+        <v>886.5</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>919.15</v>
+        <v>898.55</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>883.3</v>
+        <v>871.75</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-32.15</v>
+        <v>-11.55</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>-3.51</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>445.95</v>
+        <v>448.5</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>447.9</v>
+        <v>453</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>455.85</v>
+        <v>457</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>446.1</v>
+        <v>448.15</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>448.5</v>
+        <v>450.55</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1560.7</v>
+        <v>1536.4</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1560.1</v>
+        <v>1539.9</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1579.2</v>
+        <v>1572.6</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>1530.8</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1536.4</v>
+        <v>1553.3</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-24.3</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>-1.56</v>
+        <v>16.9</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1317.2</v>
+        <v>1306.5</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1296.3</v>
+        <v>1307.8</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1306.5</v>
+        <v>1317.6</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>11.1</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>452.5</v>
+        <v>467</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>456.2</v>
+        <v>469.85</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>473.9</v>
+        <v>485.7</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>456.2</v>
+        <v>464.05</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>467</v>
+        <v>479.9</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>14.5</v>
+        <v>12.9</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1202.4</v>
+        <v>1200.9</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1206</v>
+        <v>1206.8</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1213.8</v>
+        <v>1229.9</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1200.9</v>
+        <v>1204</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>-0.12</v>
+        <v>3.1</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2141</v>
+        <v>2125.2</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2132.7</v>
+        <v>2135</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2136.4</v>
+        <v>2175.8</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2105</v>
+        <v>2104.6</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2125.2</v>
+        <v>2132.5</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-15.8</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>-0.74</v>
+        <v>7.3</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>514.2</v>
+        <v>510.5</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>519.15</v>
+        <v>521.95</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>508.8</v>
+        <v>508.5</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>510.5</v>
+        <v>514.6</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>-0.72</v>
+        <v>4.1</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2031.1</v>
+        <v>2010.7</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>2031.1</v>
+        <v>2027.5</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2038.3</v>
+        <v>2027.5</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1996.1</v>
+        <v>1990.1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2010.7</v>
+        <v>2007.9</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-20.4</v>
+        <v>-2.8</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>-1</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>258.68</v>
+        <v>269.63</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>258.67</v>
+        <v>270.9</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>272.5</v>
+        <v>280.89</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>256.5</v>
+        <v>269.63</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>269.63</v>
+        <v>276.01</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>10.95</v>
+        <v>6.38</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>4.23</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>271.21</v>
+        <v>275.65</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>281.52</v>
+        <v>277</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>293.51</v>
+        <v>282.49</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>273.21</v>
+        <v>274.41</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>275.65</v>
+        <v>277.37</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>4.44</v>
+        <v>1.72</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>1.64</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5233.2</v>
+        <v>5258</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5260</v>
+        <v>5288</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5286.8</v>
+        <v>5324.8</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5195.1</v>
+        <v>5251.3</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5258</v>
+        <v>5288</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>24.8</v>
+        <v>30</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>452</v>
+        <v>450.15</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>452.15</v>
+        <v>449.05</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>453.1</v>
+        <v>458.25</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>449</v>
+        <v>449.05</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>450.15</v>
+        <v>456</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="J54" s="13" t="n">
-        <v>-0.41</v>
+        <v>5.85</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1972.7</v>
+        <v>1918.8</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1982.5</v>
+        <v>1920.9</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1982.6</v>
+        <v>1980</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1884</v>
+        <v>1918</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1918.8</v>
+        <v>1949.7</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-53.9</v>
-      </c>
-      <c r="J55" s="13" t="n">
-        <v>-2.73</v>
+        <v>30.9</v>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>1.61</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1684.9</v>
+        <v>1682.6</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1685</v>
+        <v>1682.6</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1694</v>
+        <v>1758</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1674.7</v>
+        <v>1680.2</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1682.6</v>
+        <v>1724.1</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="J56" s="13" t="n">
-        <v>-0.14</v>
+        <v>41.5</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>2.47</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>75.44</v>
+        <v>73.34</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>75.12</v>
+        <v>74</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>76.8</v>
+        <v>75.48</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>72.09999999999999</v>
+        <v>72.06</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>73.34</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-2.1</v>
+        <v>-0.91</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>-2.78</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6477</v>
+        <v>6432.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6505</v>
+        <v>6470</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6505</v>
+        <v>6549.5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6416.5</v>
+        <v>6454</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6432.5</v>
+        <v>6534</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-44.5</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>101.5</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>1.58</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11252</v>
+        <v>11370</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>11284</v>
+        <v>11375.5</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11595</v>
+        <v>11575</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>11254.5</v>
+        <v>11259.5</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>11370</v>
+        <v>11325</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="J59" s="10" t="n">
-        <v>1.05</v>
+        <v>-45</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>592.45</v>
+        <v>587.9</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>594</v>
+        <v>589.8</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>595.7</v>
+        <v>605.9</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>586.45</v>
+        <v>589.35</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>587.9</v>
+        <v>594.45</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-4.55</v>
-      </c>
-      <c r="J60" s="13" t="n">
-        <v>-0.77</v>
+        <v>6.55</v>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1334.5</v>
+        <v>1354.6</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1342.4</v>
+        <v>1367</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1367.9</v>
+        <v>1375.9</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1327.4</v>
+        <v>1321.5</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1354.6</v>
+        <v>1329.8</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v>1.51</v>
+        <v>-24.8</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>-1.83</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7174</v>
+        <v>7071.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7170</v>
+        <v>7106</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7254</v>
+        <v>7294</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7053</v>
+        <v>7099</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7071.5</v>
+        <v>7189.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-102.5</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>-1.43</v>
+        <v>118</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3262.5</v>
+        <v>3308.6</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3260.1</v>
+        <v>3333</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3314.9</v>
+        <v>3382</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3256.2</v>
+        <v>3259</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3308.6</v>
+        <v>3302.1</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>1.41</v>
+        <v>-6.5</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>352.35</v>
+        <v>356.25</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>352.7</v>
+        <v>357.5</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>358.5</v>
+        <v>370.3</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>351.25</v>
+        <v>356.9</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>356.25</v>
+        <v>363.45</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>3.9</v>
+        <v>7.2</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>294.05</v>
+        <v>290.6</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>292.85</v>
+        <v>296</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>295.85</v>
+        <v>301.7</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>290</v>
+        <v>282.55</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>290.6</v>
+        <v>284.75</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-3.45</v>
+        <v>-5.85</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>-1.17</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>165.74</v>
+        <v>165.68</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>165.89</v>
+        <v>166.54</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>167.22</v>
+        <v>167.96</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>165.06</v>
+        <v>164.57</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>165.68</v>
+        <v>165.66</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2325.1</v>
+        <v>2403.7</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2328.1</v>
+        <v>2418.7</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2427.4</v>
+        <v>2474</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2327.3</v>
+        <v>2403.7</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2403.7</v>
+        <v>2413.9</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>78.59999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>3.38</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>474.85</v>
+        <v>475.25</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>474</v>
+        <v>475.6</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>477</v>
+        <v>482.7</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>471.85</v>
+        <v>473.95</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>475.25</v>
+        <v>474.9</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J69" s="10" t="n">
-        <v>0.08</v>
+        <v>-0.35</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1089.25</v>
+        <v>1092</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1088.2</v>
+        <v>1104.55</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1105.2</v>
+        <v>1107.8</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1081.5</v>
+        <v>1084</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1092</v>
+        <v>1090.05</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J70" s="10" t="n">
-        <v>0.25</v>
+        <v>-1.95</v>
+      </c>
+      <c r="J70" s="13" t="n">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1828.2</v>
+        <v>1824.6</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1829.3</v>
+        <v>1831</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1845.2</v>
+        <v>1883.8</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1820</v>
+        <v>1831</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1824.6</v>
+        <v>1862.3</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="J71" s="13" t="n">
-        <v>-0.2</v>
+        <v>37.7</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>2.07</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>694.9</v>
+        <v>705.15</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>696</v>
+        <v>708.5</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>710</v>
+        <v>730.8</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>695</v>
+        <v>695.25</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>705.15</v>
+        <v>704.55</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v>1.48</v>
+        <v>-0.6</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2778.2</v>
+        <v>2783</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2780</v>
+        <v>2798</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2848.2</v>
+        <v>2838.6</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2772</v>
+        <v>2777</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2783</v>
+        <v>2803.2</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>4.8</v>
+        <v>20.2</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.17</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>383</v>
+        <v>389.45</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>384.3</v>
+        <v>389.45</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>393</v>
+        <v>392.3</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>383.55</v>
+        <v>387.05</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>389.45</v>
+        <v>391</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>6.45</v>
+        <v>1.55</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>1.68</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4310.3</v>
+        <v>4341.4</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4310.3</v>
+        <v>4360</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4360</v>
+        <v>4397.3</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4302.5</v>
+        <v>4329</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4341.4</v>
+        <v>4351.6</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>31.1</v>
+        <v>10.2</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1274.1</v>
+        <v>1272.2</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1273.1</v>
+        <v>1278</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1281.2</v>
+        <v>1290.3</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1263</v>
+        <v>1249.2</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1272.2</v>
+        <v>1252.5</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-1.9</v>
+        <v>-19.7</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>-0.15</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1228.2</v>
+        <v>1196</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1227.9</v>
+        <v>1200</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1232.7</v>
+        <v>1210.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1192.3</v>
+        <v>1192.1</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1196</v>
+        <v>1200.2</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-32.2</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>-2.62</v>
+        <v>4.2</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2756</v>
+        <v>2760.2</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2756</v>
+        <v>2770</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2788.8</v>
+        <v>2808.3</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2738.1</v>
+        <v>2760.2</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2760.2</v>
+        <v>2787.9</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>4.2</v>
+        <v>27.7</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>789.8</v>
+        <v>782.55</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>785</v>
+        <v>785.5</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>794.5</v>
+        <v>790</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>778.3</v>
+        <v>777.35</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>782.55</v>
+        <v>779</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-7.25</v>
+        <v>-3.55</v>
       </c>
       <c r="J79" s="13" t="n">
-        <v>-0.92</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>597.3</v>
+        <v>590.15</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>594.2</v>
+        <v>592</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>598.6</v>
+        <v>602.95</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>588.5</v>
+        <v>589.6</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>590.15</v>
+        <v>594.4</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-7.15</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>-1.2</v>
+        <v>4.25</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5043</v>
+        <v>5068</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5042.5</v>
+        <v>5094</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5105.5</v>
+        <v>5208.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5019</v>
+        <v>5081.5</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5068</v>
+        <v>5114.5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>25</v>
+        <v>46.5</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1061.8</v>
+        <v>1074.3</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1060</v>
+        <v>1078</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1079.7</v>
+        <v>1080</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1055.15</v>
+        <v>1053</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1074.3</v>
+        <v>1067.2</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J82" s="10" t="n">
-        <v>1.18</v>
+        <v>-7.1</v>
+      </c>
+      <c r="J82" s="13" t="n">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>559.35</v>
+        <v>556.4</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>562</v>
+        <v>558.65</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>568.45</v>
+        <v>563.4</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>554</v>
+        <v>548.25</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>556.4</v>
+        <v>555.25</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-2.95</v>
+        <v>-1.15</v>
       </c>
       <c r="J83" s="13" t="n">
-        <v>-0.53</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>380.9</v>
+        <v>380.05</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>379.5</v>
+        <v>380.05</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>382.2</v>
+        <v>384.5</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>375</v>
+        <v>377.5</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>380.05</v>
+        <v>380.6</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J84" s="13" t="n">
-        <v>-0.22</v>
+        <v>0.55</v>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2328.3</v>
+        <v>2289.5</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2321</v>
+        <v>2305</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2334.4</v>
+        <v>2349.7</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2281.1</v>
+        <v>2291</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2289.5</v>
+        <v>2314.4</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-38.8</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>-1.67</v>
+        <v>24.9</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>31850</v>
+        <v>31255</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>31900</v>
+        <v>31415</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>32005</v>
+        <v>31695</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>31150</v>
+        <v>31075</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>31255</v>
+        <v>31575</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-595</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>-1.87</v>
+        <v>320</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>70.27</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>69.68000000000001</v>
+        <v>69.02</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>69.98</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>68.5</v>
+        <v>68.55</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>68.70999999999999</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="J87" s="13" t="n">
-        <v>-2.22</v>
+        <v>1.44</v>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>126.45</v>
+        <v>125.94</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>126.41</v>
+        <v>126.6</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>127.64</v>
+        <v>127.48</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>125</v>
+        <v>125.65</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>125.94</v>
+        <v>126.05</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="J88" s="13" t="n">
-        <v>-0.4</v>
+        <v>0.11</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>164.88</v>
+        <v>166.45</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>164.8</v>
+        <v>167.5</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>168.1</v>
+        <v>169.2</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>163.9</v>
+        <v>165.94</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>166.45</v>
+        <v>167.55</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>0.95</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>647.85</v>
+        <v>652.45</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>645.1</v>
+        <v>654</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>655</v>
+        <v>656.6</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>643.25</v>
+        <v>643</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>652.45</v>
+        <v>644.65</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J90" s="10" t="n">
-        <v>0.71</v>
+        <v>-7.8</v>
+      </c>
+      <c r="J90" s="13" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2119.5</v>
+        <v>2129.3</v>
       </c>
       <c r="E91" s="9" t="n">
+        <v>2140</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>2154.9</v>
+      </c>
+      <c r="G91" s="9" t="n">
         <v>2105.1</v>
       </c>
-      <c r="F91" s="9" t="n">
-        <v>2140.1</v>
-      </c>
-      <c r="G91" s="9" t="n">
-        <v>2101.8</v>
-      </c>
       <c r="H91" s="9" t="n">
-        <v>2129.3</v>
+        <v>2130.8</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>0.46</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4561.2</v>
+        <v>4442.4</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4514.8</v>
+        <v>4442.4</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4547.9</v>
+        <v>4507.3</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4421</v>
+        <v>4335.1</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4442.4</v>
+        <v>4345.2</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-118.8</v>
+        <v>-97.2</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>-2.6</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>900.15</v>
+        <v>885.55</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>890.15</v>
+        <v>891</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>895.7</v>
+        <v>925</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>882.45</v>
+        <v>891</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>885.55</v>
+        <v>913.75</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="J93" s="13" t="n">
-        <v>-1.62</v>
+        <v>28.2</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>3.18</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>402.3</v>
+        <v>413.95</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>419.05</v>
+        <v>421.85</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>409.6</v>
+        <v>411.55</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>413.95</v>
+        <v>413.9</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="J94" s="10" t="n">
-        <v>2.9</v>
+        <v>-0.05</v>
+      </c>
+      <c r="J94" s="13" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1170.3</v>
+        <v>1152.1</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1162.7</v>
+        <v>1158.5</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1169.4</v>
+        <v>1178.2</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1149.8</v>
+        <v>1156.8</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1152.1</v>
+        <v>1167.5</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="J95" s="13" t="n">
-        <v>-1.56</v>
+        <v>15.4</v>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>146.26</v>
+        <v>145.39</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>146.15</v>
+        <v>146.11</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>146.19</v>
+        <v>147.29</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>144.31</v>
+        <v>143.94</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>145.39</v>
+        <v>144.19</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-0.87</v>
+        <v>-1.2</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>-0.59</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1541.3</v>
+        <v>1537</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1548</v>
+        <v>1542.8</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1573.9</v>
+        <v>1552.1</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1530.2</v>
+        <v>1522.6</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1537</v>
+        <v>1542.1</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="J97" s="13" t="n">
-        <v>-0.28</v>
+        <v>5.1</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>545.1</v>
+        <v>543.85</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>545.1</v>
+        <v>544.5</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>554</v>
+        <v>552.35</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>541.8</v>
+        <v>543.7</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>543.85</v>
+        <v>550.1</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="J98" s="13" t="n">
-        <v>-0.23</v>
+        <v>6.25</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>303.85</v>
+        <v>304.45</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>304.4</v>
+        <v>305.1</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>305.8</v>
+        <v>317.5</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>302.55</v>
+        <v>305.1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>304.45</v>
+        <v>316.25</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>0.6</v>
+        <v>11.8</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>0.2</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1278.2</v>
+        <v>1265.5</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1283.5</v>
+        <v>1270.9</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1290.5</v>
+        <v>1270.9</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1262.5</v>
+        <v>1224.5</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1265.5</v>
+        <v>1228.1</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-12.7</v>
+        <v>-37.4</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>-0.99</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5606.5</v>
+        <v>5472.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5606.5</v>
+        <v>5485</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5645</v>
+        <v>5540</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5401</v>
+        <v>5435</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5472.5</v>
+        <v>5458.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-134</v>
+        <v>-14</v>
       </c>
       <c r="J101" s="13" t="n">
-        <v>-2.39</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>770.4</v>
+        <v>773.85</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>776.65</v>
+        <v>776.15</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>788</v>
+        <v>788.1</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>770.65</v>
+        <v>768.55</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>773.85</v>
+        <v>782.4</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>3.45</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>0.45</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>573.8</v>
+        <v>580.9</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>578.9</v>
+        <v>584.7</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>585.65</v>
+        <v>584.7</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>580.9</v>
+        <v>560.4</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>1.24</v>
+        <v>-20.5</v>
+      </c>
+      <c r="J103" s="13" t="n">
+        <v>-3.53</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1282.7</v>
+        <v>1281.6</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1306.8</v>
+        <v>1287.8</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1275.6</v>
+        <v>1257</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1281.6</v>
+        <v>1279.7</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-1.1</v>
+        <v>-1.9</v>
       </c>
       <c r="J104" s="13" t="n">
-        <v>-0.09</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>485.1</v>
+        <v>482.4</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>482.75</v>
+        <v>482.9</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>490</v>
+        <v>488.35</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>475.5</v>
+        <v>477.25</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>482.4</v>
+        <v>485.4</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="J105" s="13" t="n">
-        <v>-0.5600000000000001</v>
+        <v>3</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1236.25</v>
+        <v>1212</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1240</v>
+        <v>1218.6</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1246.8</v>
+        <v>1236.9</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1212</v>
+        <v>1228.15</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-24.25</v>
-      </c>
-      <c r="J106" s="13" t="n">
-        <v>-1.96</v>
+        <v>16.15</v>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>376.8</v>
+        <v>377.95</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>383.25</v>
+        <v>386.05</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>372</v>
+        <v>377.55</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>377.95</v>
+        <v>382</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>1.15</v>
+        <v>4.05</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>0.31</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>735.3</v>
+        <v>734.45</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>739.8</v>
+        <v>758.9</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>722.9</v>
+        <v>737</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>734.45</v>
+        <v>740.05</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J108" s="13" t="n">
-        <v>-0.12</v>
+        <v>5.6</v>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1416</v>
+        <v>1411.7</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1416</v>
+        <v>1411.6</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1428.7</v>
+        <v>1425.8</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1403.4</v>
+        <v>1389.2</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1411.7</v>
+        <v>1397.8</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-4.3</v>
+        <v>-13.9</v>
       </c>
       <c r="J109" s="13" t="n">
-        <v>-0.3</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1123.55</v>
+        <v>1090.45</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1132</v>
+        <v>1092.45</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1133</v>
+        <v>1115.8</v>
       </c>
       <c r="G110" s="12" t="n">
         <v>1085</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1090.45</v>
+        <v>1106.1</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-33.1</v>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v>-2.95</v>
+        <v>15.65</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>543.1</v>
+        <v>550</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>543.15</v>
+        <v>552.9</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>552.95</v>
+        <v>567.7</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>540.3</v>
+        <v>545.8</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>550</v>
+        <v>562.15</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>6.9</v>
+        <v>12.15</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>1.27</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4053.6</v>
+        <v>4037.7</v>
       </c>
       <c r="E112" s="12" t="n">
         <v>4060</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4087.9</v>
+        <v>4126</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>4023.9</v>
+        <v>4051.3</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4037.7</v>
+        <v>4096.1</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-15.9</v>
-      </c>
-      <c r="J112" s="13" t="n">
-        <v>-0.39</v>
+        <v>58.4</v>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>1.45</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>287.79</v>
+        <v>285.78</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>292.58</v>
+        <v>290.45</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>284.71</v>
+        <v>284.38</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>285.78</v>
+        <v>285.42</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-2.01</v>
+        <v>-0.36</v>
       </c>
       <c r="J113" s="13" t="n">
-        <v>-0.7</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="114">
@@ -4607,7 +4607,7 @@
         <v>150</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>4346</v>
+        <v>4380.6</v>
       </c>
       <c r="E114" s="12" t="n">
         <v/>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3589.8</v>
+        <v>3566.4</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3598.9</v>
+        <v>3589.9</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3605</v>
+        <v>3643.4</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3552</v>
+        <v>3540</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3566.4</v>
+        <v>3559.6</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-23.4</v>
+        <v>-6.8</v>
       </c>
       <c r="J115" s="13" t="n">
-        <v>-0.65</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2324.5</v>
+        <v>2302.7</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2299.1</v>
+        <v>2314</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2319.4</v>
+        <v>2333.8</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2260.3</v>
+        <v>2302.7</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2302.7</v>
+        <v>2311.4</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-21.8</v>
-      </c>
-      <c r="J116" s="13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3102.4</v>
+        <v>3088.1</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3115.9</v>
+        <v>3100</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3144</v>
+        <v>3192</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3075</v>
+        <v>3092</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3088.1</v>
+        <v>3152.3</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>-0.46</v>
+        <v>64.2</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>288.2</v>
+        <v>292.75</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>290.4</v>
+        <v>293.5</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>299.75</v>
+        <v>298.9</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>289.25</v>
+        <v>293.1</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>292.75</v>
+        <v>295.35</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>4.55</v>
+        <v>2.6</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>1.58</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>787</v>
+        <v>780.85</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>785</v>
+        <v>781.8</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>790</v>
+        <v>791.2</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>775.75</v>
+        <v>775.9</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>780.85</v>
+        <v>779.3</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-6.15</v>
+        <v>-1.55</v>
       </c>
       <c r="J119" s="13" t="n">
-        <v>-0.78</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13222</v>
+        <v>12892</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13222</v>
+        <v>13090</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13307</v>
+        <v>13548</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12828</v>
+        <v>13090</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>12892</v>
+        <v>13257</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-330</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>-2.5</v>
+        <v>365</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2830</v>
+        <v>2898</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>2835</v>
+        <v>2911.9</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>2915</v>
+        <v>2980.9</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2833.1</v>
+        <v>2862</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>2898</v>
+        <v>2968.3</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>68</v>
+        <v>70.3</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>476.5</v>
+        <v>480.85</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>478.85</v>
+        <v>480.85</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>485.9</v>
+        <v>485.95</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>474.5</v>
+        <v>475</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>480.85</v>
+        <v>478.8</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="J123" s="10" t="n">
-        <v>0.91</v>
+        <v>-2.05</v>
+      </c>
+      <c r="J123" s="13" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1603</v>
+        <v>1610.8</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1601.8</v>
+        <v>1624.7</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1622.1</v>
+        <v>1634.1</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1592.9</v>
+        <v>1601.3</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1610.8</v>
+        <v>1610.4</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>0.49</v>
+        <v>-0.4</v>
+      </c>
+      <c r="J124" s="13" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1141.8</v>
+        <v>1133</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1139.65</v>
+        <v>1143.8</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1177.6</v>
+        <v>1154</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="J125" s="13" t="n">
-        <v>-0.77</v>
+        <v>13</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>127.93</v>
+        <v>125.22</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>128</v>
+        <v>125.97</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>128.8</v>
+        <v>126.98</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>124.82</v>
+        <v>122.96</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>125.22</v>
+        <v>123.24</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-2.71</v>
+        <v>-1.98</v>
       </c>
       <c r="J126" s="13" t="n">
-        <v>-2.12</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2264.9</v>
+        <v>2270.3</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2270</v>
+        <v>2284</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2288</v>
+        <v>2338</v>
       </c>
       <c r="G127" s="9" t="n">
+        <v>2232</v>
+      </c>
+      <c r="H127" s="9" t="n">
         <v>2250.7</v>
       </c>
-      <c r="H127" s="9" t="n">
-        <v>2270.3</v>
-      </c>
       <c r="I127" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J127" s="10" t="n">
-        <v>0.24</v>
+        <v>-19.6</v>
+      </c>
+      <c r="J127" s="13" t="n">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>132205</v>
+        <v>130120</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>132205</v>
+        <v>131500</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>132695</v>
+        <v>134100</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>130000</v>
+        <v>130150</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>130120</v>
+        <v>130425</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-2085</v>
-      </c>
-      <c r="J128" s="13" t="n">
-        <v>-1.58</v>
+        <v>305</v>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3493.8</v>
+        <v>3496</v>
       </c>
       <c r="E129" s="9" t="n">
         <v>3500</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3529</v>
+        <v>3536.4</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3475</v>
+        <v>3450.3</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3496</v>
+        <v>3461.1</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>0.06</v>
+        <v>-34.9</v>
+      </c>
+      <c r="J129" s="13" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>441</v>
+        <v>441.5</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>444.2</v>
+        <v>441.75</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>436.05</v>
+        <v>430</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>441.5</v>
+        <v>433.3</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v>0.11</v>
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="J130" s="13" t="n">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1000.9</v>
+        <v>1004.6</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1000.6</v>
+        <v>1011.8</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1014.75</v>
+        <v>1021.05</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>991.45</v>
+        <v>986.3</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1004.6</v>
+        <v>991.65</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>0.37</v>
+        <v>-12.95</v>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6578.5</v>
+        <v>6627</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>6590</v>
+        <v>6670</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>6675</v>
+        <v>6816</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6567.5</v>
+        <v>6660</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>6627</v>
+        <v>6758.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>48.5</v>
+        <v>131.5</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>0.74</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1417.3</v>
+        <v>1440</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1417.9</v>
+        <v>1445</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1445.1</v>
+        <v>1470</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1401</v>
+        <v>1436.1</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1440</v>
+        <v>1465.6</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>22.7</v>
+        <v>25.6</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>90.42</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>90.84</v>
+        <v>91.5</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>91.86</v>
+        <v>92.77</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>90.55</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>90.90000000000001</v>
+        <v>91.73</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>0.48</v>
+        <v>0.83</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>0.53</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>410.2</v>
+        <v>406.85</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>414</v>
+        <v>409.5</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>414.2</v>
+        <v>410</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>405.95</v>
+        <v>399.65</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>406.85</v>
+        <v>401.3</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-3.35</v>
+        <v>-5.55</v>
       </c>
       <c r="J135" s="13" t="n">
-        <v>-0.82</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1723.3</v>
+        <v>1710.3</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1725</v>
+        <v>1714.5</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1727.4</v>
+        <v>1730.3</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1700</v>
+        <v>1693.8</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1710.3</v>
+        <v>1700.3</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="J136" s="13" t="n">
-        <v>-0.75</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9360</v>
+        <v>9570</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9400</v>
+        <v>9585.5</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9624.5</v>
+        <v>9810</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9380</v>
+        <v>9575</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9570</v>
+        <v>9688</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>210</v>
+        <v>118</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>2.24</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>285.9</v>
+        <v>301.3</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>286.25</v>
+        <v>303.9</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>302.4</v>
+        <v>307.5</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>286</v>
+        <v>299.75</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>301.3</v>
+        <v>301.4</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>15.4</v>
+        <v>0.1</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>5.39</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37705</v>
+        <v>37505</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37800</v>
+        <v>37725</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37800</v>
+        <v>37725</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>37205</v>
+        <v>36700</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37505</v>
+        <v>36845</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-200</v>
+        <v>-660</v>
       </c>
       <c r="J139" s="13" t="n">
-        <v>-0.53</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4817.5</v>
+        <v>4803.5</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>4827.6</v>
+        <v>4825</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>4852</v>
+        <v>4909.4</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4745.2</v>
+        <v>4790</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4803.5</v>
+        <v>4805.8</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-14</v>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v>-0.29</v>
+        <v>2.3</v>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>279.9</v>
+        <v>277.72</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>280</v>
+        <v>280.69</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>281.5</v>
+        <v>282.5</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>275.55</v>
+        <v>278.45</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>277.72</v>
+        <v>280.12</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="J142" s="13" t="n">
-        <v>-0.78</v>
+        <v>2.4</v>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>474.9</v>
+        <v>481.4</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>471.65</v>
+        <v>477</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>486.5</v>
+        <v>477.9</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>470.2</v>
+        <v>461.9</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>481.4</v>
+        <v>464.75</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J143" s="10" t="n">
-        <v>1.37</v>
+        <v>-16.65</v>
+      </c>
+      <c r="J143" s="13" t="n">
+        <v>-3.46</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1399.3</v>
+        <v>1392.6</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1399.9</v>
+        <v>1392.6</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1405.3</v>
+        <v>1404.8</v>
       </c>
       <c r="G144" s="12" t="n">
+        <v>1386.4</v>
+      </c>
+      <c r="H144" s="12" t="n">
         <v>1389</v>
       </c>
-      <c r="H144" s="12" t="n">
-        <v>1392.6</v>
-      </c>
       <c r="I144" s="12" t="n">
-        <v>-6.7</v>
+        <v>-3.6</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>-0.48</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3083.6</v>
+        <v>3097.6</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3078.5</v>
+        <v>3135.8</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3152</v>
+        <v>3180</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3065</v>
+        <v>3083.1</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3097.6</v>
+        <v>3091.1</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="J145" s="10" t="n">
-        <v>0.45</v>
+        <v>-6.5</v>
+      </c>
+      <c r="J145" s="13" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>113.88</v>
+        <v>111.39</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>112.5</v>
+        <v>111.62</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>113</v>
+        <v>112.62</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>111.21</v>
+        <v>110.87</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>111.39</v>
+        <v>111.18</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-2.49</v>
+        <v>-0.21</v>
       </c>
       <c r="J146" s="13" t="n">
-        <v>-2.19</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8065.5</v>
+        <v>8254</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8040</v>
+        <v>8300</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8290</v>
+        <v>8338.5</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8040</v>
+        <v>8119</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8254</v>
+        <v>8148.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>188.5</v>
-      </c>
-      <c r="J147" s="10" t="n">
-        <v>2.34</v>
+        <v>-105.5</v>
+      </c>
+      <c r="J147" s="13" t="n">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>320.9</v>
+        <v>319</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>322.8</v>
+        <v>320.1</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>322.8</v>
+        <v>323.8</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>317.65</v>
+        <v>318.25</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>319</v>
+        <v>320.35</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>-0.59</v>
+        <v>1.35</v>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1018.9</v>
+        <v>1051.75</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1025.2</v>
+        <v>1056.75</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1079.9</v>
+        <v>1099</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1025</v>
+        <v>1053.05</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1051.75</v>
+        <v>1092.55</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>32.85</v>
+        <v>40.8</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>3.22</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>312.8</v>
+        <v>320.75</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>327.95</v>
+        <v>345.65</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>310</v>
+        <v>321.8</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>320.75</v>
+        <v>341.2</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>7.95</v>
+        <v>20.45</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>2.54</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>378.05</v>
+        <v>375.8</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>377</v>
+        <v>368.05</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>383.5</v>
+        <v>372.45</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>371.5</v>
+        <v>358.1</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>375.8</v>
+        <v>363.55</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-2.25</v>
+        <v>-12.25</v>
       </c>
       <c r="J151" s="13" t="n">
-        <v>-0.6</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1365.8</v>
+        <v>1388.9</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1358</v>
+        <v>1392</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1395.2</v>
+        <v>1433.8</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1357</v>
+        <v>1391.3</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1388.9</v>
+        <v>1425.4</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>23.1</v>
+        <v>36.5</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>1.69</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>184.2</v>
+        <v>185.63</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>184.2</v>
+        <v>187</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>189.1</v>
+        <v>187.3</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>183.91</v>
+        <v>181.54</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>185.63</v>
+        <v>186.16</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>1.43</v>
+        <v>0.53</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>0.78</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>670.7</v>
+        <v>647.45</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>653.1</v>
+        <v>649.5</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>669.6</v>
+        <v>661.05</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>646.1</v>
+        <v>643.05</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>647.45</v>
+        <v>651.2</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-23.25</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>-3.47</v>
+        <v>3.75</v>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1815.4</v>
+        <v>1808.3</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1814.6</v>
+        <v>1808.6</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1824</v>
+        <v>1829.5</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1798.8</v>
+        <v>1792.9</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1808.3</v>
+        <v>1816.2</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="J155" s="13" t="n">
-        <v>-0.39</v>
+        <v>7.9</v>
+      </c>
+      <c r="J155" s="10" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1111.85</v>
+        <v>1091.3</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1102.3</v>
+        <v>1094</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1110.5</v>
+        <v>1105</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1089.15</v>
+        <v>1084.25</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1091.3</v>
+        <v>1086.9</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-20.55</v>
+        <v>-4.4</v>
       </c>
       <c r="J156" s="13" t="n">
-        <v>-1.85</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>25125</v>
+        <v>24890</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25200</v>
+        <v>25100</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25230</v>
+        <v>25355</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>24680</v>
+        <v>24500</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>24890</v>
+        <v>24555</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-235</v>
+        <v>-335</v>
       </c>
       <c r="J157" s="13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>974.65</v>
+        <v>953.25</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>974.5</v>
+        <v>965</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>979.75</v>
+        <v>975.3</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>949.3</v>
+        <v>954.9</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>953.25</v>
+        <v>956.85</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-21.4</v>
-      </c>
-      <c r="J158" s="13" t="n">
-        <v>-2.2</v>
+        <v>3.6</v>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3856</v>
+        <v>3827.3</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3856</v>
+        <v>3850</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3892</v>
+        <v>3870</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3805.5</v>
+        <v>3765.6</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3827.3</v>
+        <v>3776.8</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-28.7</v>
+        <v>-50.5</v>
       </c>
       <c r="J159" s="13" t="n">
-        <v>-0.74</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2508.2</v>
+        <v>2532.8</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2508.2</v>
+        <v>2551</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2544.8</v>
+        <v>2604</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2484.4</v>
+        <v>2538.3</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2532.8</v>
+        <v>2543.6</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>24.6</v>
+        <v>10.8</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>0.98</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1733.5</v>
+        <v>1747.3</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1724</v>
+        <v>1756</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1763.9</v>
+        <v>1789.8</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1714.3</v>
+        <v>1750</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1747.3</v>
+        <v>1778.7</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>13.8</v>
+        <v>31.4</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>611</v>
+        <v>595.05</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>609.75</v>
+        <v>597</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>612.55</v>
+        <v>605.4</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>591.05</v>
+        <v>584</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>595.05</v>
+        <v>586.25</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-15.95</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="J162" s="13" t="n">
-        <v>-2.61</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>437.95</v>
+        <v>440.25</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>435</v>
+        <v>440.25</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>445.6</v>
+        <v>443.95</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>434.1</v>
+        <v>429.9</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>440.25</v>
+        <v>432.15</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J163" s="10" t="n">
-        <v>0.53</v>
+        <v>-8.1</v>
+      </c>
+      <c r="J163" s="13" t="n">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>722.3</v>
+        <v>802.15</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>720</v>
+        <v>804.5</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>818</v>
+        <v>818.2</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>717.1</v>
+        <v>781</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>802.15</v>
+        <v>799.75</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>79.84999999999999</v>
-      </c>
-      <c r="J164" s="10" t="n">
-        <v>11.05</v>
+        <v>-2.4</v>
+      </c>
+      <c r="J164" s="13" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1574.7</v>
+        <v>1598.6</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1574.7</v>
+        <v>1607</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1623</v>
+        <v>1614.2</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1569.7</v>
+        <v>1582.7</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1598.6</v>
+        <v>1602.2</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>23.9</v>
+        <v>3.6</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>1.52</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1160.5</v>
+        <v>1147.7</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1150.2</v>
+        <v>1147.7</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1159.8</v>
+        <v>1171.2</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1144</v>
+        <v>1147.7</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1147.7</v>
+        <v>1168</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="J166" s="13" t="n">
-        <v>-1.1</v>
+        <v>20.3</v>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>1.77</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>453.2</v>
+        <v>461.8</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>454</v>
+        <v>464.3</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>464.9</v>
+        <v>464.4</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>454</v>
+        <v>449.4</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>461.8</v>
+        <v>451.5</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J168" s="10" t="n">
-        <v>1.9</v>
+        <v>-10.3</v>
+      </c>
+      <c r="J168" s="13" t="n">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>213.27</v>
+        <v>215.05</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>213.2</v>
+        <v>216.1</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>218.24</v>
+        <v>217</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>212.2</v>
+        <v>211.36</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>215.05</v>
+        <v>215.88</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>1.78</v>
+        <v>0.83</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>0.83</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
+        <v>2444.7</v>
+      </c>
+      <c r="E170" s="12" t="n">
+        <v>2451</v>
+      </c>
+      <c r="F170" s="12" t="n">
+        <v>2487.9</v>
+      </c>
+      <c r="G170" s="12" t="n">
         <v>2447.6</v>
       </c>
-      <c r="E170" s="12" t="n">
-        <v>2444</v>
-      </c>
-      <c r="F170" s="12" t="n">
-        <v>2487</v>
-      </c>
-      <c r="G170" s="12" t="n">
-        <v>2427.4</v>
-      </c>
       <c r="H170" s="12" t="n">
-        <v>2444.7</v>
+        <v>2474.7</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="J170" s="13" t="n">
-        <v>-0.12</v>
+        <v>30</v>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1396.1</v>
+        <v>1408.1</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1392.5</v>
+        <v>1414</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1413</v>
+        <v>1464</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1383.6</v>
+        <v>1405.2</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1408.1</v>
+        <v>1459.8</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>12</v>
+        <v>51.7</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>0.86</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2994.4</v>
+        <v>3001</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2992.1</v>
+        <v>3032.6</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3034</v>
+        <v>3065.1</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2950.6</v>
+        <v>2955</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>3001</v>
+        <v>2965.1</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J172" s="10" t="n">
-        <v>0.22</v>
+        <v>-35.9</v>
+      </c>
+      <c r="J172" s="13" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4441.8</v>
+        <v>4417</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4412.3</v>
+        <v>4419.9</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4475</v>
+        <v>4472.4</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4395.4</v>
+        <v>4410.2</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4417</v>
+        <v>4439.8</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-24.8</v>
-      </c>
-      <c r="J173" s="13" t="n">
-        <v>-0.5600000000000001</v>
+        <v>22.8</v>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4219.8</v>
+        <v>4182.9</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4219.8</v>
+        <v>4220</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4250.4</v>
+        <v>4281.4</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4172.8</v>
+        <v>4200</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4182.9</v>
+        <v>4231.5</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-36.9</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>-0.87</v>
+        <v>48.6</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1772.5</v>
+        <v>1754.9</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1774</v>
+        <v>1764.8</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1816.6</v>
+        <v>1767.6</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1740.3</v>
+        <v>1697</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1754.9</v>
+        <v>1701.7</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-17.6</v>
+        <v>-53.2</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>-0.99</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4260.8</v>
+        <v>4253.9</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4260.8</v>
+        <v>4273</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4269.9</v>
+        <v>4304.7</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4202</v>
+        <v>4218.7</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4253.9</v>
+        <v>4228.3</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-6.9</v>
+        <v>-25.6</v>
       </c>
       <c r="J176" s="13" t="n">
-        <v>-0.16</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3552.6</v>
+        <v>3495.9</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3557.9</v>
+        <v>3513</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3565</v>
+        <v>3602</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3482.8</v>
+        <v>3501</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3495.9</v>
+        <v>3553.9</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-56.7</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>-1.6</v>
+        <v>58</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1479.2</v>
+        <v>1477.2</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1498.7</v>
+        <v>1494.9</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1477.2</v>
+        <v>1469.6</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-2</v>
+        <v>-7.6</v>
       </c>
       <c r="J178" s="13" t="n">
-        <v>-0.14</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>12010</v>
+        <v>11817</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>12282</v>
+        <v>11870</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>12282</v>
+        <v>12060</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11790</v>
+        <v>11817</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11817</v>
+        <v>11833</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-193</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>-1.61</v>
+        <v>16</v>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>176.1</v>
+        <v>170.48</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>173.25</v>
+        <v>170.46</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>174.3</v>
+        <v>172.23</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>169.17</v>
+        <v>164.28</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>170.48</v>
+        <v>167.31</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-5.62</v>
+        <v>-3.17</v>
       </c>
       <c r="J180" s="13" t="n">
-        <v>-3.19</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>639.5</v>
+        <v>645.5</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>636.8</v>
+        <v>647.9</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>651.9</v>
+        <v>651</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>634.95</v>
+        <v>641.55</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>645.5</v>
+        <v>644.1</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="J181" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.4</v>
+      </c>
+      <c r="J181" s="13" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>742.5</v>
+        <v>739.3</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>757.95</v>
+        <v>780</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>728.7</v>
+        <v>732.2</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>739.3</v>
+        <v>773.6</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="J182" s="13" t="n">
-        <v>-0.43</v>
+        <v>34.3</v>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>4.64</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1515</v>
+        <v>1511.1</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1522.4</v>
+        <v>1524</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1533.7</v>
+        <v>1537.9</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1499</v>
+        <v>1465</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1511.1</v>
+        <v>1474.8</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-3.9</v>
+        <v>-36.3</v>
       </c>
       <c r="J183" s="13" t="n">
-        <v>-0.26</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>205.05</v>
+        <v>201.58</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>204.56</v>
+        <v>201.58</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>205.68</v>
+        <v>203.6</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>201.02</v>
+        <v>200.3</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>201.58</v>
+        <v>200.68</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-3.47</v>
+        <v>-0.9</v>
       </c>
       <c r="J184" s="13" t="n">
-        <v>-1.69</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>939.65</v>
+        <v>911.3</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>925</v>
+        <v>915</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>905</v>
+        <v>908.65</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>911.3</v>
+        <v>910.85</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-28.35</v>
+        <v>-0.45</v>
       </c>
       <c r="J186" s="13" t="n">
-        <v>-3.02</v>
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  28-Apr-2026 03:26 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  29-Apr-2026 03:13 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28-Apr-2026 03:26 PM</t>
+          <t>29-Apr-2026 03:13 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 29-Apr-2026 03:13 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 30-Apr-2026 03:10 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>29-Apr-2026 03:13 PM</t>
+          <t>30-Apr-2026 03:10 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  29-Apr-2026 03:13 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  30-Apr-2026 03:10 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>501.7</v>
+        <v>502.35</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>512.4</v>
+        <v>510.05</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>499.55</v>
+        <v>495.9</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>502.35</v>
+        <v>507.5</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>0.65</v>
+        <v>5.15</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.13</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7288</v>
+        <v>7234.91</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7340</v>
+        <v>7250</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7373</v>
+        <v>7305</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7212</v>
+        <v>7102</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7264.5</v>
+        <v>7230</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-23.5</v>
+        <v>-4.91</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>-0.32</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25345</v>
+        <v>25475</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25570</v>
+        <v>25395</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25770</v>
+        <v>25485</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25405</v>
+        <v>25250</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25475</v>
+        <v>25435</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>130</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>0.51</v>
+        <v>-40</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>338.3</v>
+        <v>348.45</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>339.95</v>
+        <v>346</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>354.65</v>
+        <v>347.55</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>337.55</v>
+        <v>340.05</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>348.45</v>
+        <v>345.5</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>3</v>
+        <v>-2.95</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>63.58</v>
+        <v>65.05</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>63.95</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>66.41</v>
+        <v>66.31</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>63.3</v>
+        <v>63.87</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>65.05</v>
+        <v>64.2</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>2.31</v>
+        <v>-0.85</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1439.3</v>
+        <v>1436.6</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1447.9</v>
+        <v>1438</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1457.5</v>
+        <v>1438</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1433.3</v>
+        <v>1406</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1436.6</v>
+        <v>1422.1</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-2.7</v>
+        <v>-14.5</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>-0.19</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2412.4</v>
+        <v>2425.9</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2427.6</v>
+        <v>2394.9</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2443.8</v>
+        <v>2420</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2388</v>
+        <v>2328.8</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2425.9</v>
+        <v>2408.4</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>-17.5</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1637.6</v>
+        <v>1661.1</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1645</v>
+        <v>1650</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1672</v>
+        <v>1677</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1644.9</v>
+        <v>1596.8</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1661.1</v>
+        <v>1657.3</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>1.44</v>
+        <v>-3.8</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5418.5</v>
+        <v>5344</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5420</v>
+        <v>5354.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5453.5</v>
+        <v>5435</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5305.5</v>
+        <v>5291</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5344</v>
+        <v>5400</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-74.5</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>-1.37</v>
+        <v>56</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>458.8</v>
+        <v>454.6</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>463.7</v>
+        <v>450.2</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>465.5</v>
+        <v>450.2</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>453</v>
+        <v>440.1</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>454.6</v>
+        <v>444.2</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-4.2</v>
+        <v>-10.4</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>-0.92</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>319.27</v>
+        <v>313.1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>319.27</v>
+        <v>311.36</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>323.4</v>
+        <v>311.55</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>311.79</v>
+        <v>306.12</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>313.1</v>
+        <v>308.71</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-6.17</v>
+        <v>-4.39</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>-1.93</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1976</v>
+        <v>1966.6</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1989.4</v>
+        <v>1956.5</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1998.4</v>
+        <v>1960</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1959.5</v>
+        <v>1895.5</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1966.6</v>
+        <v>1905</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-9.4</v>
+        <v>-61.6</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>-0.48</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7753</v>
+        <v>7709</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7745</v>
+        <v>7634.5</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7799</v>
+        <v>7680</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7681</v>
+        <v>7561.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7709</v>
+        <v>7636.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-44</v>
+        <v>-72.5</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>-0.57</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>423.65</v>
+        <v>424.15</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>428.25</v>
+        <v>420</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>439.45</v>
+        <v>420.8</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>422</v>
+        <v>406.95</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>424.15</v>
+        <v>408.4</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>0.12</v>
+        <v>-15.75</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>-3.71</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>167.52</v>
+        <v>165.73</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>168.35</v>
+        <v>164.72</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>169.26</v>
+        <v>164.72</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>165.11</v>
+        <v>160.26</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>165.73</v>
+        <v>162.09</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-1.79</v>
+        <v>-3.64</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>-1.07</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2462.6</v>
+        <v>2447.3</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2469.9</v>
+        <v>2426.7</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2477.9</v>
+        <v>2455.9</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2438.6</v>
+        <v>2385.5</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2447.3</v>
+        <v>2444.5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-15.3</v>
+        <v>-2.8</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>-0.62</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
+        <v>1552.8</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>1546</v>
+      </c>
+      <c r="F19" s="9" t="n">
         <v>1548.9</v>
       </c>
-      <c r="E19" s="9" t="n">
-        <v>1557</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>1601</v>
-      </c>
       <c r="G19" s="9" t="n">
-        <v>1544.2</v>
+        <v>1520.6</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1552.8</v>
+        <v>1529.7</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>0.25</v>
+        <v>-23.1</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>653.85</v>
+        <v>656.95</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>658</v>
+        <v>657.9</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>679.95</v>
+        <v>659.85</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>650</v>
+        <v>625.8</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>656.95</v>
+        <v>634.7</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>0.47</v>
+        <v>-22.25</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6855</v>
+        <v>6812</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6867.5</v>
+        <v>6790</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6983.5</v>
+        <v>6844.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6769.5</v>
+        <v>6703</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6812</v>
+        <v>6817.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-43</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>-0.63</v>
+        <v>5.5</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1022.8</v>
+        <v>1017.65</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1030.5</v>
+        <v>1010.65</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1037.2</v>
+        <v>1025.95</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1013.5</v>
+        <v>998</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1017.65</v>
+        <v>1015.95</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-5.15</v>
+        <v>-1.7</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>-0.5</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1422.6</v>
+        <v>1396.8</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1425.9</v>
+        <v>1392</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1433</v>
+        <v>1404</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1389.3</v>
+        <v>1378.6</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1396.8</v>
+        <v>1389.5</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-25.8</v>
+        <v>-7.3</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>-1.81</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1289</v>
+        <v>1296.4</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1295</v>
+        <v>1288</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1309.2</v>
+        <v>1288</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1279</v>
+        <v>1257.3</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1296.4</v>
+        <v>1268.3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>0.57</v>
+        <v>-28.1</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>9495.5</v>
+        <v>9543.5</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>9510</v>
+        <v>9515</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>9709.5</v>
+        <v>10045</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>9496</v>
+        <v>9355</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>9543.5</v>
+        <v>9994</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>48</v>
+        <v>450.5</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>0.51</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1779</v>
+        <v>1764.2</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1778</v>
+        <v>1777.2</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1793.9</v>
+        <v>1794.5</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1760.8</v>
+        <v>1718.7</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1764.2</v>
+        <v>1747.2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-14.8</v>
+        <v>-17</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>-0.83</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>923.65</v>
+        <v>930</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>925</v>
+        <v>945</v>
       </c>
       <c r="F27" s="9" t="n">
+        <v>975</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>933.9</v>
+      </c>
+      <c r="H27" s="9" t="n">
         <v>937</v>
       </c>
-      <c r="G27" s="9" t="n">
-        <v>916.6</v>
-      </c>
-      <c r="H27" s="9" t="n">
-        <v>930</v>
-      </c>
       <c r="I27" s="9" t="n">
-        <v>6.35</v>
+        <v>7</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2189.3</v>
+        <v>2199.9</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2216</v>
+        <v>2199.9</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2247.9</v>
+        <v>2199.9</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2193.2</v>
+        <v>2136.3</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2199.9</v>
+        <v>2160.8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>0.48</v>
+        <v>-39.1</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
+        <v>510.2</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>536.4</v>
+      </c>
+      <c r="G29" s="9" t="n">
         <v>508.7</v>
       </c>
-      <c r="E29" s="9" t="n">
-        <v>513</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>518.45</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>500.25</v>
-      </c>
       <c r="H29" s="9" t="n">
-        <v>510.2</v>
+        <v>521.05</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1.5</v>
+        <v>10.85</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>0.29</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>178.65</v>
+        <v>198.3</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>186.01</v>
+        <v>198</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>204.44</v>
+        <v>201.96</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>186.01</v>
+        <v>194.47</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>198.3</v>
+        <v>199.72</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>19.65</v>
+        <v>1.42</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>11</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>267.83</v>
+        <v>268.25</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>269.2</v>
+        <v>265.9</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>271.81</v>
+        <v>266.22</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>267.4</v>
+        <v>260</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>268.25</v>
+        <v>263.46</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>0.16</v>
+        <v>-4.79</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>435.75</v>
+        <v>437.55</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>437.05</v>
+        <v>436.45</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>442.8</v>
+        <v>436.45</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>435.25</v>
+        <v>424.5</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>437.55</v>
+        <v>431.3</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>0.41</v>
+        <v>-6.25</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>459.85</v>
+        <v>463.8</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>459.95</v>
+        <v>458</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>469.05</v>
+        <v>474.9</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>456.85</v>
+        <v>455.75</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>463.8</v>
+        <v>473.1</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>3.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>0.86</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1843.8</v>
+        <v>1888.1</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1848</v>
+        <v>1860</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1900.4</v>
+        <v>1906</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1845.4</v>
+        <v>1860</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1888.1</v>
+        <v>1886.8</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v>2.4</v>
+        <v>-1.3</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>354.71</v>
+        <v>344.5</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>356.8</v>
+        <v>344.4</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>358.1</v>
+        <v>354.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>342.51</v>
+        <v>342.04</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>344.5</v>
+        <v>352.41</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-10.21</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>-2.88</v>
+        <v>7.91</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>362.8</v>
+        <v>362.25</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>364.7</v>
+        <v>360.5</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>368.2</v>
+        <v>361.65</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>361.25</v>
+        <v>354.25</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>362.25</v>
+        <v>359.65</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-0.55</v>
+        <v>-2.6</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>-0.15</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>37320</v>
+        <v>36345</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>37165</v>
+        <v>36500</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>37470</v>
+        <v>36500</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>36190</v>
+        <v>35675</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>36345</v>
+        <v>35995</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-975</v>
+        <v>-350</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>-2.61</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>307.75</v>
+        <v>303.9</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>308.4</v>
+        <v>300.05</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>310.9</v>
+        <v>302.35</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>303.15</v>
+        <v>295.55</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>303.9</v>
+        <v>300.45</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-3.85</v>
+        <v>-3.45</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>-1.25</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5662</v>
+        <v>5709</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5674</v>
+        <v>5720</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5734.5</v>
+        <v>5752</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5665</v>
+        <v>5644</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5709</v>
+        <v>5726</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.83</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>371</v>
+        <v>369.4</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>372</v>
+        <v>368.5</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>376.9</v>
+        <v>370.5</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>367.7</v>
+        <v>364.3</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>369.4</v>
+        <v>369.45</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="J40" s="13" t="n">
-        <v>-0.43</v>
+        <v>0.05</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>137.1</v>
+        <v>137.06</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>137.36</v>
+        <v>136.71</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>139.5</v>
+        <v>136.71</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>136.22</v>
+        <v>133.46</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>137.06</v>
+        <v>134.65</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.04</v>
+        <v>-2.41</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>-0.03</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>883.3</v>
+        <v>871.75</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>886.5</v>
+        <v>874</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>898.55</v>
+        <v>874</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>870</v>
+        <v>850.1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>871.75</v>
+        <v>865.25</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-11.55</v>
+        <v>-6.5</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>-1.31</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>448.5</v>
+        <v>450.55</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>448.15</v>
+        <v>436.15</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>450.55</v>
+        <v>438.05</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>0.46</v>
+        <v>-12.5</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1536.4</v>
+        <v>1553.3</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1539.9</v>
+        <v>1521.8</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1572.6</v>
+        <v>1592.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1530.8</v>
+        <v>1472.3</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1553.3</v>
+        <v>1562.9</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>16.9</v>
+        <v>9.6</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1.1</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1306.5</v>
+        <v>1317.6</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1312</v>
+        <v>1317.9</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1322</v>
+        <v>1329.8</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1307.8</v>
+        <v>1305</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1317.6</v>
+        <v>1309.6</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v>0.85</v>
+        <v>-8</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>467</v>
+        <v>479.9</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>469.85</v>
+        <v>484.45</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>485.7</v>
+        <v>491.25</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>464.05</v>
+        <v>478.4</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>479.9</v>
+        <v>481.45</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>12.9</v>
+        <v>1.55</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>2.76</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1200.9</v>
+        <v>1204</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1206.8</v>
+        <v>1202</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1229.9</v>
+        <v>1207.7</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1200</v>
+        <v>1178.1</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1204</v>
+        <v>1195.9</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>0.26</v>
+        <v>-8.1</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2125.2</v>
+        <v>2132.5</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2135</v>
+        <v>2115.2</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2175.8</v>
+        <v>2140.2</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2104.6</v>
+        <v>2090</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2132.5</v>
+        <v>2096.2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>0.34</v>
+        <v>-36.3</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>510.5</v>
+        <v>514.6</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>514</v>
+        <v>510.6</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>521.95</v>
+        <v>512.05</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>508.5</v>
+        <v>506</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>514.6</v>
+        <v>508.85</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>0.8</v>
+        <v>-5.75</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2010.7</v>
+        <v>2007.9</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>2027.5</v>
+        <v>2004</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2027.5</v>
+        <v>2007.9</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1990.1</v>
+        <v>1955.7</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2007.9</v>
+        <v>1981.7</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-2.8</v>
+        <v>-26.2</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>-0.14</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>269.63</v>
+        <v>276.01</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>270.9</v>
+        <v>272.4</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>280.89</v>
+        <v>275.09</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>269.63</v>
+        <v>266</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>276.01</v>
+        <v>272.36</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v>2.37</v>
+        <v>-3.65</v>
+      </c>
+      <c r="J51" s="13" t="n">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>275.65</v>
+        <v>277.37</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>277</v>
+        <v>277.04</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>282.49</v>
+        <v>277.37</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>274.41</v>
+        <v>268.6</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>277.37</v>
+        <v>270.09</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>0.62</v>
+        <v>-7.28</v>
+      </c>
+      <c r="J52" s="13" t="n">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5258</v>
+        <v>5288</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5288</v>
+        <v>5279.7</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5324.8</v>
+        <v>5308.8</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5251.3</v>
+        <v>5120</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5288</v>
+        <v>5266.4</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="J53" s="10" t="n">
-        <v>0.57</v>
+        <v>-21.6</v>
+      </c>
+      <c r="J53" s="13" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>450.15</v>
+        <v>456</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>449.05</v>
+        <v>456</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>458.25</v>
+        <v>456</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>449.05</v>
+        <v>440.35</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>456</v>
+        <v>441.5</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>1.3</v>
+        <v>-14.5</v>
+      </c>
+      <c r="J54" s="13" t="n">
+        <v>-3.18</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1918.8</v>
+        <v>1949.7</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1920.9</v>
+        <v>1959</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1980</v>
+        <v>1966</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1918</v>
+        <v>1897.2</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1949.7</v>
+        <v>1906.3</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="J55" s="10" t="n">
-        <v>1.61</v>
+        <v>-43.4</v>
+      </c>
+      <c r="J55" s="13" t="n">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1682.6</v>
+        <v>1724.1</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1682.6</v>
+        <v>1711.8</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>1758</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1680.2</v>
+        <v>1709.5</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1724.1</v>
+        <v>1736.9</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>41.5</v>
+        <v>12.8</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>2.47</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>73.34</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>74</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>75.48</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>72.06</v>
+        <v>69.5</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>72.43000000000001</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-0.91</v>
+        <v>-1.25</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>-1.24</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6432.5</v>
+        <v>6534</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6470</v>
+        <v>6530</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6549.5</v>
+        <v>6547</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6454</v>
+        <v>6429</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6534</v>
+        <v>6502.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>1.58</v>
+        <v>-31.5</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11370</v>
+        <v>11325</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>11375.5</v>
+        <v>11300</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11575</v>
+        <v>11300</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>11259.5</v>
+        <v>11006</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>11325</v>
+        <v>11166.5</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-45</v>
+        <v>-158.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>-0.4</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>587.9</v>
+        <v>594.45</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>589.8</v>
+        <v>590</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>605.9</v>
+        <v>591.9</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>589.35</v>
+        <v>579.8</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>594.45</v>
+        <v>587</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>1.11</v>
+        <v>-7.45</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1354.6</v>
+        <v>1329.8</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1367</v>
+        <v>1327</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1375.9</v>
+        <v>1340.3</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1321.5</v>
+        <v>1313.6</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1329.8</v>
+        <v>1322.9</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-24.8</v>
+        <v>-6.9</v>
       </c>
       <c r="J61" s="13" t="n">
-        <v>-1.83</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7071.5</v>
+        <v>7189.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7106</v>
+        <v>7120</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7294</v>
+        <v>7146</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7099</v>
+        <v>6978</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7189.5</v>
+        <v>7109</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>1.67</v>
+        <v>-80.5</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3308.6</v>
+        <v>3302.1</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3333</v>
+        <v>3290</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3382</v>
+        <v>3314.4</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3259</v>
+        <v>3215.2</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3302.1</v>
+        <v>3241.6</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-6.5</v>
+        <v>-60.5</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>-0.2</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>356.25</v>
+        <v>363.45</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>357.5</v>
+        <v>362</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>370.3</v>
+        <v>363.2</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>356.9</v>
+        <v>356</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>363.45</v>
+        <v>360.55</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J64" s="10" t="n">
-        <v>2.02</v>
+        <v>-2.9</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>290.6</v>
+        <v>284.75</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>296</v>
+        <v>284.7</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>301.7</v>
+        <v>287.95</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>282.55</v>
+        <v>280</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>284.75</v>
+        <v>286.95</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-5.85</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>-2.01</v>
+        <v>2.2</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>165.68</v>
+        <v>165.66</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>166.54</v>
+        <v>164.68</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>167.96</v>
+        <v>164.68</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>164.57</v>
+        <v>161.31</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>165.66</v>
+        <v>163.23</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.02</v>
+        <v>-2.43</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>-0.01</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2403.7</v>
+        <v>2413.9</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2418.7</v>
+        <v>2400.1</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2474</v>
+        <v>2455.9</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2403.7</v>
+        <v>2385.6</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2413.9</v>
+        <v>2406.3</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J67" s="10" t="n">
-        <v>0.42</v>
+        <v>-7.6</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>475.25</v>
+        <v>474.9</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>475.6</v>
+        <v>474.7</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>482.7</v>
+        <v>476.25</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>473.95</v>
+        <v>466</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>474.9</v>
+        <v>469.3</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-0.35</v>
+        <v>-5.6</v>
       </c>
       <c r="J69" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1092</v>
+        <v>1090.05</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1104.55</v>
+        <v>1085.1</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1107.8</v>
+        <v>1089.9</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1084</v>
+        <v>1043.05</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1090.05</v>
+        <v>1067.1</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-1.95</v>
+        <v>-22.95</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>-0.18</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1824.6</v>
+        <v>1862.3</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1831</v>
+        <v>1863.2</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1883.8</v>
+        <v>1863.2</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1831</v>
+        <v>1815.5</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1862.3</v>
+        <v>1835.2</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>2.07</v>
+        <v>-27.1</v>
+      </c>
+      <c r="J71" s="13" t="n">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>705.15</v>
+        <v>704.55</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>708.5</v>
+        <v>705</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>730.8</v>
+        <v>722.5</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>695.25</v>
+        <v>690</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>704.55</v>
+        <v>699.7</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-0.6</v>
+        <v>-4.85</v>
       </c>
       <c r="J72" s="13" t="n">
-        <v>-0.09</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
+        <v>2803.2</v>
+      </c>
+      <c r="E73" s="9" t="n">
         <v>2783</v>
       </c>
-      <c r="E73" s="9" t="n">
-        <v>2798</v>
-      </c>
       <c r="F73" s="9" t="n">
-        <v>2838.6</v>
+        <v>2801.4</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2777</v>
+        <v>2727</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2803.2</v>
+        <v>2794.5</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="J73" s="10" t="n">
-        <v>0.73</v>
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="J73" s="13" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>389.45</v>
+        <v>391</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>389.45</v>
+        <v>389.65</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>392.3</v>
+        <v>389.65</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>387.05</v>
+        <v>375.5</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>391</v>
+        <v>380.05</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J74" s="10" t="n">
-        <v>0.4</v>
+        <v>-10.95</v>
+      </c>
+      <c r="J74" s="13" t="n">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4341.4</v>
+        <v>4351.6</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4360</v>
+        <v>4349</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4397.3</v>
+        <v>4379</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4329</v>
+        <v>4289.3</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4351.6</v>
+        <v>4338.8</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J75" s="10" t="n">
-        <v>0.23</v>
+        <v>-12.8</v>
+      </c>
+      <c r="J75" s="13" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1272.2</v>
+        <v>1252.5</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1278</v>
+        <v>1252</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1290.3</v>
+        <v>1252</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1249.2</v>
+        <v>1233</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1252.5</v>
+        <v>1240.6</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-19.7</v>
+        <v>-11.9</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>-1.55</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1196</v>
+        <v>1200.2</v>
       </c>
       <c r="E77" s="9" t="n">
         <v>1200</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1210.8</v>
+        <v>1213.7</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1192.1</v>
+        <v>1184</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1200.2</v>
+        <v>1199.1</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>0.35</v>
+        <v>-1.1</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2760.2</v>
+        <v>2787.9</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2770</v>
+        <v>2770.1</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2808.3</v>
+        <v>2774.9</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2760.2</v>
+        <v>2703.7</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2787.9</v>
+        <v>2712.6</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>1</v>
+        <v>-75.3</v>
+      </c>
+      <c r="J78" s="13" t="n">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>782.55</v>
+        <v>779</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>785.5</v>
+        <v>770</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>790</v>
+        <v>778.8</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>777.35</v>
+        <v>762.25</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>779</v>
+        <v>771.7</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-3.55</v>
+        <v>-7.3</v>
       </c>
       <c r="J79" s="13" t="n">
-        <v>-0.45</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>590.15</v>
+        <v>594.4</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>592</v>
+        <v>594.35</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>602.95</v>
+        <v>594.35</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>589.6</v>
+        <v>578.4</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>594.4</v>
+        <v>586.9</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>0.72</v>
+        <v>-7.5</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5068</v>
+        <v>5114.5</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5094</v>
+        <v>5080</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5208.5</v>
+        <v>5114.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5081.5</v>
+        <v>5020</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5114.5</v>
+        <v>5099</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>0.92</v>
+        <v>-15.5</v>
+      </c>
+      <c r="J81" s="13" t="n">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1074.3</v>
+        <v>1067.2</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1078</v>
+        <v>1058.5</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1080</v>
+        <v>1063.85</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1053</v>
+        <v>1030.4</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1067.2</v>
+        <v>1038</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-7.1</v>
+        <v>-29.2</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>-0.66</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>556.4</v>
+        <v>555.25</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>558.65</v>
+        <v>553.35</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>563.4</v>
+        <v>555.25</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>548.25</v>
+        <v>532.05</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>555.25</v>
+        <v>534.85</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-1.15</v>
+        <v>-20.4</v>
       </c>
       <c r="J83" s="13" t="n">
-        <v>-0.21</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>380.05</v>
+        <v>380.6</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>380.05</v>
+        <v>375</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>384.5</v>
+        <v>376.8</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>377.5</v>
+        <v>369.3</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>380.6</v>
+        <v>374.55</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J84" s="10" t="n">
-        <v>0.14</v>
+        <v>-6.05</v>
+      </c>
+      <c r="J84" s="13" t="n">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2289.5</v>
+        <v>2314.4</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2305</v>
+        <v>2312</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2349.7</v>
+        <v>2368.8</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2291</v>
+        <v>2211.6</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2314.4</v>
+        <v>2250.9</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>1.09</v>
+        <v>-63.5</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>31255</v>
+        <v>31575</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>31415</v>
+        <v>31550</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>31695</v>
+        <v>31550</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>31075</v>
+        <v>30855</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>31575</v>
+        <v>31030</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>320</v>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v>1.02</v>
+        <v>-545</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>68.70999999999999</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>69.02</v>
+        <v>69.7</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>71.15000000000001</v>
+        <v>70</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>68.55</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>70.15000000000001</v>
+        <v>69.64</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="J87" s="10" t="n">
-        <v>2.1</v>
+        <v>-0.51</v>
+      </c>
+      <c r="J87" s="13" t="n">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>125.94</v>
+        <v>126.05</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>126.6</v>
+        <v>125.7</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>127.48</v>
+        <v>125.92</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>125.65</v>
+        <v>123.8</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>126.05</v>
+        <v>125.19</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v>0.09</v>
+        <v>-0.86</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>166.45</v>
+        <v>167.55</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>167.5</v>
+        <v>167.9</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>169.2</v>
+        <v>167.9</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>165.94</v>
+        <v>165.1</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>167.55</v>
+        <v>166.02</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J89" s="10" t="n">
-        <v>0.66</v>
+        <v>-1.53</v>
+      </c>
+      <c r="J89" s="13" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>652.45</v>
+        <v>644.65</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>656.6</v>
+        <v>644.5</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>643</v>
+        <v>626.7</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>644.65</v>
+        <v>635.85</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-7.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>-1.2</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2129.3</v>
+        <v>2130.8</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2140</v>
+        <v>2130.8</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2154.9</v>
+        <v>2139</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2105.1</v>
+        <v>2080</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2130.8</v>
+        <v>2103.6</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J91" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-27.2</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4442.4</v>
+        <v>4345.2</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4442.4</v>
+        <v>4250</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4507.3</v>
+        <v>4313</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4335.1</v>
+        <v>4172.8</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4345.2</v>
+        <v>4295.3</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-97.2</v>
+        <v>-49.9</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>-2.19</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>885.55</v>
+        <v>913.75</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>891</v>
+        <v>895.25</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>913.75</v>
+        <v>916.05</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>28.2</v>
+        <v>2.3</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>3.18</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>413.95</v>
+        <v>413.9</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>421.85</v>
+        <v>413.9</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>411.55</v>
+        <v>407</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>413.9</v>
+        <v>409.95</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-0.05</v>
+        <v>-3.95</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>-0.01</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1152.1</v>
+        <v>1167.5</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1158.5</v>
+        <v>1167.5</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1178.2</v>
+        <v>1189.8</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1156.8</v>
+        <v>1159.6</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1167.5</v>
+        <v>1181.8</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>145.39</v>
+        <v>144.19</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>146.11</v>
+        <v>142.5</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>147.29</v>
+        <v>143.4</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>143.94</v>
+        <v>141.12</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>144.19</v>
+        <v>142.25</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-1.2</v>
+        <v>-1.94</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>-0.83</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1537</v>
+        <v>1542.1</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1542.8</v>
+        <v>1542.1</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1552.1</v>
+        <v>1590</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1522.6</v>
+        <v>1524.3</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1542.1</v>
+        <v>1530.9</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="J97" s="10" t="n">
-        <v>0.33</v>
+        <v>-11.2</v>
+      </c>
+      <c r="J97" s="13" t="n">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>543.85</v>
+        <v>550.1</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>544.5</v>
+        <v>548</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>552.35</v>
+        <v>550</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>543.7</v>
+        <v>536.15</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>550.1</v>
+        <v>539.55</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>1.15</v>
+        <v>-10.55</v>
+      </c>
+      <c r="J98" s="13" t="n">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>304.45</v>
+        <v>316.25</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>305.1</v>
+        <v>316.25</v>
       </c>
       <c r="F99" s="9" t="n">
         <v>317.5</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>305.1</v>
+        <v>313.3</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>316.25</v>
+        <v>314.9</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>3.88</v>
+        <v>-1.35</v>
+      </c>
+      <c r="J99" s="13" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1265.5</v>
+        <v>1228.1</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1270.9</v>
+        <v>1224</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1270.9</v>
+        <v>1234.4</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1224.5</v>
+        <v>1201.1</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1228.1</v>
+        <v>1223.1</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-37.4</v>
+        <v>-5</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>-2.96</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5472.5</v>
+        <v>5458.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5485</v>
+        <v>5436</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5540</v>
+        <v>5436</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5435</v>
+        <v>5216</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5458.5</v>
+        <v>5287</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-14</v>
+        <v>-171.5</v>
       </c>
       <c r="J101" s="13" t="n">
-        <v>-0.26</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>773.85</v>
+        <v>782.4</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>776.15</v>
+        <v>782.4</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>788.1</v>
+        <v>784.3</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>768.55</v>
+        <v>763.7</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>782.4</v>
+        <v>767.4</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>1.1</v>
+        <v>-15</v>
+      </c>
+      <c r="J102" s="13" t="n">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>580.9</v>
+        <v>560.4</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>584.7</v>
+        <v>556</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>584.7</v>
+        <v>564.85</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>557</v>
+        <v>549.3</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>560.4</v>
+        <v>561.15</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-20.5</v>
-      </c>
-      <c r="J103" s="13" t="n">
-        <v>-3.53</v>
+        <v>0.75</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1281.6</v>
+        <v>1279.7</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1283</v>
+        <v>1272.5</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1287.8</v>
+        <v>1273.4</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1257</v>
+        <v>1250.4</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1279.7</v>
+        <v>1264.5</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-1.9</v>
+        <v>-15.2</v>
       </c>
       <c r="J104" s="13" t="n">
-        <v>-0.15</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>482.4</v>
+        <v>485.4</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>482.9</v>
+        <v>483.75</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>488.35</v>
+        <v>483.75</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>477.25</v>
+        <v>469.6</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>485.4</v>
+        <v>478.6</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>0.62</v>
+        <v>-6.8</v>
+      </c>
+      <c r="J105" s="13" t="n">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1212</v>
+        <v>1228.15</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1218.6</v>
+        <v>1232</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1236.9</v>
+        <v>1244</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1212</v>
+        <v>1162.4</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1228.15</v>
+        <v>1187.65</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="J106" s="10" t="n">
-        <v>1.33</v>
+        <v>-40.5</v>
+      </c>
+      <c r="J106" s="13" t="n">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>377.95</v>
+        <v>382</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>378</v>
+        <v>376.6</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>386.05</v>
+        <v>386.85</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>377.55</v>
+        <v>375.3</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>382</v>
+        <v>383.3</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>4.05</v>
+        <v>1.3</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>1.07</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>734.45</v>
+        <v>740.05</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>737</v>
+        <v>738.05</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>758.9</v>
+        <v>767.2</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>737</v>
+        <v>727.65</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>740.05</v>
+        <v>759.05</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>0.76</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1411.7</v>
+        <v>1397.8</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1411.6</v>
+        <v>1386.1</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1425.8</v>
+        <v>1400</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1389.2</v>
+        <v>1363</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1397.8</v>
+        <v>1367.2</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-13.9</v>
+        <v>-30.6</v>
       </c>
       <c r="J109" s="13" t="n">
-        <v>-0.98</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1090.45</v>
+        <v>1106.1</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1092.45</v>
+        <v>1086.3</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1115.8</v>
+        <v>1112.95</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1106.1</v>
+        <v>1100.95</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>15.65</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>1.44</v>
+        <v>-5.15</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>550</v>
+        <v>562.15</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>552.9</v>
+        <v>562.15</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>567.7</v>
+        <v>562.15</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>545.8</v>
+        <v>549.6</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>562.15</v>
+        <v>554.7</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="J111" s="10" t="n">
-        <v>2.21</v>
+        <v>-7.45</v>
+      </c>
+      <c r="J111" s="13" t="n">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4037.7</v>
+        <v>4096.1</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>4060</v>
+        <v>4083</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4126</v>
+        <v>4100</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>4051.3</v>
+        <v>3990</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4096.1</v>
+        <v>4014</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="J112" s="10" t="n">
-        <v>1.45</v>
+        <v>-82.09999999999999</v>
+      </c>
+      <c r="J112" s="13" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>285.78</v>
+        <v>285.42</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>286</v>
+        <v>284.42</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>290.45</v>
+        <v>284.42</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>284.38</v>
+        <v>277.38</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>285.42</v>
+        <v>279.73</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-0.36</v>
+        <v>-5.69</v>
       </c>
       <c r="J113" s="13" t="n">
-        <v>-0.13</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="114">
@@ -4607,7 +4607,7 @@
         <v>150</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>4380.6</v>
+        <v>4323.1</v>
       </c>
       <c r="E114" s="12" t="n">
         <v/>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3566.4</v>
+        <v>3559.6</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3589.9</v>
+        <v>3541.8</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3643.4</v>
+        <v>3644.1</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3540</v>
+        <v>3477.6</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3559.6</v>
+        <v>3626.3</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="J115" s="13" t="n">
-        <v>-0.19</v>
+        <v>66.7</v>
+      </c>
+      <c r="J115" s="10" t="n">
+        <v>1.87</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2302.7</v>
+        <v>2311.4</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2314</v>
+        <v>2297</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2333.8</v>
+        <v>2317.4</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2302.7</v>
+        <v>2277.7</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2311.4</v>
+        <v>2305.2</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v>0.38</v>
+        <v>-6.2</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3088.1</v>
+        <v>3152.3</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3100</v>
+        <v>3105.4</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3192</v>
+        <v>3117.3</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3092</v>
+        <v>3047</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3152.3</v>
+        <v>3097.5</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>2.08</v>
+        <v>-54.8</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>292.75</v>
+        <v>295.35</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>293.5</v>
+        <v>296</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>298.9</v>
+        <v>297</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>293.1</v>
+        <v>290.2</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>295.35</v>
+        <v>294.35</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J118" s="10" t="n">
-        <v>0.89</v>
+        <v>-1</v>
+      </c>
+      <c r="J118" s="13" t="n">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>780.85</v>
+        <v>779.3</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>781.8</v>
+        <v>778.1</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>791.2</v>
+        <v>779.5</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>775.9</v>
+        <v>765.65</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>779.3</v>
+        <v>775</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-1.55</v>
+        <v>-4.3</v>
       </c>
       <c r="J119" s="13" t="n">
-        <v>-0.2</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>12892</v>
+        <v>13257</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13090</v>
+        <v>13134</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13548</v>
+        <v>13360</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13090</v>
+        <v>12970</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13257</v>
+        <v>13314</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>365</v>
+        <v>57</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>2.83</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2898</v>
+        <v>2968.3</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>2911.9</v>
+        <v>2975</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>2980.9</v>
+        <v>2985.1</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2862</v>
+        <v>2925.7</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>2968.3</v>
+        <v>2971.5</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>70.3</v>
+        <v>3.2</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>2.43</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>480.85</v>
+        <v>478.8</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>480.85</v>
+        <v>476</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>485.95</v>
+        <v>481.95</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>475</v>
+        <v>470.95</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>478.8</v>
+        <v>476.5</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-2.05</v>
+        <v>-2.3</v>
       </c>
       <c r="J123" s="13" t="n">
-        <v>-0.43</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1610.8</v>
+        <v>1610.4</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1624.7</v>
+        <v>1598</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1634.1</v>
+        <v>1608.9</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1601.3</v>
+        <v>1572.1</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1610.4</v>
+        <v>1585.7</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-0.4</v>
+        <v>-24.7</v>
       </c>
       <c r="J124" s="13" t="n">
-        <v>-0.02</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="E125" s="9" t="n">
+        <v>1135.95</v>
+      </c>
+      <c r="F125" s="9" t="n">
         <v>1143.8</v>
       </c>
-      <c r="F125" s="9" t="n">
-        <v>1154</v>
-      </c>
       <c r="G125" s="9" t="n">
-        <v>1132</v>
+        <v>1116.95</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1146</v>
+        <v>1135.65</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>1.15</v>
+        <v>-10.35</v>
+      </c>
+      <c r="J125" s="13" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>125.22</v>
+        <v>123.24</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>125.97</v>
+        <v>123.24</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>126.98</v>
+        <v>123.25</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>122.96</v>
+        <v>119.12</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>123.24</v>
+        <v>121.21</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-1.98</v>
+        <v>-2.03</v>
       </c>
       <c r="J126" s="13" t="n">
-        <v>-1.58</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2270.3</v>
+        <v>2250.7</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2284</v>
+        <v>2314.5</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2338</v>
+        <v>2349.2</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2232</v>
+        <v>2240.8</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2250.7</v>
+        <v>2276.7</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-19.6</v>
-      </c>
-      <c r="J127" s="13" t="n">
-        <v>-0.86</v>
+        <v>26</v>
+      </c>
+      <c r="J127" s="10" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>130120</v>
+        <v>130425</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>131500</v>
+        <v>130355</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>134100</v>
+        <v>131100</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>130150</v>
+        <v>128750</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>130425</v>
+        <v>129710</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>305</v>
-      </c>
-      <c r="J128" s="10" t="n">
-        <v>0.23</v>
+        <v>-715</v>
+      </c>
+      <c r="J128" s="13" t="n">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3496</v>
+        <v>3461.1</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3536.4</v>
+        <v>3459.2</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3450.3</v>
+        <v>3385.1</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3461.1</v>
+        <v>3424.2</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-34.9</v>
+        <v>-36.9</v>
       </c>
       <c r="J129" s="13" t="n">
-        <v>-1</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>441.5</v>
+        <v>433.3</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>441.75</v>
+        <v>432.45</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>430</v>
+        <v>394.25</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>433.3</v>
+        <v>399.3</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-8.199999999999999</v>
+        <v>-34</v>
       </c>
       <c r="J130" s="13" t="n">
-        <v>-1.86</v>
+        <v>-7.85</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1004.6</v>
+        <v>991.65</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>1011.8</v>
+        <v>991.65</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>1021.05</v>
+        <v>995</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>986.3</v>
+        <v>968.25</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>991.65</v>
+        <v>972.85</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-12.95</v>
+        <v>-18.8</v>
       </c>
       <c r="J131" s="13" t="n">
-        <v>-1.29</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6627</v>
+        <v>6758.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>6670</v>
+        <v>7050</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>6816</v>
+        <v>7200</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6660</v>
+        <v>6660.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>6758.5</v>
+        <v>6821</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>131.5</v>
+        <v>62.5</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>1.98</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1440</v>
+        <v>1465.6</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1445</v>
+        <v>1466</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="G133" s="9" t="n">
         <v>1436.1</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1465.6</v>
+        <v>1458.6</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v>1.78</v>
+        <v>-7</v>
+      </c>
+      <c r="J133" s="13" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>90.90000000000001</v>
+        <v>91.73</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>91.5</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>92.77</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>89.93000000000001</v>
+        <v>89.75</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>91.73</v>
+        <v>90.37</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="J134" s="10" t="n">
-        <v>0.91</v>
+        <v>-1.36</v>
+      </c>
+      <c r="J134" s="13" t="n">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>406.85</v>
+        <v>401.3</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>409.5</v>
+        <v>400</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>410</v>
+        <v>400.3</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>399.65</v>
+        <v>393.15</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>401.3</v>
+        <v>399.15</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-5.55</v>
+        <v>-2.15</v>
       </c>
       <c r="J135" s="13" t="n">
-        <v>-1.36</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1710.3</v>
+        <v>1700.3</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1714.5</v>
+        <v>1700.1</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1730.3</v>
+        <v>1700.1</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1693.8</v>
+        <v>1658.1</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1700.3</v>
+        <v>1669.6</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-10</v>
+        <v>-30.7</v>
       </c>
       <c r="J136" s="13" t="n">
-        <v>-0.58</v>
+        <v>-1.81</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9570</v>
+        <v>9688</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9585.5</v>
+        <v>9715</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9810</v>
+        <v>9825</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9575</v>
+        <v>9611</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9688</v>
+        <v>9726.5</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>118</v>
+        <v>38.5</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>1.23</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>301.3</v>
+        <v>301.4</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>303.9</v>
+        <v>304.9</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>307.5</v>
+        <v>307.45</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>299.75</v>
+        <v>296.9</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>301.4</v>
+        <v>299.55</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J138" s="10" t="n">
-        <v>0.03</v>
+        <v>-1.85</v>
+      </c>
+      <c r="J138" s="13" t="n">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37505</v>
+        <v>36845</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37725</v>
+        <v>36975</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37725</v>
+        <v>37190</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>36700</v>
+        <v>36230</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>36845</v>
+        <v>36785</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-660</v>
+        <v>-60</v>
       </c>
       <c r="J139" s="13" t="n">
-        <v>-1.76</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4803.5</v>
+        <v>4805.8</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>4825</v>
+        <v>4805.8</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>4909.4</v>
+        <v>4829.9</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4790</v>
+        <v>4761.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4805.8</v>
+        <v>4800</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>0.05</v>
+        <v>-5.8</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>277.72</v>
+        <v>280.12</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>280.69</v>
+        <v>278.45</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>282.5</v>
+        <v>279</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>278.45</v>
+        <v>274.01</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>280.12</v>
+        <v>276.76</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v>0.86</v>
+        <v>-3.36</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>481.4</v>
+        <v>464.75</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>477.9</v>
+        <v>464.7</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>461.9</v>
+        <v>447</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>464.75</v>
+        <v>448.4</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-16.65</v>
+        <v>-16.35</v>
       </c>
       <c r="J143" s="13" t="n">
-        <v>-3.46</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1392.6</v>
+        <v>1389</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1392.6</v>
+        <v>1378.7</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1404.8</v>
+        <v>1384.8</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1386.4</v>
+        <v>1355</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1389</v>
+        <v>1375.7</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-3.6</v>
+        <v>-13.3</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>-0.26</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3097.6</v>
+        <v>3091.1</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3135.8</v>
+        <v>3090</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3180</v>
+        <v>3090</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3083.1</v>
+        <v>3015.6</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3091.1</v>
+        <v>3054.8</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-6.5</v>
+        <v>-36.3</v>
       </c>
       <c r="J145" s="13" t="n">
-        <v>-0.21</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>111.39</v>
+        <v>111.18</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>111.62</v>
+        <v>110.8</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>112.62</v>
+        <v>110.8</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>110.87</v>
+        <v>108.11</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>111.18</v>
+        <v>109.36</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-0.21</v>
+        <v>-1.82</v>
       </c>
       <c r="J146" s="13" t="n">
-        <v>-0.19</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8254</v>
+        <v>8148.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8300</v>
+        <v>8132.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8338.5</v>
+        <v>8163.5</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8119</v>
+        <v>7970.5</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8148.5</v>
+        <v>8110.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-105.5</v>
+        <v>-38</v>
       </c>
       <c r="J147" s="13" t="n">
-        <v>-1.28</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>319</v>
+        <v>320.35</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>320.1</v>
+        <v>319.6</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>323.8</v>
+        <v>321.25</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>318.25</v>
+        <v>315.95</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>320.35</v>
+        <v>318.35</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v>0.42</v>
+        <v>-2</v>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1051.75</v>
+        <v>1092.55</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1056.75</v>
+        <v>1085.5</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1099</v>
+        <v>1089.55</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1053.05</v>
+        <v>1056.2</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1092.55</v>
+        <v>1068.9</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="J149" s="10" t="n">
-        <v>3.88</v>
+        <v>-23.65</v>
+      </c>
+      <c r="J149" s="13" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>320.75</v>
+        <v>341.2</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>323</v>
+        <v>340.4</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>345.65</v>
+        <v>341.6</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>321.8</v>
+        <v>333.8</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>341.2</v>
+        <v>336.55</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="J150" s="10" t="n">
-        <v>6.38</v>
+        <v>-4.65</v>
+      </c>
+      <c r="J150" s="13" t="n">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>375.8</v>
+        <v>363.55</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>368.05</v>
+        <v>361.1</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>372.45</v>
+        <v>361.1</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>358.1</v>
+        <v>352.75</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>363.55</v>
+        <v>354.3</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-12.25</v>
+        <v>-9.25</v>
       </c>
       <c r="J151" s="13" t="n">
-        <v>-3.26</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1388.9</v>
+        <v>1425.4</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1392</v>
+        <v>1409</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1433.8</v>
+        <v>1437</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1391.3</v>
+        <v>1393.1</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1425.4</v>
+        <v>1430.8</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>36.5</v>
+        <v>5.4</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>2.63</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>185.63</v>
+        <v>186.16</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>187</v>
+        <v>184.98</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>187.3</v>
+        <v>185.4</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>181.54</v>
+        <v>179.7</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>186.16</v>
+        <v>184.62</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="J153" s="10" t="n">
-        <v>0.29</v>
+        <v>-1.54</v>
+      </c>
+      <c r="J153" s="13" t="n">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>647.45</v>
+        <v>651.2</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>649.5</v>
+        <v>650</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>661.05</v>
+        <v>650</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>643.05</v>
+        <v>632.15</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>651.2</v>
+        <v>643.9</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>0.58</v>
+        <v>-7.3</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1808.3</v>
+        <v>1816.2</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1808.6</v>
+        <v>1814.9</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1829.5</v>
+        <v>1826</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1792.9</v>
+        <v>1785.2</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1816.2</v>
+        <v>1819</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>7.9</v>
+        <v>2.8</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>0.44</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1091.3</v>
+        <v>1086.9</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1094</v>
+        <v>1075</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1105</v>
+        <v>1077.7</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1084.25</v>
+        <v>1063</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1086.9</v>
+        <v>1068.45</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-4.4</v>
+        <v>-18.45</v>
       </c>
       <c r="J156" s="13" t="n">
-        <v>-0.4</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>24890</v>
+        <v>24555</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25100</v>
+        <v>24450</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25355</v>
+        <v>24450</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>24500</v>
+        <v>23800</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>24555</v>
+        <v>24195</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-335</v>
+        <v>-360</v>
       </c>
       <c r="J157" s="13" t="n">
-        <v>-1.35</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>953.25</v>
+        <v>956.85</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>965</v>
+        <v>945.2</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>975.3</v>
+        <v>950</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>954.9</v>
+        <v>921</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>956.85</v>
+        <v>937.35</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>0.38</v>
+        <v>-19.5</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3827.3</v>
+        <v>3776.8</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3850</v>
+        <v>3790</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3870</v>
+        <v>3847.6</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3765.6</v>
+        <v>3734.5</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3776.8</v>
+        <v>3808.2</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-50.5</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>-1.32</v>
+        <v>31.4</v>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2532.8</v>
+        <v>2543.6</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2551</v>
+        <v>2543.5</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2604</v>
+        <v>2543.5</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2538.3</v>
+        <v>2488.9</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2543.6</v>
+        <v>2518.6</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J160" s="10" t="n">
-        <v>0.43</v>
+        <v>-25</v>
+      </c>
+      <c r="J160" s="13" t="n">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1747.3</v>
+        <v>1778.7</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1756</v>
+        <v>1771</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1789.8</v>
+        <v>1815</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1750</v>
+        <v>1761.4</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1778.7</v>
+        <v>1808.3</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>31.4</v>
+        <v>29.6</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>595.05</v>
+        <v>586.25</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>605.4</v>
+        <v>609</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>584</v>
+        <v>586.45</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>586.25</v>
+        <v>605.6</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="J162" s="13" t="n">
-        <v>-1.48</v>
+        <v>19.35</v>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>440.25</v>
+        <v>432.15</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>440.25</v>
+        <v>431.95</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>443.95</v>
+        <v>518.55</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>429.9</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>432.15</v>
+        <v>467.65</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="J163" s="13" t="n">
-        <v>-1.84</v>
+        <v>35.5</v>
+      </c>
+      <c r="J163" s="10" t="n">
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>802.15</v>
+        <v>799.75</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>804.5</v>
+        <v>831</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>818.2</v>
+        <v>854.85</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>781</v>
+        <v>797.5</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>799.75</v>
+        <v>809</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="J164" s="13" t="n">
-        <v>-0.3</v>
+        <v>9.25</v>
+      </c>
+      <c r="J164" s="10" t="n">
+        <v>1.16</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1598.6</v>
+        <v>1602.2</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1607</v>
+        <v>1582</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1614.2</v>
+        <v>1590.1</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1582.7</v>
+        <v>1568.3</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1602.2</v>
+        <v>1580.5</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J165" s="10" t="n">
-        <v>0.23</v>
+        <v>-21.7</v>
+      </c>
+      <c r="J165" s="13" t="n">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1147.7</v>
+        <v>1168</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1147.7</v>
+        <v>1170</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1171.2</v>
+        <v>1170</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1147.7</v>
+        <v>1139.4</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1168</v>
+        <v>1144.6</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="J166" s="10" t="n">
-        <v>1.77</v>
+        <v>-23.4</v>
+      </c>
+      <c r="J166" s="13" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>461.8</v>
+        <v>451.5</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>464.3</v>
+        <v>450</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>464.4</v>
+        <v>450</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>449.4</v>
+        <v>439.3</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>451.5</v>
+        <v>444.55</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-10.3</v>
+        <v>-6.95</v>
       </c>
       <c r="J168" s="13" t="n">
-        <v>-2.23</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>215.05</v>
+        <v>215.88</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>216.1</v>
+        <v>215.78</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>217</v>
+        <v>215.78</v>
       </c>
       <c r="G169" s="9" t="n">
+        <v>210</v>
+      </c>
+      <c r="H169" s="9" t="n">
         <v>211.36</v>
       </c>
-      <c r="H169" s="9" t="n">
-        <v>215.88</v>
-      </c>
       <c r="I169" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="J169" s="10" t="n">
-        <v>0.39</v>
+        <v>-4.52</v>
+      </c>
+      <c r="J169" s="13" t="n">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2444.7</v>
+        <v>2474.7</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2451</v>
+        <v>2479</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2487.9</v>
+        <v>2491</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2447.6</v>
+        <v>2438</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2474.7</v>
+        <v>2473.9</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="J170" s="10" t="n">
-        <v>1.23</v>
+        <v>-0.8</v>
+      </c>
+      <c r="J170" s="13" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1408.1</v>
+        <v>1459.8</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1414</v>
+        <v>1459.7</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1464</v>
+        <v>1482</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1405.2</v>
+        <v>1445.6</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1459.8</v>
+        <v>1473.5</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>51.7</v>
+        <v>13.7</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>3.67</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>3001</v>
+        <v>2965.1</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>3032.6</v>
+        <v>2965</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3065.1</v>
+        <v>2980</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2955</v>
+        <v>2892</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2965.1</v>
+        <v>2947.9</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-35.9</v>
+        <v>-17.2</v>
       </c>
       <c r="J172" s="13" t="n">
-        <v>-1.2</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4417</v>
+        <v>4439.8</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4419.9</v>
+        <v>4438</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4472.4</v>
+        <v>4438</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4410.2</v>
+        <v>4358</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4439.8</v>
+        <v>4385.2</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J173" s="10" t="n">
-        <v>0.52</v>
+        <v>-54.6</v>
+      </c>
+      <c r="J173" s="13" t="n">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4182.9</v>
+        <v>4231.5</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4220</v>
+        <v>4231.7</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4281.4</v>
+        <v>4234.7</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4200</v>
+        <v>4146.1</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4231.5</v>
+        <v>4185.1</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>1.16</v>
+        <v>-46.4</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1754.9</v>
+        <v>1701.7</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1764.8</v>
+        <v>1678.5</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1767.6</v>
+        <v>1769.9</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1697</v>
+        <v>1666.1</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1701.7</v>
+        <v>1736</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-53.2</v>
-      </c>
-      <c r="J175" s="13" t="n">
-        <v>-3.03</v>
+        <v>34.3</v>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>2.02</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4253.9</v>
+        <v>4228.3</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4273</v>
+        <v>4215.1</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4304.7</v>
+        <v>4218.4</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4218.7</v>
+        <v>4124</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4228.3</v>
+        <v>4144.6</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-25.6</v>
+        <v>-83.7</v>
       </c>
       <c r="J176" s="13" t="n">
-        <v>-0.6</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3495.9</v>
+        <v>3553.9</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3513</v>
+        <v>3462</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3602</v>
+        <v>3519</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3501</v>
+        <v>3415.1</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3553.9</v>
+        <v>3492.9</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>1.66</v>
+        <v>-61</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1477.2</v>
+        <v>1469.6</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1480</v>
+        <v>1468.8</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1494.9</v>
+        <v>1473.6</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1468</v>
+        <v>1445.5</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1469.6</v>
+        <v>1458.6</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-7.6</v>
+        <v>-11</v>
       </c>
       <c r="J178" s="13" t="n">
-        <v>-0.51</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11817</v>
+        <v>11833</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11870</v>
+        <v>11777</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>12060</v>
+        <v>11777</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11817</v>
+        <v>11484</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11833</v>
+        <v>11586</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>0.14</v>
+        <v>-247</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>170.48</v>
+        <v>167.31</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>170.46</v>
+        <v>165</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>172.23</v>
+        <v>166.75</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>164.28</v>
+        <v>162.61</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>167.31</v>
+        <v>165.94</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-3.17</v>
+        <v>-1.37</v>
       </c>
       <c r="J180" s="13" t="n">
-        <v>-1.86</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>645.5</v>
+        <v>644.1</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>647.9</v>
+        <v>644.1</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>641.55</v>
+        <v>629.8</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>644.1</v>
+        <v>641.85</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-1.4</v>
+        <v>-2.25</v>
       </c>
       <c r="J181" s="13" t="n">
-        <v>-0.22</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>739.3</v>
+        <v>773.6</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>745</v>
+        <v>289.5</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>780</v>
+        <v>292</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>732.2</v>
+        <v>268.7</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>773.6</v>
+        <v>271.55</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>4.64</v>
+        <v>-502.05</v>
+      </c>
+      <c r="J182" s="13" t="n">
+        <v>-64.90000000000001</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1511.1</v>
+        <v>1474.8</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1524</v>
+        <v>1470</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1537.9</v>
+        <v>1470</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1465</v>
+        <v>1418.2</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1474.8</v>
+        <v>1430.4</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-36.3</v>
+        <v>-44.4</v>
       </c>
       <c r="J183" s="13" t="n">
-        <v>-2.4</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>201.58</v>
+        <v>200.68</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>201.58</v>
+        <v>200.89</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>203.6</v>
+        <v>202.15</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>200.3</v>
+        <v>200</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>200.68</v>
+        <v>200.65</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-0.9</v>
+        <v>-0.03</v>
       </c>
       <c r="J184" s="13" t="n">
-        <v>-0.45</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>911.3</v>
+        <v>910.85</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>915</v>
+        <v>910.9</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>922</v>
+        <v>915.4</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>908.65</v>
+        <v>890.4</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>910.85</v>
+        <v>891.9</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-0.45</v>
+        <v>-18.95</v>
       </c>
       <c r="J186" s="13" t="n">
-        <v>-0.05</v>
+        <v>-2.08</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  29-Apr-2026 03:13 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  30-Apr-2026 03:10 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29-Apr-2026 03:13 PM</t>
+          <t>30-Apr-2026 03:10 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 30-Apr-2026 03:10 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 01-May-2026 02:17 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>30-Apr-2026 03:10 PM</t>
+          <t>01-May-2026 02:17 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  30-Apr-2026 03:10 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  01-May-2026 02:17 PM</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
         <v>150</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>4323.1</v>
+        <v/>
       </c>
       <c r="E114" s="12" t="n">
         <v/>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  30-Apr-2026 03:10 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  01-May-2026 02:17 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30-Apr-2026 03:10 PM</t>
+          <t>01-May-2026 02:17 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 01-May-2026 02:17 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 04-May-2026 03:10 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>01-May-2026 02:17 PM</t>
+          <t>04-May-2026 03:10 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  01-May-2026 02:17 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  04-May-2026 03:10 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>502.35</v>
+        <v>507.5</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>510.05</v>
+        <v>523.1</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>495.9</v>
+        <v>509</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>507.5</v>
+        <v>513.1</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>5.15</v>
+        <v>5.6</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7234.91</v>
+        <v>7230</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7250</v>
+        <v>7269</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7305</v>
+        <v>7363</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7102</v>
+        <v>7185</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7230</v>
+        <v>7236.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-4.91</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>6.5</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25475</v>
+        <v>25435</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25395</v>
+        <v>25480</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25485</v>
+        <v>25835</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25250</v>
+        <v>25365</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25435</v>
+        <v>25415</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>-0.16</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>348.45</v>
+        <v>345.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>347.55</v>
+        <v>360.5</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>340.05</v>
+        <v>340.7</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>345.5</v>
+        <v>345.85</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>-0.85</v>
+        <v>0.35</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>65.05</v>
+        <v>64.2</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>64.90000000000001</v>
+        <v>64.52</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>66.31</v>
+        <v>66.34</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>63.87</v>
+        <v>62.38</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>64.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>-1.31</v>
+        <v>1.73</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>2.69</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1436.6</v>
+        <v>1422.1</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1438</v>
+        <v>1412.1</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1438</v>
+        <v>1436.5</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1406</v>
+        <v>1391</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1422.1</v>
+        <v>1398.2</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-14.5</v>
+        <v>-23.9</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>-1.01</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2425.9</v>
+        <v>2408.4</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2394.9</v>
+        <v>2390.4</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2420</v>
+        <v>2515</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2328.8</v>
+        <v>2375</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2408.4</v>
+        <v>2485.7</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>-0.72</v>
+        <v>77.3</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>3.21</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1661.1</v>
+        <v>1657.3</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1650</v>
+        <v>1702</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1677</v>
+        <v>1748.6</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1596.8</v>
+        <v>1687.3</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1657.3</v>
+        <v>1742.6</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>-0.23</v>
+        <v>85.3</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>5.15</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5344</v>
+        <v>5400</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5354.5</v>
+        <v>5382</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5435</v>
+        <v>5393.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5291</v>
+        <v>5316</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5400</v>
+        <v>5360.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>1.05</v>
+        <v>-39.5</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>454.6</v>
+        <v>444.2</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>450.2</v>
+        <v>446</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>450.2</v>
+        <v>460.75</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>440.1</v>
+        <v>438.05</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>444.2</v>
+        <v>445.3</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>-2.29</v>
+        <v>1.1</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>313.1</v>
+        <v>308.71</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>311.36</v>
+        <v>308.7</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>311.55</v>
+        <v>313.5</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>306.12</v>
+        <v>303.95</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>308.71</v>
+        <v>307.7</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-4.39</v>
+        <v>-1.01</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>-1.4</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1966.6</v>
+        <v>1905</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1956.5</v>
+        <v>1910.1</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1960</v>
+        <v>1930.3</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1895.5</v>
+        <v>1830</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1905</v>
+        <v>1873</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-61.6</v>
+        <v>-32</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>-3.13</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7709</v>
+        <v>7636.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7634.5</v>
+        <v>7699.5</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7680</v>
+        <v>7790</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7561.5</v>
+        <v>7673</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7636.5</v>
+        <v>7737.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-72.5</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>101</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>424.15</v>
+        <v>408.4</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>420</v>
+        <v>411.25</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>420.8</v>
+        <v>417.85</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>406.95</v>
+        <v>408</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>408.4</v>
+        <v>409.45</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-15.75</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>-3.71</v>
+        <v>1.05</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>165.73</v>
+        <v>162.09</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>164.72</v>
+        <v>162.29</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>164.72</v>
+        <v>164.05</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>160.26</v>
+        <v>159.1</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>162.09</v>
+        <v>160.77</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-3.64</v>
+        <v>-1.32</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>-2.2</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2447.3</v>
+        <v>2444.5</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2426.7</v>
+        <v>2460</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2455.9</v>
+        <v>2507</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2385.5</v>
+        <v>2442.3</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2444.5</v>
+        <v>2448.1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>-0.11</v>
+        <v>3.6</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1552.8</v>
+        <v>1529.7</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1546</v>
+        <v>1534.3</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1548.9</v>
+        <v>1574.3</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1520.6</v>
+        <v>1534.3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1529.7</v>
+        <v>1559.6</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-23.1</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>-1.49</v>
+        <v>29.9</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>656.95</v>
+        <v>634.7</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>657.9</v>
+        <v>641.95</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>659.85</v>
+        <v>665.8</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>625.8</v>
+        <v>638.1</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>634.7</v>
+        <v>643.15</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-22.25</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>-3.39</v>
+        <v>8.449999999999999</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6812</v>
+        <v>6817.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6790</v>
+        <v>6890</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6844.5</v>
+        <v>7030</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6703</v>
+        <v>6857</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6817.5</v>
+        <v>6949.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>5.5</v>
+        <v>132</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>0.08</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1017.65</v>
+        <v>1015.95</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1010.65</v>
+        <v>1023.7</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1025.95</v>
+        <v>1035.2</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>998</v>
+        <v>1012.1</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1015.95</v>
+        <v>1015</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-1.7</v>
+        <v>-0.95</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>-0.17</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1396.8</v>
+        <v>1389.5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1404</v>
+        <v>1398</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1378.6</v>
+        <v>1367.1</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1389.5</v>
+        <v>1376</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-7.3</v>
+        <v>-13.5</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>-0.52</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1296.4</v>
+        <v>1268.3</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1288</v>
+        <v>1268.3</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1288</v>
+        <v>1294.4</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1257.3</v>
+        <v>1264.5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1268.3</v>
+        <v>1275.1</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-28.1</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>-2.17</v>
+        <v>6.8</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>9543.5</v>
+        <v>9994</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>9515</v>
+        <v>10244</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10045</v>
+        <v>10477.5</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>9355</v>
+        <v>10067</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>9994</v>
+        <v>10132</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>450.5</v>
+        <v>138</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>4.72</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1764.2</v>
+        <v>1747.2</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1777.2</v>
+        <v>1749.2</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1794.5</v>
+        <v>1787</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1718.7</v>
+        <v>1747.1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1747.2</v>
+        <v>1770.4</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-17</v>
-      </c>
-      <c r="J26" s="13" t="n">
-        <v>-0.96</v>
+        <v>23.2</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>1.33</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>945</v>
+        <v>938.1</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>975</v>
+        <v>966</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>933.9</v>
+        <v>938.1</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>937</v>
+        <v>950.2</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>7</v>
+        <v>13.2</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>0.75</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2199.9</v>
+        <v>2160.8</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2199.9</v>
+        <v>2182.5</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2199.9</v>
+        <v>2215.4</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2136.3</v>
+        <v>2172.5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2160.8</v>
+        <v>2205</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-39.1</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>-1.78</v>
+        <v>44.2</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>510.2</v>
+        <v>521.05</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>511.5</v>
+        <v>524.5</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>536.4</v>
+        <v>533.95</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>508.7</v>
+        <v>517.2</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>521.05</v>
+        <v>524.85</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>10.85</v>
+        <v>3.8</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2.13</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>198.3</v>
+        <v>199.72</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>198</v>
+        <v>202.7</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>201.96</v>
+        <v>212.66</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>194.47</v>
+        <v>201.3</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>199.72</v>
+        <v>206.76</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>1.42</v>
+        <v>7.04</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>0.72</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>268.25</v>
+        <v>263.46</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>265.9</v>
+        <v>264.95</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>266.22</v>
+        <v>271.6</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>260</v>
+        <v>264.2</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>263.46</v>
+        <v>265.1</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-4.79</v>
-      </c>
-      <c r="J31" s="13" t="n">
-        <v>-1.79</v>
+        <v>1.64</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>437.55</v>
+        <v>431.3</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>436.45</v>
+        <v>433</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>436.45</v>
+        <v>438.6</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>424.5</v>
+        <v>428.6</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>431.3</v>
+        <v>433.55</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>-1.43</v>
+        <v>2.25</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>463.8</v>
+        <v>473.1</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>458</v>
+        <v>473.1</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>474.9</v>
+        <v>480.2</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>455.75</v>
+        <v>468.1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>473.1</v>
+        <v>470.3</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>2.01</v>
+        <v>-2.8</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1888.1</v>
+        <v>1886.8</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1860</v>
+        <v>1873.2</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1906</v>
+        <v>1895.3</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1860</v>
+        <v>1821.7</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1886.8</v>
+        <v>1827.1</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-1.3</v>
+        <v>-59.7</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>344.5</v>
+        <v>352.41</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>344.4</v>
+        <v>355</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>354.9</v>
+        <v>399</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>342.04</v>
+        <v>353.7</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>352.41</v>
+        <v>377.05</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>7.91</v>
+        <v>24.64</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>2.3</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>362.25</v>
+        <v>359.65</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>360.5</v>
+        <v>359.2</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>361.65</v>
+        <v>366.5</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>354.25</v>
+        <v>359.2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>359.65</v>
+        <v>360.6</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="J36" s="13" t="n">
-        <v>-0.72</v>
+        <v>0.95</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>36345</v>
+        <v>35995</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>36500</v>
+        <v>36150</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>36500</v>
+        <v>36490</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>35675</v>
+        <v>35475</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>35995</v>
+        <v>35850</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-350</v>
+        <v>-145</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>-0.96</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>303.9</v>
+        <v>300.45</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>300.05</v>
+        <v>302.5</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>302.35</v>
+        <v>305.9</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>295.55</v>
+        <v>300.1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>300.45</v>
+        <v>301.7</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="J38" s="13" t="n">
-        <v>-1.14</v>
+        <v>1.25</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5709</v>
+        <v>5726</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5720</v>
+        <v>5730</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5752</v>
+        <v>5821.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5644</v>
+        <v>5715</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5726</v>
+        <v>5792.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>17</v>
+        <v>66.5</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>0.3</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>369.4</v>
+        <v>369.45</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>368.5</v>
+        <v>371.7</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>370.5</v>
+        <v>372.65</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>364.3</v>
+        <v>365.35</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>369.45</v>
+        <v>366.1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>0.01</v>
+        <v>-3.35</v>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>137.06</v>
+        <v>134.65</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>136.71</v>
+        <v>135.34</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>136.71</v>
+        <v>137.78</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>133.46</v>
+        <v>134.18</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>134.65</v>
+        <v>134.8</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-2.41</v>
-      </c>
-      <c r="J41" s="13" t="n">
-        <v>-1.76</v>
+        <v>0.15</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>871.75</v>
+        <v>865.25</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>874</v>
+        <v>898.5</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>850.1</v>
+        <v>874.1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>865.25</v>
+        <v>896.5</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>-0.75</v>
+        <v>31.25</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>3.61</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>450.55</v>
+        <v>438.05</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>452</v>
+        <v>443.8</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>436.15</v>
+        <v>439.35</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>438.05</v>
+        <v>441.55</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>-2.77</v>
+        <v>3.5</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1553.3</v>
+        <v>1562.9</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1521.8</v>
+        <v>1564.8</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1592.2</v>
+        <v>1649</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1472.3</v>
+        <v>1564.8</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1562.9</v>
+        <v>1639.5</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>9.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.62</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1317.6</v>
+        <v>1309.6</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1317.9</v>
+        <v>1320</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1329.8</v>
+        <v>1337.4</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1305</v>
+        <v>1313.6</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1309.6</v>
+        <v>1335</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-8</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>-0.61</v>
+        <v>25.4</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>1.94</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>479.9</v>
+        <v>481.45</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>484.45</v>
+        <v>481.6</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>491.25</v>
+        <v>487</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>478.4</v>
+        <v>475.6</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>481.45</v>
+        <v>479.95</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>0.32</v>
+        <v>-1.5</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1204</v>
+        <v>1195.9</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1202</v>
+        <v>1209.8</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1207.7</v>
+        <v>1211.2</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1178.1</v>
+        <v>1147.1</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1195.9</v>
+        <v>1151.6</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-8.1</v>
+        <v>-44.3</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>-0.67</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2132.5</v>
+        <v>2096.2</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2115.2</v>
+        <v>2110.2</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2140.2</v>
+        <v>2180</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2090</v>
+        <v>2099.2</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2096.2</v>
+        <v>2172.9</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-36.3</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>-1.7</v>
+        <v>76.7</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>3.66</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>514.6</v>
+        <v>508.85</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>510.6</v>
+        <v>509.5</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>512.05</v>
+        <v>519.9</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>506</v>
+        <v>509.5</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>508.85</v>
+        <v>516.35</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>-1.12</v>
+        <v>7.5</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>1.47</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2007.9</v>
+        <v>1981.7</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>2004</v>
+        <v>1990.2</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2007.9</v>
+        <v>2036.2</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1955.7</v>
+        <v>1990.2</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1981.7</v>
+        <v>2000.5</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-26.2</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>-1.3</v>
+        <v>18.8</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>276.01</v>
+        <v>272.36</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>272.4</v>
+        <v>273</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>275.09</v>
+        <v>280</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>266</v>
+        <v>270.3</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>272.36</v>
+        <v>277.95</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="J51" s="13" t="n">
-        <v>-1.32</v>
+        <v>5.59</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>277.37</v>
+        <v>270.09</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>277.04</v>
+        <v>271</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>277.37</v>
+        <v>275.8</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>268.6</v>
+        <v>269.05</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>270.09</v>
+        <v>271.85</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-7.28</v>
-      </c>
-      <c r="J52" s="13" t="n">
-        <v>-2.62</v>
+        <v>1.76</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5288</v>
+        <v>5266.4</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5279.7</v>
+        <v>5300</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5308.8</v>
+        <v>5349</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5120</v>
+        <v>5238.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5266.4</v>
+        <v>5289</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-21.6</v>
-      </c>
-      <c r="J53" s="13" t="n">
-        <v>-0.41</v>
+        <v>22.6</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>456</v>
+        <v>441.5</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>456</v>
+        <v>450.9</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>440.35</v>
+        <v>443</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>441.5</v>
+        <v>445.65</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-14.5</v>
-      </c>
-      <c r="J54" s="13" t="n">
-        <v>-3.18</v>
+        <v>4.15</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1949.7</v>
+        <v>1906.3</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1959</v>
+        <v>1928.7</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1966</v>
+        <v>2007.6</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1897.2</v>
+        <v>1920.6</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1906.3</v>
+        <v>1983.3</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-43.4</v>
-      </c>
-      <c r="J55" s="13" t="n">
-        <v>-2.23</v>
+        <v>77</v>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>4.04</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1724.1</v>
+        <v>1736.9</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1711.8</v>
+        <v>1749.9</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1758</v>
+        <v>1768.1</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1709.5</v>
+        <v>1725.6</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1736.9</v>
+        <v>1752.3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>12.8</v>
+        <v>15.4</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>72.43000000000001</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>72.73999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>72.79000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>69.5</v>
+        <v>70.41</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>71.18000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-1.25</v>
+        <v>-0.21</v>
       </c>
       <c r="J57" s="13" t="n">
-        <v>-1.73</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6534</v>
+        <v>6502.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6530</v>
+        <v>6508</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6547</v>
+        <v>6644</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6429</v>
+        <v>6483.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6502.5</v>
+        <v>6619.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-31.5</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>-0.48</v>
+        <v>117</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11325</v>
+        <v>11166.5</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>11300</v>
+        <v>11299</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11300</v>
+        <v>11492</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>11006</v>
+        <v>11159</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>11166.5</v>
+        <v>11408</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-158.5</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>-1.4</v>
+        <v>241.5</v>
+      </c>
+      <c r="J59" s="10" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>594.45</v>
+        <v>587</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>590</v>
+        <v>592.8</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>591.9</v>
+        <v>608.7</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>579.8</v>
+        <v>592.05</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>587</v>
+        <v>607.2</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-7.45</v>
-      </c>
-      <c r="J60" s="13" t="n">
-        <v>-1.25</v>
+        <v>20.2</v>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>3.44</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1329.8</v>
+        <v>1322.9</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1327</v>
+        <v>1320</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1340.3</v>
+        <v>1320</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1313.6</v>
+        <v>1280.6</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1322.9</v>
+        <v>1287.2</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-6.9</v>
+        <v>-35.7</v>
       </c>
       <c r="J61" s="13" t="n">
-        <v>-0.52</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7189.5</v>
+        <v>7109</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7120</v>
+        <v>7109</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7146</v>
+        <v>7348.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>6978</v>
+        <v>7070</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7109</v>
+        <v>7329</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-80.5</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>-1.12</v>
+        <v>220</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>3.09</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3302.1</v>
+        <v>3241.6</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3290</v>
+        <v>3305</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3314.4</v>
+        <v>3325.6</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3215.2</v>
+        <v>3176.5</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3241.6</v>
+        <v>3205.1</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-60.5</v>
+        <v>-36.5</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>-1.83</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>363.45</v>
+        <v>360.55</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>363.2</v>
+        <v>379.9</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>356</v>
+        <v>353.45</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>360.55</v>
+        <v>359.05</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-2.9</v>
+        <v>-1.5</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>-0.8</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="65">
@@ -2941,19 +2941,19 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>284.75</v>
+        <v>286.95</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>284.7</v>
+        <v>290</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>287.95</v>
+        <v>291.65</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>280</v>
+        <v>287.4</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>286.95</v>
+        <v>289.15</v>
       </c>
       <c r="I65" s="9" t="n">
         <v>2.2</v>
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>165.66</v>
+        <v>163.23</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>164.68</v>
+        <v>165.3</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>164.68</v>
+        <v>167.49</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>161.31</v>
+        <v>164.14</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>163.23</v>
+        <v>164.48</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>-1.47</v>
+        <v>1.25</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2413.9</v>
+        <v>2406.3</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2400.1</v>
+        <v>2434.3</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2455.9</v>
+        <v>2438.8</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2385.6</v>
+        <v>2382.6</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2406.3</v>
+        <v>2393.7</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-7.6</v>
+        <v>-12.6</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>-0.31</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>474.9</v>
+        <v>469.3</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>474.7</v>
+        <v>472</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>476.25</v>
+        <v>479</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>466</v>
+        <v>469.7</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>469.3</v>
+        <v>476.2</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="J69" s="13" t="n">
-        <v>-1.18</v>
+        <v>6.9</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>1.47</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1090.05</v>
+        <v>1067.1</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1085.1</v>
+        <v>1070.2</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1089.9</v>
+        <v>1090.2</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1043.05</v>
+        <v>1068.2</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1067.1</v>
+        <v>1072.5</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-22.95</v>
-      </c>
-      <c r="J70" s="13" t="n">
-        <v>-2.11</v>
+        <v>5.4</v>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1862.3</v>
+        <v>1835.2</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1863.2</v>
+        <v>1854.9</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1863.2</v>
+        <v>1951.9</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1815.5</v>
+        <v>1850.2</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1835.2</v>
+        <v>1899.8</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-27.1</v>
-      </c>
-      <c r="J71" s="13" t="n">
-        <v>-1.46</v>
+        <v>64.59999999999999</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>3.52</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>704.55</v>
+        <v>699.7</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>705</v>
+        <v>699.7</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>722.5</v>
+        <v>716</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>690</v>
+        <v>690.05</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>699.7</v>
+        <v>703.4</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-4.85</v>
-      </c>
-      <c r="J72" s="13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.7</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2803.2</v>
+        <v>2794.5</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2783</v>
+        <v>2805</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2801.4</v>
+        <v>2865.8</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2727</v>
+        <v>2805</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2794.5</v>
+        <v>2856</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="J73" s="13" t="n">
-        <v>-0.31</v>
+        <v>61.5</v>
+      </c>
+      <c r="J73" s="10" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>391</v>
+        <v>380.05</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>389.65</v>
+        <v>384</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>389.65</v>
+        <v>391.5</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>375.5</v>
+        <v>382.95</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>380.05</v>
+        <v>390.25</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>-10.95</v>
-      </c>
-      <c r="J74" s="13" t="n">
-        <v>-2.8</v>
+        <v>10.2</v>
+      </c>
+      <c r="J74" s="10" t="n">
+        <v>2.68</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4351.6</v>
+        <v>4338.8</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4349</v>
+        <v>4356</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4379</v>
+        <v>4590</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4289.3</v>
+        <v>4318</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4338.8</v>
+        <v>4559.5</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="J75" s="13" t="n">
-        <v>-0.29</v>
+        <v>220.7</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>5.09</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1252.5</v>
+        <v>1240.6</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1252</v>
+        <v>1241.1</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1252</v>
+        <v>1264</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1233</v>
+        <v>1238.1</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1240.6</v>
+        <v>1256.6</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="J76" s="13" t="n">
-        <v>-0.95</v>
+        <v>16</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>1.29</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1200.2</v>
+        <v>1199.1</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1213.7</v>
+        <v>1213.5</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1184</v>
+        <v>1191.4</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1199.1</v>
+        <v>1200.5</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>-0.09</v>
+        <v>1.4</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2787.9</v>
+        <v>2712.6</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2770.1</v>
+        <v>2725</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2774.9</v>
+        <v>2774.3</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2703.7</v>
+        <v>2725</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2712.6</v>
+        <v>2753.6</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-75.3</v>
-      </c>
-      <c r="J78" s="13" t="n">
-        <v>-2.7</v>
+        <v>41</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>779</v>
+        <v>771.7</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>770</v>
+        <v>772.6</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>778.8</v>
+        <v>786.6</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>762.25</v>
+        <v>772.6</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>771.7</v>
+        <v>779.4</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="J79" s="13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>7.7</v>
+      </c>
+      <c r="J79" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>594.4</v>
+        <v>586.9</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>594.35</v>
+        <v>591.95</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>594.35</v>
+        <v>596.2</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>578.4</v>
+        <v>583</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>586.9</v>
+        <v>588.35</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>-1.26</v>
+        <v>1.45</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5114.5</v>
+        <v>5099</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5080</v>
+        <v>5186</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5114.5</v>
+        <v>5237</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5020</v>
+        <v>5006</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5099</v>
+        <v>5066.5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-15.5</v>
+        <v>-32.5</v>
       </c>
       <c r="J81" s="13" t="n">
-        <v>-0.3</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1067.2</v>
+        <v>1038</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1058.5</v>
+        <v>1043.3</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1063.85</v>
+        <v>1049.4</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1030.4</v>
+        <v>1034.5</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1038</v>
+        <v>1042.7</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-29.2</v>
-      </c>
-      <c r="J82" s="13" t="n">
-        <v>-2.74</v>
+        <v>4.7</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>555.25</v>
+        <v>534.85</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>553.35</v>
+        <v>540</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>555.25</v>
+        <v>544.5</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>532.05</v>
+        <v>528.25</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>534.85</v>
+        <v>537.4</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-20.4</v>
-      </c>
-      <c r="J83" s="13" t="n">
-        <v>-3.67</v>
+        <v>2.55</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>380.6</v>
+        <v>374.55</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>376.8</v>
+        <v>380</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>369.3</v>
+        <v>372.5</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>374.55</v>
+        <v>373.85</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-6.05</v>
+        <v>-0.7</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>-1.59</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2314.4</v>
+        <v>2250.9</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2312</v>
+        <v>2268.8</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2368.8</v>
+        <v>2365.8</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2211.6</v>
+        <v>2268.8</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2250.9</v>
+        <v>2309.3</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-63.5</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>-2.74</v>
+        <v>58.4</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>2.59</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>31575</v>
+        <v>31030</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>31550</v>
+        <v>31400</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>31550</v>
+        <v>31400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>30855</v>
+        <v>30945</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>31030</v>
+        <v>31190</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-545</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>-1.73</v>
+        <v>160</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>70.15000000000001</v>
+        <v>69.64</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>69.7</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>70</v>
+        <v>70.72</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>68.93000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>69.64</v>
+        <v>69.59</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.51</v>
+        <v>-0.05</v>
       </c>
       <c r="J87" s="13" t="n">
-        <v>-0.73</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>126.05</v>
+        <v>125.19</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>125.7</v>
+        <v>125.5</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>125.92</v>
+        <v>127.38</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>123.8</v>
+        <v>125.34</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>125.19</v>
+        <v>126.97</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="J88" s="13" t="n">
-        <v>-0.68</v>
+        <v>1.78</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>167.55</v>
+        <v>166.02</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>167.9</v>
+        <v>168.02</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>167.9</v>
+        <v>168.76</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>165.1</v>
+        <v>166.01</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>166.02</v>
+        <v>166.91</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="J89" s="13" t="n">
-        <v>-0.91</v>
+        <v>0.89</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>644.65</v>
+        <v>635.85</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>644.5</v>
+        <v>647.75</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>626.7</v>
+        <v>635</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>635.85</v>
+        <v>643.7</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="J90" s="13" t="n">
-        <v>-1.37</v>
+        <v>7.85</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2130.8</v>
+        <v>2103.6</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2130.8</v>
+        <v>2036.6</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2139</v>
+        <v>2111.2</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2080</v>
+        <v>2013.9</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2103.6</v>
+        <v>2094.5</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-27.2</v>
+        <v>-9.1</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>-1.28</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4345.2</v>
+        <v>4295.3</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4250</v>
+        <v>4349</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4313</v>
+        <v>4387.3</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4172.8</v>
+        <v>4235.3</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4295.3</v>
+        <v>4262.4</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-49.9</v>
+        <v>-32.9</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>-1.15</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>913.75</v>
+        <v>916.05</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>906</v>
+        <v>925.25</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>920</v>
+        <v>942.4</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>895.25</v>
+        <v>911.1</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>916.05</v>
+        <v>913.9</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J93" s="10" t="n">
-        <v>0.25</v>
+        <v>-2.15</v>
+      </c>
+      <c r="J93" s="13" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>413.9</v>
+        <v>409.95</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>413</v>
+        <v>414.55</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>413.9</v>
+        <v>415</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>407</v>
+        <v>390.8</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>409.95</v>
+        <v>400.25</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-3.95</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>-0.95</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1167.5</v>
+        <v>1181.8</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1167.5</v>
+        <v>1195</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1189.8</v>
+        <v>1195</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1159.6</v>
+        <v>1165.2</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1181.8</v>
+        <v>1168.4</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="J95" s="10" t="n">
-        <v>1.22</v>
+        <v>-13.4</v>
+      </c>
+      <c r="J95" s="13" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>144.19</v>
+        <v>142.25</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>142.5</v>
+        <v>143.5</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>143.4</v>
+        <v>144.42</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>141.12</v>
+        <v>142</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>142.25</v>
+        <v>142.26</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="J96" s="13" t="n">
-        <v>-1.35</v>
+        <v>0.01</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1542.1</v>
+        <v>1530.9</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1542.1</v>
+        <v>1538</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1590</v>
+        <v>1574.1</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1524.3</v>
+        <v>1525</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1530.9</v>
+        <v>1530</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-11.2</v>
+        <v>-0.9</v>
       </c>
       <c r="J97" s="13" t="n">
-        <v>-0.73</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>550.1</v>
+        <v>539.55</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>548</v>
+        <v>544.5</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>550</v>
+        <v>556.55</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>536.15</v>
+        <v>542.05</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>539.55</v>
+        <v>555.25</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-10.55</v>
-      </c>
-      <c r="J98" s="13" t="n">
-        <v>-1.92</v>
+        <v>15.7</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>2.91</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>316.25</v>
+        <v>314.9</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>316.25</v>
+        <v>317.9</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>317.5</v>
+        <v>317.9</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>313.3</v>
+        <v>310.5</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>314.9</v>
+        <v>311.1</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-1.35</v>
+        <v>-3.8</v>
       </c>
       <c r="J99" s="13" t="n">
-        <v>-0.43</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1228.1</v>
+        <v>1223.1</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1224</v>
+        <v>1245</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1234.4</v>
+        <v>1278.9</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1201.1</v>
+        <v>1234.1</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1223.1</v>
+        <v>1261.4</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J100" s="13" t="n">
-        <v>-0.41</v>
+        <v>38.3</v>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v>3.13</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5458.5</v>
+        <v>5287</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5436</v>
+        <v>5373.5</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5436</v>
+        <v>5514</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5216</v>
+        <v>5289</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5287</v>
+        <v>5352.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-171.5</v>
-      </c>
-      <c r="J101" s="13" t="n">
-        <v>-3.14</v>
+        <v>65.5</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>1.24</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>782.4</v>
+        <v>767.4</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>782.4</v>
+        <v>774</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>784.3</v>
+        <v>789.35</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>763.7</v>
+        <v>772</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>767.4</v>
+        <v>778.4</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-15</v>
-      </c>
-      <c r="J102" s="13" t="n">
-        <v>-1.92</v>
+        <v>11</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>560.4</v>
+        <v>561.15</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>556</v>
+        <v>565.05</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>564.85</v>
+        <v>566</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>549.3</v>
+        <v>553</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>561.15</v>
+        <v>562.3</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>0.75</v>
+        <v>1.15</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1279.7</v>
+        <v>1264.5</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1272.5</v>
+        <v>1278</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1273.4</v>
+        <v>1287.9</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1250.4</v>
+        <v>1259.9</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1264.5</v>
+        <v>1266.6</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="J104" s="13" t="n">
-        <v>-1.19</v>
+        <v>2.1</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>485.4</v>
+        <v>478.6</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>483.75</v>
+        <v>481.4</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>483.75</v>
+        <v>483.9</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>469.6</v>
+        <v>472.9</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>478.6</v>
+        <v>476.4</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-6.8</v>
+        <v>-2.2</v>
       </c>
       <c r="J105" s="13" t="n">
-        <v>-1.4</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1228.15</v>
+        <v>1187.65</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1232</v>
+        <v>1187</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1244</v>
+        <v>1187</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1162.4</v>
+        <v>1096</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1187.65</v>
+        <v>1104.5</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-40.5</v>
+        <v>-83.15000000000001</v>
       </c>
       <c r="J106" s="13" t="n">
-        <v>-3.3</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>382</v>
+        <v>383.3</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>376.6</v>
+        <v>378.9</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>386.85</v>
+        <v>382.05</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>375.3</v>
+        <v>363</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>383.3</v>
+        <v>371.65</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J107" s="10" t="n">
-        <v>0.34</v>
+        <v>-11.65</v>
+      </c>
+      <c r="J107" s="13" t="n">
+        <v>-3.04</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>740.05</v>
+        <v>759.05</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>738.05</v>
+        <v>767</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>767.2</v>
+        <v>777.15</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>727.65</v>
+        <v>756.55</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>759.05</v>
+        <v>768.55</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>19</v>
+        <v>9.5</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>2.57</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1397.8</v>
+        <v>1367.2</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1386.1</v>
+        <v>1390.4</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1400</v>
+        <v>1640.6</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1363</v>
+        <v>1390</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1367.2</v>
+        <v>1573.4</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-30.6</v>
-      </c>
-      <c r="J109" s="13" t="n">
-        <v>-2.19</v>
+        <v>206.2</v>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>15.08</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1106.1</v>
+        <v>1100.95</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1086.3</v>
+        <v>1102.2</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1112.95</v>
+        <v>1171</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1080</v>
+        <v>1102</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1100.95</v>
+        <v>1166.4</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-5.15</v>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v>-0.47</v>
+        <v>65.45</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>5.94</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>562.15</v>
+        <v>554.7</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>562.15</v>
+        <v>555.2</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>562.15</v>
+        <v>561.8</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>549.6</v>
+        <v>551.25</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>554.7</v>
+        <v>557</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-7.45</v>
-      </c>
-      <c r="J111" s="13" t="n">
-        <v>-1.33</v>
+        <v>2.3</v>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4096.1</v>
+        <v>4014</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>4083</v>
+        <v>4026</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4100</v>
+        <v>4139.5</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3990</v>
+        <v>4026</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4014</v>
+        <v>4100.8</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-82.09999999999999</v>
-      </c>
-      <c r="J112" s="13" t="n">
-        <v>-2</v>
+        <v>86.8</v>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>285.42</v>
+        <v>279.73</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>284.42</v>
+        <v>280</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>284.42</v>
+        <v>287.8</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>277.38</v>
+        <v>280</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>279.73</v>
+        <v>285.65</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-5.69</v>
-      </c>
-      <c r="J113" s="13" t="n">
-        <v>-1.99</v>
+        <v>5.92</v>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v>2.12</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3559.6</v>
+        <v>3626.3</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3541.8</v>
+        <v>3626.3</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3644.1</v>
+        <v>3723.4</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3477.6</v>
+        <v>3592.1</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3626.3</v>
+        <v>3706.7</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>66.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2311.4</v>
+        <v>2305.2</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2297</v>
+        <v>2320</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2317.4</v>
+        <v>2361.9</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2277.7</v>
+        <v>2304.1</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2305.2</v>
+        <v>2348.8</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="J116" s="13" t="n">
-        <v>-0.27</v>
+        <v>43.6</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>1.89</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3152.3</v>
+        <v>3097.5</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3105.4</v>
+        <v>3131.5</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3117.3</v>
+        <v>3172</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3047</v>
+        <v>3081.5</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3097.5</v>
+        <v>3106.5</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-54.8</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>-1.74</v>
+        <v>9</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>295.35</v>
+        <v>294.35</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>297</v>
+        <v>308.6</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>290.2</v>
+        <v>298</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>294.35</v>
+        <v>305.15</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J118" s="13" t="n">
-        <v>-0.34</v>
+        <v>10.8</v>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v>3.67</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>779.3</v>
+        <v>775</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>778.1</v>
+        <v>781</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>779.5</v>
+        <v>786.75</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>765.65</v>
+        <v>774.9</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>775</v>
+        <v>784.55</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="J119" s="13" t="n">
-        <v>-0.55</v>
+        <v>9.550000000000001</v>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13257</v>
+        <v>13314</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13134</v>
+        <v>13559</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13360</v>
+        <v>13976</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12970</v>
+        <v>13435</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13314</v>
+        <v>13580</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>57</v>
+        <v>266</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>0.43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2968.3</v>
+        <v>2971.5</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>2975</v>
+        <v>3000</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>2985.1</v>
+        <v>3041</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2925.7</v>
+        <v>2870.4</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>2971.5</v>
+        <v>2912.9</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J122" s="10" t="n">
-        <v>0.11</v>
+        <v>-58.6</v>
+      </c>
+      <c r="J122" s="13" t="n">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>478.8</v>
+        <v>476.5</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>476</v>
+        <v>472.2</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>481.95</v>
+        <v>494.85</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>470.95</v>
+        <v>472.2</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>476.5</v>
+        <v>492.4</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="J123" s="13" t="n">
-        <v>-0.48</v>
+        <v>15.9</v>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>3.34</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1610.4</v>
+        <v>1585.7</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1598</v>
+        <v>1593.2</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1608.9</v>
+        <v>1615</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1572.1</v>
+        <v>1585</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1585.7</v>
+        <v>1606.7</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-24.7</v>
-      </c>
-      <c r="J124" s="13" t="n">
-        <v>-1.53</v>
+        <v>21</v>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1146</v>
+        <v>1135.65</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1135.95</v>
+        <v>1146.4</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1143.8</v>
+        <v>1151</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1116.95</v>
+        <v>1129.8</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1135.65</v>
+        <v>1135.4</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-10.35</v>
+        <v>-0.25</v>
       </c>
       <c r="J125" s="13" t="n">
-        <v>-0.9</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>123.24</v>
+        <v>121.21</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>123.24</v>
+        <v>121.99</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>123.25</v>
+        <v>123.43</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>119.12</v>
+        <v>119.59</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>121.21</v>
+        <v>120.21</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-2.03</v>
+        <v>-1</v>
       </c>
       <c r="J126" s="13" t="n">
-        <v>-1.65</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2250.7</v>
+        <v>2276.7</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2314.5</v>
+        <v>2286.9</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2349.2</v>
+        <v>2306.6</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2240.8</v>
+        <v>2247.6</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2276.7</v>
+        <v>2276.6</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>26</v>
+        <v>-0.1</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>1.16</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>130425</v>
+        <v>129710</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>130355</v>
+        <v>131000</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>131100</v>
+        <v>131895</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>128750</v>
+        <v>128690</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>129710</v>
+        <v>129235</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-715</v>
+        <v>-475</v>
       </c>
       <c r="J128" s="13" t="n">
-        <v>-0.55</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3461.1</v>
+        <v>3424.2</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3450</v>
+        <v>3424.2</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3459.2</v>
+        <v>3515</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3385.1</v>
+        <v>3410.8</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3424.2</v>
+        <v>3487.7</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-36.9</v>
-      </c>
-      <c r="J129" s="13" t="n">
-        <v>-1.07</v>
+        <v>63.5</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>433.3</v>
+        <v>399.3</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>431</v>
+        <v>399</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>432.45</v>
+        <v>412</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>394.25</v>
+        <v>388.6</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>399.3</v>
+        <v>407.8</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-34</v>
-      </c>
-      <c r="J130" s="13" t="n">
-        <v>-7.85</v>
+        <v>8.5</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>2.13</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>991.65</v>
+        <v>972.85</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>991.65</v>
+        <v>976.15</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>995</v>
+        <v>991.25</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>968.25</v>
+        <v>967.65</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>972.85</v>
+        <v>976.65</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-18.8</v>
-      </c>
-      <c r="J131" s="13" t="n">
-        <v>-1.9</v>
+        <v>3.8</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6758.5</v>
+        <v>6821</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>7050</v>
+        <v>6855</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>7200</v>
+        <v>6978</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6660.5</v>
+        <v>6755.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>6821</v>
+        <v>6796.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="J132" s="10" t="n">
-        <v>0.92</v>
+        <v>-24.5</v>
+      </c>
+      <c r="J132" s="13" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1465.6</v>
+        <v>1458.6</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1466</v>
+        <v>1472.9</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1436.1</v>
+        <v>1446.3</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1458.6</v>
+        <v>1457.1</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-7</v>
+        <v>-1.5</v>
       </c>
       <c r="J133" s="13" t="n">
-        <v>-0.48</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>91.73</v>
+        <v>90.37</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>92.04000000000001</v>
+        <v>91</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>92.06999999999999</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>89.75</v>
+        <v>88.3</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>90.37</v>
+        <v>89.09</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-1.36</v>
+        <v>-1.28</v>
       </c>
       <c r="J134" s="13" t="n">
-        <v>-1.48</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>401.3</v>
+        <v>399.15</v>
       </c>
       <c r="E135" s="9" t="n">
         <v>400</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>400.3</v>
+        <v>404.8</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>393.15</v>
+        <v>397.25</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>399.15</v>
+        <v>400.05</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J135" s="13" t="n">
-        <v>-0.54</v>
+        <v>0.9</v>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1700.3</v>
+        <v>1669.6</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1700.1</v>
+        <v>1669</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1700.1</v>
+        <v>1708.9</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1658.1</v>
+        <v>1665.4</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1669.6</v>
+        <v>1693.7</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-30.7</v>
-      </c>
-      <c r="J136" s="13" t="n">
-        <v>-1.81</v>
+        <v>24.1</v>
+      </c>
+      <c r="J136" s="10" t="n">
+        <v>1.44</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9688</v>
+        <v>9726.5</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9715</v>
+        <v>9885.5</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9825</v>
+        <v>9898</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9611</v>
+        <v>9645</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9726.5</v>
+        <v>9730</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>38.5</v>
+        <v>3.5</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>301.4</v>
+        <v>299.55</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>304.9</v>
+        <v>298.4</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>307.45</v>
+        <v>299.9</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>296.9</v>
+        <v>292.35</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>299.55</v>
+        <v>292.9</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-1.85</v>
+        <v>-6.65</v>
       </c>
       <c r="J138" s="13" t="n">
-        <v>-0.61</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>36845</v>
+        <v>36785</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>36975</v>
+        <v>36915</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37190</v>
+        <v>37270</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>36230</v>
+        <v>36735</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>36785</v>
+        <v>36955</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-60</v>
-      </c>
-      <c r="J139" s="13" t="n">
-        <v>-0.16</v>
+        <v>170</v>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4805.8</v>
+        <v>4800</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>4805.8</v>
+        <v>4815.2</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>4829.9</v>
+        <v>4844.8</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4761.5</v>
+        <v>4745.7</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4800</v>
+        <v>4788.1</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-5.8</v>
+        <v>-11.9</v>
       </c>
       <c r="J141" s="13" t="n">
-        <v>-0.12</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>280.12</v>
+        <v>276.76</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>278.45</v>
+        <v>280.45</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>274.01</v>
+        <v>275.8</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>276.76</v>
+        <v>276.7</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-3.36</v>
+        <v>-0.06</v>
       </c>
       <c r="J142" s="13" t="n">
-        <v>-1.2</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>464.75</v>
+        <v>448.4</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>464</v>
+        <v>452.35</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>464.7</v>
+        <v>456.15</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>447</v>
+        <v>446.05</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>448.4</v>
+        <v>448.25</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-16.35</v>
+        <v>-0.15</v>
       </c>
       <c r="J143" s="13" t="n">
-        <v>-3.52</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
+        <v>1375.7</v>
+      </c>
+      <c r="E144" s="12" t="n">
+        <v>1378.2</v>
+      </c>
+      <c r="F144" s="12" t="n">
         <v>1389</v>
       </c>
-      <c r="E144" s="12" t="n">
-        <v>1378.7</v>
-      </c>
-      <c r="F144" s="12" t="n">
-        <v>1384.8</v>
-      </c>
       <c r="G144" s="12" t="n">
-        <v>1355</v>
+        <v>1361.1</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1375.7</v>
+        <v>1364.6</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-13.3</v>
+        <v>-11.1</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>-0.96</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3091.1</v>
+        <v>3054.8</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3090</v>
+        <v>3065.3</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3090</v>
+        <v>3124.8</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3015.6</v>
+        <v>3030.4</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3054.8</v>
+        <v>3047.5</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-36.3</v>
+        <v>-7.3</v>
       </c>
       <c r="J145" s="13" t="n">
-        <v>-1.17</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>111.18</v>
+        <v>109.36</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>110.8</v>
+        <v>109.5</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>110.8</v>
+        <v>111.68</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>108.11</v>
+        <v>108.13</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>109.36</v>
+        <v>108.68</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-1.82</v>
+        <v>-0.68</v>
       </c>
       <c r="J146" s="13" t="n">
-        <v>-1.64</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8148.5</v>
+        <v>8110.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8132.5</v>
+        <v>8110.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8163.5</v>
+        <v>8363</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>7970.5</v>
+        <v>8062.5</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8110.5</v>
+        <v>8344.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-38</v>
-      </c>
-      <c r="J147" s="13" t="n">
-        <v>-0.47</v>
+        <v>234</v>
+      </c>
+      <c r="J147" s="10" t="n">
+        <v>2.89</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>320.35</v>
+        <v>318.35</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>319.6</v>
+        <v>314</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>321.25</v>
+        <v>323.9</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>315.95</v>
+        <v>314</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>318.35</v>
+        <v>319.05</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>-0.62</v>
+        <v>0.7</v>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1092.55</v>
+        <v>1068.9</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1085.5</v>
+        <v>1069</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1089.55</v>
+        <v>1082.7</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1056.2</v>
+        <v>1054</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1068.9</v>
+        <v>1059.1</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-23.65</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="J149" s="13" t="n">
-        <v>-2.16</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>341.2</v>
+        <v>336.55</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>340.4</v>
+        <v>339</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>341.6</v>
+        <v>344.55</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>333.8</v>
+        <v>327.65</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>336.55</v>
+        <v>330.2</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-4.65</v>
+        <v>-6.35</v>
       </c>
       <c r="J150" s="13" t="n">
-        <v>-1.36</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>363.55</v>
+        <v>354.3</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>361.1</v>
+        <v>356</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>361.1</v>
+        <v>361.15</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>352.75</v>
+        <v>351.4</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>354.3</v>
+        <v>353.5</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-9.25</v>
+        <v>-0.8</v>
       </c>
       <c r="J151" s="13" t="n">
-        <v>-2.54</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1425.4</v>
+        <v>1430.8</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1409</v>
+        <v>1433.4</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1437</v>
+        <v>1467.4</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1393.1</v>
+        <v>1433.4</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1430.8</v>
+        <v>1463.1</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>5.4</v>
+        <v>32.3</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>0.38</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>186.16</v>
+        <v>184.62</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>184.98</v>
+        <v>185.25</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>185.4</v>
+        <v>187.82</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>179.7</v>
+        <v>184.28</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>184.62</v>
+        <v>186.15</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="J153" s="13" t="n">
-        <v>-0.83</v>
+        <v>1.53</v>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>651.2</v>
+        <v>643.9</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>650</v>
+        <v>646.95</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>650</v>
+        <v>649.8</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>632.15</v>
+        <v>638.05</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>643.9</v>
+        <v>644.8</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>-1.12</v>
+        <v>0.9</v>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1816.2</v>
+        <v>1819</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1814.9</v>
+        <v>1810.1</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1826</v>
+        <v>1845</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1785.2</v>
+        <v>1810.1</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1819</v>
+        <v>1820.1</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1086.9</v>
+        <v>1068.45</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1075</v>
+        <v>1063.6</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1077.7</v>
+        <v>1089.1</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1063</v>
+        <v>1063.6</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1068.45</v>
+        <v>1068.4</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-18.45</v>
-      </c>
-      <c r="J156" s="13" t="n">
-        <v>-1.7</v>
+        <v>-0.05</v>
+      </c>
+      <c r="J156" s="10" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>24555</v>
+        <v>24195</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>24450</v>
+        <v>24295</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>24450</v>
+        <v>24900</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>23800</v>
+        <v>24295</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>24195</v>
+        <v>24740</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-360</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>-1.47</v>
+        <v>545</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>956.85</v>
+        <v>937.35</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>945.2</v>
+        <v>942</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>950</v>
+        <v>969</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>921</v>
+        <v>942</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>937.35</v>
+        <v>960.45</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-19.5</v>
-      </c>
-      <c r="J158" s="13" t="n">
-        <v>-2.04</v>
+        <v>23.1</v>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>2.46</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3776.8</v>
+        <v>3808.2</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3790</v>
+        <v>3850</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3847.6</v>
+        <v>3930</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3734.5</v>
+        <v>3820</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3808.2</v>
+        <v>3834.1</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>31.4</v>
+        <v>25.9</v>
       </c>
       <c r="J159" s="10" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2543.6</v>
+        <v>2518.6</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2543.5</v>
+        <v>2520.4</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2543.5</v>
+        <v>2565</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2488.9</v>
+        <v>2520</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2518.6</v>
+        <v>2551.4</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-25</v>
-      </c>
-      <c r="J160" s="13" t="n">
-        <v>-0.98</v>
+        <v>32.8</v>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1778.7</v>
+        <v>1808.3</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1771</v>
+        <v>1820</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1815</v>
+        <v>1841</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1761.4</v>
+        <v>1810</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1808.3</v>
+        <v>1823.5</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>29.6</v>
+        <v>15.2</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>1.66</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>586.25</v>
+        <v>605.6</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>586.45</v>
+        <v>548.1</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>605.6</v>
+        <v>575.85</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>19.35</v>
-      </c>
-      <c r="J162" s="10" t="n">
-        <v>3.3</v>
+        <v>-29.75</v>
+      </c>
+      <c r="J162" s="13" t="n">
+        <v>-4.91</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>432.15</v>
+        <v>467.65</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>431.95</v>
+        <v>467.35</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>518.55</v>
+        <v>492.25</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>429.9</v>
+        <v>453.6</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>467.65</v>
+        <v>477.35</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>35.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>8.210000000000001</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>799.75</v>
+        <v>809</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>831</v>
+        <v>825.05</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>854.85</v>
+        <v>850</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>797.5</v>
+        <v>801</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>809</v>
+        <v>805.75</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="J164" s="10" t="n">
-        <v>1.16</v>
+        <v>-3.25</v>
+      </c>
+      <c r="J164" s="13" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1602.2</v>
+        <v>1580.5</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1582</v>
+        <v>1586.7</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1590.1</v>
+        <v>1597.4</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1568.3</v>
+        <v>1550</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1580.5</v>
+        <v>1569.6</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-21.7</v>
+        <v>-10.9</v>
       </c>
       <c r="J165" s="13" t="n">
-        <v>-1.35</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1168</v>
+        <v>1144.6</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1170</v>
+        <v>1149.7</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1170</v>
+        <v>1174.4</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1139.4</v>
+        <v>1149.7</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1144.6</v>
+        <v>1160.4</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-23.4</v>
-      </c>
-      <c r="J166" s="13" t="n">
-        <v>-2</v>
+        <v>15.8</v>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>1.38</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>451.5</v>
+        <v>444.55</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>450</v>
+        <v>445.5</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>439.3</v>
+        <v>438.5</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>444.55</v>
+        <v>441.4</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-6.95</v>
+        <v>-3.15</v>
       </c>
       <c r="J168" s="13" t="n">
-        <v>-1.54</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>215.88</v>
+        <v>211.36</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>215.78</v>
+        <v>212.55</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>215.78</v>
+        <v>214.5</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>210</v>
+        <v>211.4</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>211.36</v>
+        <v>212.24</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-4.52</v>
-      </c>
-      <c r="J169" s="13" t="n">
-        <v>-2.09</v>
+        <v>0.88</v>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2474.7</v>
+        <v>2473.9</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2479</v>
+        <v>2494</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2491</v>
+        <v>2498.3</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2438</v>
+        <v>2425</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2473.9</v>
+        <v>2431.3</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-0.8</v>
+        <v>-42.6</v>
       </c>
       <c r="J170" s="13" t="n">
-        <v>-0.03</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1459.8</v>
+        <v>1473.5</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1459.7</v>
+        <v>1484</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1482</v>
+        <v>1492.4</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1445.6</v>
+        <v>1455.2</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1473.5</v>
+        <v>1471.6</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="J171" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.9</v>
+      </c>
+      <c r="J171" s="13" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2965.1</v>
+        <v>2947.9</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2965</v>
+        <v>2972.6</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2980</v>
+        <v>2978.6</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2892</v>
+        <v>2882.3</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2947.9</v>
+        <v>2906</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-17.2</v>
+        <v>-41.9</v>
       </c>
       <c r="J172" s="13" t="n">
-        <v>-0.58</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4439.8</v>
+        <v>4385.2</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4438</v>
+        <v>4407.1</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4438</v>
+        <v>4447.4</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4358</v>
+        <v>4352.7</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4385.2</v>
+        <v>4363</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-54.6</v>
+        <v>-22.2</v>
       </c>
       <c r="J173" s="13" t="n">
-        <v>-1.23</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4231.5</v>
+        <v>4185.1</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4231.7</v>
+        <v>4223.2</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4234.7</v>
+        <v>4280</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4146.1</v>
+        <v>4213</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4185.1</v>
+        <v>4251.8</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-46.4</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>-1.1</v>
+        <v>66.7</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1701.7</v>
+        <v>1736</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1678.5</v>
+        <v>1748.3</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1769.9</v>
+        <v>1780</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1666.1</v>
+        <v>1705.1</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1736</v>
+        <v>1724</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="J175" s="10" t="n">
-        <v>2.02</v>
+        <v>-12</v>
+      </c>
+      <c r="J175" s="13" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4228.3</v>
+        <v>4144.6</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4215.1</v>
+        <v>4135</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4218.4</v>
+        <v>4193.9</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4124</v>
+        <v>4067.2</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4144.6</v>
+        <v>4158.5</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-83.7</v>
-      </c>
-      <c r="J176" s="13" t="n">
-        <v>-1.98</v>
+        <v>13.9</v>
+      </c>
+      <c r="J176" s="10" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3553.9</v>
+        <v>3492.9</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3462</v>
+        <v>3400</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3519</v>
+        <v>3536.8</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3415.1</v>
+        <v>3367.8</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3492.9</v>
+        <v>3495.5</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-61</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>-1.72</v>
+        <v>2.6</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1469.6</v>
+        <v>1458.6</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1468.8</v>
+        <v>1464.7</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1473.6</v>
+        <v>1473.2</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1445.5</v>
+        <v>1451</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1458.6</v>
+        <v>1463.1</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-11</v>
-      </c>
-      <c r="J178" s="13" t="n">
-        <v>-0.75</v>
+        <v>4.5</v>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>0.31</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11833</v>
+        <v>11586</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11777</v>
+        <v>11670</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11777</v>
+        <v>11798</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11484</v>
+        <v>11590</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11586</v>
+        <v>11758</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-247</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>-2.09</v>
+        <v>172</v>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>167.31</v>
+        <v>165.94</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>166.75</v>
+        <v>168.5</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>162.61</v>
+        <v>163.32</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>165.94</v>
+        <v>163.77</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-1.37</v>
+        <v>-2.17</v>
       </c>
       <c r="J180" s="13" t="n">
-        <v>-0.82</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>644.1</v>
+        <v>641.85</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>644.1</v>
+        <v>645.9</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>629.8</v>
+        <v>639</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>641.85</v>
+        <v>643.35</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="J181" s="13" t="n">
-        <v>-0.35</v>
+        <v>1.5</v>
+      </c>
+      <c r="J181" s="10" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>773.6</v>
+        <v>271.55</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>289.5</v>
+        <v>277</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>268.7</v>
+        <v>274.95</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>271.55</v>
+        <v>294.65</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-502.05</v>
-      </c>
-      <c r="J182" s="13" t="n">
-        <v>-64.90000000000001</v>
+        <v>23.1</v>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>8.51</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1474.8</v>
+        <v>1430.4</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1470</v>
+        <v>1445.2</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1470</v>
+        <v>1463.7</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1418.2</v>
+        <v>1413.3</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1430.4</v>
+        <v>1454.2</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-44.4</v>
-      </c>
-      <c r="J183" s="13" t="n">
-        <v>-3.01</v>
+        <v>23.8</v>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>200.68</v>
+        <v>200.65</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>200.89</v>
+        <v>202.4</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>202.15</v>
+        <v>203.37</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>200</v>
+        <v>200.06</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>200.65</v>
+        <v>200.75</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="J184" s="13" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>910.85</v>
+        <v>891.9</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>910.9</v>
+        <v>895</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>915.4</v>
+        <v>905</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>890.4</v>
+        <v>893.15</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>891.9</v>
+        <v>902.35</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-18.95</v>
-      </c>
-      <c r="J186" s="13" t="n">
-        <v>-2.08</v>
+        <v>10.45</v>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  01-May-2026 02:17 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  04-May-2026 03:10 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01-May-2026 02:17 PM</t>
+          <t>04-May-2026 03:10 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 04-May-2026 03:10 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 05-May-2026 06:28 PM</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>04-May-2026 03:10 PM</t>
+          <t>05-May-2026 06:28 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  04-May-2026 03:10 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  05-May-2026 06:28 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>507.5</v>
+        <v>513.1</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>513</v>
+        <v>513.05</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>523.1</v>
+        <v>513.1</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>509</v>
+        <v>475.55</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>513.1</v>
+        <v>488</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>5.6</v>
+        <v>-25.1</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>1.1</v>
+        <v>-4.89</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7230</v>
+        <v>7236.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7269</v>
+        <v>7248</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7363</v>
+        <v>7349</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7185</v>
+        <v>7215</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7236.5</v>
+        <v>7328</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>0.09</v>
+        <v>91.5</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25435</v>
+        <v>25415</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25480</v>
+        <v>25420</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25835</v>
+        <v>25575</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25365</v>
+        <v>25175</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25415</v>
+        <v>25305</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>-0.08</v>
+        <v>-110</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>345.5</v>
+        <v>345.85</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>347</v>
+        <v>347.2</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>360.5</v>
+        <v>363.75</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>340.7</v>
+        <v>346.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>345.85</v>
+        <v>360.85</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>0.1</v>
+        <v>15</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>4.34</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>64.2</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>64.52</v>
+        <v>65.05</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>66.34</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>62.38</v>
+        <v>63.51</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>65.93000000000001</v>
+        <v>63.99</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1.73</v>
+        <v>-1.94</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>2.69</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1422.1</v>
+        <v>1398.2</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1412.1</v>
+        <v>1396.1</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1436.5</v>
+        <v>1396.1</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1391</v>
+        <v>1375.1</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1398.2</v>
+        <v>1392.6</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-23.9</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>-1.68</v>
+        <v>-5.6</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2408.4</v>
+        <v>2485.7</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2390.4</v>
+        <v>2470</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2515</v>
+        <v>2511.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2375</v>
+        <v>2450</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2485.7</v>
+        <v>2462</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>77.3</v>
+        <v>-23.7</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>3.21</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1657.3</v>
+        <v>1742.6</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1702</v>
+        <v>1749.8</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1748.6</v>
+        <v>1757.4</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1687.3</v>
+        <v>1718.7</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1742.6</v>
+        <v>1725</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>85.3</v>
+        <v>-17.6</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>5.15</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5400</v>
+        <v>5360.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5382</v>
+        <v>5389.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5393.5</v>
+        <v>5421.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5316</v>
+        <v>5313</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5360.5</v>
+        <v>5403</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-39.5</v>
+        <v>42.5</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>-0.73</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>444.2</v>
+        <v>445.3</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>460.75</v>
+        <v>441.1</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>438.05</v>
+        <v>431.5</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>445.3</v>
+        <v>433.1</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>1.1</v>
+        <v>-12.2</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.25</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>308.71</v>
+        <v>307.7</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>308.7</v>
+        <v>307.9</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>313.5</v>
+        <v>317.5</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>303.95</v>
+        <v>303.7</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>307.7</v>
+        <v>314.4</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-1.01</v>
+        <v>6.7</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>-0.33</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1905</v>
+        <v>1873</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1910.1</v>
+        <v>1882.6</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1930.3</v>
+        <v>1882.6</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1830</v>
+        <v>1848.1</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1873</v>
+        <v>1870.6</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-32</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>-1.68</v>
+        <v>-2.4</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7636.5</v>
+        <v>7737.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7699.5</v>
+        <v>7724.5</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7790</v>
+        <v>7780.5</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7673</v>
+        <v>7678</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7737.5</v>
+        <v>7772</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>101</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>1.32</v>
+        <v>34.5</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>408.4</v>
+        <v>409.45</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>411.25</v>
+        <v>409</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>417.85</v>
+        <v>410</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>408</v>
+        <v>399.6</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>409.45</v>
+        <v>402.6</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>1.05</v>
+        <v>-6.85</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>0.26</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>162.09</v>
+        <v>160.77</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>162.29</v>
+        <v>160</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>164.05</v>
+        <v>161.66</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>159.1</v>
+        <v>158.59</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>160.77</v>
+        <v>160.25</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.52</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2444.5</v>
+        <v>2448.1</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2460</v>
+        <v>2430</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2507</v>
+        <v>2454.9</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2442.3</v>
+        <v>2415</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2448.1</v>
+        <v>2430</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>3.6</v>
+        <v>-18.1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>0.15</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1529.7</v>
+        <v>1559.6</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1534.3</v>
+        <v>1570</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1574.3</v>
+        <v>1570</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1534.3</v>
+        <v>1528.5</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1559.6</v>
+        <v>1531.6</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>29.9</v>
+        <v>-28</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>1.95</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>634.7</v>
+        <v>643.15</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>641.95</v>
+        <v>644.85</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>665.8</v>
+        <v>653.6</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>638.1</v>
+        <v>636.65</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>643.15</v>
+        <v>647.2</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>1.33</v>
+        <v>4.05</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6817.5</v>
+        <v>6949.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6890</v>
+        <v>7010</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7030</v>
+        <v>7054</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6857</v>
+        <v>6876.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6949.5</v>
+        <v>6911</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>132</v>
+        <v>-38.5</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.94</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1015.95</v>
+        <v>1015</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1023.7</v>
+        <v>1015</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1035.2</v>
+        <v>1015</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1012.1</v>
+        <v>1002.1</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1015</v>
+        <v>1007.1</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>-0.09</v>
+        <v>-7.9</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1389.5</v>
+        <v>1376</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1398</v>
+        <v>1373.9</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1398</v>
+        <v>1431</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1367.1</v>
+        <v>1367</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1376</v>
+        <v>1428.1</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-13.5</v>
+        <v>52.1</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>-0.97</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1268.3</v>
+        <v>1275.1</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1268.3</v>
+        <v>1268</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1294.4</v>
+        <v>1273.7</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1264.5</v>
+        <v>1252</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1275.1</v>
+        <v>1259.7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>6.8</v>
+        <v>-15.4</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.54</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>9994</v>
+        <v>10132</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10244</v>
+        <v>10131</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10477.5</v>
+        <v>10175</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10067</v>
+        <v>10016</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>10132</v>
+        <v>10046</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>138</v>
+        <v>-86</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>1.38</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1747.2</v>
+        <v>1770.4</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1749.2</v>
+        <v>1760</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1787</v>
+        <v>1799</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1747.1</v>
+        <v>1742.1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1770.4</v>
+        <v>1794.6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>1.33</v>
+        <v>24.2</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>1.37</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>937</v>
+        <v>950.2</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>938.1</v>
+        <v>950.2</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>966</v>
+        <v>961.1</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>938.1</v>
+        <v>933.15</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>950.2</v>
+        <v>958.6</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>1.41</v>
+        <v>8.4</v>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2160.8</v>
+        <v>2205</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2182.5</v>
+        <v>2201.1</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2215.4</v>
+        <v>2227.9</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2172.5</v>
+        <v>2164.9</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2205</v>
+        <v>2172</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>44.2</v>
+        <v>-33</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>2.05</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>521.05</v>
+        <v>524.85</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>524.5</v>
+        <v>524.75</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>533.95</v>
+        <v>535.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>517.2</v>
+        <v>520</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>524.85</v>
+        <v>531</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>0.73</v>
+        <v>6.15</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>199.72</v>
+        <v>206.76</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>202.7</v>
+        <v>206.41</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>212.66</v>
+        <v>208</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>201.3</v>
+        <v>204.1</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>206.76</v>
+        <v>206.44</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>7.04</v>
+        <v>-0.32</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>3.52</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>263.46</v>
+        <v>265.1</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>264.95</v>
+        <v>265.4</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>271.6</v>
+        <v>265.8</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>264.2</v>
+        <v>261.55</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>265.1</v>
+        <v>263.4</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>1.64</v>
+        <v>-1.7</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.62</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>431.3</v>
+        <v>433.55</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>433</v>
+        <v>433.5</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>438.6</v>
+        <v>436.5</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>428.6</v>
+        <v>429.3</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>433.55</v>
+        <v>433.35</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>2.25</v>
+        <v>-0.2</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>0.52</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>473.1</v>
+        <v>470.3</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>473.1</v>
+        <v>469.1</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>480.2</v>
+        <v>476</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>468.1</v>
+        <v>465.9</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>470.3</v>
+        <v>470.6</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>-0.59</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1886.8</v>
+        <v>1827.1</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1873.2</v>
+        <v>1828</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1895.3</v>
+        <v>1846</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1821.7</v>
+        <v>1801</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1827.1</v>
+        <v>1806.1</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-59.7</v>
-      </c>
-      <c r="J34" s="13" t="n">
-        <v>-3.16</v>
+        <v>-21</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>352.41</v>
+        <v>377.05</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>355</v>
+        <v>379.9</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>399</v>
+        <v>388.4</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>353.7</v>
+        <v>371.3</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>377.05</v>
+        <v>374.95</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>24.64</v>
+        <v>-2.1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>6.99</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>359.65</v>
+        <v>360.6</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>359.2</v>
+        <v>360.6</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>366.5</v>
+        <v>370.9</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>359.2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>360.6</v>
+        <v>368.25</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>0.26</v>
+        <v>7.65</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>2.12</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>35995</v>
+        <v>35850</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>36150</v>
+        <v>36100</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>36490</v>
+        <v>36285</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>35475</v>
+        <v>35810</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>35850</v>
+        <v>35870</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-145</v>
+        <v>20</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>-0.4</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
+        <v>301.7</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>300.25</v>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>300.45</v>
       </c>
-      <c r="E38" s="12" t="n">
-        <v>302.5</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>305.9</v>
-      </c>
       <c r="G38" s="12" t="n">
-        <v>300.1</v>
+        <v>293.3</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>301.7</v>
+        <v>298.5</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>1.25</v>
+        <v>-3.2</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>0.42</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5726</v>
+        <v>5792.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5730</v>
+        <v>5775</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5821.5</v>
+        <v>5842.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5715</v>
+        <v>5734.5</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5792.5</v>
+        <v>5834.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>1.16</v>
+        <v>42</v>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>0.73</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>369.45</v>
+        <v>366.1</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>371.7</v>
+        <v>366</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>372.65</v>
+        <v>374.4</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>365.35</v>
+        <v>363.6</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>366.1</v>
+        <v>370</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-3.35</v>
+        <v>3.9</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>-0.91</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>134.65</v>
+        <v>134.8</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>135.34</v>
+        <v>134.98</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>137.78</v>
+        <v>135.33</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>134.18</v>
+        <v>133.13</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>134.8</v>
+        <v>134.31</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0.15</v>
+        <v>-0.49</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>0.11</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>865.25</v>
+        <v>896.5</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>876</v>
+        <v>900</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>898.5</v>
+        <v>900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>874.1</v>
+        <v>871.1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>896.5</v>
+        <v>874.45</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>31.25</v>
+        <v>-22.05</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>3.61</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>438.05</v>
+        <v>441.55</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>443.8</v>
+        <v>441.55</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>449</v>
+        <v>443.4</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>439.35</v>
+        <v>437.7</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>441.55</v>
+        <v>442.55</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>0.8</v>
+        <v>1</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1562.9</v>
+        <v>1639.5</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1564.8</v>
+        <v>1644</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1649</v>
+        <v>1666.9</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1564.8</v>
+        <v>1623</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1639.5</v>
+        <v>1657.4</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>4.9</v>
+        <v>17.9</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1309.6</v>
+        <v>1335</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1320</v>
+        <v>1339</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1337.4</v>
+        <v>1339.4</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1313.6</v>
+        <v>1316.4</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1335</v>
+        <v>1333.7</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>25.4</v>
+        <v>-1.3</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1.94</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>481.45</v>
+        <v>479.95</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>481.6</v>
+        <v>479.95</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>475.6</v>
+        <v>471.2</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>479.95</v>
+        <v>472.6</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>-0.31</v>
+        <v>-7.35</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1195.9</v>
+        <v>1151.6</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1209.8</v>
+        <v>1166</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1211.2</v>
+        <v>1181.3</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1147.1</v>
+        <v>1147.5</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1151.6</v>
+        <v>1168.8</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-44.3</v>
+        <v>17.2</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>-3.7</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2096.2</v>
+        <v>2172.9</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2110.2</v>
+        <v>2184</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2180</v>
+        <v>2185</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2099.2</v>
+        <v>2159</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2172.9</v>
+        <v>2178.9</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>3.66</v>
+        <v>6</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>508.85</v>
+        <v>516.35</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>509.5</v>
+        <v>516.45</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>519.9</v>
+        <v>521</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>509.5</v>
+        <v>512.9</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>516.35</v>
+        <v>518.05</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1981.7</v>
+        <v>2000.5</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1990.2</v>
+        <v>2002.3</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2036.2</v>
+        <v>2018.4</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1990.2</v>
+        <v>1961</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2000.5</v>
+        <v>2011.4</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>0.95</v>
+        <v>10.9</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>272.36</v>
+        <v>277.95</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>273</v>
+        <v>277.05</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>280</v>
+        <v>278.3</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>270.3</v>
+        <v>273.3</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>277.95</v>
+        <v>275.5</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>5.59</v>
+        <v>-2.45</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>2.05</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>270.09</v>
+        <v>271.85</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>271</v>
+        <v>270.9</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>275.8</v>
+        <v>272</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>269.05</v>
+        <v>265.25</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>271.85</v>
+        <v>269.3</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>1.76</v>
+        <v>-2.55</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>0.65</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5266.4</v>
+        <v>5289</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5300</v>
+        <v>5295</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5349</v>
+        <v>5295</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5238.5</v>
+        <v>5227.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5289</v>
+        <v>5260</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>22.6</v>
+        <v>-29</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>0.43</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>441.5</v>
+        <v/>
       </c>
       <c r="E54" s="12" t="n">
-        <v>445</v>
+        <v/>
       </c>
       <c r="F54" s="12" t="n">
-        <v>450.9</v>
+        <v/>
       </c>
       <c r="G54" s="12" t="n">
-        <v>443</v>
+        <v/>
       </c>
       <c r="H54" s="12" t="n">
-        <v>445.65</v>
+        <v/>
       </c>
       <c r="I54" s="12" t="n">
-        <v>4.15</v>
+        <v/>
       </c>
       <c r="J54" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1906.3</v>
+        <v>1983.3</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1928.7</v>
+        <v>1982.9</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>2007.6</v>
+        <v>1987.5</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1920.6</v>
+        <v>1948.3</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1983.3</v>
+        <v>1968.1</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>77</v>
+        <v>-15.2</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>4.04</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1736.9</v>
+        <v>1752.3</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1749.9</v>
+        <v>1735.2</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1768.1</v>
+        <v>1777</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1725.6</v>
+        <v>1735.2</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1752.3</v>
+        <v>1771.3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>0.89</v>
+        <v>19</v>
+      </c>
+      <c r="J56" s="13" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>71.18000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>71.2</v>
+        <v>71.5</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>72.40000000000001</v>
+        <v>71.58</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>70.41</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>70.97</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="J57" s="13" t="n">
-        <v>-0.3</v>
+        <v>-0.54</v>
+      </c>
+      <c r="J57" s="10" t="n">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6502.5</v>
+        <v>6619.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6508</v>
+        <v>6620</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6644</v>
+        <v>6675</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6483.5</v>
+        <v>6569</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6619.5</v>
+        <v>6651</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>1.8</v>
+        <v>31.5</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11166.5</v>
+        <v>11408</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>11299</v>
+        <v>11400</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11492</v>
+        <v>11674</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>11159</v>
+        <v>11200</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>11408</v>
+        <v>11253</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>241.5</v>
+        <v>-155</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>2.16</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>587</v>
+        <v>607.2</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>592.8</v>
+        <v>607.7</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>608.7</v>
+        <v>611.9</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>592.05</v>
+        <v>595.1</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>607.2</v>
+        <v>597.3</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>20.2</v>
+        <v>-9.9</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>3.44</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1322.9</v>
+        <v>1287.2</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1320</v>
+        <v>1287.6</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1320</v>
+        <v>1292.4</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1280.6</v>
+        <v>1268.5</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1287.2</v>
+        <v>1271.2</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-35.7</v>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v>-2.7</v>
+        <v>-16</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7109</v>
+        <v>7329</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7109</v>
+        <v>7325</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7348.5</v>
+        <v>7345</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7070</v>
+        <v>7213.5</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7329</v>
+        <v>7301.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>220</v>
+        <v>-27.5</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>3.09</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3241.6</v>
+        <v>3205.1</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3305</v>
+        <v>3215</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3325.6</v>
+        <v>3249.9</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3176.5</v>
+        <v>3196.2</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3205.1</v>
+        <v>3207.5</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-36.5</v>
+        <v>2.4</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>-1.13</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>360.55</v>
+        <v>359.05</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>365</v>
+        <v>361.5</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>379.9</v>
+        <v>371.75</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>353.45</v>
+        <v>358.55</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>359.05</v>
+        <v>361.15</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>-0.42</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>286.95</v>
+        <v>289.15</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>290</v>
+        <v>289.35</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>291.65</v>
+        <v>295</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>287.4</v>
+        <v>286.6</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>289.15</v>
+        <v>292.6</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J65" s="10" t="n">
-        <v>0.77</v>
+        <v>3.45</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>163.23</v>
+        <v>164.48</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>165.3</v>
+        <v>164.8</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>167.49</v>
+        <v>165.8</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>164.14</v>
+        <v>162.5</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>164.48</v>
+        <v>163.7</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>1.25</v>
+        <v>-0.78</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>0.77</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2406.3</v>
+        <v>2393.7</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2434.3</v>
+        <v>2384.3</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2438.8</v>
+        <v>2430</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2382.6</v>
+        <v>2360</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2393.7</v>
+        <v>2417.9</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-12.6</v>
+        <v>24.2</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>-0.52</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="J68" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -3077,24 +3077,24 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>469.3</v>
+        <v>476.2</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>479</v>
+        <v>491.4</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>469.7</v>
+        <v>477.5</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>476.2</v>
+        <v>483.2</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J69" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J69" s="13" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1067.1</v>
+        <v>1072.5</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1070.2</v>
+        <v>1073</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1090.2</v>
+        <v>1110.2</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1068.2</v>
+        <v>1065.4</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1072.5</v>
+        <v>1101.5</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J70" s="10" t="n">
-        <v>0.51</v>
+        <v>29</v>
+      </c>
+      <c r="J70" s="13" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1835.2</v>
+        <v>1899.8</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1854.9</v>
+        <v>1920</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1951.9</v>
+        <v>1920</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1850.2</v>
+        <v>1805.4</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1899.8</v>
+        <v>1809.5</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>64.59999999999999</v>
+        <v>-90.3</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>3.52</v>
+        <v>-4.75</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>699.7</v>
+        <v>703.4</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>699.7</v>
+        <v>703.5</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>716</v>
+        <v>715.75</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>690.05</v>
+        <v>700</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>703.4</v>
+        <v>711.8</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v>0.53</v>
+        <v>8.4</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2794.5</v>
+        <v>2856</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2805</v>
+        <v>2831</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2865.8</v>
+        <v>2879.9</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2805</v>
+        <v>2823.6</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2856</v>
+        <v>2871.5</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="J73" s="10" t="n">
-        <v>2.2</v>
+        <v>15.5</v>
+      </c>
+      <c r="J73" s="13" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>380.05</v>
+        <v>390.25</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>384</v>
+        <v>389.15</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>391.5</v>
+        <v>390.25</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>382.95</v>
+        <v>382.3</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>390.25</v>
+        <v>388.25</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>10.2</v>
+        <v>-2</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>2.68</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4338.8</v>
+        <v>4559.5</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4356</v>
+        <v>4559</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4590</v>
+        <v>4677.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4318</v>
+        <v>4534</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4559.5</v>
+        <v>4610.4</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>220.7</v>
-      </c>
-      <c r="J75" s="10" t="n">
-        <v>5.09</v>
+        <v>50.9</v>
+      </c>
+      <c r="J75" s="13" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1240.6</v>
+        <v>1256.6</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1241.1</v>
+        <v>1254</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1264</v>
+        <v>1254</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1238.1</v>
+        <v>1231</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1256.6</v>
+        <v>1239.6</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>16</v>
+        <v>-17</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>1.29</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1199.1</v>
+        <v>1200.5</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1208</v>
+        <v>1200</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1213.5</v>
+        <v>1205.4</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1191.4</v>
+        <v>1190</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1200.5</v>
+        <v>1200.2</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>1.4</v>
+        <v>-0.3</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2712.6</v>
+        <v>2753.6</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2725</v>
+        <v>2749.1</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2774.3</v>
+        <v>2825.5</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2725</v>
+        <v>2707</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2753.6</v>
+        <v>2806.3</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>1.51</v>
+        <v>52.7</v>
+      </c>
+      <c r="J78" s="13" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>771.7</v>
+        <v>779.4</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>772.6</v>
+        <v>774.4</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>786.6</v>
+        <v>776.9</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>772.6</v>
+        <v>763.7</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>779.4</v>
+        <v>772.3</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>7.7</v>
+        <v>-7.1</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>1</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>586.9</v>
+        <v>588.35</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>591.95</v>
+        <v>587.05</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>596.2</v>
+        <v>601.95</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>588.35</v>
+        <v>594.1</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>0.25</v>
+        <v>5.75</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5099</v>
+        <v>5066.5</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5186</v>
+        <v>5060</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5237</v>
+        <v>5135</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5006</v>
+        <v>5018</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5066.5</v>
+        <v>5109</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-32.5</v>
+        <v>42.5</v>
       </c>
       <c r="J81" s="13" t="n">
-        <v>-0.64</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1038</v>
+        <v>1042.7</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1043.3</v>
+        <v>1036.3</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1049.4</v>
+        <v>1059</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1034.5</v>
+        <v>1031.1</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1042.7</v>
+        <v>1054.7</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J82" s="10" t="n">
-        <v>0.45</v>
+        <v>12</v>
+      </c>
+      <c r="J82" s="13" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>534.85</v>
+        <v>537.4</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>540</v>
+        <v>531.75</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>544.5</v>
+        <v>538.3</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>528.25</v>
+        <v>530.25</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>537.4</v>
+        <v>532.05</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>2.55</v>
+        <v>-5.35</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>0.48</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>374.55</v>
+        <v>373.85</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>372.5</v>
+        <v>365.4</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>373.85</v>
+        <v>373.9</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-0.7</v>
+        <v>0.05</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>-0.19</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2250.9</v>
+        <v>2309.3</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2268.8</v>
+        <v>2301.5</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2365.8</v>
+        <v>2335.4</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2268.8</v>
+        <v>2288.1</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2309.3</v>
+        <v>2327.4</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>2.59</v>
+        <v>18.1</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>31030</v>
+        <v>31190</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>31400</v>
+        <v>31495</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>31400</v>
+        <v>31495</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>30945</v>
+        <v>30560</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>31190</v>
+        <v>30685</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>160</v>
+        <v>-505</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>0.52</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>69.64</v>
+        <v>69.59</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>70.06999999999999</v>
+        <v>69.51000000000001</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>70.72</v>
+        <v>69.59</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>69.23</v>
+        <v>68.36</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>69.59</v>
+        <v>68.75</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="J87" s="13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.84</v>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>125.19</v>
+        <v>126.97</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>125.5</v>
+        <v>126.55</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>127.38</v>
+        <v>128.78</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>125.34</v>
+        <v>125.79</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>126.97</v>
+        <v>127.62</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v>1.42</v>
+        <v>0.65</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>166.02</v>
+        <v>166.91</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>168.02</v>
+        <v>166.8</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>168.76</v>
+        <v>168.33</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>166.01</v>
+        <v>165.53</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>166.91</v>
+        <v>166.24</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0.89</v>
+        <v>-0.67</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>0.54</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>635.85</v>
+        <v>643.7</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>647.75</v>
+        <v>651.3</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>635</v>
+        <v>637.15</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>643.7</v>
+        <v>647.8</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="J90" s="10" t="n">
-        <v>1.23</v>
+        <v>4.1</v>
+      </c>
+      <c r="J90" s="13" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2103.6</v>
+        <v>2094.5</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2036.6</v>
+        <v>2094.5</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2111.2</v>
+        <v>2094.5</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2013.9</v>
+        <v>2036.1</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2094.5</v>
+        <v>2052.9</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>-0.43</v>
+        <v>-41.6</v>
+      </c>
+      <c r="J91" s="10" t="n">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4295.3</v>
+        <v>4262.4</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4349</v>
+        <v>4225</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4387.3</v>
+        <v>4285</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4235.3</v>
+        <v>4196.3</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4262.4</v>
+        <v>4238.4</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-32.9</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>-0.77</v>
+        <v>-24</v>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>916.05</v>
+        <v>913.9</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>925.25</v>
+        <v>911.1</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>942.4</v>
+        <v>918.1</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>911.1</v>
+        <v>903</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>913.9</v>
+        <v>910.7</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J93" s="13" t="n">
-        <v>-0.23</v>
+        <v>-3.2</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>409.95</v>
+        <v>400.25</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>414.55</v>
+        <v>400.4</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>415</v>
+        <v>407.55</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>390.8</v>
+        <v>396.45</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>400.25</v>
+        <v>402.7</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-9.699999999999999</v>
+        <v>2.45</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>-2.37</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1181.8</v>
+        <v>1168.4</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1195</v>
+        <v>1169.5</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1195</v>
+        <v>1185.2</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1165.2</v>
+        <v>1160.1</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1168.4</v>
+        <v>1178.1</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-13.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>-1.13</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>142.25</v>
+        <v>142.26</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>143.5</v>
+        <v>142</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>144.42</v>
+        <v>142.62</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>142</v>
+        <v>140.5</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>142.26</v>
+        <v>142.14</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1530.9</v>
+        <v>1530</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1574.1</v>
+        <v>1559</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1525</v>
+        <v>1513.6</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1530</v>
+        <v>1541.8</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-0.9</v>
+        <v>11.8</v>
       </c>
       <c r="J97" s="13" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>539.55</v>
+        <v>555.25</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>544.5</v>
+        <v>555</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>556.55</v>
+        <v>581.3</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>542.05</v>
+        <v>550.65</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>555.25</v>
+        <v>569.1</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>2.91</v>
+        <v>13.85</v>
+      </c>
+      <c r="J98" s="13" t="n">
+        <v>2.49</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>314.9</v>
+        <v>311.1</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>317.9</v>
+        <v>311.1</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>317.9</v>
+        <v>313.7</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>310.5</v>
+        <v>309.65</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>311.1</v>
+        <v>311.45</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-3.8</v>
+        <v>0.35</v>
       </c>
       <c r="J99" s="13" t="n">
-        <v>-1.21</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1223.1</v>
+        <v>1261.4</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1245</v>
+        <v>1263.1</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1278.9</v>
+        <v>1283.3</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1234.1</v>
+        <v>1254.7</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1261.4</v>
+        <v>1261.2</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>38.3</v>
+        <v>-0.2</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>3.13</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5287</v>
+        <v>5352.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5373.5</v>
+        <v>5359</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5514</v>
+        <v>5359</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5289</v>
+        <v>5260</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5352.5</v>
+        <v>5286.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>65.5</v>
+        <v>-66</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>1.24</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>767.4</v>
+        <v>778.4</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>774</v>
+        <v>788</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>789.35</v>
+        <v>788</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>772</v>
+        <v>754.85</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>778.4</v>
+        <v>779.4</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>1.43</v>
+        <v>1</v>
+      </c>
+      <c r="J102" s="13" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>561.15</v>
+        <v>562.3</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>565.05</v>
+        <v>563</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>566</v>
+        <v>569.8</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>562.3</v>
+        <v>561.95</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>1.15</v>
+        <v>-0.35</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1264.5</v>
+        <v>1266.6</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1278</v>
+        <v>1260.5</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1287.9</v>
+        <v>1264.9</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1259.9</v>
+        <v>1245.8</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1266.6</v>
+        <v>1252.4</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>2.1</v>
+        <v>-14.2</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>0.17</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>478.6</v>
+        <v>476.4</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>481.4</v>
+        <v>475.9</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>483.9</v>
+        <v>476.4</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>472.9</v>
+        <v>464.6</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>476.4</v>
+        <v>465.35</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="J105" s="13" t="n">
-        <v>-0.46</v>
+        <v>-11.05</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1187.65</v>
+        <v>1104.5</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1187</v>
+        <v>1114</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1187</v>
+        <v>1115</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1096</v>
+        <v>1050.1</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1104.5</v>
+        <v>1062.4</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-83.15000000000001</v>
-      </c>
-      <c r="J106" s="13" t="n">
-        <v>-7</v>
+        <v>-42.1</v>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>-3.81</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>383.3</v>
+        <v>371.65</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>378.9</v>
+        <v>371</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>382.05</v>
+        <v>375.5</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>363</v>
+        <v>368.75</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>371.65</v>
+        <v>371.35</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-11.65</v>
-      </c>
-      <c r="J107" s="13" t="n">
-        <v>-3.04</v>
+        <v>-0.3</v>
+      </c>
+      <c r="J107" s="10" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>759.05</v>
+        <v>768.55</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>767</v>
+        <v>768.45</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>777.15</v>
+        <v>784.6</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>756.55</v>
+        <v>764.25</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>768.55</v>
+        <v>772.5</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>1.25</v>
+        <v>3.95</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1367.2</v>
+        <v>1573.4</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1390.4</v>
+        <v>1569.2</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1640.6</v>
+        <v>1582.2</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1390</v>
+        <v>1522.4</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1573.4</v>
+        <v>1536.7</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>206.2</v>
+        <v>-36.7</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>15.08</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1100.95</v>
+        <v>1166.4</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1102.2</v>
+        <v>1172.5</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1171</v>
+        <v>1175.5</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1102</v>
+        <v>1157.7</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1166.4</v>
+        <v>1164.1</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>65.45</v>
+        <v>-2.3</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>5.94</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>554.7</v>
+        <v>557</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>555.2</v>
+        <v>557.4</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>561.8</v>
+        <v>560.7</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>551.25</v>
+        <v>550.6</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>557</v>
+        <v>558.15</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J111" s="10" t="n">
-        <v>0.41</v>
+        <v>1.15</v>
+      </c>
+      <c r="J111" s="13" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4014</v>
+        <v>4100.8</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>4026</v>
+        <v>4085</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4139.5</v>
+        <v>4090</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>4026</v>
+        <v>4024</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4100.8</v>
+        <v>4054.5</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>86.8</v>
+        <v>-46.3</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>2.16</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>279.73</v>
+        <v>285.65</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>280</v>
+        <v>286.6</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>287.8</v>
+        <v>291.4</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>280</v>
+        <v>283.1</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>285.65</v>
+        <v>290.45</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>2.12</v>
+        <v>4.8</v>
+      </c>
+      <c r="J113" s="13" t="n">
+        <v>1.68</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="13" t="n">
+      <c r="J114" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3626.3</v>
+        <v>3706.7</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3626.3</v>
+        <v>3706.7</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3723.4</v>
+        <v>3756.1</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3592.1</v>
+        <v>3687.4</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3706.7</v>
+        <v>3739.8</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="J115" s="10" t="n">
-        <v>2.22</v>
+        <v>33.1</v>
+      </c>
+      <c r="J115" s="13" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2305.2</v>
+        <v>2348.8</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2320</v>
+        <v>2354</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2361.9</v>
+        <v>2364.6</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2304.1</v>
+        <v>2326.6</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2348.8</v>
+        <v>2343.3</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>43.6</v>
+        <v>-5.5</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>1.89</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3097.5</v>
+        <v>3106.5</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3131.5</v>
+        <v>3114</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3172</v>
+        <v>3222</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3081.5</v>
+        <v>3070.2</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3106.5</v>
+        <v>3210.8</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>0.29</v>
+        <v>104.3</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>3.36</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>294.35</v>
+        <v>305.15</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>298</v>
+        <v>307.4</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>308.6</v>
+        <v>309.5</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>298</v>
+        <v>296.4</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>305.15</v>
+        <v>307.25</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="J118" s="10" t="n">
-        <v>3.67</v>
+        <v>2.1</v>
+      </c>
+      <c r="J118" s="13" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>775</v>
+        <v>784.55</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>781</v>
+        <v>789.05</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>786.75</v>
+        <v>810.5</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>774.9</v>
+        <v>760.6</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>784.55</v>
+        <v>807.2</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v>1.23</v>
+        <v>22.65</v>
+      </c>
+      <c r="J119" s="13" t="n">
+        <v>2.89</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13314</v>
+        <v>13580</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13559</v>
+        <v>13560</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13976</v>
+        <v>13568</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13435</v>
+        <v>13360</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13580</v>
+        <v>13426</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>266</v>
+        <v>-154</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>2</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="13" t="n">
+      <c r="J121" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2971.5</v>
+        <v>2912.9</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3000</v>
+        <v>2920</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3041</v>
+        <v>2926</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2870.4</v>
+        <v>2867</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>2912.9</v>
+        <v>2902.5</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>-58.6</v>
-      </c>
-      <c r="J122" s="13" t="n">
-        <v>-1.97</v>
+        <v>-10.4</v>
+      </c>
+      <c r="J122" s="10" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>476.5</v>
+        <v>492.4</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>472.2</v>
+        <v>494.9</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>494.85</v>
+        <v>516.2</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>472.2</v>
+        <v>492.6</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>492.4</v>
+        <v>506.3</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J123" s="10" t="n">
-        <v>3.34</v>
+        <v>13.9</v>
+      </c>
+      <c r="J123" s="13" t="n">
+        <v>2.82</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1585.7</v>
+        <v>1606.7</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1593.2</v>
+        <v>1590</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1615</v>
+        <v>1605.8</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1606.7</v>
+        <v>1596.2</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>21</v>
+        <v>-10.5</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>1.32</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1135.65</v>
+        <v>1135.4</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1146.4</v>
+        <v>1132</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1151</v>
+        <v>1137.8</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1129.8</v>
+        <v>1121</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1135.4</v>
+        <v>1133.5</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J125" s="13" t="n">
-        <v>-0.02</v>
+        <v>-1.9</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>121.21</v>
+        <v>120.21</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>121.99</v>
+        <v>120.21</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>123.43</v>
+        <v>121.11</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>119.59</v>
+        <v>118.41</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>120.21</v>
+        <v>120.24</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-1</v>
+        <v>0.03</v>
       </c>
       <c r="J126" s="13" t="n">
-        <v>-0.83</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2276.7</v>
+        <v>2276.6</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2286.9</v>
+        <v>2276.1</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2306.6</v>
+        <v>2298.2</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2247.6</v>
+        <v>2194.6</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2276.6</v>
+        <v>2209.8</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-0.1</v>
+        <v>-66.8</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>-0</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>129710</v>
+        <v>129235</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>131000</v>
+        <v>130095</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>131895</v>
+        <v>130095</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>128690</v>
+        <v>128110</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>129235</v>
+        <v>128270</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-475</v>
-      </c>
-      <c r="J128" s="13" t="n">
-        <v>-0.37</v>
+        <v>-965</v>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3424.2</v>
+        <v>3487.7</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3424.2</v>
+        <v>3490</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3515</v>
+        <v>3499.9</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3410.8</v>
+        <v>3391.1</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3487.7</v>
+        <v>3446.4</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>63.5</v>
+        <v>-41.3</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>1.85</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>399.3</v>
+        <v>407.8</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>399</v>
+        <v>409.8</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>412</v>
+        <v>418.6</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>388.6</v>
+        <v>406.2</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>407.8</v>
+        <v>413.6</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v>2.13</v>
+        <v>5.8</v>
+      </c>
+      <c r="J130" s="13" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>972.85</v>
+        <v>976.65</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>976.15</v>
+        <v>977</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>991.25</v>
+        <v>988.6</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>967.65</v>
+        <v>959</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>976.65</v>
+        <v>963.95</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>3.8</v>
+        <v>-12.7</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>0.39</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6821</v>
+        <v>6796.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>6855</v>
+        <v>6810</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>6978</v>
+        <v>7020</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6755.5</v>
+        <v>6765</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>6796.5</v>
+        <v>7005</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-24.5</v>
+        <v>208.5</v>
       </c>
       <c r="J132" s="13" t="n">
-        <v>-0.36</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1458.6</v>
+        <v>1457.1</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1472.9</v>
+        <v>1480.4</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1446.3</v>
+        <v>1447.6</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1457.1</v>
+        <v>1477.8</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-1.5</v>
+        <v>20.7</v>
       </c>
       <c r="J133" s="13" t="n">
-        <v>-0.1</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>90.37</v>
+        <v>89.09</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>91.70999999999999</v>
+        <v>89.64</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>88.3</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>89.09</v>
+        <v>88.83</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="J134" s="13" t="n">
-        <v>-1.42</v>
+        <v>-0.26</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>399.15</v>
+        <v>400.05</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>400</v>
+        <v>398.3</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>404.8</v>
+        <v>400.5</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>397.25</v>
+        <v>394.55</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>400.05</v>
+        <v>398.65</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>0.9</v>
+        <v>-1.4</v>
       </c>
       <c r="J135" s="10" t="n">
-        <v>0.23</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1669.6</v>
+        <v>1693.7</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1669</v>
+        <v>1684</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1708.9</v>
+        <v>1691.1</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1665.4</v>
+        <v>1656.6</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1693.7</v>
+        <v>1666.3</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>24.1</v>
+        <v>-27.4</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>1.44</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9726.5</v>
+        <v>9730</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9885.5</v>
+        <v>9770</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9898</v>
+        <v>9860</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9645</v>
+        <v>9654.5</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9730</v>
+        <v>9707</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>3.5</v>
+        <v>-23</v>
       </c>
       <c r="J137" s="10" t="n">
-        <v>0.04</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>299.55</v>
+        <v>292.9</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>298.4</v>
+        <v>294.35</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>299.9</v>
+        <v>295.9</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>292.35</v>
+        <v>287</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>292.9</v>
+        <v>289.95</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-6.65</v>
-      </c>
-      <c r="J138" s="13" t="n">
-        <v>-2.22</v>
+        <v>-2.95</v>
+      </c>
+      <c r="J138" s="10" t="n">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>36785</v>
+        <v>36955</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>36915</v>
+        <v>37070</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37270</v>
+        <v>37500</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>36735</v>
+        <v>36770</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>36955</v>
+        <v>37400</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>170</v>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v>0.46</v>
+        <v>445</v>
+      </c>
+      <c r="J139" s="13" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="13" t="n">
+      <c r="J140" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4800</v>
+        <v>4788.1</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>4815.2</v>
+        <v>4770</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>4844.8</v>
+        <v>4858.7</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4745.7</v>
+        <v>4743.1</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4788.1</v>
+        <v>4816.3</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-11.9</v>
+        <v>28.2</v>
       </c>
       <c r="J141" s="13" t="n">
-        <v>-0.25</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>276.76</v>
+        <v>276.7</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>280.45</v>
+        <v>280</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>282</v>
+        <v>286.8</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>275.8</v>
+        <v>270.85</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>276.7</v>
+        <v>282.55</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-0.06</v>
+        <v>5.85</v>
       </c>
       <c r="J142" s="13" t="n">
-        <v>-0.02</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>448.4</v>
+        <v>448.25</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>452.35</v>
+        <v>448.25</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>456.15</v>
+        <v>460.25</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>446.05</v>
+        <v>444</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>448.25</v>
+        <v>456.9</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-0.15</v>
+        <v>8.65</v>
       </c>
       <c r="J143" s="13" t="n">
-        <v>-0.03</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1375.7</v>
+        <v>1364.6</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1378.2</v>
+        <v>1365</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1389</v>
+        <v>1369</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1361.1</v>
+        <v>1347.7</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1364.6</v>
+        <v>1364.2</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="J144" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.4</v>
+      </c>
+      <c r="J144" s="10" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3054.8</v>
+        <v>3047.5</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3065.3</v>
+        <v>3028.7</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3124.8</v>
+        <v>3035</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3030.4</v>
+        <v>2992</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3047.5</v>
+        <v>3014.3</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="J145" s="13" t="n">
-        <v>-0.24</v>
+        <v>-33.2</v>
+      </c>
+      <c r="J145" s="10" t="n">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>109.36</v>
+        <v>108.68</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>109.5</v>
+        <v>108.8</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>111.68</v>
+        <v>111.41</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>108.13</v>
+        <v>105.45</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>108.68</v>
+        <v>107.89</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="J146" s="13" t="n">
-        <v>-0.62</v>
+        <v>-0.79</v>
+      </c>
+      <c r="J146" s="10" t="n">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8110.5</v>
+        <v>8344.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8110.5</v>
+        <v>8347.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8363</v>
+        <v>8374</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8062.5</v>
+        <v>8154</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8344.5</v>
+        <v>8337</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>234</v>
+        <v>-7.5</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>2.89</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>318.35</v>
+        <v>319.05</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>314</v>
+        <v>318.9</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>323.9</v>
+        <v>321.3</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>319.05</v>
+        <v>319.45</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1068.9</v>
+        <v>1059.1</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1069</v>
+        <v>1055.5</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1082.7</v>
+        <v>1079</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1054</v>
+        <v>1055.1</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1059.1</v>
+        <v>1063.1</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="J149" s="13" t="n">
-        <v>-0.92</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>336.55</v>
+        <v>330.2</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>339</v>
+        <v>330.3</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>344.55</v>
+        <v>335.7</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>327.65</v>
+        <v>326.15</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>330.2</v>
+        <v>332.95</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-6.35</v>
+        <v>2.75</v>
       </c>
       <c r="J150" s="13" t="n">
-        <v>-1.89</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>354.3</v>
+        <v>353.5</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>356</v>
+        <v>353.5</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>361.15</v>
+        <v>357.8</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>351.4</v>
+        <v>351.15</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>353.5</v>
+        <v>356.4</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J151" s="13" t="n">
-        <v>-0.23</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1430.8</v>
+        <v>1463.1</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1433.4</v>
+        <v>1460</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1467.4</v>
+        <v>1473.4</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1433.4</v>
+        <v>1450</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1463.1</v>
+        <v>1463.6</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="J152" s="10" t="n">
-        <v>2.26</v>
+        <v>0.5</v>
+      </c>
+      <c r="J152" s="13" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>184.62</v>
+        <v>186.15</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>185.25</v>
+        <v>185.8</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>187.82</v>
+        <v>188.83</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>184.28</v>
+        <v>185.02</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>186.15</v>
+        <v>187.31</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J153" s="10" t="n">
-        <v>0.83</v>
+        <v>1.16</v>
+      </c>
+      <c r="J153" s="13" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>643.9</v>
+        <v>644.8</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>646.95</v>
+        <v>645.95</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>649.8</v>
+        <v>646.9</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>638.05</v>
+        <v>638.4</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>644.8</v>
+        <v>645.65</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>0.14</v>
+        <v>0.85</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="155">
@@ -6001,24 +6001,24 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1819</v>
+        <v>1820.1</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1810.1</v>
+        <v>1820</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1845</v>
+        <v>1835</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1810.1</v>
+        <v>1802.6</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1820.1</v>
+        <v>1821.2</v>
       </c>
       <c r="I155" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="J155" s="10" t="n">
+      <c r="J155" s="13" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1068.45</v>
+        <v>1068.4</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1063.6</v>
+        <v>1060.6</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1089.1</v>
+        <v>1068.5</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1063.6</v>
+        <v>1049.4</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1068.4</v>
+        <v>1059.9</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-0.05</v>
+        <v>-8.5</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>-0</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>24195</v>
+        <v>24740</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>24295</v>
+        <v>24600</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>24900</v>
+        <v>24990</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>24295</v>
+        <v>24405</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>24740</v>
+        <v>24845</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>545</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>2.25</v>
+        <v>105</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>0.42</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>937.35</v>
+        <v>960.45</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>942</v>
+        <v>955.65</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>969</v>
+        <v>966.9</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>942</v>
+        <v>937.3</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>960.45</v>
+        <v>964.4</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>2.46</v>
+        <v>3.95</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>0.41</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3808.2</v>
+        <v>3834.1</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3850</v>
+        <v>3851.2</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3930</v>
+        <v>3866.5</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3820</v>
+        <v>3809.5</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3834.1</v>
+        <v>3846.6</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>0.68</v>
+        <v>12.5</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2518.6</v>
+        <v>2551.4</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2520.4</v>
+        <v>2553</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2565</v>
+        <v>2567.8</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2520</v>
+        <v>2495</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2551.4</v>
+        <v>2522.8</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>32.8</v>
+        <v>-28.6</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>1.3</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1808.3</v>
+        <v>1823.5</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1820</v>
+        <v>1828.5</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1841</v>
+        <v>1831.7</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1810</v>
+        <v>1798.6</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1823.5</v>
+        <v>1820.8</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>15.2</v>
+        <v>-2.7</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>0.84</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>605.6</v>
+        <v>575.85</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>610</v>
+        <v>570.7</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>614</v>
+        <v>587</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>548.1</v>
+        <v>564</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>575.85</v>
+        <v>580.1</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-29.75</v>
+        <v>4.25</v>
       </c>
       <c r="J162" s="13" t="n">
-        <v>-4.91</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>467.65</v>
+        <v>477.35</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>467.35</v>
+        <v>480.85</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>492.25</v>
+        <v>480.85</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>453.6</v>
+        <v>449.1</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>477.35</v>
+        <v>451.4</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>-25.95</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>2.07</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>809</v>
+        <v>805.75</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>825.05</v>
+        <v>790.1</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>850</v>
+        <v>816.9</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>801</v>
+        <v>778.2</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>805.75</v>
+        <v>801.45</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="J164" s="13" t="n">
-        <v>-0.4</v>
+        <v>-4.3</v>
+      </c>
+      <c r="J164" s="10" t="n">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1580.5</v>
+        <v>1569.6</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1586.7</v>
+        <v>1570</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1597.4</v>
+        <v>1572.9</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1550</v>
+        <v>1538.7</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1569.6</v>
+        <v>1559</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="J165" s="13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-10.6</v>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1144.6</v>
+        <v>1160.4</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1149.7</v>
+        <v>1161.2</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1174.4</v>
+        <v>1166.8</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1149.7</v>
+        <v>1149</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1160.4</v>
+        <v>1153.5</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>15.8</v>
+        <v>-6.9</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>1.38</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="13" t="n">
+      <c r="J167" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>444.55</v>
+        <v>441.4</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>445.5</v>
+        <v>441.05</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>448</v>
+        <v>445.75</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>438.5</v>
+        <v>436.65</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>441.4</v>
+        <v>442.65</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-3.15</v>
+        <v>1.25</v>
       </c>
       <c r="J168" s="13" t="n">
-        <v>-0.71</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>211.36</v>
+        <v>212.24</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>212.55</v>
+        <v>212.2</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>214.5</v>
+        <v>212.34</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>211.4</v>
+        <v>209.45</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>212.24</v>
+        <v>211.32</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>0.88</v>
+        <v>-0.92</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>0.42</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2473.9</v>
+        <v>2431.3</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2494</v>
+        <v>2430</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2498.3</v>
+        <v>2460.4</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2425</v>
+        <v>2412.2</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2431.3</v>
+        <v>2427.3</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-42.6</v>
-      </c>
-      <c r="J170" s="13" t="n">
-        <v>-1.72</v>
+        <v>-4</v>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1473.5</v>
+        <v>1471.6</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1484</v>
+        <v>1465</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1492.4</v>
+        <v>1483.8</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1455.2</v>
+        <v>1447.1</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1471.6</v>
+        <v>1452.2</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J171" s="13" t="n">
-        <v>-0.13</v>
+        <v>-19.4</v>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2947.9</v>
+        <v>2906</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2972.6</v>
+        <v>2917.1</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2978.6</v>
+        <v>2950</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2882.3</v>
+        <v>2895.6</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2906</v>
+        <v>2932.4</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-41.9</v>
+        <v>26.4</v>
       </c>
       <c r="J172" s="13" t="n">
-        <v>-1.42</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4385.2</v>
+        <v>4363</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4407.1</v>
+        <v>4355</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4447.4</v>
+        <v>4397</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4352.7</v>
+        <v>4330.3</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4363</v>
+        <v>4373.6</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-22.2</v>
+        <v>10.6</v>
       </c>
       <c r="J173" s="13" t="n">
-        <v>-0.51</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4185.1</v>
+        <v>4251.8</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4223.2</v>
+        <v>4251.8</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4280</v>
+        <v>4300</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4213</v>
+        <v>4236.4</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4251.8</v>
+        <v>4275.1</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>1.59</v>
+        <v>23.3</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1736</v>
+        <v>1724</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1748.3</v>
+        <v>1728.8</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1780</v>
+        <v>1743.8</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1705.1</v>
+        <v>1710.8</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1724</v>
+        <v>1734.7</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-12</v>
+        <v>10.7</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4144.6</v>
+        <v>4158.5</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4135</v>
+        <v>4150.1</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4193.9</v>
+        <v>4158.5</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4067.2</v>
+        <v>4075.6</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4158.5</v>
+        <v>4135.4</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>13.9</v>
+        <v>-23.1</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>0.34</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3492.9</v>
+        <v>3495.5</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3400</v>
+        <v>3499.9</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3536.8</v>
+        <v>3544</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3367.8</v>
+        <v>3462.8</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3495.5</v>
+        <v>3534.4</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>38.9</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1458.6</v>
+        <v>1463.1</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1464.7</v>
+        <v>1466.4</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1473.2</v>
+        <v>1469.8</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1451</v>
+        <v>1441</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1463.1</v>
+        <v>1453.8</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>4.5</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J178" s="10" t="n">
-        <v>0.31</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11586</v>
+        <v>11758</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11670</v>
+        <v>11671</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11798</v>
+        <v>11987</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11590</v>
+        <v>11624</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11758</v>
+        <v>11963</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>172</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>1.48</v>
+        <v>205</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>1.74</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>165.94</v>
+        <v>163.77</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>167</v>
+        <v>163.5</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>168.5</v>
+        <v>164.4</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>163.32</v>
+        <v>161.44</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>163.77</v>
+        <v>163.74</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-2.17</v>
-      </c>
-      <c r="J180" s="13" t="n">
-        <v>-1.31</v>
+        <v>-0.03</v>
+      </c>
+      <c r="J180" s="10" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>641.85</v>
+        <v>643.35</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>645.9</v>
+        <v>648</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>656</v>
+        <v>648.9</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>639</v>
+        <v>638.85</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>643.35</v>
+        <v>642.05</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>1.5</v>
+        <v>-1.3</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>0.23</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>271.55</v>
+        <v>294.65</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>277</v>
+        <v>296.95</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>296</v>
+        <v>305.9</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>274.95</v>
+        <v>292</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>294.65</v>
+        <v>303.9</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>8.51</v>
+        <v>9.25</v>
+      </c>
+      <c r="J182" s="13" t="n">
+        <v>3.14</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1430.4</v>
+        <v>1454.2</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1445.2</v>
+        <v>1452</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1463.7</v>
+        <v>1453</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1413.3</v>
+        <v>1360</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1454.2</v>
+        <v>1375.9</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>23.8</v>
+        <v>-78.3</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>1.66</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>200.65</v>
+        <v>200.75</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>202.4</v>
+        <v>200</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>203.37</v>
+        <v>202.3</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>200.06</v>
+        <v>199.6</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>200.75</v>
+        <v>199.78</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>0.1</v>
+        <v>-0.97</v>
       </c>
       <c r="J184" s="10" t="n">
-        <v>0.05</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="13" t="n">
+      <c r="J185" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>891.9</v>
+        <v>902.35</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>895</v>
+        <v>897.3</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>905</v>
+        <v>918</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>893.15</v>
+        <v>897</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>902.35</v>
+        <v>912.25</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="J186" s="10" t="n">
-        <v>1.17</v>
+        <v>9.9</v>
+      </c>
+      <c r="J186" s="13" t="n">
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  04-May-2026 03:10 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  05-May-2026 06:28 PM</t>
         </is>
       </c>
     </row>
@@ -7256,14 +7256,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04-May-2026 03:10 PM</t>
+          <t>05-May-2026 06:28 PM</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>184</v>
       </c>
       <c r="C2" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 05-May-2026 06:28 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 06-May-2026 02:47 PM</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5">
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>05-May-2026 06:28 PM</t>
+          <t>06-May-2026 02:47 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  05-May-2026 06:28 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  06-May-2026 02:47 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>513.1</v>
+        <v>488</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>513.05</v>
+        <v>492.2</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>513.1</v>
+        <v>506.2</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>475.55</v>
+        <v>482</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>488</v>
+        <v>497.85</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-25.1</v>
+        <v>9.85</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-4.89</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7236.5</v>
+        <v>7328</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7248</v>
+        <v>7389</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7349</v>
+        <v>7389</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7215</v>
+        <v>7135</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7328</v>
+        <v>7182.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>91.5</v>
+        <v>-145.5</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>1.26</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25415</v>
+        <v>25305</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25420</v>
+        <v>25440</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>25575</v>
+        <v>26450</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25175</v>
+        <v>25430</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>25305</v>
+        <v>26300</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-110</v>
+        <v>995</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>-0.43</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>345.85</v>
+        <v>360.85</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>347.2</v>
+        <v>365</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>363.75</v>
+        <v>372.5</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>346.5</v>
+        <v>364.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>360.85</v>
+        <v>369.3</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>4.34</v>
+        <v>8.449999999999999</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>2.34</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>65.93000000000001</v>
+        <v>63.99</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>65.05</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>65.34999999999999</v>
+        <v>66.58</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>63.51</v>
+        <v>63.55</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>63.99</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-1.94</v>
+        <v>2.22</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>-2.94</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1398.2</v>
+        <v>1392.6</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1396.1</v>
+        <v>1397.6</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1396.1</v>
+        <v>1425.9</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1375.1</v>
+        <v>1392.1</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1392.6</v>
+        <v>1414</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-5.6</v>
+        <v>21.4</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>-0.4</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2485.7</v>
+        <v>2462</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2470</v>
+        <v>2475.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2511.9</v>
+        <v>2546.5</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2450</v>
+        <v>2472.2</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2462</v>
+        <v>2540.3</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-23.7</v>
+        <v>78.3</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>-0.95</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1742.6</v>
+        <v>1725</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1749.8</v>
+        <v>1750</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1757.4</v>
+        <v>1762.4</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1718.7</v>
+        <v>1718.6</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1725</v>
+        <v>1748.3</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-17.6</v>
+        <v>23.3</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>-1.01</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5360.5</v>
+        <v>5403</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5389.5</v>
+        <v>5405</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5421.5</v>
+        <v>5635.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5313</v>
+        <v>5404</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5403</v>
+        <v>5557</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>0.79</v>
+        <v>154</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>2.85</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>445.3</v>
+        <v>433.1</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>439</v>
+        <v>438.55</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>441.1</v>
+        <v>449.6</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>431.5</v>
+        <v>435.8</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>433.1</v>
+        <v>446.9</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-12.2</v>
+        <v>13.8</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>-2.74</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>307.7</v>
+        <v>314.4</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>307.9</v>
+        <v>316.75</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>317.5</v>
+        <v>318.6</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>303.7</v>
+        <v>310.6</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>314.4</v>
+        <v>316.85</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1873</v>
+        <v>1870.6</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1882.6</v>
+        <v>1899.9</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1882.6</v>
+        <v>1921</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1848.1</v>
+        <v>1869</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1870.6</v>
+        <v>1914.7</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-2.4</v>
+        <v>44.1</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7737.5</v>
+        <v>7772</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7724.5</v>
+        <v>7810.5</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7780.5</v>
+        <v>7815</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7678</v>
+        <v>7742.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7772</v>
+        <v>7760.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>34.5</v>
+        <v>-11.5</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>0.45</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>409.45</v>
+        <v>402.6</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>409</v>
+        <v>405.5</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>410</v>
+        <v>418.6</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>399.6</v>
+        <v>403.7</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>402.6</v>
+        <v>412.65</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-6.85</v>
+        <v>10.05</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>-1.67</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>160.77</v>
+        <v>160.25</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>160</v>
+        <v>163.5</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>161.66</v>
+        <v>169.11</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>158.59</v>
+        <v>160.5</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>160.25</v>
+        <v>167.8</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-0.52</v>
+        <v>7.55</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>-0.32</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2448.1</v>
+        <v>2430</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2430</v>
+        <v>2460</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2454.9</v>
+        <v>2529</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2415</v>
+        <v>2440.4</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2430</v>
+        <v>2519</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-18.1</v>
+        <v>89</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>-0.74</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1559.6</v>
+        <v>1531.6</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1570</v>
+        <v>1545</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1570</v>
+        <v>1588.7</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1528.5</v>
+        <v>1533.1</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1531.6</v>
+        <v>1576.1</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-28</v>
+        <v>44.5</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>-1.8</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>643.15</v>
+        <v>647.2</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>644.85</v>
+        <v>652</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>653.6</v>
+        <v>658</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>636.65</v>
+        <v>641</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>647.2</v>
+        <v>651</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>0.63</v>
+        <v>3.8</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6949.5</v>
+        <v>6911</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>7010</v>
+        <v>6956</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7054</v>
+        <v>7150</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6876.5</v>
+        <v>6920.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6911</v>
+        <v>7108</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-38.5</v>
+        <v>197</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>-0.55</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1015</v>
+        <v>1007.1</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>1015</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1015</v>
+        <v>1028.4</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1002.1</v>
+        <v>1002</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1007.1</v>
+        <v>1024</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-7.9</v>
+        <v>16.9</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>-0.78</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1376</v>
+        <v>1428.1</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1373.9</v>
+        <v>1431</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1431</v>
+        <v>1489.7</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1367</v>
+        <v>1426.1</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1428.1</v>
+        <v>1484</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>3.79</v>
+        <v>55.9</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>3.91</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1275.1</v>
+        <v>1259.7</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1268</v>
+        <v>1275</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1273.7</v>
+        <v>1301</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1252</v>
+        <v>1255.2</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1259.7</v>
+        <v>1294.2</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-15.4</v>
+        <v>34.5</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>-1.21</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>10132</v>
+        <v>10046</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10131</v>
+        <v>10180</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10175</v>
+        <v>10390</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10016</v>
+        <v>10141</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>10046</v>
+        <v>10319</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-86</v>
+        <v>273</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>-0.85</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1770.4</v>
+        <v>1794.6</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1760</v>
+        <v>1810</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1799</v>
+        <v>1838.8</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1742.1</v>
+        <v>1798.1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1794.6</v>
+        <v>1836.1</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J26" s="13" t="n">
-        <v>1.37</v>
+        <v>41.5</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>2.31</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>950.2</v>
+        <v>958.6</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>950.2</v>
+        <v>965</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>961.1</v>
+        <v>984</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>933.15</v>
+        <v>965</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>958.6</v>
+        <v>980.75</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J27" s="13" t="n">
-        <v>0.88</v>
+        <v>22.15</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>2.31</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2205</v>
+        <v>2172</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2201.1</v>
+        <v>2193.5</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2227.9</v>
+        <v>2238.6</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2164.9</v>
+        <v>2188</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2172</v>
+        <v>2230.3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-33</v>
+        <v>58.3</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>-1.5</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
+        <v>531</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>536.75</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>537</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>522.6</v>
+      </c>
+      <c r="H29" s="9" t="n">
         <v>524.85</v>
       </c>
-      <c r="E29" s="9" t="n">
-        <v>524.75</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>535.9</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>520</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>531</v>
-      </c>
       <c r="I29" s="9" t="n">
-        <v>6.15</v>
+        <v>-6.15</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>1.17</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>206.76</v>
+        <v>206.44</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>206.41</v>
+        <v>209</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>208</v>
+        <v>210.63</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>204.1</v>
+        <v>205.12</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>206.44</v>
+        <v>208.88</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-0.32</v>
+        <v>2.44</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>-0.15</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>265.1</v>
+        <v>263.4</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>265.4</v>
+        <v>268.7</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>265.8</v>
+        <v>271.4</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>261.55</v>
+        <v>262.8</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>263.4</v>
+        <v>270.3</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-1.7</v>
+        <v>6.9</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>-0.64</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>433.55</v>
+        <v>433.35</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>433.5</v>
+        <v>437</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>436.5</v>
+        <v>439.65</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>429.3</v>
+        <v>435.15</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>433.35</v>
+        <v>438.2</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-0.2</v>
+        <v>4.85</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>-0.05</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
+        <v>470.6</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>474.65</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>480</v>
+      </c>
+      <c r="G33" s="9" t="n">
         <v>470.3</v>
       </c>
-      <c r="E33" s="9" t="n">
-        <v>469.1</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>476</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>465.9</v>
-      </c>
       <c r="H33" s="9" t="n">
-        <v>470.6</v>
+        <v>478.45</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>0.06</v>
+        <v>7.85</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1827.1</v>
+        <v>1806.1</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1828</v>
+        <v>1817</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1846</v>
+        <v>1841.5</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1801</v>
+        <v>1813.8</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1806.1</v>
+        <v>1833.7</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-21</v>
+        <v>27.6</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>-1.15</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>377.05</v>
+        <v>374.95</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>379.9</v>
+        <v>378</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>388.4</v>
+        <v>387.5</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>371.3</v>
+        <v>368.4</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>374.95</v>
+        <v>385.95</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-2.1</v>
+        <v>11</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>360.6</v>
+        <v>368.25</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>360.6</v>
+        <v>372.8</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>370.9</v>
+        <v>384.5</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>359.2</v>
+        <v>371.05</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>368.25</v>
+        <v>380.6</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="J36" s="13" t="n">
-        <v>2.12</v>
+        <v>12.35</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>35850</v>
+        <v>35870</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>36100</v>
+        <v>36000</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>36285</v>
+        <v>36750</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>35810</v>
+        <v>35795</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>35870</v>
+        <v>36645</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="J37" s="13" t="n">
-        <v>0.06</v>
+        <v>775</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>2.16</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>301.7</v>
+        <v>298.5</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>300.25</v>
+        <v>304.7</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>300.45</v>
+        <v>316.6</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>293.3</v>
+        <v>301.85</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>298.5</v>
+        <v>314.05</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-3.2</v>
+        <v>15.55</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>-1.06</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5792.5</v>
+        <v>5834.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5775</v>
+        <v>5878</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5842.5</v>
+        <v>5880</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5734.5</v>
+        <v>5764</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5834.5</v>
+        <v>5783</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>42</v>
+        <v>-51.5</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>0.73</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>366.1</v>
+        <v>370</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>374.4</v>
+        <v>379</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>363.6</v>
+        <v>371.4</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>370</v>
+        <v>372.5</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J40" s="13" t="n">
-        <v>1.07</v>
+        <v>2.5</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>134.8</v>
+        <v>134.31</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>134.98</v>
+        <v>137.23</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>135.33</v>
+        <v>138.36</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>133.13</v>
+        <v>134.51</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>134.31</v>
+        <v>138.04</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.49</v>
+        <v>3.73</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>-0.36</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>896.5</v>
+        <v>874.45</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>900</v>
+        <v>884</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>871.1</v>
+        <v>877.1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>874.45</v>
+        <v>903.3</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-22.05</v>
+        <v>28.85</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>-2.46</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>441.55</v>
+        <v>442.55</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>441.55</v>
+        <v>442.15</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>443.4</v>
+        <v>453.7</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>437.7</v>
+        <v>442.15</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>442.55</v>
+        <v>452.65</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>0.23</v>
+        <v>10.1</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>2.28</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1639.5</v>
+        <v>1657.4</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1644</v>
+        <v>1681.2</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1666.9</v>
+        <v>1724</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1623</v>
+        <v>1678.9</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1657.4</v>
+        <v>1711.9</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>1.09</v>
+        <v>54.5</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>3.29</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1335</v>
+        <v>1333.7</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1339.4</v>
+        <v>1372</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1316.4</v>
+        <v>1333.1</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1333.7</v>
+        <v>1364.4</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-1.3</v>
+        <v>30.7</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>-0.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>479.95</v>
+        <v>472.6</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>479.95</v>
+        <v>473.85</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>480</v>
+        <v>477.5</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>471.2</v>
+        <v>468.05</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>472.6</v>
+        <v>470.2</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-7.35</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>-1.53</v>
+        <v>-2.4</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1151.6</v>
+        <v>1168.8</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1166</v>
+        <v>1261.2</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1181.3</v>
+        <v>1295.8</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1147.5</v>
+        <v>1246.9</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1168.8</v>
+        <v>1280.4</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>1.49</v>
+        <v>111.6</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2172.9</v>
+        <v>2178.9</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2184</v>
+        <v>2198</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2185</v>
+        <v>2198</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2159</v>
+        <v>2151.9</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2178.9</v>
+        <v>2157.1</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>6</v>
+        <v>-21.8</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>0.28</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>516.35</v>
+        <v>518.05</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>516.45</v>
+        <v>522</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>512.9</v>
+        <v>518.1</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>518.05</v>
+        <v>524.2</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>0.33</v>
+        <v>6.15</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2000.5</v>
+        <v>2011.4</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>2002.3</v>
+        <v>2021.5</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2018.4</v>
+        <v>2029</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1961</v>
+        <v>1991.1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2011.4</v>
+        <v>2018.1</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>0.54</v>
+        <v>6.7</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>0.33</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>277.95</v>
+        <v>275.5</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>277.05</v>
+        <v>277</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>278.3</v>
+        <v>286.9</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>273.3</v>
+        <v>276.1</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>275.5</v>
+        <v>284.05</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-2.45</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>-0.88</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>271.85</v>
+        <v>269.3</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>270.9</v>
+        <v>275</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>272</v>
+        <v>282.5</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>265.25</v>
+        <v>268.35</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>269.3</v>
+        <v>273</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-2.55</v>
+        <v>3.7</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5289</v>
+        <v>5260</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5295</v>
+        <v>5331.5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5295</v>
+        <v>5355.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5227.5</v>
+        <v>5230.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5260</v>
+        <v>5324.5</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-29</v>
+        <v>64.5</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>-0.55</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v/>
+        <v>460.55</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v/>
+        <v>465</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v/>
+        <v>468</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v/>
+        <v>458.6</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v/>
+        <v>466.25</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v/>
+        <v>5.7</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v/>
+        <v>1.24</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1983.3</v>
+        <v>1968.1</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1982.9</v>
+        <v>1968.1</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1987.5</v>
+        <v>1993.5</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1948.3</v>
+        <v>1939.2</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1968.1</v>
+        <v>1974.6</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-15.2</v>
+        <v>6.5</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>-0.77</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1752.3</v>
+        <v>1771.3</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1735.2</v>
+        <v>1785</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1777</v>
+        <v>1833.8</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1735.2</v>
+        <v>1767</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1771.3</v>
+        <v>1821.6</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J56" s="13" t="n">
-        <v>1.08</v>
+        <v>50.3</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>2.84</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>70.97</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>71.5</v>
+        <v>72.78</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>71.58</v>
+        <v>81.2</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>69.40000000000001</v>
+        <v>68.16</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>70.43000000000001</v>
+        <v>78.92</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-0.54</v>
+        <v>8.49</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>-0.76</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6619.5</v>
+        <v>6651</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6620</v>
+        <v>6690</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6675</v>
+        <v>6765.5</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6569</v>
+        <v>6615.5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6651</v>
+        <v>6702</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>0.48</v>
+        <v>51</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>0.77</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11408</v>
+        <v>11253</v>
       </c>
       <c r="E59" s="9" t="n">
         <v>11400</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11674</v>
+        <v>11405</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>11200</v>
+        <v>11152</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>11253</v>
+        <v>11299</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-155</v>
+        <v>46</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>-1.36</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>607.2</v>
+        <v>597.3</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>607.7</v>
+        <v>600.05</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>611.9</v>
+        <v>611.8</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>595.1</v>
+        <v>594.45</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>597.3</v>
+        <v>609.6</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-9.9</v>
+        <v>12.3</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>-1.63</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1287.2</v>
+        <v>1271.2</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1287.6</v>
+        <v>1282</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1292.4</v>
+        <v>1328.6</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1268.5</v>
+        <v>1277.1</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1271.2</v>
+        <v>1311</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-16</v>
+        <v>39.8</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>-1.24</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7329</v>
+        <v>7301.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7325</v>
+        <v>7370</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7345</v>
+        <v>7392</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7213.5</v>
+        <v>7175.5</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7301.5</v>
+        <v>7310.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-27.5</v>
+        <v>9</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>-0.38</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3205.1</v>
+        <v>3207.5</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3215</v>
+        <v>3233</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3249.9</v>
+        <v>3342</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3196.2</v>
+        <v>3220.3</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3207.5</v>
+        <v>3317.1</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>109.6</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>3.42</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>359.05</v>
+        <v>361.15</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>361.5</v>
+        <v>365.7</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>371.75</v>
+        <v>366.2</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>358.55</v>
+        <v>340.25</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>361.15</v>
+        <v>351.7</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>2.1</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>0.58</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>289.15</v>
+        <v>292.6</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>289.35</v>
+        <v>295.25</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>295</v>
+        <v>296.45</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>286.6</v>
+        <v>288.85</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>292.6</v>
+        <v>293</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>1.19</v>
+        <v>0.4</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>164.48</v>
+        <v>163.7</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>164.8</v>
+        <v>164.24</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>165.8</v>
+        <v>165.95</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>162.5</v>
+        <v>163.75</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>163.7</v>
+        <v>165.68</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.78</v>
+        <v>1.98</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>-0.47</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2393.7</v>
+        <v>2417.9</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2384.3</v>
+        <v>2435</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2430</v>
+        <v>2440</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2360</v>
+        <v>2354.9</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2417.9</v>
+        <v>2377.6</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>24.2</v>
+        <v>-40.3</v>
       </c>
       <c r="J67" s="13" t="n">
-        <v>1.01</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="10" t="n">
+      <c r="J68" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>476.2</v>
+        <v>483.2</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>480</v>
+        <v>485.55</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>491.4</v>
+        <v>506</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>477.5</v>
+        <v>485.55</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>483.2</v>
+        <v>498.35</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J69" s="13" t="n">
-        <v>1.47</v>
+        <v>15.15</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>3.14</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1072.5</v>
+        <v>1101.5</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1073</v>
+        <v>1122</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1110.2</v>
+        <v>1122</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1065.4</v>
+        <v>1083.5</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1101.5</v>
+        <v>1094.1</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>29</v>
+        <v>-7.4</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>2.7</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1899.8</v>
+        <v>1809.5</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1920</v>
+        <v>1819.1</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1920</v>
+        <v>1870</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1805.4</v>
+        <v>1812.7</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1809.5</v>
+        <v>1867.2</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-90.3</v>
+        <v>57.7</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>-4.75</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>703.4</v>
+        <v>711.8</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>703.5</v>
+        <v>714.5</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>715.75</v>
+        <v>755.1</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>711.8</v>
+        <v>736</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J72" s="13" t="n">
-        <v>1.19</v>
+        <v>24.2</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2856</v>
+        <v>2871.5</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2831</v>
+        <v>2885.5</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2879.9</v>
+        <v>2923.3</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2823.6</v>
+        <v>2872.3</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2871.5</v>
+        <v>2914.8</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J73" s="13" t="n">
-        <v>0.54</v>
+        <v>43.3</v>
+      </c>
+      <c r="J73" s="10" t="n">
+        <v>1.51</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>390.25</v>
+        <v>388.25</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>389.15</v>
+        <v>391.4</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>390.25</v>
+        <v>399</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>382.3</v>
+        <v>387.2</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>388.25</v>
+        <v>397.55</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>-2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>-0.51</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4559.5</v>
+        <v>4610.4</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4559</v>
+        <v>4628.9</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4677.5</v>
+        <v>4671.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4534</v>
+        <v>4610</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4610.4</v>
+        <v>4626.9</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="J75" s="13" t="n">
-        <v>1.12</v>
+        <v>16.5</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1256.6</v>
+        <v>1239.6</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1254</v>
+        <v>1259.8</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1231</v>
+        <v>1241.2</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1239.6</v>
+        <v>1257.3</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-17</v>
+        <v>17.7</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>-1.35</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1200.5</v>
+        <v>1200.2</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1200</v>
+        <v>1208</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1205.4</v>
+        <v>1212</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1190</v>
+        <v>1186.4</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1200.2</v>
+        <v>1189.1</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>-0.02</v>
+        <v>-11.1</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2753.6</v>
+        <v>2806.3</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2749.1</v>
+        <v>2830</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2825.5</v>
+        <v>2866</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2707</v>
+        <v>2807.4</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2806.3</v>
+        <v>2815.9</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="J78" s="13" t="n">
-        <v>1.91</v>
+        <v>9.6</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>779.4</v>
+        <v>772.3</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>774.4</v>
+        <v>775.15</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>776.9</v>
+        <v>798.95</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>763.7</v>
+        <v>773.5</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>772.3</v>
+        <v>796.55</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-7.1</v>
+        <v>24.25</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>-0.91</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>588.35</v>
+        <v>594.1</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>587.05</v>
+        <v>597.9</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>601.95</v>
+        <v>612.6</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>586</v>
+        <v>594.55</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>594.1</v>
+        <v>606.35</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>0.98</v>
+        <v>12.25</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>2.06</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5066.5</v>
+        <v>5109</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5060</v>
+        <v>5240</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5135</v>
+        <v>5281</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5018</v>
+        <v>4950</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5109</v>
+        <v>5170</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="J81" s="13" t="n">
-        <v>0.84</v>
+        <v>61</v>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>1.19</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1042.7</v>
+        <v>1054.7</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1036.3</v>
+        <v>1067.8</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1059</v>
+        <v>1073.7</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1031.1</v>
+        <v>1042.4</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1054.7</v>
+        <v>1045.8</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>12</v>
+        <v>-8.9</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>1.15</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>537.4</v>
+        <v>532.05</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>531.75</v>
+        <v>544</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>538.3</v>
+        <v>553.5</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>530.25</v>
+        <v>540.7</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>532.05</v>
+        <v>550.5</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-5.35</v>
+        <v>18.45</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>-1</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>373.85</v>
+        <v>373.9</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>376</v>
+        <v>402.4</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>365.4</v>
+        <v>377.4</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>373.9</v>
+        <v>399.2</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J84" s="13" t="n">
-        <v>0.01</v>
+        <v>25.3</v>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>6.77</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2309.3</v>
+        <v>2327.4</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2301.5</v>
+        <v>2330</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2335.4</v>
+        <v>2339.4</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2288.1</v>
+        <v>2288.3</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2327.4</v>
+        <v>2317.1</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>18.1</v>
+        <v>-10.3</v>
       </c>
       <c r="J85" s="13" t="n">
-        <v>0.78</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>31190</v>
+        <v>30685</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>31495</v>
+        <v>31210</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>31495</v>
+        <v>31210</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>30560</v>
+        <v>30000</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>30685</v>
+        <v>30180</v>
       </c>
       <c r="I86" s="12" t="n">
         <v>-505</v>
       </c>
-      <c r="J86" s="10" t="n">
-        <v>-1.62</v>
+      <c r="J86" s="13" t="n">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="G87" s="9" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="H87" s="9" t="n">
         <v>69.59</v>
       </c>
-      <c r="E87" s="9" t="n">
-        <v>69.51000000000001</v>
-      </c>
-      <c r="F87" s="9" t="n">
-        <v>69.59</v>
-      </c>
-      <c r="G87" s="9" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="H87" s="9" t="n">
-        <v>68.75</v>
-      </c>
       <c r="I87" s="9" t="n">
-        <v>-0.84</v>
+        <v>0.84</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>-1.21</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>126.97</v>
+        <v>127.62</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>126.55</v>
+        <v>129.07</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>128.78</v>
+        <v>129.98</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>125.79</v>
+        <v>128.34</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>127.62</v>
+        <v>129.8</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J88" s="13" t="n">
-        <v>0.51</v>
+        <v>2.18</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>166.91</v>
+        <v>166.24</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>166.8</v>
+        <v>168</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>168.33</v>
+        <v>170.19</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>165.53</v>
+        <v>166.2</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>166.24</v>
+        <v>169.46</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-0.67</v>
+        <v>3.22</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>-0.4</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>643.7</v>
+        <v>647.8</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>651.3</v>
+        <v>669</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>637.15</v>
+        <v>651</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>647.8</v>
+        <v>666.15</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J90" s="13" t="n">
-        <v>0.64</v>
+        <v>18.35</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>2.83</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2094.5</v>
+        <v>2052.9</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2094.5</v>
+        <v>2066.9</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2094.5</v>
+        <v>2068.8</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2036.1</v>
+        <v>2025.3</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2052.9</v>
+        <v>2056.9</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-41.6</v>
+        <v>4</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>-1.99</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4262.4</v>
+        <v>4238.4</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4225</v>
+        <v>4320</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4285</v>
+        <v>4565.6</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4196.3</v>
+        <v>4315.6</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4238.4</v>
+        <v>4520.2</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-24</v>
+        <v>281.8</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>913.9</v>
+        <v>910.7</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>911.1</v>
+        <v>920.4</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>918.1</v>
+        <v>949.75</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>903</v>
+        <v>917.95</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>910.7</v>
+        <v>946.75</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-3.2</v>
+        <v>36.05</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>-0.35</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>400.25</v>
+        <v>402.7</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>400.4</v>
+        <v>406.15</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>407.55</v>
+        <v>412.9</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>396.45</v>
+        <v>404.45</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>402.7</v>
+        <v>408.3</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J94" s="13" t="n">
-        <v>0.61</v>
+        <v>5.6</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>1.39</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1168.4</v>
+        <v>1178.1</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1169.5</v>
+        <v>1187</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1185.2</v>
+        <v>1191.5</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1160.1</v>
+        <v>1164.1</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1178.1</v>
+        <v>1167.2</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>9.699999999999999</v>
+        <v>-10.9</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>0.83</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>142.26</v>
+        <v>142.14</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>142</v>
+        <v>143.5</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>142.62</v>
+        <v>148.75</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>140.5</v>
+        <v>143.22</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>142.14</v>
+        <v>148.21</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-0.12</v>
+        <v>6.07</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>-0.08</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1530</v>
+        <v>1541.8</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1535</v>
+        <v>1548</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1559</v>
+        <v>1581</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1513.6</v>
+        <v>1542</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1541.8</v>
+        <v>1564.4</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J97" s="13" t="n">
-        <v>0.77</v>
+        <v>22.6</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>1.47</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>555.25</v>
+        <v>569.1</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>555</v>
+        <v>574.5</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>581.3</v>
+        <v>576.7</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>550.65</v>
+        <v>566.05</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>569.1</v>
+        <v>572.75</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="J98" s="13" t="n">
-        <v>2.49</v>
+        <v>3.65</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>311.1</v>
+        <v>311.45</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>311.1</v>
+        <v>312.8</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>313.7</v>
+        <v>313.6</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>309.65</v>
+        <v>309.25</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>311.45</v>
+        <v>310.7</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>0.35</v>
+        <v>-0.75</v>
       </c>
       <c r="J99" s="13" t="n">
-        <v>0.11</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1261.4</v>
+        <v>1261.2</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1263.1</v>
+        <v>1272</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1283.3</v>
+        <v>1283.6</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1254.7</v>
+        <v>1250</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1261.2</v>
+        <v>1264.3</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-0.2</v>
+        <v>3.1</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5352.5</v>
+        <v>5286.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5359</v>
+        <v>5340</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5359</v>
+        <v>5556</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5260</v>
+        <v>5302.5</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5286.5</v>
+        <v>5521.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-66</v>
+        <v>235</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>-1.23</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>778.4</v>
+        <v>779.4</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>788</v>
+        <v>781.95</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>788</v>
+        <v>787.4</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>754.85</v>
+        <v>760.05</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>779.4</v>
+        <v>766.3</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>1</v>
+        <v>-13.1</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>0.13</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>562.3</v>
+        <v>561.95</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>563</v>
+        <v>567.6</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>569.8</v>
+        <v>571.45</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>560</v>
+        <v>561.3</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>561.95</v>
+        <v>567.9</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-0.35</v>
+        <v>5.95</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>-0.06</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1266.6</v>
+        <v>1252.4</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1260.5</v>
+        <v>1262.5</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1264.9</v>
+        <v>1278.6</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1245.8</v>
+        <v>1253</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1252.4</v>
+        <v>1273.3</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-14.2</v>
+        <v>20.9</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>-1.12</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>476.4</v>
+        <v>465.35</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>475.9</v>
+        <v>469</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>476.4</v>
+        <v>472.7</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>464.6</v>
+        <v>461</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>465.35</v>
+        <v>471.25</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-11.05</v>
+        <v>5.9</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>-2.32</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1104.5</v>
+        <v>1062.4</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1114</v>
+        <v>1080</v>
       </c>
       <c r="F106" s="12" t="n">
         <v>1115</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1050.1</v>
+        <v>1077.9</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1062.4</v>
+        <v>1110.8</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-42.1</v>
+        <v>48.4</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>-3.81</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>371.65</v>
+        <v>371.35</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>375.5</v>
+        <v>380</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>368.75</v>
+        <v>365.65</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>371.35</v>
+        <v>376.6</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-0.3</v>
+        <v>5.25</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>-0.08</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>768.55</v>
+        <v>772.5</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>768.45</v>
+        <v>783.95</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>784.6</v>
+        <v>795.3</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>764.25</v>
+        <v>722.5</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>772.5</v>
+        <v>748.6</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>3.95</v>
+        <v>-23.9</v>
       </c>
       <c r="J108" s="13" t="n">
-        <v>0.51</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1573.4</v>
+        <v>1536.7</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1569.2</v>
+        <v>1538</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1582.2</v>
+        <v>1615</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1522.4</v>
+        <v>1537.2</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1536.7</v>
+        <v>1586.2</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-36.7</v>
+        <v>49.5</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>-2.33</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1166.4</v>
+        <v>1164.1</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1172.5</v>
+        <v>1174</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1175.5</v>
+        <v>1200.6</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1157.7</v>
+        <v>1164.2</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1164.1</v>
+        <v>1177.6</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>-2.3</v>
+        <v>13.5</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>-0.2</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>557</v>
+        <v>558.15</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>557.4</v>
+        <v>560.7</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>560.7</v>
+        <v>585</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>550.6</v>
+        <v>560.05</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>558.15</v>
+        <v>582.15</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J111" s="13" t="n">
-        <v>0.21</v>
+        <v>24</v>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>4.3</v>
       </c>
     </row>
     <row r="112">
@@ -4539,24 +4539,24 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4100.8</v>
+        <v>4054.5</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>4085</v>
+        <v>3974</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4090</v>
+        <v>4021</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>4024</v>
+        <v>3900</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4054.5</v>
+        <v>4008.5</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-46.3</v>
-      </c>
-      <c r="J112" s="10" t="n">
+        <v>-46</v>
+      </c>
+      <c r="J112" s="13" t="n">
         <v>-1.13</v>
       </c>
     </row>
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>285.65</v>
+        <v>290.45</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>286.6</v>
+        <v>295</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>291.4</v>
+        <v>303</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>283.1</v>
+        <v>294.45</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>290.45</v>
+        <v>300.3</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J113" s="13" t="n">
-        <v>1.68</v>
+        <v>9.85</v>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v>3.39</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="10" t="n">
+      <c r="J114" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3706.7</v>
+        <v>3739.8</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3706.7</v>
+        <v>3747</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3756.1</v>
+        <v>3825.8</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3687.4</v>
+        <v>3714</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3739.8</v>
+        <v>3804.8</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="J115" s="13" t="n">
-        <v>0.89</v>
+        <v>65</v>
+      </c>
+      <c r="J115" s="10" t="n">
+        <v>1.74</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2348.8</v>
+        <v>2343.3</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2354</v>
+        <v>2362.3</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2364.6</v>
+        <v>2459</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2326.6</v>
+        <v>2350.4</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2343.3</v>
+        <v>2442.9</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-5.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>-0.23</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3106.5</v>
+        <v>3210.8</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3114</v>
+        <v>3245</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3222</v>
+        <v>3315.7</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3070.2</v>
+        <v>3243.5</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3210.8</v>
+        <v>3300.8</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>104.3</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>3.36</v>
+        <v>90</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>305.15</v>
+        <v>307.25</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>307.4</v>
+        <v>309.4</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>309.5</v>
+        <v>313.45</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>296.4</v>
+        <v>306.1</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>307.25</v>
+        <v>309.95</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J118" s="13" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.7</v>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>784.55</v>
+        <v>807.2</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>789.05</v>
+        <v>826.2</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>810.5</v>
+        <v>843.15</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>760.6</v>
+        <v>811.75</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>807.2</v>
+        <v>814.8</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>22.65</v>
-      </c>
-      <c r="J119" s="13" t="n">
-        <v>2.89</v>
+        <v>7.6</v>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13580</v>
+        <v>13426</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13560</v>
+        <v>13555</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13568</v>
+        <v>13762</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13360</v>
+        <v>13379</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13426</v>
+        <v>13722</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-154</v>
+        <v>296</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>-1.13</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="10" t="n">
+      <c r="J121" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2912.9</v>
+        <v>2902.5</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>2920</v>
+        <v>2939.8</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>2926</v>
+        <v>2989.4</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2867</v>
+        <v>2911</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>2902.5</v>
+        <v>2973.2</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>-10.4</v>
+        <v>70.7</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>-0.36</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>492.4</v>
+        <v>506.3</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>494.9</v>
+        <v>511</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>516.2</v>
+        <v>511.6</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>492.6</v>
+        <v>503.1</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>506.3</v>
+        <v>506.4</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="J123" s="13" t="n">
-        <v>2.82</v>
+        <v>0.1</v>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1606.7</v>
+        <v>1596.2</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1590</v>
+        <v>1604.9</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1605.8</v>
+        <v>1657</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1580</v>
+        <v>1604.9</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1596.2</v>
+        <v>1652.8</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-10.5</v>
+        <v>56.6</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>-0.65</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1135.4</v>
+        <v>1133.5</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1132</v>
+        <v>1141</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1137.8</v>
+        <v>1173</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1121</v>
+        <v>1141</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1133.5</v>
+        <v>1166.8</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-1.9</v>
+        <v>33.3</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>-0.17</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>120.21</v>
+        <v>120.24</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>120.21</v>
+        <v>121.81</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>121.11</v>
+        <v>128</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>118.41</v>
+        <v>121.51</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>120.24</v>
+        <v>127.41</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J126" s="13" t="n">
-        <v>0.02</v>
+        <v>7.17</v>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>5.96</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2276.6</v>
+        <v>2209.8</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2276.1</v>
+        <v>2244.7</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2298.2</v>
+        <v>2269.9</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2194.6</v>
+        <v>2191.2</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2209.8</v>
+        <v>2218.5</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-66.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>-2.93</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>129235</v>
+        <v>128270</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>130095</v>
+        <v>129540</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>130095</v>
+        <v>130750</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>128110</v>
+        <v>128720</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>128270</v>
+        <v>130335</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-965</v>
+        <v>2065</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>-0.75</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3487.7</v>
+        <v>3446.4</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3490</v>
+        <v>3480</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3499.9</v>
+        <v>3568.3</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3391.1</v>
+        <v>3456.3</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3446.4</v>
+        <v>3533.6</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-41.3</v>
+        <v>87.2</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>-1.18</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>407.8</v>
+        <v>413.6</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>409.8</v>
+        <v>418</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>418.6</v>
+        <v>420.95</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>406.2</v>
+        <v>405</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>413.6</v>
+        <v>406.55</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>5.8</v>
+        <v>-7.05</v>
       </c>
       <c r="J130" s="13" t="n">
-        <v>1.42</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>976.65</v>
+        <v>963.95</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>977</v>
+        <v>970.05</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>988.6</v>
+        <v>989</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>959</v>
+        <v>962.25</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>963.95</v>
+        <v>981.4</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-12.7</v>
+        <v>17.45</v>
       </c>
       <c r="J131" s="10" t="n">
-        <v>-1.3</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6796.5</v>
+        <v>7005</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>6810</v>
+        <v>7080</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>7020</v>
+        <v>7088</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6765</v>
+        <v>6978</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>7005</v>
+        <v>7043</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>208.5</v>
-      </c>
-      <c r="J132" s="13" t="n">
-        <v>3.07</v>
+        <v>38</v>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>0.54</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1457.1</v>
+        <v>1477.8</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1456</v>
+        <v>1485</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1480.4</v>
+        <v>1490</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1447.6</v>
+        <v>1468.2</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1477.8</v>
+        <v>1486.1</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="J133" s="13" t="n">
-        <v>1.42</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>89.09</v>
+        <v>88.83</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>89.64</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>87.95999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>88.83</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-0.26</v>
+        <v>0.35</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>-0.29</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>400.05</v>
+        <v>398.65</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>398.3</v>
+        <v>400</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>400.5</v>
+        <v>403</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>394.55</v>
+        <v>391.65</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>398.65</v>
+        <v>394.85</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>-0.35</v>
+        <v>-3.8</v>
+      </c>
+      <c r="J135" s="13" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1693.7</v>
+        <v>1666.3</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1691.1</v>
+        <v>1682.3</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1656.6</v>
+        <v>1655.6</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1666.3</v>
+        <v>1673.4</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-27.4</v>
+        <v>7.1</v>
       </c>
       <c r="J136" s="10" t="n">
-        <v>-1.62</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9730</v>
+        <v>9707</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9770</v>
+        <v>9794</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9860</v>
+        <v>9804</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9654.5</v>
+        <v>9650</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9707</v>
+        <v>9694.5</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-23</v>
-      </c>
-      <c r="J137" s="10" t="n">
-        <v>-0.24</v>
+        <v>-12.5</v>
+      </c>
+      <c r="J137" s="13" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>292.9</v>
+        <v>289.95</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>294.35</v>
+        <v>289.95</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>295.9</v>
+        <v>290.25</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>289.95</v>
+        <v>280.8</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="J138" s="10" t="n">
-        <v>-1.01</v>
+        <v>-9.15</v>
+      </c>
+      <c r="J138" s="13" t="n">
+        <v>-3.16</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>36955</v>
+        <v>37400</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37070</v>
+        <v>37295</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37500</v>
+        <v>37740</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>36770</v>
+        <v>37160</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37400</v>
+        <v>37540</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>445</v>
-      </c>
-      <c r="J139" s="13" t="n">
-        <v>1.2</v>
+        <v>140</v>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="10" t="n">
+      <c r="J140" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4788.1</v>
+        <v>4816.3</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>4770</v>
+        <v>4880</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>4858.7</v>
+        <v>5037.6</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4743.1</v>
+        <v>4850</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4816.3</v>
+        <v>5014</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v>0.59</v>
+        <v>197.7</v>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>276.7</v>
+        <v>282.55</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>280</v>
+        <v>284.9</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>286.8</v>
+        <v>285</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>270.85</v>
+        <v>278.5</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>282.55</v>
+        <v>283.3</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="J142" s="13" t="n">
-        <v>2.11</v>
+        <v>0.75</v>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>448.25</v>
+        <v>456.9</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>448.25</v>
+        <v>459.3</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>460.25</v>
+        <v>464.85</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>444</v>
+        <v>454.6</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>456.9</v>
+        <v>463.9</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>8.65</v>
-      </c>
-      <c r="J143" s="13" t="n">
-        <v>1.93</v>
+        <v>7</v>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1364.6</v>
+        <v>1364.2</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1365</v>
+        <v>1374.8</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1369</v>
+        <v>1426</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1347.7</v>
+        <v>1373</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1364.2</v>
+        <v>1421.5</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-0.4</v>
+        <v>57.3</v>
       </c>
       <c r="J144" s="10" t="n">
-        <v>-0.03</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3047.5</v>
+        <v>3014.3</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3028.7</v>
+        <v>3025</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3035</v>
+        <v>3094</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2992</v>
+        <v>3021.1</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3014.3</v>
+        <v>3071</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-33.2</v>
+        <v>56.7</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>-1.09</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>108.68</v>
+        <v>107.89</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>108.8</v>
+        <v>110.41</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>111.41</v>
+        <v>111.74</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>105.45</v>
+        <v>107.89</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>107.89</v>
+        <v>110.18</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-0.79</v>
+        <v>2.29</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>-0.73</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8344.5</v>
+        <v>8337</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8347.5</v>
+        <v>8400</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8374</v>
+        <v>8525</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8154</v>
+        <v>8355.5</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8337</v>
+        <v>8415.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-7.5</v>
+        <v>78.5</v>
       </c>
       <c r="J147" s="10" t="n">
-        <v>-0.09</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>319.05</v>
+        <v>319.45</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>318.9</v>
+        <v>320.05</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>321.3</v>
+        <v>321.5</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>315</v>
+        <v>314.6</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>319.45</v>
+        <v>315.95</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>0.4</v>
+        <v>-3.5</v>
       </c>
       <c r="J148" s="13" t="n">
-        <v>0.13</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1059.1</v>
+        <v>1063.1</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1055.5</v>
+        <v>1066</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1079</v>
+        <v>1081.9</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1055.1</v>
+        <v>1060</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1063.1</v>
+        <v>1068.9</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J149" s="13" t="n">
-        <v>0.38</v>
+        <v>5.8</v>
+      </c>
+      <c r="J149" s="10" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>330.2</v>
+        <v>332.95</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>330.3</v>
+        <v>336.1</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>335.7</v>
+        <v>342.15</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>326.15</v>
+        <v>331.4</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>332.95</v>
+        <v>335.85</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J150" s="13" t="n">
-        <v>0.83</v>
+        <v>2.9</v>
+      </c>
+      <c r="J150" s="10" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>353.5</v>
+        <v>356.4</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>353.5</v>
+        <v>358.9</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>357.8</v>
+        <v>361.1</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>351.15</v>
+        <v>351.85</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>356.4</v>
+        <v>359.1</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>0.82</v>
+        <v>2.7</v>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>0.76</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1463.1</v>
+        <v>1463.6</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1473.4</v>
+        <v>1473.3</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1450</v>
+        <v>1427.5</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1463.6</v>
+        <v>1437.9</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>0.5</v>
+        <v>-25.7</v>
       </c>
       <c r="J152" s="13" t="n">
-        <v>0.03</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>186.15</v>
+        <v>187.31</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>185.8</v>
+        <v>189</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>188.83</v>
+        <v>190.5</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>185.02</v>
+        <v>184.71</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>187.31</v>
+        <v>186.04</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>1.16</v>
+        <v>-1.27</v>
       </c>
       <c r="J153" s="13" t="n">
-        <v>0.62</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>644.8</v>
+        <v>645.65</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>645.95</v>
+        <v>651</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>646.9</v>
+        <v>660</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>638.4</v>
+        <v>643.15</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>645.65</v>
+        <v>649.65</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>0.13</v>
+        <v>4</v>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1820.1</v>
+        <v>1821.2</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1820</v>
+        <v>1839</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1835</v>
+        <v>1868.9</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1802.6</v>
+        <v>1825.9</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1821.2</v>
+        <v>1859</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J155" s="13" t="n">
-        <v>0.06</v>
+        <v>37.8</v>
+      </c>
+      <c r="J155" s="10" t="n">
+        <v>2.08</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1068.4</v>
+        <v>1059.9</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1060.6</v>
+        <v>1072</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1068.5</v>
+        <v>1101.1</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1049.4</v>
+        <v>1061.2</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1059.9</v>
+        <v>1096</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-8.5</v>
+        <v>36.1</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>-0.8</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>24740</v>
+        <v>24845</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>24600</v>
+        <v>25105</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>24990</v>
+        <v>25200</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>24405</v>
+        <v>24660</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>24845</v>
+        <v>24975</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>0.42</v>
+        <v>130</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>960.45</v>
+        <v>964.4</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>955.65</v>
+        <v>980</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>966.9</v>
+        <v>1007.45</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>937.3</v>
+        <v>976.05</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>964.4</v>
+        <v>1004.1</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J158" s="13" t="n">
-        <v>0.41</v>
+        <v>39.7</v>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>4.12</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3834.1</v>
+        <v>3846.6</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3851.2</v>
+        <v>3880</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3866.5</v>
+        <v>3885</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3809.5</v>
+        <v>3783</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3846.6</v>
+        <v>3841.8</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>12.5</v>
+        <v>-4.8</v>
       </c>
       <c r="J159" s="13" t="n">
-        <v>0.33</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2551.4</v>
+        <v>2522.8</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2553</v>
+        <v>2605</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2567.8</v>
+        <v>2762</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2495</v>
+        <v>2582.2</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2522.8</v>
+        <v>2719.6</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-28.6</v>
+        <v>196.8</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>-1.12</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1823.5</v>
+        <v>1820.8</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1828.5</v>
+        <v>1837</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1831.7</v>
+        <v>1857.8</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1798.6</v>
+        <v>1818.4</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1820.8</v>
+        <v>1850.2</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-2.7</v>
+        <v>29.4</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>-0.15</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>575.85</v>
+        <v>580.1</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>570.7</v>
+        <v>588</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>564</v>
+        <v>568.15</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>580.1</v>
+        <v>570.75</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>4.25</v>
+        <v>-9.35</v>
       </c>
       <c r="J162" s="13" t="n">
-        <v>0.74</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>477.35</v>
+        <v>451.4</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>480.85</v>
+        <v>455.95</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>480.85</v>
+        <v>459.55</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>449.1</v>
+        <v>439.5</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>451.4</v>
+        <v>450.1</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-25.95</v>
-      </c>
-      <c r="J163" s="10" t="n">
-        <v>-5.44</v>
+        <v>-1.3</v>
+      </c>
+      <c r="J163" s="13" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>805.75</v>
+        <v>801.45</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>790.1</v>
+        <v>804</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>816.9</v>
+        <v>830.5</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>778.2</v>
+        <v>802.2</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>801.45</v>
+        <v>815.95</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-4.3</v>
+        <v>14.5</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-0.53</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1569.6</v>
+        <v>1559</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1570</v>
+        <v>1579</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1572.9</v>
+        <v>1609.5</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1538.7</v>
+        <v>1557.1</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1559</v>
+        <v>1591</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-10.6</v>
+        <v>32</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>-0.68</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1160.4</v>
+        <v>1153.5</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1161.2</v>
+        <v>1160</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1166.8</v>
+        <v>1166.9</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1149</v>
+        <v>1138.9</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1153.5</v>
+        <v>1152.2</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="J166" s="10" t="n">
-        <v>-0.59</v>
+        <v>-1.3</v>
+      </c>
+      <c r="J166" s="13" t="n">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="10" t="n">
+      <c r="J167" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>441.4</v>
+        <v>442.65</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>441.05</v>
+        <v>444.5</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>445.75</v>
+        <v>446.3</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>436.65</v>
+        <v>439.5</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>442.65</v>
+        <v>443.25</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J168" s="13" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>212.24</v>
+        <v>211.32</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>212.2</v>
+        <v>214</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>212.34</v>
+        <v>216.73</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>209.45</v>
+        <v>212.42</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>211.32</v>
+        <v>215.47</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-0.92</v>
+        <v>4.15</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>-0.43</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2431.3</v>
+        <v>2427.3</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2430</v>
+        <v>2441.9</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2460.4</v>
+        <v>2471</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2412.2</v>
+        <v>2406.5</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2427.3</v>
+        <v>2435.4</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-4</v>
+        <v>8.1</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>-0.16</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1471.6</v>
+        <v>1452.2</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1465</v>
+        <v>1467.9</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1483.8</v>
+        <v>1480.6</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1447.1</v>
+        <v>1455.4</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1452.2</v>
+        <v>1466.7</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-19.4</v>
+        <v>14.5</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>-1.32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2906</v>
+        <v>2932.4</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2917.1</v>
+        <v>2947.1</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2950</v>
+        <v>2964.5</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2895.6</v>
+        <v>2872.8</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2932.4</v>
+        <v>2917</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>26.4</v>
+        <v>-15.4</v>
       </c>
       <c r="J172" s="13" t="n">
-        <v>0.91</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4363</v>
+        <v>4373.6</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4355</v>
+        <v>4397.5</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4397</v>
+        <v>4441.1</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4330.3</v>
+        <v>4297.1</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4373.6</v>
+        <v>4359.6</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>10.6</v>
+        <v>-14</v>
       </c>
       <c r="J173" s="13" t="n">
-        <v>0.24</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4251.8</v>
+        <v>4275.1</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4251.8</v>
+        <v>4299.9</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4300</v>
+        <v>4436.8</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4236.4</v>
+        <v>4274</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4275.1</v>
+        <v>4358.3</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>0.55</v>
+        <v>83.2</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>1.95</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1724</v>
+        <v>1734.7</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1728.8</v>
+        <v>1757</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1743.8</v>
+        <v>1757</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1710.8</v>
+        <v>1713.5</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1734.7</v>
+        <v>1734</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>10.7</v>
+        <v>-0.7</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>0.62</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4158.5</v>
+        <v>4135.4</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4150.1</v>
+        <v>4157.9</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4158.5</v>
+        <v>4324.5</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4075.6</v>
+        <v>4156.5</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4135.4</v>
+        <v>4289.8</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-23.1</v>
+        <v>154.4</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-0.5600000000000001</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3495.5</v>
+        <v>3534.4</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3499.9</v>
+        <v>3575</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3544</v>
+        <v>3625</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3462.8</v>
+        <v>3514.6</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3534.4</v>
+        <v>3617.9</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>1.11</v>
+        <v>83.5</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1463.1</v>
+        <v>1453.8</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1466.4</v>
+        <v>1428.3</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1469.8</v>
+        <v>1428.3</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1441</v>
+        <v>1382</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1453.8</v>
+        <v>1412.8</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v>-0.64</v>
+        <v>-41</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>-2.82</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11758</v>
+        <v>11963</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11671</v>
+        <v>12022</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11987</v>
+        <v>12141</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11624</v>
+        <v>11942</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11963</v>
+        <v>12093</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>205</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>1.74</v>
+        <v>130</v>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>163.77</v>
+        <v>163.74</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>163.5</v>
+        <v>165.76</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>164.4</v>
+        <v>169.75</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>161.44</v>
+        <v>164.83</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>163.74</v>
+        <v>168.75</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-0.03</v>
+        <v>5.01</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>-0.02</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>643.35</v>
+        <v>642.05</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>648.9</v>
+        <v>663.1</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>638.85</v>
+        <v>642.3</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>642.05</v>
+        <v>660</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-1.3</v>
+        <v>17.95</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>-0.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>294.65</v>
+        <v>303.9</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>296.95</v>
+        <v>310</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>305.9</v>
+        <v>318</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>292</v>
+        <v>308.6</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>303.9</v>
+        <v>316.4</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="J182" s="13" t="n">
-        <v>3.14</v>
+        <v>12.5</v>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>4.11</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1454.2</v>
+        <v>1375.9</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1452</v>
+        <v>1380</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1453</v>
+        <v>1385.9</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1360</v>
+        <v>1361.5</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1375.9</v>
+        <v>1379.6</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-78.3</v>
+        <v>3.7</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>-5.38</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>200.75</v>
+        <v>199.78</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>200</v>
+        <v>200.51</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>202.3</v>
+        <v>201.13</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>199.6</v>
+        <v>198.25</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>199.78</v>
+        <v>199.12</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="J184" s="10" t="n">
-        <v>-0.48</v>
+        <v>-0.66</v>
+      </c>
+      <c r="J184" s="13" t="n">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="10" t="n">
+      <c r="J185" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>902.35</v>
+        <v>912.25</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>897.3</v>
+        <v>919.1</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>918</v>
+        <v>943.9</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>897</v>
+        <v>915</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>912.25</v>
+        <v>938.8</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J186" s="13" t="n">
-        <v>1.1</v>
+        <v>26.55</v>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v>2.91</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  05-May-2026 06:28 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  06-May-2026 02:47 PM</t>
         </is>
       </c>
     </row>
@@ -7256,14 +7256,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05-May-2026 06:28 PM</t>
+          <t>06-May-2026 02:47 PM</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>184</v>
       </c>
       <c r="C2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 06-May-2026 02:47 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 06-May-2026 03:26 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>06-May-2026 02:47 PM</t>
+          <t>06-May-2026 03:26 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  06-May-2026 02:47 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  06-May-2026 03:26 PM</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  06-May-2026 02:47 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  06-May-2026 03:26 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06-May-2026 02:47 PM</t>
+          <t>06-May-2026 03:26 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 06-May-2026 03:26 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 07-May-2026 03:28 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>06-May-2026 03:26 PM</t>
+          <t>07-May-2026 03:28 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  06-May-2026 03:26 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  07-May-2026 03:28 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>488</v>
+        <v>497.85</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>492.2</v>
+        <v>496.75</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>506.2</v>
+        <v>498.2</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>497.85</v>
+        <v>488.15</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>9.85</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>2.02</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7328</v>
+        <v>7182.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7389</v>
+        <v>7183</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7389</v>
+        <v>7279.5</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7135</v>
+        <v>7000</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7182.5</v>
+        <v>7188</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-145.5</v>
+        <v>5.5</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>-1.99</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>25305</v>
+        <v>26300</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>25440</v>
+        <v>26550</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>26450</v>
+        <v>27100</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>25430</v>
+        <v>26430</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26300</v>
+        <v>26700</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>995</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>3.93</v>
+        <v>400</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>360.85</v>
+        <v>369.3</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>365</v>
+        <v>370.85</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>372.5</v>
+        <v>375.95</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>364.5</v>
+        <v>368.1</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>369.3</v>
+        <v>369</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>8.449999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>2.34</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>63.99</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>64.45999999999999</v>
+        <v>66.48999999999999</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>66.58</v>
+        <v>69.09</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>63.55</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>66.20999999999999</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>3.47</v>
+        <v>1.58</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>2.39</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1392.6</v>
+        <v>1414</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1397.6</v>
+        <v>1421.6</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1425.9</v>
+        <v>1435</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1392.1</v>
+        <v>1409.2</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1414</v>
+        <v>1414.6</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>1.54</v>
+        <v>0.6</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2462</v>
+        <v>2540.3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2475.5</v>
+        <v>2540.3</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2546.5</v>
+        <v>2549.9</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2472.2</v>
+        <v>2506.2</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2540.3</v>
+        <v>2513.7</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>78.3</v>
+        <v>-26.6</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>3.18</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1725</v>
+        <v>1748.3</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1750</v>
+        <v>1748.3</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1762.4</v>
+        <v>1755.9</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1718.6</v>
+        <v>1708</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1748.3</v>
+        <v>1732.8</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>23.3</v>
+        <v>-15.5</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>1.35</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5403</v>
+        <v>5557</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5405</v>
+        <v>5570</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5635.5</v>
+        <v>5608</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5404</v>
+        <v>5529.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5557</v>
+        <v>5590.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>154</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>2.85</v>
+        <v>33.5</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>433.1</v>
+        <v>446.9</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>438.55</v>
+        <v>446.5</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>449.6</v>
+        <v>454.2</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>435.8</v>
+        <v>445.1</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>446.9</v>
+        <v>450.65</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>3.19</v>
+        <v>3.75</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>314.4</v>
+        <v>316.85</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>316.75</v>
+        <v>318.4</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>318.6</v>
+        <v>324.7</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>310.6</v>
+        <v>315.55</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>316.85</v>
+        <v>322.6</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>0.78</v>
+        <v>5.75</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>1.81</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1870.6</v>
+        <v>1914.7</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1899.9</v>
+        <v>1932.7</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1921</v>
+        <v>1983</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1869</v>
+        <v>1925.7</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1914.7</v>
+        <v>1973.7</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>2.36</v>
+        <v>59</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>3.08</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7772</v>
+        <v>7760.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7810.5</v>
+        <v>7760.5</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7815</v>
+        <v>7855</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7742.5</v>
+        <v>7744</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7760.5</v>
+        <v>7837</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-11.5</v>
+        <v>76.5</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>-0.15</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>402.6</v>
+        <v>412.65</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>405.5</v>
+        <v>414</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>418.6</v>
+        <v>418.85</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>403.7</v>
+        <v>409.2</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>412.65</v>
+        <v>410.05</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>10.05</v>
+        <v>-2.6</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>2.5</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>160.25</v>
+        <v>167.8</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>163.5</v>
+        <v>168.99</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>169.11</v>
+        <v>172.8</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>160.5</v>
+        <v>166.41</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>167.8</v>
+        <v>170.78</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>4.71</v>
+        <v>2.98</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2430</v>
+        <v>2519</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2460</v>
+        <v>2534.6</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2529</v>
+        <v>2555.8</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2440.4</v>
+        <v>2511.3</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2519</v>
+        <v>2530.6</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>89</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>3.66</v>
+        <v>11.6</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>0.46</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1531.6</v>
+        <v>1576.1</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1545</v>
+        <v>1577.9</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1588.7</v>
+        <v>1597.8</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1533.1</v>
+        <v>1561.9</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1576.1</v>
+        <v>1569.1</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>44.5</v>
+        <v>-7</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>2.91</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>647.2</v>
+        <v>651</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>641</v>
+        <v>640.5</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>651</v>
+        <v>644.25</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>3.8</v>
+        <v>-6.75</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>0.59</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6911</v>
+        <v>7108</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6956</v>
+        <v>7171</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7150</v>
+        <v>7180</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6920.5</v>
+        <v>6986</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7108</v>
+        <v>7033.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>197</v>
+        <v>-74.5</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>2.85</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1007.1</v>
+        <v>1024</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1015</v>
+        <v>1024.9</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1028.4</v>
+        <v>1041</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1002</v>
+        <v>1019.3</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1024</v>
+        <v>1032.4</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>1.68</v>
+        <v>8.4</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>0.82</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1428.1</v>
+        <v>1484</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1431</v>
+        <v>1475.1</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1489.7</v>
+        <v>1498.5</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1426.1</v>
+        <v>1469.3</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1484</v>
+        <v>1478.7</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>55.9</v>
+        <v>-5.3</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>3.91</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1259.7</v>
+        <v>1294.2</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1275</v>
+        <v>1299</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1301</v>
+        <v>1308.1</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1255.2</v>
+        <v>1281.2</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1294.2</v>
+        <v>1292.7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>34.5</v>
+        <v>-1.5</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>2.74</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>10046</v>
+        <v>10319</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10180</v>
+        <v>10582</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10390</v>
+        <v>10740</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10141</v>
+        <v>10324.5</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>10319</v>
+        <v>10605</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>273</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>2.72</v>
+        <v>286</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>2.77</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1794.6</v>
+        <v>1836.1</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1810</v>
+        <v>1849.6</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1838.8</v>
+        <v>1849.6</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1798.1</v>
+        <v>1816.6</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1836.1</v>
+        <v>1824.5</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>41.5</v>
+        <v>-11.6</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>2.31</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>958.6</v>
+        <v>980.75</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>965</v>
+        <v>992.25</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>984</v>
+        <v>992.25</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>980.75</v>
+        <v>972.75</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>22.15</v>
+        <v>-8</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>2.31</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2172</v>
+        <v>2230.3</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2193.5</v>
+        <v>2255</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2238.6</v>
+        <v>2283</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2188</v>
+        <v>2228.7</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2230.3</v>
+        <v>2258.4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>2.68</v>
+        <v>28.1</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>531</v>
+        <v>524.85</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>536.75</v>
+        <v>530</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>522.6</v>
+        <v>521.2</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>524.85</v>
+        <v>525.5</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-6.15</v>
+        <v>0.65</v>
       </c>
       <c r="J29" s="13" t="n">
-        <v>-1.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>206.44</v>
+        <v>208.88</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>209</v>
+        <v>208.8</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>210.63</v>
+        <v>209.39</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>205.12</v>
+        <v>206</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>208.88</v>
+        <v>207.63</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>2.44</v>
+        <v>-1.25</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>1.18</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>263.4</v>
+        <v>270.3</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>268.7</v>
+        <v>271.25</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>271.4</v>
+        <v>271.9</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>262.8</v>
+        <v>267.1</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>270.3</v>
+        <v>270.35</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>2.62</v>
+        <v>0.05</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>433.35</v>
+        <v>438.2</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>437</v>
+        <v>439.9</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>439.65</v>
+        <v>441</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>435.15</v>
+        <v>433.5</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>438.2</v>
+        <v>439.45</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>470.6</v>
+        <v>478.45</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>474.65</v>
+        <v>488</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>480</v>
+        <v>498.95</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>470.3</v>
+        <v>484.6</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>478.45</v>
+        <v>488.25</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>1.67</v>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1806.1</v>
+        <v>1833.7</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1817</v>
+        <v>1835</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1841.5</v>
+        <v>1843.9</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1813.8</v>
+        <v>1821.2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1833.7</v>
+        <v>1826.6</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>27.6</v>
+        <v>-7.1</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1.53</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>374.95</v>
+        <v>385.95</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>378</v>
+        <v>385.5</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>387.5</v>
+        <v>408.35</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>368.4</v>
+        <v>383.45</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>385.95</v>
+        <v>406.45</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v>2.93</v>
+        <v>20.5</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>5.31</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>368.25</v>
+        <v>380.6</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>372.8</v>
+        <v>384</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>384.5</v>
+        <v>386.3</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>371.05</v>
+        <v>379.6</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>380.6</v>
+        <v>382.25</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>12.35</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>3.35</v>
+        <v>1.65</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>35870</v>
+        <v>36645</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>36000</v>
+        <v>36880</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>36750</v>
+        <v>38380</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>35795</v>
+        <v>36645</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>36645</v>
+        <v>37895</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>775</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>2.16</v>
+        <v>1250</v>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v>3.41</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>298.5</v>
+        <v>314.05</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>304.7</v>
+        <v>315.7</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>316.6</v>
+        <v>316.95</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>301.85</v>
+        <v>305.1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>314.05</v>
+        <v>307.6</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>15.55</v>
+        <v>-6.45</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>5.21</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5834.5</v>
+        <v>5783</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5878</v>
+        <v>5798</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5880</v>
+        <v>5891.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5764</v>
+        <v>5733.5</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5783</v>
+        <v>5814</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-51.5</v>
+        <v>31</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>-0.88</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>370</v>
+        <v>372.5</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>379</v>
+        <v>381.95</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>371.4</v>
+        <v>359.35</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>372.5</v>
+        <v>362.2</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>2.5</v>
+        <v>-10.3</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>0.68</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>134.31</v>
+        <v>138.04</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>137.23</v>
+        <v>138.8</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>138.36</v>
+        <v>138.9</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>134.51</v>
+        <v>135.54</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>138.04</v>
+        <v>135.93</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>3.73</v>
+        <v>-2.11</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>2.78</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>874.45</v>
+        <v>903.3</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>884</v>
+        <v>908.7</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>910</v>
+        <v>909.55</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>877.1</v>
+        <v>883.7</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>903.3</v>
+        <v>886.3</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>28.85</v>
+        <v>-17</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>3.3</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>442.55</v>
+        <v>452.65</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>442.15</v>
+        <v>455.8</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>453.7</v>
+        <v>456.5</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>442.15</v>
+        <v>450.25</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>452.65</v>
+        <v>453.95</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>2.28</v>
+        <v>1.3</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>0.29</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1657.4</v>
+        <v>1711.9</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1681.2</v>
+        <v>1725</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1724</v>
+        <v>1734.8</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1678.9</v>
+        <v>1677.8</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1711.9</v>
+        <v>1689.2</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>54.5</v>
+        <v>-22.7</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>3.29</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1333.7</v>
+        <v>1364.4</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1340</v>
+        <v>1370</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1372</v>
+        <v>1379.5</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1333.1</v>
+        <v>1360.1</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1364.4</v>
+        <v>1362.3</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>30.7</v>
+        <v>-2.1</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>2.3</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>472.6</v>
+        <v>470.2</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>473.85</v>
+        <v>470.2</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>477.5</v>
+        <v>472.85</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>468.05</v>
+        <v>456.1</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>470.2</v>
+        <v>466.65</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>-0.51</v>
+        <v>-3.55</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1168.8</v>
+        <v>1280.4</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1261.2</v>
+        <v>1294.9</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1295.8</v>
+        <v>1312.6</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1246.9</v>
+        <v>1277.7</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1280.4</v>
+        <v>1285.3</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>111.6</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>9.550000000000001</v>
+        <v>4.9</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>0.38</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2178.9</v>
+        <v>2157.1</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2198</v>
+        <v>2172</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2198</v>
+        <v>2185</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2151.9</v>
+        <v>2144.9</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2157.1</v>
+        <v>2167</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-21.8</v>
+        <v>9.9</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>-1</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>518.05</v>
+        <v>524.2</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>527</v>
+        <v>528.9</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>518.1</v>
+        <v>523</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>524.2</v>
+        <v>526.7</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>1.19</v>
+        <v>2.5</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2011.4</v>
+        <v>2018.1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>2021.5</v>
+        <v>2035</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2029</v>
+        <v>2035</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1991.1</v>
+        <v>1931.5</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>2018.1</v>
+        <v>1965</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>6.7</v>
+        <v>-53.1</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>0.33</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>275.5</v>
+        <v>284.05</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>277</v>
+        <v>284.6</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>286.9</v>
+        <v>292.95</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>276.1</v>
+        <v>283.25</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>284.05</v>
+        <v>290.75</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v>3.1</v>
+        <v>6.7</v>
+      </c>
+      <c r="J51" s="13" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>269.3</v>
+        <v>273</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>275</v>
+        <v>272.95</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>282.5</v>
+        <v>273.9</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>268.35</v>
+        <v>268.6</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>273</v>
+        <v>270.85</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>3.7</v>
+        <v>-2.15</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>1.37</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5260</v>
+        <v>5324.5</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5331.5</v>
+        <v>5352.5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5355.5</v>
+        <v>5424</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5230.5</v>
+        <v>5317.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5324.5</v>
+        <v>5403</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J53" s="10" t="n">
-        <v>1.23</v>
+        <v>78.5</v>
+      </c>
+      <c r="J53" s="13" t="n">
+        <v>1.47</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>460.55</v>
+        <v>466.25</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>465</v>
+        <v>469.35</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>468</v>
+        <v>474.5</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>458.6</v>
+        <v>461.1</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>466.25</v>
+        <v>470</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>1.24</v>
+        <v>3.75</v>
+      </c>
+      <c r="J54" s="13" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1968.1</v>
+        <v>1974.6</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1968.1</v>
+        <v>1989.5</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1993.5</v>
+        <v>1993.9</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1939.2</v>
+        <v>1959.5</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1974.6</v>
+        <v>1974.3</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>6.5</v>
+        <v>-0.3</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>0.33</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1771.3</v>
+        <v>1821.6</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1785</v>
+        <v>1825</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1833.8</v>
+        <v>1860</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1767</v>
+        <v>1812.6</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1821.6</v>
+        <v>1854.4</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="J56" s="10" t="n">
-        <v>2.84</v>
+        <v>32.8</v>
+      </c>
+      <c r="J56" s="13" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>70.43000000000001</v>
+        <v>78.92</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>72.78</v>
+        <v>79.75</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>81.2</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>68.16</v>
+        <v>78.19</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>78.92</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="J57" s="10" t="n">
-        <v>12.05</v>
+        <v>0.9</v>
+      </c>
+      <c r="J57" s="13" t="n">
+        <v>1.14</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6651</v>
+        <v>6702</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6690</v>
+        <v>6705</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6765.5</v>
+        <v>6780</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6615.5</v>
+        <v>6683</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6702</v>
+        <v>6702.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11253</v>
+        <v>11299</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>11400</v>
+        <v>11350</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11405</v>
+        <v>11395</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>11152</v>
+        <v>11006</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>11299</v>
+        <v>11048</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>46</v>
+        <v>-251</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>0.41</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>597.3</v>
+        <v>609.6</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>600.05</v>
+        <v>615</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>611.8</v>
+        <v>620</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>594.45</v>
+        <v>607.75</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>609.6</v>
+        <v>618.85</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>2.06</v>
+        <v>9.25</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>1.52</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1271.2</v>
+        <v>1311</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1282</v>
+        <v>1309.1</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1328.6</v>
+        <v>1315.7</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1277.1</v>
+        <v>1297.3</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1311</v>
+        <v>1307.6</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>39.8</v>
+        <v>-3.4</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>3.13</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7301.5</v>
+        <v>7310.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7370</v>
+        <v>7360.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7392</v>
+        <v>7471.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7175.5</v>
+        <v>7310.5</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7310.5</v>
+        <v>7327.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>0.12</v>
+        <v>17</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>0.23</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3207.5</v>
+        <v>3317.1</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3233</v>
+        <v>3335</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3342</v>
+        <v>3408</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3220.3</v>
+        <v>3300</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3317.1</v>
+        <v>3345.9</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>109.6</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>3.42</v>
+        <v>28.8</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>361.15</v>
+        <v>351.7</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>365.7</v>
+        <v>352</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>366.2</v>
+        <v>365.6</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>340.25</v>
+        <v>342</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>351.7</v>
+        <v>364.45</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-9.449999999999999</v>
+        <v>12.75</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>-2.62</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>292.6</v>
+        <v>293</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>295.25</v>
+        <v>294.5</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>296.45</v>
+        <v>297.75</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>288.85</v>
+        <v>290</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>293</v>
+        <v>297.05</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J65" s="10" t="n">
-        <v>0.14</v>
+        <v>4.05</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>1.38</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>163.7</v>
+        <v>165.68</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>164.24</v>
+        <v>165.9</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>165.95</v>
+        <v>167.85</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>163.75</v>
+        <v>165.9</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>165.68</v>
+        <v>167.26</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>0.95</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2417.9</v>
+        <v>2377.6</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2435</v>
+        <v>2390</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2440</v>
+        <v>2404</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2354.9</v>
+        <v>2355.7</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2377.6</v>
+        <v>2371.6</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-40.3</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>-1.67</v>
+        <v>-6</v>
+      </c>
+      <c r="J67" s="10" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="J68" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>483.2</v>
+        <v>498.35</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>485.55</v>
+        <v>502</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>485.55</v>
+        <v>495</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>498.35</v>
+        <v>501.15</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>15.15</v>
-      </c>
-      <c r="J69" s="10" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1101.5</v>
+        <v>1094.1</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1122</v>
+        <v>1064.7</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1122</v>
+        <v>1064.7</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1083.5</v>
+        <v>1034</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1094.1</v>
+        <v>1036.6</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="J70" s="13" t="n">
-        <v>-0.67</v>
+        <v>-57.5</v>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v>-5.26</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1809.5</v>
+        <v>1867.2</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1819.1</v>
+        <v>1870</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1870</v>
+        <v>1890</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1812.7</v>
+        <v>1835.6</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1867.2</v>
+        <v>1878.6</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>3.19</v>
+        <v>11.4</v>
+      </c>
+      <c r="J71" s="13" t="n">
+        <v>0.61</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>711.8</v>
+        <v>736</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>714.5</v>
+        <v>737.1</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>755.1</v>
+        <v>752.7</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>710</v>
+        <v>732.15</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>736</v>
+        <v>743.5</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2871.5</v>
+        <v>2914.8</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2885.5</v>
+        <v>2902.3</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2923.3</v>
+        <v>2975</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2872.3</v>
+        <v>2900</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2914.8</v>
+        <v>2960.6</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="J73" s="10" t="n">
-        <v>1.51</v>
+        <v>45.8</v>
+      </c>
+      <c r="J73" s="13" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>388.25</v>
+        <v>397.55</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>391.4</v>
+        <v>400</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>387.2</v>
+        <v>397.45</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>397.55</v>
+        <v>408.95</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J74" s="10" t="n">
-        <v>2.4</v>
+        <v>11.4</v>
+      </c>
+      <c r="J74" s="13" t="n">
+        <v>2.87</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4610.4</v>
+        <v>4626.9</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4628.9</v>
+        <v>4647.8</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4671.5</v>
+        <v>4796</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4610</v>
+        <v>4628.1</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4626.9</v>
+        <v>4782.1</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J75" s="10" t="n">
-        <v>0.36</v>
+        <v>155.2</v>
+      </c>
+      <c r="J75" s="13" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1239.6</v>
+        <v>1257.3</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1251</v>
+        <v>1260</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1259.8</v>
+        <v>1276.7</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1241.2</v>
+        <v>1254.1</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1257.3</v>
+        <v>1268.9</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>1.43</v>
+        <v>11.6</v>
+      </c>
+      <c r="J76" s="13" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1200.2</v>
+        <v>1189.1</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1208</v>
+        <v>1195</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1212</v>
+        <v>1196</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1186.4</v>
+        <v>1181.1</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1189.1</v>
+        <v>1183.4</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>-0.92</v>
+        <v>-5.7</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2806.3</v>
+        <v>2815.9</v>
       </c>
       <c r="E78" s="12" t="n">
         <v>2830</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2866</v>
+        <v>2854.9</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2807.4</v>
+        <v>2780</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2815.9</v>
+        <v>2834.6</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>0.34</v>
+        <v>18.7</v>
+      </c>
+      <c r="J78" s="13" t="n">
+        <v>0.66</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>772.3</v>
+        <v>796.55</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>775.15</v>
+        <v>794</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>798.95</v>
+        <v>801.55</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>773.5</v>
+        <v>788.55</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>796.55</v>
+        <v>796.05</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>24.25</v>
+        <v>-0.5</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>3.14</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>594.1</v>
+        <v>606.35</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>597.9</v>
+        <v>611</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>612.6</v>
+        <v>629.3</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>594.55</v>
+        <v>608.85</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>606.35</v>
+        <v>625.4</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>2.06</v>
+        <v>19.05</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>3.14</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5109</v>
+        <v>5170</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5240</v>
+        <v>5235</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5281</v>
+        <v>5458.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>4950</v>
+        <v>5189.5</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5170</v>
+        <v>5343</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>61</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>1.19</v>
+        <v>173</v>
+      </c>
+      <c r="J81" s="13" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1054.7</v>
+        <v>1045.8</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1067.8</v>
+        <v>1048</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1073.7</v>
+        <v>1060.9</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1042.4</v>
+        <v>1036.6</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1045.8</v>
+        <v>1055.7</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-8.9</v>
+        <v>9.9</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>-0.84</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>532.05</v>
+        <v>550.5</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>553.5</v>
+        <v>584</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>540.7</v>
+        <v>556</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>550.5</v>
+        <v>568.6</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="J83" s="10" t="n">
-        <v>3.47</v>
+        <v>18.1</v>
+      </c>
+      <c r="J83" s="13" t="n">
+        <v>3.29</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>373.9</v>
+        <v>399.2</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>379</v>
+        <v>399.4</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>402.4</v>
+        <v>404.25</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>377.4</v>
+        <v>387</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>399.2</v>
+        <v>396.5</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>25.3</v>
+        <v>-2.7</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>6.77</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2327.4</v>
+        <v>2317.1</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2330</v>
+        <v>2310</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2339.4</v>
+        <v>2327.9</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2288.3</v>
+        <v>2268.1</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2317.1</v>
+        <v>2272.2</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>-0.44</v>
+        <v>-44.9</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>30685</v>
+        <v>30180</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>31210</v>
+        <v>30310</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>31210</v>
+        <v>30970</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>30000</v>
+        <v>30255</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>30180</v>
+        <v>30605</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-505</v>
+        <v>425</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>-1.65</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>68.75</v>
+        <v>69.59</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>69.5</v>
+        <v>69.91</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>70.69</v>
+        <v>71</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>68.40000000000001</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>69.59</v>
+        <v>70.39</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J87" s="10" t="n">
-        <v>1.22</v>
+        <v>0.8</v>
+      </c>
+      <c r="J87" s="13" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>127.62</v>
+        <v>129.8</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>129.07</v>
+        <v>130</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>129.98</v>
+        <v>134.15</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>128.34</v>
+        <v>129.51</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>129.8</v>
+        <v>133.81</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v>1.71</v>
+        <v>4.01</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>3.09</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>166.24</v>
+        <v>169.46</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>168</v>
+        <v>170.8</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>170.19</v>
+        <v>171.84</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>166.2</v>
+        <v>168.95</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>169.46</v>
+        <v>169.84</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="J89" s="10" t="n">
-        <v>1.94</v>
+        <v>0.38</v>
+      </c>
+      <c r="J89" s="13" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>647.8</v>
+        <v>666.15</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>652</v>
+        <v>668</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>669</v>
+        <v>675.45</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>651</v>
+        <v>664.4</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>666.15</v>
+        <v>669.1</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="J90" s="10" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
+      </c>
+      <c r="J90" s="13" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2052.9</v>
+        <v>2056.9</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2066.9</v>
+        <v>2068.5</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2068.8</v>
+        <v>2105.4</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2025.3</v>
+        <v>2062.2</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2056.9</v>
+        <v>2091</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" s="10" t="n">
-        <v>0.19</v>
+        <v>34.1</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>1.66</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4238.4</v>
+        <v>4520.2</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4320</v>
+        <v>4530</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4565.6</v>
+        <v>4560</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4315.6</v>
+        <v>4455.1</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4520.2</v>
+        <v>4506.9</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>281.8</v>
+        <v>-13.3</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>6.65</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>910.7</v>
+        <v>946.75</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>920.4</v>
+        <v>948.25</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>949.75</v>
+        <v>951.65</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>917.95</v>
+        <v>934.1</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>946.75</v>
+        <v>946.95</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>36.05</v>
-      </c>
-      <c r="J93" s="10" t="n">
-        <v>3.96</v>
+        <v>0.2</v>
+      </c>
+      <c r="J93" s="13" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>402.7</v>
+        <v>408.3</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>406.15</v>
+        <v>410.45</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>412.9</v>
+        <v>411.8</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>404.45</v>
+        <v>399.6</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>408.3</v>
+        <v>402.9</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>5.6</v>
+        <v>-5.4</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>1.39</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1178.1</v>
+        <v>1167.2</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1187</v>
+        <v>1173</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1191.5</v>
+        <v>1175.4</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1164.1</v>
+        <v>1159.2</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1167.2</v>
+        <v>1162.7</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="J95" s="13" t="n">
-        <v>-0.93</v>
+        <v>-4.5</v>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>142.14</v>
+        <v>148.21</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>143.5</v>
+        <v>148.9</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>148.75</v>
+        <v>149.3</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>143.22</v>
+        <v>145.13</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>148.21</v>
+        <v>146.89</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>6.07</v>
+        <v>-1.32</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>4.27</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1541.8</v>
+        <v>1564.4</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1548</v>
+        <v>1572.2</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1581</v>
+        <v>1590.4</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1542</v>
+        <v>1555.1</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1564.4</v>
+        <v>1560.1</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>22.6</v>
+        <v>-4.3</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>1.47</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>569.1</v>
+        <v>572.75</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>574.5</v>
+        <v>575</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>576.7</v>
+        <v>578.05</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>566.05</v>
+        <v>567</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>572.75</v>
+        <v>568.5</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>3.65</v>
+        <v>-4.25</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>0.64</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
+        <v>310.7</v>
+      </c>
+      <c r="E99" s="9" t="n">
         <v>311.45</v>
       </c>
-      <c r="E99" s="9" t="n">
-        <v>312.8</v>
-      </c>
       <c r="F99" s="9" t="n">
-        <v>313.6</v>
+        <v>311.65</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>309.25</v>
+        <v>307</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>310.7</v>
+        <v>307.4</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="J99" s="13" t="n">
-        <v>-0.24</v>
+        <v>-3.3</v>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1261.2</v>
+        <v>1264.3</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1283.6</v>
+        <v>1284.4</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1250</v>
+        <v>1254.2</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1264.3</v>
+        <v>1258.2</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>3.1</v>
+        <v>-6.1</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>0.25</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5286.5</v>
+        <v>5521.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5340</v>
+        <v>5570</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5556</v>
+        <v>5740</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5302.5</v>
+        <v>5519</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5521.5</v>
+        <v>5626</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>235</v>
-      </c>
-      <c r="J101" s="10" t="n">
-        <v>4.45</v>
+        <v>104.5</v>
+      </c>
+      <c r="J101" s="13" t="n">
+        <v>1.89</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>779.4</v>
+        <v>766.3</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>781.95</v>
+        <v>767.15</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>787.4</v>
+        <v>773.75</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>760.05</v>
+        <v>763</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>766.3</v>
+        <v>766.6</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-13.1</v>
+        <v>0.3</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>-1.68</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>561.95</v>
+        <v>567.9</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>567.6</v>
+        <v>570</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>571.45</v>
+        <v>578.9</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>561.3</v>
+        <v>567.85</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>567.9</v>
+        <v>575.9</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>1.06</v>
+        <v>8</v>
+      </c>
+      <c r="J103" s="13" t="n">
+        <v>1.41</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1252.4</v>
+        <v>1273.3</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1262.5</v>
+        <v>1272.1</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1278.6</v>
+        <v>1293.6</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1253</v>
+        <v>1268.6</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1273.3</v>
+        <v>1283.4</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>1.67</v>
+        <v>10.1</v>
+      </c>
+      <c r="J104" s="13" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>465.35</v>
+        <v>471.25</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>469</v>
+        <v>473.05</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>472.7</v>
+        <v>483.3</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>461</v>
+        <v>467.25</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>471.25</v>
+        <v>479</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>1.27</v>
+        <v>7.75</v>
+      </c>
+      <c r="J105" s="13" t="n">
+        <v>1.64</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1062.4</v>
+        <v>1110.8</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1080</v>
+        <v>1118.9</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1115</v>
+        <v>1124.4</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1077.9</v>
+        <v>1090.5</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1110.8</v>
+        <v>1098.8</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>48.4</v>
+        <v>-12</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>4.56</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>371.35</v>
+        <v>376.6</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>374</v>
+        <v>376.1</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>380</v>
+        <v>382.45</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>365.65</v>
+        <v>374.3</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>376.6</v>
+        <v>379.4</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="J107" s="10" t="n">
-        <v>1.41</v>
+        <v>2.8</v>
+      </c>
+      <c r="J107" s="13" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>772.5</v>
+        <v>748.6</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>783.95</v>
+        <v>748.55</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>795.3</v>
+        <v>748.55</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>722.5</v>
+        <v>709.2</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>748.6</v>
+        <v>722.65</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-23.9</v>
-      </c>
-      <c r="J108" s="13" t="n">
-        <v>-3.09</v>
+        <v>-25.95</v>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>-3.47</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1536.7</v>
+        <v>1586.2</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1538</v>
+        <v>1593.9</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1615</v>
+        <v>1621</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1537.2</v>
+        <v>1545</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1586.2</v>
+        <v>1565.5</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>49.5</v>
+        <v>-20.7</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>3.22</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1164.1</v>
+        <v>1177.6</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1174</v>
+        <v>1188.7</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1200.6</v>
+        <v>1223.7</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1164.2</v>
+        <v>1183.7</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1177.6</v>
+        <v>1206.5</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>1.16</v>
+        <v>28.9</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>558.15</v>
+        <v>582.15</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>560.7</v>
+        <v>586.5</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>585</v>
+        <v>594.9</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>560.05</v>
+        <v>580.2</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>582.15</v>
+        <v>586.35</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="J111" s="10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
+      </c>
+      <c r="J111" s="13" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4054.5</v>
+        <v>4008.5</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3974</v>
+        <v>4028</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4021</v>
+        <v>4065.8</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3900</v>
+        <v>3991</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4008.5</v>
+        <v>4023</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-46</v>
+        <v>14.5</v>
       </c>
       <c r="J112" s="13" t="n">
-        <v>-1.13</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>290.45</v>
+        <v>300.3</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>295</v>
+        <v>301.8</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>303</v>
+        <v>305.2</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>294.45</v>
+        <v>297.85</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>300.3</v>
+        <v>303.65</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
+      </c>
+      <c r="J113" s="13" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="13" t="n">
+      <c r="J114" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3739.8</v>
+        <v>3804.8</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3747</v>
+        <v>3804.9</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3825.8</v>
+        <v>3843.2</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3714</v>
+        <v>3756</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3804.8</v>
+        <v>3772.9</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>65</v>
+        <v>-31.9</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>1.74</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2343.3</v>
+        <v>2442.9</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2362.3</v>
+        <v>2454.9</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2459</v>
+        <v>2494</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2350.4</v>
+        <v>2430.4</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2442.9</v>
+        <v>2460.1</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v>4.25</v>
+        <v>17.2</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3210.8</v>
+        <v>3300.8</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3245</v>
+        <v>3311.9</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3315.7</v>
+        <v>3399</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3243.5</v>
+        <v>3305</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3300.8</v>
+        <v>3370.7</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>90</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>2.8</v>
+        <v>69.90000000000001</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>2.12</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>307.25</v>
+        <v>309.95</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>309.4</v>
+        <v>312</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>313.45</v>
+        <v>318.2</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>306.1</v>
+        <v>309.05</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>309.95</v>
+        <v>316.3</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J118" s="10" t="n">
-        <v>0.88</v>
+        <v>6.35</v>
+      </c>
+      <c r="J118" s="13" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>807.2</v>
+        <v>814.8</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>826.2</v>
+        <v>818.85</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>843.15</v>
+        <v>833.95</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>811.75</v>
+        <v>812.85</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>814.8</v>
+        <v>832.15</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>17.35</v>
+      </c>
+      <c r="J119" s="13" t="n">
+        <v>2.13</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13426</v>
+        <v>13722</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13555</v>
+        <v>13722</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13762</v>
+        <v>13870</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13379</v>
+        <v>13672</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13722</v>
+        <v>13770</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>296</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>2.2</v>
+        <v>48</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="13" t="n">
+      <c r="J121" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2902.5</v>
+        <v>2973.2</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>2939.8</v>
+        <v>2989.4</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>2989.4</v>
+        <v>3058</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2911</v>
+        <v>2962.5</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>2973.2</v>
+        <v>3042.6</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="J122" s="10" t="n">
-        <v>2.44</v>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="J122" s="13" t="n">
+        <v>2.33</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>506.3</v>
+        <v>506.4</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>511</v>
+        <v>506.5</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>511.6</v>
+        <v>514.45</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>503.1</v>
+        <v>504.35</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>506.4</v>
+        <v>505.6</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>0.02</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1596.2</v>
+        <v>1652.8</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1604.9</v>
+        <v>1658</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1657</v>
+        <v>1716.8</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1604.9</v>
+        <v>1642.3</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1652.8</v>
+        <v>1707.4</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>3.55</v>
+        <v>54.6</v>
+      </c>
+      <c r="J124" s="13" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1133.5</v>
+        <v>1166.8</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1141</v>
+        <v>1170.3</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1173</v>
+        <v>1190.7</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1141</v>
+        <v>1165.6</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1166.8</v>
+        <v>1179.8</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>2.94</v>
+        <v>13</v>
+      </c>
+      <c r="J125" s="13" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>120.24</v>
+        <v>127.41</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>121.81</v>
+        <v>128.31</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>128</v>
+        <v>131.4</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>121.51</v>
+        <v>126.8</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>127.41</v>
+        <v>130.43</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="J126" s="10" t="n">
-        <v>5.96</v>
+        <v>3.02</v>
+      </c>
+      <c r="J126" s="13" t="n">
+        <v>2.37</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2209.8</v>
+        <v>2218.5</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2244.7</v>
+        <v>2228</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2269.9</v>
+        <v>2237.3</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2191.2</v>
+        <v>2177.1</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2218.5</v>
+        <v>2193.1</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>8.699999999999999</v>
+        <v>-25.4</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>0.39</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>128270</v>
+        <v>130335</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>129540</v>
+        <v>131495</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>130750</v>
+        <v>133950</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>128720</v>
+        <v>129350</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>130335</v>
+        <v>129965</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>2065</v>
+        <v>-370</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>1.61</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3446.4</v>
+        <v>3533.6</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3480</v>
+        <v>3537.9</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3568.3</v>
+        <v>3614.4</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3456.3</v>
+        <v>3533.6</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3533.6</v>
+        <v>3584.3</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>2.53</v>
+        <v>50.7</v>
+      </c>
+      <c r="J129" s="13" t="n">
+        <v>1.43</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>413.6</v>
+        <v>406.55</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>418</v>
+        <v>409.8</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>420.95</v>
+        <v>412.05</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>405</v>
+        <v>402.65</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>406.55</v>
+        <v>403.5</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-7.05</v>
-      </c>
-      <c r="J130" s="13" t="n">
-        <v>-1.7</v>
+        <v>-3.05</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>963.95</v>
+        <v>981.4</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>970.05</v>
+        <v>988.05</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>962.25</v>
+        <v>968.7</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>981.4</v>
+        <v>981.85</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>17.45</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>1.81</v>
+        <v>0.45</v>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>7005</v>
+        <v>7043</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>7080</v>
+        <v>7099</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>7088</v>
+        <v>7119</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6978</v>
+        <v>6985.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>7043</v>
+        <v>7085</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J132" s="10" t="n">
-        <v>0.54</v>
+        <v>42</v>
+      </c>
+      <c r="J132" s="13" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1477.8</v>
+        <v>1486.1</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1468.2</v>
+        <v>1468.3</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1486.1</v>
+        <v>1476</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>88.83</v>
+        <v>89.18000000000001</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>90</v>
+        <v>89.7</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>90.84999999999999</v>
+        <v>90.89</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>88.5</v>
+        <v>89.14</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>89.18000000000001</v>
+        <v>90.14</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J134" s="10" t="n">
-        <v>0.39</v>
+        <v>0.96</v>
+      </c>
+      <c r="J134" s="13" t="n">
+        <v>1.08</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>398.65</v>
+        <v>394.85</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>400</v>
+        <v>396.75</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>403</v>
+        <v>403.5</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>391.65</v>
+        <v>393.15</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>394.85</v>
+        <v>400.35</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J135" s="13" t="n">
-        <v>-0.95</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1666.3</v>
+        <v>1673.4</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1682.3</v>
+        <v>1684.4</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1655.6</v>
+        <v>1659.5</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1673.4</v>
+        <v>1675</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J136" s="10" t="n">
-        <v>0.43</v>
+        <v>1.6</v>
+      </c>
+      <c r="J136" s="13" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9707</v>
+        <v>9424.5</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9794</v>
+        <v>9475</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9804</v>
+        <v>9547.5</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9650</v>
+        <v>9410</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9694.5</v>
+        <v>9498.5</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-12.5</v>
+        <v>74</v>
       </c>
       <c r="J137" s="13" t="n">
-        <v>-0.13</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>289.95</v>
+        <v>280.8</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>289.95</v>
+        <v>282</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>290.25</v>
+        <v>285.2</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>280</v>
+        <v>279.7</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>280.8</v>
+        <v>283.9</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-9.15</v>
+        <v>3.1</v>
       </c>
       <c r="J138" s="13" t="n">
-        <v>-3.16</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37400</v>
+        <v>37540</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37295</v>
+        <v>37405</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37740</v>
+        <v>37700</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>37160</v>
+        <v>37120</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37540</v>
+        <v>37345</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>140</v>
+        <v>-195</v>
       </c>
       <c r="J139" s="10" t="n">
-        <v>0.37</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="13" t="n">
+      <c r="J140" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4816.3</v>
+        <v>5014</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>4880</v>
+        <v>5030</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5037.6</v>
+        <v>5074.4</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4850</v>
+        <v>4911.5</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5014</v>
+        <v>4984</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>197.7</v>
+        <v>-30</v>
       </c>
       <c r="J141" s="10" t="n">
-        <v>4.1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>282.55</v>
+        <v>283.3</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>284.9</v>
+        <v>283.35</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>285</v>
+        <v>284.05</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>278.5</v>
+        <v>278.1</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>283.3</v>
+        <v>282.1</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>0.75</v>
+        <v>-1.2</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>0.27</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>456.9</v>
+        <v>463.9</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>459.3</v>
+        <v>464.45</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>464.85</v>
+        <v>467.4</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>454.6</v>
+        <v>456</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>463.9</v>
+        <v>457.55</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>7</v>
+        <v>-6.35</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v>1.53</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1364.2</v>
+        <v>1421.5</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1374.8</v>
+        <v>1442.6</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1426</v>
+        <v>1461.1</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1373</v>
+        <v>1428</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1421.5</v>
+        <v>1450.4</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J144" s="10" t="n">
-        <v>4.2</v>
+        <v>28.9</v>
+      </c>
+      <c r="J144" s="13" t="n">
+        <v>2.03</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3014.3</v>
+        <v>3071</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3025</v>
+        <v>3087.6</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3094</v>
+        <v>3121</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3021.1</v>
+        <v>3072.5</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3071</v>
+        <v>3101.5</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="J145" s="10" t="n">
-        <v>1.88</v>
+        <v>30.5</v>
+      </c>
+      <c r="J145" s="13" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>107.89</v>
+        <v>110.18</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>110.41</v>
+        <v>110.95</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>111.74</v>
+        <v>111</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>107.89</v>
+        <v>109</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>110.18</v>
+        <v>109.11</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>2.29</v>
+        <v>-1.07</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>2.12</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8337</v>
+        <v>8415.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8400</v>
+        <v>8499</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>8525</v>
+        <v>9050</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8355.5</v>
+        <v>8450</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8415.5</v>
+        <v>9003</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="J147" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>587.5</v>
+      </c>
+      <c r="J147" s="13" t="n">
+        <v>6.98</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>319.45</v>
+        <v>315.95</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>320.05</v>
+        <v>315.75</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>321.5</v>
+        <v>316.75</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>314.6</v>
+        <v>312.5</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>315.95</v>
+        <v>313.8</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>-1.1</v>
+        <v>-2.15</v>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1063.1</v>
+        <v>1068.9</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1066</v>
+        <v>1067.1</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1081.9</v>
+        <v>1090.4</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1060</v>
+        <v>1060.8</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1068.9</v>
+        <v>1066.1</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>5.8</v>
+        <v>-2.8</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>0.55</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>332.95</v>
+        <v>335.85</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>336.1</v>
+        <v>337.85</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>342.15</v>
+        <v>349.9</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>331.4</v>
+        <v>331.3</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>335.85</v>
+        <v>345.75</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J150" s="10" t="n">
-        <v>0.87</v>
+        <v>9.9</v>
+      </c>
+      <c r="J150" s="13" t="n">
+        <v>2.95</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>356.4</v>
+        <v>359.1</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>358.9</v>
+        <v>360</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>361.1</v>
+        <v>367.3</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>351.85</v>
+        <v>357.6</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>359.1</v>
+        <v>359.75</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1463.6</v>
+        <v>1437.9</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1463</v>
+        <v>1438.8</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1473.3</v>
+        <v>1449.5</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1427.5</v>
+        <v>1430.3</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1437.9</v>
+        <v>1436.2</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-25.7</v>
-      </c>
-      <c r="J152" s="13" t="n">
-        <v>-1.76</v>
+        <v>-1.7</v>
+      </c>
+      <c r="J152" s="10" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>187.31</v>
+        <v>186.04</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>189</v>
+        <v>186.25</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>190.5</v>
+        <v>190.25</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>184.71</v>
+        <v>185.9</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>186.04</v>
+        <v>187.28</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-1.27</v>
+        <v>1.24</v>
       </c>
       <c r="J153" s="13" t="n">
-        <v>-0.68</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>645.65</v>
+        <v>649.65</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>651</v>
+        <v>653.95</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>660</v>
+        <v>655.75</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>643.15</v>
+        <v>644.05</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>649.65</v>
+        <v>648.15</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>4</v>
+        <v>-1.5</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>0.62</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1821.2</v>
+        <v>1859</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1839</v>
+        <v>1868</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1868.9</v>
+        <v>1879.2</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1825.9</v>
+        <v>1860</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1859</v>
+        <v>1872.2</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="J155" s="10" t="n">
-        <v>2.08</v>
+        <v>13.2</v>
+      </c>
+      <c r="J155" s="13" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1059.9</v>
+        <v>1096</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1072</v>
+        <v>1106</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1101.1</v>
+        <v>1108</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1061.2</v>
+        <v>1086.1</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>36.1</v>
+        <v>-4</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>3.41</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>24845</v>
+        <v>24975</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25105</v>
+        <v>25450</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25200</v>
+        <v>25990</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>24660</v>
+        <v>25430</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>24975</v>
+        <v>25595</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>130</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>0.52</v>
+        <v>620</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>2.48</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>964.4</v>
+        <v>1004.1</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>980</v>
+        <v>1009</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1007.45</v>
+        <v>1023.75</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>976.05</v>
+        <v>1002.05</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1004.1</v>
+        <v>1015.65</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>4.12</v>
+        <v>11.55</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3846.6</v>
+        <v>3841.8</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3880</v>
+        <v>3860</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3885</v>
+        <v>3895.5</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3783</v>
+        <v>3792.9</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3841.8</v>
+        <v>3871.5</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-4.8</v>
+        <v>29.7</v>
       </c>
       <c r="J159" s="13" t="n">
-        <v>-0.12</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2522.8</v>
+        <v>2719.6</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2605</v>
+        <v>2714.9</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2762</v>
+        <v>2780</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2582.2</v>
+        <v>2655</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2719.6</v>
+        <v>2771.3</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="J160" s="10" t="n">
-        <v>7.8</v>
+        <v>51.7</v>
+      </c>
+      <c r="J160" s="13" t="n">
+        <v>1.9</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1820.8</v>
+        <v>1850.2</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1837</v>
+        <v>1850.2</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1857.8</v>
+        <v>1857.1</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1818.4</v>
+        <v>1826.3</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1850.2</v>
+        <v>1834.4</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>29.4</v>
+        <v>-15.8</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>1.61</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>580.1</v>
+        <v>570.75</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>588</v>
+        <v>575.3</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>588</v>
+        <v>578.9</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>568.15</v>
+        <v>569.05</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>570.75</v>
+        <v>571.1</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-9.35</v>
+        <v>0.35</v>
       </c>
       <c r="J162" s="13" t="n">
-        <v>-1.61</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>451.4</v>
+        <v>450.1</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>455.95</v>
+        <v>454</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>459.55</v>
+        <v>477</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>439.5</v>
+        <v>450.15</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>450.1</v>
+        <v>467.35</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-1.3</v>
+        <v>17.25</v>
       </c>
       <c r="J163" s="13" t="n">
-        <v>-0.29</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>801.45</v>
+        <v>815.95</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>804</v>
+        <v>822</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>830.5</v>
+        <v>828.35</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>802.2</v>
+        <v>801.1</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>815.95</v>
+        <v>805.35</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>14.5</v>
+        <v>-10.6</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>1.81</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1559</v>
+        <v>1591</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1579</v>
+        <v>1599.2</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1609.5</v>
+        <v>1609.8</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1557.1</v>
+        <v>1580</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1591</v>
+        <v>1593.5</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="J165" s="10" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
+      </c>
+      <c r="J165" s="13" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1153.5</v>
+        <v>1152.2</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1160</v>
+        <v>1152.2</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1166.9</v>
+        <v>1162.2</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1138.9</v>
+        <v>1135.6</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1152.2</v>
+        <v>1151.7</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J166" s="13" t="n">
-        <v>-0.11</v>
+        <v>-0.5</v>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="13" t="n">
+      <c r="J167" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>442.65</v>
+        <v>443.25</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>444.5</v>
+        <v>445.15</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>446.3</v>
+        <v>446</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>439.5</v>
+        <v>438.2</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>443.25</v>
+        <v>439.25</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>0.6</v>
+        <v>-4</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>0.14</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>211.32</v>
+        <v>215.47</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>214</v>
+        <v>216.7</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>216.73</v>
+        <v>219.2</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>212.42</v>
+        <v>215.75</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>215.47</v>
+        <v>217.09</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="J169" s="10" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
+      </c>
+      <c r="J169" s="13" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2427.3</v>
+        <v>2435.4</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2441.9</v>
+        <v>2438.2</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2471</v>
+        <v>2439.7</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2406.5</v>
+        <v>2398</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2435.4</v>
+        <v>2401.4</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>8.1</v>
+        <v>-34</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>0.33</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1452.2</v>
+        <v>1466.7</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1467.9</v>
+        <v>1467</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1480.6</v>
+        <v>1475.9</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1455.4</v>
+        <v>1444</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1466.7</v>
+        <v>1448.2</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>14.5</v>
+        <v>-18.5</v>
       </c>
       <c r="J171" s="10" t="n">
-        <v>1</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2932.4</v>
+        <v>2917</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2947.1</v>
+        <v>2928.5</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>2964.5</v>
+        <v>3024.9</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2872.8</v>
+        <v>2928.5</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2917</v>
+        <v>3015.5</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-15.4</v>
+        <v>98.5</v>
       </c>
       <c r="J172" s="13" t="n">
-        <v>-0.53</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4373.6</v>
+        <v>4359.6</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4397.5</v>
+        <v>4349.9</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4441.1</v>
+        <v>4359</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4297.1</v>
+        <v>4261</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4359.6</v>
+        <v>4307.5</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-14</v>
-      </c>
-      <c r="J173" s="13" t="n">
-        <v>-0.32</v>
+        <v>-52.1</v>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4275.1</v>
+        <v>4358.3</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4299.9</v>
+        <v>4360</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4436.8</v>
+        <v>4405.7</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4274</v>
+        <v>4346.5</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4358.3</v>
+        <v>4362.7</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1734.7</v>
+        <v>1734</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1757</v>
+        <v>1739.6</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1757</v>
+        <v>1761.9</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1713.5</v>
+        <v>1706.9</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1734</v>
+        <v>1712.5</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="J175" s="13" t="n">
-        <v>-0.04</v>
+        <v>-21.5</v>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4135.4</v>
+        <v>4289.8</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4157.9</v>
+        <v>4340.8</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4324.5</v>
+        <v>4355</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4156.5</v>
+        <v>4287.7</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4289.8</v>
+        <v>4294.1</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>154.4</v>
-      </c>
-      <c r="J176" s="10" t="n">
-        <v>3.73</v>
+        <v>4.3</v>
+      </c>
+      <c r="J176" s="13" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3534.4</v>
+        <v>3617.9</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3575</v>
+        <v>3600</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3625</v>
+        <v>3730</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3514.6</v>
+        <v>3592.6</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3617.9</v>
+        <v>3706.7</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>2.36</v>
+        <v>88.8</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>2.45</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1453.8</v>
+        <v>1412.8</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1428.3</v>
+        <v>1425.5</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1428.3</v>
+        <v>1451</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1382</v>
+        <v>1416</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1412.8</v>
+        <v>1428.2</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-41</v>
+        <v>15.4</v>
       </c>
       <c r="J178" s="13" t="n">
-        <v>-2.82</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11963</v>
+        <v>12093</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>12022</v>
+        <v>12270</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>12141</v>
+        <v>12275</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11942</v>
+        <v>12120</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>12093</v>
+        <v>12146</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>130</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>1.09</v>
+        <v>53</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>0.44</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>163.74</v>
+        <v>168.75</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>165.76</v>
+        <v>169.68</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>169.75</v>
+        <v>169.9</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>164.83</v>
+        <v>166.12</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>168.75</v>
+        <v>167.28</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>5.01</v>
+        <v>-1.47</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>3.06</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>642.05</v>
+        <v>660</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>645</v>
+        <v>664</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>663.1</v>
+        <v>664</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>642.3</v>
+        <v>649.15</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>660</v>
+        <v>650.45</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>17.95</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>2.8</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>303.9</v>
+        <v>316.4</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>310</v>
+        <v>319.9</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>318</v>
+        <v>322.75</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>308.6</v>
+        <v>303.6</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>316.4</v>
+        <v>305.4</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>12.5</v>
+        <v>-11</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v>4.11</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1375.9</v>
+        <v>1379.6</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1380</v>
+        <v>1389</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1385.9</v>
+        <v>1389</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1361.5</v>
+        <v>1352.3</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1379.6</v>
+        <v>1363.9</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>3.7</v>
+        <v>-15.7</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>0.27</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>199.78</v>
+        <v>199.12</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>200.51</v>
+        <v>199.5</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>201.13</v>
+        <v>200.28</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>198.25</v>
+        <v>197.19</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>199.12</v>
+        <v>197.36</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="J184" s="13" t="n">
-        <v>-0.33</v>
+        <v>-1.76</v>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="13" t="n">
+      <c r="J185" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>912.25</v>
+        <v>938.8</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>919.1</v>
+        <v>945</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>943.9</v>
+        <v>945.45</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>915</v>
+        <v>936.25</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>938.8</v>
+        <v>940.3</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="J186" s="10" t="n">
-        <v>2.91</v>
+        <v>1.5</v>
+      </c>
+      <c r="J186" s="13" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  06-May-2026 03:26 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  07-May-2026 03:28 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06-May-2026 03:26 PM</t>
+          <t>07-May-2026 03:28 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 07-May-2026 03:28 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 08-May-2026 02:51 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>07-May-2026 03:28 PM</t>
+          <t>08-May-2026 02:51 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  07-May-2026 03:28 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  08-May-2026 02:51 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>497.85</v>
+        <v>488.15</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>496.75</v>
+        <v>485</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>498.2</v>
+        <v>490.55</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>484</v>
+        <v>484.1</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>488.15</v>
+        <v>485.45</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-9.699999999999999</v>
+        <v>-2.7</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-1.95</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7182.5</v>
+        <v>7188</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7183</v>
+        <v>7210</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7279.5</v>
+        <v>7210</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>7000</v>
+        <v>6991.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7188</v>
+        <v>7012.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>0.08</v>
+        <v>-175.5</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>26300</v>
+        <v>26700</v>
       </c>
       <c r="E5" s="9" t="n">
+        <v>26840</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>26880</v>
+      </c>
+      <c r="G5" s="9" t="n">
         <v>26550</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>27100</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>26430</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>26700</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>369.3</v>
+        <v>369</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>370.85</v>
+        <v>369</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>375.95</v>
+        <v>369.85</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>368.1</v>
+        <v>361.35</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>369</v>
+        <v>362.95</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-0.3</v>
+        <v>-6.05</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>-0.08</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>66.20999999999999</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>66.48999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>69.09</v>
+        <v>67.7</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>66.26000000000001</v>
+        <v>66.09</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>67.79000000000001</v>
+        <v>66.33</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>2.39</v>
+        <v>-1.46</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1414</v>
+        <v>1414.6</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1421.6</v>
+        <v>1416.8</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1435</v>
+        <v>1432.9</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1409.2</v>
+        <v>1387.7</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1414.6</v>
+        <v>1391.9</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>0.04</v>
+        <v>-22.7</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2540.3</v>
+        <v>2513.7</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2540.3</v>
+        <v>2519</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2549.9</v>
+        <v>2546.1</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2506.2</v>
+        <v>2500</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2513.7</v>
+        <v>2505.9</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-26.6</v>
+        <v>-7.8</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>-1.05</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1748.3</v>
+        <v>1732.8</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1748.3</v>
+        <v>1740.4</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1755.9</v>
+        <v>1792</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1708</v>
+        <v>1727.7</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1732.8</v>
+        <v>1760.4</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>-0.89</v>
+        <v>27.6</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5557</v>
+        <v>5590.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5570</v>
+        <v>5588</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5608</v>
+        <v>5665.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5529.5</v>
+        <v>5550</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5590.5</v>
+        <v>5585.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>0.6</v>
+        <v>-5</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>446.9</v>
+        <v>450.65</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>446.5</v>
+        <v>449</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>454.2</v>
+        <v>457.95</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>445.1</v>
+        <v>442.5</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>450.65</v>
+        <v>444.3</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>0.84</v>
+        <v>-6.35</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>316.85</v>
+        <v>322.6</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>318.4</v>
+        <v>322</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>324.7</v>
+        <v>334.95</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>315.55</v>
+        <v>319</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>322.6</v>
+        <v>326</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1.81</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1914.7</v>
+        <v>1973.7</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1932.7</v>
+        <v>1986.8</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1983</v>
+        <v>2011.7</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1925.7</v>
+        <v>1943.4</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1973.7</v>
+        <v>1948.6</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="J14" s="13" t="n">
-        <v>3.08</v>
+        <v>-25.1</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7760.5</v>
+        <v>7837</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7760.5</v>
+        <v>7837</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>7855</v>
+        <v>8115</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7744</v>
+        <v>7812.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7837</v>
+        <v>8097</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>76.5</v>
+        <v>260</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>0.99</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>412.65</v>
+        <v>410.05</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>414</v>
+        <v>412.05</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>418.85</v>
+        <v>413.25</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>409.2</v>
+        <v>407.55</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>410.05</v>
+        <v>409.25</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-2.6</v>
+        <v>-0.8</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>-0.63</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>167.8</v>
+        <v>170.78</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>168.99</v>
+        <v>170</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>172.8</v>
+        <v>170</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>166.41</v>
+        <v>167.27</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>170.78</v>
+        <v>168.57</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>1.78</v>
+        <v>-2.21</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2519</v>
+        <v>2530.6</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2534.6</v>
+        <v>2540</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2555.8</v>
+        <v>2607.4</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2511.3</v>
+        <v>2515.4</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2530.6</v>
+        <v>2599.9</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>11.6</v>
+        <v>69.3</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>0.46</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1576.1</v>
+        <v>1569.1</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1577.9</v>
+        <v>1565.2</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1597.8</v>
+        <v>1594.6</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1561.9</v>
+        <v>1565.2</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1569.1</v>
+        <v>1569.8</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>-0.44</v>
+        <v>0.7</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>651</v>
+        <v>644.25</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>655</v>
+        <v>643.95</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>657</v>
+        <v>648.95</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>640.5</v>
+        <v>629.3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>644.25</v>
+        <v>633.05</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-6.75</v>
+        <v>-11.2</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-1.04</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>7108</v>
+        <v>7033.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>7171</v>
+        <v>7025</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7180</v>
+        <v>7112</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6986</v>
+        <v>7016.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7033.5</v>
+        <v>7088.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-74.5</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>-1.05</v>
+        <v>55</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>0.78</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1024</v>
+        <v>1032.4</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1024.9</v>
+        <v>1032.4</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1041</v>
+        <v>1052.3</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1019.3</v>
+        <v>1026.3</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1032.4</v>
+        <v>1050.4</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>0.82</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1484</v>
+        <v>1478.7</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1475.1</v>
+        <v>1485</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1498.5</v>
+        <v>1513.4</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1469.3</v>
+        <v>1480.1</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1478.7</v>
+        <v>1487.3</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>-0.36</v>
+        <v>8.6</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1294.2</v>
+        <v>1292.7</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1299</v>
+        <v>1280</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1308.1</v>
+        <v>1282</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1281.2</v>
+        <v>1264.6</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1292.7</v>
+        <v>1268.3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-1.5</v>
+        <v>-24.4</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>-0.12</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>10319</v>
+        <v>10605</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10582</v>
+        <v>10625</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10740</v>
+        <v>10785</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10324.5</v>
+        <v>10540</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>10605</v>
+        <v>10711.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>286</v>
+        <v>106.5</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>2.77</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1836.1</v>
+        <v>1824.5</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1849.6</v>
+        <v>1824.5</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1849.6</v>
+        <v>1827.2</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1816.6</v>
+        <v>1802.5</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1824.5</v>
+        <v>1818.3</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-11.6</v>
+        <v>-6.2</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>-0.63</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>980.75</v>
+        <v>972.75</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>992.25</v>
+        <v>971</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>992.25</v>
+        <v>971.95</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>969</v>
+        <v>951</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>972.75</v>
+        <v>955.35</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-8</v>
+        <v>-17.4</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>-0.82</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2230.3</v>
+        <v>2258.4</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2255</v>
+        <v>2264</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2283</v>
+        <v>2300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2228.7</v>
+        <v>2237.3</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2258.4</v>
+        <v>2262.5</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>28.1</v>
+        <v>4.1</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>1.26</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>524.85</v>
+        <v>525.5</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>530</v>
+        <v>525.4</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>530</v>
+        <v>525.4</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>521.2</v>
+        <v>517.2</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>525.5</v>
+        <v>522.75</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J29" s="13" t="n">
-        <v>0.12</v>
+        <v>-2.75</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>208.88</v>
+        <v>207.63</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>208.8</v>
+        <v>207.44</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>209.39</v>
+        <v>207.95</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>206</v>
+        <v>203.68</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>207.63</v>
+        <v>206.11</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-1.25</v>
+        <v>-1.52</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>-0.6</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>270.3</v>
+        <v>270.35</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>271.25</v>
+        <v>269.75</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>271.9</v>
+        <v>269.75</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>267.1</v>
+        <v>259.3</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>270.35</v>
+        <v>263.9</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J31" s="13" t="n">
-        <v>0.02</v>
+        <v>-6.45</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>438.2</v>
+        <v>439.45</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>439.9</v>
+        <v>439</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>441</v>
+        <v>443.8</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>433.5</v>
+        <v>437.8</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>439.45</v>
+        <v>439.7</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>0.29</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>478.45</v>
+        <v>488.25</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>498.95</v>
+        <v>521.95</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>484.6</v>
+        <v>488.05</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>488.25</v>
+        <v>515.75</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>27.5</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>2.05</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1833.7</v>
+        <v>1826.6</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1835</v>
+        <v>1820</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1843.9</v>
+        <v>1840.8</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1821.2</v>
+        <v>1815.2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1826.6</v>
+        <v>1834.5</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v>-0.39</v>
+        <v>7.9</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>385.95</v>
+        <v>406.45</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>385.5</v>
+        <v>406.1</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>408.35</v>
+        <v>408.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>383.45</v>
+        <v>400.1</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>406.45</v>
+        <v>404.6</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>5.31</v>
+        <v>-1.85</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>380.6</v>
+        <v>382.25</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>386.3</v>
+        <v>396.4</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>379.6</v>
+        <v>377.25</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>382.25</v>
+        <v>380.4</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J36" s="13" t="n">
-        <v>0.43</v>
+        <v>-1.85</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>36645</v>
+        <v>37895</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>36880</v>
+        <v>37750</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>38380</v>
+        <v>38855</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>36645</v>
+        <v>37650</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>37895</v>
+        <v>38145</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>1250</v>
+        <v>250</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>3.41</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>314.05</v>
+        <v>307.6</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>315.7</v>
+        <v>306</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>316.95</v>
+        <v>306.35</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>305.1</v>
+        <v>301.4</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>307.6</v>
+        <v>302.75</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-6.45</v>
+        <v>-4.85</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>-2.05</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5783</v>
+        <v>5814</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5798</v>
+        <v>5634</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5891.5</v>
+        <v>5654</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5733.5</v>
+        <v>5503</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5814</v>
+        <v>5520</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="J39" s="13" t="n">
-        <v>0.54</v>
+        <v>-294</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>-5.06</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>372.5</v>
+        <v>362.2</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>377</v>
+        <v>363.2</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>381.95</v>
+        <v>367.95</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>359.35</v>
+        <v>361.55</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>362.2</v>
+        <v>362.15</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-10.3</v>
+        <v>-0.05</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>-2.77</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>138.04</v>
+        <v>135.93</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>138.8</v>
+        <v>135</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>138.9</v>
+        <v>135.7</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>135.54</v>
+        <v>133.8</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>135.93</v>
+        <v>134.34</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-2.11</v>
+        <v>-1.59</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>-1.53</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>903.3</v>
+        <v>886.3</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>908.7</v>
+        <v>890</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>909.55</v>
+        <v>894.8</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>883.7</v>
+        <v>877.2</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>886.3</v>
+        <v>879.55</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-17</v>
+        <v>-6.75</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>-1.88</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>452.65</v>
+        <v>453.95</v>
       </c>
       <c r="E43" s="9" t="n">
+        <v>456.45</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>460.15</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>451.55</v>
+      </c>
+      <c r="H43" s="9" t="n">
         <v>455.8</v>
       </c>
-      <c r="F43" s="9" t="n">
-        <v>456.5</v>
-      </c>
-      <c r="G43" s="9" t="n">
-        <v>450.25</v>
-      </c>
-      <c r="H43" s="9" t="n">
-        <v>453.95</v>
-      </c>
       <c r="I43" s="9" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1711.9</v>
+        <v>1689.2</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1725</v>
+        <v>1688.1</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1734.8</v>
+        <v>1694.9</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1677.8</v>
+        <v>1670.6</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1689.2</v>
+        <v>1674.1</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-22.7</v>
+        <v>-15.1</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>-1.33</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1364.4</v>
+        <v>1362.3</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1370</v>
+        <v>1355</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1379.5</v>
+        <v>1366.7</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1360.1</v>
+        <v>1341.3</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1362.3</v>
+        <v>1347</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-2.1</v>
+        <v>-15.3</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>-0.15</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>470.2</v>
+        <v>466.65</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>470.2</v>
+        <v>461.2</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>472.85</v>
+        <v>463.35</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>456.1</v>
+        <v>454.9</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>466.65</v>
+        <v>456.4</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-3.55</v>
+        <v>-10.25</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>-0.75</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1280.4</v>
+        <v>1285.3</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1294.9</v>
+        <v>1279.1</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1312.6</v>
+        <v>1374</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1277.7</v>
+        <v>1275</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1285.3</v>
+        <v>1368.1</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>4.9</v>
+        <v>82.8</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>0.38</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2157.1</v>
+        <v>2167</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2172</v>
+        <v>2161.2</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2185</v>
+        <v>2205.9</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2144.9</v>
+        <v>2157.3</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2167</v>
+        <v>2197.4</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>9.9</v>
+        <v>30.4</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>0.46</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>524.2</v>
+        <v>526.7</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>527</v>
+        <v>526.65</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>528.9</v>
+        <v>537</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>523</v>
+        <v>524.25</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>526.7</v>
+        <v>534.75</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>2.5</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="J49" s="13" t="n">
-        <v>0.48</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>2018.1</v>
+        <v>1965</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>2035</v>
+        <v>1961.7</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>2035</v>
+        <v>1984.3</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1931.5</v>
+        <v>1901.8</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1965</v>
+        <v>1927.6</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-53.1</v>
+        <v>-37.4</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>-2.63</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>284.05</v>
+        <v>290.75</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>284.6</v>
+        <v>290.9</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>292.95</v>
+        <v>299.15</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>283.25</v>
+        <v>289.35</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>290.75</v>
+        <v>293.3</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>6.7</v>
+        <v>2.55</v>
       </c>
       <c r="J51" s="13" t="n">
-        <v>2.36</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>273</v>
+        <v>270.85</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>272.95</v>
+        <v>271.05</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>273.9</v>
+        <v>271.55</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>268.6</v>
+        <v>258.15</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>270.85</v>
+        <v>260.35</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-2.15</v>
+        <v>-10.5</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>-0.79</v>
+        <v>-3.88</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5324.5</v>
+        <v>5403</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5352.5</v>
+        <v>5415</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5424</v>
+        <v>5470.5</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5317.5</v>
+        <v>5381</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5403</v>
+        <v>5401</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="J53" s="13" t="n">
-        <v>1.47</v>
+        <v>-2</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>466.25</v>
+        <v>470</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>469.35</v>
+        <v>485</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>474.5</v>
+        <v>490.5</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>461.1</v>
+        <v>469.1</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>470</v>
+        <v>487.7</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>3.75</v>
+        <v>17.7</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>0.8</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1974.6</v>
+        <v>1974.3</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1989.5</v>
+        <v>1974.3</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1993.9</v>
+        <v>1977.5</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1959.5</v>
+        <v>1813.6</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1974.3</v>
+        <v>1823.6</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-0.3</v>
+        <v>-150.7</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>-0.02</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1821.6</v>
+        <v>1854.4</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1825</v>
+        <v>1854.4</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1860</v>
+        <v>1888</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1812.6</v>
+        <v>1842</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1854.4</v>
+        <v>1875.9</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>32.8</v>
+        <v>21.5</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>78.92</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>79.75</v>
+        <v>79</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>81.34999999999999</v>
+        <v>79.77</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>78.19</v>
+        <v>76.3</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>79.81999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J57" s="13" t="n">
-        <v>1.14</v>
+        <v>-2.17</v>
+      </c>
+      <c r="J57" s="10" t="n">
+        <v>-2.72</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6702</v>
+        <v>6702.5</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6705</v>
+        <v>6700</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6780</v>
+        <v>6759</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6683</v>
+        <v>6675</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6702.5</v>
+        <v>6710.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="59">
@@ -2737,22 +2737,22 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11299</v>
+        <v>11048</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>11350</v>
+        <v>11040</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11395</v>
+        <v>11265</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>11006</v>
+        <v>10580</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>11048</v>
+        <v>10803</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-251</v>
+        <v>-245</v>
       </c>
       <c r="J59" s="10" t="n">
         <v>-2.22</v>
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>609.6</v>
+        <v>618.85</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>615</v>
+        <v>617.1</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>620</v>
+        <v>619.95</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>607.75</v>
+        <v>606</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>618.85</v>
+        <v>608.25</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="J60" s="13" t="n">
-        <v>1.52</v>
+        <v>-10.6</v>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1311</v>
+        <v>1307.6</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1309.1</v>
+        <v>1303.5</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1315.7</v>
+        <v>1310.2</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1297.3</v>
+        <v>1290</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1307.6</v>
+        <v>1293.9</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-3.4</v>
+        <v>-13.7</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>-0.26</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7310.5</v>
+        <v>7327.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7360.5</v>
+        <v>7299.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7471.5</v>
+        <v>7370</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7310.5</v>
+        <v>7228</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7327.5</v>
+        <v>7302.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>0.23</v>
+        <v>-25</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3317.1</v>
+        <v>3345.9</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3335</v>
+        <v>3345.9</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3408</v>
+        <v>3345.9</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3300</v>
+        <v>3137.5</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3345.9</v>
+        <v>3146.6</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>0.87</v>
+        <v>-199.3</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>-5.96</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>351.7</v>
+        <v>364.45</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>365.6</v>
+        <v>366.8</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>342</v>
+        <v>360.35</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>364.45</v>
+        <v>362.25</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>3.63</v>
+        <v>-2.2</v>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>293</v>
+        <v>297.05</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>294.5</v>
+        <v>297</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>297.75</v>
+        <v>298.45</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>290</v>
+        <v>291.45</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>297.05</v>
+        <v>297.25</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>4.05</v>
+        <v>0.2</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>1.38</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>165.68</v>
+        <v>167.26</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>165.9</v>
+        <v>167.4</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>167.85</v>
+        <v>168.09</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>165.9</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>167.26</v>
+        <v>166.49</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>0.95</v>
+        <v>-0.77</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2377.6</v>
+        <v>2371.6</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2390</v>
+        <v>2350</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2404</v>
+        <v>2384.9</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2355.7</v>
+        <v>2315.8</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2371.6</v>
+        <v>2366.4</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-6</v>
+        <v>-5.2</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="68">
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>498.35</v>
+        <v>501.15</v>
       </c>
       <c r="E69" s="9" t="n">
         <v>502</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>504</v>
+        <v>506.7</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>495</v>
+        <v>492.9</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>501.15</v>
+        <v>496.15</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J69" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>-5</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1094.1</v>
+        <v>1036.6</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1064.7</v>
+        <v>1038.1</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1064.7</v>
+        <v>1049.8</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1034</v>
+        <v>1026.9</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1036.6</v>
+        <v>1042.4</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-57.5</v>
-      </c>
-      <c r="J70" s="10" t="n">
-        <v>-5.26</v>
+        <v>5.8</v>
+      </c>
+      <c r="J70" s="13" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1867.2</v>
+        <v>1878.6</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1870</v>
+        <v>1869.9</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1890</v>
+        <v>1889.2</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1835.6</v>
+        <v>1847</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1878.6</v>
+        <v>1873.6</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J71" s="13" t="n">
-        <v>0.61</v>
+        <v>-5</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>736</v>
+        <v>743.5</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>737.1</v>
+        <v>738</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>752.7</v>
+        <v>761.4</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>732.15</v>
+        <v>738</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>743.5</v>
+        <v>752.95</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>7.5</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J72" s="13" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2914.8</v>
+        <v>2960.6</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2902.3</v>
+        <v>2960.6</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2975</v>
+        <v>2980.4</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2900</v>
+        <v>2932.1</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2960.6</v>
+        <v>2968.6</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>45.8</v>
+        <v>8</v>
       </c>
       <c r="J73" s="13" t="n">
-        <v>1.57</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>397.55</v>
+        <v>408.95</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>400</v>
+        <v>408.9</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>410</v>
+        <v>408.9</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>397.45</v>
+        <v>393.5</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>408.95</v>
+        <v>396.45</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J74" s="13" t="n">
-        <v>2.87</v>
+        <v>-12.5</v>
+      </c>
+      <c r="J74" s="10" t="n">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4626.9</v>
+        <v>4782.1</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4647.8</v>
+        <v>4794</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4796</v>
+        <v>4836.3</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4628.1</v>
+        <v>4733</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4782.1</v>
+        <v>4788.1</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>155.2</v>
+        <v>6</v>
       </c>
       <c r="J75" s="13" t="n">
-        <v>3.35</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1257.3</v>
+        <v>1268.9</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1260</v>
+        <v>1268.9</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1276.7</v>
+        <v>1274.7</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1254.1</v>
+        <v>1252</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1268.9</v>
+        <v>1255.2</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="J76" s="13" t="n">
-        <v>0.92</v>
+        <v>-13.7</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1189.1</v>
+        <v>1183.4</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1195</v>
+        <v>1179.8</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1196</v>
+        <v>1202.8</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1181.1</v>
+        <v>1176.8</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1183.4</v>
+        <v>1198.4</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>-0.48</v>
+        <v>15</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>1.27</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2815.9</v>
+        <v>2834.6</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2830</v>
+        <v>2820</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2854.9</v>
+        <v>2872.4</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2780</v>
+        <v>2815.3</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2834.6</v>
+        <v>2854</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>18.7</v>
+        <v>19.4</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>796.55</v>
+        <v>796.05</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>801.55</v>
+        <v>788.75</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>788.55</v>
+        <v>777.2</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>796.05</v>
+        <v>780.85</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-0.5</v>
+        <v>-15.2</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>-0.06</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>606.35</v>
+        <v>625.4</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>611</v>
+        <v>625.5</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>629.3</v>
+        <v>628</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>608.85</v>
+        <v>618.3</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>625.4</v>
+        <v>621.7</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="J80" s="13" t="n">
-        <v>3.14</v>
+        <v>-3.7</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5170</v>
+        <v>5343</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5235</v>
+        <v>5341</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5458.5</v>
+        <v>5398.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5189.5</v>
+        <v>5265</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5343</v>
+        <v>5322</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>173</v>
-      </c>
-      <c r="J81" s="13" t="n">
-        <v>3.35</v>
+        <v>-21</v>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1045.8</v>
+        <v>1055.7</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1048</v>
+        <v>1048.4</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1060.9</v>
+        <v>1058</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1036.6</v>
+        <v>1035.3</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1055.7</v>
+        <v>1044.4</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J82" s="13" t="n">
-        <v>0.95</v>
+        <v>-11.3</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>550.5</v>
+        <v>568.6</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>556</v>
+        <v>559.1</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>568.6</v>
+        <v>569.2</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>18.1</v>
+        <v>0.6</v>
       </c>
       <c r="J83" s="13" t="n">
-        <v>3.29</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>399.2</v>
+        <v>396.5</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>399.4</v>
+        <v>393.5</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>404.25</v>
+        <v>395.1</v>
       </c>
       <c r="G84" s="12" t="n">
+        <v>385</v>
+      </c>
+      <c r="H84" s="12" t="n">
         <v>387</v>
       </c>
-      <c r="H84" s="12" t="n">
-        <v>396.5</v>
-      </c>
       <c r="I84" s="12" t="n">
-        <v>-2.7</v>
+        <v>-9.5</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>-0.68</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2317.1</v>
+        <v>2272.2</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2310</v>
+        <v>2272.2</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2327.9</v>
+        <v>2297.3</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2268.1</v>
+        <v>2256</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2272.2</v>
+        <v>2287.7</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-44.9</v>
-      </c>
-      <c r="J85" s="10" t="n">
-        <v>-1.94</v>
+        <v>15.5</v>
+      </c>
+      <c r="J85" s="13" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>30180</v>
+        <v>30605</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>30310</v>
+        <v>30650</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>30970</v>
+        <v>30885</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>30255</v>
+        <v>30110</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>30605</v>
+        <v>30170</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>425</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>1.41</v>
+        <v>-435</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>-1.42</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>69.59</v>
+        <v>70.39</v>
       </c>
       <c r="E87" s="9" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>71.45</v>
+      </c>
+      <c r="G87" s="9" t="n">
         <v>69.91</v>
       </c>
-      <c r="F87" s="9" t="n">
-        <v>71</v>
-      </c>
-      <c r="G87" s="9" t="n">
-        <v>69.15000000000001</v>
-      </c>
       <c r="H87" s="9" t="n">
-        <v>70.39</v>
+        <v>71.27</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="J87" s="13" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>129.8</v>
+        <v>133.81</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>130</v>
+        <v>134.15</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>134.15</v>
+        <v>134.82</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>129.51</v>
+        <v>132.6</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>133.81</v>
+        <v>134.12</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>4.01</v>
+        <v>0.31</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>3.09</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>169.46</v>
+        <v>169.84</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>170.8</v>
+        <v>168.95</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>171.84</v>
+        <v>168.95</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>168.95</v>
+        <v>165.08</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>169.84</v>
+        <v>165.99</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J89" s="13" t="n">
-        <v>0.22</v>
+        <v>-3.85</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>666.15</v>
+        <v>669.1</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>668</v>
+        <v>670.45</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>675.45</v>
+        <v>678.5</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>664.4</v>
+        <v>663.15</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>669.1</v>
+        <v>673.05</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>2.95</v>
+        <v>3.95</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2056.9</v>
+        <v>2091</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2068.5</v>
+        <v>2104.9</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2105.4</v>
+        <v>2122.2</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2062.2</v>
+        <v>2075</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2091</v>
+        <v>2091.8</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>34.1</v>
+        <v>0.8</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>1.66</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4520.2</v>
+        <v>4506.9</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4530</v>
+        <v>4488</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4560</v>
+        <v>4545.8</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4455.1</v>
+        <v>4465.7</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4506.9</v>
+        <v>4522.7</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-13.3</v>
-      </c>
-      <c r="J92" s="10" t="n">
-        <v>-0.29</v>
+        <v>15.8</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>946.75</v>
+        <v>946.95</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>948.25</v>
+        <v>946</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>951.65</v>
+        <v>957.9</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>934.1</v>
+        <v>940.5</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>946.95</v>
+        <v>950.75</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J93" s="13" t="n">
-        <v>0.02</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>408.3</v>
+        <v>402.9</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>410.45</v>
+        <v>403.9</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>411.8</v>
+        <v>406.55</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>399.6</v>
+        <v>397.6</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>402.9</v>
+        <v>404.3</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="J94" s="10" t="n">
-        <v>-1.32</v>
+        <v>1.4</v>
+      </c>
+      <c r="J94" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1167.2</v>
+        <v>1162.7</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1173</v>
+        <v>1161</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1175.4</v>
+        <v>1183.5</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1159.2</v>
+        <v>1158.8</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1162.7</v>
+        <v>1179.2</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="J95" s="10" t="n">
-        <v>-0.39</v>
+        <v>16.5</v>
+      </c>
+      <c r="J95" s="13" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>148.21</v>
+        <v>146.89</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>148.9</v>
+        <v>145.8</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>149.3</v>
+        <v>146.3</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>145.13</v>
+        <v>144.19</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>146.89</v>
+        <v>144.69</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-1.32</v>
+        <v>-2.2</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>-0.89</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1564.4</v>
+        <v>1560.1</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1572.2</v>
+        <v>1560.1</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1590.4</v>
+        <v>1610.5</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1555.1</v>
+        <v>1545.6</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1560.1</v>
+        <v>1552.6</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-4.3</v>
+        <v>-7.5</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>-0.27</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>572.75</v>
+        <v>568.5</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>575</v>
+        <v>566.05</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>578.05</v>
+        <v>570.85</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>568.5</v>
+        <v>564.9</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-4.25</v>
+        <v>-3.6</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>-0.74</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>310.7</v>
+        <v>307.4</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>311.45</v>
+        <v>308.9</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>311.65</v>
+        <v>308.9</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>307</v>
+        <v>305.7</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>307.4</v>
+        <v>307.45</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>-1.06</v>
+        <v>0.05</v>
+      </c>
+      <c r="J99" s="13" t="n">
+        <v>0.02</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1264.3</v>
+        <v>1258.2</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1273</v>
+        <v>1258.2</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1284.4</v>
+        <v>1260</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1254.2</v>
+        <v>1239.2</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1258.2</v>
+        <v>1248.4</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-6.1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>-0.48</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5521.5</v>
+        <v>5626</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5570</v>
+        <v>5626</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5740</v>
+        <v>5642</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5519</v>
+        <v>5536</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5626</v>
+        <v>5571.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="J101" s="13" t="n">
-        <v>1.89</v>
+        <v>-54.5</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>766.3</v>
+        <v>766.6</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>767.15</v>
+        <v>771.7</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>773.75</v>
+        <v>773.8</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>763</v>
+        <v>750.3</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>766.6</v>
+        <v>754.8</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J102" s="13" t="n">
-        <v>0.04</v>
+        <v>-11.8</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>567.9</v>
+        <v>575.9</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>578.9</v>
+        <v>577.8</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>567.85</v>
+        <v>563.3</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>575.9</v>
+        <v>571.2</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J103" s="13" t="n">
-        <v>1.41</v>
+        <v>-4.7</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1273.3</v>
+        <v>1283.4</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1272.1</v>
+        <v>1283.4</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1293.6</v>
+        <v>1284.9</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1268.6</v>
+        <v>1266.8</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1283.4</v>
+        <v>1277.8</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J104" s="13" t="n">
-        <v>0.79</v>
+        <v>-5.6</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>471.25</v>
+        <v>479</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>473.05</v>
+        <v>479.05</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>483.3</v>
+        <v>482.4</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>467.25</v>
+        <v>471.5</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>479</v>
+        <v>473.3</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="J105" s="13" t="n">
-        <v>1.64</v>
+        <v>-5.7</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1110.8</v>
+        <v>1098.8</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1118.9</v>
+        <v>1098.8</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1124.4</v>
+        <v>1108.8</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1090.5</v>
+        <v>1092.1</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1098.8</v>
+        <v>1104.1</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-12</v>
-      </c>
-      <c r="J106" s="10" t="n">
-        <v>-1.08</v>
+        <v>5.3</v>
+      </c>
+      <c r="J106" s="13" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>376.6</v>
+        <v>379.4</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>376.1</v>
+        <v>379</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>382.45</v>
+        <v>381.5</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>374.3</v>
+        <v>374</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>379.4</v>
+        <v>380.8</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J107" s="13" t="n">
-        <v>0.74</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>748.6</v>
+        <v>722.65</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>748.55</v>
+        <v>722.6</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>748.55</v>
+        <v>735.8</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>709.2</v>
+        <v>704</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>722.65</v>
+        <v>729.15</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-25.95</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>-3.47</v>
+        <v>6.5</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1586.2</v>
+        <v>1565.5</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1593.9</v>
+        <v>1558</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1621</v>
+        <v>1660</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1545</v>
+        <v>1551.9</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1565.5</v>
+        <v>1649.8</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-20.7</v>
-      </c>
-      <c r="J109" s="10" t="n">
-        <v>-1.31</v>
+        <v>84.3</v>
+      </c>
+      <c r="J109" s="13" t="n">
+        <v>5.38</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1177.6</v>
+        <v>1205.3</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1188.7</v>
+        <v>1206</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1223.7</v>
+        <v>1237.9</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1183.7</v>
+        <v>1206</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1206.5</v>
+        <v>1228.3</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>28.9</v>
+        <v>23</v>
       </c>
       <c r="J110" s="13" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>582.15</v>
+        <v>586.35</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>586.5</v>
+        <v>586.35</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>594.9</v>
+        <v>587.5</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>580.2</v>
+        <v>578.05</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>586.35</v>
+        <v>581.5</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J111" s="13" t="n">
-        <v>0.72</v>
+        <v>-4.85</v>
+      </c>
+      <c r="J111" s="10" t="n">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4008.5</v>
+        <v>4023</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>4028</v>
+        <v>4010</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4065.8</v>
+        <v>4014</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3991</v>
+        <v>3960</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>4023</v>
+        <v>3974.5</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="J112" s="13" t="n">
-        <v>0.36</v>
+        <v>-48.5</v>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>300.3</v>
+        <v>303.65</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>301.8</v>
+        <v>303</v>
       </c>
       <c r="F113" s="9" t="n">
         <v>305.2</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>297.85</v>
+        <v>300.7</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>303.65</v>
+        <v>303.4</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J113" s="13" t="n">
-        <v>1.12</v>
+        <v>-0.25</v>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="114">
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3804.8</v>
+        <v>3772.9</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3804.9</v>
+        <v>3795</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3843.2</v>
+        <v>3847.9</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3756</v>
+        <v>3774.1</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3772.9</v>
+        <v>3802.6</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-31.9</v>
-      </c>
-      <c r="J115" s="10" t="n">
-        <v>-0.84</v>
+        <v>29.7</v>
+      </c>
+      <c r="J115" s="13" t="n">
+        <v>0.79</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2442.9</v>
+        <v>2460.1</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2454.9</v>
+        <v>2425</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2494</v>
+        <v>2475</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2430.4</v>
+        <v>2347.9</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2460.1</v>
+        <v>2379.5</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="J116" s="13" t="n">
-        <v>0.7</v>
+        <v>-80.59999999999999</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3300.8</v>
+        <v>3370.7</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3311.9</v>
+        <v>3357.8</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3399</v>
+        <v>3363</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3305</v>
+        <v>3317.6</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3370.7</v>
+        <v>3330.4</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>2.12</v>
+        <v>-40.3</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>309.95</v>
+        <v>316.3</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>318.2</v>
+        <v>317.75</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>309.05</v>
+        <v>311.5</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>316.3</v>
+        <v>316</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="J118" s="13" t="n">
-        <v>2.05</v>
+        <v>-0.3</v>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>814.8</v>
+        <v>832.15</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>818.85</v>
+        <v>832.15</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>833.95</v>
+        <v>836.5</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>812.85</v>
+        <v>825.1</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>832.15</v>
+        <v>831.3</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="J119" s="13" t="n">
-        <v>2.13</v>
+        <v>-0.85</v>
+      </c>
+      <c r="J119" s="10" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13722</v>
+        <v>13770</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13722</v>
+        <v>13672</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13870</v>
+        <v>13789</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13672</v>
+        <v>13626</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13770</v>
+        <v>13726</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>0.35</v>
+        <v>-44</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="121">
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>2973.2</v>
+        <v>3042.6</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>2989.4</v>
+        <v>3069</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3058</v>
+        <v>3136</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>2962.5</v>
+        <v>3022.4</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3042.6</v>
+        <v>3097.8</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>69.40000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>2.33</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>506.4</v>
+        <v>505.6</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>506.5</v>
+        <v>511</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>514.45</v>
+        <v>574.9</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>504.35</v>
+        <v>511</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>505.6</v>
+        <v>549.5</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J123" s="10" t="n">
-        <v>-0.16</v>
+        <v>43.9</v>
+      </c>
+      <c r="J123" s="13" t="n">
+        <v>8.68</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1652.8</v>
+        <v>1707.4</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1658</v>
+        <v>1718.8</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1716.8</v>
+        <v>1718.8</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1642.3</v>
+        <v>1686.1</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1707.4</v>
+        <v>1699.7</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="J124" s="13" t="n">
-        <v>3.3</v>
+        <v>-7.7</v>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1166.8</v>
+        <v>1179.8</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1170.3</v>
+        <v>1140</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1190.7</v>
+        <v>1179.2</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1165.6</v>
+        <v>1131.1</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1179.8</v>
+        <v>1172.9</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="J125" s="13" t="n">
-        <v>1.11</v>
+        <v>-6.9</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>127.41</v>
+        <v>130.43</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>128.31</v>
+        <v>130.99</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>131.4</v>
+        <v>132.76</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>126.8</v>
+        <v>130.52</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>130.43</v>
+        <v>132.03</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>3.02</v>
+        <v>1.6</v>
       </c>
       <c r="J126" s="13" t="n">
-        <v>2.37</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2218.5</v>
+        <v>2193.1</v>
       </c>
       <c r="E127" s="9" t="n">
+        <v>2199</v>
+      </c>
+      <c r="F127" s="9" t="n">
         <v>2228</v>
       </c>
-      <c r="F127" s="9" t="n">
-        <v>2237.3</v>
-      </c>
       <c r="G127" s="9" t="n">
-        <v>2177.1</v>
+        <v>2182.9</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2193.1</v>
+        <v>2214.2</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-25.4</v>
-      </c>
-      <c r="J127" s="10" t="n">
-        <v>-1.14</v>
+        <v>21.1</v>
+      </c>
+      <c r="J127" s="13" t="n">
+        <v>0.96</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>130335</v>
+        <v>129965</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>131495</v>
+        <v>131745</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>133950</v>
+        <v>132000</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>129350</v>
+        <v>130135</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>129965</v>
+        <v>130425</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-370</v>
-      </c>
-      <c r="J128" s="10" t="n">
-        <v>-0.28</v>
+        <v>460</v>
+      </c>
+      <c r="J128" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3533.6</v>
+        <v>3584.3</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3537.9</v>
+        <v>3594</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3614.4</v>
+        <v>3594</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3533.6</v>
+        <v>3514.1</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3584.3</v>
+        <v>3528.9</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="J129" s="13" t="n">
-        <v>1.43</v>
+        <v>-55.4</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>406.55</v>
+        <v>401.5</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>409.8</v>
+        <v>403.2</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>412.05</v>
+        <v>403.9</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>402.65</v>
+        <v>396.15</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>403.5</v>
+        <v>401.95</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-3.05</v>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v>-0.75</v>
+        <v>0.45</v>
+      </c>
+      <c r="J130" s="13" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>981.4</v>
+        <v>981.85</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>988.05</v>
+        <v>981.85</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>996</v>
+        <v>988.8</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>968.7</v>
+        <v>973.3</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>981.85</v>
+        <v>978.35</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J131" s="13" t="n">
-        <v>0.05</v>
+        <v>-3.5</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>7043</v>
+        <v>7085</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>7099</v>
+        <v>7049</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>7119</v>
+        <v>7095.5</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6985.5</v>
+        <v>6996.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>7085</v>
+        <v>7041.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="J132" s="13" t="n">
-        <v>0.6</v>
+        <v>-43.5</v>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1486.1</v>
+        <v>1476</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1488</v>
+        <v>1476.6</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1493</v>
+        <v>1496.3</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1468.3</v>
+        <v>1470</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1476</v>
+        <v>1482.4</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-10.1</v>
-      </c>
-      <c r="J133" s="10" t="n">
-        <v>-0.68</v>
+        <v>6.4</v>
+      </c>
+      <c r="J133" s="13" t="n">
+        <v>0.43</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>89.18000000000001</v>
+        <v>90.14</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>89.7</v>
+        <v>90.05</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>90.89</v>
+        <v>90.5</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>89.14</v>
+        <v>88.67</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>90.14</v>
+        <v>88.8</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J134" s="13" t="n">
-        <v>1.08</v>
+        <v>-1.34</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>394.85</v>
+        <v>400.35</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>396.75</v>
+        <v>398</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>403.5</v>
+        <v>405.1</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>393.15</v>
+        <v>397.15</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>400.35</v>
+        <v>402.15</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="J135" s="13" t="n">
-        <v>1.39</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1673.4</v>
+        <v>1675</v>
       </c>
       <c r="E136" s="12" t="n">
         <v>1681</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1684.4</v>
+        <v>1715</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1659.5</v>
+        <v>1666.9</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1675</v>
+        <v>1703</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>1.6</v>
+        <v>28</v>
       </c>
       <c r="J136" s="13" t="n">
-        <v>0.1</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9424.5</v>
+        <v>9498.5</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9475</v>
+        <v>9500.5</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9547.5</v>
+        <v>9580</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9410</v>
+        <v>9301</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9498.5</v>
+        <v>9345.5</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>74</v>
-      </c>
-      <c r="J137" s="13" t="n">
-        <v>0.79</v>
+        <v>-153</v>
+      </c>
+      <c r="J137" s="10" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>280.8</v>
+        <v>283.9</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>282</v>
+        <v>283.6</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>285.2</v>
+        <v>284</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>279.7</v>
+        <v>278.6</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>283.9</v>
+        <v>279.2</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J138" s="13" t="n">
-        <v>1.1</v>
+        <v>-4.7</v>
+      </c>
+      <c r="J138" s="10" t="n">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37540</v>
+        <v>37345</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37405</v>
+        <v>37200</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37700</v>
+        <v>37500</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>37120</v>
+        <v>36840</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37345</v>
+        <v>37365</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-195</v>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v>-0.52</v>
+        <v>20</v>
+      </c>
+      <c r="J139" s="13" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="140">
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5014</v>
+        <v>4984</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5030</v>
+        <v>4990</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5074.4</v>
+        <v>5137</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4911.5</v>
+        <v>4960</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4984</v>
+        <v>5113.6</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-30</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>-0.6</v>
+        <v>129.6</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>283.3</v>
+        <v>282.1</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>283.35</v>
+        <v>282.1</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>284.05</v>
+        <v>286.25</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>278.1</v>
+        <v>278.95</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>282.1</v>
+        <v>283.8</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v>-0.42</v>
+        <v>1.7</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>463.9</v>
+        <v>457.55</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>464.45</v>
+        <v>458</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>467.4</v>
+        <v>467.25</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>456</v>
+        <v>455.55</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>457.55</v>
+        <v>461.35</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-6.35</v>
-      </c>
-      <c r="J143" s="10" t="n">
-        <v>-1.37</v>
+        <v>3.8</v>
+      </c>
+      <c r="J143" s="13" t="n">
+        <v>0.83</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1421.5</v>
+        <v>1450.4</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1442.6</v>
+        <v>1503.6</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1461.1</v>
+        <v>1515</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1428</v>
+        <v>1470</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1450.4</v>
+        <v>1476</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>28.9</v>
+        <v>25.6</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3071</v>
+        <v>3101.5</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3087.6</v>
+        <v>3099</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3121</v>
+        <v>3134.7</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3072.5</v>
+        <v>3067.5</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3101.5</v>
+        <v>3110.8</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>30.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J145" s="13" t="n">
-        <v>0.99</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>110.18</v>
+        <v>109.11</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>110.95</v>
+        <v>108.9</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>111</v>
+        <v>108.9</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>109</v>
+        <v>106.62</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>109.11</v>
+        <v>107.24</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-1.07</v>
+        <v>-1.87</v>
       </c>
       <c r="J146" s="10" t="n">
-        <v>-0.97</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>8415.5</v>
+        <v>9003</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8499</v>
+        <v>9030</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>9050</v>
+        <v>9159</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8450</v>
+        <v>8952.5</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>9003</v>
+        <v>9083</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>587.5</v>
+        <v>80</v>
       </c>
       <c r="J147" s="13" t="n">
-        <v>6.98</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>315.95</v>
+        <v>313.8</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>315.75</v>
+        <v>315.2</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>316.75</v>
+        <v>315.2</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>312.5</v>
+        <v>310.6</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>313.8</v>
+        <v>313.95</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v>-0.68</v>
+        <v>0.15</v>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1068.9</v>
+        <v>1066.1</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1067.1</v>
+        <v>1061.1</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1090.4</v>
+        <v>1077.1</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1060.8</v>
+        <v>1061.1</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1066.1</v>
+        <v>1073.8</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="J149" s="10" t="n">
-        <v>-0.26</v>
+        <v>7.7</v>
+      </c>
+      <c r="J149" s="13" t="n">
+        <v>0.72</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>335.85</v>
+        <v>345.75</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>337.85</v>
+        <v>348</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>349.9</v>
+        <v>349.7</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>331.3</v>
+        <v>339.4</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>345.75</v>
+        <v>343.45</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J150" s="13" t="n">
-        <v>2.95</v>
+        <v>-2.3</v>
+      </c>
+      <c r="J150" s="10" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>359.1</v>
+        <v>359.75</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>360</v>
+        <v>359.75</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>367.3</v>
+        <v>363.6</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>357.6</v>
+        <v>356.15</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>359.75</v>
+        <v>359.4</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>0.18</v>
+        <v>-0.35</v>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1437.9</v>
+        <v>1436.2</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1438.8</v>
+        <v>1426</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1449.5</v>
+        <v>1442.8</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1430.3</v>
+        <v>1417.5</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1436.2</v>
+        <v>1435.2</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-1.7</v>
+        <v>-1</v>
       </c>
       <c r="J152" s="10" t="n">
-        <v>-0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>186.04</v>
+        <v>187.28</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>186.25</v>
+        <v>187</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>190.25</v>
+        <v>187.7</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>185.9</v>
+        <v>184.15</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>187.28</v>
+        <v>184.88</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="J153" s="13" t="n">
-        <v>0.67</v>
+        <v>-2.4</v>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>649.65</v>
+        <v>648.15</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>653.95</v>
+        <v>649.95</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>655.75</v>
+        <v>650.75</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>644.05</v>
+        <v>643.8</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>648.15</v>
+        <v>645.4</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-1.5</v>
+        <v>-2.75</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>-0.23</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1859</v>
+        <v>1872.2</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1868</v>
+        <v>1874.9</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1879.2</v>
+        <v>1885</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1860</v>
+        <v>1865.2</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1872.2</v>
+        <v>1872.1</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J155" s="13" t="n">
-        <v>0.71</v>
+        <v>-0.1</v>
+      </c>
+      <c r="J155" s="10" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1106</v>
+        <v>1090</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1108</v>
+        <v>1095</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1086.1</v>
+        <v>1010.9</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1092</v>
+        <v>1019.3</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-4</v>
+        <v>-72.7</v>
       </c>
       <c r="J156" s="10" t="n">
-        <v>-0.36</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>24975</v>
+        <v>25595</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25450</v>
+        <v>25590</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25990</v>
+        <v>25590</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>25430</v>
+        <v>25165</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>25595</v>
+        <v>25435</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>620</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>2.48</v>
+        <v>-160</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1004.1</v>
+        <v>1015.65</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1023.75</v>
+        <v>1013.35</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1002.05</v>
+        <v>1001.25</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1015.65</v>
+        <v>1007.75</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="J158" s="13" t="n">
-        <v>1.15</v>
+        <v>-7.9</v>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3841.8</v>
+        <v>3871.5</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3860</v>
+        <v>3871.6</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3895.5</v>
+        <v>3906.9</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3792.9</v>
+        <v>3786</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3871.5</v>
+        <v>3822.6</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>0.77</v>
+        <v>-48.9</v>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2719.6</v>
+        <v>2771.3</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2714.9</v>
+        <v>2775.4</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2780</v>
+        <v>2819.3</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2655</v>
+        <v>2770</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2771.3</v>
+        <v>2780.8</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>51.7</v>
+        <v>9.5</v>
       </c>
       <c r="J160" s="13" t="n">
-        <v>1.9</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1850.2</v>
+        <v>1834.4</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1850.2</v>
+        <v>1822</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1857.1</v>
+        <v>1857.5</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1826.3</v>
+        <v>1819.2</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1834.4</v>
+        <v>1847.9</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-15.8</v>
-      </c>
-      <c r="J161" s="10" t="n">
-        <v>-0.85</v>
+        <v>13.5</v>
+      </c>
+      <c r="J161" s="13" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>570.75</v>
+        <v>571.1</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>575.3</v>
+        <v>574</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>578.9</v>
+        <v>575.45</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>569.05</v>
+        <v>569</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>571.1</v>
+        <v>573.55</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>0.35</v>
+        <v>2.45</v>
       </c>
       <c r="J162" s="13" t="n">
-        <v>0.06</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>450.1</v>
+        <v>467.35</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>454</v>
+        <v>466.6</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>477</v>
+        <v>469.9</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>450.15</v>
+        <v>456.15</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>467.35</v>
+        <v>458.1</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>17.25</v>
-      </c>
-      <c r="J163" s="13" t="n">
-        <v>3.83</v>
+        <v>-9.25</v>
+      </c>
+      <c r="J163" s="10" t="n">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>815.95</v>
+        <v>805.35</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>822</v>
+        <v>805.35</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>828.35</v>
+        <v>809.7</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>801.1</v>
+        <v>778</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>805.35</v>
+        <v>781.55</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-10.6</v>
+        <v>-23.8</v>
       </c>
       <c r="J164" s="10" t="n">
-        <v>-1.3</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1591</v>
+        <v>1593.5</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1599.2</v>
+        <v>1593.9</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1609.8</v>
+        <v>1609.4</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1580</v>
+        <v>1575.1</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1593.5</v>
+        <v>1592.3</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J165" s="13" t="n">
-        <v>0.16</v>
+        <v>-1.2</v>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1152.2</v>
+        <v>1151.7</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1152.2</v>
+        <v>1155</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1162.2</v>
+        <v>1194</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1135.6</v>
+        <v>1155</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1151.7</v>
+        <v>1176.2</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J166" s="10" t="n">
-        <v>-0.04</v>
+        <v>24.5</v>
+      </c>
+      <c r="J166" s="13" t="n">
+        <v>2.13</v>
       </c>
     </row>
     <row r="167">
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>443.25</v>
+        <v>439.25</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>445.15</v>
+        <v>438.1</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>446</v>
+        <v>440.6</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>438.2</v>
+        <v>434.7</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>439.25</v>
+        <v>436</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-4</v>
+        <v>-3.25</v>
       </c>
       <c r="J168" s="10" t="n">
-        <v>-0.9</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>215.47</v>
+        <v>217.09</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>216.7</v>
+        <v>217</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>219.2</v>
+        <v>217.4</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>215.75</v>
+        <v>214.25</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>217.09</v>
+        <v>214.49</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="J169" s="13" t="n">
-        <v>0.75</v>
+        <v>-2.6</v>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2435.4</v>
+        <v>2401.4</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2438.2</v>
+        <v>2398</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2439.7</v>
+        <v>2407</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2398</v>
+        <v>2375.1</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2401.4</v>
+        <v>2394.4</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-34</v>
+        <v>-7</v>
       </c>
       <c r="J170" s="10" t="n">
-        <v>-1.4</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1466.7</v>
+        <v>1448.2</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1467</v>
+        <v>1453.5</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1475.9</v>
+        <v>1469.8</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1444</v>
+        <v>1448.4</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1448.2</v>
+        <v>1463</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-18.5</v>
-      </c>
-      <c r="J171" s="10" t="n">
-        <v>-1.26</v>
+        <v>14.8</v>
+      </c>
+      <c r="J171" s="13" t="n">
+        <v>1.02</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2917</v>
+        <v>3015.5</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2928.5</v>
+        <v>3008.9</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3024.9</v>
+        <v>3066</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2928.5</v>
+        <v>2980</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>3015.5</v>
+        <v>3049.8</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>98.5</v>
+        <v>34.3</v>
       </c>
       <c r="J172" s="13" t="n">
-        <v>3.38</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4359.6</v>
+        <v>4307.5</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4349.9</v>
+        <v>4314</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4359</v>
+        <v>4605</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4261</v>
+        <v>4213.4</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4307.5</v>
+        <v>4509</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-52.1</v>
-      </c>
-      <c r="J173" s="10" t="n">
-        <v>-1.2</v>
+        <v>201.5</v>
+      </c>
+      <c r="J173" s="13" t="n">
+        <v>4.68</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4358.3</v>
+        <v>4362.7</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4360</v>
+        <v>4350</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4405.7</v>
+        <v>4398.4</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4346.5</v>
+        <v>4336.7</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4362.7</v>
+        <v>4380.8</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>4.4</v>
+        <v>18.1</v>
       </c>
       <c r="J174" s="13" t="n">
-        <v>0.1</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1734</v>
+        <v>1712.5</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1739.6</v>
+        <v>1715.1</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1761.9</v>
+        <v>1734.9</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1706.9</v>
+        <v>1710</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1712.5</v>
+        <v>1724.4</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="J175" s="10" t="n">
-        <v>-1.24</v>
+        <v>11.9</v>
+      </c>
+      <c r="J175" s="13" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4289.8</v>
+        <v>4294.1</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4340.8</v>
+        <v>4283.2</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4355</v>
+        <v>4318.9</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4287.7</v>
+        <v>4221.9</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4294.1</v>
+        <v>4242.3</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J176" s="13" t="n">
-        <v>0.1</v>
+        <v>-51.8</v>
+      </c>
+      <c r="J176" s="10" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3617.9</v>
+        <v>3706.7</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3600</v>
+        <v>3654.5</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3730</v>
+        <v>3718.7</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3592.6</v>
+        <v>3633.1</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3706.7</v>
+        <v>3695.2</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>2.45</v>
+        <v>-11.5</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1412.8</v>
+        <v>1428.2</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1425.5</v>
+        <v>1429</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1451</v>
+        <v>1441.9</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1416</v>
+        <v>1415.5</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1428.2</v>
+        <v>1419.8</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="J178" s="13" t="n">
-        <v>1.09</v>
+        <v>-8.4</v>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>12093</v>
+        <v>12146</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>12270</v>
+        <v>12090</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>12275</v>
+        <v>12110</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>12120</v>
+        <v>11877</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>12146</v>
+        <v>11950</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>53</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>0.44</v>
+        <v>-196</v>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>168.75</v>
+        <v>167.28</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>169.68</v>
+        <v>166.5</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>169.9</v>
+        <v>167.28</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>166.12</v>
+        <v>164.5</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>167.28</v>
+        <v>166.24</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-1.47</v>
+        <v>-1.04</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>-0.87</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>660</v>
+        <v>650.45</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>664</v>
+        <v>653.65</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>664</v>
+        <v>654.3</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>649.15</v>
+        <v>643.5</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>650.45</v>
+        <v>646</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-9.550000000000001</v>
+        <v>-4.45</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>-1.45</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>316.4</v>
+        <v>305.4</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>319.9</v>
+        <v>305.65</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>322.75</v>
+        <v>306.4</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>303.6</v>
+        <v>295.9</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>305.4</v>
+        <v>296.45</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-11</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v>-3.48</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1379.6</v>
+        <v>1363.9</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1389</v>
+        <v>1363</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1389</v>
+        <v>1363</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1352.3</v>
+        <v>1321</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1363.9</v>
+        <v>1324.8</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-15.7</v>
+        <v>-39.1</v>
       </c>
       <c r="J183" s="10" t="n">
-        <v>-1.14</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>199.12</v>
+        <v>197.36</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>199.5</v>
+        <v>198</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>200.28</v>
+        <v>198.94</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>197.19</v>
+        <v>196.7</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>197.36</v>
+        <v>197.91</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-1.76</v>
-      </c>
-      <c r="J184" s="10" t="n">
-        <v>-0.88</v>
+        <v>0.55</v>
+      </c>
+      <c r="J184" s="13" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="185">
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>938.8</v>
+        <v>940.3</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>945</v>
+        <v>938.05</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>945.45</v>
+        <v>953</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>936.25</v>
+        <v>935.55</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>940.3</v>
+        <v>940.05</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J186" s="13" t="n">
-        <v>0.16</v>
+        <v>-0.25</v>
+      </c>
+      <c r="J186" s="10" t="n">
+        <v>-0.03</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  07-May-2026 03:28 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  08-May-2026 02:51 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07-May-2026 03:28 PM</t>
+          <t>08-May-2026 02:51 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 08-May-2026 02:51 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 11-May-2026 03:55 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>08-May-2026 02:51 PM</t>
+          <t>11-May-2026 03:55 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  08-May-2026 02:51 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  11-May-2026 03:55 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>488.15</v>
+        <v>485.45</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>490.55</v>
+        <v>498</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>484.1</v>
+        <v>475</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>485.45</v>
+        <v>487.45</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-2.7</v>
+        <v>2</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-0.55</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7188</v>
+        <v>7012.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>7210</v>
+        <v>6662</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>7210</v>
+        <v>6687</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>6991.5</v>
+        <v>6323.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>7012.5</v>
+        <v>6387.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-175.5</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>-2.44</v>
+        <v>-625</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>-8.91</v>
       </c>
     </row>
     <row r="5">
@@ -904,22 +904,22 @@
         <v>26700</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>26840</v>
+        <v>26700</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>26880</v>
+        <v>27910</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>26550</v>
+        <v>26335</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26700</v>
+        <v>27795</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>0</v>
+        <v>1095</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>369</v>
+        <v>362.95</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>369.85</v>
+        <v>358.5</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>361.35</v>
+        <v>351.35</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>362.95</v>
+        <v>352.95</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-6.05</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>-1.64</v>
+        <v>-10</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>-2.76</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>67.79000000000001</v>
+        <v>66.33</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>67.7</v>
+        <v>65.55</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>67.7</v>
+        <v>65.78</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>66.09</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>66.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>-2.15</v>
+        <v>-1.34</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1414.6</v>
+        <v>1391.9</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1416.8</v>
+        <v>1385</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1432.9</v>
+        <v>1390</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1387.7</v>
+        <v>1340.4</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1391.9</v>
+        <v>1357.9</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-22.7</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>-1.6</v>
+        <v>-34</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2513.7</v>
+        <v>2505.9</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2519</v>
+        <v>2495</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2546.1</v>
+        <v>2514</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2500</v>
+        <v>2460</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2505.9</v>
+        <v>2500.2</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>-0.31</v>
+        <v>-5.7</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1732.8</v>
+        <v>1760.4</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1740.4</v>
+        <v>1757.1</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1792</v>
+        <v>1785.6</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1727.7</v>
+        <v>1733.1</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1760.4</v>
+        <v>1767.3</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="J10" s="13" t="n">
-        <v>1.59</v>
+        <v>6.9</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5590.5</v>
+        <v>5585.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5588</v>
+        <v>5585</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5665.5</v>
+        <v>5673</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5550</v>
+        <v>5494.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5585.5</v>
+        <v>5599.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-5</v>
+        <v>14</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>-0.09</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>450.65</v>
+        <v>444.3</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>449</v>
+        <v>441.75</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>457.95</v>
+        <v>441.75</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>442.5</v>
+        <v>432.4</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>444.3</v>
+        <v>436.2</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-6.35</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>-1.41</v>
+        <v>-8.1</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>322.6</v>
+        <v>326</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>322</v>
+        <v>323.75</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>334.95</v>
+        <v>326.95</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>319</v>
+        <v>316.15</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>326</v>
+        <v>317.2</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>3.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1.05</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1973.7</v>
+        <v>1948.6</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1986.8</v>
+        <v>1954</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>2011.7</v>
+        <v>1967.6</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1943.4</v>
+        <v>1926.9</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1948.6</v>
+        <v>1949.8</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-25.1</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>-1.27</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>7837</v>
+        <v>8097</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7837</v>
+        <v>8046</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8115</v>
+        <v>8144</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7812.5</v>
+        <v>8022.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8097</v>
+        <v>8082</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>260</v>
+        <v>-15</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>3.32</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>410.05</v>
+        <v>409.25</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>412.05</v>
+        <v>408.45</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>413.25</v>
+        <v>409</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>407.55</v>
+        <v>401.2</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>409.25</v>
+        <v>405.7</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>-0.2</v>
+        <v>-3.55</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>170.78</v>
+        <v>168.57</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>170</v>
+        <v>166.38</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>170</v>
+        <v>166.38</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>167.27</v>
+        <v>161</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>168.57</v>
+        <v>161.52</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>-1.29</v>
+        <v>-7.05</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>-4.18</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2530.6</v>
+        <v>2599.9</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2540</v>
+        <v>2578.9</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2607.4</v>
+        <v>2607.9</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2515.4</v>
+        <v>2555</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2599.9</v>
+        <v>2566.1</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>69.3</v>
+        <v>-33.8</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>2.74</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1569.1</v>
+        <v>1569.8</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1565.2</v>
+        <v>1571.1</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1594.6</v>
+        <v>1590</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1565.2</v>
+        <v>1560</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1569.8</v>
+        <v>1572.1</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>0.04</v>
+        <v>2.3</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>644.25</v>
+        <v>633.05</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>643.95</v>
+        <v>629.8</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>648.95</v>
+        <v>629.8</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>629.3</v>
+        <v>615.7</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>633.05</v>
+        <v>620.5</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-11.2</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>-1.74</v>
+        <v>-12.55</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>7033.5</v>
+        <v>7088.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>7025</v>
+        <v>7050</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7112</v>
+        <v>7051</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>7016.5</v>
+        <v>6870</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7088.5</v>
+        <v>6892</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>55</v>
+        <v>-196.5</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>0.78</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1032.4</v>
+        <v>1050.4</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1032.4</v>
+        <v>1045</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1052.3</v>
+        <v>1045</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1026.3</v>
+        <v>1017.6</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1050.4</v>
+        <v>1021.4</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>18</v>
+        <v>-29</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>1.74</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1478.7</v>
+        <v>1487.3</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1485</v>
+        <v>1487.3</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1513.4</v>
+        <v>1505.5</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1480.1</v>
+        <v>1477.4</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1487.3</v>
+        <v>1486.6</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>8.6</v>
+        <v>-0.7</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>0.58</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1292.7</v>
+        <v>1268.3</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1280</v>
+        <v>1258.7</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1264.6</v>
+        <v>1251.7</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1268.3</v>
+        <v>1272.3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-24.4</v>
+        <v>4</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>-1.89</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>10605</v>
+        <v>10711.5</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10625</v>
+        <v>10599</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10785</v>
+        <v>10650</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10540</v>
+        <v>10511</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>10711.5</v>
+        <v>10595.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>106.5</v>
+        <v>-116</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>1</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1824.5</v>
+        <v>1818.3</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1824.5</v>
+        <v>1804.2</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1827.2</v>
+        <v>1814</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1802.5</v>
+        <v>1786</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1818.3</v>
+        <v>1794.2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>-0.34</v>
+        <v>-24.1</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>972.75</v>
+        <v>955.35</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>971</v>
+        <v>946</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>971.95</v>
+        <v>956</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>951</v>
+        <v>933.55</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>955.35</v>
+        <v>936.05</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>-1.79</v>
+        <v>-19.3</v>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2258.4</v>
+        <v>2262.5</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2264</v>
+        <v>2250</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2237.3</v>
+        <v>2148.5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2262.5</v>
+        <v>2181.9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>4.1</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>0.18</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>525.5</v>
+        <v>522.75</v>
       </c>
       <c r="E29" s="9" t="n">
+        <v>520.7</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>530.95</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>511.95</v>
+      </c>
+      <c r="H29" s="9" t="n">
         <v>525.4</v>
       </c>
-      <c r="F29" s="9" t="n">
-        <v>525.4</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>517.2</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>522.75</v>
-      </c>
       <c r="I29" s="9" t="n">
-        <v>-2.75</v>
+        <v>2.65</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>-0.52</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>207.63</v>
+        <v>206.11</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>207.44</v>
+        <v>203.52</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>207.95</v>
+        <v>204.9</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>203.68</v>
+        <v>199.91</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>206.11</v>
+        <v>201.23</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>-0.73</v>
+        <v>-4.88</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>270.35</v>
+        <v>263.9</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>269.75</v>
+        <v>265.9</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>269.75</v>
+        <v>269.7</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>259.3</v>
+        <v>262.35</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>263.9</v>
+        <v>266</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-6.45</v>
+        <v>2.1</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>-2.39</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>439.45</v>
+        <v>439.7</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>443.8</v>
+        <v>439.15</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>437.8</v>
+        <v>431</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>439.7</v>
+        <v>431.95</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0.25</v>
+        <v>-7.75</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>0.06</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>488.25</v>
+        <v>515.75</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>490</v>
+        <v>511.95</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>521.95</v>
+        <v>511.95</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>488.05</v>
+        <v>491.05</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>515.75</v>
+        <v>493.85</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>27.5</v>
+        <v>-21.9</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>5.63</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1826.6</v>
+        <v>1834.5</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1820</v>
+        <v>1814</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1840.8</v>
+        <v>1819.8</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1815.2</v>
+        <v>1756</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1834.5</v>
+        <v>1759.8</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>7.9</v>
+        <v>-74.7</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>0.43</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>406.45</v>
+        <v>404.6</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>406.1</v>
+        <v>400</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>408.9</v>
+        <v>406.6</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>400.1</v>
+        <v>393.05</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>404.6</v>
+        <v>401.35</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v>-0.46</v>
+        <v>-3.25</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>382.25</v>
+        <v>380.4</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>379</v>
+        <v>380.45</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>396.4</v>
+        <v>396.25</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>377.25</v>
+        <v>371.75</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>380.4</v>
+        <v>390.45</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>-1.85</v>
+        <v>10.05</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>-0.48</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>37895</v>
+        <v>38145</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>37750</v>
+        <v>38020</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>38855</v>
+        <v>38020</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>37650</v>
+        <v>37220</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>38145</v>
+        <v>37315</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>250</v>
+        <v>-830</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>0.66</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>307.6</v>
+        <v>302.75</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>306</v>
+        <v>298.75</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>306.35</v>
+        <v>299.4</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>301.4</v>
+        <v>293.75</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>302.75</v>
+        <v>294.45</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-4.85</v>
-      </c>
-      <c r="J38" s="10" t="n">
-        <v>-1.58</v>
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="J38" s="13" t="n">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5814</v>
+        <v>5520</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5634</v>
+        <v>5505.5</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5654</v>
+        <v>5508</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5503</v>
+        <v>5395</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5520</v>
+        <v>5410.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-294</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>-5.06</v>
+        <v>-109.5</v>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>362.2</v>
+        <v>362.15</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>363.2</v>
+        <v>360</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>367.95</v>
+        <v>360.3</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>361.55</v>
+        <v>352.85</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>362.15</v>
+        <v>355.9</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>-0.01</v>
+        <v>-6.25</v>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>135.93</v>
+        <v>134.34</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>135</v>
+        <v>133.02</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>135.7</v>
+        <v>139.4</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>133.8</v>
+        <v>128.58</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>134.34</v>
+        <v>129.43</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="J41" s="10" t="n">
-        <v>-1.17</v>
+        <v>-4.91</v>
+      </c>
+      <c r="J41" s="13" t="n">
+        <v>-3.65</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>886.3</v>
+        <v>879.55</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>894.8</v>
+        <v>876.8</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>877.2</v>
+        <v>852</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>879.55</v>
+        <v>855.3</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-6.75</v>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>-0.76</v>
+        <v>-24.25</v>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v>-2.76</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>453.95</v>
+        <v>455.8</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>456.45</v>
+        <v>451</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>460.15</v>
+        <v>456.5</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>451.55</v>
+        <v>446</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>455.8</v>
+        <v>452.3</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1.85</v>
+        <v>-3.5</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>0.41</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1689.2</v>
+        <v>1674.1</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1688.1</v>
+        <v>1630.4</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1694.9</v>
+        <v>1646.4</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1670.6</v>
+        <v>1621</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1674.1</v>
+        <v>1624.5</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-15.1</v>
-      </c>
-      <c r="J44" s="10" t="n">
-        <v>-0.89</v>
+        <v>-49.6</v>
+      </c>
+      <c r="J44" s="13" t="n">
+        <v>-2.96</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1362.3</v>
+        <v>1347</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1355</v>
+        <v>1347</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1366.7</v>
+        <v>1350</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1341.3</v>
+        <v>1300.1</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1347</v>
+        <v>1304.9</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-15.3</v>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v>-1.12</v>
+        <v>-42.1</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>-3.13</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>466.65</v>
+        <v>456.4</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>461.2</v>
+        <v>456</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>463.35</v>
+        <v>465.75</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>454.9</v>
+        <v>452.85</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>456.4</v>
+        <v>464.45</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-10.25</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>-2.2</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1285.3</v>
+        <v>1368.1</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1279.1</v>
+        <v>1375.8</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1374</v>
+        <v>1387.8</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1275</v>
+        <v>1359.6</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1368.1</v>
+        <v>1375.2</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>6.44</v>
+        <v>7.1</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2167</v>
+        <v>2197.4</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2161.2</v>
+        <v>2196.9</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2205.9</v>
+        <v>2204.2</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2157.3</v>
+        <v>2132.4</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2197.4</v>
+        <v>2139</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>30.4</v>
+        <v>-58.4</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>1.4</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>526.7</v>
+        <v>534.75</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>526.65</v>
+        <v>535.75</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>537</v>
+        <v>535.75</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>524.25</v>
+        <v>528.05</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>534.75</v>
+        <v>530</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>8.050000000000001</v>
+        <v>-4.75</v>
       </c>
       <c r="J49" s="13" t="n">
-        <v>1.53</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1965</v>
+        <v>1927.6</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1961.7</v>
+        <v>1924.9</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1984.3</v>
+        <v>1925</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1901.8</v>
+        <v>1858.4</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1927.6</v>
+        <v>1866.2</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-37.4</v>
-      </c>
-      <c r="J50" s="10" t="n">
-        <v>-1.9</v>
+        <v>-61.4</v>
+      </c>
+      <c r="J50" s="13" t="n">
+        <v>-3.19</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>290.75</v>
+        <v>293.3</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>290.9</v>
+        <v>290.2</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>299.15</v>
+        <v>292.9</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>289.35</v>
+        <v>285.7</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>293.3</v>
+        <v>290.2</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2.55</v>
+        <v>-3.1</v>
       </c>
       <c r="J51" s="13" t="n">
-        <v>0.88</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>270.85</v>
+        <v>260.35</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>271.05</v>
+        <v>258.85</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>271.55</v>
+        <v>258.85</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>258.15</v>
+        <v>249.3</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>260.35</v>
+        <v>254.2</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>-3.88</v>
+        <v>-6.15</v>
+      </c>
+      <c r="J52" s="13" t="n">
+        <v>-2.36</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5403</v>
+        <v>5401</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5415</v>
+        <v>5350</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5470.5</v>
+        <v>5350</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5381</v>
+        <v>5191</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5401</v>
+        <v>5238.5</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J53" s="10" t="n">
-        <v>-0.04</v>
+        <v>-162.5</v>
+      </c>
+      <c r="J53" s="13" t="n">
+        <v>-3.01</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>470</v>
+        <v>487.7</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>485</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>490.5</v>
+        <v>485</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>469.1</v>
+        <v>471.2</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>487.7</v>
+        <v>473.45</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>17.7</v>
+        <v>-14.25</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>3.77</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1974.3</v>
+        <v>1823.6</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1974.3</v>
+        <v>1825</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1977.5</v>
+        <v>1834.8</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1813.6</v>
+        <v>1761</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1823.6</v>
+        <v>1772.2</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-150.7</v>
-      </c>
-      <c r="J55" s="10" t="n">
-        <v>-7.63</v>
+        <v>-51.4</v>
+      </c>
+      <c r="J55" s="13" t="n">
+        <v>-2.82</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1854.4</v>
+        <v>1875.9</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1854.4</v>
+        <v>1865</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1888</v>
+        <v>1895</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1842</v>
+        <v>1814.3</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1875.9</v>
+        <v>1863.6</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>21.5</v>
+        <v>-12.3</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>1.16</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>79.81999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>79</v>
+        <v>77.45</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>79.77</v>
+        <v>77.45</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>76.3</v>
+        <v>74.08</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>77.65000000000001</v>
+        <v>74.53</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-2.17</v>
-      </c>
-      <c r="J57" s="10" t="n">
-        <v>-2.72</v>
+        <v>-3.12</v>
+      </c>
+      <c r="J57" s="13" t="n">
+        <v>-4.02</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6702.5</v>
+        <v>6710.5</v>
       </c>
       <c r="E58" s="12" t="n">
         <v>6700</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6759</v>
+        <v>6785</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6675</v>
+        <v>6650</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6710.5</v>
+        <v>6714</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>0.12</v>
+        <v>3.5</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>11048</v>
+        <v>10803</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>11040</v>
+        <v>10773</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11265</v>
+        <v>10956</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>10580</v>
+        <v>10537</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>10803</v>
+        <v>10772</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-245</v>
-      </c>
-      <c r="J59" s="10" t="n">
-        <v>-2.22</v>
+        <v>-31</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>618.85</v>
+        <v>608.25</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>617.1</v>
+        <v>600</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>619.95</v>
+        <v>600</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>606</v>
+        <v>588.6</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>608.25</v>
+        <v>590.25</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>-1.71</v>
+        <v>-18</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>-2.96</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1307.6</v>
+        <v>1293.9</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1303.5</v>
+        <v>1288</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1310.2</v>
+        <v>1299.9</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1290</v>
+        <v>1272.5</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1293.9</v>
+        <v>1279.9</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-13.7</v>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v>-1.05</v>
+        <v>-14</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7327.5</v>
+        <v>7302.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7299.5</v>
+        <v>7269</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7370</v>
+        <v>7269</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7228</v>
+        <v>7159</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7302.5</v>
+        <v>7202.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-25</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>-0.34</v>
+        <v>-100</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3345.9</v>
+        <v>3146.6</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3345.9</v>
+        <v>3138.4</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3345.9</v>
+        <v>3140</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>3137.5</v>
+        <v>2948.6</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3146.6</v>
+        <v>2966.7</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-199.3</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>-5.96</v>
+        <v>-179.9</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>-5.72</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>364.45</v>
+        <v>362.25</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>366.8</v>
+        <v>360.1</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>360.35</v>
+        <v>351.55</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>362.25</v>
+        <v>352.7</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="J64" s="10" t="n">
-        <v>-0.6</v>
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>297.05</v>
+        <v>297.25</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>298.45</v>
+        <v>297.4</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>291.45</v>
+        <v>291.15</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>297.25</v>
+        <v>292.45</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>0.2</v>
+        <v>-4.8</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>167.26</v>
+        <v>166.49</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>167.4</v>
+        <v>165.6</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>168.09</v>
+        <v>165.6</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>165.9</v>
+        <v>162.21</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>166.49</v>
+        <v>162.51</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="J66" s="10" t="n">
-        <v>-0.46</v>
+        <v>-3.98</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2371.6</v>
+        <v>2366.4</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2350</v>
+        <v>2356.5</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2384.9</v>
+        <v>2368.8</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2315.8</v>
+        <v>2317.7</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2366.4</v>
+        <v>2347.3</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="J67" s="10" t="n">
-        <v>-0.22</v>
+        <v>-19.1</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="10" t="n">
+      <c r="J68" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>501.15</v>
+        <v>496.15</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>502</v>
+        <v>497.85</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>506.7</v>
+        <v>497.85</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>492.9</v>
+        <v>482.35</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>496.15</v>
+        <v>485</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J69" s="10" t="n">
-        <v>-1</v>
+        <v>-11.15</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1036.6</v>
+        <v>1042.4</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1038.1</v>
+        <v>1042.5</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1049.8</v>
+        <v>1045</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1026.9</v>
+        <v>1006.9</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1042.4</v>
+        <v>1010.9</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>5.8</v>
+        <v>-31.5</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>0.5600000000000001</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1878.6</v>
+        <v>1873.6</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1869.9</v>
+        <v>1862.1</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1889.2</v>
+        <v>1862.1</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1847</v>
+        <v>1784</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1873.6</v>
+        <v>1794.3</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>-0.27</v>
+        <v>-79.3</v>
+      </c>
+      <c r="J71" s="13" t="n">
+        <v>-4.23</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>743.5</v>
+        <v>752.95</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>761.4</v>
+        <v>760.25</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>738</v>
+        <v>742.3</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>752.95</v>
+        <v>755.6</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="J72" s="13" t="n">
-        <v>1.27</v>
+        <v>2.65</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2960.6</v>
+        <v>2968.6</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2960.6</v>
+        <v>2954.1</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2980.4</v>
+        <v>3007.3</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2932.1</v>
+        <v>2928</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2968.6</v>
+        <v>2984.2</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J73" s="13" t="n">
-        <v>0.27</v>
+        <v>15.6</v>
+      </c>
+      <c r="J73" s="10" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>408.95</v>
+        <v>396.45</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>408.9</v>
+        <v>396</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>408.9</v>
+        <v>400.4</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>393.5</v>
+        <v>376.75</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>396.45</v>
+        <v>380.95</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="J74" s="10" t="n">
-        <v>-3.06</v>
+        <v>-15.5</v>
+      </c>
+      <c r="J74" s="13" t="n">
+        <v>-3.91</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4782.1</v>
+        <v>4788.1</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4794</v>
+        <v>4779.2</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4836.3</v>
+        <v>4808.5</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4733</v>
+        <v>4739.7</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4788.1</v>
+        <v>4756.3</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>6</v>
+        <v>-31.8</v>
       </c>
       <c r="J75" s="13" t="n">
-        <v>0.13</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1268.9</v>
+        <v>1255.2</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1268.9</v>
+        <v>1248.2</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1274.7</v>
+        <v>1249</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1252</v>
+        <v>1226.6</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1255.2</v>
+        <v>1230</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-13.7</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>-1.08</v>
+        <v>-25.2</v>
+      </c>
+      <c r="J76" s="13" t="n">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1183.4</v>
+        <v>1198.4</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1179.8</v>
+        <v>1196.9</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1202.8</v>
+        <v>1206.3</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1176.8</v>
+        <v>1191.1</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1198.4</v>
+        <v>1194.9</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>15</v>
+        <v>-3.5</v>
       </c>
       <c r="J77" s="13" t="n">
-        <v>1.27</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2834.6</v>
+        <v>2854</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2820</v>
+        <v>2845</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2872.4</v>
+        <v>2845</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2815.3</v>
+        <v>2738.9</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2854</v>
+        <v>2747.2</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>19.4</v>
+        <v>-106.8</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>0.68</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>796.05</v>
+        <v>780.85</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>784</v>
+        <v>771.95</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>788.75</v>
+        <v>774.85</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>777.2</v>
+        <v>761.9</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>780.85</v>
+        <v>763.65</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="J79" s="10" t="n">
-        <v>-1.91</v>
+        <v>-17.2</v>
+      </c>
+      <c r="J79" s="13" t="n">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>625.4</v>
+        <v>621.7</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>625.5</v>
+        <v>619</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>618.3</v>
+        <v>611.2</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>621.7</v>
+        <v>622.7</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-3.7</v>
+        <v>1</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>-0.59</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5343</v>
+        <v>5322</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5341</v>
+        <v>5262.5</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5398.5</v>
+        <v>5283.5</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5265</v>
+        <v>5146</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5322</v>
+        <v>5228.5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-21</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>-0.39</v>
+        <v>-93.5</v>
+      </c>
+      <c r="J81" s="13" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1055.7</v>
+        <v>1044.4</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1048.4</v>
+        <v>1031.1</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1058</v>
+        <v>1042.4</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1035.3</v>
+        <v>1022.1</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1044.4</v>
+        <v>1023.5</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-11.3</v>
-      </c>
-      <c r="J82" s="10" t="n">
-        <v>-1.07</v>
+        <v>-20.9</v>
+      </c>
+      <c r="J82" s="13" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>568.6</v>
+        <v>569.2</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>559.1</v>
+        <v>564.1</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>569.2</v>
+        <v>572.9</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J83" s="13" t="n">
-        <v>0.11</v>
+        <v>3.7</v>
+      </c>
+      <c r="J83" s="10" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>396.5</v>
+        <v>387</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>393.5</v>
+        <v>383</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>395.1</v>
+        <v>383.4</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>385</v>
+        <v>375.1</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>387</v>
+        <v>377.8</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="J84" s="10" t="n">
-        <v>-2.4</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="J84" s="13" t="n">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2272.2</v>
+        <v>2287.7</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2272.2</v>
+        <v>2277.1</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2297.3</v>
+        <v>2317.1</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2256</v>
+        <v>2259.2</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2287.7</v>
+        <v>2307.2</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="J85" s="13" t="n">
-        <v>0.68</v>
+        <v>19.5</v>
+      </c>
+      <c r="J85" s="10" t="n">
+        <v>0.85</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>30605</v>
+        <v>30170</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>30650</v>
+        <v>30155</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>30885</v>
+        <v>30155</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>30110</v>
+        <v>29250</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>30170</v>
+        <v>29340</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-435</v>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v>-1.42</v>
+        <v>-830</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>70.39</v>
+        <v>71.27</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>70.39</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>71.45</v>
+        <v>70.78</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>69.91</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>71.27</v>
+        <v>69.22</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0.88</v>
+        <v>-2.05</v>
       </c>
       <c r="J87" s="13" t="n">
-        <v>1.25</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>133.81</v>
+        <v>134.12</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>134.15</v>
+        <v>133.76</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>134.82</v>
+        <v>137.34</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>132.6</v>
+        <v>130.17</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>134.12</v>
+        <v>130.71</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>0.31</v>
+        <v>-3.41</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>0.23</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>169.84</v>
+        <v>165.99</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>168.95</v>
+        <v>164.5</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>168.95</v>
+        <v>164.5</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>165.08</v>
+        <v>160.19</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>165.99</v>
+        <v>160.69</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="J89" s="10" t="n">
-        <v>-2.27</v>
+        <v>-5.3</v>
+      </c>
+      <c r="J89" s="13" t="n">
+        <v>-3.19</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>669.1</v>
+        <v>673.05</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>670.45</v>
+        <v>670</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>678.5</v>
+        <v>671.9</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>663.15</v>
+        <v>655.9</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>673.05</v>
+        <v>661.3</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>3.95</v>
+        <v>-11.75</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>0.59</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2091</v>
+        <v>2091.8</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2104.9</v>
+        <v>2071.1</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2122.2</v>
+        <v>2088.9</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2075</v>
+        <v>2034</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2091.8</v>
+        <v>2065</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>0.8</v>
+        <v>-26.8</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>0.04</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4506.9</v>
+        <v>4522.7</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4488</v>
+        <v>4430</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4545.8</v>
+        <v>4432.3</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4465.7</v>
+        <v>4276.6</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4522.7</v>
+        <v>4299.4</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>15.8</v>
+        <v>-223.3</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>0.35</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>946.95</v>
+        <v>950.75</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>957.9</v>
+        <v>940.9</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>940.5</v>
+        <v>918.1</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>950.75</v>
+        <v>922.3</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>3.8</v>
+        <v>-28.45</v>
       </c>
       <c r="J93" s="13" t="n">
-        <v>0.4</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>402.9</v>
+        <v>404.3</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>403.9</v>
+        <v>402.8</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>406.55</v>
+        <v>415.45</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>397.6</v>
+        <v>396.5</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>404.3</v>
+        <v>410.65</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J94" s="13" t="n">
-        <v>0.35</v>
+        <v>6.35</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1162.7</v>
+        <v>1179.2</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1161</v>
+        <v>1176</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1183.5</v>
+        <v>1187</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1158.8</v>
+        <v>1172.1</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1179.2</v>
+        <v>1177</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>16.5</v>
+        <v>-2.2</v>
       </c>
       <c r="J95" s="13" t="n">
-        <v>1.42</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>146.89</v>
+        <v>144.69</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>145.8</v>
+        <v>143</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>146.3</v>
+        <v>143</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>144.19</v>
+        <v>140.04</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>144.69</v>
+        <v>140.37</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="J96" s="10" t="n">
-        <v>-1.5</v>
+        <v>-4.32</v>
+      </c>
+      <c r="J96" s="13" t="n">
+        <v>-2.99</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1560.1</v>
+        <v>1552.6</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1560.1</v>
+        <v>1557.2</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1610.5</v>
+        <v>1569</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1545.6</v>
+        <v>1525.2</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1552.6</v>
+        <v>1535</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="J97" s="10" t="n">
-        <v>-0.48</v>
+        <v>-17.6</v>
+      </c>
+      <c r="J97" s="13" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>568.5</v>
+        <v>564.9</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>566.05</v>
+        <v>562.55</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>570.85</v>
+        <v>562.55</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>564</v>
+        <v>552.1</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>564.9</v>
+        <v>556.8</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>-0.63</v>
+        <v>-8.1</v>
+      </c>
+      <c r="J98" s="13" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>307.4</v>
+        <v>307.45</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>308.9</v>
+        <v>307</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>308.9</v>
+        <v>308</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>305.7</v>
+        <v>305.15</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>307.45</v>
+        <v>305.85</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>0.05</v>
+        <v>-1.6</v>
       </c>
       <c r="J99" s="13" t="n">
-        <v>0.02</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1258.2</v>
+        <v>1248.4</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1258.2</v>
+        <v>1250</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1239.2</v>
+        <v>1230.2</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1248.4</v>
+        <v>1232</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="J100" s="10" t="n">
-        <v>-0.78</v>
+        <v>-16.4</v>
+      </c>
+      <c r="J100" s="13" t="n">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5626</v>
+        <v>5571.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5626</v>
+        <v>5490.5</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5642</v>
+        <v>5549</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5536</v>
+        <v>5416.5</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5571.5</v>
+        <v>5465</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-54.5</v>
-      </c>
-      <c r="J101" s="10" t="n">
-        <v>-0.97</v>
+        <v>-106.5</v>
+      </c>
+      <c r="J101" s="13" t="n">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>766.6</v>
+        <v>754.8</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>771.7</v>
+        <v>754.8</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>773.8</v>
+        <v>757</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>750.3</v>
+        <v>727.5</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>754.8</v>
+        <v>741.3</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>-1.54</v>
+        <v>-13.5</v>
+      </c>
+      <c r="J102" s="13" t="n">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>575.9</v>
+        <v>571.2</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>577.8</v>
+        <v>572</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>563.3</v>
+        <v>549.25</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>571.2</v>
+        <v>556.65</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>-0.82</v>
+        <v>-14.55</v>
+      </c>
+      <c r="J103" s="13" t="n">
+        <v>-2.55</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1283.4</v>
+        <v>1277.8</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1283.4</v>
+        <v>1276</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1284.9</v>
+        <v>1282.2</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1266.8</v>
+        <v>1258.6</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1277.8</v>
+        <v>1262.6</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>-0.44</v>
+        <v>-15.2</v>
+      </c>
+      <c r="J104" s="13" t="n">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>479</v>
+        <v>473.3</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>479.05</v>
+        <v>470.8</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>482.4</v>
+        <v>470.8</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>471.5</v>
+        <v>458.6</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>473.3</v>
+        <v>460.5</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>-1.19</v>
+        <v>-12.8</v>
+      </c>
+      <c r="J105" s="13" t="n">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1098.8</v>
+        <v>1104.1</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1098.8</v>
+        <v>1102.3</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1108.8</v>
+        <v>1125.6</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1092.1</v>
+        <v>1085.1</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1104.1</v>
+        <v>1095.5</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>5.3</v>
+        <v>-8.6</v>
       </c>
       <c r="J106" s="13" t="n">
-        <v>0.48</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>379.4</v>
+        <v>380.8</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>379</v>
+        <v>376.1</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>381.5</v>
+        <v>386</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>374</v>
+        <v>374.4</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>380.8</v>
+        <v>381.05</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J107" s="13" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
+      </c>
+      <c r="J107" s="10" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>722.65</v>
+        <v>729.15</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>722.6</v>
+        <v>728</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>735.8</v>
+        <v>737.2</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>729.15</v>
+        <v>733.45</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J108" s="13" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>0.59</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1565.5</v>
+        <v>1649.8</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1558</v>
+        <v>1637.9</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1660</v>
+        <v>1698</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1551.9</v>
+        <v>1629.3</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1649.8</v>
+        <v>1652.4</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="J109" s="13" t="n">
-        <v>5.38</v>
+        <v>2.6</v>
+      </c>
+      <c r="J109" s="10" t="n">
+        <v>0.16</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1205.3</v>
+        <v>1228.3</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1206</v>
+        <v>1232.5</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1237.9</v>
+        <v>1277.3</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1206</v>
+        <v>1221.4</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1228.3</v>
+        <v>1266.8</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v>1.91</v>
+        <v>38.5</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>3.13</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>586.35</v>
+        <v>581.5</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>586.35</v>
+        <v>578.85</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>587.5</v>
+        <v>598.2</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>578.05</v>
+        <v>571.2</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>581.5</v>
+        <v>585.6</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-4.85</v>
+        <v>4.1</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>-0.83</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>4023</v>
+        <v>3974.5</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>4010</v>
+        <v>3948</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>4014</v>
+        <v>3953.5</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3960</v>
+        <v>3886.1</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3974.5</v>
+        <v>3940.2</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="J112" s="10" t="n">
-        <v>-1.21</v>
+        <v>-34.3</v>
+      </c>
+      <c r="J112" s="13" t="n">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>303.65</v>
+        <v>303.4</v>
       </c>
       <c r="E113" s="9" t="n">
         <v>303</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>305.2</v>
+        <v>305</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>300.7</v>
+        <v>294.15</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>303.4</v>
+        <v>295</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J113" s="10" t="n">
-        <v>-0.08</v>
+        <v>-8.4</v>
+      </c>
+      <c r="J113" s="13" t="n">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="10" t="n">
+      <c r="J114" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3772.9</v>
+        <v>3802.6</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3795</v>
+        <v>3825</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3847.9</v>
+        <v>3844</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3774.1</v>
+        <v>3750</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3802.6</v>
+        <v>3788.4</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>29.7</v>
+        <v>-14.2</v>
       </c>
       <c r="J115" s="13" t="n">
-        <v>0.79</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2460.1</v>
+        <v>2379.5</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2425</v>
+        <v>2330.4</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2475</v>
+        <v>2330.4</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2347.9</v>
+        <v>2236.1</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2379.5</v>
+        <v>2255.9</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-80.59999999999999</v>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v>-3.28</v>
+        <v>-123.6</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>-5.19</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3370.7</v>
+        <v>3330.4</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3357.8</v>
+        <v>3235</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3363</v>
+        <v>3292</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3317.6</v>
+        <v>3224.2</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3330.4</v>
+        <v>3245.9</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-40.3</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>-1.2</v>
+        <v>-84.5</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>316.3</v>
+        <v>315.5</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>317</v>
+        <v>312.3</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>317.75</v>
+        <v>312.3</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>311.5</v>
+        <v>303.55</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>316</v>
+        <v>305.45</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="J118" s="10" t="n">
-        <v>-0.09</v>
+        <v>-10.05</v>
+      </c>
+      <c r="J118" s="13" t="n">
+        <v>-3.19</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>832.15</v>
+        <v>831.3</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>832.15</v>
+        <v>829.75</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>836.5</v>
+        <v>848.8</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>825.1</v>
+        <v>824.8</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>831.3</v>
+        <v>842.55</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-0.85</v>
+        <v>11.25</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>-0.1</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13770</v>
+        <v>13726</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13672</v>
+        <v>13547</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13789</v>
+        <v>13657</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13626</v>
+        <v>13231</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13726</v>
+        <v>13483</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-44</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>-0.32</v>
+        <v>-243</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="10" t="n">
+      <c r="J121" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3042.6</v>
+        <v>3097.8</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3069</v>
+        <v>3120</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3136</v>
+        <v>3219.6</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3022.4</v>
+        <v>3042.5</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3097.8</v>
+        <v>3187.9</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="J122" s="13" t="n">
-        <v>1.81</v>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="J122" s="10" t="n">
+        <v>2.91</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>505.6</v>
+        <v>549.5</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>574.9</v>
+        <v>568.9</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>511</v>
+        <v>544</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>549.5</v>
+        <v>559.9</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="J123" s="13" t="n">
-        <v>8.68</v>
+        <v>10.4</v>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>1.89</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1707.4</v>
+        <v>1699.7</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1718.8</v>
+        <v>1694</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1718.8</v>
+        <v>1703.9</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1686.1</v>
+        <v>1677</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1699.7</v>
+        <v>1695.5</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>-0.45</v>
+        <v>-4.2</v>
+      </c>
+      <c r="J124" s="13" t="n">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1179.8</v>
+        <v>1172.9</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1140</v>
+        <v>1160.8</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1179.2</v>
+        <v>1160.8</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1131.1</v>
+        <v>1101</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1172.9</v>
+        <v>1106.4</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-6.9</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>-0.58</v>
+        <v>-66.5</v>
+      </c>
+      <c r="J125" s="13" t="n">
+        <v>-5.67</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>130.43</v>
+        <v>132.03</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>130.99</v>
+        <v>130.58</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>132.76</v>
+        <v>131.39</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>130.52</v>
+        <v>128.94</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>132.03</v>
+        <v>130.3</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>1.6</v>
+        <v>-1.73</v>
       </c>
       <c r="J126" s="13" t="n">
-        <v>1.23</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2193.1</v>
+        <v>2214.2</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2199</v>
+        <v>2214.2</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2228</v>
+        <v>2222</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2182.9</v>
+        <v>2193.2</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2214.2</v>
+        <v>2201.2</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>21.1</v>
+        <v>-13</v>
       </c>
       <c r="J127" s="13" t="n">
-        <v>0.96</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>129965</v>
+        <v>130425</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>131745</v>
+        <v>130330</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>132000</v>
+        <v>130500</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>130135</v>
+        <v>128620</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>130425</v>
+        <v>128910</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>460</v>
+        <v>-1515</v>
       </c>
       <c r="J128" s="13" t="n">
-        <v>0.35</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3584.3</v>
+        <v>3528.9</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3594</v>
+        <v>3481.5</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3594</v>
+        <v>3493.9</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3514.1</v>
+        <v>3405</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3528.9</v>
+        <v>3438.2</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-55.4</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>-1.55</v>
+        <v>-90.7</v>
+      </c>
+      <c r="J129" s="13" t="n">
+        <v>-2.57</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>401.5</v>
+        <v>401.95</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>403.2</v>
+        <v>401.75</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>403.9</v>
+        <v>402.5</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>396.15</v>
+        <v>391.7</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>401.95</v>
+        <v>393.05</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>0.45</v>
+        <v>-8.9</v>
       </c>
       <c r="J130" s="13" t="n">
-        <v>0.11</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>981.85</v>
+        <v>978.35</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>981.85</v>
+        <v>978.35</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>988.8</v>
+        <v>980.95</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>973.3</v>
+        <v>956.95</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>978.35</v>
+        <v>961.2</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>-0.36</v>
+        <v>-17.15</v>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v>-1.75</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>7085</v>
+        <v>7041.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>7049</v>
+        <v>7000</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>7095.5</v>
+        <v>7120</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6996.5</v>
+        <v>6945</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>7041.5</v>
+        <v>7071.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-43.5</v>
+        <v>30</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>-0.61</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1476</v>
+        <v>1482.4</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1476.6</v>
+        <v>1475.3</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1496.3</v>
+        <v>1498.1</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1470</v>
+        <v>1470.5</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1482.4</v>
+        <v>1481.9</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>6.4</v>
+        <v>-0.5</v>
       </c>
       <c r="J133" s="13" t="n">
-        <v>0.43</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>90.14</v>
+        <v>88.8</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>90.05</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>90.5</v>
+        <v>88.3</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>88.67</v>
+        <v>86.59</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>88.8</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="J134" s="10" t="n">
-        <v>-1.49</v>
+        <v>-2.01</v>
+      </c>
+      <c r="J134" s="13" t="n">
+        <v>-2.26</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>400.35</v>
+        <v>402.15</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>398</v>
+        <v>401.9</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>405.1</v>
+        <v>405</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>397.15</v>
+        <v>391</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>402.15</v>
+        <v>392.95</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>1.8</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="J135" s="13" t="n">
-        <v>0.45</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1675</v>
+        <v>1703</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1681</v>
+        <v>1712.8</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1715</v>
+        <v>1712.8</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1666.9</v>
+        <v>1630.6</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1703</v>
+        <v>1634.7</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>28</v>
+        <v>-68.3</v>
       </c>
       <c r="J136" s="13" t="n">
-        <v>1.67</v>
+        <v>-4.01</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9498.5</v>
+        <v>9345.5</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9500.5</v>
+        <v>9395</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9580</v>
+        <v>9401.5</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9301</v>
+        <v>9190</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9345.5</v>
+        <v>9239.5</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-153</v>
-      </c>
-      <c r="J137" s="10" t="n">
-        <v>-1.61</v>
+        <v>-106</v>
+      </c>
+      <c r="J137" s="13" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>283.9</v>
+        <v>279.2</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>283.6</v>
+        <v>280.7</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>284</v>
+        <v>281.8</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>278.6</v>
+        <v>277.65</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>279.2</v>
+        <v>281</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>-4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J138" s="10" t="n">
-        <v>-1.66</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37345</v>
+        <v>37365</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37200</v>
+        <v>37220</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37500</v>
+        <v>37305</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>36840</v>
+        <v>36120</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>37365</v>
+        <v>36245</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>20</v>
+        <v>-1120</v>
       </c>
       <c r="J139" s="13" t="n">
-        <v>0.05</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="10" t="n">
+      <c r="J140" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4984</v>
+        <v>5113.6</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>4990</v>
+        <v>5124.9</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5137</v>
+        <v>5173.3</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4960</v>
+        <v>5080</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5113.6</v>
+        <v>5098.1</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>129.6</v>
+        <v>-15.5</v>
       </c>
       <c r="J141" s="13" t="n">
-        <v>2.6</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>282.1</v>
+        <v>283.8</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>282.1</v>
+        <v>282.25</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>286.25</v>
+        <v>282.25</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>278.95</v>
+        <v>275</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>283.8</v>
+        <v>275.75</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>1.7</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="J142" s="13" t="n">
-        <v>0.6</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>457.55</v>
+        <v>461.35</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>467.25</v>
+        <v>459.45</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>455.55</v>
+        <v>447.4</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>461.35</v>
+        <v>448.5</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>3.8</v>
+        <v>-12.85</v>
       </c>
       <c r="J143" s="13" t="n">
-        <v>0.83</v>
+        <v>-2.79</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1450.4</v>
+        <v>1476</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1503.6</v>
+        <v>1468.5</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1515</v>
+        <v>1468.5</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1470</v>
+        <v>1432</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1476</v>
+        <v>1437.2</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>25.6</v>
+        <v>-38.8</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>1.77</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3101.5</v>
+        <v>3110.8</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3099</v>
+        <v>3101</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3134.7</v>
+        <v>3110</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3067.5</v>
+        <v>3055</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3110.8</v>
+        <v>3090.8</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>9.300000000000001</v>
+        <v>-20</v>
       </c>
       <c r="J145" s="13" t="n">
-        <v>0.3</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>109.11</v>
+        <v>107.24</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>108.9</v>
+        <v>106.2</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>108.9</v>
+        <v>106.45</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>106.62</v>
+        <v>104.33</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>107.24</v>
+        <v>104.62</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-1.87</v>
-      </c>
-      <c r="J146" s="10" t="n">
-        <v>-1.71</v>
+        <v>-2.62</v>
+      </c>
+      <c r="J146" s="13" t="n">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>9003</v>
+        <v>9083</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>9030</v>
+        <v>9004.5</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>9159</v>
+        <v>9136</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8952.5</v>
+        <v>8963</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>9083</v>
+        <v>9065.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>80</v>
+        <v>-17.5</v>
       </c>
       <c r="J147" s="13" t="n">
-        <v>0.89</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>313.8</v>
+        <v>313.95</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>315.2</v>
+        <v>313.95</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>315.2</v>
+        <v>314.05</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>310.6</v>
+        <v>309.95</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>313.95</v>
+        <v>310.9</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>0.15</v>
+        <v>-3.05</v>
       </c>
       <c r="J148" s="13" t="n">
-        <v>0.05</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1066.1</v>
+        <v>1073.8</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1061.1</v>
+        <v>1074.9</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1077.1</v>
+        <v>1110</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1061.1</v>
+        <v>1017</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1073.8</v>
+        <v>1026</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>7.7</v>
+        <v>-47.8</v>
       </c>
       <c r="J149" s="13" t="n">
-        <v>0.72</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>345.75</v>
+        <v>343.45</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>348</v>
+        <v>341.3</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>349.7</v>
+        <v>342.6</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>339.4</v>
+        <v>334.25</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>343.45</v>
+        <v>337.5</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="J150" s="10" t="n">
-        <v>-0.67</v>
+        <v>-5.95</v>
+      </c>
+      <c r="J150" s="13" t="n">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>359.75</v>
+        <v>359.4</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>359.75</v>
+        <v>358</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>363.6</v>
+        <v>358.8</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>356.15</v>
+        <v>350.5</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>359.4</v>
+        <v>351.55</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>-0.1</v>
+        <v>-7.85</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1436.2</v>
+        <v>1435.2</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1426</v>
+        <v>1420</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1442.8</v>
+        <v>1428</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1417.5</v>
+        <v>1382</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1435.2</v>
+        <v>1388.2</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J152" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-47</v>
+      </c>
+      <c r="J152" s="13" t="n">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>187.28</v>
+        <v>184.88</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>187</v>
+        <v>182.89</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>187.7</v>
+        <v>184.87</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>184.15</v>
+        <v>179.91</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>184.88</v>
+        <v>180.72</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="J153" s="10" t="n">
-        <v>-1.28</v>
+        <v>-4.16</v>
+      </c>
+      <c r="J153" s="13" t="n">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>648.15</v>
+        <v>645.4</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>649.95</v>
+        <v>642</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>650.75</v>
+        <v>645.85</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>643.8</v>
+        <v>634.3</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>645.4</v>
+        <v>641.5</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="J154" s="10" t="n">
-        <v>-0.42</v>
+        <v>-3.9</v>
+      </c>
+      <c r="J154" s="13" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1872.2</v>
+        <v>1872.1</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1874.9</v>
+        <v>1865.6</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1865.2</v>
+        <v>1863.9</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1872.1</v>
+        <v>1884.4</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-0.1</v>
+        <v>12.3</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>-0.01</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1092</v>
+        <v>1019.3</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1090</v>
+        <v>1007</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1095</v>
+        <v>1007</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>1010.9</v>
+        <v>971.1</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>1019.3</v>
+        <v>973.6</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-72.7</v>
-      </c>
-      <c r="J156" s="10" t="n">
-        <v>-6.66</v>
+        <v>-45.7</v>
+      </c>
+      <c r="J156" s="13" t="n">
+        <v>-4.48</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>25595</v>
+        <v>25435</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25590</v>
+        <v>25190</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25590</v>
+        <v>25385</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>25165</v>
+        <v>25000</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>25435</v>
+        <v>25205</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-160</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>-0.63</v>
+        <v>-230</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1015.65</v>
+        <v>1007.75</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>1013</v>
+        <v>990</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>1013.35</v>
+        <v>990.85</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>1001.25</v>
+        <v>970.45</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>1007.75</v>
+        <v>975.95</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-7.9</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>-0.78</v>
+        <v>-31.8</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>-3.16</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3871.5</v>
+        <v>3822.6</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3871.6</v>
+        <v>3720</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3906.9</v>
+        <v>3720</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3786</v>
+        <v>3552.9</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3822.6</v>
+        <v>3605.6</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-48.9</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>-1.26</v>
+        <v>-217</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>-5.68</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2771.3</v>
+        <v>2780.8</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2775.4</v>
+        <v>2777</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2819.3</v>
+        <v>2832.1</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2770</v>
+        <v>2739.6</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2780.8</v>
+        <v>2798.5</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J160" s="13" t="n">
-        <v>0.34</v>
+        <v>17.7</v>
+      </c>
+      <c r="J160" s="10" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1834.4</v>
+        <v>1847.9</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1822</v>
+        <v>1827.2</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1857.5</v>
+        <v>1885.8</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1819.2</v>
+        <v>1825</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1847.9</v>
+        <v>1872.7</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J161" s="13" t="n">
-        <v>0.74</v>
+        <v>24.8</v>
+      </c>
+      <c r="J161" s="10" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>571.1</v>
+        <v>573.55</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>574</v>
+        <v>572.5</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>575.45</v>
+        <v>574.5</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>569</v>
+        <v>560.95</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>573.55</v>
+        <v>567.75</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>2.45</v>
+        <v>-5.8</v>
       </c>
       <c r="J162" s="13" t="n">
-        <v>0.43</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>467.35</v>
+        <v>458.1</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>466.6</v>
+        <v>455</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>469.9</v>
+        <v>490.7</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>456.15</v>
+        <v>453.4</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>458.1</v>
+        <v>482.5</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-9.25</v>
+        <v>24.4</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>-1.98</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>805.35</v>
+        <v>781.55</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>805.35</v>
+        <v>777</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>809.7</v>
+        <v>777</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>778</v>
+        <v>756</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>781.55</v>
+        <v>761.35</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-23.8</v>
-      </c>
-      <c r="J164" s="10" t="n">
-        <v>-2.96</v>
+        <v>-20.2</v>
+      </c>
+      <c r="J164" s="13" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1593.5</v>
+        <v>1592.3</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1593.9</v>
+        <v>1576.9</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1609.4</v>
+        <v>1592</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1575.1</v>
+        <v>1560</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1592.3</v>
+        <v>1571.5</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J165" s="10" t="n">
-        <v>-0.08</v>
+        <v>-20.8</v>
+      </c>
+      <c r="J165" s="13" t="n">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1151.7</v>
+        <v>1176.2</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1155</v>
+        <v>1202.2</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1194</v>
+        <v>1279.4</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1155</v>
+        <v>1200</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1176.2</v>
+        <v>1271</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="J166" s="13" t="n">
-        <v>2.13</v>
+        <v>94.8</v>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>8.06</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="10" t="n">
+      <c r="J167" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>439.25</v>
+        <v>436</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>438.1</v>
+        <v>434</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>440.6</v>
+        <v>437.95</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>434.7</v>
+        <v>428.7</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>436</v>
+        <v>433.2</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="J168" s="10" t="n">
-        <v>-0.74</v>
+        <v>-2.8</v>
+      </c>
+      <c r="J168" s="13" t="n">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>217.09</v>
+        <v>214.49</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>217</v>
+        <v>213.5</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>217.4</v>
+        <v>215</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>214.25</v>
+        <v>211.52</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>214.49</v>
+        <v>212.08</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="J169" s="10" t="n">
-        <v>-1.2</v>
+        <v>-2.41</v>
+      </c>
+      <c r="J169" s="13" t="n">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2401.4</v>
+        <v>2394.4</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2398</v>
+        <v>2371</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2407</v>
+        <v>2415</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2375.1</v>
+        <v>2371</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2394.4</v>
+        <v>2392.9</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-7</v>
-      </c>
-      <c r="J170" s="10" t="n">
-        <v>-0.29</v>
+        <v>-1.5</v>
+      </c>
+      <c r="J170" s="13" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1448.2</v>
+        <v>1463</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1453.5</v>
+        <v>1460</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1469.8</v>
+        <v>1475.4</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1448.4</v>
+        <v>1451.8</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1463</v>
+        <v>1457.4</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>14.8</v>
+        <v>-5.6</v>
       </c>
       <c r="J171" s="13" t="n">
-        <v>1.02</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>3015.5</v>
+        <v>3049.8</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>3008.9</v>
+        <v>3046.1</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3066</v>
+        <v>3046.1</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2980</v>
+        <v>2966</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>3049.8</v>
+        <v>2992.2</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>34.3</v>
+        <v>-57.6</v>
       </c>
       <c r="J172" s="13" t="n">
-        <v>1.14</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4307.5</v>
+        <v>4509</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4314</v>
+        <v>4350.4</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4605</v>
+        <v>4379.5</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4213.4</v>
+        <v>4150.1</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4509</v>
+        <v>4205.6</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>201.5</v>
+        <v>-303.4</v>
       </c>
       <c r="J173" s="13" t="n">
-        <v>4.68</v>
+        <v>-6.73</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4362.7</v>
+        <v>4380.8</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4350</v>
+        <v>4406.3</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4398.4</v>
+        <v>4555.1</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4336.7</v>
+        <v>4337.9</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4380.8</v>
+        <v>4517.1</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J174" s="13" t="n">
-        <v>0.41</v>
+        <v>136.3</v>
+      </c>
+      <c r="J174" s="10" t="n">
+        <v>3.11</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1712.5</v>
+        <v>1724.4</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1715.1</v>
+        <v>1724.4</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1734.9</v>
+        <v>1725.9</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1710</v>
+        <v>1667.8</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1724.4</v>
+        <v>1680.9</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>11.9</v>
+        <v>-43.5</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4294.1</v>
+        <v>4242.3</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4283.2</v>
+        <v>4227.2</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4318.9</v>
+        <v>4239</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4221.9</v>
+        <v>4153.3</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4242.3</v>
+        <v>4181.1</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-51.8</v>
-      </c>
-      <c r="J176" s="10" t="n">
-        <v>-1.21</v>
+        <v>-61.2</v>
+      </c>
+      <c r="J176" s="13" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3706.7</v>
+        <v>3695.2</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3654.5</v>
+        <v>3651</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3718.7</v>
+        <v>3684.9</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3633.1</v>
+        <v>3601</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3695.2</v>
+        <v>3613.7</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>-0.31</v>
+        <v>-81.5</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1428.2</v>
+        <v>1419.8</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1429</v>
+        <v>1420</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1441.9</v>
+        <v>1423.9</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1415.5</v>
+        <v>1395</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1419.8</v>
+        <v>1412.2</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v>-0.59</v>
+        <v>-7.6</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>12146</v>
+        <v>11950</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>12090</v>
+        <v>11801</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>12110</v>
+        <v>11937</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11877</v>
+        <v>11773</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11950</v>
+        <v>11866</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-196</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>-1.61</v>
+        <v>-84</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>167.28</v>
+        <v>166.24</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>166.5</v>
+        <v>165</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>167.28</v>
+        <v>166.2</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>164.5</v>
+        <v>163.23</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>166.24</v>
+        <v>163.81</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="J180" s="10" t="n">
-        <v>-0.62</v>
+        <v>-2.43</v>
+      </c>
+      <c r="J180" s="13" t="n">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>650.45</v>
+        <v>646</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>653.65</v>
+        <v>644</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>654.3</v>
+        <v>682.6</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>643.5</v>
+        <v>634.05</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-4.45</v>
+        <v>23</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>-0.68</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>305.4</v>
+        <v>296.45</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>305.65</v>
+        <v>296.6</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>306.4</v>
+        <v>301.55</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>295.9</v>
+        <v>294.2</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>296.45</v>
+        <v>298.4</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>-8.949999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="J182" s="10" t="n">
-        <v>-2.93</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1363.9</v>
+        <v>1324.8</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1363</v>
+        <v>1315.6</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1363</v>
+        <v>1322.5</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1321</v>
+        <v>1299</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1324.8</v>
+        <v>1306.5</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-39.1</v>
-      </c>
-      <c r="J183" s="10" t="n">
-        <v>-2.87</v>
+        <v>-18.3</v>
+      </c>
+      <c r="J183" s="13" t="n">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>197.36</v>
+        <v>197.91</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>198</v>
+        <v>197.88</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>198.94</v>
+        <v>198.24</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>196.7</v>
+        <v>196.15</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>197.91</v>
+        <v>196.68</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>0.55</v>
+        <v>-1.23</v>
       </c>
       <c r="J184" s="13" t="n">
-        <v>0.28</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="10" t="n">
+      <c r="J185" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>940.3</v>
+        <v>940.05</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>938.05</v>
+        <v>940</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>953</v>
+        <v>962</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>935.55</v>
+        <v>927</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>940.05</v>
+        <v>956.95</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-0.25</v>
+        <v>16.9</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>-0.03</v>
+        <v>1.8</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  08-May-2026 02:51 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  11-May-2026 03:55 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08-May-2026 02:51 PM</t>
+          <t>11-May-2026 03:55 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 11-May-2026 03:55 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 12-May-2026 03:39 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>11-May-2026 03:55 PM</t>
+          <t>12-May-2026 03:39 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  11-May-2026 03:55 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  12-May-2026 03:39 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>485.45</v>
+        <v>487.45</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>498</v>
+        <v>489.3</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>475</v>
+        <v>461.15</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>487.45</v>
+        <v>468.5</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>2</v>
+        <v>-18.95</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.41</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>7012.5</v>
+        <v>6387.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>6662</v>
+        <v>6360</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>6687</v>
+        <v>6403</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>6323.5</v>
+        <v>6171.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>6387.5</v>
+        <v>6328.5</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-625</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>-8.91</v>
+        <v>-59</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>26700</v>
+        <v>27795</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>26700</v>
+        <v>28000</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>27910</v>
+        <v>28000</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>26335</v>
+        <v>26685</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>27795</v>
+        <v>26900</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1095</v>
+        <v>-895</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>4.1</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>362.95</v>
+        <v>352.95</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>358</v>
+        <v>352.45</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>358.5</v>
+        <v>354</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>351.35</v>
+        <v>340</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>352.95</v>
+        <v>341.2</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>-2.76</v>
+        <v>-11.75</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>-3.33</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>66.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>65.55</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>65.78</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>64.20999999999999</v>
+        <v>62.25</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>64.98999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>-2.02</v>
+        <v>-2.59</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>-3.99</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1391.9</v>
+        <v>1357.9</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1385</v>
+        <v>1354</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1390</v>
+        <v>1370</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1340.4</v>
+        <v>1340</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1357.9</v>
+        <v>1347</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-34</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>-2.44</v>
+        <v>-10.9</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2505.9</v>
+        <v>2500.2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2495</v>
+        <v>2487.7</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2514</v>
+        <v>2511.7</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2460</v>
+        <v>2400.1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2500.2</v>
+        <v>2405.2</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>-0.23</v>
+        <v>-95</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>-3.8</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1760.4</v>
+        <v>1767.3</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1757.1</v>
+        <v>1752</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1785.6</v>
+        <v>1765.9</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1733.1</v>
+        <v>1683.2</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1767.3</v>
+        <v>1688.2</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>6.9</v>
+        <v>-79.09999999999999</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.39</v>
+        <v>-4.48</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5585.5</v>
+        <v>5599.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5585</v>
+        <v>5624</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5673</v>
+        <v>5624</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5494.5</v>
+        <v>5482.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5599.5</v>
+        <v>5496.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>14</v>
+        <v>-103</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>0.25</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>444.3</v>
+        <v>436.2</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>441.75</v>
+        <v>434.9</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>441.75</v>
+        <v>442</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>432.4</v>
+        <v>425.2</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>436.2</v>
+        <v>426.95</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>-1.82</v>
+        <v>-9.25</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>326</v>
+        <v>317.2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>323.75</v>
+        <v>315.65</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>326.95</v>
+        <v>315.95</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>316.15</v>
+        <v>296.95</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>317.2</v>
+        <v>299.1</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>-2.7</v>
+        <v>-18.1</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>-5.71</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1948.6</v>
+        <v>1949.8</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1967.6</v>
+        <v>1962</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1926.9</v>
+        <v>1876.1</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1949.8</v>
+        <v>1881.2</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>1.2</v>
+        <v>-68.59999999999999</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.06</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8097</v>
+        <v>8082</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8046</v>
+        <v>8050</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8144</v>
+        <v>8078</v>
       </c>
       <c r="G15" s="9" t="n">
+        <v>7995</v>
+      </c>
+      <c r="H15" s="9" t="n">
         <v>8022.5</v>
       </c>
-      <c r="H15" s="9" t="n">
-        <v>8082</v>
-      </c>
       <c r="I15" s="9" t="n">
-        <v>-15</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>-0.19</v>
+        <v>-59.5</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>409.25</v>
+        <v>405.7</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>408.45</v>
+        <v>405.65</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>409</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>401.2</v>
+        <v>397.45</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>405.7</v>
+        <v>398.75</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-3.55</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>-0.87</v>
+        <v>-6.95</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>168.57</v>
+        <v>161.52</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>166.38</v>
+        <v>160.8</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>166.38</v>
+        <v>161.47</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>161</v>
+        <v>155.1</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>161.52</v>
+        <v>155.95</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-7.05</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>-4.18</v>
+        <v>-5.57</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-3.45</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2599.9</v>
+        <v>2566.1</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2578.9</v>
+        <v>2546.2</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2607.9</v>
+        <v>2555.7</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2555</v>
+        <v>2500</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2566.1</v>
+        <v>2505.5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-33.8</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>-1.3</v>
+        <v>-60.6</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>-2.36</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1569.8</v>
+        <v>1572.1</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1571.1</v>
+        <v>1565</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1590</v>
+        <v>1579.6</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1560</v>
+        <v>1524.1</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1572.1</v>
+        <v>1527.6</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>2.3</v>
+        <v>-44.5</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>0.15</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>633.05</v>
+        <v>620.5</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>629.8</v>
+        <v>619.95</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>629.8</v>
+        <v>623.75</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>615.7</v>
+        <v>588.1</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>620.5</v>
+        <v>591.3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-12.55</v>
-      </c>
-      <c r="J20" s="13" t="n">
-        <v>-1.98</v>
+        <v>-29.2</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>-4.71</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>7088.5</v>
+        <v>6892</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>7050</v>
+        <v>6870</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7051</v>
+        <v>6939.5</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6870</v>
+        <v>6804</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6892</v>
+        <v>6851.5</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-196.5</v>
-      </c>
-      <c r="J21" s="13" t="n">
-        <v>-2.77</v>
+        <v>-40.5</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1050.4</v>
+        <v>1021.4</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1045</v>
+        <v>1020.6</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1045</v>
+        <v>1022.4</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1017.6</v>
+        <v>997.3</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1021.4</v>
+        <v>999.6</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-29</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>-2.76</v>
+        <v>-21.8</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1487.3</v>
+        <v>1486.6</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1487.3</v>
+        <v>1486.6</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1505.5</v>
+        <v>1504</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1477.4</v>
+        <v>1478.6</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1486.6</v>
+        <v>1488.2</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>-0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>-0.05</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1268.3</v>
+        <v>1272.3</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1258.7</v>
+        <v>1270.4</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1251.7</v>
+        <v>1256.9</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1272.3</v>
+        <v>1260.1</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>4</v>
+        <v>-12.2</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.32</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>10711.5</v>
+        <v>10595.5</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10599</v>
+        <v>10550</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10650</v>
+        <v>10684.5</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10511</v>
+        <v>10366</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>10595.5</v>
+        <v>10397</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-116</v>
-      </c>
-      <c r="J25" s="13" t="n">
-        <v>-1.08</v>
+        <v>-198.5</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1818.3</v>
+        <v>1794.2</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1804.2</v>
+        <v>1783.8</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1814</v>
+        <v>1791</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1786</v>
+        <v>1741.5</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1794.2</v>
+        <v>1744.8</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-24.1</v>
-      </c>
-      <c r="J26" s="13" t="n">
-        <v>-1.33</v>
+        <v>-49.4</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>955.35</v>
+        <v>936.05</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>946</v>
+        <v>928</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>956</v>
+        <v>932.65</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>933.55</v>
+        <v>901.75</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>936.05</v>
+        <v>904.2</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-19.3</v>
-      </c>
-      <c r="J27" s="13" t="n">
-        <v>-2.02</v>
+        <v>-31.85</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2262.5</v>
+        <v>2181.9</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2250</v>
+        <v>2181.9</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2250</v>
+        <v>2205</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2148.5</v>
+        <v>2084.1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2181.9</v>
+        <v>2110.6</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-80.59999999999999</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>-3.56</v>
+        <v>-71.3</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>522.75</v>
+        <v>525.4</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>520.7</v>
+        <v>525.25</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>530.95</v>
+        <v>536.45</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>511.95</v>
+        <v>521.45</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>525.4</v>
+        <v>534.15</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="J29" s="10" t="n">
-        <v>0.51</v>
+        <v>8.75</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>206.11</v>
+        <v>201.23</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>203.52</v>
+        <v>200</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>204.9</v>
+        <v>203.8</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>199.91</v>
+        <v>195.46</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>201.23</v>
+        <v>196.07</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-4.88</v>
-      </c>
-      <c r="J30" s="13" t="n">
-        <v>-2.37</v>
+        <v>-5.16</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>-2.56</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>263.9</v>
+        <v>266</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>265.9</v>
+        <v>263.95</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>269.7</v>
+        <v>267.45</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>262.35</v>
+        <v>259.15</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>266</v>
+        <v>259.95</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>2.1</v>
+        <v>-6.05</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>0.8</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>439.7</v>
+        <v>431.95</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>438</v>
+        <v>430.2</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>439.15</v>
+        <v>432.5</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>431</v>
+        <v>415.5</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>431.95</v>
+        <v>416.5</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-7.75</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>-1.76</v>
+        <v>-15.45</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>-3.58</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>515.75</v>
+        <v>493.85</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>511.95</v>
+        <v>490</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>511.95</v>
+        <v>498.55</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>491.05</v>
+        <v>479</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>493.85</v>
+        <v>488.1</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-21.9</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>-4.25</v>
+        <v>-5.75</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1834.5</v>
+        <v>1759.8</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1814</v>
+        <v>1751.5</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1819.8</v>
+        <v>1776.5</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1756</v>
+        <v>1751.5</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1759.8</v>
+        <v>1756.8</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-74.7</v>
-      </c>
-      <c r="J34" s="13" t="n">
-        <v>-4.07</v>
+        <v>-3</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>404.6</v>
+        <v>401.35</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>400</v>
+        <v>397.1</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>406.6</v>
+        <v>407.2</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>393.05</v>
+        <v>390.55</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>401.35</v>
+        <v>391.75</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>-0.8</v>
+        <v>-9.6</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>380.4</v>
+        <v>390.45</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>380.45</v>
+        <v>392.9</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>396.25</v>
+        <v>406.6</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>371.75</v>
+        <v>392.25</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>390.45</v>
+        <v>402.45</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>2.64</v>
+        <v>12</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>3.07</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>38145</v>
+        <v>37315</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>38020</v>
+        <v>37315</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>38020</v>
+        <v>37625</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>37220</v>
+        <v>36345</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>37315</v>
+        <v>36510</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-830</v>
-      </c>
-      <c r="J37" s="13" t="n">
-        <v>-2.18</v>
+        <v>-805</v>
+      </c>
+      <c r="J37" s="10" t="n">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>302.75</v>
+        <v>294.45</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>298.75</v>
+        <v>286</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>299.4</v>
+        <v>293.7</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>293.75</v>
+        <v>286</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>294.45</v>
+        <v>287.85</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="J38" s="13" t="n">
-        <v>-2.74</v>
+        <v>-6.6</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5520</v>
+        <v>5410.5</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5505.5</v>
+        <v>5403.5</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5508</v>
+        <v>5425</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5395</v>
+        <v>5315</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5410.5</v>
+        <v>5334</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-109.5</v>
-      </c>
-      <c r="J39" s="13" t="n">
-        <v>-1.98</v>
+        <v>-76.5</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>362.15</v>
+        <v>355.9</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>360</v>
+        <v>354.5</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>360.3</v>
+        <v>354.5</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>352.85</v>
+        <v>330</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>355.9</v>
+        <v>331.6</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-6.25</v>
-      </c>
-      <c r="J40" s="13" t="n">
-        <v>-1.73</v>
+        <v>-24.3</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>-6.83</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>134.34</v>
+        <v>129.43</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>133.02</v>
+        <v>127.66</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>139.4</v>
+        <v>132.35</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>128.58</v>
+        <v>127.43</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>129.43</v>
+        <v>130.01</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-4.91</v>
+        <v>0.58</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>-3.65</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>879.55</v>
+        <v>855.3</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>875</v>
+        <v>856.1</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>876.8</v>
+        <v>862.85</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>852</v>
+        <v>826.4</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>855.3</v>
+        <v>831.85</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-24.25</v>
-      </c>
-      <c r="J42" s="13" t="n">
-        <v>-2.76</v>
+        <v>-23.45</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>455.8</v>
+        <v>452.3</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>451</v>
+        <v>452.3</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>456.5</v>
+        <v>452.3</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>446</v>
+        <v>431.5</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>452.3</v>
+        <v>433.9</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>-0.77</v>
+        <v>-18.4</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>-4.07</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1674.1</v>
+        <v>1624.5</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1630.4</v>
+        <v>1617.2</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1646.4</v>
+        <v>1628.8</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1621</v>
+        <v>1556.5</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1624.5</v>
+        <v>1561</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-49.6</v>
-      </c>
-      <c r="J44" s="13" t="n">
-        <v>-2.96</v>
+        <v>-63.5</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>-3.91</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1347</v>
+        <v>1304.9</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1347</v>
+        <v>1304.6</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1350</v>
+        <v>1309</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1300.1</v>
+        <v>1289</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1304.9</v>
+        <v>1292.3</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-42.1</v>
-      </c>
-      <c r="J45" s="13" t="n">
-        <v>-3.13</v>
+        <v>-12.6</v>
+      </c>
+      <c r="J45" s="10" t="n">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>456.4</v>
+        <v>464.45</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>465.75</v>
+        <v>469</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>452.85</v>
+        <v>461.65</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>464.45</v>
+        <v>463.05</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>8.050000000000001</v>
+        <v>-1.4</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>1.76</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1368.1</v>
+        <v>1375.2</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1375.8</v>
+        <v>1373.4</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1387.8</v>
+        <v>1373.4</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1359.6</v>
+        <v>1316.9</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1375.2</v>
+        <v>1320.4</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>7.1</v>
+        <v>-54.8</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>0.52</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2197.4</v>
+        <v>2139</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2196.9</v>
+        <v>2139.9</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2204.2</v>
+        <v>2157.2</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2132.4</v>
+        <v>2118</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2139</v>
+        <v>2125.2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-58.4</v>
-      </c>
-      <c r="J48" s="13" t="n">
-        <v>-2.66</v>
+        <v>-13.8</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>534.75</v>
+        <v>530</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>535.75</v>
+        <v>527.35</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>535.75</v>
+        <v>529.65</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>528.05</v>
+        <v>511.6</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-4.75</v>
-      </c>
-      <c r="J49" s="13" t="n">
-        <v>-0.89</v>
+        <v>-14</v>
+      </c>
+      <c r="J49" s="10" t="n">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1927.6</v>
+        <v>1866.2</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1924.9</v>
+        <v>1880</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1925</v>
+        <v>1909.5</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1858.4</v>
+        <v>1839.3</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1866.2</v>
+        <v>1872.7</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-61.4</v>
+        <v>6.5</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>-3.19</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>293.3</v>
+        <v>290.2</v>
       </c>
       <c r="E51" s="9" t="n">
+        <v>290</v>
+      </c>
+      <c r="F51" s="9" t="n">
         <v>290.2</v>
       </c>
-      <c r="F51" s="9" t="n">
-        <v>292.9</v>
-      </c>
       <c r="G51" s="9" t="n">
-        <v>285.7</v>
+        <v>280.3</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>290.2</v>
+        <v>282.05</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="J51" s="13" t="n">
-        <v>-1.06</v>
+        <v>-8.15</v>
+      </c>
+      <c r="J51" s="10" t="n">
+        <v>-2.81</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>260.35</v>
+        <v>254.2</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>258.85</v>
+        <v>254.2</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>258.85</v>
+        <v>254.9</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>249.3</v>
+        <v>243.1</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>254.2</v>
+        <v>244.45</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-6.15</v>
-      </c>
-      <c r="J52" s="13" t="n">
-        <v>-2.36</v>
+        <v>-9.75</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>-3.84</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5401</v>
+        <v>5238.5</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5350</v>
+        <v>5265</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5350</v>
+        <v>5265</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5191</v>
+        <v>5147.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5238.5</v>
+        <v>5160</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-162.5</v>
-      </c>
-      <c r="J53" s="13" t="n">
-        <v>-3.01</v>
+        <v>-78.5</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>487.7</v>
+        <v>473.45</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>485</v>
+        <v>472.75</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>485</v>
+        <v>476.25</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>471.2</v>
+        <v>469.55</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>473.45</v>
+        <v>473.25</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-14.25</v>
-      </c>
-      <c r="J54" s="13" t="n">
-        <v>-2.92</v>
+        <v>-0.2</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1823.6</v>
+        <v>1772.2</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1825</v>
+        <v>1772.2</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1834.8</v>
+        <v>1803.4</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1761</v>
+        <v>1760.6</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1772.2</v>
+        <v>1781.2</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-51.4</v>
+        <v>9</v>
       </c>
       <c r="J55" s="13" t="n">
-        <v>-2.82</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1875.9</v>
+        <v>1863.6</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1865</v>
+        <v>1854.4</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1895</v>
+        <v>1897.9</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1814.3</v>
+        <v>1783.5</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1863.6</v>
+        <v>1848.3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-12.3</v>
-      </c>
-      <c r="J56" s="13" t="n">
-        <v>-0.66</v>
+        <v>-15.3</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>77.65000000000001</v>
+        <v>74.53</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>77.45</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>77.45</v>
+        <v>75</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>74.08</v>
+        <v>71.8</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>74.53</v>
+        <v>72.14</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-3.12</v>
-      </c>
-      <c r="J57" s="13" t="n">
-        <v>-4.02</v>
+        <v>-2.39</v>
+      </c>
+      <c r="J57" s="10" t="n">
+        <v>-3.21</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6710.5</v>
+        <v>6714</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6700</v>
+        <v>6710</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6785</v>
+        <v>6745</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6650</v>
+        <v>6636</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6714</v>
+        <v>6644</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>3.5</v>
+        <v>-70</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>0.05</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>10803</v>
+        <v>10772</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>10773</v>
+        <v>10744</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>10956</v>
+        <v>10744</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>10537</v>
+        <v>10100</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>10772</v>
+        <v>10138</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-31</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>-0.29</v>
+        <v>-634</v>
+      </c>
+      <c r="J59" s="10" t="n">
+        <v>-5.89</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>608.25</v>
+        <v>590.25</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>600</v>
+        <v>586.9</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>600</v>
+        <v>590.6</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>588.6</v>
+        <v>566.3</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>590.25</v>
+        <v>569.2</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-18</v>
-      </c>
-      <c r="J60" s="13" t="n">
-        <v>-2.96</v>
+        <v>-21.05</v>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>-3.57</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1293.9</v>
+        <v>1279.9</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1288</v>
+        <v>1278.9</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1299.9</v>
+        <v>1288.3</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1272.5</v>
+        <v>1264.5</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1279.9</v>
+        <v>1270</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-14</v>
-      </c>
-      <c r="J61" s="13" t="n">
-        <v>-1.08</v>
+        <v>-9.9</v>
+      </c>
+      <c r="J61" s="10" t="n">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7302.5</v>
+        <v>7202.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7269</v>
+        <v>7203.5</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7269</v>
+        <v>7275.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7159</v>
+        <v>7105</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7202.5</v>
+        <v>7126</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>-1.37</v>
+        <v>-76.5</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>3146.6</v>
+        <v>2966.7</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>3138.4</v>
+        <v>2974</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3140</v>
+        <v>2981.2</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2948.6</v>
+        <v>2922</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2966.7</v>
+        <v>2960.7</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-179.9</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>-5.72</v>
+        <v>-6</v>
+      </c>
+      <c r="J63" s="10" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>362.25</v>
+        <v>352.7</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>360</v>
+        <v>350.15</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>360.1</v>
+        <v>353.2</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>351.55</v>
+        <v>344.75</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>352.7</v>
+        <v>346.3</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>-2.64</v>
+        <v>-6.4</v>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>297.25</v>
+        <v>292.45</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>295</v>
+        <v>291.55</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>297.4</v>
+        <v>293.65</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>291.15</v>
+        <v>283.8</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>292.45</v>
+        <v>284.8</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>-1.61</v>
+        <v>-7.65</v>
+      </c>
+      <c r="J65" s="10" t="n">
+        <v>-2.62</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>166.49</v>
+        <v>162.51</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>165.6</v>
+        <v>161.01</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>165.6</v>
+        <v>162.79</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>162.21</v>
+        <v>159.7</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>162.51</v>
+        <v>160.35</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-3.98</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <v>-2.39</v>
+        <v>-2.16</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2366.4</v>
+        <v>2347.3</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2356.5</v>
+        <v>2340.9</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2368.8</v>
+        <v>2340.9</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2317.7</v>
+        <v>2244</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2347.3</v>
+        <v>2257.1</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-19.1</v>
-      </c>
-      <c r="J67" s="13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-90.2</v>
+      </c>
+      <c r="J67" s="10" t="n">
+        <v>-3.84</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="J68" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>496.15</v>
+        <v>485</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>497.85</v>
+        <v>484.5</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>497.85</v>
+        <v>484.5</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>482.35</v>
+        <v>467.9</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>485</v>
+        <v>470.15</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-11.15</v>
-      </c>
-      <c r="J69" s="13" t="n">
-        <v>-2.25</v>
+        <v>-14.85</v>
+      </c>
+      <c r="J69" s="10" t="n">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1042.4</v>
+        <v>1005.9</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1042.5</v>
+        <v>1011.1</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1045</v>
+        <v>1045.9</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1006.9</v>
+        <v>1005.3</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1010.9</v>
+        <v>1030.2</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>-31.5</v>
+        <v>24.3</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>-3.02</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1873.6</v>
+        <v>1794.3</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1862.1</v>
+        <v>1788</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1862.1</v>
+        <v>1791.8</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1784</v>
+        <v>1710</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1794.3</v>
+        <v>1712.4</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-79.3</v>
-      </c>
-      <c r="J71" s="13" t="n">
-        <v>-4.23</v>
+        <v>-81.90000000000001</v>
+      </c>
+      <c r="J71" s="10" t="n">
+        <v>-4.56</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>752.95</v>
+        <v>755.6</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>760.25</v>
+        <v>757.4</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>742.3</v>
+        <v>726.1</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>755.6</v>
+        <v>729.05</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>2.65</v>
+        <v>-26.55</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>0.35</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2968.6</v>
+        <v>2984.2</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2954.1</v>
+        <v>2980</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>3007.3</v>
+        <v>2984.2</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2928</v>
+        <v>2893.7</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2984.2</v>
+        <v>2903</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>15.6</v>
+        <v>-81.2</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>0.53</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>396.45</v>
+        <v>380.95</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>396</v>
+        <v>382.9</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>400.4</v>
+        <v>383.2</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>376.75</v>
+        <v>367</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>380.95</v>
+        <v>368.25</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="J74" s="13" t="n">
-        <v>-3.91</v>
+        <v>-12.7</v>
+      </c>
+      <c r="J74" s="10" t="n">
+        <v>-3.33</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4788.1</v>
+        <v>4756.3</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4779.2</v>
+        <v>4730</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4808.5</v>
+        <v>4744.9</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4739.7</v>
+        <v>4556.1</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4756.3</v>
+        <v>4572.5</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-31.8</v>
-      </c>
-      <c r="J75" s="13" t="n">
-        <v>-0.66</v>
+        <v>-183.8</v>
+      </c>
+      <c r="J75" s="10" t="n">
+        <v>-3.86</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1255.2</v>
+        <v>1230</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1248.2</v>
+        <v>1225.5</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1249</v>
+        <v>1231.6</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1226.6</v>
+        <v>1187.4</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1230</v>
+        <v>1190.9</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-25.2</v>
-      </c>
-      <c r="J76" s="13" t="n">
-        <v>-2.01</v>
+        <v>-39.1</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>-3.18</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1198.4</v>
+        <v>1194.9</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1196.9</v>
+        <v>1183</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1206.3</v>
+        <v>1184</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1191.1</v>
+        <v>1142.6</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1194.9</v>
+        <v>1145.8</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>-0.29</v>
+        <v>-49.1</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>-4.11</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2854</v>
+        <v>2747.2</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2845</v>
+        <v>2713</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2845</v>
+        <v>2759.3</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2738.9</v>
+        <v>2623.4</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2747.2</v>
+        <v>2632.8</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-106.8</v>
-      </c>
-      <c r="J78" s="13" t="n">
-        <v>-3.74</v>
+        <v>-114.4</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>-4.16</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>780.85</v>
+        <v>763.65</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>771.95</v>
+        <v>756.6</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>774.85</v>
+        <v>759.7</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>761.9</v>
+        <v>747.8</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>763.65</v>
+        <v>750.45</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-17.2</v>
-      </c>
-      <c r="J79" s="13" t="n">
-        <v>-2.2</v>
+        <v>-13.2</v>
+      </c>
+      <c r="J79" s="10" t="n">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>621.7</v>
+        <v>622.7</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>611.2</v>
+        <v>600.35</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>622.7</v>
+        <v>601.8</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>1</v>
+        <v>-20.9</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>0.16</v>
+        <v>-3.36</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5322</v>
+        <v>5228.5</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5262.5</v>
+        <v>5230</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5283.5</v>
+        <v>5270</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5146</v>
+        <v>5070</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5228.5</v>
+        <v>5082.5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-93.5</v>
-      </c>
-      <c r="J81" s="13" t="n">
-        <v>-1.76</v>
+        <v>-146</v>
+      </c>
+      <c r="J81" s="10" t="n">
+        <v>-2.79</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1044.4</v>
+        <v>1023.5</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1031.1</v>
+        <v>1027.2</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1042.4</v>
+        <v>1054.6</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1022.1</v>
+        <v>1025</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1023.5</v>
+        <v>1041.4</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>-20.9</v>
+        <v>17.9</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>-2</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>569.2</v>
+        <v>572.9</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>579</v>
+        <v>592.3</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>564.1</v>
+        <v>560.35</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>572.9</v>
+        <v>564.2</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>3.7</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>0.65</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>387</v>
+        <v>377.8</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>383</v>
+        <v>370.5</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>383.4</v>
+        <v>375.05</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>375.1</v>
+        <v>363.7</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>377.8</v>
+        <v>369.9</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="J84" s="13" t="n">
-        <v>-2.38</v>
+        <v>-7.9</v>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2287.7</v>
+        <v>2307.2</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2277.1</v>
+        <v>2285.3</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2317.1</v>
+        <v>2307</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2259.2</v>
+        <v>2256</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2307.2</v>
+        <v>2262</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>19.5</v>
+        <v>-45.2</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.85</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>30170</v>
+        <v>29340</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>30155</v>
+        <v>29340</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>30155</v>
+        <v>29540</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>29250</v>
+        <v>28100</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>29340</v>
+        <v>28455</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-830</v>
-      </c>
-      <c r="J86" s="13" t="n">
-        <v>-2.75</v>
+        <v>-885</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>-3.02</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>71.27</v>
+        <v>69.22</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>70.65000000000001</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>70.78</v>
+        <v>69.27</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>69.09999999999999</v>
+        <v>67.53</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>69.22</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="J87" s="13" t="n">
-        <v>-2.88</v>
+        <v>-1.54</v>
+      </c>
+      <c r="J87" s="10" t="n">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>134.12</v>
+        <v>130.71</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>133.76</v>
+        <v>130</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>137.34</v>
+        <v>131.25</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>130.17</v>
+        <v>127</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>130.71</v>
+        <v>127.21</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-3.41</v>
-      </c>
-      <c r="J88" s="13" t="n">
-        <v>-2.54</v>
+        <v>-3.5</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>165.99</v>
+        <v>160.69</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>164.5</v>
+        <v>160</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>164.5</v>
+        <v>161.09</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>160.19</v>
+        <v>156.41</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>160.69</v>
+        <v>156.81</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="J89" s="13" t="n">
-        <v>-3.19</v>
+        <v>-3.88</v>
+      </c>
+      <c r="J89" s="10" t="n">
+        <v>-2.41</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>673.05</v>
+        <v>661.3</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>670</v>
+        <v>674.15</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>671.9</v>
+        <v>674.9</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>655.9</v>
+        <v>633.15</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>661.3</v>
+        <v>634.4</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-11.75</v>
-      </c>
-      <c r="J90" s="13" t="n">
-        <v>-1.75</v>
+        <v>-26.9</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>-4.07</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2091.8</v>
+        <v>2065</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2071.1</v>
+        <v>2075</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2088.9</v>
+        <v>2079.3</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2034</v>
+        <v>2004.8</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2065</v>
+        <v>2011.8</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-26.8</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>-1.28</v>
+        <v>-53.2</v>
+      </c>
+      <c r="J91" s="10" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4522.7</v>
+        <v>4299.4</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4430</v>
+        <v>4297.1</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4432.3</v>
+        <v>4309.1</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4276.6</v>
+        <v>4187.7</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4299.4</v>
+        <v>4201.7</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-223.3</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>-4.94</v>
+        <v>-97.7</v>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>950.75</v>
+        <v>922.3</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>939</v>
+        <v>920</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>940.9</v>
+        <v>922.3</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>918.1</v>
+        <v>890.1</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>922.3</v>
+        <v>892.85</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-28.45</v>
-      </c>
-      <c r="J93" s="13" t="n">
-        <v>-2.99</v>
+        <v>-29.45</v>
+      </c>
+      <c r="J93" s="10" t="n">
+        <v>-3.19</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>404.3</v>
+        <v>410.65</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>402.8</v>
+        <v>411.8</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>415.45</v>
+        <v>411.85</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>396.5</v>
+        <v>400</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>410.65</v>
+        <v>400.8</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>6.35</v>
+        <v>-9.85</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>1.57</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1179.2</v>
+        <v>1177</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1176</v>
+        <v>1162</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1187</v>
+        <v>1162</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1172.1</v>
+        <v>1123</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1177</v>
+        <v>1140.3</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="J95" s="13" t="n">
-        <v>-0.19</v>
+        <v>-36.7</v>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>-3.12</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>144.69</v>
+        <v>140.37</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>143</v>
+        <v>139.39</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>143</v>
+        <v>139.76</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>140.04</v>
+        <v>137.25</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>140.37</v>
+        <v>137.65</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-4.32</v>
-      </c>
-      <c r="J96" s="13" t="n">
-        <v>-2.99</v>
+        <v>-2.72</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1552.6</v>
+        <v>1535</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1557.2</v>
+        <v>1535</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1569</v>
+        <v>1544.8</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1525.2</v>
+        <v>1499</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1535</v>
+        <v>1509.1</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-17.6</v>
-      </c>
-      <c r="J97" s="13" t="n">
-        <v>-1.13</v>
+        <v>-25.9</v>
+      </c>
+      <c r="J97" s="10" t="n">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>564.9</v>
+        <v>556.8</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>562.55</v>
+        <v>555</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>562.55</v>
+        <v>557.85</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>552.1</v>
+        <v>531</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>556.8</v>
+        <v>534</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="J98" s="13" t="n">
-        <v>-1.43</v>
+        <v>-22.8</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>-4.09</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>307.45</v>
+        <v>305.85</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>307</v>
+        <v>305.35</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>308</v>
+        <v>306.25</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>305.15</v>
+        <v>300.1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>305.85</v>
+        <v>300.7</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="J99" s="13" t="n">
-        <v>-0.52</v>
+        <v>-5.15</v>
+      </c>
+      <c r="J99" s="10" t="n">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1248.4</v>
+        <v>1232</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1250</v>
+        <v>1233.1</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1256</v>
+        <v>1242.8</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1230.2</v>
+        <v>1211.1</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1232</v>
+        <v>1214.3</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-16.4</v>
-      </c>
-      <c r="J100" s="13" t="n">
-        <v>-1.31</v>
+        <v>-17.7</v>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5571.5</v>
+        <v>5465</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5490.5</v>
+        <v>5465</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5549</v>
+        <v>5494</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5416.5</v>
+        <v>5334</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5465</v>
+        <v>5377.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-106.5</v>
-      </c>
-      <c r="J101" s="13" t="n">
-        <v>-1.91</v>
+        <v>-87.5</v>
+      </c>
+      <c r="J101" s="10" t="n">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>754.8</v>
+        <v>741.3</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>754.8</v>
+        <v>741.25</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>757</v>
+        <v>745.25</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>727.5</v>
+        <v>724.3</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>741.3</v>
+        <v>732.1</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="J102" s="13" t="n">
-        <v>-1.79</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>571.2</v>
+        <v>556.65</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>572</v>
+        <v>539.75</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>572</v>
+        <v>539.75</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>549.25</v>
+        <v>512</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>556.65</v>
+        <v>517.95</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-14.55</v>
-      </c>
-      <c r="J103" s="13" t="n">
-        <v>-2.55</v>
+        <v>-38.7</v>
+      </c>
+      <c r="J103" s="10" t="n">
+        <v>-6.95</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1277.8</v>
+        <v>1262.6</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1276</v>
+        <v>1262</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1282.2</v>
+        <v>1272.6</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1258.6</v>
+        <v>1246.2</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1262.6</v>
+        <v>1252.3</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-15.2</v>
-      </c>
-      <c r="J104" s="13" t="n">
-        <v>-1.19</v>
+        <v>-10.3</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>473.3</v>
+        <v>460.5</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>470.8</v>
+        <v>460.5</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>470.8</v>
+        <v>463.65</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>458.6</v>
+        <v>440.1</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>460.5</v>
+        <v>442.15</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-12.8</v>
-      </c>
-      <c r="J105" s="13" t="n">
-        <v>-2.7</v>
+        <v>-18.35</v>
+      </c>
+      <c r="J105" s="10" t="n">
+        <v>-3.98</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1104.1</v>
+        <v>1095.5</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1102.3</v>
+        <v>1090.5</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1125.6</v>
+        <v>1097</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1085.1</v>
+        <v>1068.5</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1095.5</v>
+        <v>1072.6</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-8.6</v>
-      </c>
-      <c r="J106" s="13" t="n">
-        <v>-0.78</v>
+        <v>-22.9</v>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>380.8</v>
+        <v>381.05</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>376.1</v>
+        <v>380.2</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>386</v>
+        <v>381.05</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>374.4</v>
+        <v>374.55</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>381.05</v>
+        <v>376</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>0.25</v>
+        <v>-5.05</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>729.15</v>
+        <v>733.45</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>737.2</v>
+        <v>733</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>715</v>
+        <v>703.25</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>733.45</v>
+        <v>712.05</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>4.3</v>
+        <v>-21.4</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>0.59</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1649.8</v>
+        <v>1652.4</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1637.9</v>
+        <v>1641</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1698</v>
+        <v>1658.7</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1629.3</v>
+        <v>1581.5</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1652.4</v>
+        <v>1587</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>2.6</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>0.16</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1228.3</v>
+        <v>1266.8</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1232.5</v>
+        <v>1273</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1277.3</v>
+        <v>1289</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1221.4</v>
+        <v>1260.1</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1266.8</v>
+        <v>1268</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>3.13</v>
+        <v>1.2</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>581.5</v>
+        <v>585.6</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>578.85</v>
+        <v>585.6</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>598.2</v>
+        <v>590</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>571.2</v>
+        <v>565.6</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>585.6</v>
+        <v>567.65</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>4.1</v>
+        <v>-17.95</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>0.71</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3974.5</v>
+        <v>3940.2</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3948</v>
+        <v>3925.1</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3953.5</v>
+        <v>3940</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3886.1</v>
+        <v>3847</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3940.2</v>
+        <v>3856.5</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-34.3</v>
-      </c>
-      <c r="J112" s="13" t="n">
-        <v>-0.86</v>
+        <v>-83.7</v>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>303.4</v>
+        <v>295</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>305</v>
+        <v>295.1</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>294.15</v>
+        <v>279.25</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>295</v>
+        <v>280.65</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="J113" s="13" t="n">
-        <v>-2.77</v>
+        <v>-14.35</v>
+      </c>
+      <c r="J113" s="10" t="n">
+        <v>-4.86</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="13" t="n">
+      <c r="J114" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3802.6</v>
+        <v>3788.4</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3825</v>
+        <v>3769.5</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3844</v>
+        <v>3802.2</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3750</v>
+        <v>3561.6</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3788.4</v>
+        <v>3603.7</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="J115" s="13" t="n">
-        <v>-0.37</v>
+        <v>-184.7</v>
+      </c>
+      <c r="J115" s="10" t="n">
+        <v>-4.88</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2379.5</v>
+        <v>2255.9</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2330.4</v>
+        <v>2256</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2330.4</v>
+        <v>2289.8</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2236.1</v>
+        <v>2233</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2255.9</v>
+        <v>2245.4</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-123.6</v>
-      </c>
-      <c r="J116" s="13" t="n">
-        <v>-5.19</v>
+        <v>-10.5</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3330.4</v>
+        <v>3245.9</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3235</v>
+        <v>3240</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3292</v>
+        <v>3261.6</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3224.2</v>
+        <v>3166.3</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3245.9</v>
+        <v>3176</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-84.5</v>
-      </c>
-      <c r="J117" s="13" t="n">
-        <v>-2.54</v>
+        <v>-69.90000000000001</v>
+      </c>
+      <c r="J117" s="10" t="n">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>315.5</v>
+        <v>305.45</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>312.3</v>
+        <v>305.45</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>312.3</v>
+        <v>307.75</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>303.55</v>
+        <v>292.05</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>305.45</v>
+        <v>293.2</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-10.05</v>
-      </c>
-      <c r="J118" s="13" t="n">
-        <v>-3.19</v>
+        <v>-12.25</v>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v>-4.01</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>831.3</v>
+        <v>842.55</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>829.75</v>
+        <v>842</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>848.8</v>
+        <v>846</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>824.8</v>
+        <v>827.35</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>842.55</v>
+        <v>830</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>11.25</v>
+        <v>-12.55</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>1.35</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13726</v>
+        <v>13483</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13547</v>
+        <v>13442</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13657</v>
+        <v>13455</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13231</v>
+        <v>13150</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13483</v>
+        <v>13172</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-243</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>-1.77</v>
+        <v>-311</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>-2.31</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="13" t="n">
+      <c r="J121" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3097.8</v>
+        <v>3187.9</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3120</v>
+        <v>3200</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3219.6</v>
+        <v>3256</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3042.5</v>
+        <v>3146.3</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3187.9</v>
+        <v>3156.9</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>90.09999999999999</v>
+        <v>-31</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>2.91</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>549.5</v>
+        <v>559.9</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>549</v>
+        <v>552.5</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>568.9</v>
+        <v>554.2</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>544</v>
+        <v>515</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>559.9</v>
+        <v>548.1</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>10.4</v>
+        <v>-11.8</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>1.89</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1699.7</v>
+        <v>1695.5</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1694</v>
+        <v>1690.1</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1703.9</v>
+        <v>1694.1</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1677</v>
+        <v>1640.6</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1695.5</v>
+        <v>1653.7</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="J124" s="13" t="n">
-        <v>-0.25</v>
+        <v>-41.8</v>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v>-2.47</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1172.9</v>
+        <v>1106.4</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1160.8</v>
+        <v>1108.7</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1160.8</v>
+        <v>1110.9</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1101</v>
+        <v>1058.7</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1106.4</v>
+        <v>1064.4</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-66.5</v>
-      </c>
-      <c r="J125" s="13" t="n">
-        <v>-5.67</v>
+        <v>-42</v>
+      </c>
+      <c r="J125" s="10" t="n">
+        <v>-3.8</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>132.03</v>
+        <v>130.3</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>130.58</v>
+        <v>130</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>131.39</v>
+        <v>130.66</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>128.94</v>
+        <v>123.55</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>130.3</v>
+        <v>124.26</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-1.73</v>
-      </c>
-      <c r="J126" s="13" t="n">
-        <v>-1.31</v>
+        <v>-6.04</v>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>-4.64</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2214.2</v>
+        <v>2201.2</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2214.2</v>
+        <v>2175.5</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2222</v>
+        <v>2179</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2193.2</v>
+        <v>2122.5</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2201.2</v>
+        <v>2146.5</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-13</v>
-      </c>
-      <c r="J127" s="13" t="n">
-        <v>-0.59</v>
+        <v>-54.7</v>
+      </c>
+      <c r="J127" s="10" t="n">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>130425</v>
+        <v>128910</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>130330</v>
+        <v>129000</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>130500</v>
+        <v>129565</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>128620</v>
+        <v>126050</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>128910</v>
+        <v>126505</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-1515</v>
-      </c>
-      <c r="J128" s="13" t="n">
-        <v>-1.16</v>
+        <v>-2405</v>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3528.9</v>
+        <v>3438.2</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3481.5</v>
+        <v>3435</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3493.9</v>
+        <v>3450</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3405</v>
+        <v>3339.3</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3438.2</v>
+        <v>3353.4</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-90.7</v>
-      </c>
-      <c r="J129" s="13" t="n">
-        <v>-2.57</v>
+        <v>-84.8</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>-2.47</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>401.95</v>
+        <v>393.05</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>401.75</v>
+        <v>395</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>402.5</v>
+        <v>403.2</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>391.7</v>
+        <v>392.3</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>393.05</v>
+        <v>394.05</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>-8.9</v>
+        <v>1</v>
       </c>
       <c r="J130" s="13" t="n">
-        <v>-2.21</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>978.35</v>
+        <v>961.2</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>978.35</v>
+        <v>958.3</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>980.95</v>
+        <v>958.3</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>956.95</v>
+        <v>928.6</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>961.2</v>
+        <v>930.9</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-17.15</v>
-      </c>
-      <c r="J131" s="13" t="n">
-        <v>-1.75</v>
+        <v>-30.3</v>
+      </c>
+      <c r="J131" s="10" t="n">
+        <v>-3.15</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>7041.5</v>
+        <v>7071.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>7000</v>
+        <v>7070</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>7120</v>
+        <v>7070</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6945</v>
+        <v>6912.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>7071.5</v>
+        <v>6950.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>30</v>
+        <v>-121</v>
       </c>
       <c r="J132" s="10" t="n">
-        <v>0.43</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1482.4</v>
+        <v>1481.9</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1475.3</v>
+        <v>1470</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1498.1</v>
+        <v>1491</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1470.5</v>
+        <v>1466.1</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1481.9</v>
+        <v>1468.6</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="J133" s="13" t="n">
-        <v>-0.03</v>
+        <v>-13.3</v>
+      </c>
+      <c r="J133" s="10" t="n">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>88.8</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>88.01000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>88.3</v>
+        <v>88.47</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>86.59</v>
+        <v>86.38</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>86.79000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="J134" s="13" t="n">
-        <v>-2.26</v>
+        <v>-0.17</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>402.15</v>
+        <v>392.95</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>401.9</v>
+        <v>392.2</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>405</v>
+        <v>399.85</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>391</v>
+        <v>391.25</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>392.95</v>
+        <v>392.7</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="J135" s="13" t="n">
-        <v>-2.29</v>
+        <v>-0.25</v>
+      </c>
+      <c r="J135" s="10" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1703</v>
+        <v>1634.7</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1712.8</v>
+        <v>1669</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1712.8</v>
+        <v>1712</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1630.6</v>
+        <v>1622.6</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1634.7</v>
+        <v>1626.7</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-68.3</v>
-      </c>
-      <c r="J136" s="13" t="n">
-        <v>-4.01</v>
+        <v>-8</v>
+      </c>
+      <c r="J136" s="10" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9345.5</v>
+        <v>9239.5</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9395</v>
+        <v>9201</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9401.5</v>
+        <v>9235</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>9190</v>
+        <v>8985</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9239.5</v>
+        <v>9010.5</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-106</v>
-      </c>
-      <c r="J137" s="13" t="n">
-        <v>-1.13</v>
+        <v>-229</v>
+      </c>
+      <c r="J137" s="10" t="n">
+        <v>-2.48</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>279.2</v>
+        <v>281</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>280.7</v>
+        <v>286.9</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>281.8</v>
+        <v>299.9</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>277.65</v>
+        <v>286.85</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>281</v>
+        <v>294.5</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J138" s="10" t="n">
-        <v>0.64</v>
+        <v>13.5</v>
+      </c>
+      <c r="J138" s="13" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>37365</v>
+        <v>36245</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>37220</v>
+        <v>36390</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>37305</v>
+        <v>36390</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>36120</v>
+        <v>34950</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>36245</v>
+        <v>35085</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-1120</v>
-      </c>
-      <c r="J139" s="13" t="n">
-        <v>-3</v>
+        <v>-1160</v>
+      </c>
+      <c r="J139" s="10" t="n">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="13" t="n">
+      <c r="J140" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5113.6</v>
+        <v>5098.1</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5124.9</v>
+        <v>5073.8</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5173.3</v>
+        <v>5073.8</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>5080</v>
+        <v>4841</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>5098.1</v>
+        <v>4877.1</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-15.5</v>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v>-0.3</v>
+        <v>-221</v>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>-4.33</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>283.8</v>
+        <v>275.75</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>282.25</v>
+        <v>274.75</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>282.25</v>
+        <v>276.5</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>275</v>
+        <v>270.4</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>275.75</v>
+        <v>271.15</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="J142" s="13" t="n">
-        <v>-2.84</v>
+        <v>-4.6</v>
+      </c>
+      <c r="J142" s="10" t="n">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>461.35</v>
+        <v>448.5</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>459.45</v>
+        <v>456.8</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>447.4</v>
+        <v>439.45</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>448.5</v>
+        <v>440.7</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-12.85</v>
-      </c>
-      <c r="J143" s="13" t="n">
-        <v>-2.79</v>
+        <v>-7.8</v>
+      </c>
+      <c r="J143" s="10" t="n">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1476</v>
+        <v>1437.2</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1468.5</v>
+        <v>1433.1</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1468.5</v>
+        <v>1480</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1432</v>
+        <v>1427.6</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1437.2</v>
+        <v>1453</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-38.8</v>
+        <v>15.8</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>-2.63</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3110.8</v>
+        <v>3090.8</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3101</v>
+        <v>3088.8</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3110</v>
+        <v>3088.8</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>3055</v>
+        <v>2991</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3090.8</v>
+        <v>2997.6</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J145" s="13" t="n">
-        <v>-0.64</v>
+        <v>-93.2</v>
+      </c>
+      <c r="J145" s="10" t="n">
+        <v>-3.02</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>107.24</v>
+        <v>104.62</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>106.2</v>
+        <v>104</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>106.45</v>
+        <v>104.97</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>104.33</v>
+        <v>102.55</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>104.62</v>
+        <v>102.78</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-2.62</v>
-      </c>
-      <c r="J146" s="13" t="n">
-        <v>-2.44</v>
+        <v>-1.84</v>
+      </c>
+      <c r="J146" s="10" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>9083</v>
+        <v>9065.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>9004.5</v>
+        <v>9115</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>9136</v>
+        <v>9220</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8963</v>
+        <v>8979</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>9065.5</v>
+        <v>9021.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-17.5</v>
-      </c>
-      <c r="J147" s="13" t="n">
-        <v>-0.19</v>
+        <v>-44</v>
+      </c>
+      <c r="J147" s="10" t="n">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>313.95</v>
+        <v>310.9</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>313.95</v>
+        <v>309.45</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>314.05</v>
+        <v>310.75</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>309.95</v>
+        <v>305.5</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>310.9</v>
+        <v>306.3</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-3.05</v>
-      </c>
-      <c r="J148" s="13" t="n">
-        <v>-0.97</v>
+        <v>-4.6</v>
+      </c>
+      <c r="J148" s="10" t="n">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1073.8</v>
+        <v>1026</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1074.9</v>
+        <v>1045</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1110</v>
+        <v>1045</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1017</v>
+        <v>1000</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1026</v>
+        <v>1014.6</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-47.8</v>
-      </c>
-      <c r="J149" s="13" t="n">
-        <v>-4.45</v>
+        <v>-11.4</v>
+      </c>
+      <c r="J149" s="10" t="n">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>343.45</v>
+        <v>337.5</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>341.3</v>
+        <v>335.2</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>342.6</v>
+        <v>339</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>334.25</v>
+        <v>324.1</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>337.5</v>
+        <v>325.25</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-5.95</v>
-      </c>
-      <c r="J150" s="13" t="n">
-        <v>-1.73</v>
+        <v>-12.25</v>
+      </c>
+      <c r="J150" s="10" t="n">
+        <v>-3.63</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>359.4</v>
+        <v>351.55</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>358</v>
+        <v>350.15</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>358.8</v>
+        <v>353.65</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>350.5</v>
+        <v>343.55</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>351.55</v>
+        <v>344.35</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-7.85</v>
-      </c>
-      <c r="J151" s="13" t="n">
-        <v>-2.18</v>
+        <v>-7.2</v>
+      </c>
+      <c r="J151" s="10" t="n">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1435.2</v>
+        <v>1388.2</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1420</v>
+        <v>1392</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1428</v>
+        <v>1393.5</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1382</v>
+        <v>1360.3</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1388.2</v>
+        <v>1364</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-47</v>
-      </c>
-      <c r="J152" s="13" t="n">
-        <v>-3.27</v>
+        <v>-24.2</v>
+      </c>
+      <c r="J152" s="10" t="n">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>184.88</v>
+        <v>180.72</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>182.89</v>
+        <v>179.9</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>184.87</v>
+        <v>180.9</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>179.91</v>
+        <v>175.16</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>180.72</v>
+        <v>176.09</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="J153" s="13" t="n">
-        <v>-2.25</v>
+        <v>-4.63</v>
+      </c>
+      <c r="J153" s="10" t="n">
+        <v>-2.56</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>645.4</v>
+        <v>641.5</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>642</v>
+        <v>643.55</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>645.85</v>
+        <v>643.6</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>634.3</v>
+        <v>623.3</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>641.5</v>
+        <v>625.1</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="J154" s="13" t="n">
-        <v>-0.6</v>
+        <v>-16.4</v>
+      </c>
+      <c r="J154" s="10" t="n">
+        <v>-2.56</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1872.1</v>
+        <v>1884.4</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1865.6</v>
+        <v>1866</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1895</v>
+        <v>1875.6</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1863.9</v>
+        <v>1825</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1884.4</v>
+        <v>1833.9</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>12.3</v>
+        <v>-50.5</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>0.66</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>1019.3</v>
+        <v>973.6</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>1007</v>
+        <v>976.9</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>1007</v>
+        <v>981.4</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>971.1</v>
+        <v>962.4</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>973.6</v>
+        <v>974.6</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-45.7</v>
+        <v>1</v>
       </c>
       <c r="J156" s="13" t="n">
-        <v>-4.48</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>25435</v>
+        <v>25205</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25190</v>
+        <v>25100</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25385</v>
+        <v>25325</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>25000</v>
+        <v>24800</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>25205</v>
+        <v>24860</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-230</v>
-      </c>
-      <c r="J157" s="13" t="n">
-        <v>-0.9</v>
+        <v>-345</v>
+      </c>
+      <c r="J157" s="10" t="n">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>1007.75</v>
+        <v>975.95</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>990</v>
+        <v>971</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>990.85</v>
+        <v>979.95</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>970.45</v>
+        <v>925.95</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>975.95</v>
+        <v>930.45</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-31.8</v>
-      </c>
-      <c r="J158" s="13" t="n">
-        <v>-3.16</v>
+        <v>-45.5</v>
+      </c>
+      <c r="J158" s="10" t="n">
+        <v>-4.66</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3822.6</v>
+        <v>3605.6</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3720</v>
+        <v>3605</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3720</v>
+        <v>3644.8</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3552.9</v>
+        <v>3555.8</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3605.6</v>
+        <v>3574.4</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-217</v>
-      </c>
-      <c r="J159" s="13" t="n">
-        <v>-5.68</v>
+        <v>-31.2</v>
+      </c>
+      <c r="J159" s="10" t="n">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2780.8</v>
+        <v>2798.5</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2777</v>
+        <v>2785</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2832.1</v>
+        <v>2800</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2739.6</v>
+        <v>2714.1</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2798.5</v>
+        <v>2721.2</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>17.7</v>
+        <v>-77.3</v>
       </c>
       <c r="J160" s="10" t="n">
-        <v>0.64</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1847.9</v>
+        <v>1872.7</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1827.2</v>
+        <v>1875</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1885.8</v>
+        <v>1879.4</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1825</v>
+        <v>1840</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1872.7</v>
+        <v>1845.7</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>24.8</v>
+        <v>-27</v>
       </c>
       <c r="J161" s="10" t="n">
-        <v>1.34</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>573.55</v>
+        <v>567.75</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>572.5</v>
+        <v>567.75</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>574.5</v>
+        <v>570.25</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>560.95</v>
+        <v>558.05</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>567.75</v>
+        <v>560.2</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-5.8</v>
-      </c>
-      <c r="J162" s="13" t="n">
-        <v>-1.01</v>
+        <v>-7.55</v>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>458.1</v>
+        <v>482.5</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>455</v>
+        <v>486.25</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>490.7</v>
+        <v>486.25</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>453.4</v>
+        <v>470</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>482.5</v>
+        <v>478.75</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>24.4</v>
+        <v>-3.75</v>
       </c>
       <c r="J163" s="10" t="n">
-        <v>5.33</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>781.55</v>
+        <v>761.35</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>777</v>
+        <v>793.75</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>761.35</v>
+        <v>770.25</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-20.2</v>
+        <v>8.9</v>
       </c>
       <c r="J164" s="13" t="n">
-        <v>-2.58</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1592.3</v>
+        <v>1571.5</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1576.9</v>
+        <v>1571.5</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1592</v>
+        <v>1591.4</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1560</v>
+        <v>1530.4</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1571.5</v>
+        <v>1539.9</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-20.8</v>
-      </c>
-      <c r="J165" s="13" t="n">
-        <v>-1.31</v>
+        <v>-31.6</v>
+      </c>
+      <c r="J165" s="10" t="n">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1176.2</v>
+        <v>1271</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1202.2</v>
+        <v>1269.7</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1279.4</v>
+        <v>1282.7</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1200</v>
+        <v>1250.4</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1271</v>
+        <v>1253</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>94.8</v>
+        <v>-18</v>
       </c>
       <c r="J166" s="10" t="n">
-        <v>8.06</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="13" t="n">
+      <c r="J167" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>436</v>
+        <v>433.2</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>434</v>
+        <v>431.2</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>437.95</v>
+        <v>433.4</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>428.7</v>
+        <v>417.25</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>433.2</v>
+        <v>418.4</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="J168" s="13" t="n">
-        <v>-0.64</v>
+        <v>-14.8</v>
+      </c>
+      <c r="J168" s="10" t="n">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>214.49</v>
+        <v>212.08</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>213.5</v>
+        <v>212</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>215</v>
+        <v>216.33</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>211.52</v>
+        <v>211.5</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>212.08</v>
+        <v>212</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-2.41</v>
-      </c>
-      <c r="J169" s="13" t="n">
-        <v>-1.12</v>
+        <v>-0.08</v>
+      </c>
+      <c r="J169" s="10" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2394.4</v>
+        <v>2392.9</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2371</v>
+        <v>2375</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2415</v>
+        <v>2375</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2371</v>
+        <v>2283</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2392.9</v>
+        <v>2300.3</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="J170" s="13" t="n">
-        <v>-0.06</v>
+        <v>-92.59999999999999</v>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>-3.87</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1463</v>
+        <v>1457.4</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1460</v>
+        <v>1447</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1475.4</v>
+        <v>1447</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1451.8</v>
+        <v>1388.9</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1457.4</v>
+        <v>1392.9</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="J171" s="13" t="n">
-        <v>-0.38</v>
+        <v>-64.5</v>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v>-4.43</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>3049.8</v>
+        <v>2992.2</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>3046.1</v>
+        <v>3014.3</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3046.1</v>
+        <v>3057.3</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2966</v>
+        <v>2931.3</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2992.2</v>
+        <v>2954</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-57.6</v>
-      </c>
-      <c r="J172" s="13" t="n">
-        <v>-1.89</v>
+        <v>-38.2</v>
+      </c>
+      <c r="J172" s="10" t="n">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4509</v>
+        <v>4205.6</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4350.4</v>
+        <v>4160</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4379.5</v>
+        <v>4213.6</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4150.1</v>
+        <v>4047</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4205.6</v>
+        <v>4055.3</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-303.4</v>
-      </c>
-      <c r="J173" s="13" t="n">
-        <v>-6.73</v>
+        <v>-150.3</v>
+      </c>
+      <c r="J173" s="10" t="n">
+        <v>-3.57</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4380.8</v>
+        <v>4517.1</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4406.3</v>
+        <v>4509.5</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4555.1</v>
+        <v>4509.5</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4337.9</v>
+        <v>4373</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4517.1</v>
+        <v>4381.9</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>136.3</v>
+        <v>-135.2</v>
       </c>
       <c r="J174" s="10" t="n">
-        <v>3.11</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1724.4</v>
+        <v>1680.9</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1724.4</v>
+        <v>1670</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1725.9</v>
+        <v>1687.9</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1667.8</v>
+        <v>1585.5</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1680.9</v>
+        <v>1597.6</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-43.5</v>
-      </c>
-      <c r="J175" s="13" t="n">
-        <v>-2.52</v>
+        <v>-83.3</v>
+      </c>
+      <c r="J175" s="10" t="n">
+        <v>-4.96</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4242.3</v>
+        <v>4181.1</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4227.2</v>
+        <v>4156</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4239</v>
+        <v>4183.5</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4153.3</v>
+        <v>4037.6</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4181.1</v>
+        <v>4050.6</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-61.2</v>
-      </c>
-      <c r="J176" s="13" t="n">
-        <v>-1.44</v>
+        <v>-130.5</v>
+      </c>
+      <c r="J176" s="10" t="n">
+        <v>-3.12</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3695.2</v>
+        <v>3613.7</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3651</v>
+        <v>3596.2</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3684.9</v>
+        <v>3613</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3601</v>
+        <v>3535</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3613.7</v>
+        <v>3561</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-81.5</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>-2.21</v>
+        <v>-52.7</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1419.8</v>
+        <v>1412.2</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1420</v>
+        <v>1412.5</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1423.9</v>
+        <v>1420.1</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1395</v>
+        <v>1391.5</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1412.2</v>
+        <v>1410.5</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="J178" s="13" t="n">
-        <v>-0.54</v>
+        <v>-1.7</v>
+      </c>
+      <c r="J178" s="10" t="n">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11950</v>
+        <v>11866</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11801</v>
+        <v>11866</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11937</v>
+        <v>11866</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11773</v>
+        <v>11503</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11866</v>
+        <v>11516</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-84</v>
-      </c>
-      <c r="J179" s="13" t="n">
-        <v>-0.7</v>
+        <v>-350</v>
+      </c>
+      <c r="J179" s="10" t="n">
+        <v>-2.95</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>166.24</v>
+        <v>163.81</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>166.2</v>
+        <v>164.95</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>163.23</v>
+        <v>161.39</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>163.81</v>
+        <v>162.19</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="J180" s="13" t="n">
-        <v>-1.46</v>
+        <v>-1.62</v>
+      </c>
+      <c r="J180" s="10" t="n">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>646</v>
+        <v>669</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>644</v>
+        <v>670.8</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>682.6</v>
+        <v>671.15</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>634.05</v>
+        <v>622.25</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>669</v>
+        <v>626.15</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>23</v>
+        <v>-42.85</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>3.56</v>
+        <v>-6.41</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>296.45</v>
+        <v>298.4</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>296.6</v>
+        <v>298.1</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>301.55</v>
+        <v>309.9</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>294.2</v>
+        <v>298.1</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>298.4</v>
+        <v>305.05</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>0.66</v>
+        <v>6.65</v>
+      </c>
+      <c r="J182" s="13" t="n">
+        <v>2.23</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1324.8</v>
+        <v>1306.5</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1315.6</v>
+        <v>1316</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1322.5</v>
+        <v>1348</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1299</v>
+        <v>1265.6</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1306.5</v>
+        <v>1269.6</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-18.3</v>
-      </c>
-      <c r="J183" s="13" t="n">
-        <v>-1.38</v>
+        <v>-36.9</v>
+      </c>
+      <c r="J183" s="10" t="n">
+        <v>-2.82</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>197.91</v>
+        <v>196.68</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>197.88</v>
+        <v>196.1</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>198.24</v>
+        <v>196.14</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>196.15</v>
+        <v>189.1</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>196.68</v>
+        <v>189.57</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="J184" s="13" t="n">
-        <v>-0.62</v>
+        <v>-7.11</v>
+      </c>
+      <c r="J184" s="10" t="n">
+        <v>-3.62</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="13" t="n">
+      <c r="J185" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>940.05</v>
+        <v>956.95</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>940</v>
+        <v>960.1</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>962</v>
+        <v>963.95</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>927</v>
+        <v>928.6</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>956.95</v>
+        <v>930.65</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>16.9</v>
+        <v>-26.3</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>1.8</v>
+        <v>-2.75</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  11-May-2026 03:55 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  12-May-2026 03:39 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11-May-2026 03:55 PM</t>
+          <t>12-May-2026 03:39 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 12-May-2026 03:39 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 13-May-2026 03:42 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>12-May-2026 03:39 PM</t>
+          <t>13-May-2026 03:42 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  12-May-2026 03:39 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  13-May-2026 03:42 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>487.45</v>
+        <v>468.5</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>489.3</v>
+        <v>476</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>461.15</v>
+        <v>465.6</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>468.5</v>
+        <v>468.55</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-18.95</v>
+        <v>0.05</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-3.89</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>6387.5</v>
+        <v>6328.5</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>6360</v>
+        <v>6344</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>6403</v>
+        <v>6395</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>6171.5</v>
+        <v>6212.5</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>6328.5</v>
+        <v>6305</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-59</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>-0.92</v>
+        <v>-23.5</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>27795</v>
+        <v>26900</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>28000</v>
+        <v>27100</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>28000</v>
+        <v>27595</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>26685</v>
+        <v>26920</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26900</v>
+        <v>27280</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>-895</v>
+        <v>380</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>-3.22</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>352.95</v>
+        <v>341.2</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>352.45</v>
+        <v>340</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>354</v>
+        <v>348.55</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>340</v>
+        <v>339.45</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>341.2</v>
+        <v>344.3</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-11.75</v>
+        <v>3.1</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>-3.33</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>64.98999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>64.90000000000001</v>
+        <v>62.7</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>64.90000000000001</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>62.25</v>
+        <v>62.7</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>62.4</v>
+        <v>63.59</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-2.59</v>
+        <v>1.19</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>-3.99</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1357.9</v>
+        <v>1347</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1354</v>
+        <v>1347.4</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1370</v>
+        <v>1372.5</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1340</v>
+        <v>1341.8</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1347</v>
+        <v>1366.4</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>-10.9</v>
+        <v>19.4</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>-0.8</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2500.2</v>
+        <v>2405.2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2487.7</v>
+        <v>2401.1</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2511.7</v>
+        <v>2530</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2400.1</v>
+        <v>2401.1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2405.2</v>
+        <v>2498</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>-95</v>
+        <v>92.8</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>-3.8</v>
+        <v>3.86</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1767.3</v>
+        <v>1688.2</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1752</v>
+        <v>1688.2</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1765.9</v>
+        <v>1752.3</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1683.2</v>
+        <v>1688</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1688.2</v>
+        <v>1737.8</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-79.09999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>-4.48</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5599.5</v>
+        <v>5496.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5624</v>
+        <v>5450</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5624</v>
+        <v>5553</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5482.5</v>
+        <v>5441.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5496.5</v>
+        <v>5462.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-103</v>
-      </c>
-      <c r="J11" s="10" t="n">
-        <v>-1.84</v>
+        <v>-34</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>436.2</v>
+        <v>426.95</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>434.9</v>
+        <v>428.15</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>442</v>
+        <v>441.15</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>425.2</v>
+        <v>425.4</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>426.95</v>
+        <v>438.4</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-9.25</v>
+        <v>11.45</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>-2.12</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>317.2</v>
+        <v>299.1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>315.65</v>
+        <v>300.1</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>315.95</v>
+        <v>303.4</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>296.95</v>
+        <v>297.05</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>299.1</v>
+        <v>298.15</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="J13" s="10" t="n">
-        <v>-5.71</v>
+        <v>-0.95</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1949.8</v>
+        <v>1881.2</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1953</v>
+        <v>1869.1</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1962</v>
+        <v>1906.3</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1876.1</v>
+        <v>1865.2</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1881.2</v>
+        <v>1891.1</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-68.59999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>-3.52</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8082</v>
+        <v>8022.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8050</v>
+        <v>7981</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8078</v>
+        <v>8112</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7995</v>
+        <v>7981</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8022.5</v>
+        <v>8004.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-59.5</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>-0.74</v>
+        <v>-18</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>405.7</v>
+        <v>398.75</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>405.65</v>
+        <v>397.65</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>409</v>
+        <v>401.2</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>397.45</v>
+        <v>394.6</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>398.75</v>
+        <v>396.45</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-6.95</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>-1.71</v>
+        <v>-2.3</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>161.52</v>
+        <v>155.95</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>160.8</v>
+        <v>155.95</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>161.47</v>
+        <v>157.36</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>155.1</v>
+        <v>152.76</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>155.95</v>
+        <v>153.21</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-5.57</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>-3.45</v>
+        <v>-2.74</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2566.1</v>
+        <v>2505.5</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2546.2</v>
+        <v>2554</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2555.7</v>
+        <v>2642.4</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2500</v>
+        <v>2554</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2505.5</v>
+        <v>2617.6</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-60.6</v>
+        <v>112.1</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>-2.36</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1572.1</v>
+        <v>1527.6</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1565</v>
+        <v>1521.4</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1579.6</v>
+        <v>1571.5</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1524.1</v>
+        <v>1503</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1527.6</v>
+        <v>1544</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>-44.5</v>
+        <v>16.4</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>-2.83</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>620.5</v>
+        <v>591.3</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>619.95</v>
+        <v>594.95</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>623.75</v>
+        <v>617</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>588.1</v>
+        <v>590</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>591.3</v>
+        <v>606.5</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>-29.2</v>
+        <v>15.2</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>-4.71</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6892</v>
+        <v>6851.5</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6870</v>
+        <v>6886.5</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6939.5</v>
+        <v>7070</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6804</v>
+        <v>6862</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6851.5</v>
+        <v>6988</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-40.5</v>
+        <v>136.5</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>-0.59</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1021.4</v>
+        <v>999.6</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1020.6</v>
+        <v>996.1</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1022.4</v>
+        <v>1010.6</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>997.3</v>
+        <v>988.7</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>999.6</v>
+        <v>994.8</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-21.8</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>-2.13</v>
+        <v>-4.8</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1486.6</v>
+        <v>1488.2</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1486.6</v>
+        <v>1490</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1504</v>
+        <v>1509.8</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1478.6</v>
+        <v>1483.6</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1488.2</v>
+        <v>1497.5</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J23" s="13" t="n">
-        <v>0.11</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>0.62</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1272.3</v>
+        <v>1260.1</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1270.4</v>
+        <v>1256.1</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1274</v>
+        <v>1275.3</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1256.9</v>
+        <v>1247.5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1260.1</v>
+        <v>1255.7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-12.2</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>-0.96</v>
+        <v>-4.4</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>10595.5</v>
+        <v>10397</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10550</v>
+        <v>10370.5</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10684.5</v>
+        <v>10455</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10366</v>
+        <v>10220</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>10397</v>
+        <v>10262</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-198.5</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>-1.87</v>
+        <v>-135</v>
+      </c>
+      <c r="J25" s="13" t="n">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1794.2</v>
+        <v>1744.8</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1783.8</v>
+        <v>1748.9</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1791</v>
+        <v>1758</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1741.5</v>
+        <v>1726</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1744.8</v>
+        <v>1728.9</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-49.4</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>-2.75</v>
+        <v>-15.9</v>
+      </c>
+      <c r="J26" s="13" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>936.05</v>
+        <v>904.2</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>928</v>
+        <v>902</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>932.65</v>
+        <v>907.4</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>901.75</v>
+        <v>890.05</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>904.2</v>
+        <v>896.15</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-31.85</v>
-      </c>
-      <c r="J27" s="10" t="n">
-        <v>-3.4</v>
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="J27" s="13" t="n">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2181.9</v>
+        <v>2110.6</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2181.9</v>
+        <v>2114.4</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2205</v>
+        <v>2151.8</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2084.1</v>
+        <v>2063.7</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2110.6</v>
+        <v>2105.1</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-71.3</v>
-      </c>
-      <c r="J28" s="10" t="n">
-        <v>-3.27</v>
+        <v>-5.5</v>
+      </c>
+      <c r="J28" s="13" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>525.4</v>
+        <v>534.15</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>525.25</v>
+        <v>534</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>536.45</v>
+        <v>561.9</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>521.45</v>
+        <v>531.55</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>534.15</v>
+        <v>548.9</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="J29" s="13" t="n">
-        <v>1.67</v>
+        <v>14.75</v>
+      </c>
+      <c r="J29" s="10" t="n">
+        <v>2.76</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>201.23</v>
+        <v>196.07</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>200</v>
+        <v>196.09</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>203.8</v>
+        <v>200.73</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>195.46</v>
+        <v>194.5</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>196.07</v>
+        <v>194.88</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="J30" s="10" t="n">
-        <v>-2.56</v>
+        <v>-1.19</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>266</v>
+        <v>259.95</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>263.95</v>
+        <v>260.7</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>267.45</v>
+        <v>264.3</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>259.15</v>
+        <v>258.1</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>259.95</v>
+        <v>261.65</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>-6.05</v>
+        <v>1.7</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>-2.27</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>431.95</v>
+        <v>416.5</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>430.2</v>
+        <v>416.6</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>432.5</v>
+        <v>432</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>415.5</v>
+        <v>415.75</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>416.5</v>
+        <v>428.25</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>-15.45</v>
+        <v>11.75</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>-3.58</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>493.85</v>
+        <v>488.1</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>498.55</v>
+        <v>533.35</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>488.1</v>
+        <v>507.7</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>-5.75</v>
+        <v>19.6</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>-1.16</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1759.8</v>
+        <v>1756.8</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1751.5</v>
+        <v>1740.5</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1776.5</v>
+        <v>1798</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1751.5</v>
+        <v>1740.5</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1756.8</v>
+        <v>1789.2</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>-3</v>
+        <v>32.4</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>-0.17</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>401.35</v>
+        <v>391.75</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>397.1</v>
+        <v>392.5</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>407.2</v>
+        <v>407.75</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>390.55</v>
+        <v>392.5</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>391.75</v>
+        <v>403.85</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-9.6</v>
+        <v>12.1</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>-2.39</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>390.45</v>
+        <v>402.45</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>392.9</v>
+        <v>403.05</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>406.6</v>
+        <v>420.25</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>392.25</v>
+        <v>402.85</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>402.45</v>
+        <v>417.6</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J36" s="13" t="n">
-        <v>3.07</v>
+        <v>15.15</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>3.76</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>37315</v>
+        <v>36510</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>37315</v>
+        <v>36510</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>37625</v>
+        <v>36880</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>36345</v>
+        <v>36235</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>36510</v>
+        <v>36315</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-805</v>
-      </c>
-      <c r="J37" s="10" t="n">
-        <v>-2.16</v>
+        <v>-195</v>
+      </c>
+      <c r="J37" s="13" t="n">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>294.45</v>
+        <v>287.85</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>286</v>
+        <v>288.55</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>293.7</v>
+        <v>299</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>286</v>
+        <v>288.55</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>287.85</v>
+        <v>297.1</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>-6.6</v>
+        <v>9.25</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>-2.24</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5410.5</v>
+        <v>5334</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5403.5</v>
+        <v>5345</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5425</v>
+        <v>5383.5</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5315</v>
+        <v>5279.5</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5334</v>
+        <v>5336</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-76.5</v>
+        <v>2</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>-1.41</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>355.9</v>
+        <v>331.6</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>354.5</v>
+        <v>331.6</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>354.5</v>
+        <v>334.75</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>330</v>
+        <v>317.45</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>331.6</v>
+        <v>318.7</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-24.3</v>
-      </c>
-      <c r="J40" s="10" t="n">
-        <v>-6.83</v>
+        <v>-12.9</v>
+      </c>
+      <c r="J40" s="13" t="n">
+        <v>-3.89</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>129.43</v>
+        <v>130.01</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>127.66</v>
+        <v>130.46</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>132.35</v>
+        <v>131.2</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>127.43</v>
+        <v>127.9</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>130.01</v>
+        <v>129.26</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0.58</v>
+        <v>-0.75</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>0.45</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>855.3</v>
+        <v>831.85</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>856.1</v>
+        <v>836.35</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>862.85</v>
+        <v>839.35</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>826.4</v>
+        <v>820.05</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>831.85</v>
+        <v>827.4</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-23.45</v>
-      </c>
-      <c r="J42" s="10" t="n">
-        <v>-2.74</v>
+        <v>-4.45</v>
+      </c>
+      <c r="J42" s="13" t="n">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>452.3</v>
+        <v>433.9</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>452.3</v>
+        <v>435</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>452.3</v>
+        <v>437.35</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>431.5</v>
+        <v>427.7</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>433.9</v>
+        <v>428.6</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-18.4</v>
-      </c>
-      <c r="J43" s="10" t="n">
-        <v>-4.07</v>
+        <v>-5.3</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1624.5</v>
+        <v>1561</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1617.2</v>
+        <v>1567.8</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1628.8</v>
+        <v>1597.5</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1556.5</v>
+        <v>1550.2</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1561</v>
+        <v>1574.6</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>-63.5</v>
+        <v>13.6</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>-3.91</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1304.9</v>
+        <v>1292.3</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1304.6</v>
+        <v>1279.1</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1309</v>
+        <v>1356.6</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1289</v>
+        <v>1274.7</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1292.3</v>
+        <v>1327.6</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-12.6</v>
+        <v>35.3</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>-0.97</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>464.45</v>
+        <v>463.05</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>465</v>
+        <v>463.25</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>469</v>
+        <v>473.6</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>461.65</v>
+        <v>459.5</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>463.05</v>
+        <v>462.25</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="J46" s="10" t="n">
-        <v>-0.3</v>
+        <v>-0.8</v>
+      </c>
+      <c r="J46" s="13" t="n">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1375.2</v>
+        <v>1320.4</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1373.4</v>
+        <v>1321</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1373.4</v>
+        <v>1328</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1316.9</v>
+        <v>1291.4</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1320.4</v>
+        <v>1297.1</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-54.8</v>
-      </c>
-      <c r="J47" s="10" t="n">
-        <v>-3.98</v>
+        <v>-23.3</v>
+      </c>
+      <c r="J47" s="13" t="n">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2139</v>
+        <v>2125.2</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2139.9</v>
+        <v>2127.8</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2157.2</v>
+        <v>2147</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2118</v>
+        <v>2111.6</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2125.2</v>
+        <v>2134.5</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>-13.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>-0.65</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>527.35</v>
+        <v>512.6</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>529.65</v>
+        <v>525.35</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>511.6</v>
+        <v>512.6</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>516</v>
+        <v>519.85</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-14</v>
+        <v>3.85</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>-2.64</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1866.2</v>
+        <v>1872.7</v>
       </c>
       <c r="E50" s="12" t="n">
+        <v>1872.7</v>
+      </c>
+      <c r="F50" s="12" t="n">
         <v>1880</v>
       </c>
-      <c r="F50" s="12" t="n">
-        <v>1909.5</v>
-      </c>
       <c r="G50" s="12" t="n">
-        <v>1839.3</v>
+        <v>1814.9</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1872.7</v>
+        <v>1860.5</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>6.5</v>
+        <v>-12.2</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>0.35</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>290.2</v>
+        <v>282.05</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>290</v>
+        <v>282.25</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>290.2</v>
+        <v>287.65</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>280.3</v>
+        <v>280</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>282.05</v>
+        <v>284.8</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-8.15</v>
+        <v>2.75</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>-2.81</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>254.2</v>
+        <v>244.45</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>254.2</v>
+        <v>245</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>254.9</v>
+        <v>249.4</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>243.1</v>
+        <v>242.35</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>244.45</v>
+        <v>245.6</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>-9.75</v>
+        <v>1.15</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>-3.84</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5238.5</v>
+        <v>5160</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5265</v>
+        <v>5170</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5265</v>
+        <v>5270</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>5147.5</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5160</v>
+        <v>5212</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-78.5</v>
+        <v>52</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>-1.5</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>473.45</v>
+        <v>473.25</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>472.75</v>
+        <v>480.8</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>476.25</v>
+        <v>480.8</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>469.55</v>
+        <v>461.6</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>473.25</v>
+        <v>463.1</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="J54" s="10" t="n">
-        <v>-0.04</v>
+        <v>-10.15</v>
+      </c>
+      <c r="J54" s="13" t="n">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1772.2</v>
+        <v>1781.2</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1772.2</v>
+        <v>1781.2</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1803.4</v>
+        <v>1793.6</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1760.6</v>
+        <v>1745.2</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1781.2</v>
+        <v>1776.9</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>9</v>
+        <v>-4.3</v>
       </c>
       <c r="J55" s="13" t="n">
-        <v>0.51</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1863.6</v>
+        <v>1848.3</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1854.4</v>
+        <v>1840</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1897.9</v>
+        <v>1874.8</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1783.5</v>
+        <v>1803.8</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1848.3</v>
+        <v>1856.4</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>-15.3</v>
+        <v>8.1</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>-0.82</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="57">
@@ -2669,25 +2669,25 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>74.53</v>
+        <v>72.14</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>74.54000000000001</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>75</v>
+        <v>73.13</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>71.8</v>
+        <v>71.11</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>72.14</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>-2.39</v>
-      </c>
-      <c r="J57" s="10" t="n">
-        <v>-3.21</v>
+        <v>-0.04</v>
+      </c>
+      <c r="J57" s="13" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="58">
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6714</v>
+        <v>6644</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6710</v>
+        <v>6680</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6745</v>
+        <v>6870</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6636</v>
+        <v>6643</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6644</v>
+        <v>6796</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>-70</v>
+        <v>152</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>-1.04</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>10772</v>
+        <v>10138</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>10744</v>
+        <v>10255</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>10744</v>
+        <v>11232</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>10100</v>
+        <v>10158</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>10138</v>
+        <v>11124</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>-634</v>
+        <v>986</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>-5.89</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>590.25</v>
+        <v>569.2</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>586.9</v>
+        <v>568.75</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>590.6</v>
+        <v>581.2</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>566.3</v>
+        <v>567.15</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>569.2</v>
+        <v>574.15</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>-21.05</v>
+        <v>4.95</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>-3.57</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1279.9</v>
+        <v>1270</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1278.9</v>
+        <v>1245.6</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1288.3</v>
+        <v>1303.8</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1264.5</v>
+        <v>1230</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1270</v>
+        <v>1265.3</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="J61" s="10" t="n">
-        <v>-0.77</v>
+        <v>-4.7</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7202.5</v>
+        <v>7126</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7203.5</v>
+        <v>7125</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7275.5</v>
+        <v>7157</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>7105</v>
+        <v>6863</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7126</v>
+        <v>6971.5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-76.5</v>
-      </c>
-      <c r="J62" s="10" t="n">
-        <v>-1.06</v>
+        <v>-154.5</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2966.7</v>
+        <v>2960.7</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2974</v>
+        <v>2977.9</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2981.2</v>
+        <v>3005</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2922</v>
+        <v>2944</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2960.7</v>
+        <v>2982.7</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>-6</v>
+        <v>22</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>-0.2</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>352.7</v>
+        <v>346.3</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>350.15</v>
+        <v>346</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>353.2</v>
+        <v>355.4</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>344.75</v>
+        <v>346</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>346.3</v>
+        <v>349.3</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>-6.4</v>
+        <v>3</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>-1.81</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>292.45</v>
+        <v>284.8</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>291.55</v>
+        <v>285.9</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>293.65</v>
+        <v>285.9</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>283.8</v>
+        <v>277.1</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>284.8</v>
+        <v>280.05</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-7.65</v>
-      </c>
-      <c r="J65" s="10" t="n">
-        <v>-2.62</v>
+        <v>-4.75</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>162.51</v>
+        <v>160.35</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>161.01</v>
+        <v>160</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>162.79</v>
+        <v>164.81</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>159.7</v>
+        <v>159.1</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>160.35</v>
+        <v>163.31</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>-2.16</v>
+        <v>2.96</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>-1.33</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2347.3</v>
+        <v>2257.1</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2340.9</v>
+        <v>2245.2</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2340.9</v>
+        <v>2326.5</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2244</v>
+        <v>2245.2</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2257.1</v>
+        <v>2277.6</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>-90.2</v>
+        <v>20.5</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>-3.84</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="10" t="n">
+      <c r="J68" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>485</v>
+        <v>470.15</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>484.5</v>
+        <v>472</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>484.5</v>
+        <v>496</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>467.9</v>
+        <v>471.15</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>470.15</v>
+        <v>489.95</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>-14.85</v>
+        <v>19.8</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>-3.06</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1005.9</v>
+        <v>1030.2</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1011.1</v>
+        <v>1033</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1045.9</v>
+        <v>1043.8</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1005.3</v>
+        <v>1014.9</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1030.2</v>
+        <v>1030.5</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="J70" s="13" t="n">
-        <v>2.42</v>
+        <v>0.3</v>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1794.3</v>
+        <v>1712.4</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1788</v>
+        <v>1710</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1791.8</v>
+        <v>1756.4</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1710</v>
+        <v>1696</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1712.4</v>
+        <v>1730.6</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>-81.90000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>-4.56</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>755.6</v>
+        <v>729.05</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>754</v>
+        <v>729.05</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>757.4</v>
+        <v>744</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>726.1</v>
+        <v>724.35</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>729.05</v>
+        <v>728.35</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-26.55</v>
-      </c>
-      <c r="J72" s="10" t="n">
-        <v>-3.51</v>
+        <v>-0.7</v>
+      </c>
+      <c r="J72" s="13" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2984.2</v>
+        <v>2903</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2980</v>
+        <v>2910.3</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2984.2</v>
+        <v>2969.3</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2893.7</v>
+        <v>2910</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2903</v>
+        <v>2945.6</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>-81.2</v>
+        <v>42.6</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>-2.72</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>380.95</v>
+        <v>368.25</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>382.9</v>
+        <v>368.75</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>383.2</v>
+        <v>369.35</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>367</v>
+        <v>359.5</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>368.25</v>
+        <v>360.85</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="J74" s="10" t="n">
-        <v>-3.33</v>
+        <v>-7.4</v>
+      </c>
+      <c r="J74" s="13" t="n">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4756.3</v>
+        <v>4572.5</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4730</v>
+        <v>4550</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4744.9</v>
+        <v>4692</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4556.1</v>
+        <v>4536.7</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4572.5</v>
+        <v>4618.5</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>-183.8</v>
+        <v>46</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>-3.86</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1230</v>
+        <v>1190.9</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1225.5</v>
+        <v>1190.5</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1231.6</v>
+        <v>1204</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1187.4</v>
+        <v>1183.2</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1190.9</v>
+        <v>1199.2</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>-39.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>-3.18</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1194.9</v>
+        <v>1145.8</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1183</v>
+        <v>1146.3</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1184</v>
+        <v>1154.6</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1142.6</v>
+        <v>1137.1</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1145.8</v>
+        <v>1143.2</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-49.1</v>
-      </c>
-      <c r="J77" s="10" t="n">
-        <v>-4.11</v>
+        <v>-2.6</v>
+      </c>
+      <c r="J77" s="13" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2747.2</v>
+        <v>2632.8</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2713</v>
+        <v>2630</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2759.3</v>
+        <v>2689.2</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2623.4</v>
+        <v>2630</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2632.8</v>
+        <v>2652.3</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>-114.4</v>
+        <v>19.5</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>-4.16</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>763.65</v>
+        <v>750.45</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>756.6</v>
+        <v>752</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>759.7</v>
+        <v>759.95</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>747.8</v>
+        <v>747.35</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>750.45</v>
+        <v>749.6</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-13.2</v>
-      </c>
-      <c r="J79" s="10" t="n">
-        <v>-1.73</v>
+        <v>-0.85</v>
+      </c>
+      <c r="J79" s="13" t="n">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>622.7</v>
+        <v>601.8</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>622</v>
+        <v>602.95</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>622</v>
+        <v>608.5</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>600.35</v>
+        <v>598.85</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>601.8</v>
+        <v>602.8</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>-20.9</v>
+        <v>1</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>-3.36</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5228.5</v>
+        <v>5082.5</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5230</v>
+        <v>5117.5</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5270</v>
+        <v>5128</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>5070</v>
+        <v>4977</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5082.5</v>
+        <v>4995</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-146</v>
-      </c>
-      <c r="J81" s="10" t="n">
-        <v>-2.79</v>
+        <v>-87.5</v>
+      </c>
+      <c r="J81" s="13" t="n">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1023.5</v>
+        <v>1041.4</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1027.2</v>
+        <v>1048</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1054.6</v>
+        <v>1082.4</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1025</v>
+        <v>1047</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1041.4</v>
+        <v>1073.1</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="J82" s="13" t="n">
-        <v>1.75</v>
+        <v>31.7</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>3.04</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>572.9</v>
+        <v>564.2</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>592.3</v>
+        <v>600</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>560.35</v>
+        <v>577</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>564.2</v>
+        <v>595.3</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>-8.699999999999999</v>
+        <v>31.1</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>-1.52</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>377.8</v>
+        <v>369.9</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>370.5</v>
+        <v>372.4</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>375.05</v>
+        <v>392</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>363.7</v>
+        <v>370.55</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>369.9</v>
+        <v>390.1</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>-7.9</v>
+        <v>20.2</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>-2.09</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2307.2</v>
+        <v>2262</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2285.3</v>
+        <v>2265</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2307</v>
+        <v>2295.8</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2256</v>
+        <v>2250</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2262</v>
+        <v>2267.3</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>-45.2</v>
+        <v>5.3</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>-1.96</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>29340</v>
+        <v>28455</v>
       </c>
       <c r="E86" s="12" t="n">
-        <v>29340</v>
+        <v>28450</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>29540</v>
+        <v>28860</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>28100</v>
+        <v>28000</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>28455</v>
+        <v>28215</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-885</v>
-      </c>
-      <c r="J86" s="10" t="n">
-        <v>-3.02</v>
+        <v>-240</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>69.22</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>69.01000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>69.27</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>67.53</v>
+        <v>67.5</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>67.68000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>-1.54</v>
+        <v>0.62</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>-2.22</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>130.71</v>
+        <v>127.21</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>130</v>
+        <v>127.2</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>131.25</v>
+        <v>128.81</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>127</v>
+        <v>125.69</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>127.21</v>
+        <v>127.53</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>-3.5</v>
+        <v>0.32</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>-2.68</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>160.69</v>
+        <v>156.81</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>160</v>
+        <v>156.21</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>161.09</v>
+        <v>160.1</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>156.41</v>
+        <v>154.74</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>156.81</v>
+        <v>159.3</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>-3.88</v>
+        <v>2.49</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>-2.41</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>661.3</v>
+        <v>634.4</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>674.15</v>
+        <v>636.95</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>674.9</v>
+        <v>644.85</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>633.15</v>
+        <v>622.45</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>634.4</v>
+        <v>637.4</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>-26.9</v>
+        <v>3</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>-4.07</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2065</v>
+        <v>2011.8</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2075</v>
+        <v>2000</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2079.3</v>
+        <v>2022.8</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>2004.8</v>
+        <v>1966</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>2011.8</v>
+        <v>1969.2</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-53.2</v>
-      </c>
-      <c r="J91" s="10" t="n">
-        <v>-2.58</v>
+        <v>-42.6</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4299.4</v>
+        <v>4201.7</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4297.1</v>
+        <v>4205.4</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4309.1</v>
+        <v>4283.6</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4187.7</v>
+        <v>4146.3</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4201.7</v>
+        <v>4255.8</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>-97.7</v>
+        <v>54.1</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>-2.27</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>922.3</v>
+        <v>892.85</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>920</v>
+        <v>891</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>922.3</v>
+        <v>906.8</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>890.1</v>
+        <v>890.3</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>892.85</v>
+        <v>892.5</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-29.45</v>
-      </c>
-      <c r="J93" s="10" t="n">
-        <v>-3.19</v>
+        <v>-0.35</v>
+      </c>
+      <c r="J93" s="13" t="n">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>410.65</v>
+        <v>400.8</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>411.8</v>
+        <v>402</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>411.85</v>
+        <v>416.7</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>400</v>
+        <v>399.65</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>400.8</v>
+        <v>413.2</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>-9.85</v>
+        <v>12.4</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>-2.4</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1177</v>
+        <v>1140.3</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1162</v>
+        <v>1136.6</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1162</v>
+        <v>1142.6</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1140.3</v>
+        <v>1123.1</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-36.7</v>
-      </c>
-      <c r="J95" s="10" t="n">
-        <v>-3.12</v>
+        <v>-17.2</v>
+      </c>
+      <c r="J95" s="13" t="n">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>140.37</v>
+        <v>137.65</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>139.39</v>
+        <v>138</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>139.76</v>
+        <v>142.6</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>137.25</v>
+        <v>137.84</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>137.65</v>
+        <v>141.69</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>-2.72</v>
+        <v>4.04</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>-1.94</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1535</v>
+        <v>1509.1</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1535</v>
+        <v>1518</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1544.8</v>
+        <v>1538.9</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1509.1</v>
+        <v>1506.3</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-25.9</v>
-      </c>
-      <c r="J97" s="10" t="n">
-        <v>-1.69</v>
+        <v>-2.8</v>
+      </c>
+      <c r="J97" s="13" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>556.8</v>
+        <v>534</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>555</v>
+        <v>530.5</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>557.85</v>
+        <v>542.45</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>531</v>
+        <v>530.5</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>534</v>
+        <v>536.1</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>-22.8</v>
+        <v>2.1</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>-4.09</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>305.85</v>
+        <v>300.7</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>305.35</v>
+        <v>302</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>306.25</v>
+        <v>305.8</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>300.1</v>
+        <v>301.05</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>300.7</v>
+        <v>304.45</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>-5.15</v>
+        <v>3.75</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>-1.68</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1232</v>
+        <v>1214.3</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1233.1</v>
+        <v>1219</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1242.8</v>
+        <v>1258</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1211.1</v>
+        <v>1216.1</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1214.3</v>
+        <v>1242.9</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>-17.7</v>
+        <v>28.6</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>-1.44</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5465</v>
+        <v>5377.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5465</v>
+        <v>5360</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5494</v>
+        <v>5449</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5334</v>
+        <v>5296.5</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5377.5</v>
+        <v>5422.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>-87.5</v>
+        <v>45</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>-1.6</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>741.3</v>
+        <v>732.1</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>741.25</v>
+        <v>732.1</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>745.25</v>
+        <v>743.7</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>724.3</v>
+        <v>722.45</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>732.1</v>
+        <v>725.25</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="J102" s="10" t="n">
-        <v>-1.24</v>
+        <v>-6.85</v>
+      </c>
+      <c r="J102" s="13" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>556.65</v>
+        <v>517.95</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>539.75</v>
+        <v>517.95</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>539.75</v>
+        <v>521.8</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>512</v>
+        <v>506.9</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>517.95</v>
+        <v>509.2</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-38.7</v>
-      </c>
-      <c r="J103" s="10" t="n">
-        <v>-6.95</v>
+        <v>-8.75</v>
+      </c>
+      <c r="J103" s="13" t="n">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1262.6</v>
+        <v>1252.3</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1262</v>
+        <v>1255</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1272.6</v>
+        <v>1282.4</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1246.2</v>
+        <v>1255</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1252.3</v>
+        <v>1274.9</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>-10.3</v>
+        <v>22.6</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>-0.82</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>460.5</v>
+        <v>442.15</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>460.5</v>
+        <v>433.7</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>463.65</v>
+        <v>453.15</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>440.1</v>
+        <v>422.25</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>442.15</v>
+        <v>448.4</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>-18.35</v>
+        <v>6.25</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>-3.98</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1095.5</v>
+        <v>1072.6</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1090.5</v>
+        <v>1070.5</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1068.5</v>
+        <v>1066.4</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1072.6</v>
+        <v>1072.7</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>-22.9</v>
+        <v>0.1</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>-2.09</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>381.05</v>
+        <v>376</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>380.2</v>
+        <v>377.9</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>381.05</v>
+        <v>384</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>374.55</v>
+        <v>376.85</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>376</v>
+        <v>377.65</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>-5.05</v>
+        <v>1.65</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>-1.33</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>733.45</v>
+        <v>712.05</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>733</v>
+        <v>711</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>733</v>
+        <v>718.05</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>703.25</v>
+        <v>705</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>712.05</v>
+        <v>710.65</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-21.4</v>
-      </c>
-      <c r="J108" s="10" t="n">
-        <v>-2.92</v>
+        <v>-1.4</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1652.4</v>
+        <v>1587</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1641</v>
+        <v>1581.5</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1658.7</v>
+        <v>1613.4</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1581.5</v>
+        <v>1568</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1587</v>
+        <v>1575.7</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-65.40000000000001</v>
-      </c>
-      <c r="J109" s="10" t="n">
-        <v>-3.96</v>
+        <v>-11.3</v>
+      </c>
+      <c r="J109" s="13" t="n">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1266.8</v>
+        <v>1268</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1289</v>
+        <v>1292.5</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1260.1</v>
+        <v>1246.6</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1268</v>
+        <v>1280.5</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J110" s="13" t="n">
-        <v>0.09</v>
+        <v>12.5</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>585.6</v>
+        <v>567.65</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>585.6</v>
+        <v>565.8</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>590</v>
+        <v>587.85</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>565.6</v>
+        <v>565.8</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>567.65</v>
+        <v>585.65</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>-17.95</v>
+        <v>18</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>-3.07</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3940.2</v>
+        <v>3856.5</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3925.1</v>
+        <v>3848</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3940</v>
+        <v>3953</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3847</v>
+        <v>3848</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3856.5</v>
+        <v>3915.8</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>-83.7</v>
+        <v>59.3</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>-2.12</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>295</v>
+        <v>280.65</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>295.1</v>
+        <v>290.25</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>279.25</v>
+        <v>278.8</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>280.65</v>
+        <v>281.9</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>-14.35</v>
+        <v>1.25</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>-4.86</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="10" t="n">
+      <c r="J114" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3788.4</v>
+        <v>3603.7</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3769.5</v>
+        <v>3578</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3802.2</v>
+        <v>3602.4</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3561.6</v>
+        <v>3487.3</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3603.7</v>
+        <v>3497.9</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-184.7</v>
-      </c>
-      <c r="J115" s="10" t="n">
-        <v>-4.88</v>
+        <v>-105.8</v>
+      </c>
+      <c r="J115" s="13" t="n">
+        <v>-2.94</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2255.9</v>
+        <v>2245.4</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2256</v>
+        <v>2245.8</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2289.8</v>
+        <v>2267.2</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2233</v>
+        <v>2210.6</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2245.4</v>
+        <v>2215.6</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="J116" s="10" t="n">
-        <v>-0.47</v>
+        <v>-29.8</v>
+      </c>
+      <c r="J116" s="13" t="n">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3245.9</v>
+        <v>3176</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3240</v>
+        <v>3176</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3261.6</v>
+        <v>3189.6</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3166.3</v>
+        <v>3103.6</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3176</v>
+        <v>3111.8</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-69.90000000000001</v>
-      </c>
-      <c r="J117" s="10" t="n">
-        <v>-2.15</v>
+        <v>-64.2</v>
+      </c>
+      <c r="J117" s="13" t="n">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>305.45</v>
+        <v>293.2</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>305.45</v>
+        <v>301.55</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>307.75</v>
+        <v>311.5</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>292.05</v>
+        <v>297</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>293.2</v>
+        <v>309.5</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>-12.25</v>
+        <v>16.3</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>-4.01</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>842.55</v>
+        <v>830</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>842</v>
+        <v>828.05</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>846</v>
+        <v>837.2</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>827.35</v>
+        <v>825.2</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>830</v>
+        <v>833.4</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>-12.55</v>
+        <v>3.4</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>-1.49</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13483</v>
+        <v>13172</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13442</v>
+        <v>13187</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13455</v>
+        <v>13285</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>13150</v>
+        <v>12986</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13172</v>
+        <v>13103</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-311</v>
-      </c>
-      <c r="J120" s="10" t="n">
-        <v>-2.31</v>
+        <v>-69</v>
+      </c>
+      <c r="J120" s="13" t="n">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="10" t="n">
+      <c r="J121" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3187.9</v>
+        <v>3156.9</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3200</v>
+        <v>3249</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3256</v>
+        <v>3265</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3146.3</v>
+        <v>3131</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3156.9</v>
+        <v>3204.2</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>-31</v>
+        <v>47.3</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>-0.97</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>559.9</v>
+        <v>548.1</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>552.5</v>
+        <v>549</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>554.2</v>
+        <v>559.1</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>515</v>
+        <v>541.3</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>548.1</v>
+        <v>548</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-11.8</v>
-      </c>
-      <c r="J123" s="10" t="n">
-        <v>-2.11</v>
+        <v>-0.1</v>
+      </c>
+      <c r="J123" s="13" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1695.5</v>
+        <v>1653.7</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1690.1</v>
+        <v>1670.5</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1694.1</v>
+        <v>1698.8</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1640.6</v>
+        <v>1590.1</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1653.7</v>
+        <v>1597.9</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-41.8</v>
-      </c>
-      <c r="J124" s="10" t="n">
-        <v>-2.47</v>
+        <v>-55.8</v>
+      </c>
+      <c r="J124" s="13" t="n">
+        <v>-3.37</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1106.4</v>
+        <v>1064.4</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1108.7</v>
+        <v>1053.3</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1110.9</v>
+        <v>1065</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1058.7</v>
+        <v>1024</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1064.4</v>
+        <v>1046.9</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-42</v>
-      </c>
-      <c r="J125" s="10" t="n">
-        <v>-3.8</v>
+        <v>-17.5</v>
+      </c>
+      <c r="J125" s="13" t="n">
+        <v>-1.64</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>130.3</v>
+        <v>124.26</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>130.66</v>
+        <v>127.53</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>123.55</v>
+        <v>123.83</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>124.26</v>
+        <v>126.32</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>-6.04</v>
+        <v>2.06</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>-4.64</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2201.2</v>
+        <v>2146.5</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2175.5</v>
+        <v>2143</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2179</v>
+        <v>2161.6</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2122.5</v>
+        <v>2127</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2146.5</v>
+        <v>2145.2</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-54.7</v>
-      </c>
-      <c r="J127" s="10" t="n">
-        <v>-2.49</v>
+        <v>-1.3</v>
+      </c>
+      <c r="J127" s="13" t="n">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="128">
@@ -5083,25 +5083,25 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>128910</v>
+        <v>126505</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>129000</v>
+        <v>126535</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>129565</v>
+        <v>127500</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>126050</v>
+        <v>124900</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>126505</v>
+        <v>126480</v>
       </c>
       <c r="I128" s="12" t="n">
-        <v>-2405</v>
-      </c>
-      <c r="J128" s="10" t="n">
-        <v>-1.87</v>
+        <v>-25</v>
+      </c>
+      <c r="J128" s="13" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="129">
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3438.2</v>
+        <v>3353.4</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3435</v>
+        <v>3421.8</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3450</v>
+        <v>3533.1</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3339.3</v>
+        <v>3383.7</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3353.4</v>
+        <v>3506.4</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>-84.8</v>
+        <v>153</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>-2.47</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>393.05</v>
+        <v>394.05</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>403.2</v>
+        <v>411.25</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>392.3</v>
+        <v>397</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>394.05</v>
+        <v>408.25</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J130" s="13" t="n">
-        <v>0.25</v>
+        <v>14.2</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>961.2</v>
+        <v>930.9</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>958.3</v>
+        <v>930.9</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>958.3</v>
+        <v>940.9</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>928.6</v>
+        <v>920.2</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>930.9</v>
+        <v>927.85</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-30.3</v>
-      </c>
-      <c r="J131" s="10" t="n">
-        <v>-3.15</v>
+        <v>-3.05</v>
+      </c>
+      <c r="J131" s="13" t="n">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>7071.5</v>
+        <v>6950.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>7070</v>
+        <v>6940</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>7070</v>
+        <v>7120</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6912.5</v>
+        <v>6890</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>6950.5</v>
+        <v>6910.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-121</v>
-      </c>
-      <c r="J132" s="10" t="n">
-        <v>-1.71</v>
+        <v>-40</v>
+      </c>
+      <c r="J132" s="13" t="n">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1481.9</v>
+        <v>1468.6</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1470</v>
+        <v>1468.6</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1466.1</v>
+        <v>1463.5</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1468.6</v>
+        <v>1468.9</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>-13.3</v>
+        <v>0.3</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>-0.9</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>86.79000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>86.62</v>
+        <v>86.5</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>88.47</v>
+        <v>91.8</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>86.38</v>
+        <v>86.42</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>86.62</v>
+        <v>91.11</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>-0.17</v>
+        <v>4.49</v>
       </c>
       <c r="J134" s="10" t="n">
-        <v>-0.2</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>392.95</v>
+        <v>392.7</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>392.2</v>
+        <v>392</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>399.85</v>
+        <v>394.05</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>391.25</v>
+        <v>385.8</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>392.7</v>
+        <v>390.45</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J135" s="10" t="n">
-        <v>-0.06</v>
+        <v>-2.25</v>
+      </c>
+      <c r="J135" s="13" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="136">
@@ -5355,24 +5355,24 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1634.7</v>
+        <v>1626.7</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1669</v>
+        <v>1638</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1712</v>
+        <v>1643.1</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1622.6</v>
+        <v>1610.1</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1626.7</v>
+        <v>1618.7</v>
       </c>
       <c r="I136" s="12" t="n">
         <v>-8</v>
       </c>
-      <c r="J136" s="10" t="n">
+      <c r="J136" s="13" t="n">
         <v>-0.49</v>
       </c>
     </row>
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9239.5</v>
+        <v>9010.5</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9201</v>
+        <v>9000</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9235</v>
+        <v>9090</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>8985</v>
+        <v>8910</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>9010.5</v>
+        <v>8928.5</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-229</v>
-      </c>
-      <c r="J137" s="10" t="n">
-        <v>-2.48</v>
+        <v>-82</v>
+      </c>
+      <c r="J137" s="13" t="n">
+        <v>-0.91</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>281</v>
+        <v>294.5</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>286.9</v>
+        <v>297</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>299.9</v>
+        <v>300.2</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>286.85</v>
+        <v>294.1</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>294.5</v>
+        <v>297.15</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J138" s="13" t="n">
-        <v>4.8</v>
+        <v>2.65</v>
+      </c>
+      <c r="J138" s="10" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>36245</v>
+        <v>35085</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>36390</v>
+        <v>35115</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>36390</v>
+        <v>35830</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>34950</v>
+        <v>34720</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>35085</v>
+        <v>35330</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>-1160</v>
+        <v>245</v>
       </c>
       <c r="J139" s="10" t="n">
-        <v>-3.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="10" t="n">
+      <c r="J140" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>5098.1</v>
+        <v>4877.1</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>5073.8</v>
+        <v>4855</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>5073.8</v>
+        <v>4914</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4841</v>
+        <v>4815.8</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4877.1</v>
+        <v>4845</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-221</v>
-      </c>
-      <c r="J141" s="10" t="n">
-        <v>-4.33</v>
+        <v>-32.1</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>275.75</v>
+        <v>271.15</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>274.75</v>
+        <v>273.5</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>276.5</v>
+        <v>274.1</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>270.4</v>
+        <v>269.2</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>271.15</v>
+        <v>271.35</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>-4.6</v>
+        <v>0.2</v>
       </c>
       <c r="J142" s="10" t="n">
-        <v>-1.67</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>448.5</v>
+        <v>440.7</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>448</v>
+        <v>440.05</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>456.8</v>
+        <v>453.9</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>439.45</v>
+        <v>437.1</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>440.7</v>
+        <v>446</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>-7.8</v>
+        <v>5.3</v>
       </c>
       <c r="J143" s="10" t="n">
-        <v>-1.74</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1437.2</v>
+        <v>1453</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1433.1</v>
+        <v>1453</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1480</v>
+        <v>1472</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1427.6</v>
+        <v>1438.3</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1453</v>
+        <v>1445.6</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>15.8</v>
+        <v>-7.4</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>1.1</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>3090.8</v>
+        <v>2997.6</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>3088.8</v>
+        <v>2998.7</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3088.8</v>
+        <v>3098.3</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2991</v>
+        <v>2998.7</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>2997.6</v>
+        <v>3051</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>-93.2</v>
+        <v>53.4</v>
       </c>
       <c r="J145" s="10" t="n">
-        <v>-3.02</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>104.62</v>
+        <v>102.78</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>104</v>
+        <v>102.99</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>104.97</v>
+        <v>103.89</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>102.55</v>
+        <v>101.35</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>102.78</v>
+        <v>102.77</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="J146" s="10" t="n">
-        <v>-1.76</v>
+        <v>-0.01</v>
+      </c>
+      <c r="J146" s="13" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>9065.5</v>
+        <v>9021.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>9115</v>
+        <v>8991</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>9220</v>
+        <v>9072.5</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8979</v>
+        <v>8865</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>9021.5</v>
+        <v>8887.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-44</v>
-      </c>
-      <c r="J147" s="10" t="n">
-        <v>-0.49</v>
+        <v>-134</v>
+      </c>
+      <c r="J147" s="13" t="n">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>310.9</v>
+        <v>306.3</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>309.45</v>
+        <v>304.25</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>310.75</v>
+        <v>305.4</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>305.5</v>
+        <v>295.65</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>306.3</v>
+        <v>301.5</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="J148" s="10" t="n">
-        <v>-1.48</v>
+        <v>-4.8</v>
+      </c>
+      <c r="J148" s="13" t="n">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1026</v>
+        <v>1014.6</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>1045</v>
+        <v>995</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1045</v>
+        <v>1032</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>1000</v>
+        <v>992.3</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1014.6</v>
+        <v>1023.5</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>-11.4</v>
+        <v>8.9</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>-1.11</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>337.5</v>
+        <v>325.25</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>335.2</v>
+        <v>325.25</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>339</v>
+        <v>332.4</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>324.1</v>
+        <v>324.9</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>325.25</v>
+        <v>325.75</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>-12.25</v>
+        <v>0.5</v>
       </c>
       <c r="J150" s="10" t="n">
-        <v>-3.63</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>351.55</v>
+        <v>344.35</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>350.15</v>
+        <v>345.45</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>353.65</v>
+        <v>351.1</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>343.55</v>
+        <v>342</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>344.35</v>
+        <v>346.55</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>-7.2</v>
+        <v>2.2</v>
       </c>
       <c r="J151" s="10" t="n">
-        <v>-2.05</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1388.2</v>
+        <v>1364</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1392</v>
+        <v>1361.4</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1393.5</v>
+        <v>1372.4</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1360.3</v>
+        <v>1352.4</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1364</v>
+        <v>1358.8</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-24.2</v>
-      </c>
-      <c r="J152" s="10" t="n">
-        <v>-1.74</v>
+        <v>-5.2</v>
+      </c>
+      <c r="J152" s="13" t="n">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>180.72</v>
+        <v>176.09</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>179.9</v>
+        <v>176.31</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>180.9</v>
+        <v>202.35</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>175.16</v>
+        <v>176.31</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>176.09</v>
+        <v>201.31</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>-4.63</v>
+        <v>25.22</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>-2.56</v>
+        <v>14.32</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>641.5</v>
+        <v>625.1</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>643.55</v>
+        <v>625.1</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>643.6</v>
+        <v>640.65</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>623.3</v>
+        <v>622.25</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>625.1</v>
+        <v>634.15</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>-16.4</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>-2.56</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1884.4</v>
+        <v>1833.9</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1866</v>
+        <v>1820</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1875.6</v>
+        <v>1851.4</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1825</v>
+        <v>1818.2</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1833.9</v>
+        <v>1837.5</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>-50.5</v>
+        <v>3.6</v>
       </c>
       <c r="J155" s="10" t="n">
-        <v>-2.68</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>973.6</v>
+        <v>974.6</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>976.9</v>
+        <v>978</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>981.4</v>
+        <v>981.2</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>962.4</v>
+        <v>961.2</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>974.6</v>
+        <v>970.1</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>1</v>
+        <v>-4.5</v>
       </c>
       <c r="J156" s="13" t="n">
-        <v>0.1</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>25205</v>
+        <v>24860</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>25100</v>
+        <v>24705</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25325</v>
+        <v>25285</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>24800</v>
+        <v>24705</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>24860</v>
+        <v>24995</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>-345</v>
+        <v>135</v>
       </c>
       <c r="J157" s="10" t="n">
-        <v>-1.37</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>975.95</v>
+        <v>930.45</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>971</v>
+        <v>925.2</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>979.95</v>
+        <v>938.4</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>925.95</v>
+        <v>915</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>930.45</v>
+        <v>920.55</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-45.5</v>
-      </c>
-      <c r="J158" s="10" t="n">
-        <v>-4.66</v>
+        <v>-9.9</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3605.6</v>
+        <v>3574.4</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3605</v>
+        <v>3574.4</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3644.8</v>
+        <v>3628.5</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3555.8</v>
+        <v>3518.2</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3574.4</v>
+        <v>3532.2</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-31.2</v>
-      </c>
-      <c r="J159" s="10" t="n">
-        <v>-0.87</v>
+        <v>-42.2</v>
+      </c>
+      <c r="J159" s="13" t="n">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2798.5</v>
+        <v>2721.2</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2785</v>
+        <v>2738.9</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2800</v>
+        <v>2756.3</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2714.1</v>
+        <v>2688.8</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2721.2</v>
+        <v>2695.2</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-77.3</v>
-      </c>
-      <c r="J160" s="10" t="n">
-        <v>-2.76</v>
+        <v>-26</v>
+      </c>
+      <c r="J160" s="13" t="n">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1872.7</v>
+        <v>1845.7</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1875</v>
+        <v>1845.7</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1879.4</v>
+        <v>1860</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1840</v>
+        <v>1820</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1845.7</v>
+        <v>1824.8</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-27</v>
-      </c>
-      <c r="J161" s="10" t="n">
-        <v>-1.44</v>
+        <v>-20.9</v>
+      </c>
+      <c r="J161" s="13" t="n">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>567.75</v>
+        <v>560.2</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>567.75</v>
+        <v>560.5</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>570.25</v>
+        <v>560.5</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>558.05</v>
+        <v>530</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>560.2</v>
+        <v>532.95</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-7.55</v>
-      </c>
-      <c r="J162" s="10" t="n">
-        <v>-1.33</v>
+        <v>-27.25</v>
+      </c>
+      <c r="J162" s="13" t="n">
+        <v>-4.86</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>482.5</v>
+        <v>478.75</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>486.25</v>
+        <v>478</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>486.25</v>
+        <v>478.75</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>478.75</v>
+        <v>463.25</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="J163" s="10" t="n">
-        <v>-0.78</v>
+        <v>-15.5</v>
+      </c>
+      <c r="J163" s="13" t="n">
+        <v>-3.24</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>761.35</v>
+        <v>770.25</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>765</v>
+        <v>770.6</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>793.75</v>
+        <v>779.75</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>761</v>
+        <v>765.15</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>770.25</v>
+        <v>768.1</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>8.9</v>
+        <v>-2.15</v>
       </c>
       <c r="J164" s="13" t="n">
-        <v>1.17</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1571.5</v>
+        <v>1539.9</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1571.5</v>
+        <v>1545</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1591.4</v>
+        <v>1575.9</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1530.4</v>
+        <v>1532.3</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1539.9</v>
+        <v>1558.8</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>-31.6</v>
+        <v>18.9</v>
       </c>
       <c r="J165" s="10" t="n">
-        <v>-2.01</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1271</v>
+        <v>1253</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1269.7</v>
+        <v>1249.1</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1282.7</v>
+        <v>1277.9</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1250.4</v>
+        <v>1233</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1253</v>
+        <v>1235</v>
       </c>
       <c r="I166" s="12" t="n">
         <v>-18</v>
       </c>
-      <c r="J166" s="10" t="n">
-        <v>-1.42</v>
+      <c r="J166" s="13" t="n">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="10" t="n">
+      <c r="J167" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>433.2</v>
+        <v>418.4</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>431.2</v>
+        <v>391</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>433.4</v>
+        <v>413.75</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>417.25</v>
+        <v>390.8</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>418.4</v>
+        <v>404.45</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="J168" s="10" t="n">
-        <v>-3.42</v>
+        <v>-13.95</v>
+      </c>
+      <c r="J168" s="13" t="n">
+        <v>-3.33</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>212.08</v>
+        <v>212</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>212</v>
+        <v>213.24</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>216.33</v>
+        <v>220.91</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>211.5</v>
+        <v>213.07</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>212</v>
+        <v>219.62</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>-0.08</v>
+        <v>7.62</v>
       </c>
       <c r="J169" s="10" t="n">
-        <v>-0.04</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2392.9</v>
+        <v>2300.3</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2375</v>
+        <v>2306</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2375</v>
+        <v>2309.2</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2283</v>
+        <v>2269</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2300.3</v>
+        <v>2272.8</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-92.59999999999999</v>
-      </c>
-      <c r="J170" s="10" t="n">
-        <v>-3.87</v>
+        <v>-27.5</v>
+      </c>
+      <c r="J170" s="13" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1457.4</v>
+        <v>1392.9</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1447</v>
+        <v>1392.9</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1447</v>
+        <v>1399.9</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1388.9</v>
+        <v>1371.6</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1392.9</v>
+        <v>1375</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-64.5</v>
-      </c>
-      <c r="J171" s="10" t="n">
-        <v>-4.43</v>
+        <v>-17.9</v>
+      </c>
+      <c r="J171" s="13" t="n">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2992.2</v>
+        <v>2954</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>3014.3</v>
+        <v>2959</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3057.3</v>
+        <v>3070.7</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2931.3</v>
+        <v>2918.5</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2954</v>
+        <v>2941</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-38.2</v>
-      </c>
-      <c r="J172" s="10" t="n">
-        <v>-1.28</v>
+        <v>-13</v>
+      </c>
+      <c r="J172" s="13" t="n">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4205.6</v>
+        <v>4055.3</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4160</v>
+        <v>4030</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4213.6</v>
+        <v>4110</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>4047</v>
+        <v>3985.1</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4055.3</v>
+        <v>4090.7</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>-150.3</v>
+        <v>35.4</v>
       </c>
       <c r="J173" s="10" t="n">
-        <v>-3.57</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4517.1</v>
+        <v>4381.9</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4509.5</v>
+        <v>4355.8</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4509.5</v>
+        <v>4409.9</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4373</v>
+        <v>4264</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4381.9</v>
+        <v>4295.8</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-135.2</v>
-      </c>
-      <c r="J174" s="10" t="n">
-        <v>-2.99</v>
+        <v>-86.09999999999999</v>
+      </c>
+      <c r="J174" s="13" t="n">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1680.9</v>
+        <v>1597.6</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1670</v>
+        <v>1538.2</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1687.9</v>
+        <v>1561.5</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1585.5</v>
+        <v>1450</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1597.6</v>
+        <v>1457.1</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-83.3</v>
-      </c>
-      <c r="J175" s="10" t="n">
-        <v>-4.96</v>
+        <v>-140.5</v>
+      </c>
+      <c r="J175" s="13" t="n">
+        <v>-8.789999999999999</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4181.1</v>
+        <v>4050.6</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4156</v>
+        <v>4038.5</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4183.5</v>
+        <v>4127</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4037.6</v>
+        <v>4021</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4050.6</v>
+        <v>4084.5</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>-130.5</v>
+        <v>33.9</v>
       </c>
       <c r="J176" s="10" t="n">
-        <v>-3.12</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3613.7</v>
+        <v>3561</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3596.2</v>
+        <v>3565</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3613</v>
+        <v>3647.5</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3535</v>
+        <v>3483</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3561</v>
+        <v>3527.2</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-52.7</v>
-      </c>
-      <c r="J177" s="10" t="n">
-        <v>-1.46</v>
+        <v>-33.8</v>
+      </c>
+      <c r="J177" s="13" t="n">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1412.2</v>
+        <v>1410.5</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1412.5</v>
+        <v>1414</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1420.1</v>
+        <v>1415.4</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1391.5</v>
+        <v>1362</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1410.5</v>
+        <v>1381.2</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="J178" s="10" t="n">
-        <v>-0.12</v>
+        <v>-29.3</v>
+      </c>
+      <c r="J178" s="13" t="n">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11866</v>
+        <v>11516</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11866</v>
+        <v>11500</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11866</v>
+        <v>11652</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11503</v>
+        <v>11431</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11516</v>
+        <v>11573</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>-350</v>
+        <v>57</v>
       </c>
       <c r="J179" s="10" t="n">
-        <v>-2.95</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
+        <v>162.19</v>
+      </c>
+      <c r="E180" s="12" t="n">
+        <v>162.35</v>
+      </c>
+      <c r="F180" s="12" t="n">
         <v>163.81</v>
       </c>
-      <c r="E180" s="12" t="n">
-        <v>162</v>
-      </c>
-      <c r="F180" s="12" t="n">
-        <v>164.95</v>
-      </c>
       <c r="G180" s="12" t="n">
-        <v>161.39</v>
+        <v>159.76</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>162.19</v>
+        <v>162.46</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>-1.62</v>
+        <v>0.27</v>
       </c>
       <c r="J180" s="10" t="n">
-        <v>-0.99</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>669</v>
+        <v>626.15</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>670.8</v>
+        <v>627</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>671.15</v>
+        <v>636.5</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>622.25</v>
+        <v>624.3</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>626.15</v>
+        <v>630.1</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>-42.85</v>
+        <v>3.95</v>
       </c>
       <c r="J181" s="10" t="n">
-        <v>-6.41</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>298.4</v>
+        <v>305.05</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>298.1</v>
+        <v>311.95</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>309.9</v>
+        <v>325.5</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>298.1</v>
+        <v>308.8</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>305.05</v>
+        <v>323.35</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="J182" s="13" t="n">
-        <v>2.23</v>
+        <v>18.3</v>
+      </c>
+      <c r="J182" s="10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1306.5</v>
+        <v>1269.6</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1316</v>
+        <v>1269.6</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1348</v>
+        <v>1302.7</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1265.6</v>
+        <v>1255</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1269.6</v>
+        <v>1258.9</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-36.9</v>
-      </c>
-      <c r="J183" s="10" t="n">
-        <v>-2.82</v>
+        <v>-10.7</v>
+      </c>
+      <c r="J183" s="13" t="n">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>196.68</v>
+        <v>189.57</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>196.1</v>
+        <v>190.67</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>196.14</v>
+        <v>191.3</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>189.1</v>
+        <v>187.31</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>189.57</v>
+        <v>187.8</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-7.11</v>
-      </c>
-      <c r="J184" s="10" t="n">
-        <v>-3.62</v>
+        <v>-1.77</v>
+      </c>
+      <c r="J184" s="13" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="10" t="n">
+      <c r="J185" s="13" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>956.95</v>
+        <v>930.65</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>960.1</v>
+        <v>928.6</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>963.95</v>
+        <v>944.15</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>928.6</v>
+        <v>925.1</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>930.65</v>
+        <v>939.25</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>-26.3</v>
+        <v>8.6</v>
       </c>
       <c r="J186" s="10" t="n">
-        <v>-2.75</v>
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  12-May-2026 03:39 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  13-May-2026 03:42 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12-May-2026 03:39 PM</t>
+          <t>13-May-2026 03:42 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -93,12 +93,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 13-May-2026 03:42 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 14-May-2026 03:18 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>13-May-2026 03:42 PM</t>
+          <t>14-May-2026 03:18 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  13-May-2026 03:42 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  14-May-2026 03:18 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>468.5</v>
+        <v>468.55</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>466</v>
+        <v>469.05</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>476</v>
+        <v>472.55</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>465.6</v>
+        <v>458.25</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>468.55</v>
+        <v>468</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>0.05</v>
+        <v>-0.55</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>6328.5</v>
+        <v>6305</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>6344</v>
+        <v>6350</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>6395</v>
+        <v>6439</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>6212.5</v>
+        <v>6220</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>6305</v>
+        <v>6429</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>-23.5</v>
+        <v>124</v>
       </c>
       <c r="J4" s="13" t="n">
-        <v>-0.37</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>26900</v>
+        <v>27280</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>27100</v>
+        <v>27590</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>27595</v>
+        <v>27610</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>26920</v>
+        <v>27270</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>27280</v>
+        <v>27520</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>380</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>1.41</v>
+        <v>240</v>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>0.88</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>341.2</v>
+        <v>344.3</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>340</v>
+        <v>346.35</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>348.55</v>
+        <v>353.85</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>339.45</v>
+        <v>345.1</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>344.3</v>
+        <v>349.65</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>0.91</v>
+        <v>5.35</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>1.55</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>62.4</v>
+        <v>63.59</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>62.7</v>
+        <v>64</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>64.54000000000001</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>62.7</v>
+        <v>62.78</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>63.59</v>
+        <v>63.48</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1.19</v>
+        <v>-0.11</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>1.91</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1347</v>
+        <v>1366.4</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1347.4</v>
+        <v>1369.8</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1372.5</v>
+        <v>1387.5</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1341.8</v>
+        <v>1357.2</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1366.4</v>
+        <v>1378.2</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>1.44</v>
+        <v>11.8</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>0.86</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2405.2</v>
+        <v>2498</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2401.1</v>
+        <v>2530.1</v>
       </c>
       <c r="F9" s="9" t="n">
+        <v>2720</v>
+      </c>
+      <c r="G9" s="9" t="n">
         <v>2530</v>
       </c>
-      <c r="G9" s="9" t="n">
-        <v>2401.1</v>
-      </c>
       <c r="H9" s="9" t="n">
-        <v>2498</v>
+        <v>2712.9</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>3.86</v>
+        <v>214.9</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>8.6</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1688.2</v>
+        <v>1737.8</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1688.2</v>
+        <v>1761</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1752.3</v>
+        <v>1782.5</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1688</v>
+        <v>1745.4</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1737.8</v>
+        <v>1773.4</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>2.94</v>
+        <v>35.6</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>2.05</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5496.5</v>
+        <v>5462.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5450</v>
+        <v>5540</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5553</v>
+        <v>5629.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5441.5</v>
+        <v>5462.5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5462.5</v>
+        <v>5576.5</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>-34</v>
+        <v>114</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>-0.62</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>426.95</v>
+        <v>438.4</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>428.15</v>
+        <v>438.9</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>441.15</v>
+        <v>447.15</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>425.4</v>
+        <v>433.25</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>438.4</v>
+        <v>443.9</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>2.68</v>
+        <v>5.5</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>299.1</v>
+        <v>298.15</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>300.1</v>
+        <v>300.3</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>303.4</v>
+        <v>306.3</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>297.05</v>
+        <v>290.8</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>298.15</v>
+        <v>303.7</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>-0.95</v>
+        <v>5.55</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>-0.32</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1881.2</v>
+        <v>1891.1</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1869.1</v>
+        <v>1910</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1906.3</v>
+        <v>1912.7</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1865.2</v>
+        <v>1840.3</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1891.1</v>
+        <v>1890.1</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>9.9</v>
+        <v>-1</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>0.53</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8022.5</v>
+        <v>8004.5</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>7981</v>
+        <v>8011</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8112</v>
+        <v>8180</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>7981</v>
+        <v>8011</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8004.5</v>
+        <v>8119</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>-18</v>
+        <v>114.5</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>-0.22</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>398.75</v>
+        <v>396.45</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>397.65</v>
+        <v>398.8</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>401.2</v>
+        <v>404.15</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>394.6</v>
+        <v>396.15</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>396.45</v>
+        <v>401.8</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>-2.3</v>
+        <v>5.35</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>-0.58</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>155.95</v>
+        <v>153.21</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>155.95</v>
+        <v>154.09</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>157.36</v>
+        <v>155.38</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>152.76</v>
+        <v>149.89</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>153.21</v>
+        <v>154.34</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>-2.74</v>
+        <v>1.13</v>
       </c>
       <c r="J17" s="13" t="n">
-        <v>-1.76</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2505.5</v>
+        <v>2617.6</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2554</v>
+        <v>2620</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2642.4</v>
+        <v>2665.7</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2554</v>
+        <v>2610</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2617.6</v>
+        <v>2622.2</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>4.47</v>
+        <v>4.6</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1527.6</v>
+        <v>1544</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1521.4</v>
+        <v>1544.1</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1571.5</v>
+        <v>1568.3</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1503</v>
+        <v>1526.4</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1544</v>
+        <v>1561.3</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>1.07</v>
+        <v>17.3</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>591.3</v>
+        <v>606.5</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>594.95</v>
+        <v>608</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>617</v>
+        <v>618.5</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>606.5</v>
+        <v>612.6</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>2.57</v>
+        <v>6.1</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6851.5</v>
+        <v>6988</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6886.5</v>
+        <v>6990</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7070</v>
+        <v>7099</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6862</v>
+        <v>6953.5</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6988</v>
+        <v>6970</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>136.5</v>
+        <v>-18</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>1.99</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>999.6</v>
+        <v>994.8</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>996.1</v>
+        <v>1000.9</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1010.6</v>
+        <v>1007.5</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>988.7</v>
+        <v>990.6</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>994.8</v>
+        <v>1004.7</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>-4.8</v>
+        <v>9.9</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>-0.48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1488.2</v>
+        <v>1497.5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1490</v>
+        <v>1504.4</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1509.8</v>
+        <v>1525.9</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1483.6</v>
+        <v>1497</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1497.5</v>
+        <v>1510.9</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>0.62</v>
+        <v>13.4</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1260.1</v>
+        <v>1255.7</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1256.1</v>
+        <v>1256.6</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1275.3</v>
+        <v>1269</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1247.5</v>
+        <v>1235.8</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1255.7</v>
+        <v>1254.6</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="J24" s="13" t="n">
-        <v>-0.35</v>
+        <v>-1.1</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>10397</v>
+        <v>10262</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10370.5</v>
+        <v>10380</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10455</v>
+        <v>10517</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10220</v>
+        <v>10251.5</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>10262</v>
+        <v>10451</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>-135</v>
+        <v>189</v>
       </c>
       <c r="J25" s="13" t="n">
-        <v>-1.3</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1744.8</v>
+        <v>1728.9</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>1748.9</v>
+        <v>1735.1</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1758</v>
+        <v>1743</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1726</v>
+        <v>1713.3</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1728.9</v>
+        <v>1740.2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>-15.9</v>
+        <v>11.3</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>-0.91</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>904.2</v>
+        <v>896.15</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>902</v>
+        <v>902.9</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>907.4</v>
+        <v>915</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>890.05</v>
+        <v>889</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>896.15</v>
+        <v>912.15</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>-8.050000000000001</v>
+        <v>16</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>-0.89</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2110.6</v>
+        <v>2105.1</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2114.4</v>
+        <v>2120</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2151.8</v>
+        <v>2197.1</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2063.7</v>
+        <v>2120</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2105.1</v>
+        <v>2191.1</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-5.5</v>
+        <v>86</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>-0.26</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>534.15</v>
+        <v>548.9</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>534</v>
+        <v>543.95</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>561.9</v>
+        <v>548</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>531.55</v>
+        <v>517.75</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>548.9</v>
+        <v>540.7</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>14.75</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2.76</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>196.07</v>
+        <v>194.88</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>196.09</v>
+        <v>196</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>200.73</v>
+        <v>200.85</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>194.5</v>
+        <v>194.59</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>194.88</v>
+        <v>199.04</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>-1.19</v>
+        <v>4.16</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>-0.61</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>259.95</v>
+        <v>261.65</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>260.7</v>
+        <v>263.8</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>264.3</v>
+        <v>270.1</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>258.1</v>
+        <v>262.65</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>261.65</v>
+        <v>267.8</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J31" s="10" t="n">
-        <v>0.65</v>
+        <v>6.15</v>
+      </c>
+      <c r="J31" s="13" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>416.5</v>
+        <v>428.25</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>416.6</v>
+        <v>431</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>432</v>
+        <v>435.15</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>415.75</v>
+        <v>424.45</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>428.25</v>
+        <v>428.85</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="J32" s="10" t="n">
-        <v>2.82</v>
+        <v>0.6</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>0.14</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>488.1</v>
+        <v>507.7</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>505</v>
+        <v>514.95</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>533.35</v>
+        <v>540.35</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>507.7</v>
+        <v>533.9</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J33" s="10" t="n">
-        <v>4.02</v>
+        <v>26.2</v>
+      </c>
+      <c r="J33" s="13" t="n">
+        <v>5.16</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1756.8</v>
+        <v>1789.2</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1740.5</v>
+        <v>1820</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1798</v>
+        <v>1889.2</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1740.5</v>
+        <v>1797.3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1789.2</v>
+        <v>1883.5</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="J34" s="10" t="n">
-        <v>1.84</v>
+        <v>94.3</v>
+      </c>
+      <c r="J34" s="13" t="n">
+        <v>5.27</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>391.75</v>
+        <v>403.85</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>392.5</v>
+        <v>407.2</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>407.75</v>
+        <v>417.9</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>392.5</v>
+        <v>402.05</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>403.85</v>
+        <v>413.15</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="J35" s="10" t="n">
-        <v>3.09</v>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J35" s="13" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
         <v>2900</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>402.45</v>
+        <v>417.6</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>403.05</v>
+        <v>417.55</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>420.25</v>
+        <v>424.4</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>402.85</v>
+        <v>416.5</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>417.6</v>
+        <v>419</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>15.15</v>
-      </c>
-      <c r="J36" s="10" t="n">
-        <v>3.76</v>
+        <v>1.4</v>
+      </c>
+      <c r="J36" s="13" t="n">
+        <v>0.34</v>
       </c>
     </row>
     <row r="37">
@@ -1989,25 +1989,25 @@
         <v>50</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>36510</v>
+        <v>36315</v>
       </c>
       <c r="E37" s="9" t="n">
-        <v>36510</v>
+        <v>36545</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>36880</v>
+        <v>37180</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>36235</v>
+        <v>36065</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>36315</v>
+        <v>36945</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-195</v>
+        <v>630</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>-0.53</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="38">
@@ -2023,25 +2023,25 @@
         <v>1800</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>287.85</v>
+        <v>297.1</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>288.55</v>
+        <v>301.1</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>299</v>
+        <v>301.1</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>288.55</v>
+        <v>291.15</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>297.1</v>
+        <v>295</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>9.25</v>
+        <v>-2.1</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>3.21</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="39">
@@ -2057,25 +2057,25 @@
         <v>200</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>5334</v>
+        <v>5336</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>5345</v>
+        <v>5343.5</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>5383.5</v>
+        <v>5397</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>5279.5</v>
+        <v>5310</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5336</v>
+        <v>5372.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="10" t="n">
-        <v>0.04</v>
+        <v>36.5</v>
+      </c>
+      <c r="J39" s="13" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="40">
@@ -2091,25 +2091,25 @@
         <v>2200</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>331.6</v>
+        <v>318.7</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>331.6</v>
+        <v>320</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>334.75</v>
+        <v>323</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>317.45</v>
+        <v>309.2</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>318.7</v>
+        <v>310.9</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>-12.9</v>
-      </c>
-      <c r="J40" s="13" t="n">
-        <v>-3.89</v>
+        <v>-7.8</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="41">
@@ -2125,25 +2125,25 @@
         <v>4350</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>130.01</v>
+        <v>129.26</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>130.46</v>
+        <v>129.9</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>131.2</v>
+        <v>132.95</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>127.9</v>
+        <v>127.23</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>129.26</v>
+        <v>130.84</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.75</v>
+        <v>1.58</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>-0.58</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="42">
@@ -2159,25 +2159,25 @@
         <v>975</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>831.85</v>
+        <v>827.4</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>836.35</v>
+        <v>834.9</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>839.35</v>
+        <v>847.8</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>820.05</v>
+        <v>818</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>827.4</v>
+        <v>843.2</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>-4.45</v>
+        <v>15.8</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>-0.53</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="43">
@@ -2193,25 +2193,25 @@
         <v>2400</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>433.9</v>
+        <v>428.6</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>435</v>
+        <v>432.75</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>437.35</v>
+        <v>434.9</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>427.7</v>
+        <v>422</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>428.6</v>
+        <v>424.6</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>-1.22</v>
+        <v>-4</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="44">
@@ -2227,25 +2227,25 @@
         <v>700</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>1561</v>
+        <v>1574.6</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1567.8</v>
+        <v>1580</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>1597.5</v>
+        <v>1590</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1550.2</v>
+        <v>1545.5</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1574.6</v>
+        <v>1567.1</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>13.6</v>
+        <v>-7.5</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>0.87</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="45">
@@ -2261,25 +2261,25 @@
         <v>650</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1292.3</v>
+        <v>1327.6</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>1279.1</v>
+        <v>1362.2</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1356.6</v>
+        <v>1442</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1274.7</v>
+        <v>1362.2</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>1327.6</v>
+        <v>1436.7</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="J45" s="10" t="n">
-        <v>2.73</v>
+        <v>109.1</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>8.220000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2295,25 +2295,25 @@
         <v>2100</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>463.05</v>
+        <v>462.25</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>463.25</v>
+        <v>464</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>473.6</v>
+        <v>469.8</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>459.5</v>
+        <v>451.45</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>462.25</v>
+        <v>454.05</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>-0.17</v>
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="47">
@@ -2329,25 +2329,25 @@
         <v>200</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1320.4</v>
+        <v>1297.1</v>
       </c>
       <c r="E47" s="9" t="n">
-        <v>1321</v>
+        <v>1305.9</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1328</v>
+        <v>1305.9</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1291.4</v>
+        <v>1249.8</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1297.1</v>
+        <v>1274.6</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-23.3</v>
-      </c>
-      <c r="J47" s="13" t="n">
-        <v>-1.76</v>
+        <v>-22.5</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="48">
@@ -2363,25 +2363,25 @@
         <v>350</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2125.2</v>
+        <v>2134.5</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>2127.8</v>
+        <v>2134.6</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>2147</v>
+        <v>2163.5</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2111.6</v>
+        <v>2124.7</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>2134.5</v>
+        <v>2146.6</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J48" s="10" t="n">
-        <v>0.44</v>
+        <v>12.1</v>
+      </c>
+      <c r="J48" s="13" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="49">
@@ -2397,25 +2397,25 @@
         <v>1250</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>516</v>
+        <v>519.85</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>512.6</v>
+        <v>522.35</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>525.35</v>
+        <v>527.75</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>512.6</v>
+        <v>517.95</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>519.85</v>
+        <v>522.95</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J49" s="10" t="n">
-        <v>0.75</v>
+        <v>3.1</v>
+      </c>
+      <c r="J49" s="13" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="50">
@@ -2431,25 +2431,25 @@
         <v>500</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>1872.7</v>
+        <v>1860.5</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>1872.7</v>
+        <v>1860.5</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>1880</v>
+        <v>1885</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1814.9</v>
+        <v>1828</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>1860.5</v>
+        <v>1860.3</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>-12.2</v>
-      </c>
-      <c r="J50" s="13" t="n">
-        <v>-0.65</v>
+        <v>-0.2</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="51">
@@ -2465,25 +2465,25 @@
         <v>3000</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>282.05</v>
+        <v>284.8</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>282.25</v>
+        <v>286.4</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>287.65</v>
+        <v>293.5</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>280</v>
+        <v>280.35</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>284.8</v>
+        <v>288.95</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v>0.98</v>
+        <v>4.15</v>
+      </c>
+      <c r="J51" s="13" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="52">
@@ -2499,25 +2499,25 @@
         <v>4700</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>244.45</v>
+        <v>245.6</v>
       </c>
       <c r="E52" s="12" t="n">
-        <v>245</v>
+        <v>247.8</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>249.4</v>
+        <v>251.05</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>242.35</v>
+        <v>242.4</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>245.6</v>
+        <v>246.8</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J52" s="10" t="n">
-        <v>0.47</v>
+        <v>1.2</v>
+      </c>
+      <c r="J52" s="13" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="53">
@@ -2533,25 +2533,25 @@
         <v>600</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>5160</v>
+        <v>5212</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>5170</v>
+        <v>5257</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>5270</v>
+        <v>5383</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5147.5</v>
+        <v>5229</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>5212</v>
+        <v>5367</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>52</v>
-      </c>
-      <c r="J53" s="10" t="n">
-        <v>1.01</v>
+        <v>155</v>
+      </c>
+      <c r="J53" s="13" t="n">
+        <v>2.97</v>
       </c>
     </row>
     <row r="54">
@@ -2567,25 +2567,25 @@
         <v>2750</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>473.25</v>
+        <v>463.1</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>480.8</v>
+        <v>467</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>480.8</v>
+        <v>469.9</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>461.6</v>
+        <v>457.85</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>463.1</v>
+        <v>464.75</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>-10.15</v>
+        <v>1.65</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>-2.14</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="55">
@@ -2601,25 +2601,25 @@
         <v>300</v>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1781.2</v>
+        <v>1776.9</v>
       </c>
       <c r="E55" s="9" t="n">
-        <v>1781.2</v>
+        <v>1790</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>1793.6</v>
+        <v>1790</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>1745.2</v>
+        <v>1740.1</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1776.9</v>
+        <v>1764.7</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="J55" s="13" t="n">
-        <v>-0.24</v>
+        <v>-12.2</v>
+      </c>
+      <c r="J55" s="10" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2635,25 +2635,25 @@
         <v>300</v>
       </c>
       <c r="D56" s="12" t="n">
-        <v>1848.3</v>
+        <v>1856.4</v>
       </c>
       <c r="E56" s="12" t="n">
-        <v>1840</v>
+        <v>1857</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>1874.8</v>
+        <v>1877.9</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>1803.8</v>
+        <v>1795</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1856.4</v>
+        <v>1840.2</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>8.1</v>
+        <v>-16.2</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>0.44</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="57">
@@ -2669,24 +2669,24 @@
         <v>4200</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>72.14</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E57" s="9" t="n">
-        <v>72.76000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>73.13</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>71.11</v>
+        <v>70.42</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>72.09999999999999</v>
+        <v>72.06</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>-0.04</v>
       </c>
-      <c r="J57" s="13" t="n">
+      <c r="J57" s="10" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -2703,25 +2703,25 @@
         <v>200</v>
       </c>
       <c r="D58" s="12" t="n">
-        <v>6644</v>
+        <v>6796</v>
       </c>
       <c r="E58" s="12" t="n">
-        <v>6680</v>
+        <v>6830</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>6870</v>
+        <v>6948</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>6643</v>
+        <v>6817</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6796</v>
+        <v>6921.5</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>152</v>
-      </c>
-      <c r="J58" s="10" t="n">
-        <v>2.29</v>
+        <v>125.5</v>
+      </c>
+      <c r="J58" s="13" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="59">
@@ -2737,25 +2737,25 @@
         <v>150</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>10138</v>
+        <v>11124</v>
       </c>
       <c r="E59" s="9" t="n">
-        <v>10255</v>
+        <v>11150</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>11232</v>
+        <v>11191</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>10158</v>
+        <v>10834</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>11124</v>
+        <v>11103</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>986</v>
+        <v>-21</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>9.73</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="60">
@@ -2771,25 +2771,25 @@
         <v>1650</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>569.2</v>
+        <v>574.15</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>568.75</v>
+        <v>572.1</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>581.2</v>
+        <v>588.45</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>567.15</v>
+        <v>553.8</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>574.15</v>
+        <v>583.25</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="J60" s="10" t="n">
-        <v>0.87</v>
+        <v>9.1</v>
+      </c>
+      <c r="J60" s="13" t="n">
+        <v>1.58</v>
       </c>
     </row>
     <row r="61">
@@ -2805,25 +2805,25 @@
         <v>250</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1270</v>
+        <v>1265.3</v>
       </c>
       <c r="E61" s="9" t="n">
-        <v>1245.6</v>
+        <v>1265.3</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1303.8</v>
+        <v>1307.7</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>1230</v>
+        <v>1255</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1265.3</v>
+        <v>1303.6</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>-4.7</v>
+        <v>38.3</v>
       </c>
       <c r="J61" s="13" t="n">
-        <v>-0.37</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="62">
@@ -2839,25 +2839,25 @@
         <v>175</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>7126</v>
+        <v>6971.5</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7125</v>
+        <v>7000</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>7157</v>
+        <v>7102</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>6863</v>
+        <v>6842.5</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>6971.5</v>
+        <v>7034</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>-154.5</v>
+        <v>62.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>-2.17</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="63">
@@ -2873,25 +2873,25 @@
         <v>275</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2960.7</v>
+        <v>2982.7</v>
       </c>
       <c r="E63" s="9" t="n">
-        <v>2977.9</v>
+        <v>2985.4</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>3005</v>
+        <v>3010</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>2944</v>
+        <v>2979.3</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>2982.7</v>
+        <v>2999.2</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="J63" s="10" t="n">
-        <v>0.74</v>
+        <v>16.5</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="64">
@@ -2907,25 +2907,25 @@
         <v>3600</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>346.3</v>
+        <v>349.3</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>346</v>
+        <v>350.85</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>355.4</v>
+        <v>356</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>346</v>
+        <v>344.6</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>349.3</v>
+        <v>349.7</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J64" s="10" t="n">
-        <v>0.87</v>
+        <v>0.4</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="65">
@@ -2941,25 +2941,25 @@
         <v>5000</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>284.8</v>
+        <v>280.05</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>285.9</v>
+        <v>282</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>285.9</v>
+        <v>282.85</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>277.1</v>
+        <v>277.55</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>280.05</v>
+        <v>280.25</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>-4.75</v>
+        <v>0.2</v>
       </c>
       <c r="J65" s="13" t="n">
-        <v>-1.67</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
         <v>6400</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>160.35</v>
+        <v>163.31</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>160</v>
+        <v>164.25</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>164.81</v>
+        <v>165.9</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>159.1</v>
+        <v>159.4</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>163.31</v>
+        <v>162.61</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>2.96</v>
+        <v>-0.7</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>1.85</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="67">
@@ -3009,25 +3009,25 @@
         <v>1150</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>2257.1</v>
+        <v>2277.6</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>2245.2</v>
+        <v>2300</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>2326.5</v>
+        <v>2350.4</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2245.2</v>
+        <v>2292.6</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>2277.6</v>
+        <v>2340.6</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="J67" s="10" t="n">
-        <v>0.91</v>
+        <v>63</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>2.77</v>
       </c>
     </row>
     <row r="68">
@@ -3060,7 +3060,7 @@
       <c r="I68" s="12" t="n">
         <v/>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="J68" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -3077,25 +3077,25 @@
         <v>1200</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>470.15</v>
+        <v>489.95</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>496</v>
+        <v>521.7</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>471.15</v>
+        <v>499</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>489.95</v>
+        <v>519.95</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="J69" s="10" t="n">
-        <v>4.21</v>
+        <v>30</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>6.12</v>
       </c>
     </row>
     <row r="70">
@@ -3111,25 +3111,25 @@
         <v>1000</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>1030.2</v>
+        <v>1030.5</v>
       </c>
       <c r="E70" s="12" t="n">
-        <v>1033</v>
+        <v>1038</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>1043.8</v>
+        <v>1038</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1014.9</v>
+        <v>1015.7</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>1030.5</v>
+        <v>1033.3</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J70" s="10" t="n">
-        <v>0.03</v>
+        <v>2.8</v>
+      </c>
+      <c r="J70" s="13" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="71">
@@ -3145,25 +3145,25 @@
         <v>400</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1712.4</v>
+        <v>1730.6</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>1710</v>
+        <v>1740</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>1756.4</v>
+        <v>1748.5</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1696</v>
+        <v>1688.2</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1730.6</v>
+        <v>1733.5</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="J71" s="10" t="n">
-        <v>1.06</v>
+        <v>2.9</v>
+      </c>
+      <c r="J71" s="13" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="72">
@@ -3179,25 +3179,25 @@
         <v>2700</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>729.05</v>
+        <v>728.35</v>
       </c>
       <c r="E72" s="12" t="n">
-        <v>729.05</v>
+        <v>737</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>744</v>
+        <v>744.8</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>724.35</v>
+        <v>730.05</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>728.35</v>
+        <v>735.3</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>-0.7</v>
+        <v>6.95</v>
       </c>
       <c r="J72" s="13" t="n">
-        <v>-0.1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="73">
@@ -3213,25 +3213,25 @@
         <v>475</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2903</v>
+        <v>2945.6</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>2910.3</v>
+        <v>2955</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>2969.3</v>
+        <v>2983.3</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>2910</v>
+        <v>2933.1</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2945.6</v>
+        <v>2938.7</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>42.6</v>
+        <v>-6.9</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>1.47</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="74">
@@ -3247,25 +3247,25 @@
         <v>750</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>368.25</v>
+        <v>360.85</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>368.75</v>
+        <v>362.65</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>369.35</v>
+        <v>367.85</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>359.5</v>
+        <v>361.45</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>360.85</v>
+        <v>362.1</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>-7.4</v>
+        <v>1.25</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>-2.01</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="75">
@@ -3281,25 +3281,25 @@
         <v>200</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>4572.5</v>
+        <v>4618.5</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>4550</v>
+        <v>4649</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>4692</v>
+        <v>4808.6</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>4536.7</v>
+        <v>4548</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4618.5</v>
+        <v>4608</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>46</v>
+        <v>-10.5</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>1.01</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="76">
@@ -3315,25 +3315,25 @@
         <v>500</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1190.9</v>
+        <v>1199.2</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>1190.5</v>
+        <v>1205</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>1204</v>
+        <v>1214.8</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1183.2</v>
+        <v>1186</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1199.2</v>
+        <v>1210.8</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J76" s="10" t="n">
-        <v>0.7</v>
+        <v>11.6</v>
+      </c>
+      <c r="J76" s="13" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="77">
@@ -3349,25 +3349,25 @@
         <v>350</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1145.8</v>
+        <v>1143.2</v>
       </c>
       <c r="E77" s="9" t="n">
-        <v>1146.3</v>
+        <v>1139</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>1154.6</v>
+        <v>1143.2</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1137.1</v>
+        <v>1103.4</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1143.2</v>
+        <v>1124</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="J77" s="13" t="n">
-        <v>-0.23</v>
+        <v>-19.2</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="78">
@@ -3383,25 +3383,25 @@
         <v>200</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>2632.8</v>
+        <v>2652.3</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>2630</v>
+        <v>2670</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>2689.2</v>
+        <v>2705</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2630</v>
+        <v>2618</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2652.3</v>
+        <v>2691.6</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="J78" s="10" t="n">
-        <v>0.74</v>
+        <v>39.3</v>
+      </c>
+      <c r="J78" s="13" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="79">
@@ -3417,25 +3417,25 @@
         <v>550</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>750.45</v>
+        <v>749.6</v>
       </c>
       <c r="E79" s="9" t="n">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>759.95</v>
+        <v>778.3</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>747.35</v>
+        <v>747</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>749.6</v>
+        <v>769.55</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>-0.85</v>
+        <v>19.95</v>
       </c>
       <c r="J79" s="13" t="n">
-        <v>-0.11</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="80">
@@ -3451,25 +3451,25 @@
         <v>1500</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>601.8</v>
+        <v>602.8</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>602.95</v>
+        <v>603.85</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>608.5</v>
+        <v>614.5</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>598.85</v>
+        <v>602.5</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>602.8</v>
+        <v>612.55</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="10" t="n">
-        <v>0.17</v>
+        <v>9.75</v>
+      </c>
+      <c r="J80" s="13" t="n">
+        <v>1.62</v>
       </c>
     </row>
     <row r="81">
@@ -3485,25 +3485,25 @@
         <v>300</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>5082.5</v>
+        <v>4995</v>
       </c>
       <c r="E81" s="9" t="n">
-        <v>5117.5</v>
+        <v>5020</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>5128</v>
+        <v>5091</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>4977</v>
+        <v>4880</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>4995</v>
+        <v>5077</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>-87.5</v>
+        <v>82</v>
       </c>
       <c r="J81" s="13" t="n">
-        <v>-1.72</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="82">
@@ -3519,25 +3519,25 @@
         <v>2150</v>
       </c>
       <c r="D82" s="12" t="n">
-        <v>1041.4</v>
+        <v>1073.1</v>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1048</v>
+        <v>1083.9</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>1082.4</v>
+        <v>1105</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1047</v>
+        <v>1080.9</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1073.1</v>
+        <v>1103.3</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J82" s="10" t="n">
-        <v>3.04</v>
+        <v>30.2</v>
+      </c>
+      <c r="J82" s="13" t="n">
+        <v>2.81</v>
       </c>
     </row>
     <row r="83">
@@ -3553,25 +3553,25 @@
         <v>3650</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>564.2</v>
+        <v>595.3</v>
       </c>
       <c r="E83" s="9" t="n">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>600</v>
+        <v>618.1</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>577</v>
+        <v>599.15</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>595.3</v>
+        <v>606.45</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="J83" s="10" t="n">
-        <v>5.51</v>
+        <v>11.15</v>
+      </c>
+      <c r="J83" s="13" t="n">
+        <v>1.87</v>
       </c>
     </row>
     <row r="84">
@@ -3587,25 +3587,25 @@
         <v>2700</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>369.9</v>
+        <v>390.1</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>372.4</v>
+        <v>388.8</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>392</v>
+        <v>388.8</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>370.55</v>
+        <v>370.95</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>390.1</v>
+        <v>377.55</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>20.2</v>
+        <v>-12.55</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>5.46</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="85">
@@ -3621,25 +3621,25 @@
         <v>300</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2262</v>
+        <v>2267.3</v>
       </c>
       <c r="E85" s="9" t="n">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>2295.8</v>
+        <v>2285.9</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>2250</v>
+        <v>2245</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2267.3</v>
+        <v>2248.7</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>5.3</v>
+        <v>-18.6</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>0.23</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="86">
@@ -3655,25 +3655,25 @@
         <v>15</v>
       </c>
       <c r="D86" s="12" t="n">
+        <v>28215</v>
+      </c>
+      <c r="E86" s="12" t="n">
         <v>28455</v>
       </c>
-      <c r="E86" s="12" t="n">
-        <v>28450</v>
-      </c>
       <c r="F86" s="12" t="n">
-        <v>28860</v>
+        <v>28810</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>28000</v>
+        <v>28260</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>28215</v>
+        <v>28720</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>-240</v>
+        <v>505</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>-0.84</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="87">
@@ -3689,25 +3689,25 @@
         <v>7500</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>67.68000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="E87" s="9" t="n">
-        <v>67.5</v>
+        <v>68.52</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>69.48999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>67.5</v>
+        <v>67.25</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>68.3</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="J87" s="10" t="n">
-        <v>0.92</v>
+        <v>0.24</v>
+      </c>
+      <c r="J87" s="13" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="88">
@@ -3723,25 +3723,25 @@
         <v>3750</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>127.21</v>
+        <v>127.53</v>
       </c>
       <c r="E88" s="12" t="n">
-        <v>127.2</v>
+        <v>128.01</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>128.81</v>
+        <v>129.55</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>125.69</v>
+        <v>126</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>127.53</v>
+        <v>128.44</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J88" s="10" t="n">
-        <v>0.25</v>
+        <v>0.91</v>
+      </c>
+      <c r="J88" s="13" t="n">
+        <v>0.71</v>
       </c>
     </row>
     <row r="89">
@@ -3757,25 +3757,25 @@
         <v>1375</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>156.81</v>
+        <v>159.3</v>
       </c>
       <c r="E89" s="9" t="n">
-        <v>156.21</v>
+        <v>159.5</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>160.1</v>
+        <v>161.29</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>154.74</v>
+        <v>154.98</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>159.3</v>
+        <v>155.71</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>2.49</v>
+        <v>-3.59</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>1.59</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="90">
@@ -3791,25 +3791,25 @@
         <v>3000</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>634.4</v>
+        <v>637.4</v>
       </c>
       <c r="E90" s="12" t="n">
-        <v>636.95</v>
+        <v>641.6</v>
       </c>
       <c r="F90" s="12" t="n">
-        <v>644.85</v>
+        <v>655.4</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>622.45</v>
+        <v>636.4</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>637.4</v>
+        <v>650.2</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J90" s="10" t="n">
-        <v>0.47</v>
+        <v>12.8</v>
+      </c>
+      <c r="J90" s="13" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="91">
@@ -3825,25 +3825,25 @@
         <v>150</v>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2011.8</v>
+        <v>1969.2</v>
       </c>
       <c r="E91" s="9" t="n">
-        <v>2000</v>
+        <v>1970</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>2022.8</v>
+        <v>1979.9</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1966</v>
+        <v>1934.4</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>1969.2</v>
+        <v>1971.2</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>-42.6</v>
+        <v>2</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>-2.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="92">
@@ -3859,25 +3859,25 @@
         <v>300</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>4201.7</v>
+        <v>4255.8</v>
       </c>
       <c r="E92" s="12" t="n">
-        <v>4205.4</v>
+        <v>4261.9</v>
       </c>
       <c r="F92" s="12" t="n">
-        <v>4283.6</v>
+        <v>4313</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>4146.3</v>
+        <v>4193.6</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>4255.8</v>
+        <v>4280.5</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="J92" s="10" t="n">
-        <v>1.29</v>
+        <v>24.7</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="93">
@@ -3893,25 +3893,25 @@
         <v>500</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>892.85</v>
+        <v>892.5</v>
       </c>
       <c r="E93" s="9" t="n">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>906.8</v>
+        <v>914.5</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>890.3</v>
+        <v>886.2</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>892.5</v>
+        <v>907.9</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>-0.35</v>
+        <v>15.4</v>
       </c>
       <c r="J93" s="13" t="n">
-        <v>-0.04</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="94">
@@ -3927,25 +3927,25 @@
         <v>2800</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>400.8</v>
+        <v>413.2</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>402</v>
+        <v>415.95</v>
       </c>
       <c r="F94" s="12" t="n">
-        <v>416.7</v>
+        <v>425.1</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>399.65</v>
+        <v>415</v>
       </c>
       <c r="H94" s="12" t="n">
-        <v>413.2</v>
+        <v>422.35</v>
       </c>
       <c r="I94" s="12" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J94" s="10" t="n">
-        <v>3.09</v>
+        <v>9.15</v>
+      </c>
+      <c r="J94" s="13" t="n">
+        <v>2.21</v>
       </c>
     </row>
     <row r="95">
@@ -3961,25 +3961,25 @@
         <v>400</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1140.3</v>
+        <v>1123.1</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>1136.6</v>
+        <v>1119.8</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>1142.6</v>
+        <v>1121.9</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1121</v>
+        <v>1089</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>1123.1</v>
+        <v>1095</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>-17.2</v>
-      </c>
-      <c r="J95" s="13" t="n">
-        <v>-1.51</v>
+        <v>-28.1</v>
+      </c>
+      <c r="J95" s="10" t="n">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="96">
@@ -3995,25 +3995,25 @@
         <v>3500</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>137.65</v>
+        <v>141.69</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>142.6</v>
+        <v>143</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>137.84</v>
+        <v>139.1</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>141.69</v>
+        <v>140.26</v>
       </c>
       <c r="I96" s="12" t="n">
-        <v>4.04</v>
+        <v>-1.43</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>2.93</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="97">
@@ -4029,25 +4029,25 @@
         <v>700</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1509.1</v>
+        <v>1506.3</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>1518</v>
+        <v>1510</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>1538.9</v>
+        <v>1593.8</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>1494</v>
+        <v>1510</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>1506.3</v>
+        <v>1583.9</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>-2.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J97" s="13" t="n">
-        <v>-0.19</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="98">
@@ -4063,25 +4063,25 @@
         <v>875</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>534</v>
+        <v>536.1</v>
       </c>
       <c r="E98" s="12" t="n">
-        <v>530.5</v>
+        <v>537.75</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>542.45</v>
+        <v>544.6</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>530.5</v>
+        <v>528.75</v>
       </c>
       <c r="H98" s="12" t="n">
-        <v>536.1</v>
+        <v>538.85</v>
       </c>
       <c r="I98" s="12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J98" s="10" t="n">
-        <v>0.39</v>
+        <v>2.75</v>
+      </c>
+      <c r="J98" s="13" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="99">
@@ -4097,25 +4097,25 @@
         <v>3200</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>300.7</v>
+        <v>304.45</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>305.8</v>
+        <v>309.2</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>301.05</v>
+        <v>304.85</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>304.45</v>
+        <v>307.2</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J99" s="10" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
+      </c>
+      <c r="J99" s="13" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="100">
@@ -4131,25 +4131,25 @@
         <v>1250</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>1214.3</v>
+        <v>1242.9</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>1219</v>
+        <v>1253.1</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>1258</v>
+        <v>1258.4</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>1216.1</v>
+        <v>1237.2</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1242.9</v>
+        <v>1252.8</v>
       </c>
       <c r="I100" s="12" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="J100" s="10" t="n">
-        <v>2.36</v>
+        <v>9.9</v>
+      </c>
+      <c r="J100" s="13" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="101">
@@ -4165,25 +4165,25 @@
         <v>200</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5377.5</v>
+        <v>5422.5</v>
       </c>
       <c r="E101" s="9" t="n">
-        <v>5360</v>
+        <v>5490</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>5449</v>
+        <v>5545</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>5296.5</v>
+        <v>5436.5</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5422.5</v>
+        <v>5521.5</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="J101" s="10" t="n">
-        <v>0.84</v>
+        <v>99</v>
+      </c>
+      <c r="J101" s="13" t="n">
+        <v>1.83</v>
       </c>
     </row>
     <row r="102">
@@ -4199,25 +4199,25 @@
         <v>3000</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>732.1</v>
+        <v>725.25</v>
       </c>
       <c r="E102" s="12" t="n">
-        <v>732.1</v>
+        <v>730.4</v>
       </c>
       <c r="F102" s="12" t="n">
-        <v>743.7</v>
+        <v>751.5</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>722.45</v>
+        <v>725.6</v>
       </c>
       <c r="H102" s="12" t="n">
-        <v>725.25</v>
+        <v>748.7</v>
       </c>
       <c r="I102" s="12" t="n">
-        <v>-6.85</v>
+        <v>23.45</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>-0.9399999999999999</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="103">
@@ -4233,25 +4233,25 @@
         <v>1500</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>517.95</v>
+        <v>509.2</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>517.95</v>
+        <v>514.4</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>521.8</v>
+        <v>517.75</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>506.9</v>
+        <v>505.2</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>509.2</v>
+        <v>512.8</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>-8.75</v>
+        <v>3.6</v>
       </c>
       <c r="J103" s="13" t="n">
-        <v>-1.69</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="104">
@@ -4267,25 +4267,25 @@
         <v>600</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>1252.3</v>
+        <v>1274.9</v>
       </c>
       <c r="E104" s="12" t="n">
-        <v>1255</v>
+        <v>1287.9</v>
       </c>
       <c r="F104" s="12" t="n">
-        <v>1282.4</v>
+        <v>1306</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>1255</v>
+        <v>1281.9</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>1274.9</v>
+        <v>1296.9</v>
       </c>
       <c r="I104" s="12" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="J104" s="10" t="n">
-        <v>1.8</v>
+        <v>22</v>
+      </c>
+      <c r="J104" s="13" t="n">
+        <v>1.73</v>
       </c>
     </row>
     <row r="105">
@@ -4301,25 +4301,25 @@
         <v>625</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>442.15</v>
+        <v>448.4</v>
       </c>
       <c r="E105" s="9" t="n">
-        <v>433.7</v>
+        <v>449.8</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>453.15</v>
+        <v>463.8</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>422.25</v>
+        <v>445.35</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>448.4</v>
+        <v>460.45</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J105" s="10" t="n">
-        <v>1.41</v>
+        <v>12.05</v>
+      </c>
+      <c r="J105" s="13" t="n">
+        <v>2.69</v>
       </c>
     </row>
     <row r="106">
@@ -4335,25 +4335,25 @@
         <v>1000</v>
       </c>
       <c r="D106" s="12" t="n">
-        <v>1072.6</v>
+        <v>1072.7</v>
       </c>
       <c r="E106" s="12" t="n">
-        <v>1070.5</v>
+        <v>1089.2</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>1098</v>
+        <v>1089.2</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1066.4</v>
+        <v>1062.2</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>1072.7</v>
+        <v>1064.7</v>
       </c>
       <c r="I106" s="12" t="n">
-        <v>0.1</v>
+        <v>-8</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>0.01</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="107">
@@ -4369,25 +4369,25 @@
         <v>400</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>376</v>
+        <v>377.65</v>
       </c>
       <c r="E107" s="9" t="n">
-        <v>377.9</v>
+        <v>378</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>376.85</v>
+        <v>375.6</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>377.65</v>
+        <v>383.2</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J107" s="10" t="n">
-        <v>0.44</v>
+        <v>5.55</v>
+      </c>
+      <c r="J107" s="13" t="n">
+        <v>1.47</v>
       </c>
     </row>
     <row r="108">
@@ -4403,25 +4403,25 @@
         <v>800</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>712.05</v>
+        <v>710.65</v>
       </c>
       <c r="E108" s="12" t="n">
         <v>711</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>718.05</v>
+        <v>716.7</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>710.65</v>
+        <v>709</v>
       </c>
       <c r="I108" s="12" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="J108" s="13" t="n">
-        <v>-0.2</v>
+        <v>-1.65</v>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="109">
@@ -4437,25 +4437,25 @@
         <v>300</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1587</v>
+        <v>1575.7</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>1581.5</v>
+        <v>1588.5</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>1613.4</v>
+        <v>1609.6</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1568</v>
+        <v>1571.2</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>1575.7</v>
+        <v>1600.1</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>-11.3</v>
+        <v>24.4</v>
       </c>
       <c r="J109" s="13" t="n">
-        <v>-0.71</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="110">
@@ -4471,25 +4471,25 @@
         <v>2500</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1268</v>
+        <v>1280.5</v>
       </c>
       <c r="E110" s="12" t="n">
-        <v>1275</v>
+        <v>1291.5</v>
       </c>
       <c r="F110" s="12" t="n">
-        <v>1292.5</v>
+        <v>1324.1</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>1246.6</v>
+        <v>1283.1</v>
       </c>
       <c r="H110" s="12" t="n">
-        <v>1280.5</v>
+        <v>1315.5</v>
       </c>
       <c r="I110" s="12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J110" s="10" t="n">
-        <v>0.99</v>
+        <v>35</v>
+      </c>
+      <c r="J110" s="13" t="n">
+        <v>2.73</v>
       </c>
     </row>
     <row r="111">
@@ -4505,25 +4505,25 @@
         <v>1600</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>567.65</v>
+        <v>585.65</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>565.8</v>
+        <v>570.25</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>587.85</v>
+        <v>580.95</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>565.8</v>
+        <v>546.8</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>585.65</v>
+        <v>560.4</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>18</v>
+        <v>-25.25</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>3.17</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="112">
@@ -4539,25 +4539,25 @@
         <v>150</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>3856.5</v>
+        <v>3915.8</v>
       </c>
       <c r="E112" s="12" t="n">
-        <v>3848</v>
+        <v>3942</v>
       </c>
       <c r="F112" s="12" t="n">
-        <v>3953</v>
+        <v>3988</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>3848</v>
+        <v>3925</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>3915.8</v>
+        <v>3940.4</v>
       </c>
       <c r="I112" s="12" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="J112" s="10" t="n">
-        <v>1.54</v>
+        <v>24.6</v>
+      </c>
+      <c r="J112" s="13" t="n">
+        <v>0.63</v>
       </c>
     </row>
     <row r="113">
@@ -4573,25 +4573,25 @@
         <v>5000</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>280.65</v>
+        <v>281.9</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>290.25</v>
+        <v>285.8</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>278.8</v>
+        <v>275.75</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>281.9</v>
+        <v>281.3</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>1.25</v>
+        <v>-0.6</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>0.45</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="114">
@@ -4624,7 +4624,7 @@
       <c r="I114" s="12" t="n">
         <v/>
       </c>
-      <c r="J114" s="13" t="n">
+      <c r="J114" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4641,25 +4641,25 @@
         <v>200</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>3603.7</v>
+        <v>3497.9</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>3578</v>
+        <v>3508.9</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>3602.4</v>
+        <v>3527.1</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>3487.3</v>
+        <v>3431</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3497.9</v>
+        <v>3466.6</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>-105.8</v>
-      </c>
-      <c r="J115" s="13" t="n">
-        <v>-2.94</v>
+        <v>-31.3</v>
+      </c>
+      <c r="J115" s="10" t="n">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="116">
@@ -4675,25 +4675,25 @@
         <v>500</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>2245.4</v>
+        <v>2215.6</v>
       </c>
       <c r="E116" s="12" t="n">
-        <v>2245.8</v>
+        <v>2248</v>
       </c>
       <c r="F116" s="12" t="n">
-        <v>2267.2</v>
+        <v>2273.8</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>2210.6</v>
+        <v>2225</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2215.6</v>
+        <v>2258.2</v>
       </c>
       <c r="I116" s="12" t="n">
-        <v>-29.8</v>
+        <v>42.6</v>
       </c>
       <c r="J116" s="13" t="n">
-        <v>-1.33</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="117">
@@ -4709,25 +4709,25 @@
         <v>175</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>3176</v>
+        <v>3111.8</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>3176</v>
+        <v>3137</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>3189.6</v>
+        <v>3181</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>3103.6</v>
+        <v>3101.1</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>3111.8</v>
+        <v>3173.9</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>-64.2</v>
+        <v>62.1</v>
       </c>
       <c r="J117" s="13" t="n">
-        <v>-2.02</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -4743,25 +4743,25 @@
         <v>4000</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>293.2</v>
+        <v>309.5</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>301.55</v>
+        <v>313.1</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>311.5</v>
+        <v>313.5</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>297</v>
+        <v>304.3</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>309.5</v>
+        <v>311.1</v>
       </c>
       <c r="I118" s="12" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="J118" s="10" t="n">
-        <v>5.56</v>
+        <v>1.6</v>
+      </c>
+      <c r="J118" s="13" t="n">
+        <v>0.52</v>
       </c>
     </row>
     <row r="119">
@@ -4777,25 +4777,25 @@
         <v>1200</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>830</v>
+        <v>833.4</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>828.05</v>
+        <v>834.4</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>837.2</v>
+        <v>845.65</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>825.2</v>
+        <v>833.55</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>833.4</v>
+        <v>835</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J119" s="10" t="n">
-        <v>0.41</v>
+        <v>1.6</v>
+      </c>
+      <c r="J119" s="13" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="120">
@@ -4811,25 +4811,25 @@
         <v>100</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>13172</v>
+        <v>13103</v>
       </c>
       <c r="E120" s="12" t="n">
-        <v>13187</v>
+        <v>13234</v>
       </c>
       <c r="F120" s="12" t="n">
-        <v>13285</v>
+        <v>13234</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>12986</v>
+        <v>12926</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>13103</v>
+        <v>13075</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-69</v>
-      </c>
-      <c r="J120" s="13" t="n">
-        <v>-0.52</v>
+        <v>-28</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="121">
@@ -4862,7 +4862,7 @@
       <c r="I121" s="9" t="n">
         <v/>
       </c>
-      <c r="J121" s="13" t="n">
+      <c r="J121" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -4879,25 +4879,25 @@
         <v>400</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>3156.9</v>
+        <v>3204.2</v>
       </c>
       <c r="E122" s="12" t="n">
-        <v>3249</v>
+        <v>3219.3</v>
       </c>
       <c r="F122" s="12" t="n">
-        <v>3265</v>
+        <v>3364</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>3131</v>
+        <v>3210</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>3204.2</v>
+        <v>3339.1</v>
       </c>
       <c r="I122" s="12" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="J122" s="10" t="n">
-        <v>1.5</v>
+        <v>134.9</v>
+      </c>
+      <c r="J122" s="13" t="n">
+        <v>4.21</v>
       </c>
     </row>
     <row r="123">
@@ -4913,25 +4913,25 @@
         <v>400</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>548.1</v>
+        <v>548</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>549</v>
+        <v>600</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>559.1</v>
+        <v>600</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>541.3</v>
+        <v>532</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>548</v>
+        <v>540.7</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="J123" s="13" t="n">
-        <v>-0.02</v>
+        <v>-7.3</v>
+      </c>
+      <c r="J123" s="10" t="n">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="124">
@@ -4947,25 +4947,25 @@
         <v>1100</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>1653.7</v>
+        <v>1597.9</v>
       </c>
       <c r="E124" s="12" t="n">
-        <v>1670.5</v>
+        <v>1606</v>
       </c>
       <c r="F124" s="12" t="n">
-        <v>1698.8</v>
+        <v>1642.7</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>1590.1</v>
+        <v>1605.6</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>1597.9</v>
+        <v>1631.4</v>
       </c>
       <c r="I124" s="12" t="n">
-        <v>-55.8</v>
+        <v>33.5</v>
       </c>
       <c r="J124" s="13" t="n">
-        <v>-3.37</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="125">
@@ -4981,25 +4981,25 @@
         <v>550</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1064.4</v>
+        <v>1046.9</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>1053.3</v>
+        <v>1047</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>1065</v>
+        <v>1074</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1024</v>
+        <v>1047</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1046.9</v>
+        <v>1067.4</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>-17.5</v>
+        <v>20.5</v>
       </c>
       <c r="J125" s="13" t="n">
-        <v>-1.64</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="126">
@@ -5015,25 +5015,25 @@
         <v>14000</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>124.26</v>
+        <v>126.32</v>
       </c>
       <c r="E126" s="12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F126" s="12" t="n">
-        <v>127.53</v>
+        <v>128</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>123.83</v>
+        <v>125.24</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>126.32</v>
+        <v>126.11</v>
       </c>
       <c r="I126" s="12" t="n">
-        <v>2.06</v>
+        <v>-0.21</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>1.66</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="127">
@@ -5049,25 +5049,25 @@
         <v>300</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2146.5</v>
+        <v>2145.2</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>2143</v>
+        <v>2105</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>2161.6</v>
+        <v>2133.7</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2127</v>
+        <v>2075.2</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>2145.2</v>
+        <v>2115.1</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="J127" s="13" t="n">
-        <v>-0.06</v>
+        <v>-30.1</v>
+      </c>
+      <c r="J127" s="10" t="n">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="128">
@@ -5083,24 +5083,24 @@
         <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>126505</v>
+        <v>126480</v>
       </c>
       <c r="E128" s="12" t="n">
-        <v>126535</v>
+        <v>127000</v>
       </c>
       <c r="F128" s="12" t="n">
-        <v>127500</v>
+        <v>128320</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>124900</v>
+        <v>126000</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>126480</v>
+        <v>126455</v>
       </c>
       <c r="I128" s="12" t="n">
         <v>-25</v>
       </c>
-      <c r="J128" s="13" t="n">
+      <c r="J128" s="10" t="n">
         <v>-0.02</v>
       </c>
     </row>
@@ -5117,25 +5117,25 @@
         <v>600</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>3353.4</v>
+        <v>3506.4</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>3421.8</v>
+        <v>3534</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>3533.1</v>
+        <v>3587</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>3383.7</v>
+        <v>3497.1</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3506.4</v>
+        <v>3531.1</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>153</v>
-      </c>
-      <c r="J129" s="10" t="n">
-        <v>4.56</v>
+        <v>24.7</v>
+      </c>
+      <c r="J129" s="13" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="130">
@@ -5151,25 +5151,25 @@
         <v>7500</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>394.05</v>
+        <v>408.25</v>
       </c>
       <c r="E130" s="12" t="n">
-        <v>398</v>
+        <v>414.6</v>
       </c>
       <c r="F130" s="12" t="n">
-        <v>411.25</v>
+        <v>420.7</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>397</v>
+        <v>410.7</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>408.25</v>
+        <v>416.45</v>
       </c>
       <c r="I130" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J130" s="10" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J130" s="13" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="131">
@@ -5185,25 +5185,25 @@
         <v>150</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>930.9</v>
+        <v>927.85</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>930.9</v>
+        <v>926.05</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>940.9</v>
+        <v>951.8</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>920.2</v>
+        <v>921.5</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>927.85</v>
+        <v>937.75</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>-3.05</v>
+        <v>9.9</v>
       </c>
       <c r="J131" s="13" t="n">
-        <v>-0.33</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="132">
@@ -5219,25 +5219,25 @@
         <v>200</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>6950.5</v>
+        <v>6910.5</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>6940</v>
+        <v>6979</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>7120</v>
+        <v>6979</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>6890</v>
+        <v>6818.5</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>6910.5</v>
+        <v>6892.5</v>
       </c>
       <c r="I132" s="12" t="n">
-        <v>-40</v>
-      </c>
-      <c r="J132" s="13" t="n">
-        <v>-0.58</v>
+        <v>-18</v>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="133">
@@ -5253,25 +5253,25 @@
         <v>50</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1468.6</v>
+        <v>1468.9</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>1468.6</v>
+        <v>1468.9</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>1486</v>
+        <v>1479.4</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>1463.5</v>
+        <v>1453</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1468.9</v>
+        <v>1459.6</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>0.3</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="J133" s="10" t="n">
-        <v>0.02</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="134">
@@ -5287,25 +5287,25 @@
         <v>6750</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>86.62</v>
+        <v>91.11</v>
       </c>
       <c r="E134" s="12" t="n">
-        <v>86.5</v>
+        <v>92</v>
       </c>
       <c r="F134" s="12" t="n">
-        <v>91.8</v>
+        <v>93.78</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>86.42</v>
+        <v>91.63</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>91.11</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="I134" s="12" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="J134" s="10" t="n">
-        <v>5.18</v>
+        <v>2.1</v>
+      </c>
+      <c r="J134" s="13" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="135">
@@ -5321,25 +5321,25 @@
         <v>2250</v>
       </c>
       <c r="D135" s="9" t="n">
-        <v>392.7</v>
+        <v>390.45</v>
       </c>
       <c r="E135" s="9" t="n">
-        <v>392</v>
+        <v>393.7</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>394.05</v>
+        <v>398.55</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>385.8</v>
+        <v>391.2</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>390.45</v>
+        <v>396.3</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>-2.25</v>
+        <v>5.85</v>
       </c>
       <c r="J135" s="13" t="n">
-        <v>-0.57</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="136">
@@ -5355,25 +5355,25 @@
         <v>700</v>
       </c>
       <c r="D136" s="12" t="n">
-        <v>1626.7</v>
+        <v>1616.7</v>
       </c>
       <c r="E136" s="12" t="n">
-        <v>1638</v>
+        <v>1625.4</v>
       </c>
       <c r="F136" s="12" t="n">
-        <v>1643.1</v>
+        <v>1644.5</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1610.1</v>
+        <v>1599.4</v>
       </c>
       <c r="H136" s="12" t="n">
-        <v>1618.7</v>
+        <v>1637.6</v>
       </c>
       <c r="I136" s="12" t="n">
-        <v>-8</v>
+        <v>20.9</v>
       </c>
       <c r="J136" s="13" t="n">
-        <v>-0.49</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="137">
@@ -5389,25 +5389,25 @@
         <v>75</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>9010.5</v>
+        <v>8928.5</v>
       </c>
       <c r="E137" s="9" t="n">
-        <v>9000</v>
+        <v>8930</v>
       </c>
       <c r="F137" s="9" t="n">
-        <v>9090</v>
+        <v>8960</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>8910</v>
+        <v>8646.5</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>8928.5</v>
+        <v>8904.5</v>
       </c>
       <c r="I137" s="9" t="n">
-        <v>-82</v>
-      </c>
-      <c r="J137" s="13" t="n">
-        <v>-0.91</v>
+        <v>-24</v>
+      </c>
+      <c r="J137" s="10" t="n">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="138">
@@ -5423,25 +5423,25 @@
         <v>1925</v>
       </c>
       <c r="D138" s="12" t="n">
-        <v>294.5</v>
+        <v>297.15</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>300.2</v>
+        <v>303.7</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>294.1</v>
+        <v>298.7</v>
       </c>
       <c r="H138" s="12" t="n">
-        <v>297.15</v>
+        <v>300.9</v>
       </c>
       <c r="I138" s="12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="J138" s="10" t="n">
-        <v>0.9</v>
+        <v>3.75</v>
+      </c>
+      <c r="J138" s="13" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="139">
@@ -5457,25 +5457,25 @@
         <v>15</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>35085</v>
+        <v>35330</v>
       </c>
       <c r="E139" s="9" t="n">
-        <v>35115</v>
+        <v>35395</v>
       </c>
       <c r="F139" s="9" t="n">
-        <v>35830</v>
+        <v>36535</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>34720</v>
+        <v>35345</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>35330</v>
+        <v>36125</v>
       </c>
       <c r="I139" s="9" t="n">
-        <v>245</v>
-      </c>
-      <c r="J139" s="10" t="n">
-        <v>0.7</v>
+        <v>795</v>
+      </c>
+      <c r="J139" s="13" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="140">
@@ -5508,7 +5508,7 @@
       <c r="I140" s="12" t="n">
         <v/>
       </c>
-      <c r="J140" s="13" t="n">
+      <c r="J140" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -5525,25 +5525,25 @@
         <v>175</v>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4877.1</v>
+        <v>4845</v>
       </c>
       <c r="E141" s="9" t="n">
-        <v>4855</v>
+        <v>4831</v>
       </c>
       <c r="F141" s="9" t="n">
-        <v>4914</v>
+        <v>4831</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>4815.8</v>
+        <v>4577</v>
       </c>
       <c r="H141" s="9" t="n">
-        <v>4845</v>
+        <v>4628.8</v>
       </c>
       <c r="I141" s="9" t="n">
-        <v>-32.1</v>
-      </c>
-      <c r="J141" s="13" t="n">
-        <v>-0.66</v>
+        <v>-216.2</v>
+      </c>
+      <c r="J141" s="10" t="n">
+        <v>-4.46</v>
       </c>
     </row>
     <row r="142">
@@ -5559,25 +5559,25 @@
         <v>3000</v>
       </c>
       <c r="D142" s="12" t="n">
-        <v>271.15</v>
+        <v>271.35</v>
       </c>
       <c r="E142" s="12" t="n">
-        <v>273.5</v>
+        <v>274.6</v>
       </c>
       <c r="F142" s="12" t="n">
-        <v>274.1</v>
+        <v>274.65</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>269.2</v>
+        <v>268.25</v>
       </c>
       <c r="H142" s="12" t="n">
-        <v>271.35</v>
+        <v>271.75</v>
       </c>
       <c r="I142" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J142" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.4</v>
+      </c>
+      <c r="J142" s="13" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="143">
@@ -5593,25 +5593,25 @@
         <v>2700</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>440.7</v>
+        <v>446</v>
       </c>
       <c r="E143" s="9" t="n">
-        <v>440.05</v>
+        <v>449.75</v>
       </c>
       <c r="F143" s="9" t="n">
-        <v>453.9</v>
+        <v>452.95</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>437.1</v>
+        <v>439.1</v>
       </c>
       <c r="H143" s="9" t="n">
-        <v>446</v>
+        <v>451.45</v>
       </c>
       <c r="I143" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J143" s="10" t="n">
-        <v>1.2</v>
+        <v>5.45</v>
+      </c>
+      <c r="J143" s="13" t="n">
+        <v>1.22</v>
       </c>
     </row>
     <row r="144">
@@ -5627,25 +5627,25 @@
         <v>250</v>
       </c>
       <c r="D144" s="12" t="n">
-        <v>1453</v>
+        <v>1445.6</v>
       </c>
       <c r="E144" s="12" t="n">
-        <v>1453</v>
+        <v>1458.7</v>
       </c>
       <c r="F144" s="12" t="n">
-        <v>1472</v>
+        <v>1489.8</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>1438.3</v>
+        <v>1458.7</v>
       </c>
       <c r="H144" s="12" t="n">
-        <v>1445.6</v>
+        <v>1483.8</v>
       </c>
       <c r="I144" s="12" t="n">
-        <v>-7.4</v>
+        <v>38.2</v>
       </c>
       <c r="J144" s="13" t="n">
-        <v>-0.51</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="145">
@@ -5661,25 +5661,25 @@
         <v>250</v>
       </c>
       <c r="D145" s="9" t="n">
-        <v>2997.6</v>
+        <v>3051</v>
       </c>
       <c r="E145" s="9" t="n">
-        <v>2998.7</v>
+        <v>3064.8</v>
       </c>
       <c r="F145" s="9" t="n">
-        <v>3098.3</v>
+        <v>3169.2</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>2998.7</v>
+        <v>3060.5</v>
       </c>
       <c r="H145" s="9" t="n">
-        <v>3051</v>
+        <v>3103.6</v>
       </c>
       <c r="I145" s="9" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="J145" s="10" t="n">
-        <v>1.78</v>
+        <v>52.6</v>
+      </c>
+      <c r="J145" s="13" t="n">
+        <v>1.72</v>
       </c>
     </row>
     <row r="146">
@@ -5695,25 +5695,25 @@
         <v>8000</v>
       </c>
       <c r="D146" s="12" t="n">
-        <v>102.78</v>
+        <v>102.77</v>
       </c>
       <c r="E146" s="12" t="n">
-        <v>102.99</v>
+        <v>103.3</v>
       </c>
       <c r="F146" s="12" t="n">
-        <v>103.89</v>
+        <v>104.98</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>101.35</v>
+        <v>102.3</v>
       </c>
       <c r="H146" s="12" t="n">
-        <v>102.77</v>
+        <v>104.62</v>
       </c>
       <c r="I146" s="12" t="n">
-        <v>-0.01</v>
+        <v>1.85</v>
       </c>
       <c r="J146" s="13" t="n">
-        <v>-0.01</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="147">
@@ -5729,25 +5729,25 @@
         <v>175</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>9021.5</v>
+        <v>8887.5</v>
       </c>
       <c r="E147" s="9" t="n">
-        <v>8991</v>
+        <v>8948</v>
       </c>
       <c r="F147" s="9" t="n">
-        <v>9072.5</v>
+        <v>9239</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>8865</v>
+        <v>8925.5</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>8887.5</v>
+        <v>9217.5</v>
       </c>
       <c r="I147" s="9" t="n">
-        <v>-134</v>
+        <v>330</v>
       </c>
       <c r="J147" s="13" t="n">
-        <v>-1.49</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="148">
@@ -5763,25 +5763,25 @@
         <v>2700</v>
       </c>
       <c r="D148" s="12" t="n">
-        <v>306.3</v>
+        <v>301.5</v>
       </c>
       <c r="E148" s="12" t="n">
-        <v>304.25</v>
+        <v>306</v>
       </c>
       <c r="F148" s="12" t="n">
-        <v>305.4</v>
+        <v>307.55</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>295.65</v>
+        <v>300.6</v>
       </c>
       <c r="H148" s="12" t="n">
-        <v>301.5</v>
+        <v>301.75</v>
       </c>
       <c r="I148" s="12" t="n">
-        <v>-4.8</v>
+        <v>0.25</v>
       </c>
       <c r="J148" s="13" t="n">
-        <v>-1.57</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="149">
@@ -5797,25 +5797,25 @@
         <v>873</v>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1014.6</v>
+        <v>1023.5</v>
       </c>
       <c r="E149" s="9" t="n">
-        <v>995</v>
+        <v>1024.3</v>
       </c>
       <c r="F149" s="9" t="n">
-        <v>1032</v>
+        <v>1032.4</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>992.3</v>
+        <v>1008</v>
       </c>
       <c r="H149" s="9" t="n">
-        <v>1023.5</v>
+        <v>1021.9</v>
       </c>
       <c r="I149" s="9" t="n">
-        <v>8.9</v>
+        <v>-1.6</v>
       </c>
       <c r="J149" s="10" t="n">
-        <v>0.88</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="150">
@@ -5831,25 +5831,25 @@
         <v>5000</v>
       </c>
       <c r="D150" s="12" t="n">
-        <v>325.25</v>
+        <v>325.75</v>
       </c>
       <c r="E150" s="12" t="n">
-        <v>325.25</v>
+        <v>328.85</v>
       </c>
       <c r="F150" s="12" t="n">
-        <v>332.4</v>
+        <v>338.45</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>324.9</v>
+        <v>322.6</v>
       </c>
       <c r="H150" s="12" t="n">
-        <v>325.75</v>
+        <v>337.2</v>
       </c>
       <c r="I150" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J150" s="10" t="n">
-        <v>0.15</v>
+        <v>11.45</v>
+      </c>
+      <c r="J150" s="13" t="n">
+        <v>3.51</v>
       </c>
     </row>
     <row r="151">
@@ -5865,25 +5865,25 @@
         <v>3000</v>
       </c>
       <c r="D151" s="9" t="n">
-        <v>344.35</v>
+        <v>346.55</v>
       </c>
       <c r="E151" s="9" t="n">
-        <v>345.45</v>
+        <v>349</v>
       </c>
       <c r="F151" s="9" t="n">
-        <v>351.1</v>
+        <v>350.55</v>
       </c>
       <c r="G151" s="9" t="n">
-        <v>342</v>
+        <v>341.7</v>
       </c>
       <c r="H151" s="9" t="n">
-        <v>346.55</v>
+        <v>348.3</v>
       </c>
       <c r="I151" s="9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J151" s="10" t="n">
-        <v>0.64</v>
+        <v>1.75</v>
+      </c>
+      <c r="J151" s="13" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
@@ -5899,25 +5899,25 @@
         <v>1250</v>
       </c>
       <c r="D152" s="12" t="n">
-        <v>1364</v>
+        <v>1358.8</v>
       </c>
       <c r="E152" s="12" t="n">
-        <v>1361.4</v>
+        <v>1365.2</v>
       </c>
       <c r="F152" s="12" t="n">
-        <v>1372.4</v>
+        <v>1378</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1352.4</v>
+        <v>1358.4</v>
       </c>
       <c r="H152" s="12" t="n">
-        <v>1358.8</v>
+        <v>1361.8</v>
       </c>
       <c r="I152" s="12" t="n">
-        <v>-5.2</v>
+        <v>3</v>
       </c>
       <c r="J152" s="13" t="n">
-        <v>-0.38</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="153">
@@ -5933,25 +5933,25 @@
         <v>8500</v>
       </c>
       <c r="D153" s="9" t="n">
-        <v>176.09</v>
+        <v>201.31</v>
       </c>
       <c r="E153" s="9" t="n">
-        <v>176.31</v>
+        <v>203</v>
       </c>
       <c r="F153" s="9" t="n">
-        <v>202.35</v>
+        <v>209.7</v>
       </c>
       <c r="G153" s="9" t="n">
-        <v>176.31</v>
+        <v>198.55</v>
       </c>
       <c r="H153" s="9" t="n">
-        <v>201.31</v>
+        <v>199.08</v>
       </c>
       <c r="I153" s="9" t="n">
-        <v>25.22</v>
+        <v>-2.23</v>
       </c>
       <c r="J153" s="10" t="n">
-        <v>14.32</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="154">
@@ -5967,25 +5967,25 @@
         <v>1000</v>
       </c>
       <c r="D154" s="12" t="n">
-        <v>625.1</v>
+        <v>634.15</v>
       </c>
       <c r="E154" s="12" t="n">
-        <v>625.1</v>
+        <v>636.8</v>
       </c>
       <c r="F154" s="12" t="n">
-        <v>640.65</v>
+        <v>638.3</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>622.25</v>
+        <v>620.55</v>
       </c>
       <c r="H154" s="12" t="n">
-        <v>634.15</v>
+        <v>631.55</v>
       </c>
       <c r="I154" s="12" t="n">
-        <v>9.050000000000001</v>
+        <v>-2.6</v>
       </c>
       <c r="J154" s="10" t="n">
-        <v>1.45</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="155">
@@ -6001,25 +6001,25 @@
         <v>750</v>
       </c>
       <c r="D155" s="9" t="n">
-        <v>1833.9</v>
+        <v>1837.5</v>
       </c>
       <c r="E155" s="9" t="n">
-        <v>1820</v>
+        <v>1831</v>
       </c>
       <c r="F155" s="9" t="n">
-        <v>1851.4</v>
+        <v>1870</v>
       </c>
       <c r="G155" s="9" t="n">
-        <v>1818.2</v>
+        <v>1825</v>
       </c>
       <c r="H155" s="9" t="n">
-        <v>1837.5</v>
+        <v>1866.7</v>
       </c>
       <c r="I155" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J155" s="10" t="n">
-        <v>0.2</v>
+        <v>29.2</v>
+      </c>
+      <c r="J155" s="13" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="156">
@@ -6035,25 +6035,25 @@
         <v>1500</v>
       </c>
       <c r="D156" s="12" t="n">
-        <v>974.6</v>
+        <v>970.1</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>978</v>
+        <v>973.5</v>
       </c>
       <c r="F156" s="12" t="n">
-        <v>981.2</v>
+        <v>987</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>961.2</v>
+        <v>963.6</v>
       </c>
       <c r="H156" s="12" t="n">
-        <v>970.1</v>
+        <v>979.9</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>-4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J156" s="13" t="n">
-        <v>-0.46</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="157">
@@ -6069,25 +6069,25 @@
         <v>25</v>
       </c>
       <c r="D157" s="9" t="n">
-        <v>24860</v>
+        <v>24995</v>
       </c>
       <c r="E157" s="9" t="n">
-        <v>24705</v>
+        <v>25210</v>
       </c>
       <c r="F157" s="9" t="n">
-        <v>25285</v>
+        <v>25300</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>24705</v>
+        <v>24900</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>24995</v>
+        <v>25025</v>
       </c>
       <c r="I157" s="9" t="n">
-        <v>135</v>
-      </c>
-      <c r="J157" s="10" t="n">
-        <v>0.54</v>
+        <v>30</v>
+      </c>
+      <c r="J157" s="13" t="n">
+        <v>0.12</v>
       </c>
     </row>
     <row r="158">
@@ -6103,25 +6103,25 @@
         <v>300</v>
       </c>
       <c r="D158" s="12" t="n">
-        <v>930.45</v>
+        <v>920.55</v>
       </c>
       <c r="E158" s="12" t="n">
-        <v>925.2</v>
+        <v>929.9</v>
       </c>
       <c r="F158" s="12" t="n">
-        <v>938.4</v>
+        <v>941.65</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>915</v>
+        <v>901.3</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>920.55</v>
+        <v>935.1</v>
       </c>
       <c r="I158" s="12" t="n">
-        <v>-9.9</v>
+        <v>14.55</v>
       </c>
       <c r="J158" s="13" t="n">
-        <v>-1.06</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="159">
@@ -6137,25 +6137,25 @@
         <v>275</v>
       </c>
       <c r="D159" s="9" t="n">
-        <v>3574.4</v>
+        <v>3532.2</v>
       </c>
       <c r="E159" s="9" t="n">
-        <v>3574.4</v>
+        <v>3574</v>
       </c>
       <c r="F159" s="9" t="n">
-        <v>3628.5</v>
+        <v>3712</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>3518.2</v>
+        <v>3469</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>3532.2</v>
+        <v>3693.8</v>
       </c>
       <c r="I159" s="9" t="n">
-        <v>-42.2</v>
+        <v>161.6</v>
       </c>
       <c r="J159" s="13" t="n">
-        <v>-1.18</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="160">
@@ -6171,25 +6171,25 @@
         <v>375</v>
       </c>
       <c r="D160" s="12" t="n">
-        <v>2721.2</v>
+        <v>2695.2</v>
       </c>
       <c r="E160" s="12" t="n">
-        <v>2738.9</v>
+        <v>2714</v>
       </c>
       <c r="F160" s="12" t="n">
-        <v>2756.3</v>
+        <v>2739.9</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>2688.8</v>
+        <v>2664.9</v>
       </c>
       <c r="H160" s="12" t="n">
-        <v>2695.2</v>
+        <v>2729.4</v>
       </c>
       <c r="I160" s="12" t="n">
-        <v>-26</v>
+        <v>34.2</v>
       </c>
       <c r="J160" s="13" t="n">
-        <v>-0.96</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="161">
@@ -6205,25 +6205,25 @@
         <v>350</v>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1845.7</v>
+        <v>1824.8</v>
       </c>
       <c r="E161" s="9" t="n">
-        <v>1845.7</v>
+        <v>1852</v>
       </c>
       <c r="F161" s="9" t="n">
-        <v>1860</v>
+        <v>1867.5</v>
       </c>
       <c r="G161" s="9" t="n">
-        <v>1820</v>
+        <v>1829.7</v>
       </c>
       <c r="H161" s="9" t="n">
-        <v>1824.8</v>
+        <v>1863.2</v>
       </c>
       <c r="I161" s="9" t="n">
-        <v>-20.9</v>
+        <v>38.4</v>
       </c>
       <c r="J161" s="13" t="n">
-        <v>-1.13</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="162">
@@ -6239,25 +6239,25 @@
         <v>1500</v>
       </c>
       <c r="D162" s="12" t="n">
-        <v>560.2</v>
+        <v>532.95</v>
       </c>
       <c r="E162" s="12" t="n">
-        <v>560.5</v>
+        <v>533.05</v>
       </c>
       <c r="F162" s="12" t="n">
-        <v>560.5</v>
+        <v>539.35</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="H162" s="12" t="n">
-        <v>532.95</v>
+        <v>523.25</v>
       </c>
       <c r="I162" s="12" t="n">
-        <v>-27.25</v>
-      </c>
-      <c r="J162" s="13" t="n">
-        <v>-4.86</v>
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="J162" s="10" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="163">
@@ -6273,25 +6273,25 @@
         <v>1500</v>
       </c>
       <c r="D163" s="9" t="n">
-        <v>478.75</v>
+        <v>463.25</v>
       </c>
       <c r="E163" s="9" t="n">
-        <v>478</v>
+        <v>466.95</v>
       </c>
       <c r="F163" s="9" t="n">
-        <v>478.75</v>
+        <v>485.1</v>
       </c>
       <c r="G163" s="9" t="n">
-        <v>462</v>
+        <v>464.1</v>
       </c>
       <c r="H163" s="9" t="n">
-        <v>463.25</v>
+        <v>467.95</v>
       </c>
       <c r="I163" s="9" t="n">
-        <v>-15.5</v>
+        <v>4.7</v>
       </c>
       <c r="J163" s="13" t="n">
-        <v>-3.24</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="164">
@@ -6307,25 +6307,25 @@
         <v>1100</v>
       </c>
       <c r="D164" s="12" t="n">
-        <v>770.25</v>
+        <v>768.1</v>
       </c>
       <c r="E164" s="12" t="n">
-        <v>770.6</v>
+        <v>773.8</v>
       </c>
       <c r="F164" s="12" t="n">
-        <v>779.75</v>
+        <v>773.8</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>765.15</v>
+        <v>755</v>
       </c>
       <c r="H164" s="12" t="n">
-        <v>768.1</v>
+        <v>757.1</v>
       </c>
       <c r="I164" s="12" t="n">
-        <v>-2.15</v>
-      </c>
-      <c r="J164" s="13" t="n">
-        <v>-0.28</v>
+        <v>-11</v>
+      </c>
+      <c r="J164" s="10" t="n">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="165">
@@ -6341,25 +6341,25 @@
         <v>700</v>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1539.9</v>
+        <v>1558.8</v>
       </c>
       <c r="E165" s="9" t="n">
-        <v>1545</v>
+        <v>1574</v>
       </c>
       <c r="F165" s="9" t="n">
-        <v>1575.9</v>
+        <v>1670</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>1532.3</v>
+        <v>1573.8</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>1558.8</v>
+        <v>1656.1</v>
       </c>
       <c r="I165" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="J165" s="10" t="n">
-        <v>1.23</v>
+        <v>97.3</v>
+      </c>
+      <c r="J165" s="13" t="n">
+        <v>6.24</v>
       </c>
     </row>
     <row r="166">
@@ -6375,25 +6375,25 @@
         <v>1100</v>
       </c>
       <c r="D166" s="12" t="n">
-        <v>1253</v>
+        <v>1235</v>
       </c>
       <c r="E166" s="12" t="n">
-        <v>1249.1</v>
+        <v>1241</v>
       </c>
       <c r="F166" s="12" t="n">
-        <v>1277.9</v>
+        <v>1250</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>1233</v>
+        <v>1224.3</v>
       </c>
       <c r="H166" s="12" t="n">
-        <v>1235</v>
+        <v>1228.3</v>
       </c>
       <c r="I166" s="12" t="n">
-        <v>-18</v>
-      </c>
-      <c r="J166" s="13" t="n">
-        <v>-1.44</v>
+        <v>-6.7</v>
+      </c>
+      <c r="J166" s="10" t="n">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="167">
@@ -6426,7 +6426,7 @@
       <c r="I167" s="9" t="n">
         <v/>
       </c>
-      <c r="J167" s="13" t="n">
+      <c r="J167" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -6443,25 +6443,25 @@
         <v>3375</v>
       </c>
       <c r="D168" s="12" t="n">
-        <v>418.4</v>
+        <v>404.45</v>
       </c>
       <c r="E168" s="12" t="n">
-        <v>391</v>
+        <v>405.85</v>
       </c>
       <c r="F168" s="12" t="n">
-        <v>413.75</v>
+        <v>411.3</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>390.8</v>
+        <v>402.2</v>
       </c>
       <c r="H168" s="12" t="n">
-        <v>404.45</v>
+        <v>407.85</v>
       </c>
       <c r="I168" s="12" t="n">
-        <v>-13.95</v>
+        <v>3.4</v>
       </c>
       <c r="J168" s="13" t="n">
-        <v>-3.33</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="169">
@@ -6477,25 +6477,25 @@
         <v>5500</v>
       </c>
       <c r="D169" s="9" t="n">
-        <v>212</v>
+        <v>219.62</v>
       </c>
       <c r="E169" s="9" t="n">
-        <v>213.24</v>
+        <v>222.3</v>
       </c>
       <c r="F169" s="9" t="n">
-        <v>220.91</v>
+        <v>222.9</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>213.07</v>
+        <v>219.02</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>219.62</v>
+        <v>221.13</v>
       </c>
       <c r="I169" s="9" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="J169" s="10" t="n">
-        <v>3.59</v>
+        <v>1.51</v>
+      </c>
+      <c r="J169" s="13" t="n">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -6511,25 +6511,25 @@
         <v>150</v>
       </c>
       <c r="D170" s="12" t="n">
-        <v>2300.3</v>
+        <v>2272.8</v>
       </c>
       <c r="E170" s="12" t="n">
-        <v>2306</v>
+        <v>2265</v>
       </c>
       <c r="F170" s="12" t="n">
-        <v>2309.2</v>
+        <v>2265</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>2269</v>
+        <v>2206.4</v>
       </c>
       <c r="H170" s="12" t="n">
-        <v>2272.8</v>
+        <v>2246</v>
       </c>
       <c r="I170" s="12" t="n">
-        <v>-27.5</v>
-      </c>
-      <c r="J170" s="13" t="n">
-        <v>-1.2</v>
+        <v>-26.8</v>
+      </c>
+      <c r="J170" s="10" t="n">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="171">
@@ -6545,25 +6545,25 @@
         <v>400</v>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1392.9</v>
+        <v>1375</v>
       </c>
       <c r="E171" s="9" t="n">
-        <v>1392.9</v>
+        <v>1370</v>
       </c>
       <c r="F171" s="9" t="n">
-        <v>1399.9</v>
+        <v>1374</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>1371.6</v>
+        <v>1327.3</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>1375</v>
+        <v>1343.4</v>
       </c>
       <c r="I171" s="9" t="n">
-        <v>-17.9</v>
-      </c>
-      <c r="J171" s="13" t="n">
-        <v>-1.29</v>
+        <v>-31.6</v>
+      </c>
+      <c r="J171" s="10" t="n">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="172">
@@ -6579,25 +6579,25 @@
         <v>275</v>
       </c>
       <c r="D172" s="12" t="n">
-        <v>2954</v>
+        <v>2941</v>
       </c>
       <c r="E172" s="12" t="n">
-        <v>2959</v>
+        <v>2949</v>
       </c>
       <c r="F172" s="12" t="n">
-        <v>3070.7</v>
+        <v>2976.4</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>2918.5</v>
+        <v>2761.9</v>
       </c>
       <c r="H172" s="12" t="n">
-        <v>2941</v>
+        <v>2800.8</v>
       </c>
       <c r="I172" s="12" t="n">
-        <v>-13</v>
-      </c>
-      <c r="J172" s="13" t="n">
-        <v>-0.44</v>
+        <v>-140.2</v>
+      </c>
+      <c r="J172" s="10" t="n">
+        <v>-4.77</v>
       </c>
     </row>
     <row r="173">
@@ -6613,25 +6613,25 @@
         <v>375</v>
       </c>
       <c r="D173" s="9" t="n">
-        <v>4055.3</v>
+        <v>4090.7</v>
       </c>
       <c r="E173" s="9" t="n">
-        <v>4030</v>
+        <v>4115</v>
       </c>
       <c r="F173" s="9" t="n">
-        <v>4110</v>
+        <v>4147</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>3985.1</v>
+        <v>4059.1</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>4090.7</v>
+        <v>4135.2</v>
       </c>
       <c r="I173" s="9" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="J173" s="10" t="n">
-        <v>0.87</v>
+        <v>44.5</v>
+      </c>
+      <c r="J173" s="13" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="174">
@@ -6647,25 +6647,25 @@
         <v>500</v>
       </c>
       <c r="D174" s="12" t="n">
-        <v>4381.9</v>
+        <v>4295.8</v>
       </c>
       <c r="E174" s="12" t="n">
-        <v>4355.8</v>
+        <v>4348.2</v>
       </c>
       <c r="F174" s="12" t="n">
-        <v>4409.9</v>
+        <v>4420.7</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>4264</v>
+        <v>4318</v>
       </c>
       <c r="H174" s="12" t="n">
-        <v>4295.8</v>
+        <v>4403.9</v>
       </c>
       <c r="I174" s="12" t="n">
-        <v>-86.09999999999999</v>
+        <v>108.1</v>
       </c>
       <c r="J174" s="13" t="n">
-        <v>-1.96</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="175">
@@ -6681,25 +6681,25 @@
         <v>1500</v>
       </c>
       <c r="D175" s="9" t="n">
-        <v>1597.6</v>
+        <v>1457.1</v>
       </c>
       <c r="E175" s="9" t="n">
-        <v>1538.2</v>
+        <v>1464.2</v>
       </c>
       <c r="F175" s="9" t="n">
-        <v>1561.5</v>
+        <v>1484</v>
       </c>
       <c r="G175" s="9" t="n">
-        <v>1450</v>
+        <v>1443</v>
       </c>
       <c r="H175" s="9" t="n">
-        <v>1457.1</v>
+        <v>1457.7</v>
       </c>
       <c r="I175" s="9" t="n">
-        <v>-140.5</v>
+        <v>0.6</v>
       </c>
       <c r="J175" s="13" t="n">
-        <v>-8.789999999999999</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="176">
@@ -6715,25 +6715,25 @@
         <v>375</v>
       </c>
       <c r="D176" s="12" t="n">
-        <v>4050.6</v>
+        <v>4084.5</v>
       </c>
       <c r="E176" s="12" t="n">
-        <v>4038.5</v>
+        <v>4099.2</v>
       </c>
       <c r="F176" s="12" t="n">
-        <v>4127</v>
+        <v>4166.5</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>4021</v>
+        <v>4099.2</v>
       </c>
       <c r="H176" s="12" t="n">
-        <v>4084.5</v>
+        <v>4132.4</v>
       </c>
       <c r="I176" s="12" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="J176" s="10" t="n">
-        <v>0.84</v>
+        <v>47.9</v>
+      </c>
+      <c r="J176" s="13" t="n">
+        <v>1.17</v>
       </c>
     </row>
     <row r="177">
@@ -6749,25 +6749,25 @@
         <v>350</v>
       </c>
       <c r="D177" s="9" t="n">
-        <v>3561</v>
+        <v>3527.2</v>
       </c>
       <c r="E177" s="9" t="n">
-        <v>3565</v>
+        <v>3543.8</v>
       </c>
       <c r="F177" s="9" t="n">
-        <v>3647.5</v>
+        <v>3543.8</v>
       </c>
       <c r="G177" s="9" t="n">
-        <v>3483</v>
+        <v>3382.8</v>
       </c>
       <c r="H177" s="9" t="n">
-        <v>3527.2</v>
+        <v>3460.8</v>
       </c>
       <c r="I177" s="9" t="n">
-        <v>-33.8</v>
-      </c>
-      <c r="J177" s="13" t="n">
-        <v>-0.95</v>
+        <v>-66.40000000000001</v>
+      </c>
+      <c r="J177" s="10" t="n">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="178">
@@ -6783,25 +6783,25 @@
         <v>700</v>
       </c>
       <c r="D178" s="12" t="n">
-        <v>1410.5</v>
+        <v>1381.2</v>
       </c>
       <c r="E178" s="12" t="n">
-        <v>1414</v>
+        <v>1394.8</v>
       </c>
       <c r="F178" s="12" t="n">
-        <v>1415.4</v>
+        <v>1395.5</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>1362</v>
+        <v>1370.5</v>
       </c>
       <c r="H178" s="12" t="n">
-        <v>1381.2</v>
+        <v>1389.2</v>
       </c>
       <c r="I178" s="12" t="n">
-        <v>-29.3</v>
+        <v>8</v>
       </c>
       <c r="J178" s="13" t="n">
-        <v>-2.08</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="179">
@@ -6817,25 +6817,25 @@
         <v>200</v>
       </c>
       <c r="D179" s="9" t="n">
-        <v>11516</v>
+        <v>11573</v>
       </c>
       <c r="E179" s="9" t="n">
-        <v>11500</v>
+        <v>11600</v>
       </c>
       <c r="F179" s="9" t="n">
-        <v>11652</v>
+        <v>11769</v>
       </c>
       <c r="G179" s="9" t="n">
-        <v>11431</v>
+        <v>11550</v>
       </c>
       <c r="H179" s="9" t="n">
-        <v>11573</v>
+        <v>11692</v>
       </c>
       <c r="I179" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="J179" s="10" t="n">
-        <v>0.49</v>
+        <v>119</v>
+      </c>
+      <c r="J179" s="13" t="n">
+        <v>1.03</v>
       </c>
     </row>
     <row r="180">
@@ -6851,25 +6851,25 @@
         <v>8400</v>
       </c>
       <c r="D180" s="12" t="n">
-        <v>162.19</v>
+        <v>162.46</v>
       </c>
       <c r="E180" s="12" t="n">
-        <v>162.35</v>
+        <v>163.24</v>
       </c>
       <c r="F180" s="12" t="n">
-        <v>163.81</v>
+        <v>166.9</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>159.76</v>
+        <v>161.33</v>
       </c>
       <c r="H180" s="12" t="n">
-        <v>162.46</v>
+        <v>164.9</v>
       </c>
       <c r="I180" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J180" s="10" t="n">
-        <v>0.17</v>
+        <v>2.44</v>
+      </c>
+      <c r="J180" s="13" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="181">
@@ -6885,25 +6885,25 @@
         <v>1300</v>
       </c>
       <c r="D181" s="9" t="n">
-        <v>626.15</v>
+        <v>630.1</v>
       </c>
       <c r="E181" s="9" t="n">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="F181" s="9" t="n">
-        <v>636.5</v>
+        <v>641.25</v>
       </c>
       <c r="G181" s="9" t="n">
-        <v>624.3</v>
+        <v>629.9</v>
       </c>
       <c r="H181" s="9" t="n">
-        <v>630.1</v>
+        <v>638.4</v>
       </c>
       <c r="I181" s="9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J181" s="10" t="n">
-        <v>0.63</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J181" s="13" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="182">
@@ -6919,25 +6919,25 @@
         <v>2750</v>
       </c>
       <c r="D182" s="12" t="n">
-        <v>305.05</v>
+        <v>323.35</v>
       </c>
       <c r="E182" s="12" t="n">
-        <v>311.95</v>
+        <v>329</v>
       </c>
       <c r="F182" s="12" t="n">
-        <v>325.5</v>
+        <v>340.65</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>308.8</v>
+        <v>325.1</v>
       </c>
       <c r="H182" s="12" t="n">
-        <v>323.35</v>
+        <v>338.9</v>
       </c>
       <c r="I182" s="12" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="J182" s="10" t="n">
-        <v>6</v>
+        <v>15.55</v>
+      </c>
+      <c r="J182" s="13" t="n">
+        <v>4.81</v>
       </c>
     </row>
     <row r="183">
@@ -6953,25 +6953,25 @@
         <v>1000</v>
       </c>
       <c r="D183" s="9" t="n">
-        <v>1269.6</v>
+        <v>1258.9</v>
       </c>
       <c r="E183" s="9" t="n">
-        <v>1269.6</v>
+        <v>1262.9</v>
       </c>
       <c r="F183" s="9" t="n">
-        <v>1302.7</v>
+        <v>1300</v>
       </c>
       <c r="G183" s="9" t="n">
-        <v>1255</v>
+        <v>1245.6</v>
       </c>
       <c r="H183" s="9" t="n">
-        <v>1258.9</v>
+        <v>1293.5</v>
       </c>
       <c r="I183" s="9" t="n">
-        <v>-10.7</v>
+        <v>34.6</v>
       </c>
       <c r="J183" s="13" t="n">
-        <v>-0.84</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="184">
@@ -6987,25 +6987,25 @@
         <v>1500</v>
       </c>
       <c r="D184" s="12" t="n">
-        <v>189.57</v>
+        <v>187.8</v>
       </c>
       <c r="E184" s="12" t="n">
-        <v>190.67</v>
+        <v>188.25</v>
       </c>
       <c r="F184" s="12" t="n">
-        <v>191.3</v>
+        <v>190.18</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>187.31</v>
+        <v>187</v>
       </c>
       <c r="H184" s="12" t="n">
-        <v>187.8</v>
+        <v>188.3</v>
       </c>
       <c r="I184" s="12" t="n">
-        <v>-1.77</v>
+        <v>0.5</v>
       </c>
       <c r="J184" s="13" t="n">
-        <v>-0.93</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="185">
@@ -7038,7 +7038,7 @@
       <c r="I185" s="9" t="n">
         <v/>
       </c>
-      <c r="J185" s="13" t="n">
+      <c r="J185" s="10" t="n">
         <v/>
       </c>
     </row>
@@ -7055,25 +7055,25 @@
         <v>700</v>
       </c>
       <c r="D186" s="12" t="n">
-        <v>930.65</v>
+        <v>939.25</v>
       </c>
       <c r="E186" s="12" t="n">
-        <v>928.6</v>
+        <v>968</v>
       </c>
       <c r="F186" s="12" t="n">
-        <v>944.15</v>
+        <v>997</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>925.1</v>
+        <v>961.1</v>
       </c>
       <c r="H186" s="12" t="n">
-        <v>939.25</v>
+        <v>991.7</v>
       </c>
       <c r="I186" s="12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J186" s="10" t="n">
-        <v>0.92</v>
+        <v>52.45</v>
+      </c>
+      <c r="J186" s="13" t="n">
+        <v>5.58</v>
       </c>
     </row>
   </sheetData>
@@ -7102,7 +7102,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE Index F&amp;O Lot Sizes  |  13-May-2026 03:42 PM</t>
+          <t>NSE Index F&amp;O Lot Sizes  |  14-May-2026 03:18 PM</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13-May-2026 03:42 PM</t>
+          <t>14-May-2026 03:18 PM</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/data/nfo_lot_sizes.xlsx
+++ b/data/nfo_lot_sizes.xlsx
@@ -575,7 +575,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE NFO Snapshot  |  Updated: 14-May-2026 03:18 PM</t>
+          <t>NSE NFO Snapshot  |  Updated: 15-May-2026 03:13 PM</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>14-May-2026 03:18 PM</t>
+          <t>15-May-2026 03:13 PM</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  14-May-2026 03:18 PM</t>
+          <t>NSE F&amp;O Stocks — Lot Size &amp; OHLC  |  15-May-2026 03:13 PM</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
         <v>1200</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>468.55</v>
+        <v>468</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>469.05</v>
+        <v>468</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>472.55</v>
+        <v>470</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>458.25</v>
+        <v>463.4</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>468</v>
+        <v>466.25</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>-0.55</v>
+        <v>-1.75</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>-0.12</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="4">
@@ -867,25 +867,25 @@
         <v>250</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>6305</v>
+        <v>6429</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>6350</v>
+        <v>6425</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>6439</v>
+        <v>6433.5</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>6220</v>
+        <v>6307</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>6429</v>
+        <v>6381</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>124</v>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>1.97</v>
+        <v>-48</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="5">
@@ -901,25 +901,25 @@
         <v>40</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>27280</v>
+        <v>27520</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>27590</v>
+        <v>27700</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>27610</v>
+        <v>28100</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>27270</v>
+        <v>27505</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>27520</v>
+        <v>27940</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>0.88</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="6">
@@ -935,25 +935,25 @@
         <v>3200</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>344.3</v>
+        <v>349.65</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>346.35</v>
+        <v>349.65</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>353.85</v>
+        <v>363.35</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>345.1</v>
+        <v>346.25</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>349.65</v>
+        <v>357.15</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>5.35</v>
+        <v>7.5</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="7">
@@ -969,25 +969,25 @@
         <v>2800</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>63.59</v>
+        <v>63.48</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>64</v>
+        <v>63.97</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>64.48999999999999</v>
+        <v>63.97</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>62.78</v>
+        <v>62.51</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>63.48</v>
+        <v>62.66</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>-0.11</v>
+        <v>-0.82</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>-0.17</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="8">
@@ -1003,25 +1003,25 @@
         <v>500</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1366.4</v>
+        <v>1378.2</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1369.8</v>
+        <v>1386</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>1387.5</v>
+        <v>1398.8</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1357.2</v>
+        <v>1356.4</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>1378.2</v>
+        <v>1362.8</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J8" s="13" t="n">
-        <v>0.86</v>
+        <v>-15.4</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="9">
@@ -1037,25 +1037,25 @@
         <v>875</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2498</v>
+        <v>2712.9</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2530.1</v>
+        <v>2781.1</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2720</v>
+        <v>2803.1</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>2530</v>
+        <v>2661</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>2712.9</v>
+        <v>2716</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>214.9</v>
+        <v>3.1</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>8.6</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="10">
@@ -1071,25 +1071,25 @@
         <v>1250</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>1737.8</v>
+        <v>1773.4</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>1761</v>
+        <v>1796.8</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>1782.5</v>
+        <v>1823.9</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1745.4</v>
+        <v>1766.2</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>1773.4</v>
+        <v>1795.1</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>35.6</v>
+        <v>21.7</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="11">
@@ -1105,25 +1105,25 @@
         <v>200</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5462.5</v>
+        <v>5576.5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5540</v>
+        <v>5628</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>5629.5</v>
+        <v>5638.5</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5462.5</v>
+        <v>5465</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>5576.5</v>
+        <v>5486</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>114</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>2.09</v>
+        <v>-90.5</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="12">
@@ -1139,25 +1139,25 @@
         <v>2000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>438.4</v>
+        <v>443.9</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>438.9</v>
+        <v>449</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>447.15</v>
+        <v>451.55</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>433.25</v>
+        <v>431.4</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>443.9</v>
+        <v>433.75</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>1.25</v>
+        <v>-10.15</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="13">
@@ -1173,25 +1173,25 @@
         <v>300</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>298.15</v>
+        <v>303.7</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>300.3</v>
+        <v>305.3</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>306.3</v>
+        <v>311.55</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>290.8</v>
+        <v>303.15</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>303.7</v>
+        <v>306.85</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>5.55</v>
+        <v>3.15</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="14">
@@ -1207,25 +1207,25 @@
         <v>750</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1891.1</v>
+        <v>1890.1</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>1910</v>
+        <v>1893</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1912.7</v>
+        <v>1900.6</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1840.3</v>
+        <v>1870.6</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>1890.1</v>
+        <v>1890.2</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>-0.05</v>
+        <v>0.1</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="15">
@@ -1241,25 +1241,25 @@
         <v>125</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>8004.5</v>
+        <v>8119</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8011</v>
+        <v>8170</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8180</v>
+        <v>8170</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>8011</v>
+        <v>8028.5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>8119</v>
+        <v>8082.5</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>114.5</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>1.43</v>
+        <v>-36.5</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="16">
@@ -1275,25 +1275,25 @@
         <v>2700</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>396.45</v>
+        <v>401.8</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>398.8</v>
+        <v>421</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>404.15</v>
+        <v>428.75</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>396.15</v>
+        <v>392</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>401.8</v>
+        <v>394.5</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="J16" s="13" t="n">
-        <v>1.35</v>
+        <v>-7.3</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="17">
@@ -1309,25 +1309,25 @@
         <v>5500</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>153.21</v>
+        <v>154.34</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>154.09</v>
+        <v>154.6</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>155.38</v>
+        <v>157.35</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>149.89</v>
+        <v>152.12</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>154.34</v>
+        <v>153.13</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>0.74</v>
+        <v>-1.21</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="18">
@@ -1343,25 +1343,25 @@
         <v>200</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2617.6</v>
+        <v>2622.2</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>2620</v>
+        <v>2622.2</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>2665.7</v>
+        <v>2640</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2610</v>
+        <v>2592.8</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>2622.2</v>
+        <v>2605.6</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <v>0.18</v>
+        <v>-16.6</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="19">
@@ -1377,25 +1377,25 @@
         <v>400</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1544</v>
+        <v>1561.3</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>1544.1</v>
+        <v>1568.7</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1568.3</v>
+        <v>1588</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>1526.4</v>
+        <v>1547.1</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>1561.3</v>
+        <v>1550.8</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="J19" s="13" t="n">
-        <v>1.12</v>
+        <v>-10.5</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="20">
@@ -1411,25 +1411,25 @@
         <v>750</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>606.5</v>
+        <v>612.6</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>608</v>
+        <v>645</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>618.5</v>
+        <v>657.75</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>602</v>
+        <v>606.3</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>612.6</v>
+        <v>616.25</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>6.1</v>
+        <v>3.65</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>1.01</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21">
@@ -1445,25 +1445,25 @@
         <v>125</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>6988</v>
+        <v>6970</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6990</v>
+        <v>6976</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7099</v>
+        <v>7140</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6953.5</v>
+        <v>6976</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6970</v>
+        <v>7100</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>-18</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>-0.26</v>
+        <v>130</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <v>1.87</v>
       </c>
     </row>
     <row r="22">
@@ -1479,25 +1479,25 @@
         <v>1000</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>994.8</v>
+        <v>1004.7</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>1000.9</v>
+        <v>1009.9</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>1007.5</v>
+        <v>1009.9</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>990.6</v>
+        <v>976.2</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>1004.7</v>
+        <v>990.5</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J22" s="13" t="n">
-        <v>1</v>
+        <v>-14.2</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="23">
@@ -1513,25 +1513,25 @@
         <v>650</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1497.5</v>
+        <v>1510.9</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>1504.4</v>
+        <v>1519</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1525.9</v>
+        <v>1528</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1497</v>
+        <v>1503.3</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1510.9</v>
+        <v>1511.8</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>13.4</v>
+        <v>0.9</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>0.89</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="24">
@@ -1547,25 +1547,25 @@
         <v>625</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>1255.7</v>
+        <v>1254.6</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>1256.6</v>
+        <v>1259.6</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>1269</v>
+        <v>1263.4</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1235.8</v>
+        <v>1242</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1254.6</v>
+        <v>1244.8</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-1.1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>-0.09</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="25">
@@ -1581,25 +1581,25 @@
         <v>250</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>10262</v>
+        <v>10451</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>10380</v>
+        <v>10500</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10517</v>
+        <v>10540.5</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10251.5</v>
+        <v>10296</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>10451</v>
+        <v>10377.5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>189</v>
-      </c>
-      <c r="J25" s="13" t="n">
-        <v>1.84</v>
+        <v>-73.5</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="26">
@@ -1615,25 +1615,25 @@
         <v>500</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1728.9</v>
+        <v>1740.2</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>1735.1</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>1743</v>
+        <v>1755.8</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1713.3</v>
+        <v>1721.9</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1740.2</v>
+        <v>1728.1</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J26" s="13" t="n">
-        <v>0.65</v>
+        <v>-12.1</v>
+      </c>
+      <c r="J26" s="10" t="n">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="27">
@@ -1649,25 +1649,25 @@
         <v>125</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>896.15</v>
+        <v>912.15</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>902.9</v>
+        <v>913</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>915</v>
+        <v>921.6</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>889</v>
+        <v>907.35</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>912.15</v>
+        <v>910.45</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="J27" s="13" t="n">
-        <v>1.79</v>
+        <v>-1.7</v>
+      </c>
+      <c r="J27" s="10" t="n">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>400</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2105.1</v>
+        <v>2191.1</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>2120</v>
+        <v>2192.8</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>2197.1</v>
+        <v>2209.1</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2120</v>
+        <v>2132</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>2191.1</v>
+        <v>2148.3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="J28" s="13" t="n">
-        <v>4.09</v>
+        <v>-42.8</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="29">
@@ -1717,25 +1717,25 @@
         <v>1600</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>548.9</v>
+        <v>540.7</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>543.95</v>
+        <v>537</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>548</v>
+        <v>549.8</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>517.75</v>
+        <v>532.65</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>540.7</v>
+        <v>539.6</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-8.199999999999999</v>
+        <v>-1.1</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>-1.49</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="30">
@@ -1751,25 +1751,25 @@
         <v>3600</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>194.88</v>
+        <v>199.04</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>196</v>
+        <v>199.04</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>200.85</v>
+        <v>200.19</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>194.59</v>
+        <v>194.01</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>199.04</v>
+        <v>194.46</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="J30" s="13" t="n">
-        <v>2.13</v>
+        <v>-4.58</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="31">
@@ -1785,25 +1785,25 @@
         <v>5850</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>261.65</v>
+        <v>267.8</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>263.8</v>
+        <v>268</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>270.1</v>
+        <v>270.25</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>262.65</v>
+        <v>260.75</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>267.8</v>
+        <v>261.4</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="J31" s="13" t="n">
-        <v>2.35</v>
+        <v>-6.4</v>
+      </c>
+      <c r="J31" s="10" t="n">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="32">
@@ -1819,25 +1819,25 @@
         <v>3750</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>428.25</v>
+        <v>428.85</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>431</v>
+        <v>428.85</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>435.15</v>
+        <v>429.5</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>424.45</v>
+        <v>422.2</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>428.85</v>
+        <v>423.65</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>0.14</v>
+        <v>-5.2</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="33">
@@ -1853,25 +1853,25 @@
         <v>1100</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>507.7</v>
+        <v>533.9</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>514.95</v>
+        <v>534</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>540.35</v>
+        <v>536.2</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>512</v>
+        <v>528.1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>533.9</v>
+        <v>533.45</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="J33" s="13" t="n">
-        <v>5.16</v>
+        <v>-0.45</v>
+      </c>
+      <c r="J33" s="10" t="n">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="34">
@@ -1887,25 +1887,25 @@
         <v>500</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1789.2</v>
+        <v>1883.5</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1820</v>
+        <v>1883.2</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>1889.2</v>
+        <v>1922.9</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1797.3</v>
+        <v>1880.4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1883.5</v>
+        <v>1905.4</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>94.3</v>
+        <v>21.9</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>5.27</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="35">
@@ -1921,25 +1921,25 @@
         <v>10500</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>403.85</v>
+        <v>413.15</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>407.2</v>
+        <v>414.8</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>417.9</v>
+        <v>415.65</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>402.05</v>
+        <v>397</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>413.15</v>
+        <v>398.3</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J35" s="13" t="n">
-        <v>2.3</v>
+        <v>-14.85</v>
+      </c>
+      <c r="J35" s="10" t="n">
+        <v>-3.59</v>
       </c>
     </row>
     <row r="36">
@@ -1955,25 +1955,25 @@
   